--- a/Xpost_df_comments.xlsx
+++ b/Xpost_df_comments.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P114"/>
+  <dimension ref="A1:P107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,42 +511,42 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://x.com/Rita09729643/status/2037955706662604958</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2037936526093430909</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2037955706662604958</t>
+          <t>2037936526093430909</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2037895388909142325</t>
+          <t>2037801868244533349</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037895388909142325</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2037801868244533349</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Get guaranteed vouchers worth of AED750
-Apply for Emirates NBD noon One Visa Credit Card and receive a guaranteed Majid Al Futtaim voucher worth AED 750.
-https://t.co/Rj1kVb2Rck https://t.co/MQajcVjmt6</t>
+          <t>What’s more suspicious?
+Stay Safe, Stay Vigilant. #UnitedAgainstFraud
+https://t.co/YpRWtBZrhq</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1774707097000</v>
+        <v>1774684800000</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2037895388909142325</t>
+          <t>2037801868244533349</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEgPDX9WsAEtE9T.jpg', 'type': 'photo', 'id': '2037895382030528513'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -561,14 +561,14 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>641</t>
+          <t>506</t>
         </is>
       </c>
       <c r="P2" t="inlineStr"/>
@@ -579,35 +579,35 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://x.com/Rita09729643/status/2037955706662604958</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2037936526093430909</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2037955706662604958</t>
+          <t>2037936526093430909</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2037955706662604958</t>
+          <t>2037911596106715381</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://x.com/Rita09729643/status/2037955706662604958</t>
+          <t>https://x.com/cruizomfs/status/2037911596106715381</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Hi I have a credit card of Emirates NBD, but I haven’t used it for many years, suddenly I received the email of statement that I need to pay 764.13AED as the total payment due, this is really unacceptable.</t>
+          <t>@EmiratesNBD_AE Hello. Do I need a residency in order to open an account?</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1774721478000</v>
+        <v>1774710961000</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2037895388909142325</t>
+          <t>2037801868244533349</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -617,14 +617,14 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>{'name': 'Rita', 'screenName': 'Rita09729643', 'followersCount': 2, 'favouritesCount': 51, 'friendsCount': 24, 'description': 'Hi'}</t>
+          <t>{'name': 'Los 🥚 De Donald Trump 🇺🇸', 'screenName': 'cruizomfs', 'followersCount': 456, 'favouritesCount': 14498, 'friendsCount': 1923, 'description': 'libre.'}</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -634,12 +634,12 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2037895388909142325</t>
+          <t>2037801868244533349</t>
         </is>
       </c>
     </row>
@@ -649,163 +649,25 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://x.com/cruizomfs/status/2037928218003382573</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2037936526093430909</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2037928218003382573</t>
+          <t>2037936526093430909</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2037801868244533349</t>
+          <t>2037921044221010067</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037801868244533349</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2037921044221010067</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
-        <is>
-          <t>What’s more suspicious?
-Stay Safe, Stay Vigilant. #UnitedAgainstFraud
-https://t.co/YpRWtBZrhq</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>1774684800000</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>2037801868244533349</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>3</v>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>497</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>https://x.com/cruizomfs/status/2037928218003382573</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>2037928218003382573</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2037911596106715381</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>https://x.com/cruizomfs/status/2037911596106715381</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE Hello. Do I need a residency in order to open an account?</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>1774710961000</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>2037801868244533349</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>{'name': 'Los 🥚 De Donald Trump 🇺🇸', 'screenName': 'cruizomfs', 'followersCount': 456, 'favouritesCount': 14453, 'friendsCount': 1923, 'description': 'libre.'}</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2037801868244533349</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>https://x.com/cruizomfs/status/2037928218003382573</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>2037928218003382573</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2037921044221010067</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037921044221010067</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
         <is>
           <t>Hi, thank you for reaching out, please be informed that you can apply for non-resident account by a visit to one of our branches within the UAE.
 Documents:
@@ -826,8 +688,148 @@
 (Bill should not be more than 3 months old)</t>
         </is>
       </c>
+      <c r="G4" t="n">
+        <v>1774713214000</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2037801868244533349</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2037911596106715381</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2037936526093430909</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2037936526093430909</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2037928218003382573</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>https://x.com/cruizomfs/status/2037928218003382573</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE I just got back from the UAE, is there any chance I can start the process online. I'll probably go again in august.</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>1774714924000</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2037801868244533349</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>{'name': 'Los 🥚 De Donald Trump 🇺🇸', 'screenName': 'cruizomfs', 'followersCount': 456, 'favouritesCount': 14498, 'friendsCount': 1923, 'description': 'libre.'}</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2037921044221010067</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2037936526093430909</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2037936526093430909</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2037936526093430909</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2037936526093430909</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>@cruizomfs We regret to inform you that this process can be done only by a branch visit within the UAE.</t>
+        </is>
+      </c>
       <c r="G6" t="n">
-        <v>1774713214000</v>
+        <v>1774716905000</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -845,7 +847,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -858,12 +860,12 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>17</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2037911596106715381</t>
+          <t>2037928218003382573</t>
         </is>
       </c>
     </row>
@@ -873,69 +875,67 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://x.com/cruizomfs/status/2037928218003382573</t>
+          <t>https://x.com/Rita09729643/status/2037955706662604958</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2037928218003382573</t>
+          <t>2037955706662604958</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2037928218003382573</t>
+          <t>2037895388909142325</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://x.com/cruizomfs/status/2037928218003382573</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2037895388909142325</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE I just got back from the UAE, is there any chance I can start the process online. I'll probably go again in august.</t>
+          <t>Get guaranteed vouchers worth of AED750
+Apply for Emirates NBD noon One Visa Credit Card and receive a guaranteed Majid Al Futtaim voucher worth AED 750.
+https://t.co/Rj1kVb2Rck https://t.co/MQajcVjmt6</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1774714924000</v>
+        <v>1774707097000</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2037801868244533349</t>
+          <t>2037895388909142325</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEgPDX9WsAEtE9T.jpg', 'type': 'photo', 'id': '2037895382030528513'}]</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>{'name': 'Los 🥚 De Donald Trump 🇺🇸', 'screenName': 'cruizomfs', 'followersCount': 456, 'favouritesCount': 14453, 'friendsCount': 1923, 'description': 'libre.'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="K7" t="n">
+        <v>2</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
         <v>1</v>
       </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2037921044221010067</t>
-        </is>
-      </c>
+          <t>651</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -943,35 +943,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>https://x.com/cruizomfs/status/2037928218003382573</t>
+          <t>https://x.com/Rita09729643/status/2037955706662604958</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2037928218003382573</t>
+          <t>2037955706662604958</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2037936526093430909</t>
+          <t>2037955706662604958</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037936526093430909</t>
+          <t>https://x.com/Rita09729643/status/2037955706662604958</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>@cruizomfs We regret to inform you that this process can be done only by a branch visit within the UAE.</t>
+          <t>@EmiratesNBD_AE Hi I have a credit card of Emirates NBD, but I haven’t used it for many years, suddenly I received the email of statement that I need to pay 764.13AED as the total payment due, this is really unacceptable.</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1774716905000</v>
+        <v>1774721478000</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2037801868244533349</t>
+          <t>2037895388909142325</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -981,29 +981,29 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Rita', 'screenName': 'Rita09729643', 'followersCount': 2, 'favouritesCount': 51, 'friendsCount': 24, 'description': 'Hi'}</t>
         </is>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2037928218003382573</t>
+          <t>2037895388909142325</t>
         </is>
       </c>
     </row>
@@ -1013,12 +1013,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037936526093430909</t>
+          <t>https://x.com/cruizomfs/status/2037928218003382573</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2037936526093430909</t>
+          <t>2037928218003382573</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1070,7 +1070,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>497</t>
+          <t>506</t>
         </is>
       </c>
       <c r="P9" t="inlineStr"/>
@@ -1081,12 +1081,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037936526093430909</t>
+          <t>https://x.com/cruizomfs/status/2037928218003382573</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2037936526093430909</t>
+          <t>2037928218003382573</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>{'name': 'Los 🥚 De Donald Trump 🇺🇸', 'screenName': 'cruizomfs', 'followersCount': 456, 'favouritesCount': 14453, 'friendsCount': 1923, 'description': 'libre.'}</t>
+          <t>{'name': 'Los 🥚 De Donald Trump 🇺🇸', 'screenName': 'cruizomfs', 'followersCount': 456, 'favouritesCount': 14498, 'friendsCount': 1923, 'description': 'libre.'}</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1151,12 +1151,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037936526093430909</t>
+          <t>https://x.com/cruizomfs/status/2037928218003382573</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2037936526093430909</t>
+          <t>2037928218003382573</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037936526093430909</t>
+          <t>https://x.com/cruizomfs/status/2037928218003382573</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2037936526093430909</t>
+          <t>2037928218003382573</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>{'name': 'Los 🥚 De Donald Trump 🇺🇸', 'screenName': 'cruizomfs', 'followersCount': 456, 'favouritesCount': 14453, 'friendsCount': 1923, 'description': 'libre.'}</t>
+          <t>{'name': 'Los 🥚 De Donald Trump 🇺🇸', 'screenName': 'cruizomfs', 'followersCount': 456, 'favouritesCount': 14498, 'friendsCount': 1923, 'description': 'libre.'}</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1307,12 +1307,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037936526093430909</t>
+          <t>https://x.com/cruizomfs/status/2037928218003382573</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2037936526093430909</t>
+          <t>2037928218003382573</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1377,12 +1377,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037921044221010067</t>
+          <t>https://x.com/cruizomfs/status/2037911596106715381</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2037921044221010067</t>
+          <t>2037911596106715381</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>497</t>
+          <t>506</t>
         </is>
       </c>
       <c r="P14" t="inlineStr"/>
@@ -1445,12 +1445,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037921044221010067</t>
+          <t>https://x.com/cruizomfs/status/2037911596106715381</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2037921044221010067</t>
+          <t>2037911596106715381</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -1515,12 +1515,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037921044221010067</t>
+          <t>https://x.com/cruizomfs/status/2037911596106715381</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2037921044221010067</t>
+          <t>2037911596106715381</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -1611,21 +1611,23 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2037928218003382573</t>
+          <t>2037801868244533349</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://x.com/cruizomfs/status/2037928218003382573</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2037801868244533349</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE I just got back from the UAE, is there any chance I can start the process online. I'll probably go again in august.</t>
+          <t>What’s more suspicious?
+Stay Safe, Stay Vigilant. #UnitedAgainstFraud
+https://t.co/YpRWtBZrhq</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1774714924000</v>
+        <v>1774684800000</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1639,11 +1641,11 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>{'name': 'Los 🥚 De Donald Trump 🇺🇸', 'screenName': 'cruizomfs', 'followersCount': 456, 'favouritesCount': 14453, 'friendsCount': 1923, 'description': 'libre.'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -1652,18 +1654,14 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>2037921044221010067</t>
-        </is>
-      </c>
+          <t>506</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
@@ -1671,67 +1669,69 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2037921044221010067</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2037921044221010067</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2037911596106715381</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>https://x.com/cruizomfs/status/2037911596106715381</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>2037911596106715381</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE Hello. Do I need a residency in order to open an account?</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>1774710961000</v>
+      </c>
+      <c r="H18" t="inlineStr">
         <is>
           <t>2037801868244533349</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037801868244533349</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>What’s more suspicious?
-Stay Safe, Stay Vigilant. #UnitedAgainstFraud
-https://t.co/YpRWtBZrhq</t>
-        </is>
-      </c>
-      <c r="G18" t="n">
-        <v>1774684800000</v>
-      </c>
-      <c r="H18" t="inlineStr">
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>{'name': 'Los 🥚 De Donald Trump 🇺🇸', 'screenName': 'cruizomfs', 'followersCount': 456, 'favouritesCount': 14498, 'friendsCount': 1923, 'description': 'libre.'}</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
         <is>
           <t>2037801868244533349</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="K18" t="n">
-        <v>2</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>3</v>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>497</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
@@ -1739,95 +1739,25 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>https://x.com/cruizomfs/status/2037911596106715381</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2037921044221010067</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2037911596106715381</t>
+          <t>2037921044221010067</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2037911596106715381</t>
+          <t>2037921044221010067</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://x.com/cruizomfs/status/2037911596106715381</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2037921044221010067</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE Hello. Do I need a residency in order to open an account?</t>
-        </is>
-      </c>
-      <c r="G19" t="n">
-        <v>1774710961000</v>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>2037801868244533349</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>{'name': 'Los 🥚 De Donald Trump 🇺🇸', 'screenName': 'cruizomfs', 'followersCount': 456, 'favouritesCount': 14453, 'friendsCount': 1923, 'description': 'libre.'}</t>
-        </is>
-      </c>
-      <c r="K19" t="n">
-        <v>1</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>2037801868244533349</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>https://x.com/cruizomfs/status/2037911596106715381</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>2037911596106715381</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>2037921044221010067</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037921044221010067</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
         <is>
           <t>Hi, thank you for reaching out, please be informed that you can apply for non-resident account by a visit to one of our branches within the UAE.
 Documents:
@@ -1848,8 +1778,78 @@
 (Bill should not be more than 3 months old)</t>
         </is>
       </c>
+      <c r="G19" t="n">
+        <v>1774713214000</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>2037801868244533349</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>2037911596106715381</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2037921044221010067</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2037921044221010067</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2037928218003382573</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>https://x.com/cruizomfs/status/2037928218003382573</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE I just got back from the UAE, is there any chance I can start the process online. I'll probably go again in august.</t>
+        </is>
+      </c>
       <c r="G20" t="n">
-        <v>1774713214000</v>
+        <v>1774714924000</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Los 🥚 De Donald Trump 🇺🇸', 'screenName': 'cruizomfs', 'followersCount': 456, 'favouritesCount': 14498, 'friendsCount': 1923, 'description': 'libre.'}</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -1876,16 +1876,16 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2037911596106715381</t>
+          <t>2037921044221010067</t>
         </is>
       </c>
     </row>
@@ -1895,62 +1895,64 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>https://x.com/rated_sm/status/2037867679802122593</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2037895388909142325</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2037867679802122593</t>
+          <t>2037895388909142325</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2037865010320539854</t>
+          <t>2037895388909142325</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://x.com/rated_sm/status/2037865010320539854</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2037895388909142325</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE My phone is broken and is pending repair with Apple. I need to make a payment and I logged into the website using OTP, but when attempting payment, its still asking for Smart Pass confirmation and no OTP option. Same when attempting to contact Whatsapp Support.</t>
+          <t>Get guaranteed vouchers worth of AED750
+Apply for Emirates NBD noon One Visa Credit Card and receive a guaranteed Majid Al Futtaim voucher worth AED 750.
+https://t.co/Rj1kVb2Rck https://t.co/MQajcVjmt6</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>1774699854000</v>
+        <v>1774707097000</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2037865010320539854</t>
+          <t>2037895388909142325</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEgPDX9WsAEtE9T.jpg', 'type': 'photo', 'id': '2037895382030528513'}]</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>{'name': 'rated_sm', 'screenName': 'rated_sm', 'followersCount': 42, 'favouritesCount': 119, 'friendsCount': 122, 'description': ''}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="K21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
         <v>1</v>
       </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>652</t>
         </is>
       </c>
       <c r="P21" t="inlineStr"/>
@@ -1961,257 +1963,251 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2037895388909142325</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2037895388909142325</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2037955706662604958</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>https://x.com/Rita09729643/status/2037955706662604958</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE Hi I have a credit card of Emirates NBD, but I haven’t used it for many years, suddenly I received the email of statement that I need to pay 764.13AED as the total payment due, this is really unacceptable.</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>1774721478000</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>2037895388909142325</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>{'name': 'Rita', 'screenName': 'Rita09729643', 'followersCount': 2, 'favouritesCount': 51, 'friendsCount': 24, 'description': 'Hi'}</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>2037895388909142325</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2037895388909142325</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2037895388909142325</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2037801868244533349</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2037801868244533349</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>What’s more suspicious?
+Stay Safe, Stay Vigilant. #UnitedAgainstFraud
+https://t.co/YpRWtBZrhq</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>1774684800000</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>2037801868244533349</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>2</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>3</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>506</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
           <t>https://x.com/rated_sm/status/2037867679802122593</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>2037867679802122593</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2037865010320539854</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>https://x.com/rated_sm/status/2037865010320539854</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE My phone is broken and is pending repair with Apple. I need to make a payment and I logged into the website using OTP, but when attempting payment, its still asking for Smart Pass confirmation and no OTP option. Same when attempting to contact Whatsapp Support.</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>1774699854000</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>2037865010320539854</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>{'name': 'rated_sm', 'screenName': 'rated_sm', 'followersCount': 42, 'favouritesCount': 119, 'friendsCount': 122, 'description': ''}</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>1</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>https://x.com/rated_sm/status/2037867679802122593</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2037867679802122593</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
         <is>
           <t>2037866970410811411</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE/status/2037866970410811411</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>@rated_sm We sincerely regret for the inconvenience To be able to assist further, we kindly request you to reach out to us at 
 social@emiratesnbd.com
 Quoting case #989891 in the subject line of the email from your registered email address We will make every effort to address the matter</t>
         </is>
       </c>
-      <c r="G22" t="n">
+      <c r="G25" t="n">
         <v>1774700322000</v>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>2037865010320539854</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="K22" t="n">
-        <v>1</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>2037865010320539854</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>https://x.com/rated_sm/status/2037867679802122593</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>2037867679802122593</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>2037867679802122593</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>https://x.com/rated_sm/status/2037867679802122593</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE I was hoping for a more immediate support and solution cause inability to make this payment will cause me to incur a large overlimit fee.</t>
-        </is>
-      </c>
-      <c r="G23" t="n">
-        <v>1774700491000</v>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>2037865010320539854</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>{'name': 'rated_sm', 'screenName': 'rated_sm', 'followersCount': 42, 'favouritesCount': 119, 'friendsCount': 122, 'description': ''}</t>
-        </is>
-      </c>
-      <c r="K23" t="n">
-        <v>1</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>2037866970410811411</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>https://x.com/rated_sm/status/2037867679802122593</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>2037867679802122593</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>2037873211728081164</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037873211728081164</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>@rated_sm Please note that we don't have access to your profile from this channel due to security reasons, so kindly share the details through email, so we can check accordingly</t>
-        </is>
-      </c>
-      <c r="G24" t="n">
-        <v>1774701810000</v>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>2037865010320539854</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>2037867679802122593</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037873211728081164</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>2037873211728081164</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>2037865010320539854</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>https://x.com/rated_sm/status/2037865010320539854</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE My phone is broken and is pending repair with Apple. I need to make a payment and I logged into the website using OTP, but when attempting payment, its still asking for Smart Pass confirmation and no OTP option. Same when attempting to contact Whatsapp Support.</t>
-        </is>
-      </c>
-      <c r="G25" t="n">
-        <v>1774699854000</v>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>2037865010320539854</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>{'name': 'rated_sm', 'screenName': 'rated_sm', 'followersCount': 42, 'favouritesCount': 119, 'friendsCount': 122, 'description': ''}</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -2228,10 +2224,14 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>2037865010320539854</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
@@ -2239,279 +2239,277 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
+          <t>https://x.com/rated_sm/status/2037867679802122593</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2037867679802122593</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2037867679802122593</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>https://x.com/rated_sm/status/2037867679802122593</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE I was hoping for a more immediate support and solution cause inability to make this payment will cause me to incur a large overlimit fee.</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>1774700491000</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>2037865010320539854</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>{'name': 'rated_sm', 'screenName': 'rated_sm', 'followersCount': 42, 'favouritesCount': 119, 'friendsCount': 122, 'description': ''}</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>1</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>2037866970410811411</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>https://x.com/rated_sm/status/2037867679802122593</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2037867679802122593</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2037873211728081164</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>https://x.com/EmiratesNBD_AE/status/2037873211728081164</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>@rated_sm Please note that we don't have access to your profile from this channel due to security reasons, so kindly share the details through email, so we can check accordingly</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>1774701810000</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>2037865010320539854</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>2037867679802122593</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2037873211728081164</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
         <is>
           <t>2037873211728081164</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2037865010320539854</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>https://x.com/rated_sm/status/2037865010320539854</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE My phone is broken and is pending repair with Apple. I need to make a payment and I logged into the website using OTP, but when attempting payment, its still asking for Smart Pass confirmation and no OTP option. Same when attempting to contact Whatsapp Support.</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>1774699854000</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>2037865010320539854</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>{'name': 'rated_sm', 'screenName': 'rated_sm', 'followersCount': 42, 'favouritesCount': 119, 'friendsCount': 122, 'description': ''}</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>1</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2037873211728081164</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2037873211728081164</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
         <is>
           <t>2037866970410811411</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE/status/2037866970410811411</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>@rated_sm We sincerely regret for the inconvenience To be able to assist further, we kindly request you to reach out to us at 
 social@emiratesnbd.com
 Quoting case #989891 in the subject line of the email from your registered email address We will make every effort to address the matter</t>
         </is>
       </c>
-      <c r="G26" t="n">
+      <c r="G29" t="n">
         <v>1774700322000</v>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>2037865010320539854</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
-      <c r="K26" t="n">
+      <c r="K29" t="n">
         <v>1</v>
       </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
         <is>
           <t>2037865010320539854</t>
         </is>
       </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037873211728081164</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>2037873211728081164</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>2037867679802122593</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>https://x.com/rated_sm/status/2037867679802122593</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE I was hoping for a more immediate support and solution cause inability to make this payment will cause me to incur a large overlimit fee.</t>
-        </is>
-      </c>
-      <c r="G27" t="n">
-        <v>1774700491000</v>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>2037865010320539854</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>{'name': 'rated_sm', 'screenName': 'rated_sm', 'followersCount': 42, 'favouritesCount': 119, 'friendsCount': 122, 'description': ''}</t>
-        </is>
-      </c>
-      <c r="K27" t="n">
-        <v>1</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>2037866970410811411</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037873211728081164</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>2037873211728081164</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>2037873211728081164</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037873211728081164</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>@rated_sm Please note that we don't have access to your profile from this channel due to security reasons, so kindly share the details through email, so we can check accordingly</t>
-        </is>
-      </c>
-      <c r="G28" t="n">
-        <v>1774701810000</v>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>2037865010320539854</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>2037867679802122593</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037895388909142325</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>2037895388909142325</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>2037895388909142325</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037895388909142325</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Get guaranteed vouchers worth of AED750
-Apply for Emirates NBD noon One Visa Credit Card and receive a guaranteed Majid Al Futtaim voucher worth AED 750.
-https://t.co/Rj1kVb2Rck https://t.co/MQajcVjmt6</t>
-        </is>
-      </c>
-      <c r="G29" t="n">
-        <v>1774707097000</v>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>2037895388909142325</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEgPDX9WsAEtE9T.jpg', 'type': 'photo', 'id': '2037895382030528513'}]</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="K29" t="n">
-        <v>2</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>1</v>
-      </c>
-      <c r="N29" t="n">
-        <v>2</v>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>642</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
@@ -2519,35 +2517,35 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037895388909142325</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2037873211728081164</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2037895388909142325</t>
+          <t>2037873211728081164</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2037955706662604958</t>
+          <t>2037867679802122593</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://x.com/Rita09729643/status/2037955706662604958</t>
+          <t>https://x.com/rated_sm/status/2037867679802122593</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Hi I have a credit card of Emirates NBD, but I haven’t used it for many years, suddenly I received the email of statement that I need to pay 764.13AED as the total payment due, this is really unacceptable.</t>
+          <t>@EmiratesNBD_AE I was hoping for a more immediate support and solution cause inability to make this payment will cause me to incur a large overlimit fee.</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>1774721478000</v>
+        <v>1774700491000</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2037895388909142325</t>
+          <t>2037865010320539854</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2557,14 +2555,14 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>{'name': 'Rita', 'screenName': 'Rita09729643', 'followersCount': 2, 'favouritesCount': 51, 'friendsCount': 24, 'description': 'Hi'}</t>
+          <t>{'name': 'rated_sm', 'screenName': 'rated_sm', 'followersCount': 42, 'favouritesCount': 119, 'friendsCount': 122, 'description': ''}</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -2574,12 +2572,12 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2037895388909142325</t>
+          <t>2037866970410811411</t>
         </is>
       </c>
     </row>
@@ -2589,37 +2587,35 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037895388909142325</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2037873211728081164</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2037895388909142325</t>
+          <t>2037873211728081164</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2037801868244533349</t>
+          <t>2037873211728081164</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037801868244533349</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2037873211728081164</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>What’s more suspicious?
-Stay Safe, Stay Vigilant. #UnitedAgainstFraud
-https://t.co/YpRWtBZrhq</t>
+          <t>@rated_sm Please note that we don't have access to your profile from this channel due to security reasons, so kindly share the details through email, so we can check accordingly</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>1774684800000</v>
+        <v>1774701810000</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2037801868244533349</t>
+          <t>2037865010320539854</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2633,7 +2629,7 @@
         </is>
       </c>
       <c r="K31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -2642,14 +2638,18 @@
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>497</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>2037867679802122593</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="P32" t="inlineStr"/>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -2850,7 +2850,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="P35" t="inlineStr"/>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -3003,50 +3003,49 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2037827252075839770</t>
+          <t>https://x.com/eazyislit/status/2037804608517509572</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2037827252075839770</t>
+          <t>2037804608517509572</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2037818020597215557</t>
+          <t>2037804608517509572</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://x.com/Talal_Hus/status/2037818020597215557</t>
+          <t>https://x.com/eazyislit/status/2037804608517509572</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA بالنسبة للتقسيط بدون هامش ربح هل لو سددت من خلال الفيزا ابل باي اقدر استفيد من العرض ؟ 
-يعني ععندب في نون اشتري ابل باي وبعدها اقسطها ؟</t>
+          <t>THE WOMAN DAT CARRIED YOU FOR 9 MONTHS MAY SHE LIVE LONG AND WITNESS YOU SUCCEED 🤍 https://t.co/0XDJyqkART</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>1774688651000</v>
+        <v>1774685453000</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2037818020597215557</t>
+          <t>2037804608517509572</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/tweet_video_thumb/HEe8fFcXcAAIJKZ.jpg', 'type': 'animated_gif', 'id': '2037804598631559168'}]</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>{'name': 'T.A', 'screenName': 'Talal_Hus', 'followersCount': 57, 'favouritesCount': 741, 'friendsCount': 983, 'description': '👷🏻\u200d♂️⏳🏗 ——— ✈️'}</t>
+          <t>{'name': 'Dat Dark Rich Dude 💎🇳🇬🇬🇧', 'screenName': 'eazyislit', 'followersCount': 66, 'favouritesCount': 752, 'friendsCount': 238, 'description': 'Best in Maintaining Maximum 🕴🏽Composure 🥇🇺🇸🇳🇬 I Love Peace 🤍🛐Graphics Designer 👩\u200d🎤  A product of Grace 🕊️❤️✝️'}</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
@@ -3059,7 +3058,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P37" t="inlineStr"/>
@@ -3070,35 +3069,35 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2037827252075839770</t>
+          <t>https://x.com/eazyislit/status/2037804608517509572</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2037827252075839770</t>
+          <t>2037804608517509572</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2037827252075839770</t>
+          <t>2037855319393464474</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2037827252075839770</t>
+          <t>https://x.com/eazyislit/status/2037855319393464474</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>@Talal_Hus نعم يمكنك تقسيط المبلغ, لطلب التقسيط وتفاصيل أكثر قبل إجراء المعاملة يرجى الاتصال بنا على الرقم المجاني 8007547777</t>
+          <t>I claim it 🙏🏼🙏🏼🙏🏼</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>1774690852000</v>
+        <v>1774697544000</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2037818020597215557</t>
+          <t>2037855319393464474</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3108,7 +3107,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>{'name': 'EmiratesNBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17237, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
+          <t>{'name': 'Dat Dark Rich Dude 💎🇳🇬🇬🇧', 'screenName': 'eazyislit', 'followersCount': 66, 'favouritesCount': 752, 'friendsCount': 238, 'description': 'Best in Maintaining Maximum 🕴🏽Composure 🥇🇺🇸🇳🇬 I Love Peace 🤍🛐Graphics Designer 👩\u200d🎤  A product of Grace 🕊️❤️✝️'}</t>
         </is>
       </c>
       <c r="K38" t="n">
@@ -3125,14 +3124,10 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>2037818020597215557</t>
-        </is>
-      </c>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
@@ -3140,12 +3135,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>https://x.com/Talal_Hus/status/2037818020597215557</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2037827252075839770</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2037818020597215557</t>
+          <t>2037827252075839770</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -3196,7 +3191,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P39" t="inlineStr"/>
@@ -3207,12 +3202,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>https://x.com/Talal_Hus/status/2037818020597215557</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2037827252075839770</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2037818020597215557</t>
+          <t>2037827252075839770</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3262,7 +3257,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -3277,49 +3272,50 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>https://x.com/eazyislit/status/2037804608517509572</t>
+          <t>https://x.com/Talal_Hus/status/2037818020597215557</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2037804608517509572</t>
+          <t>2037818020597215557</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2037804608517509572</t>
+          <t>2037818020597215557</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://x.com/eazyislit/status/2037804608517509572</t>
+          <t>https://x.com/Talal_Hus/status/2037818020597215557</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>THE WOMAN DAT CARRIED YOU FOR 9 MONTHS MAY SHE LIVE LONG AND WITNESS YOU SUCCEED 🤍 https://t.co/0XDJyqkART</t>
+          <t>@EmiratesNBD_KSA بالنسبة للتقسيط بدون هامش ربح هل لو سددت من خلال الفيزا ابل باي اقدر استفيد من العرض ؟ 
+يعني ععندب في نون اشتري ابل باي وبعدها اقسطها ؟</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>1774685453000</v>
+        <v>1774688651000</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2037804608517509572</t>
+          <t>2037818020597215557</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/tweet_video_thumb/HEe8fFcXcAAIJKZ.jpg', 'type': 'animated_gif', 'id': '2037804598631559168'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>{'name': 'Dat Dark Rich Dude 💎🇳🇬🇬🇧', 'screenName': 'eazyislit', 'followersCount': 66, 'favouritesCount': 752, 'friendsCount': 238, 'description': 'Best in Maintaining Maximum 🕴🏽Composure 🥇🇺🇸🇳🇬 I Love Peace 🤍🛐Graphics Designer 👩\u200d🎤  A product of Grace 🕊️❤️✝️'}</t>
+          <t>{'name': 'T.A', 'screenName': 'Talal_Hus', 'followersCount': 57, 'favouritesCount': 741, 'friendsCount': 983, 'description': '👷🏻\u200d♂️⏳🏗 ——— ✈️'}</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -3332,7 +3328,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P41" t="inlineStr"/>
@@ -3343,35 +3339,35 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>https://x.com/eazyislit/status/2037804608517509572</t>
+          <t>https://x.com/Talal_Hus/status/2037818020597215557</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2037804608517509572</t>
+          <t>2037818020597215557</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2037855319393464474</t>
+          <t>2037827252075839770</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://x.com/eazyislit/status/2037855319393464474</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2037827252075839770</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>I claim it 🙏🏼🙏🏼🙏🏼</t>
+          <t>@Talal_Hus نعم يمكنك تقسيط المبلغ, لطلب التقسيط وتفاصيل أكثر قبل إجراء المعاملة يرجى الاتصال بنا على الرقم المجاني 8007547777</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>1774697544000</v>
+        <v>1774690852000</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2037855319393464474</t>
+          <t>2037818020597215557</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3381,7 +3377,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>{'name': 'Dat Dark Rich Dude 💎🇳🇬🇬🇧', 'screenName': 'eazyislit', 'followersCount': 66, 'favouritesCount': 752, 'friendsCount': 238, 'description': 'Best in Maintaining Maximum 🕴🏽Composure 🥇🇺🇸🇳🇬 I Love Peace 🤍🛐Graphics Designer 👩\u200d🎤  A product of Grace 🕊️❤️✝️'}</t>
+          <t>{'name': 'EmiratesNBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17238, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
       <c r="K42" t="n">
@@ -3398,10 +3394,14 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="P42" t="inlineStr"/>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>2037818020597215557</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>{'name': 'GP Q', 'screenName': 'argosaki', 'followersCount': 111379, 'favouritesCount': 302129, 'friendsCount': 1637, 'description': 'Special? Mmmmm not really, just me :). *Standard disclaimer that nothing in these posts should be used as a substitute for financial or medical advice*'}</t>
+          <t>{'name': 'GP Q', 'screenName': 'argosaki', 'followersCount': 111374, 'favouritesCount': 302141, 'friendsCount': 1637, 'description': 'Special? Mmmmm not really, just me :). *Standard disclaimer that nothing in these posts should be used as a substitute for financial or medical advice*'}</t>
         </is>
       </c>
       <c r="K43" t="n">
@@ -3467,7 +3467,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>428</t>
+          <t>430</t>
         </is>
       </c>
       <c r="P43" t="inlineStr"/>
@@ -3488,55 +3488,52 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2038052874803118423</t>
+          <t>2038054346693435744</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://x.com/argosaki/status/2038052874803118423</t>
+          <t>https://x.com/argosaki/status/2038054346693435744</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>This picture of Donald Trump and John F. Kennedy Jr was at a New York Knicks game at Madison Square Garden on March 31, 1999
-March 31, 1999 - July 16, 1999 
-was exactly 107 days.  
-Everything always lines up so perfectly‼️‼️‼️ https://t.co/VdFCGIRBKl</t>
+          <t>.👇♥️🙏 https://t.co/k2P5WezRfZ</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>1774744645000</v>
+        <v>1774744996000</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2038052874803118423</t>
+          <t>2038054346693435744</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEieSZEakAAXfdV.jpg', 'type': 'photo', 'id': '2038052870189387776'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEifoD5b0AEmFq5.jpg', 'type': 'photo', 'id': '2038054341974937601'}]</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>{'name': 'GP Q', 'screenName': 'argosaki', 'followersCount': 111379, 'favouritesCount': 302129, 'friendsCount': 1637, 'description': 'Special? Mmmmm not really, just me :). *Standard disclaimer that nothing in these posts should be used as a substitute for financial or medical advice*'}</t>
+          <t>{'name': 'GP Q', 'screenName': 'argosaki', 'followersCount': 111374, 'favouritesCount': 302141, 'friendsCount': 1637, 'description': 'Special? Mmmmm not really, just me :). *Standard disclaimer that nothing in these posts should be used as a substitute for financial or medical advice*'}</t>
         </is>
       </c>
       <c r="K44" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>54</v>
+        <v>4</v>
       </c>
       <c r="N44" t="n">
-        <v>213</v>
+        <v>29</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>4001</t>
+          <t>677</t>
         </is>
       </c>
       <c r="P44" t="inlineStr"/>
@@ -3604,7 +3601,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>498</t>
+          <t>507</t>
         </is>
       </c>
       <c r="P45" t="inlineStr"/>
@@ -3672,7 +3669,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>525</t>
         </is>
       </c>
       <c r="P46" t="inlineStr"/>
@@ -3683,12 +3680,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037792667782824069</t>
+          <t>https://x.com/ZaibKang/status/2037796434725269639</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2037792667782824069</t>
+          <t>2037796434725269639</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3740,7 +3737,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>518</t>
+          <t>526</t>
         </is>
       </c>
       <c r="P47" t="inlineStr"/>
@@ -3751,12 +3748,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037792667782824069</t>
+          <t>https://x.com/ZaibKang/status/2037796434725269639</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2037792667782824069</t>
+          <t>2037796434725269639</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3808,7 +3805,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>31</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -3823,12 +3820,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037792667782824069</t>
+          <t>https://x.com/ZaibKang/status/2037796434725269639</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2037792667782824069</t>
+          <t>2037796434725269639</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3878,7 +3875,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -3893,12 +3890,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037792667782824069</t>
+          <t>https://x.com/ZaibKang/status/2037796434725269639</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2037792667782824069</t>
+          <t>2037796434725269639</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3948,7 +3945,7 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -3963,305 +3960,25 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>https://x.com/ZaibKang/status/2037796434725269639</t>
+          <t>https://x.com/MazBalushi35285/status/2037796009921900610</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2037796434725269639</t>
+          <t>2037796009921900610</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2037784344333275440</t>
+          <t>2035436745538281762</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037784344333275440</t>
+          <t>https://x.com/RotanaLive/status/2035436745538281762</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
-        <is>
-          <t>Before clicking a link, what do you do?
-Stay Safe, Stay Vigilant. #UnitedAgainstFraud
-https://t.co/YpRWtBZrhq</t>
-        </is>
-      </c>
-      <c r="G51" t="n">
-        <v>1774680622000</v>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>2037784344333275440</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="K51" t="n">
-        <v>3</v>
-      </c>
-      <c r="L51" t="n">
-        <v>0</v>
-      </c>
-      <c r="M51" t="n">
-        <v>0</v>
-      </c>
-      <c r="N51" t="n">
-        <v>3</v>
-      </c>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>518</t>
-        </is>
-      </c>
-      <c r="P51" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>https://x.com/ZaibKang/status/2037796434725269639</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>2037796434725269639</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>2037785874474430532</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>https://x.com/ZaibKang/status/2037785874474430532</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE I applied for liv X account Still not received any response 
-Reference number 
-2026038379331830</t>
-        </is>
-      </c>
-      <c r="G52" t="n">
-        <v>1774680987000</v>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>2037784344333275440</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>{'name': 'Jahan Zaib Akbar Kang', 'screenName': 'ZaibKang', 'followersCount': 599, 'favouritesCount': 4475, 'friendsCount': 18, 'description': 'سُبْحَانَ اللَّهِ ، وَالْحَمْدُ لِلَّهِ ، وَلَا إِلَهَ إِلَّا اللَّهُ ، وَاللَّهُ أَكْبَرُ\nEntrepreneur &amp; investor'}</t>
-        </is>
-      </c>
-      <c r="K52" t="n">
-        <v>1</v>
-      </c>
-      <c r="L52" t="n">
-        <v>0</v>
-      </c>
-      <c r="M52" t="n">
-        <v>0</v>
-      </c>
-      <c r="N52" t="n">
-        <v>0</v>
-      </c>
-      <c r="O52" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="P52" t="inlineStr">
-        <is>
-          <t>2037784344333275440</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="1" t="n">
-        <v>51</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>https://x.com/ZaibKang/status/2037796434725269639</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>2037796434725269639</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>2037792667782824069</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037792667782824069</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>@ZaibKang We are so sorry to hear you had an unpleasant experience, please share with us your concern from your registered email address for further communication to social@emiratesnbd.com and tag the case reference number #989763 in the subject line.</t>
-        </is>
-      </c>
-      <c r="G53" t="n">
-        <v>1774682607000</v>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>2037784344333275440</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="K53" t="n">
-        <v>1</v>
-      </c>
-      <c r="L53" t="n">
-        <v>0</v>
-      </c>
-      <c r="M53" t="n">
-        <v>0</v>
-      </c>
-      <c r="N53" t="n">
-        <v>1</v>
-      </c>
-      <c r="O53" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="P53" t="inlineStr">
-        <is>
-          <t>2037785874474430532</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="1" t="n">
-        <v>52</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>https://x.com/ZaibKang/status/2037796434725269639</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>2037796434725269639</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>2037796434725269639</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>https://x.com/ZaibKang/status/2037796434725269639</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE Thanks for your timely response.</t>
-        </is>
-      </c>
-      <c r="G54" t="n">
-        <v>1774683505000</v>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>2037784344333275440</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>{'name': 'Jahan Zaib Akbar Kang', 'screenName': 'ZaibKang', 'followersCount': 599, 'favouritesCount': 4475, 'friendsCount': 18, 'description': 'سُبْحَانَ اللَّهِ ، وَالْحَمْدُ لِلَّهِ ، وَلَا إِلَهَ إِلَّا اللَّهُ ، وَاللَّهُ أَكْبَرُ\nEntrepreneur &amp; investor'}</t>
-        </is>
-      </c>
-      <c r="K54" t="n">
-        <v>0</v>
-      </c>
-      <c r="L54" t="n">
-        <v>0</v>
-      </c>
-      <c r="M54" t="n">
-        <v>0</v>
-      </c>
-      <c r="N54" t="n">
-        <v>0</v>
-      </c>
-      <c r="O54" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>2037792667782824069</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="1" t="n">
-        <v>53</v>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>https://x.com/MazBalushi35285/status/2037796009921900610</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>2037796009921900610</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>2035436745538281762</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>https://x.com/RotanaLive/status/2035436745538281762</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
         <is>
           <t>جمهور الصقر جاهزين لحفل العيد مع صقر الأغنية الخليجية #رابح_صقر ؟🦅🎶
 #روتانا_لايف
@@ -4275,42 +3992,322 @@
 @EmiratesNBD_KSA https://t.co/0V3B6UgNKV</t>
         </is>
       </c>
+      <c r="G51" t="n">
+        <v>1774120911000</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>2035436745538281762</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2035436341970788352/img/OfSY4fBJEacp25TH.jpg', 'type': 'video', 'id': '2035436341970788352'}]</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>{'name': 'Rotana Live', 'screenName': 'RotanaLive', 'followersCount': 193214, 'favouritesCount': 7051, 'friendsCount': 147, 'description': 'روتانا لايف الحساب الرسمي لحفلات روتانا | Rotana events https://t.co/wTAoLH4wPm'}</t>
+        </is>
+      </c>
+      <c r="K51" t="n">
+        <v>3</v>
+      </c>
+      <c r="L51" t="n">
+        <v>1</v>
+      </c>
+      <c r="M51" t="n">
+        <v>6</v>
+      </c>
+      <c r="N51" t="n">
+        <v>28</v>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>7289</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>https://x.com/MazBalushi35285/status/2037796009921900610</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>2037796009921900610</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2037796009921900610</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>https://x.com/MazBalushi35285/status/2037796009921900610</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>@RotanaLive @Turki_alalshikh @RabehSaqer @GEA_SA @EidSeason @Mabdoarena @EmiratesNBD_KSA 🥳مزيد من النواة الفн على مسابقة رابح صقر! راحت لكم الحفل العيد في الرياض! 🎉 فوق_النهاية فقط</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>1774683403000</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>2035436745538281762</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>{'name': 'مازن البلوشي', 'screenName': 'MazBalushi35285', 'followersCount': 1, 'favouritesCount': 458, 'friendsCount': 1, 'description': 'عربي. رجل أعمال. أبني المستقبل خطوة بخطوة.'}</t>
+        </is>
+      </c>
+      <c r="K52" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>2035436745538281762</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="n">
+        <v>51</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2037792667782824069</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2037792667782824069</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2037784344333275440</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2037784344333275440</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Before clicking a link, what do you do?
+Stay Safe, Stay Vigilant. #UnitedAgainstFraud
+https://t.co/YpRWtBZrhq</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>1774680622000</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>2037784344333275440</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="K53" t="n">
+        <v>3</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" t="n">
+        <v>3</v>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>526</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="n">
+        <v>52</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2037792667782824069</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2037792667782824069</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2037785874474430532</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>https://x.com/ZaibKang/status/2037785874474430532</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE I applied for liv X account Still not received any response 
+Reference number 
+2026038379331830</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>1774680987000</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>2037784344333275440</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>{'name': 'Jahan Zaib Akbar Kang', 'screenName': 'ZaibKang', 'followersCount': 599, 'favouritesCount': 4475, 'friendsCount': 18, 'description': 'سُبْحَانَ اللَّهِ ، وَالْحَمْدُ لِلَّهِ ، وَلَا إِلَهَ إِلَّا اللَّهُ ، وَاللَّهُ أَكْبَرُ\nEntrepreneur &amp; investor'}</t>
+        </is>
+      </c>
+      <c r="K54" t="n">
+        <v>1</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>2037784344333275440</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="n">
+        <v>53</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2037792667782824069</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2037792667782824069</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2037792667782824069</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2037792667782824069</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>@ZaibKang We are so sorry to hear you had an unpleasant experience, please share with us your concern from your registered email address for further communication to social@emiratesnbd.com and tag the case reference number #989763 in the subject line.</t>
+        </is>
+      </c>
       <c r="G55" t="n">
-        <v>1774120911000</v>
+        <v>1774682607000</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2035436745538281762</t>
+          <t>2037784344333275440</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2035436341970788352/img/OfSY4fBJEacp25TH.jpg', 'type': 'video', 'id': '2035436341970788352'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>{'name': 'Rotana Live', 'screenName': 'RotanaLive', 'followersCount': 193209, 'favouritesCount': 7051, 'friendsCount': 147, 'description': 'روتانا لايف الحساب الرسمي لحفلات روتانا | Rotana events https://t.co/wTAoLH4wPm'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="K55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" t="n">
         <v>1</v>
       </c>
-      <c r="M55" t="n">
-        <v>6</v>
-      </c>
-      <c r="N55" t="n">
-        <v>28</v>
-      </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>7288</t>
-        </is>
-      </c>
-      <c r="P55" t="inlineStr"/>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>2037785874474430532</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
@@ -4318,35 +4315,35 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>https://x.com/MazBalushi35285/status/2037796009921900610</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2037792667782824069</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2037796009921900610</t>
+          <t>2037792667782824069</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2037796009921900610</t>
+          <t>2037796434725269639</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://x.com/MazBalushi35285/status/2037796009921900610</t>
+          <t>https://x.com/ZaibKang/status/2037796434725269639</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>@RotanaLive @Turki_alalshikh @RabehSaqer @GEA_SA @EidSeason @Mabdoarena @EmiratesNBD_KSA 🥳مزيد من النواة الفн على مسابقة رابح صقر! راحت لكم الحفل العيد في الرياض! 🎉 فوق_النهاية فقط</t>
+          <t>@EmiratesNBD_AE Thanks for your timely response.</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>1774683403000</v>
+        <v>1774683505000</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2035436745538281762</t>
+          <t>2037784344333275440</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -4356,7 +4353,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>{'name': 'مازن البلوشي', 'screenName': 'MazBalushi35285', 'followersCount': 1, 'favouritesCount': 458, 'friendsCount': 1, 'description': 'عربي. رجل أعمال. أبني المستقبل خطوة بخطوة.'}</t>
+          <t>{'name': 'Jahan Zaib Akbar Kang', 'screenName': 'ZaibKang', 'followersCount': 599, 'favouritesCount': 4475, 'friendsCount': 18, 'description': 'سُبْحَانَ اللَّهِ ، وَالْحَمْدُ لِلَّهِ ، وَلَا إِلَهَ إِلَّا اللَّهُ ، وَاللَّهُ أَكْبَرُ\nEntrepreneur &amp; investor'}</t>
         </is>
       </c>
       <c r="K56" t="n">
@@ -4373,12 +4370,12 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>2035436745538281762</t>
+          <t>2037792667782824069</t>
         </is>
       </c>
     </row>
@@ -4388,172 +4385,25 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>https://x.com/SelmaRomola/status/2037789707321622955</t>
+          <t>https://x.com/SelmaRomola/status/2037790087141101872</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2037789707321622955</t>
+          <t>2037790087141101872</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2034225946308358408</t>
+          <t>2031673422921564269</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2034225946308358408</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2031673422921564269</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
-        <is>
-          <t>اجعل مفاجآت العيد أكثر قيمة.
-من الفضة إلى الذهب، اكتشف طريقة أذكى لامتلاك أو إهداء شيء ثمين بحق.
-شاهد هذه الحلقة وأخبرنا:
-كيف يمكنك شراء الذهب والفضه من البنك؟
-للمشاركة:
-تابع حساب بنك الإمارات دبي الوطني 
-قم بالإشارة إلى 3 من أصدقائك
-اكتب إجابتك في التعليقات أدناه لفرصة ربح 10,000 درهم</t>
-        </is>
-      </c>
-      <c r="G57" t="n">
-        <v>1773832234000</v>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>2034225946308358408</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2034225772156563456/img/fizQ3vAEH0uqiLix.jpg', 'type': 'video', 'id': '2034225772156563456'}]</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="K57" t="n">
-        <v>91</v>
-      </c>
-      <c r="L57" t="n">
-        <v>1</v>
-      </c>
-      <c r="M57" t="n">
-        <v>39</v>
-      </c>
-      <c r="N57" t="n">
-        <v>50</v>
-      </c>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t>2632</t>
-        </is>
-      </c>
-      <c r="P57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="1" t="n">
-        <v>56</v>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>https://x.com/SelmaRomola/status/2037789707321622955</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>2037789707321622955</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>2037789707321622955</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>https://x.com/SelmaRomola/status/2037789707321622955</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE To buy gold and silver through Emirates NBD, the fastest way is using the ENBD X mobile app. 
-Tagging 
-@FazilAnas 
-@Emy191990 
-@Bushrasabih2</t>
-        </is>
-      </c>
-      <c r="G58" t="n">
-        <v>1774681901000</v>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>2034225946308358408</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>{'name': 'Selma Romola', 'screenName': 'SelmaRomola', 'followersCount': 1152, 'favouritesCount': 19738, 'friendsCount': 1787, 'description': ''}</t>
-        </is>
-      </c>
-      <c r="K58" t="n">
-        <v>0</v>
-      </c>
-      <c r="L58" t="n">
-        <v>0</v>
-      </c>
-      <c r="M58" t="n">
-        <v>0</v>
-      </c>
-      <c r="N58" t="n">
-        <v>0</v>
-      </c>
-      <c r="O58" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>2034225946308358408</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="1" t="n">
-        <v>57</v>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>https://x.com/SelmaRomola/status/2037790087141101872</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>2037790087141101872</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>2031673422921564269</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2031673422921564269</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
         <is>
           <t>نفذت أموال أم خماس قبل نهاية الشهر.
 هناك قاعدة بسيطة تُساعدها على إدارة أموالها بحكمة:
@@ -4580,68 +4430,68 @@
 - Drop your answer below for a chance to win AED 10,000</t>
         </is>
       </c>
-      <c r="G59" t="n">
+      <c r="G57" t="n">
         <v>1773223665000</v>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="H57" t="inlineStr">
         <is>
           <t>2031673422921564269</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HDH0NZXWQAAnKTa.jpg', 'type': 'video', 'id': '2031673271423295488'}]</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr">
+      <c r="J57" t="inlineStr">
         <is>
           <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
-      <c r="K59" t="n">
+      <c r="K57" t="n">
         <v>128</v>
       </c>
-      <c r="L59" t="n">
-        <v>0</v>
-      </c>
-      <c r="M59" t="n">
+      <c r="L57" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" t="n">
         <v>40</v>
       </c>
-      <c r="N59" t="n">
+      <c r="N57" t="n">
         <v>53</v>
       </c>
-      <c r="O59" t="inlineStr">
-        <is>
-          <t>2342</t>
-        </is>
-      </c>
-      <c r="P59" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="1" t="n">
-        <v>58</v>
-      </c>
-      <c r="B60" t="inlineStr">
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>2345</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="n">
+        <v>56</v>
+      </c>
+      <c r="B58" t="inlineStr">
         <is>
           <t>https://x.com/SelmaRomola/status/2037790087141101872</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>2037790087141101872</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>2037790087141101872</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>https://x.com/SelmaRomola/status/2037790087141101872</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>@EmiratesNBD_AE Fin well Financial well-being program with Emirates NBD 
 @Sabaashraff
@@ -4649,12 +4499,159 @@
 @Amanekhattab1</t>
         </is>
       </c>
+      <c r="G58" t="n">
+        <v>1774681991000</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>2031673422921564269</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>{'name': 'Selma Romola', 'screenName': 'SelmaRomola', 'followersCount': 1152, 'favouritesCount': 19738, 'friendsCount': 1787, 'description': ''}</t>
+        </is>
+      </c>
+      <c r="K58" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>2031673422921564269</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="n">
+        <v>57</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>https://x.com/SelmaRomola/status/2037789707321622955</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>2037789707321622955</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2034225946308358408</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2034225946308358408</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>اجعل مفاجآت العيد أكثر قيمة.
+من الفضة إلى الذهب، اكتشف طريقة أذكى لامتلاك أو إهداء شيء ثمين بحق.
+شاهد هذه الحلقة وأخبرنا:
+كيف يمكنك شراء الذهب والفضه من البنك؟
+للمشاركة:
+تابع حساب بنك الإمارات دبي الوطني 
+قم بالإشارة إلى 3 من أصدقائك
+اكتب إجابتك في التعليقات أدناه لفرصة ربح 10,000 درهم</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>1773832234000</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>2034225946308358408</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2034225772156563456/img/fizQ3vAEH0uqiLix.jpg', 'type': 'video', 'id': '2034225772156563456'}]</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="K59" t="n">
+        <v>91</v>
+      </c>
+      <c r="L59" t="n">
+        <v>1</v>
+      </c>
+      <c r="M59" t="n">
+        <v>39</v>
+      </c>
+      <c r="N59" t="n">
+        <v>50</v>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>2638</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="n">
+        <v>58</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>https://x.com/SelmaRomola/status/2037789707321622955</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2037789707321622955</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2037789707321622955</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>https://x.com/SelmaRomola/status/2037789707321622955</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE To buy gold and silver through Emirates NBD, the fastest way is using the ENBD X mobile app. 
+Tagging 
+@FazilAnas 
+@Emy191990 
+@Bushrasabih2</t>
+        </is>
+      </c>
       <c r="G60" t="n">
-        <v>1774681991000</v>
+        <v>1774681901000</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2031673422921564269</t>
+          <t>2034225946308358408</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4681,12 +4678,12 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>11</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>2031673422921564269</t>
+          <t>2034225946308358408</t>
         </is>
       </c>
     </row>
@@ -4758,7 +4755,7 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>1676</t>
+          <t>1678</t>
         </is>
       </c>
       <c r="P61" t="inlineStr"/>
@@ -4828,7 +4825,7 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -4900,7 +4897,7 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>518</t>
+          <t>526</t>
         </is>
       </c>
       <c r="P63" t="inlineStr"/>
@@ -4968,7 +4965,7 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>31</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -5038,7 +5035,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -5115,7 +5112,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>2633</t>
+          <t>2639</t>
         </is>
       </c>
       <c r="P66" t="inlineStr"/>
@@ -5185,7 +5182,7 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -5200,44 +5197,42 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784853866029145</t>
+          <t>https://x.com/ZaibKang/status/2037785071189671937</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2037784853866029145</t>
+          <t>2037785071189671937</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025123939970584932</t>
+          <t>2037784344333275440</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2025123939970584932</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2037784344333275440</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>حل اللغز واربح 10,000 درهم.💰
-أم علاوي تعبت من مشاكل السيارة، ومستعدة لسيارة جديدة بفضل قرض السيارات السريع من بنك الإمارات دبي الوطني، من خلال طلب سهل وسريع عبر الإنترنت.
-تابع @EmiratesNBD_ae
-قم بالإشارة إلى 3 من أصدقائك
-حل اللغز لفرصة الفوز بـ 10 آلاف درهم. https://t.co/NBQE3PzfgZ</t>
+          <t>Before clicking a link, what do you do?
+Stay Safe, Stay Vigilant. #UnitedAgainstFraud
+https://t.co/YpRWtBZrhq</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>1771662146000</v>
+        <v>1774680622000</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2025123939970584932</t>
+          <t>2037784344333275440</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2025123808986718208/img/anriFRhFhmo7262r.jpg', 'type': 'video', 'id': '2025123808986718208'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -5246,20 +5241,20 @@
         </is>
       </c>
       <c r="K68" t="n">
-        <v>857</v>
+        <v>3</v>
       </c>
       <c r="L68" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" t="n">
+        <v>0</v>
+      </c>
+      <c r="N68" t="n">
         <v>3</v>
       </c>
-      <c r="M68" t="n">
-        <v>183</v>
-      </c>
-      <c r="N68" t="n">
-        <v>191</v>
-      </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>9395</t>
+          <t>526</t>
         </is>
       </c>
       <c r="P68" t="inlineStr"/>
@@ -5270,45 +5265,45 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784853866029145</t>
+          <t>https://x.com/ZaibKang/status/2037785071189671937</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2037784853866029145</t>
+          <t>2037785071189671937</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2037784853866029145</t>
+          <t>2037785071189671937</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784853866029145</t>
+          <t>https://x.com/ZaibKang/status/2037785071189671937</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE B- 1.89% @zeynp_qas @Salma2232019 @semeet 🌿🇦🇪❤️</t>
+          <t>@EmiratesNBD_AE @EmiratesNBD_AE I applied for liv X account 3 days ago still not received any response please Check and respond as soon as possible https://t.co/LXfxy0AGqW</t>
         </is>
       </c>
       <c r="G69" t="n">
-        <v>1774680744000</v>
+        <v>1774680795000</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2025123939970584932</t>
+          <t>2037784344333275440</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEequS2a4AAftLC.jpg', 'type': 'photo', 'id': '2037785068719235072'}]</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>{'name': 'Soha.mostafa77', 'screenName': 'Sosomostafa729S', 'followersCount': 345, 'favouritesCount': 22185, 'friendsCount': 967, 'description': 'Moom of 2 🙍\u200d♂️🙍\u200d♀️\nShopping 🛍 food 😋 traveling \nLive in UAE 🇦🇪🕊💕'}</t>
+          <t>{'name': 'Jahan Zaib Akbar Kang', 'screenName': 'ZaibKang', 'followersCount': 599, 'favouritesCount': 4475, 'friendsCount': 18, 'description': 'سُبْحَانَ اللَّهِ ، وَالْحَمْدُ لِلَّهِ ، وَلَا إِلَهَ إِلَّا اللَّهُ ، وَاللَّهُ أَكْبَرُ\nEntrepreneur &amp; investor'}</t>
         </is>
       </c>
       <c r="K69" t="n">
@@ -5325,12 +5320,12 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>14</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>2025123939970584932</t>
+          <t>2037784344333275440</t>
         </is>
       </c>
     </row>
@@ -5340,443 +5335,25 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>https://x.com/ZaibKang/status/2037785071189671937</t>
+          <t>https://x.com/Sosomostafa729S/status/2037784498885243377</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2037785071189671937</t>
+          <t>2037784498885243377</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2037784344333275440</t>
+          <t>2027634643315404863</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037784344333275440</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2027634643315404863</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
-        <is>
-          <t>Before clicking a link, what do you do?
-Stay Safe, Stay Vigilant. #UnitedAgainstFraud
-https://t.co/YpRWtBZrhq</t>
-        </is>
-      </c>
-      <c r="G70" t="n">
-        <v>1774680622000</v>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>2037784344333275440</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="K70" t="n">
-        <v>3</v>
-      </c>
-      <c r="L70" t="n">
-        <v>0</v>
-      </c>
-      <c r="M70" t="n">
-        <v>0</v>
-      </c>
-      <c r="N70" t="n">
-        <v>3</v>
-      </c>
-      <c r="O70" t="inlineStr">
-        <is>
-          <t>519</t>
-        </is>
-      </c>
-      <c r="P70" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="1" t="n">
-        <v>69</v>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>https://x.com/ZaibKang/status/2037785071189671937</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>2037785071189671937</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>2037785071189671937</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>https://x.com/ZaibKang/status/2037785071189671937</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE @EmiratesNBD_AE I applied for liv X account 3 days ago still not received any response please Check and respond as soon as possible https://t.co/LXfxy0AGqW</t>
-        </is>
-      </c>
-      <c r="G71" t="n">
-        <v>1774680795000</v>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>2037784344333275440</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEequS2a4AAftLC.jpg', 'type': 'photo', 'id': '2037785068719235072'}]</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>{'name': 'Jahan Zaib Akbar Kang', 'screenName': 'ZaibKang', 'followersCount': 599, 'favouritesCount': 4475, 'friendsCount': 18, 'description': 'سُبْحَانَ اللَّهِ ، وَالْحَمْدُ لِلَّهِ ، وَلَا إِلَهَ إِلَّا اللَّهُ ، وَاللَّهُ أَكْبَرُ\nEntrepreneur &amp; investor'}</t>
-        </is>
-      </c>
-      <c r="K71" t="n">
-        <v>0</v>
-      </c>
-      <c r="L71" t="n">
-        <v>0</v>
-      </c>
-      <c r="M71" t="n">
-        <v>0</v>
-      </c>
-      <c r="N71" t="n">
-        <v>0</v>
-      </c>
-      <c r="O71" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="P71" t="inlineStr">
-        <is>
-          <t>2037784344333275440</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="1" t="n">
-        <v>70</v>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784668028985459</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>2037784668028985459</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>2025123939970584932</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2025123939970584932</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>حل اللغز واربح 10,000 درهم.💰
-أم علاوي تعبت من مشاكل السيارة، ومستعدة لسيارة جديدة بفضل قرض السيارات السريع من بنك الإمارات دبي الوطني، من خلال طلب سهل وسريع عبر الإنترنت.
-تابع @EmiratesNBD_ae
-قم بالإشارة إلى 3 من أصدقائك
-حل اللغز لفرصة الفوز بـ 10 آلاف درهم. https://t.co/NBQE3PzfgZ</t>
-        </is>
-      </c>
-      <c r="G72" t="n">
-        <v>1771662146000</v>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>2025123939970584932</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2025123808986718208/img/anriFRhFhmo7262r.jpg', 'type': 'video', 'id': '2025123808986718208'}]</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="K72" t="n">
-        <v>857</v>
-      </c>
-      <c r="L72" t="n">
-        <v>3</v>
-      </c>
-      <c r="M72" t="n">
-        <v>183</v>
-      </c>
-      <c r="N72" t="n">
-        <v>191</v>
-      </c>
-      <c r="O72" t="inlineStr">
-        <is>
-          <t>9395</t>
-        </is>
-      </c>
-      <c r="P72" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="1" t="n">
-        <v>71</v>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784668028985459</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>2037784668028985459</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>2037784668028985459</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784668028985459</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE B- 1.89% @Emy191990 @ibushra_03 @parulghalout 🌿🇦🇪❤️</t>
-        </is>
-      </c>
-      <c r="G73" t="n">
-        <v>1774680699000</v>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>2025123939970584932</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>{'name': 'Soha.mostafa77', 'screenName': 'Sosomostafa729S', 'followersCount': 345, 'favouritesCount': 22185, 'friendsCount': 967, 'description': 'Moom of 2 🙍\u200d♂️🙍\u200d♀️\nShopping 🛍 food 😋 traveling \nLive in UAE 🇦🇪🕊💕'}</t>
-        </is>
-      </c>
-      <c r="K73" t="n">
-        <v>0</v>
-      </c>
-      <c r="L73" t="n">
-        <v>0</v>
-      </c>
-      <c r="M73" t="n">
-        <v>0</v>
-      </c>
-      <c r="N73" t="n">
-        <v>0</v>
-      </c>
-      <c r="O73" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="P73" t="inlineStr">
-        <is>
-          <t>2025123939970584932</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="1" t="n">
-        <v>72</v>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784763122217375</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>2037784763122217375</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>2025123939970584932</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2025123939970584932</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>حل اللغز واربح 10,000 درهم.💰
-أم علاوي تعبت من مشاكل السيارة، ومستعدة لسيارة جديدة بفضل قرض السيارات السريع من بنك الإمارات دبي الوطني، من خلال طلب سهل وسريع عبر الإنترنت.
-تابع @EmiratesNBD_ae
-قم بالإشارة إلى 3 من أصدقائك
-حل اللغز لفرصة الفوز بـ 10 آلاف درهم. https://t.co/NBQE3PzfgZ</t>
-        </is>
-      </c>
-      <c r="G74" t="n">
-        <v>1771662146000</v>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>2025123939970584932</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2025123808986718208/img/anriFRhFhmo7262r.jpg', 'type': 'video', 'id': '2025123808986718208'}]</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="K74" t="n">
-        <v>857</v>
-      </c>
-      <c r="L74" t="n">
-        <v>3</v>
-      </c>
-      <c r="M74" t="n">
-        <v>183</v>
-      </c>
-      <c r="N74" t="n">
-        <v>191</v>
-      </c>
-      <c r="O74" t="inlineStr">
-        <is>
-          <t>9395</t>
-        </is>
-      </c>
-      <c r="P74" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="1" t="n">
-        <v>73</v>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784763122217375</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>2037784763122217375</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>2037784763122217375</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784763122217375</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE B- 1.89% @semeet @Salma2232019 @SelmaRomola 🌿🇦🇪❤️</t>
-        </is>
-      </c>
-      <c r="G75" t="n">
-        <v>1774680722000</v>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>2025123939970584932</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>{'name': 'Soha.mostafa77', 'screenName': 'Sosomostafa729S', 'followersCount': 345, 'favouritesCount': 22185, 'friendsCount': 967, 'description': 'Moom of 2 🙍\u200d♂️🙍\u200d♀️\nShopping 🛍 food 😋 traveling \nLive in UAE 🇦🇪🕊💕'}</t>
-        </is>
-      </c>
-      <c r="K75" t="n">
-        <v>0</v>
-      </c>
-      <c r="L75" t="n">
-        <v>0</v>
-      </c>
-      <c r="M75" t="n">
-        <v>0</v>
-      </c>
-      <c r="N75" t="n">
-        <v>0</v>
-      </c>
-      <c r="O75" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="P75" t="inlineStr">
-        <is>
-          <t>2025123939970584932</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="1" t="n">
-        <v>74</v>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784498885243377</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>2037784498885243377</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>2027634643315404863</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2027634643315404863</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
         <is>
           <t>حلّ فزورة رمضان واربح 10,000 درهم.
 من توزيع الوجبات، إلى دعم العاملين وقضاء الوقت مع كبار المواطنين، يجمع برنامج واحد كل ذلك تحت مظلًة واحدة.
@@ -5787,68 +5364,68 @@
 3.اكتب إجابتك في التعليقات أدناه https://t.co/aADoQF5a2E</t>
         </is>
       </c>
-      <c r="G76" t="n">
+      <c r="G70" t="n">
         <v>1772260745000</v>
       </c>
-      <c r="H76" t="inlineStr">
+      <c r="H70" t="inlineStr">
         <is>
           <t>2027634643315404863</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
+      <c r="I70" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2027634528185901056/img/L9yGlrO1upMqeKpB.jpg', 'type': 'video', 'id': '2027634528185901056'}]</t>
         </is>
       </c>
-      <c r="J76" t="inlineStr">
+      <c r="J70" t="inlineStr">
         <is>
           <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
-      <c r="K76" t="n">
+      <c r="K70" t="n">
         <v>366</v>
       </c>
-      <c r="L76" t="n">
+      <c r="L70" t="n">
         <v>2</v>
       </c>
-      <c r="M76" t="n">
+      <c r="M70" t="n">
         <v>154</v>
       </c>
-      <c r="N76" t="n">
+      <c r="N70" t="n">
         <v>183</v>
       </c>
-      <c r="O76" t="inlineStr">
-        <is>
-          <t>10500</t>
-        </is>
-      </c>
-      <c r="P76" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="1" t="n">
-        <v>75</v>
-      </c>
-      <c r="B77" t="inlineStr">
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>10504</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="n">
+        <v>69</v>
+      </c>
+      <c r="B71" t="inlineStr">
         <is>
           <t>https://x.com/Sosomostafa729S/status/2037784498885243377</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="C71" t="inlineStr">
         <is>
           <t>2037784498885243377</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
+      <c r="D71" t="inlineStr">
         <is>
           <t>2027634776555872373</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="E71" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE/status/2027634776555872373</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
+      <c r="F71" t="inlineStr">
         <is>
           <t>Solve this Ramadan riddle and win AED 10,000.
 From food distribution to supporting workers and spending time with senior citizens, one program brings it all together.
@@ -5859,17 +5436,440 @@
 3.Drop your answer below https://t.co/PDRSppGlrJ</t>
         </is>
       </c>
+      <c r="G71" t="n">
+        <v>1772260777000</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>2027634643315404863</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2027634660532973568/img/NcwS9qq5kEQQ1U9q.jpg', 'type': 'video', 'id': '2027634660532973568'}]</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="K71" t="n">
+        <v>100</v>
+      </c>
+      <c r="L71" t="n">
+        <v>2</v>
+      </c>
+      <c r="M71" t="n">
+        <v>38</v>
+      </c>
+      <c r="N71" t="n">
+        <v>46</v>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>2289</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>2027634643315404863</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="n">
+        <v>70</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2037784498885243377</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>2037784498885243377</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2037784498885243377</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2037784498885243377</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE Exchanger volunteer program 
+@semeet @Emy191990 @ibushra_03 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="G72" t="n">
+        <v>1774680659000</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>2027634643315404863</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>{'name': 'Soha.mostafa77', 'screenName': 'Sosomostafa729S', 'followersCount': 345, 'favouritesCount': 22185, 'friendsCount': 968, 'description': 'Moom of 2 🙍\u200d♂️🙍\u200d♀️\nShopping 🛍 food 😋 traveling \nLive in UAE 🇦🇪🕊💕'}</t>
+        </is>
+      </c>
+      <c r="K72" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" t="n">
+        <v>0</v>
+      </c>
+      <c r="M72" t="n">
+        <v>0</v>
+      </c>
+      <c r="N72" t="n">
+        <v>0</v>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>2027634776555872373</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="n">
+        <v>71</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2037784668028985459</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>2037784668028985459</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>2025123939970584932</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2025123939970584932</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>حل اللغز واربح 10,000 درهم.💰
+أم علاوي تعبت من مشاكل السيارة، ومستعدة لسيارة جديدة بفضل قرض السيارات السريع من بنك الإمارات دبي الوطني، من خلال طلب سهل وسريع عبر الإنترنت.
+تابع @EmiratesNBD_ae
+قم بالإشارة إلى 3 من أصدقائك
+حل اللغز لفرصة الفوز بـ 10 آلاف درهم. https://t.co/NBQE3PzfgZ</t>
+        </is>
+      </c>
+      <c r="G73" t="n">
+        <v>1771662146000</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>2025123939970584932</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2025123808986718208/img/anriFRhFhmo7262r.jpg', 'type': 'video', 'id': '2025123808986718208'}]</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="K73" t="n">
+        <v>857</v>
+      </c>
+      <c r="L73" t="n">
+        <v>3</v>
+      </c>
+      <c r="M73" t="n">
+        <v>183</v>
+      </c>
+      <c r="N73" t="n">
+        <v>191</v>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>9397</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="n">
+        <v>72</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2037784668028985459</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>2037784668028985459</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>2037784668028985459</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2037784668028985459</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE B- 1.89% @Emy191990 @ibushra_03 @parulghalout 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="G74" t="n">
+        <v>1774680699000</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>2025123939970584932</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>{'name': 'Soha.mostafa77', 'screenName': 'Sosomostafa729S', 'followersCount': 345, 'favouritesCount': 22185, 'friendsCount': 968, 'description': 'Moom of 2 🙍\u200d♂️🙍\u200d♀️\nShopping 🛍 food 😋 traveling \nLive in UAE 🇦🇪🕊💕'}</t>
+        </is>
+      </c>
+      <c r="K74" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" t="n">
+        <v>0</v>
+      </c>
+      <c r="M74" t="n">
+        <v>0</v>
+      </c>
+      <c r="N74" t="n">
+        <v>0</v>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>2025123939970584932</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="n">
+        <v>73</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2037784763122217375</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>2037784763122217375</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>2025123939970584932</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2025123939970584932</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>حل اللغز واربح 10,000 درهم.💰
+أم علاوي تعبت من مشاكل السيارة، ومستعدة لسيارة جديدة بفضل قرض السيارات السريع من بنك الإمارات دبي الوطني، من خلال طلب سهل وسريع عبر الإنترنت.
+تابع @EmiratesNBD_ae
+قم بالإشارة إلى 3 من أصدقائك
+حل اللغز لفرصة الفوز بـ 10 آلاف درهم. https://t.co/NBQE3PzfgZ</t>
+        </is>
+      </c>
+      <c r="G75" t="n">
+        <v>1771662146000</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>2025123939970584932</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2025123808986718208/img/anriFRhFhmo7262r.jpg', 'type': 'video', 'id': '2025123808986718208'}]</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="K75" t="n">
+        <v>857</v>
+      </c>
+      <c r="L75" t="n">
+        <v>3</v>
+      </c>
+      <c r="M75" t="n">
+        <v>183</v>
+      </c>
+      <c r="N75" t="n">
+        <v>191</v>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>9397</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="n">
+        <v>74</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2037784763122217375</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>2037784763122217375</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>2037784763122217375</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2037784763122217375</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE B- 1.89% @semeet @Salma2232019 @SelmaRomola 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="G76" t="n">
+        <v>1774680722000</v>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>2025123939970584932</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>{'name': 'Soha.mostafa77', 'screenName': 'Sosomostafa729S', 'followersCount': 345, 'favouritesCount': 22185, 'friendsCount': 968, 'description': 'Moom of 2 🙍\u200d♂️🙍\u200d♀️\nShopping 🛍 food 😋 traveling \nLive in UAE 🇦🇪🕊💕'}</t>
+        </is>
+      </c>
+      <c r="K76" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" t="n">
+        <v>0</v>
+      </c>
+      <c r="M76" t="n">
+        <v>0</v>
+      </c>
+      <c r="N76" t="n">
+        <v>0</v>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>2025123939970584932</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="n">
+        <v>75</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2037784344333275440</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>2037784344333275440</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2037784344333275440</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2037784344333275440</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Before clicking a link, what do you do?
+Stay Safe, Stay Vigilant. #UnitedAgainstFraud
+https://t.co/YpRWtBZrhq</t>
+        </is>
+      </c>
       <c r="G77" t="n">
-        <v>1772260777000</v>
+        <v>1774680622000</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2027634643315404863</t>
+          <t>2037784344333275440</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2027634660532973568/img/NcwS9qq5kEQQ1U9q.jpg', 'type': 'video', 'id': '2027634660532973568'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -5878,27 +5878,23 @@
         </is>
       </c>
       <c r="K77" t="n">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="L77" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>46</v>
+        <v>3</v>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>2285</t>
-        </is>
-      </c>
-      <c r="P77" t="inlineStr">
-        <is>
-          <t>2027634643315404863</t>
-        </is>
-      </c>
+          <t>528</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
@@ -5906,36 +5902,37 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784498885243377</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2037784344333275440</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2037784498885243377</t>
+          <t>2037784344333275440</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2037784498885243377</t>
+          <t>2037785874474430532</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784498885243377</t>
+          <t>https://x.com/ZaibKang/status/2037785874474430532</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Exchanger volunteer program 
-@semeet @Emy191990 @ibushra_03 🌿🇦🇪❤️</t>
+          <t>@EmiratesNBD_AE I applied for liv X account Still not received any response 
+Reference number 
+2026038379331830</t>
         </is>
       </c>
       <c r="G78" t="n">
-        <v>1774680659000</v>
+        <v>1774680987000</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2027634643315404863</t>
+          <t>2037784344333275440</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5945,11 +5942,11 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>{'name': 'Soha.mostafa77', 'screenName': 'Sosomostafa729S', 'followersCount': 345, 'favouritesCount': 22185, 'friendsCount': 967, 'description': 'Moom of 2 🙍\u200d♂️🙍\u200d♀️\nShopping 🛍 food 😋 traveling \nLive in UAE 🇦🇪🕊💕'}</t>
+          <t>{'name': 'Jahan Zaib Akbar Kang', 'screenName': 'ZaibKang', 'followersCount': 599, 'favouritesCount': 4475, 'friendsCount': 18, 'description': 'سُبْحَانَ اللَّهِ ، وَالْحَمْدُ لِلَّهِ ، وَلَا إِلَهَ إِلَّا اللَّهُ ، وَاللَّهُ أَكْبَرُ\nEntrepreneur &amp; investor'}</t>
         </is>
       </c>
       <c r="K78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L78" t="n">
         <v>0</v>
@@ -5962,12 +5959,12 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>32</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>2027634776555872373</t>
+          <t>2037784344333275440</t>
         </is>
       </c>
     </row>
@@ -5987,27 +5984,27 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2037784344333275440</t>
+          <t>2037801868244533349</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037784344333275440</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2037801868244533349</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Before clicking a link, what do you do?
+          <t>What’s more suspicious?
 Stay Safe, Stay Vigilant. #UnitedAgainstFraud
 https://t.co/YpRWtBZrhq</t>
         </is>
       </c>
       <c r="G79" t="n">
-        <v>1774680622000</v>
+        <v>1774684800000</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2037784344333275440</t>
+          <t>2037801868244533349</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -6021,7 +6018,7 @@
         </is>
       </c>
       <c r="K79" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L79" t="n">
         <v>0</v>
@@ -6034,7 +6031,7 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>520</t>
+          <t>508</t>
         </is>
       </c>
       <c r="P79" t="inlineStr"/>
@@ -6045,165 +6042,25 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037784344333275440</t>
+          <t>https://x.com/Sosomostafa729S/status/2037784405700419683</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2037784344333275440</t>
+          <t>2037784405700419683</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2037785874474430532</t>
+          <t>2027634643315404863</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>https://x.com/ZaibKang/status/2037785874474430532</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2027634643315404863</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE I applied for liv X account Still not received any response 
-Reference number 
-2026038379331830</t>
-        </is>
-      </c>
-      <c r="G80" t="n">
-        <v>1774680987000</v>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>2037784344333275440</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>{'name': 'Jahan Zaib Akbar Kang', 'screenName': 'ZaibKang', 'followersCount': 599, 'favouritesCount': 4475, 'friendsCount': 18, 'description': 'سُبْحَانَ اللَّهِ ، وَالْحَمْدُ لِلَّهِ ، وَلَا إِلَهَ إِلَّا اللَّهُ ، وَاللَّهُ أَكْبَرُ\nEntrepreneur &amp; investor'}</t>
-        </is>
-      </c>
-      <c r="K80" t="n">
-        <v>1</v>
-      </c>
-      <c r="L80" t="n">
-        <v>0</v>
-      </c>
-      <c r="M80" t="n">
-        <v>0</v>
-      </c>
-      <c r="N80" t="n">
-        <v>0</v>
-      </c>
-      <c r="O80" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="P80" t="inlineStr">
-        <is>
-          <t>2037784344333275440</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="1" t="n">
-        <v>79</v>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037784344333275440</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>2037784344333275440</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>2037801868244533349</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037801868244533349</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>What’s more suspicious?
-Stay Safe, Stay Vigilant. #UnitedAgainstFraud
-https://t.co/YpRWtBZrhq</t>
-        </is>
-      </c>
-      <c r="G81" t="n">
-        <v>1774684800000</v>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>2037801868244533349</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="K81" t="n">
-        <v>2</v>
-      </c>
-      <c r="L81" t="n">
-        <v>0</v>
-      </c>
-      <c r="M81" t="n">
-        <v>0</v>
-      </c>
-      <c r="N81" t="n">
-        <v>3</v>
-      </c>
-      <c r="O81" t="inlineStr">
-        <is>
-          <t>499</t>
-        </is>
-      </c>
-      <c r="P81" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="1" t="n">
-        <v>80</v>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784405700419683</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>2037784405700419683</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>2027634643315404863</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2027634643315404863</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
         <is>
           <t>حلّ فزورة رمضان واربح 10,000 درهم.
 من توزيع الوجبات، إلى دعم العاملين وقضاء الوقت مع كبار المواطنين، يجمع برنامج واحد كل ذلك تحت مظلًة واحدة.
@@ -6214,68 +6071,68 @@
 3.اكتب إجابتك في التعليقات أدناه https://t.co/aADoQF5a2E</t>
         </is>
       </c>
-      <c r="G82" t="n">
+      <c r="G80" t="n">
         <v>1772260745000</v>
       </c>
-      <c r="H82" t="inlineStr">
+      <c r="H80" t="inlineStr">
         <is>
           <t>2027634643315404863</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
+      <c r="I80" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2027634528185901056/img/L9yGlrO1upMqeKpB.jpg', 'type': 'video', 'id': '2027634528185901056'}]</t>
         </is>
       </c>
-      <c r="J82" t="inlineStr">
+      <c r="J80" t="inlineStr">
         <is>
           <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
-      <c r="K82" t="n">
+      <c r="K80" t="n">
         <v>366</v>
       </c>
-      <c r="L82" t="n">
+      <c r="L80" t="n">
         <v>2</v>
       </c>
-      <c r="M82" t="n">
+      <c r="M80" t="n">
         <v>154</v>
       </c>
-      <c r="N82" t="n">
+      <c r="N80" t="n">
         <v>183</v>
       </c>
-      <c r="O82" t="inlineStr">
-        <is>
-          <t>10500</t>
-        </is>
-      </c>
-      <c r="P82" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="1" t="n">
-        <v>81</v>
-      </c>
-      <c r="B83" t="inlineStr">
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>10505</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="n">
+        <v>79</v>
+      </c>
+      <c r="B81" t="inlineStr">
         <is>
           <t>https://x.com/Sosomostafa729S/status/2037784405700419683</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
+      <c r="C81" t="inlineStr">
         <is>
           <t>2037784405700419683</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
+      <c r="D81" t="inlineStr">
         <is>
           <t>2027634776555872373</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
+      <c r="E81" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE/status/2027634776555872373</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
+      <c r="F81" t="inlineStr">
         <is>
           <t>Solve this Ramadan riddle and win AED 10,000.
 From food distribution to supporting workers and spending time with senior citizens, one program brings it all together.
@@ -6286,142 +6143,142 @@
 3.Drop your answer below https://t.co/PDRSppGlrJ</t>
         </is>
       </c>
-      <c r="G83" t="n">
+      <c r="G81" t="n">
         <v>1772260777000</v>
       </c>
-      <c r="H83" t="inlineStr">
+      <c r="H81" t="inlineStr">
         <is>
           <t>2027634643315404863</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr">
+      <c r="I81" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2027634660532973568/img/NcwS9qq5kEQQ1U9q.jpg', 'type': 'video', 'id': '2027634660532973568'}]</t>
         </is>
       </c>
-      <c r="J83" t="inlineStr">
+      <c r="J81" t="inlineStr">
         <is>
           <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
-      <c r="K83" t="n">
+      <c r="K81" t="n">
         <v>100</v>
       </c>
-      <c r="L83" t="n">
+      <c r="L81" t="n">
         <v>2</v>
       </c>
-      <c r="M83" t="n">
+      <c r="M81" t="n">
         <v>38</v>
       </c>
-      <c r="N83" t="n">
+      <c r="N81" t="n">
         <v>46</v>
       </c>
-      <c r="O83" t="inlineStr">
-        <is>
-          <t>2285</t>
-        </is>
-      </c>
-      <c r="P83" t="inlineStr">
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>2290</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
         <is>
           <t>2027634643315404863</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="1" t="n">
-        <v>82</v>
-      </c>
-      <c r="B84" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="1" t="n">
+        <v>80</v>
+      </c>
+      <c r="B82" t="inlineStr">
         <is>
           <t>https://x.com/Sosomostafa729S/status/2037784405700419683</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
+      <c r="C82" t="inlineStr">
         <is>
           <t>2037784405700419683</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr">
+      <c r="D82" t="inlineStr">
         <is>
           <t>2037784405700419683</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
+      <c r="E82" t="inlineStr">
         <is>
           <t>https://x.com/Sosomostafa729S/status/2037784405700419683</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
+      <c r="F82" t="inlineStr">
         <is>
           <t>@EmiratesNBD_AE Exchanger volunteer program @semeet @zeynp_qas @SelmaRomola 🌿🇦🇪❤️</t>
         </is>
       </c>
-      <c r="G84" t="n">
+      <c r="G82" t="n">
         <v>1774680637000</v>
       </c>
-      <c r="H84" t="inlineStr">
+      <c r="H82" t="inlineStr">
         <is>
           <t>2027634643315404863</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr">
+      <c r="I82" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>{'name': 'Soha.mostafa77', 'screenName': 'Sosomostafa729S', 'followersCount': 345, 'favouritesCount': 22185, 'friendsCount': 967, 'description': 'Moom of 2 🙍\u200d♂️🙍\u200d♀️\nShopping 🛍 food 😋 traveling \nLive in UAE 🇦🇪🕊💕'}</t>
-        </is>
-      </c>
-      <c r="K84" t="n">
-        <v>0</v>
-      </c>
-      <c r="L84" t="n">
-        <v>0</v>
-      </c>
-      <c r="M84" t="n">
-        <v>0</v>
-      </c>
-      <c r="N84" t="n">
-        <v>0</v>
-      </c>
-      <c r="O84" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="P84" t="inlineStr">
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>{'name': 'Soha.mostafa77', 'screenName': 'Sosomostafa729S', 'followersCount': 345, 'favouritesCount': 22185, 'friendsCount': 968, 'description': 'Moom of 2 🙍\u200d♂️🙍\u200d♀️\nShopping 🛍 food 😋 traveling \nLive in UAE 🇦🇪🕊💕'}</t>
+        </is>
+      </c>
+      <c r="K82" t="n">
+        <v>0</v>
+      </c>
+      <c r="L82" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" t="n">
+        <v>0</v>
+      </c>
+      <c r="N82" t="n">
+        <v>0</v>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
         <is>
           <t>2027634776555872373</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="1" t="n">
-        <v>83</v>
-      </c>
-      <c r="B85" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="1" t="n">
+        <v>81</v>
+      </c>
+      <c r="B83" t="inlineStr">
         <is>
           <t>https://x.com/Sosomostafa729S/status/2037784337337532619</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
+      <c r="C83" t="inlineStr">
         <is>
           <t>2037784337337532619</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
+      <c r="D83" t="inlineStr">
         <is>
           <t>2027634643315404863</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
+      <c r="E83" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE/status/2027634643315404863</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
+      <c r="F83" t="inlineStr">
         <is>
           <t>حلّ فزورة رمضان واربح 10,000 درهم.
 من توزيع الوجبات، إلى دعم العاملين وقضاء الوقت مع كبار المواطنين، يجمع برنامج واحد كل ذلك تحت مظلًة واحدة.
@@ -6432,68 +6289,68 @@
 3.اكتب إجابتك في التعليقات أدناه https://t.co/aADoQF5a2E</t>
         </is>
       </c>
-      <c r="G85" t="n">
+      <c r="G83" t="n">
         <v>1772260745000</v>
       </c>
-      <c r="H85" t="inlineStr">
+      <c r="H83" t="inlineStr">
         <is>
           <t>2027634643315404863</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr">
+      <c r="I83" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2027634528185901056/img/L9yGlrO1upMqeKpB.jpg', 'type': 'video', 'id': '2027634528185901056'}]</t>
         </is>
       </c>
-      <c r="J85" t="inlineStr">
+      <c r="J83" t="inlineStr">
         <is>
           <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
-      <c r="K85" t="n">
+      <c r="K83" t="n">
         <v>366</v>
       </c>
-      <c r="L85" t="n">
+      <c r="L83" t="n">
         <v>2</v>
       </c>
-      <c r="M85" t="n">
+      <c r="M83" t="n">
         <v>154</v>
       </c>
-      <c r="N85" t="n">
+      <c r="N83" t="n">
         <v>183</v>
       </c>
-      <c r="O85" t="inlineStr">
-        <is>
-          <t>10501</t>
-        </is>
-      </c>
-      <c r="P85" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="1" t="n">
-        <v>84</v>
-      </c>
-      <c r="B86" t="inlineStr">
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>10505</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="n">
+        <v>82</v>
+      </c>
+      <c r="B84" t="inlineStr">
         <is>
           <t>https://x.com/Sosomostafa729S/status/2037784337337532619</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
+      <c r="C84" t="inlineStr">
         <is>
           <t>2037784337337532619</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr">
+      <c r="D84" t="inlineStr">
         <is>
           <t>2027634776555872373</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
+      <c r="E84" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE/status/2027634776555872373</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
+      <c r="F84" t="inlineStr">
         <is>
           <t>Solve this Ramadan riddle and win AED 10,000.
 From food distribution to supporting workers and spending time with senior citizens, one program brings it all together.
@@ -6504,142 +6361,142 @@
 3.Drop your answer below https://t.co/PDRSppGlrJ</t>
         </is>
       </c>
-      <c r="G86" t="n">
+      <c r="G84" t="n">
         <v>1772260777000</v>
       </c>
-      <c r="H86" t="inlineStr">
+      <c r="H84" t="inlineStr">
         <is>
           <t>2027634643315404863</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr">
+      <c r="I84" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2027634660532973568/img/NcwS9qq5kEQQ1U9q.jpg', 'type': 'video', 'id': '2027634660532973568'}]</t>
         </is>
       </c>
-      <c r="J86" t="inlineStr">
+      <c r="J84" t="inlineStr">
         <is>
           <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
-      <c r="K86" t="n">
+      <c r="K84" t="n">
         <v>100</v>
       </c>
-      <c r="L86" t="n">
+      <c r="L84" t="n">
         <v>2</v>
       </c>
-      <c r="M86" t="n">
+      <c r="M84" t="n">
         <v>38</v>
       </c>
-      <c r="N86" t="n">
+      <c r="N84" t="n">
         <v>46</v>
       </c>
-      <c r="O86" t="inlineStr">
-        <is>
-          <t>2285</t>
-        </is>
-      </c>
-      <c r="P86" t="inlineStr">
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>2290</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
         <is>
           <t>2027634643315404863</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="1" t="n">
-        <v>85</v>
-      </c>
-      <c r="B87" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="1" t="n">
+        <v>83</v>
+      </c>
+      <c r="B85" t="inlineStr">
         <is>
           <t>https://x.com/Sosomostafa729S/status/2037784337337532619</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
+      <c r="C85" t="inlineStr">
         <is>
           <t>2037784337337532619</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr">
+      <c r="D85" t="inlineStr">
         <is>
           <t>2037784337337532619</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
+      <c r="E85" t="inlineStr">
         <is>
           <t>https://x.com/Sosomostafa729S/status/2037784337337532619</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
+      <c r="F85" t="inlineStr">
         <is>
           <t>@EmiratesNBD_AE Exchanger volunteer program @Emy191990 @ibushra_03 @parulghalout 🌿🇦🇪❤️</t>
         </is>
       </c>
-      <c r="G87" t="n">
+      <c r="G85" t="n">
         <v>1774680620000</v>
       </c>
-      <c r="H87" t="inlineStr">
+      <c r="H85" t="inlineStr">
         <is>
           <t>2027634643315404863</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr">
+      <c r="I85" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>{'name': 'Soha.mostafa77', 'screenName': 'Sosomostafa729S', 'followersCount': 345, 'favouritesCount': 22185, 'friendsCount': 967, 'description': 'Moom of 2 🙍\u200d♂️🙍\u200d♀️\nShopping 🛍 food 😋 traveling \nLive in UAE 🇦🇪🕊💕'}</t>
-        </is>
-      </c>
-      <c r="K87" t="n">
-        <v>0</v>
-      </c>
-      <c r="L87" t="n">
-        <v>0</v>
-      </c>
-      <c r="M87" t="n">
-        <v>0</v>
-      </c>
-      <c r="N87" t="n">
-        <v>0</v>
-      </c>
-      <c r="O87" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="P87" t="inlineStr">
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>{'name': 'Soha.mostafa77', 'screenName': 'Sosomostafa729S', 'followersCount': 345, 'favouritesCount': 22185, 'friendsCount': 968, 'description': 'Moom of 2 🙍\u200d♂️🙍\u200d♀️\nShopping 🛍 food 😋 traveling \nLive in UAE 🇦🇪🕊💕'}</t>
+        </is>
+      </c>
+      <c r="K85" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" t="n">
+        <v>0</v>
+      </c>
+      <c r="N85" t="n">
+        <v>0</v>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
         <is>
           <t>2027634776555872373</t>
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="1" t="n">
-        <v>86</v>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784141006344295</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>2037784141006344295</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="1" t="n">
+        <v>84</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2037784225022365938</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>2037784225022365938</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
         <is>
           <t>2027634643315404863</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
+      <c r="E86" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE/status/2027634643315404863</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
+      <c r="F86" t="inlineStr">
         <is>
           <t>حلّ فزورة رمضان واربح 10,000 درهم.
 من توزيع الوجبات، إلى دعم العاملين وقضاء الوقت مع كبار المواطنين، يجمع برنامج واحد كل ذلك تحت مظلًة واحدة.
@@ -6650,68 +6507,68 @@
 3.اكتب إجابتك في التعليقات أدناه https://t.co/aADoQF5a2E</t>
         </is>
       </c>
-      <c r="G88" t="n">
+      <c r="G86" t="n">
         <v>1772260745000</v>
       </c>
-      <c r="H88" t="inlineStr">
+      <c r="H86" t="inlineStr">
         <is>
           <t>2027634643315404863</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr">
+      <c r="I86" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2027634528185901056/img/L9yGlrO1upMqeKpB.jpg', 'type': 'video', 'id': '2027634528185901056'}]</t>
         </is>
       </c>
-      <c r="J88" t="inlineStr">
+      <c r="J86" t="inlineStr">
         <is>
           <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
-      <c r="K88" t="n">
+      <c r="K86" t="n">
         <v>366</v>
       </c>
-      <c r="L88" t="n">
+      <c r="L86" t="n">
         <v>2</v>
       </c>
-      <c r="M88" t="n">
+      <c r="M86" t="n">
         <v>154</v>
       </c>
-      <c r="N88" t="n">
+      <c r="N86" t="n">
         <v>183</v>
       </c>
-      <c r="O88" t="inlineStr">
-        <is>
-          <t>10501</t>
-        </is>
-      </c>
-      <c r="P88" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="1" t="n">
-        <v>87</v>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784141006344295</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>2037784141006344295</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>10505</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="n">
+        <v>85</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2037784225022365938</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>2037784225022365938</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
         <is>
           <t>2027634776555872373</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
+      <c r="E87" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE/status/2027634776555872373</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
+      <c r="F87" t="inlineStr">
         <is>
           <t>Solve this Ramadan riddle and win AED 10,000.
 From food distribution to supporting workers and spending time with senior citizens, one program brings it all together.
@@ -6722,142 +6579,142 @@
 3.Drop your answer below https://t.co/PDRSppGlrJ</t>
         </is>
       </c>
-      <c r="G89" t="n">
+      <c r="G87" t="n">
         <v>1772260777000</v>
       </c>
-      <c r="H89" t="inlineStr">
+      <c r="H87" t="inlineStr">
         <is>
           <t>2027634643315404863</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr">
+      <c r="I87" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2027634660532973568/img/NcwS9qq5kEQQ1U9q.jpg', 'type': 'video', 'id': '2027634660532973568'}]</t>
         </is>
       </c>
-      <c r="J89" t="inlineStr">
+      <c r="J87" t="inlineStr">
         <is>
           <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
-      <c r="K89" t="n">
+      <c r="K87" t="n">
         <v>100</v>
       </c>
-      <c r="L89" t="n">
+      <c r="L87" t="n">
         <v>2</v>
       </c>
-      <c r="M89" t="n">
+      <c r="M87" t="n">
         <v>38</v>
       </c>
-      <c r="N89" t="n">
+      <c r="N87" t="n">
         <v>46</v>
       </c>
-      <c r="O89" t="inlineStr">
-        <is>
-          <t>2286</t>
-        </is>
-      </c>
-      <c r="P89" t="inlineStr">
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>2290</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
         <is>
           <t>2027634643315404863</t>
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="1" t="n">
-        <v>88</v>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784141006344295</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>2037784141006344295</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>2037784141006344295</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784141006344295</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE Exchanger volunteer program @semeet @Salma2232019 @ibushra_03 🌿🇦🇪❤️</t>
-        </is>
-      </c>
-      <c r="G90" t="n">
-        <v>1774680574000</v>
-      </c>
-      <c r="H90" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="1" t="n">
+        <v>86</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2037784225022365938</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>2037784225022365938</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>2037784225022365938</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2037784225022365938</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE Exchanger volunteer program @semeet @parulghalout @Salma2232019 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="G88" t="n">
+        <v>1774680594000</v>
+      </c>
+      <c r="H88" t="inlineStr">
         <is>
           <t>2027634643315404863</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr">
+      <c r="I88" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>{'name': 'Soha.mostafa77', 'screenName': 'Sosomostafa729S', 'followersCount': 345, 'favouritesCount': 22185, 'friendsCount': 967, 'description': 'Moom of 2 🙍\u200d♂️🙍\u200d♀️\nShopping 🛍 food 😋 traveling \nLive in UAE 🇦🇪🕊💕'}</t>
-        </is>
-      </c>
-      <c r="K90" t="n">
-        <v>0</v>
-      </c>
-      <c r="L90" t="n">
-        <v>0</v>
-      </c>
-      <c r="M90" t="n">
-        <v>0</v>
-      </c>
-      <c r="N90" t="n">
-        <v>0</v>
-      </c>
-      <c r="O90" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="P90" t="inlineStr">
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>{'name': 'Soha.mostafa77', 'screenName': 'Sosomostafa729S', 'followersCount': 345, 'favouritesCount': 22185, 'friendsCount': 968, 'description': 'Moom of 2 🙍\u200d♂️🙍\u200d♀️\nShopping 🛍 food 😋 traveling \nLive in UAE 🇦🇪🕊💕'}</t>
+        </is>
+      </c>
+      <c r="K88" t="n">
+        <v>0</v>
+      </c>
+      <c r="L88" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" t="n">
+        <v>0</v>
+      </c>
+      <c r="N88" t="n">
+        <v>0</v>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
         <is>
           <t>2027634776555872373</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="1" t="n">
-        <v>89</v>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784225022365938</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>2037784225022365938</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="1" t="n">
+        <v>87</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2037784038774317555</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>2037784038774317555</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
         <is>
           <t>2027634643315404863</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
+      <c r="E89" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE/status/2027634643315404863</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr">
+      <c r="F89" t="inlineStr">
         <is>
           <t>حلّ فزورة رمضان واربح 10,000 درهم.
 من توزيع الوجبات، إلى دعم العاملين وقضاء الوقت مع كبار المواطنين، يجمع برنامج واحد كل ذلك تحت مظلًة واحدة.
@@ -6868,68 +6725,68 @@
 3.اكتب إجابتك في التعليقات أدناه https://t.co/aADoQF5a2E</t>
         </is>
       </c>
-      <c r="G91" t="n">
+      <c r="G89" t="n">
         <v>1772260745000</v>
       </c>
-      <c r="H91" t="inlineStr">
+      <c r="H89" t="inlineStr">
         <is>
           <t>2027634643315404863</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr">
+      <c r="I89" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2027634528185901056/img/L9yGlrO1upMqeKpB.jpg', 'type': 'video', 'id': '2027634528185901056'}]</t>
         </is>
       </c>
-      <c r="J91" t="inlineStr">
+      <c r="J89" t="inlineStr">
         <is>
           <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
-      <c r="K91" t="n">
+      <c r="K89" t="n">
         <v>366</v>
       </c>
-      <c r="L91" t="n">
+      <c r="L89" t="n">
         <v>2</v>
       </c>
-      <c r="M91" t="n">
+      <c r="M89" t="n">
         <v>154</v>
       </c>
-      <c r="N91" t="n">
+      <c r="N89" t="n">
         <v>183</v>
       </c>
-      <c r="O91" t="inlineStr">
-        <is>
-          <t>10501</t>
-        </is>
-      </c>
-      <c r="P91" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="1" t="n">
-        <v>90</v>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784225022365938</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>2037784225022365938</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>10505</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="n">
+        <v>88</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2037784038774317555</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>2037784038774317555</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
         <is>
           <t>2027634776555872373</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
+      <c r="E90" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE/status/2027634776555872373</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr">
+      <c r="F90" t="inlineStr">
         <is>
           <t>Solve this Ramadan riddle and win AED 10,000.
 From food distribution to supporting workers and spending time with senior citizens, one program brings it all together.
@@ -6940,361 +6797,143 @@
 3.Drop your answer below https://t.co/PDRSppGlrJ</t>
         </is>
       </c>
-      <c r="G92" t="n">
+      <c r="G90" t="n">
         <v>1772260777000</v>
       </c>
-      <c r="H92" t="inlineStr">
+      <c r="H90" t="inlineStr">
         <is>
           <t>2027634643315404863</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr">
+      <c r="I90" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2027634660532973568/img/NcwS9qq5kEQQ1U9q.jpg', 'type': 'video', 'id': '2027634660532973568'}]</t>
         </is>
       </c>
-      <c r="J92" t="inlineStr">
+      <c r="J90" t="inlineStr">
         <is>
           <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
-      <c r="K92" t="n">
+      <c r="K90" t="n">
         <v>100</v>
       </c>
-      <c r="L92" t="n">
+      <c r="L90" t="n">
         <v>2</v>
       </c>
-      <c r="M92" t="n">
+      <c r="M90" t="n">
         <v>38</v>
       </c>
-      <c r="N92" t="n">
+      <c r="N90" t="n">
         <v>46</v>
       </c>
-      <c r="O92" t="inlineStr">
-        <is>
-          <t>2285</t>
-        </is>
-      </c>
-      <c r="P92" t="inlineStr">
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>2290</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
         <is>
           <t>2027634643315404863</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="1" t="n">
-        <v>91</v>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784225022365938</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>2037784225022365938</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>2037784225022365938</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784225022365938</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE Exchanger volunteer program @semeet @parulghalout @Salma2232019 🌿🇦🇪❤️</t>
-        </is>
-      </c>
-      <c r="G93" t="n">
-        <v>1774680594000</v>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>2027634643315404863</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>{'name': 'Soha.mostafa77', 'screenName': 'Sosomostafa729S', 'followersCount': 345, 'favouritesCount': 22185, 'friendsCount': 967, 'description': 'Moom of 2 🙍\u200d♂️🙍\u200d♀️\nShopping 🛍 food 😋 traveling \nLive in UAE 🇦🇪🕊💕'}</t>
-        </is>
-      </c>
-      <c r="K93" t="n">
-        <v>0</v>
-      </c>
-      <c r="L93" t="n">
-        <v>0</v>
-      </c>
-      <c r="M93" t="n">
-        <v>0</v>
-      </c>
-      <c r="N93" t="n">
-        <v>0</v>
-      </c>
-      <c r="O93" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="P93" t="inlineStr">
-        <is>
-          <t>2027634776555872373</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="1" t="n">
-        <v>92</v>
-      </c>
-      <c r="B94" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="1" t="n">
+        <v>89</v>
+      </c>
+      <c r="B91" t="inlineStr">
         <is>
           <t>https://x.com/Sosomostafa729S/status/2037784038774317555</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
+      <c r="C91" t="inlineStr">
         <is>
           <t>2037784038774317555</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>2027634643315404863</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2027634643315404863</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>حلّ فزورة رمضان واربح 10,000 درهم.
-من توزيع الوجبات، إلى دعم العاملين وقضاء الوقت مع كبار المواطنين، يجمع برنامج واحد كل ذلك تحت مظلًة واحدة.
-ما اسم هذا البرنامج؟
-للمشاركة:
-1.تابع حساب بنك الإمارات دبي الوطني
-2.قم بالإشارة إلى 3 من أصدقائك
-3.اكتب إجابتك في التعليقات أدناه https://t.co/aADoQF5a2E</t>
-        </is>
-      </c>
-      <c r="G94" t="n">
-        <v>1772260745000</v>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>2027634643315404863</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2027634528185901056/img/L9yGlrO1upMqeKpB.jpg', 'type': 'video', 'id': '2027634528185901056'}]</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="K94" t="n">
-        <v>366</v>
-      </c>
-      <c r="L94" t="n">
-        <v>2</v>
-      </c>
-      <c r="M94" t="n">
-        <v>154</v>
-      </c>
-      <c r="N94" t="n">
-        <v>183</v>
-      </c>
-      <c r="O94" t="inlineStr">
-        <is>
-          <t>10501</t>
-        </is>
-      </c>
-      <c r="P94" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="1" t="n">
-        <v>93</v>
-      </c>
-      <c r="B95" t="inlineStr">
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>2037784038774317555</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
         <is>
           <t>https://x.com/Sosomostafa729S/status/2037784038774317555</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>2037784038774317555</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>2027634776555872373</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2027634776555872373</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>Solve this Ramadan riddle and win AED 10,000.
-From food distribution to supporting workers and spending time with senior citizens, one program brings it all together.
-What is the name of the program?
-To participate:
-1.Follow Emirates NBD
-2.Tag 3 friends
-3.Drop your answer below https://t.co/PDRSppGlrJ</t>
-        </is>
-      </c>
-      <c r="G95" t="n">
-        <v>1772260777000</v>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>2027634643315404863</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2027634660532973568/img/NcwS9qq5kEQQ1U9q.jpg', 'type': 'video', 'id': '2027634660532973568'}]</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="K95" t="n">
-        <v>100</v>
-      </c>
-      <c r="L95" t="n">
-        <v>2</v>
-      </c>
-      <c r="M95" t="n">
-        <v>38</v>
-      </c>
-      <c r="N95" t="n">
-        <v>46</v>
-      </c>
-      <c r="O95" t="inlineStr">
-        <is>
-          <t>2285</t>
-        </is>
-      </c>
-      <c r="P95" t="inlineStr">
-        <is>
-          <t>2027634643315404863</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="1" t="n">
-        <v>94</v>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784038774317555</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>2037784038774317555</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>2037784038774317555</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784038774317555</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
+      <c r="F91" t="inlineStr">
         <is>
           <t>@EmiratesNBD_AE Exchanger volunteer program 
 @Emy191990 @ibushra_03 @parulghalout 🌿🇦🇪❤️</t>
         </is>
       </c>
-      <c r="G96" t="n">
+      <c r="G91" t="n">
         <v>1774680549000</v>
       </c>
-      <c r="H96" t="inlineStr">
+      <c r="H91" t="inlineStr">
         <is>
           <t>2027634643315404863</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr">
+      <c r="I91" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>{'name': 'Soha.mostafa77', 'screenName': 'Sosomostafa729S', 'followersCount': 345, 'favouritesCount': 22185, 'friendsCount': 967, 'description': 'Moom of 2 🙍\u200d♂️🙍\u200d♀️\nShopping 🛍 food 😋 traveling \nLive in UAE 🇦🇪🕊💕'}</t>
-        </is>
-      </c>
-      <c r="K96" t="n">
-        <v>0</v>
-      </c>
-      <c r="L96" t="n">
-        <v>0</v>
-      </c>
-      <c r="M96" t="n">
-        <v>0</v>
-      </c>
-      <c r="N96" t="n">
-        <v>0</v>
-      </c>
-      <c r="O96" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="P96" t="inlineStr">
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>{'name': 'Soha.mostafa77', 'screenName': 'Sosomostafa729S', 'followersCount': 345, 'favouritesCount': 22185, 'friendsCount': 968, 'description': 'Moom of 2 🙍\u200d♂️🙍\u200d♀️\nShopping 🛍 food 😋 traveling \nLive in UAE 🇦🇪🕊💕'}</t>
+        </is>
+      </c>
+      <c r="K91" t="n">
+        <v>0</v>
+      </c>
+      <c r="L91" t="n">
+        <v>0</v>
+      </c>
+      <c r="M91" t="n">
+        <v>0</v>
+      </c>
+      <c r="N91" t="n">
+        <v>0</v>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
         <is>
           <t>2027634776555872373</t>
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="1" t="n">
-        <v>95</v>
-      </c>
-      <c r="B97" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="1" t="n">
+        <v>90</v>
+      </c>
+      <c r="B92" t="inlineStr">
         <is>
           <t>https://x.com/Sosomostafa729S/status/2037783859769876728</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr">
+      <c r="C92" t="inlineStr">
         <is>
           <t>2037783859769876728</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr">
+      <c r="D92" t="inlineStr">
         <is>
           <t>2031673422921564269</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr">
+      <c r="E92" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE/status/2031673422921564269</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr">
+      <c r="F92" t="inlineStr">
         <is>
           <t>نفذت أموال أم خماس قبل نهاية الشهر.
 هناك قاعدة بسيطة تُساعدها على إدارة أموالها بحكمة:
@@ -7321,138 +6960,138 @@
 - Drop your answer below for a chance to win AED 10,000</t>
         </is>
       </c>
-      <c r="G97" t="n">
+      <c r="G92" t="n">
         <v>1773223665000</v>
       </c>
-      <c r="H97" t="inlineStr">
+      <c r="H92" t="inlineStr">
         <is>
           <t>2031673422921564269</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr">
+      <c r="I92" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HDH0NZXWQAAnKTa.jpg', 'type': 'video', 'id': '2031673271423295488'}]</t>
         </is>
       </c>
-      <c r="J97" t="inlineStr">
+      <c r="J92" t="inlineStr">
         <is>
           <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
-      <c r="K97" t="n">
+      <c r="K92" t="n">
         <v>128</v>
       </c>
-      <c r="L97" t="n">
-        <v>0</v>
-      </c>
-      <c r="M97" t="n">
+      <c r="L92" t="n">
+        <v>0</v>
+      </c>
+      <c r="M92" t="n">
         <v>40</v>
       </c>
-      <c r="N97" t="n">
+      <c r="N92" t="n">
         <v>53</v>
       </c>
-      <c r="O97" t="inlineStr">
-        <is>
-          <t>2343</t>
-        </is>
-      </c>
-      <c r="P97" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="1" t="n">
-        <v>96</v>
-      </c>
-      <c r="B98" t="inlineStr">
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>2346</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="n">
+        <v>91</v>
+      </c>
+      <c r="B93" t="inlineStr">
         <is>
           <t>https://x.com/Sosomostafa729S/status/2037783859769876728</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr">
+      <c r="C93" t="inlineStr">
         <is>
           <t>2037783859769876728</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr">
+      <c r="D93" t="inlineStr">
         <is>
           <t>2037783859769876728</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr">
+      <c r="E93" t="inlineStr">
         <is>
           <t>https://x.com/Sosomostafa729S/status/2037783859769876728</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr">
+      <c r="F93" t="inlineStr">
         <is>
           <t>@EmiratesNBD_AE FINWELL ( Financial Well-being program) with Emirates NBD @semeet @zeynp_qas @Emy191990 🌿🇦🇪❤️</t>
         </is>
       </c>
-      <c r="G98" t="n">
+      <c r="G93" t="n">
         <v>1774680507000</v>
       </c>
-      <c r="H98" t="inlineStr">
+      <c r="H93" t="inlineStr">
         <is>
           <t>2031673422921564269</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr">
+      <c r="I93" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>{'name': 'Soha.mostafa77', 'screenName': 'Sosomostafa729S', 'followersCount': 345, 'favouritesCount': 22185, 'friendsCount': 967, 'description': 'Moom of 2 🙍\u200d♂️🙍\u200d♀️\nShopping 🛍 food 😋 traveling \nLive in UAE 🇦🇪🕊💕'}</t>
-        </is>
-      </c>
-      <c r="K98" t="n">
-        <v>0</v>
-      </c>
-      <c r="L98" t="n">
-        <v>0</v>
-      </c>
-      <c r="M98" t="n">
-        <v>0</v>
-      </c>
-      <c r="N98" t="n">
-        <v>0</v>
-      </c>
-      <c r="O98" t="inlineStr">
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>{'name': 'Soha.mostafa77', 'screenName': 'Sosomostafa729S', 'followersCount': 345, 'favouritesCount': 22185, 'friendsCount': 968, 'description': 'Moom of 2 🙍\u200d♂️🙍\u200d♀️\nShopping 🛍 food 😋 traveling \nLive in UAE 🇦🇪🕊💕'}</t>
+        </is>
+      </c>
+      <c r="K93" t="n">
+        <v>0</v>
+      </c>
+      <c r="L93" t="n">
+        <v>0</v>
+      </c>
+      <c r="M93" t="n">
+        <v>0</v>
+      </c>
+      <c r="N93" t="n">
+        <v>0</v>
+      </c>
+      <c r="O93" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="P98" t="inlineStr">
+      <c r="P93" t="inlineStr">
         <is>
           <t>2031673422921564269</t>
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="1" t="n">
-        <v>97</v>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2037783775896313876</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>2037783775896313876</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="1" t="n">
+        <v>92</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2037783673144230370</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>2037783673144230370</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
         <is>
           <t>2031673422921564269</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr">
+      <c r="E94" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE/status/2031673422921564269</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr">
+      <c r="F94" t="inlineStr">
         <is>
           <t>نفذت أموال أم خماس قبل نهاية الشهر.
 هناك قاعدة بسيطة تُساعدها على إدارة أموالها بحكمة:
@@ -7479,138 +7118,139 @@
 - Drop your answer below for a chance to win AED 10,000</t>
         </is>
       </c>
-      <c r="G99" t="n">
+      <c r="G94" t="n">
         <v>1773223665000</v>
       </c>
-      <c r="H99" t="inlineStr">
+      <c r="H94" t="inlineStr">
         <is>
           <t>2031673422921564269</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr">
+      <c r="I94" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HDH0NZXWQAAnKTa.jpg', 'type': 'video', 'id': '2031673271423295488'}]</t>
         </is>
       </c>
-      <c r="J99" t="inlineStr">
+      <c r="J94" t="inlineStr">
         <is>
           <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
-      <c r="K99" t="n">
+      <c r="K94" t="n">
         <v>128</v>
       </c>
-      <c r="L99" t="n">
-        <v>0</v>
-      </c>
-      <c r="M99" t="n">
+      <c r="L94" t="n">
+        <v>0</v>
+      </c>
+      <c r="M94" t="n">
         <v>40</v>
       </c>
-      <c r="N99" t="n">
+      <c r="N94" t="n">
         <v>53</v>
       </c>
-      <c r="O99" t="inlineStr">
-        <is>
-          <t>2343</t>
-        </is>
-      </c>
-      <c r="P99" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="1" t="n">
-        <v>98</v>
-      </c>
-      <c r="B100" t="inlineStr">
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>2347</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="n">
+        <v>93</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2037783673144230370</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>2037783673144230370</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>2037783673144230370</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2037783673144230370</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE FINWELL ( Financial Well-being program) with Emirates NBD 
+@Emy191990 @ibushra_03 @SelmaRomola 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="G95" t="n">
+        <v>1774680462000</v>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>2031673422921564269</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>{'name': 'Soha.mostafa77', 'screenName': 'Sosomostafa729S', 'followersCount': 345, 'favouritesCount': 22185, 'friendsCount': 968, 'description': 'Moom of 2 🙍\u200d♂️🙍\u200d♀️\nShopping 🛍 food 😋 traveling \nLive in UAE 🇦🇪🕊💕'}</t>
+        </is>
+      </c>
+      <c r="K95" t="n">
+        <v>0</v>
+      </c>
+      <c r="L95" t="n">
+        <v>0</v>
+      </c>
+      <c r="M95" t="n">
+        <v>0</v>
+      </c>
+      <c r="N95" t="n">
+        <v>0</v>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>2031673422921564269</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="n">
+        <v>94</v>
+      </c>
+      <c r="B96" t="inlineStr">
         <is>
           <t>https://x.com/Sosomostafa729S/status/2037783775896313876</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr">
+      <c r="C96" t="inlineStr">
         <is>
           <t>2037783775896313876</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>2037783775896313876</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2037783775896313876</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE FINWELL ( Financial Well-being program) with Emirates NBD @SelmaRomola @Emy191990 @parulghalout 🌿🇦🇪❤️</t>
-        </is>
-      </c>
-      <c r="G100" t="n">
-        <v>1774680487000</v>
-      </c>
-      <c r="H100" t="inlineStr">
+      <c r="D96" t="inlineStr">
         <is>
           <t>2031673422921564269</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>{'name': 'Soha.mostafa77', 'screenName': 'Sosomostafa729S', 'followersCount': 345, 'favouritesCount': 22185, 'friendsCount': 967, 'description': 'Moom of 2 🙍\u200d♂️🙍\u200d♀️\nShopping 🛍 food 😋 traveling \nLive in UAE 🇦🇪🕊💕'}</t>
-        </is>
-      </c>
-      <c r="K100" t="n">
-        <v>0</v>
-      </c>
-      <c r="L100" t="n">
-        <v>0</v>
-      </c>
-      <c r="M100" t="n">
-        <v>0</v>
-      </c>
-      <c r="N100" t="n">
-        <v>0</v>
-      </c>
-      <c r="O100" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="P100" t="inlineStr">
-        <is>
-          <t>2031673422921564269</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="1" t="n">
-        <v>99</v>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2037783673144230370</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>2037783673144230370</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>2031673422921564269</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
+      <c r="E96" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE/status/2031673422921564269</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr">
+      <c r="F96" t="inlineStr">
         <is>
           <t>نفذت أموال أم خماس قبل نهاية الشهر.
 هناك قاعدة بسيطة تُساعدها على إدارة أموالها بحكمة:
@@ -7637,139 +7277,138 @@
 - Drop your answer below for a chance to win AED 10,000</t>
         </is>
       </c>
-      <c r="G101" t="n">
+      <c r="G96" t="n">
         <v>1773223665000</v>
       </c>
-      <c r="H101" t="inlineStr">
+      <c r="H96" t="inlineStr">
         <is>
           <t>2031673422921564269</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr">
+      <c r="I96" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HDH0NZXWQAAnKTa.jpg', 'type': 'video', 'id': '2031673271423295488'}]</t>
         </is>
       </c>
-      <c r="J101" t="inlineStr">
+      <c r="J96" t="inlineStr">
         <is>
           <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
-      <c r="K101" t="n">
+      <c r="K96" t="n">
         <v>128</v>
       </c>
-      <c r="L101" t="n">
-        <v>0</v>
-      </c>
-      <c r="M101" t="n">
+      <c r="L96" t="n">
+        <v>0</v>
+      </c>
+      <c r="M96" t="n">
         <v>40</v>
       </c>
-      <c r="N101" t="n">
+      <c r="N96" t="n">
         <v>53</v>
       </c>
-      <c r="O101" t="inlineStr">
-        <is>
-          <t>2343</t>
-        </is>
-      </c>
-      <c r="P101" t="inlineStr"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2037783673144230370</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>2037783673144230370</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>2037783673144230370</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2037783673144230370</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE FINWELL ( Financial Well-being program) with Emirates NBD 
-@Emy191990 @ibushra_03 @SelmaRomola 🌿🇦🇪❤️</t>
-        </is>
-      </c>
-      <c r="G102" t="n">
-        <v>1774680462000</v>
-      </c>
-      <c r="H102" t="inlineStr">
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>2347</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2037783775896313876</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>2037783775896313876</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>2037783775896313876</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2037783775896313876</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE FINWELL ( Financial Well-being program) with Emirates NBD @SelmaRomola @Emy191990 @parulghalout 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="G97" t="n">
+        <v>1774680487000</v>
+      </c>
+      <c r="H97" t="inlineStr">
         <is>
           <t>2031673422921564269</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr">
+      <c r="I97" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>{'name': 'Soha.mostafa77', 'screenName': 'Sosomostafa729S', 'followersCount': 345, 'favouritesCount': 22185, 'friendsCount': 967, 'description': 'Moom of 2 🙍\u200d♂️🙍\u200d♀️\nShopping 🛍 food 😋 traveling \nLive in UAE 🇦🇪🕊💕'}</t>
-        </is>
-      </c>
-      <c r="K102" t="n">
-        <v>0</v>
-      </c>
-      <c r="L102" t="n">
-        <v>0</v>
-      </c>
-      <c r="M102" t="n">
-        <v>0</v>
-      </c>
-      <c r="N102" t="n">
-        <v>0</v>
-      </c>
-      <c r="O102" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="P102" t="inlineStr">
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>{'name': 'Soha.mostafa77', 'screenName': 'Sosomostafa729S', 'followersCount': 345, 'favouritesCount': 22185, 'friendsCount': 968, 'description': 'Moom of 2 🙍\u200d♂️🙍\u200d♀️\nShopping 🛍 food 😋 traveling \nLive in UAE 🇦🇪🕊💕'}</t>
+        </is>
+      </c>
+      <c r="K97" t="n">
+        <v>0</v>
+      </c>
+      <c r="L97" t="n">
+        <v>0</v>
+      </c>
+      <c r="M97" t="n">
+        <v>0</v>
+      </c>
+      <c r="N97" t="n">
+        <v>0</v>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
         <is>
           <t>2031673422921564269</t>
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="1" t="n">
-        <v>101</v>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2037783477979091314</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>2037783477979091314</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="1" t="n">
+        <v>96</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2037783335389540775</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>2037783335389540775</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
         <is>
           <t>2034225946308358408</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr">
+      <c r="E98" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE/status/2034225946308358408</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr">
+      <c r="F98" t="inlineStr">
         <is>
           <t>اجعل مفاجآت العيد أكثر قيمة.
 من الفضة إلى الذهب، اكتشف طريقة أذكى لامتلاك أو إهداء شيء ثمين بحق.
@@ -7781,138 +7420,138 @@
 اكتب إجابتك في التعليقات أدناه لفرصة ربح 10,000 درهم</t>
         </is>
       </c>
-      <c r="G103" t="n">
+      <c r="G98" t="n">
         <v>1773832234000</v>
       </c>
-      <c r="H103" t="inlineStr">
+      <c r="H98" t="inlineStr">
         <is>
           <t>2034225946308358408</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr">
+      <c r="I98" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2034225772156563456/img/fizQ3vAEH0uqiLix.jpg', 'type': 'video', 'id': '2034225772156563456'}]</t>
         </is>
       </c>
-      <c r="J103" t="inlineStr">
+      <c r="J98" t="inlineStr">
         <is>
           <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
-      <c r="K103" t="n">
+      <c r="K98" t="n">
         <v>91</v>
       </c>
-      <c r="L103" t="n">
+      <c r="L98" t="n">
         <v>1</v>
       </c>
-      <c r="M103" t="n">
+      <c r="M98" t="n">
         <v>39</v>
       </c>
-      <c r="N103" t="n">
+      <c r="N98" t="n">
         <v>50</v>
       </c>
-      <c r="O103" t="inlineStr">
-        <is>
-          <t>2634</t>
-        </is>
-      </c>
-      <c r="P103" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="1" t="n">
-        <v>102</v>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2037783477979091314</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>2037783477979091314</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>2037783477979091314</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2037783477979091314</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE Through ENBD X Mobile Banking's App @parulghalout @semeet @Emy191990 🌿🇦🇪❤️</t>
-        </is>
-      </c>
-      <c r="G104" t="n">
-        <v>1774680415000</v>
-      </c>
-      <c r="H104" t="inlineStr">
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>2640</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="n">
+        <v>97</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2037783335389540775</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>2037783335389540775</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>2037783335389540775</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2037783335389540775</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE Through ENBD X Mobile Banking's App @Emy191990 @parulghalout @ibushra_03 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="G99" t="n">
+        <v>1774680381000</v>
+      </c>
+      <c r="H99" t="inlineStr">
         <is>
           <t>2034225946308358408</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr">
+      <c r="I99" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>{'name': 'Soha.mostafa77', 'screenName': 'Sosomostafa729S', 'followersCount': 345, 'favouritesCount': 22185, 'friendsCount': 967, 'description': 'Moom of 2 🙍\u200d♂️🙍\u200d♀️\nShopping 🛍 food 😋 traveling \nLive in UAE 🇦🇪🕊💕'}</t>
-        </is>
-      </c>
-      <c r="K104" t="n">
-        <v>0</v>
-      </c>
-      <c r="L104" t="n">
-        <v>0</v>
-      </c>
-      <c r="M104" t="n">
-        <v>0</v>
-      </c>
-      <c r="N104" t="n">
-        <v>0</v>
-      </c>
-      <c r="O104" t="inlineStr">
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>{'name': 'Soha.mostafa77', 'screenName': 'Sosomostafa729S', 'followersCount': 345, 'favouritesCount': 22185, 'friendsCount': 968, 'description': 'Moom of 2 🙍\u200d♂️🙍\u200d♀️\nShopping 🛍 food 😋 traveling \nLive in UAE 🇦🇪🕊💕'}</t>
+        </is>
+      </c>
+      <c r="K99" t="n">
+        <v>0</v>
+      </c>
+      <c r="L99" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" t="n">
+        <v>0</v>
+      </c>
+      <c r="N99" t="n">
+        <v>0</v>
+      </c>
+      <c r="O99" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="P104" t="inlineStr">
+      <c r="P99" t="inlineStr">
         <is>
           <t>2034225946308358408</t>
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="1" t="n">
-        <v>103</v>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2037783335389540775</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>2037783335389540775</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2037783402758508685</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>2037783402758508685</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
         <is>
           <t>2034225946308358408</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr">
+      <c r="E100" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE/status/2034225946308358408</t>
         </is>
       </c>
-      <c r="F105" t="inlineStr">
+      <c r="F100" t="inlineStr">
         <is>
           <t>اجعل مفاجآت العيد أكثر قيمة.
 من الفضة إلى الذهب، اكتشف طريقة أذكى لامتلاك أو إهداء شيء ثمين بحق.
@@ -7924,418 +7563,275 @@
 اكتب إجابتك في التعليقات أدناه لفرصة ربح 10,000 درهم</t>
         </is>
       </c>
-      <c r="G105" t="n">
+      <c r="G100" t="n">
         <v>1773832234000</v>
       </c>
-      <c r="H105" t="inlineStr">
+      <c r="H100" t="inlineStr">
         <is>
           <t>2034225946308358408</t>
         </is>
       </c>
-      <c r="I105" t="inlineStr">
+      <c r="I100" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2034225772156563456/img/fizQ3vAEH0uqiLix.jpg', 'type': 'video', 'id': '2034225772156563456'}]</t>
         </is>
       </c>
-      <c r="J105" t="inlineStr">
+      <c r="J100" t="inlineStr">
         <is>
           <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
-      <c r="K105" t="n">
+      <c r="K100" t="n">
         <v>91</v>
       </c>
-      <c r="L105" t="n">
+      <c r="L100" t="n">
         <v>1</v>
       </c>
-      <c r="M105" t="n">
+      <c r="M100" t="n">
         <v>39</v>
       </c>
-      <c r="N105" t="n">
+      <c r="N100" t="n">
         <v>50</v>
       </c>
-      <c r="O105" t="inlineStr">
-        <is>
-          <t>2634</t>
-        </is>
-      </c>
-      <c r="P105" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="1" t="n">
-        <v>104</v>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2037783335389540775</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>2037783335389540775</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>2037783335389540775</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2037783335389540775</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE Through ENBD X Mobile Banking's App @Emy191990 @parulghalout @ibushra_03 🌿🇦🇪❤️</t>
-        </is>
-      </c>
-      <c r="G106" t="n">
-        <v>1774680381000</v>
-      </c>
-      <c r="H106" t="inlineStr">
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>2640</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="n">
+        <v>99</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2037783402758508685</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>2037783402758508685</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>2037783402758508685</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2037783402758508685</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE Through ENBD X Mobile Banking's App @zeynp_qas @SelmaRomola @Salma2232019 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="G101" t="n">
+        <v>1774680398000</v>
+      </c>
+      <c r="H101" t="inlineStr">
         <is>
           <t>2034225946308358408</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr">
+      <c r="I101" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>{'name': 'Soha.mostafa77', 'screenName': 'Sosomostafa729S', 'followersCount': 345, 'favouritesCount': 22185, 'friendsCount': 967, 'description': 'Moom of 2 🙍\u200d♂️🙍\u200d♀️\nShopping 🛍 food 😋 traveling \nLive in UAE 🇦🇪🕊💕'}</t>
-        </is>
-      </c>
-      <c r="K106" t="n">
-        <v>0</v>
-      </c>
-      <c r="L106" t="n">
-        <v>0</v>
-      </c>
-      <c r="M106" t="n">
-        <v>0</v>
-      </c>
-      <c r="N106" t="n">
-        <v>0</v>
-      </c>
-      <c r="O106" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="P106" t="inlineStr">
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>{'name': 'Soha.mostafa77', 'screenName': 'Sosomostafa729S', 'followersCount': 345, 'favouritesCount': 22185, 'friendsCount': 968, 'description': 'Moom of 2 🙍\u200d♂️🙍\u200d♀️\nShopping 🛍 food 😋 traveling \nLive in UAE 🇦🇪🕊💕'}</t>
+        </is>
+      </c>
+      <c r="K101" t="n">
+        <v>0</v>
+      </c>
+      <c r="L101" t="n">
+        <v>0</v>
+      </c>
+      <c r="M101" t="n">
+        <v>0</v>
+      </c>
+      <c r="N101" t="n">
+        <v>0</v>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
         <is>
           <t>2034225946308358408</t>
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="1" t="n">
-        <v>105</v>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2037783402758508685</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>2037783402758508685</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>2034225946308358408</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2034225946308358408</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>اجعل مفاجآت العيد أكثر قيمة.
-من الفضة إلى الذهب، اكتشف طريقة أذكى لامتلاك أو إهداء شيء ثمين بحق.
-شاهد هذه الحلقة وأخبرنا:
-كيف يمكنك شراء الذهب والفضه من البنك؟
-للمشاركة:
-تابع حساب بنك الإمارات دبي الوطني 
-قم بالإشارة إلى 3 من أصدقائك
-اكتب إجابتك في التعليقات أدناه لفرصة ربح 10,000 درهم</t>
-        </is>
-      </c>
-      <c r="G107" t="n">
-        <v>1773832234000</v>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>2034225946308358408</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2034225772156563456/img/fizQ3vAEH0uqiLix.jpg', 'type': 'video', 'id': '2034225772156563456'}]</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="K107" t="n">
-        <v>91</v>
-      </c>
-      <c r="L107" t="n">
-        <v>1</v>
-      </c>
-      <c r="M107" t="n">
-        <v>39</v>
-      </c>
-      <c r="N107" t="n">
-        <v>50</v>
-      </c>
-      <c r="O107" t="inlineStr">
-        <is>
-          <t>2634</t>
-        </is>
-      </c>
-      <c r="P107" t="inlineStr"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="1" t="n">
-        <v>106</v>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2037783402758508685</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>2037783402758508685</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>2037783402758508685</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2037783402758508685</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE Through ENBD X Mobile Banking's App @zeynp_qas @SelmaRomola @Salma2232019 🌿🇦🇪❤️</t>
-        </is>
-      </c>
-      <c r="G108" t="n">
-        <v>1774680398000</v>
-      </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>2034225946308358408</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>{'name': 'Soha.mostafa77', 'screenName': 'Sosomostafa729S', 'followersCount': 345, 'favouritesCount': 22185, 'friendsCount': 967, 'description': 'Moom of 2 🙍\u200d♂️🙍\u200d♀️\nShopping 🛍 food 😋 traveling \nLive in UAE 🇦🇪🕊💕'}</t>
-        </is>
-      </c>
-      <c r="K108" t="n">
-        <v>0</v>
-      </c>
-      <c r="L108" t="n">
-        <v>0</v>
-      </c>
-      <c r="M108" t="n">
-        <v>0</v>
-      </c>
-      <c r="N108" t="n">
-        <v>0</v>
-      </c>
-      <c r="O108" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="P108" t="inlineStr">
-        <is>
-          <t>2034225946308358408</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="1" t="n">
-        <v>107</v>
-      </c>
-      <c r="B109" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="B102" t="inlineStr">
         <is>
           <t>https://x.com/wil3020/status/2037730056920088898</t>
         </is>
       </c>
-      <c r="C109" t="inlineStr">
+      <c r="C102" t="inlineStr">
         <is>
           <t>2037730056920088898</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr">
+      <c r="D102" t="inlineStr">
         <is>
           <t>2037432200166277382</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr">
+      <c r="E102" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE/status/2037432200166277382</t>
         </is>
       </c>
-      <c r="F109" t="inlineStr">
+      <c r="F102" t="inlineStr">
         <is>
           <t>Stay safe and bank with ease with ENBD X and businessONLINE 
 Visit https://t.co/0Z1tddYvqD https://t.co/l7XrKjfHOu</t>
         </is>
       </c>
-      <c r="G109" t="n">
+      <c r="G102" t="n">
         <v>1774596664000</v>
       </c>
-      <c r="H109" t="inlineStr">
+      <c r="H102" t="inlineStr">
         <is>
           <t>2037432200166277382</t>
         </is>
       </c>
-      <c r="I109" t="inlineStr">
+      <c r="I102" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEZpyN2aMAAR1EU.jpg', 'type': 'photo', 'id': '2037432192863973376'}]</t>
         </is>
       </c>
-      <c r="J109" t="inlineStr">
+      <c r="J102" t="inlineStr">
         <is>
           <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
-      <c r="K109" t="n">
+      <c r="K102" t="n">
         <v>2</v>
       </c>
-      <c r="L109" t="n">
-        <v>0</v>
-      </c>
-      <c r="M109" t="n">
+      <c r="L102" t="n">
+        <v>0</v>
+      </c>
+      <c r="M102" t="n">
         <v>1</v>
       </c>
-      <c r="N109" t="n">
+      <c r="N102" t="n">
         <v>9</v>
       </c>
-      <c r="O109" t="inlineStr">
-        <is>
-          <t>936</t>
-        </is>
-      </c>
-      <c r="P109" t="inlineStr"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="1" t="n">
-        <v>108</v>
-      </c>
-      <c r="B110" t="inlineStr">
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="n">
+        <v>101</v>
+      </c>
+      <c r="B103" t="inlineStr">
         <is>
           <t>https://x.com/wil3020/status/2037730056920088898</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr">
+      <c r="C103" t="inlineStr">
         <is>
           <t>2037730056920088898</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr">
+      <c r="D103" t="inlineStr">
         <is>
           <t>2037730056920088898</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr">
+      <c r="E103" t="inlineStr">
         <is>
           <t>https://x.com/wil3020/status/2037730056920088898</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr">
+      <c r="F103" t="inlineStr">
         <is>
           <t>@EmiratesNBD_AE The UAE is no longer safe Continuous and comprehensive bombing of the UAE now</t>
         </is>
       </c>
-      <c r="G110" t="n">
+      <c r="G103" t="n">
         <v>1774667679000</v>
       </c>
-      <c r="H110" t="inlineStr">
+      <c r="H103" t="inlineStr">
         <is>
           <t>2037432200166277382</t>
         </is>
       </c>
-      <c r="I110" t="inlineStr">
+      <c r="I103" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="J110" t="inlineStr">
+      <c r="J103" t="inlineStr">
         <is>
           <t>{'name': 'wiil', 'screenName': 'wil3020', 'followersCount': 49, 'favouritesCount': 1810, 'friendsCount': 24, 'description': 'تهوى العين من يعجبها، ويهوى العقل من يفهمه، أمّا الروح فلا تهوى إلاّ من يُشبهها.'}</t>
         </is>
       </c>
-      <c r="K110" t="n">
-        <v>0</v>
-      </c>
-      <c r="L110" t="n">
-        <v>0</v>
-      </c>
-      <c r="M110" t="n">
-        <v>0</v>
-      </c>
-      <c r="N110" t="n">
-        <v>0</v>
-      </c>
-      <c r="O110" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="P110" t="inlineStr">
+      <c r="K103" t="n">
+        <v>0</v>
+      </c>
+      <c r="L103" t="n">
+        <v>0</v>
+      </c>
+      <c r="M103" t="n">
+        <v>0</v>
+      </c>
+      <c r="N103" t="n">
+        <v>0</v>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
         <is>
           <t>2037432200166277382</t>
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="1" t="n">
-        <v>109</v>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2037783125854679453</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>2037783125854679453</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="1" t="n">
+        <v>102</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2037783049065390446</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>2037783049065390446</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
         <is>
           <t>2034225964863893587</t>
         </is>
       </c>
-      <c r="E111" t="inlineStr">
+      <c r="E104" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE/status/2034225964863893587</t>
         </is>
       </c>
-      <c r="F111" t="inlineStr">
+      <c r="F104" t="inlineStr">
         <is>
           <t>Make Eid surprises even more valuable.
 From silver to gold, discover a smarter way to own or gift something truly precious.
@@ -8347,138 +7843,139 @@
 Drop your answer below for a chance to win AED 10,000</t>
         </is>
       </c>
-      <c r="G111" t="n">
+      <c r="G104" t="n">
         <v>1773832238000</v>
       </c>
-      <c r="H111" t="inlineStr">
+      <c r="H104" t="inlineStr">
         <is>
           <t>2034225964863893587</t>
         </is>
       </c>
-      <c r="I111" t="inlineStr">
+      <c r="I104" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2034225751092822016/img/ppYucbpuWh6bd_l0.jpg', 'type': 'video', 'id': '2034225751092822016'}]</t>
         </is>
       </c>
-      <c r="J111" t="inlineStr">
+      <c r="J104" t="inlineStr">
         <is>
           <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
-      <c r="K111" t="n">
+      <c r="K104" t="n">
         <v>72</v>
       </c>
-      <c r="L111" t="n">
-        <v>0</v>
-      </c>
-      <c r="M111" t="n">
+      <c r="L104" t="n">
+        <v>0</v>
+      </c>
+      <c r="M104" t="n">
         <v>29</v>
       </c>
-      <c r="N111" t="n">
+      <c r="N104" t="n">
         <v>46</v>
       </c>
-      <c r="O111" t="inlineStr">
-        <is>
-          <t>1677</t>
-        </is>
-      </c>
-      <c r="P111" t="inlineStr"/>
-    </row>
-    <row r="112">
-      <c r="A112" s="1" t="n">
-        <v>110</v>
-      </c>
-      <c r="B112" t="inlineStr">
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>1679</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="n">
+        <v>103</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2037783049065390446</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>2037783049065390446</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>2037783049065390446</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2037783049065390446</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE Through ENBD X Mobile Banking's App 
+@Emy191990 @ibushra_03 @semeet 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="G105" t="n">
+        <v>1774680313000</v>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>2034225964863893587</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>{'name': 'Soha.mostafa77', 'screenName': 'Sosomostafa729S', 'followersCount': 345, 'favouritesCount': 22185, 'friendsCount': 968, 'description': 'Moom of 2 🙍\u200d♂️🙍\u200d♀️\nShopping 🛍 food 😋 traveling \nLive in UAE 🇦🇪🕊💕'}</t>
+        </is>
+      </c>
+      <c r="K105" t="n">
+        <v>0</v>
+      </c>
+      <c r="L105" t="n">
+        <v>0</v>
+      </c>
+      <c r="M105" t="n">
+        <v>0</v>
+      </c>
+      <c r="N105" t="n">
+        <v>0</v>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>2034225964863893587</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="n">
+        <v>104</v>
+      </c>
+      <c r="B106" t="inlineStr">
         <is>
           <t>https://x.com/Sosomostafa729S/status/2037783125854679453</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr">
+      <c r="C106" t="inlineStr">
         <is>
           <t>2037783125854679453</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>2037783125854679453</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2037783125854679453</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE Through ENBD X Mobile Banking's App @parulghalout @Salma2232019 @semeet 🌿🇦🇪❤️</t>
-        </is>
-      </c>
-      <c r="G112" t="n">
-        <v>1774680332000</v>
-      </c>
-      <c r="H112" t="inlineStr">
+      <c r="D106" t="inlineStr">
         <is>
           <t>2034225964863893587</t>
         </is>
       </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>{'name': 'Soha.mostafa77', 'screenName': 'Sosomostafa729S', 'followersCount': 345, 'favouritesCount': 22185, 'friendsCount': 967, 'description': 'Moom of 2 🙍\u200d♂️🙍\u200d♀️\nShopping 🛍 food 😋 traveling \nLive in UAE 🇦🇪🕊💕'}</t>
-        </is>
-      </c>
-      <c r="K112" t="n">
-        <v>0</v>
-      </c>
-      <c r="L112" t="n">
-        <v>0</v>
-      </c>
-      <c r="M112" t="n">
-        <v>0</v>
-      </c>
-      <c r="N112" t="n">
-        <v>0</v>
-      </c>
-      <c r="O112" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="P112" t="inlineStr">
-        <is>
-          <t>2034225964863893587</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="1" t="n">
-        <v>111</v>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2037783049065390446</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>2037783049065390446</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>2034225964863893587</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
+      <c r="E106" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE/status/2034225964863893587</t>
         </is>
       </c>
-      <c r="F113" t="inlineStr">
+      <c r="F106" t="inlineStr">
         <is>
           <t>Make Eid surprises even more valuable.
 From silver to gold, discover a smarter way to own or gift something truly precious.
@@ -8490,109 +7987,108 @@
 Drop your answer below for a chance to win AED 10,000</t>
         </is>
       </c>
-      <c r="G113" t="n">
+      <c r="G106" t="n">
         <v>1773832238000</v>
       </c>
-      <c r="H113" t="inlineStr">
+      <c r="H106" t="inlineStr">
         <is>
           <t>2034225964863893587</t>
         </is>
       </c>
-      <c r="I113" t="inlineStr">
+      <c r="I106" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2034225751092822016/img/ppYucbpuWh6bd_l0.jpg', 'type': 'video', 'id': '2034225751092822016'}]</t>
         </is>
       </c>
-      <c r="J113" t="inlineStr">
+      <c r="J106" t="inlineStr">
         <is>
           <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
-      <c r="K113" t="n">
+      <c r="K106" t="n">
         <v>72</v>
       </c>
-      <c r="L113" t="n">
-        <v>0</v>
-      </c>
-      <c r="M113" t="n">
+      <c r="L106" t="n">
+        <v>0</v>
+      </c>
+      <c r="M106" t="n">
         <v>29</v>
       </c>
-      <c r="N113" t="n">
+      <c r="N106" t="n">
         <v>46</v>
       </c>
-      <c r="O113" t="inlineStr">
-        <is>
-          <t>1677</t>
-        </is>
-      </c>
-      <c r="P113" t="inlineStr"/>
-    </row>
-    <row r="114">
-      <c r="A114" s="1" t="n">
-        <v>112</v>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2037783049065390446</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>2037783049065390446</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>2037783049065390446</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2037783049065390446</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE Through ENBD X Mobile Banking's App 
-@Emy191990 @ibushra_03 @semeet 🌿🇦🇪❤️</t>
-        </is>
-      </c>
-      <c r="G114" t="n">
-        <v>1774680313000</v>
-      </c>
-      <c r="H114" t="inlineStr">
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>1679</t>
+        </is>
+      </c>
+      <c r="P106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="n">
+        <v>105</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2037783125854679453</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>2037783125854679453</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>2037783125854679453</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2037783125854679453</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE Through ENBD X Mobile Banking's App @parulghalout @Salma2232019 @semeet 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="G107" t="n">
+        <v>1774680332000</v>
+      </c>
+      <c r="H107" t="inlineStr">
         <is>
           <t>2034225964863893587</t>
         </is>
       </c>
-      <c r="I114" t="inlineStr">
+      <c r="I107" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="J114" t="inlineStr">
-        <is>
-          <t>{'name': 'Soha.mostafa77', 'screenName': 'Sosomostafa729S', 'followersCount': 345, 'favouritesCount': 22185, 'friendsCount': 967, 'description': 'Moom of 2 🙍\u200d♂️🙍\u200d♀️\nShopping 🛍 food 😋 traveling \nLive in UAE 🇦🇪🕊💕'}</t>
-        </is>
-      </c>
-      <c r="K114" t="n">
-        <v>0</v>
-      </c>
-      <c r="L114" t="n">
-        <v>0</v>
-      </c>
-      <c r="M114" t="n">
-        <v>0</v>
-      </c>
-      <c r="N114" t="n">
-        <v>0</v>
-      </c>
-      <c r="O114" t="inlineStr">
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>{'name': 'Soha.mostafa77', 'screenName': 'Sosomostafa729S', 'followersCount': 345, 'favouritesCount': 22185, 'friendsCount': 968, 'description': 'Moom of 2 🙍\u200d♂️🙍\u200d♀️\nShopping 🛍 food 😋 traveling \nLive in UAE 🇦🇪🕊💕'}</t>
+        </is>
+      </c>
+      <c r="K107" t="n">
+        <v>0</v>
+      </c>
+      <c r="L107" t="n">
+        <v>0</v>
+      </c>
+      <c r="M107" t="n">
+        <v>0</v>
+      </c>
+      <c r="N107" t="n">
+        <v>0</v>
+      </c>
+      <c r="O107" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="P114" t="inlineStr">
+      <c r="P107" t="inlineStr">
         <is>
           <t>2034225964863893587</t>
         </is>

--- a/Xpost_df_comments.xlsx
+++ b/Xpost_df_comments.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P107"/>
+  <dimension ref="A1:P109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,163 +511,301 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037936526093430909</t>
+          <t>https://x.com/Rita09729643/status/2037955706662604958</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2037936526093430909</t>
+          <t>2037955706662604958</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>2037895388909142325</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2037895388909142325</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Get guaranteed vouchers worth of AED750
+Apply for Emirates NBD noon One Visa Credit Card and receive a guaranteed Majid Al Futtaim voucher worth AED 750.
+https://t.co/Rj1kVb2Rck https://t.co/MQajcVjmt6</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>1774707097000</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2037895388909142325</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEgPDX9WsAEtE9T.jpg', 'type': 'photo', 'id': '2037895382030528513'}]</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174061, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>665</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>https://x.com/Rita09729643/status/2037955706662604958</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2037955706662604958</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2037955706662604958</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>https://x.com/Rita09729643/status/2037955706662604958</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE Hi I have a credit card of Emirates NBD, but I haven’t used it for many years, suddenly I received the email of statement that I need to pay 764.13AED as the total payment due, this is really unacceptable.</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>1774721478000</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2037895388909142325</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>{'name': 'Rita', 'screenName': 'Rita09729643', 'followersCount': 2, 'favouritesCount': 51, 'friendsCount': 24, 'description': 'Hi'}</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2037895388909142325</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>https://x.com/cruizomfs/status/2037928218003382573</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2037928218003382573</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>2037801868244533349</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE/status/2037801868244533349</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>What’s more suspicious?
 Stay Safe, Stay Vigilant. #UnitedAgainstFraud
 https://t.co/YpRWtBZrhq</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="G4" t="n">
         <v>1774684800000</v>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>2037801868244533349</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174061, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
         <v>2</v>
       </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>4</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>512</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>506</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>https://x.com/cruizomfs/status/2037928218003382573</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2037928218003382573</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2037911596106715381</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>https://x.com/cruizomfs/status/2037911596106715381</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE Hello. Do I need a residency in order to open an account?</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>1774710961000</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2037801868244533349</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>{'name': 'Los 🥚 De Donald Trump 🇺🇸', 'screenName': 'cruizomfs', 'followersCount': 456, 'favouritesCount': 14453, 'friendsCount': 1923, 'description': 'libre.'}</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
         <v>1</v>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037936526093430909</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2037936526093430909</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2037911596106715381</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>https://x.com/cruizomfs/status/2037911596106715381</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE Hello. Do I need a residency in order to open an account?</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>1774710961000</v>
-      </c>
-      <c r="H3" t="inlineStr">
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
         <is>
           <t>2037801868244533349</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>{'name': 'Los 🥚 De Donald Trump 🇺🇸', 'screenName': 'cruizomfs', 'followersCount': 456, 'favouritesCount': 14498, 'friendsCount': 1923, 'description': 'libre.'}</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2037801868244533349</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037936526093430909</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2037936526093430909</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>https://x.com/cruizomfs/status/2037928218003382573</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2037928218003382573</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
         <is>
           <t>2037921044221010067</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE/status/2037921044221010067</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Hi, thank you for reaching out, please be informed that you can apply for non-resident account by a visit to one of our branches within the UAE.
 Documents:
@@ -688,166 +826,26 @@
 (Bill should not be more than 3 months old)</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="G6" t="n">
         <v>1774713214000</v>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>2037801868244533349</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174061, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
         <v>1</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2037911596106715381</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037936526093430909</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>2037936526093430909</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2037928218003382573</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>https://x.com/cruizomfs/status/2037928218003382573</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE I just got back from the UAE, is there any chance I can start the process online. I'll probably go again in august.</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>1774714924000</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>2037801868244533349</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>{'name': 'Los 🥚 De Donald Trump 🇺🇸', 'screenName': 'cruizomfs', 'followersCount': 456, 'favouritesCount': 14498, 'friendsCount': 1923, 'description': 'libre.'}</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2037921044221010067</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037936526093430909</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>2037936526093430909</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2037936526093430909</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037936526093430909</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>@cruizomfs We regret to inform you that this process can be done only by a branch visit within the UAE.</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>1774716905000</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>2037801868244533349</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -860,12 +858,12 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>11</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2037928218003382573</t>
+          <t>2037911596106715381</t>
         </is>
       </c>
     </row>
@@ -875,67 +873,69 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://x.com/Rita09729643/status/2037955706662604958</t>
+          <t>https://x.com/cruizomfs/status/2037928218003382573</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2037955706662604958</t>
+          <t>2037928218003382573</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2037895388909142325</t>
+          <t>2037928218003382573</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037895388909142325</t>
+          <t>https://x.com/cruizomfs/status/2037928218003382573</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Get guaranteed vouchers worth of AED750
-Apply for Emirates NBD noon One Visa Credit Card and receive a guaranteed Majid Al Futtaim voucher worth AED 750.
-https://t.co/Rj1kVb2Rck https://t.co/MQajcVjmt6</t>
+          <t>@EmiratesNBD_AE I just got back from the UAE, is there any chance I can start the process online. I'll probably go again in august.</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1774707097000</v>
+        <v>1774714924000</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2037895388909142325</t>
+          <t>2037801868244533349</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEgPDX9WsAEtE9T.jpg', 'type': 'photo', 'id': '2037895382030528513'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Los 🥚 De Donald Trump 🇺🇸', 'screenName': 'cruizomfs', 'followersCount': 456, 'favouritesCount': 14453, 'friendsCount': 1923, 'description': 'libre.'}</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>651</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr"/>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2037921044221010067</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -943,35 +943,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>https://x.com/Rita09729643/status/2037955706662604958</t>
+          <t>https://x.com/cruizomfs/status/2037928218003382573</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2037955706662604958</t>
+          <t>2037928218003382573</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2037955706662604958</t>
+          <t>2037936526093430909</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://x.com/Rita09729643/status/2037955706662604958</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2037936526093430909</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Hi I have a credit card of Emirates NBD, but I haven’t used it for many years, suddenly I received the email of statement that I need to pay 764.13AED as the total payment due, this is really unacceptable.</t>
+          <t>@cruizomfs We regret to inform you that this process can be done only by a branch visit within the UAE.</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1774721478000</v>
+        <v>1774716905000</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2037895388909142325</t>
+          <t>2037801868244533349</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -981,29 +981,29 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>{'name': 'Rita', 'screenName': 'Rita09729643', 'followersCount': 2, 'favouritesCount': 51, 'friendsCount': 24, 'description': 'Hi'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174061, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
         <v>1</v>
       </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>19</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2037895388909142325</t>
+          <t>2037928218003382573</t>
         </is>
       </c>
     </row>
@@ -1013,12 +1013,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>https://x.com/cruizomfs/status/2037928218003382573</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2037936526093430909</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2037928218003382573</t>
+          <t>2037936526093430909</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1053,7 +1053,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174061, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -1066,11 +1066,11 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>506</t>
+          <t>512</t>
         </is>
       </c>
       <c r="P9" t="inlineStr"/>
@@ -1081,12 +1081,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>https://x.com/cruizomfs/status/2037928218003382573</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2037936526093430909</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2037928218003382573</t>
+          <t>2037936526093430909</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>{'name': 'Los 🥚 De Donald Trump 🇺🇸', 'screenName': 'cruizomfs', 'followersCount': 456, 'favouritesCount': 14498, 'friendsCount': 1923, 'description': 'libre.'}</t>
+          <t>{'name': 'Los 🥚 De Donald Trump 🇺🇸', 'screenName': 'cruizomfs', 'followersCount': 456, 'favouritesCount': 14453, 'friendsCount': 1923, 'description': 'libre.'}</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1151,12 +1151,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>https://x.com/cruizomfs/status/2037928218003382573</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2037936526093430909</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2037928218003382573</t>
+          <t>2037936526093430909</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174061, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>https://x.com/cruizomfs/status/2037928218003382573</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2037936526093430909</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2037928218003382573</t>
+          <t>2037936526093430909</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>{'name': 'Los 🥚 De Donald Trump 🇺🇸', 'screenName': 'cruizomfs', 'followersCount': 456, 'favouritesCount': 14498, 'friendsCount': 1923, 'description': 'libre.'}</t>
+          <t>{'name': 'Los 🥚 De Donald Trump 🇺🇸', 'screenName': 'cruizomfs', 'followersCount': 456, 'favouritesCount': 14453, 'friendsCount': 1923, 'description': 'libre.'}</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1307,12 +1307,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>https://x.com/cruizomfs/status/2037928218003382573</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2037936526093430909</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2037928218003382573</t>
+          <t>2037936526093430909</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174061, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1377,12 +1377,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>https://x.com/cruizomfs/status/2037911596106715381</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2037921044221010067</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2037911596106715381</t>
+          <t>2037921044221010067</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174061, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1430,11 +1430,11 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>506</t>
+          <t>512</t>
         </is>
       </c>
       <c r="P14" t="inlineStr"/>
@@ -1445,12 +1445,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>https://x.com/cruizomfs/status/2037911596106715381</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2037921044221010067</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2037911596106715381</t>
+          <t>2037921044221010067</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>{'name': 'Los 🥚 De Donald Trump 🇺🇸', 'screenName': 'cruizomfs', 'followersCount': 456, 'favouritesCount': 14453, 'friendsCount': 1923, 'description': 'libre.'}</t>
+          <t>{'name': 'Los 🥚 De Donald Trump 🇺🇸', 'screenName': 'cruizomfs', 'followersCount': 456, 'favouritesCount': 14498, 'friendsCount': 1923, 'description': 'libre.'}</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -1515,12 +1515,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>https://x.com/cruizomfs/status/2037911596106715381</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2037921044221010067</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2037911596106715381</t>
+          <t>2037921044221010067</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174061, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -1611,108 +1611,112 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>2037928218003382573</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>https://x.com/cruizomfs/status/2037928218003382573</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE I just got back from the UAE, is there any chance I can start the process online. I'll probably go again in august.</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>1774714924000</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
           <t>2037801868244533349</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>{'name': 'Los 🥚 De Donald Trump 🇺🇸', 'screenName': 'cruizomfs', 'followersCount': 456, 'favouritesCount': 14498, 'friendsCount': 1923, 'description': 'libre.'}</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>2037921044221010067</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>https://x.com/cruizomfs/status/2037911596106715381</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2037911596106715381</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2037801868244533349</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE/status/2037801868244533349</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>What’s more suspicious?
 Stay Safe, Stay Vigilant. #UnitedAgainstFraud
 https://t.co/YpRWtBZrhq</t>
         </is>
       </c>
-      <c r="G17" t="n">
+      <c r="G18" t="n">
         <v>1774684800000</v>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>2037801868244533349</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="K17" t="n">
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174061, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
         <v>2</v>
       </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>3</v>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>506</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037921044221010067</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>2037921044221010067</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2037911596106715381</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>https://x.com/cruizomfs/status/2037911596106715381</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE Hello. Do I need a residency in order to open an account?</t>
-        </is>
-      </c>
-      <c r="G18" t="n">
-        <v>1774710961000</v>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>2037801868244533349</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>{'name': 'Los 🥚 De Donald Trump 🇺🇸', 'screenName': 'cruizomfs', 'followersCount': 456, 'favouritesCount': 14498, 'friendsCount': 1923, 'description': 'libre.'}</t>
-        </is>
-      </c>
-      <c r="K18" t="n">
-        <v>1</v>
-      </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
@@ -1720,18 +1724,14 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>2037801868244533349</t>
-        </is>
-      </c>
+          <t>512</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
@@ -1739,25 +1739,95 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
+          <t>https://x.com/cruizomfs/status/2037911596106715381</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2037911596106715381</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2037911596106715381</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>https://x.com/cruizomfs/status/2037911596106715381</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE Hello. Do I need a residency in order to open an account?</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>1774710961000</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>2037801868244533349</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>{'name': 'Los 🥚 De Donald Trump 🇺🇸', 'screenName': 'cruizomfs', 'followersCount': 456, 'favouritesCount': 14453, 'friendsCount': 1923, 'description': 'libre.'}</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>2037801868244533349</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>https://x.com/cruizomfs/status/2037911596106715381</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2037911596106715381</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2037921044221010067</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>https://x.com/EmiratesNBD_AE/status/2037921044221010067</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>2037921044221010067</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2037921044221010067</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037921044221010067</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>Hi, thank you for reaching out, please be informed that you can apply for non-resident account by a visit to one of our branches within the UAE.
 Documents:
@@ -1778,92 +1848,22 @@
 (Bill should not be more than 3 months old)</t>
         </is>
       </c>
-      <c r="G19" t="n">
+      <c r="G20" t="n">
         <v>1774713214000</v>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>2037801868244533349</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="K19" t="n">
-        <v>1</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>1</v>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>2037911596106715381</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037921044221010067</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>2037921044221010067</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>2037928218003382573</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>https://x.com/cruizomfs/status/2037928218003382573</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE I just got back from the UAE, is there any chance I can start the process online. I'll probably go again in august.</t>
-        </is>
-      </c>
-      <c r="G20" t="n">
-        <v>1774714924000</v>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>2037801868244533349</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>{'name': 'Los 🥚 De Donald Trump 🇺🇸', 'screenName': 'cruizomfs', 'followersCount': 456, 'favouritesCount': 14498, 'friendsCount': 1923, 'description': 'libre.'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174061, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -1876,16 +1876,16 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2037921044221010067</t>
+          <t>2037911596106715381</t>
         </is>
       </c>
     </row>
@@ -1895,1067 +1895,1067 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
+          <t>https://x.com/rated_sm/status/2037867679802122593</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2037867679802122593</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2037865010320539854</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>https://x.com/rated_sm/status/2037865010320539854</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE My phone is broken and is pending repair with Apple. I need to make a payment and I logged into the website using OTP, but when attempting payment, its still asking for Smart Pass confirmation and no OTP option. Same when attempting to contact Whatsapp Support.</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>1774699854000</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>2037865010320539854</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>{'name': 'rated_sm', 'screenName': 'rated_sm', 'followersCount': 42, 'favouritesCount': 119, 'friendsCount': 122, 'description': ''}</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>https://x.com/rated_sm/status/2037867679802122593</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2037867679802122593</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2037866970410811411</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2037866970410811411</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>@rated_sm We sincerely regret for the inconvenience To be able to assist further, we kindly request you to reach out to us at 
+social@emiratesnbd.com
+Quoting case #989891 in the subject line of the email from your registered email address We will make every effort to address the matter</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>1774700322000</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>2037865010320539854</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174061, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>2037865010320539854</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>https://x.com/rated_sm/status/2037867679802122593</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2037867679802122593</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2037867679802122593</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>https://x.com/rated_sm/status/2037867679802122593</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE I was hoping for a more immediate support and solution cause inability to make this payment will cause me to incur a large overlimit fee.</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>1774700491000</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>2037865010320539854</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>{'name': 'rated_sm', 'screenName': 'rated_sm', 'followersCount': 42, 'favouritesCount': 119, 'friendsCount': 122, 'description': ''}</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>1</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>2037866970410811411</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>https://x.com/rated_sm/status/2037867679802122593</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2037867679802122593</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2037873211728081164</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2037873211728081164</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>@rated_sm Please note that we don't have access to your profile from this channel due to security reasons, so kindly share the details through email, so we can check accordingly</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>1774701810000</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>2037865010320539854</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174061, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>2037867679802122593</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2037873211728081164</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2037873211728081164</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2037865010320539854</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>https://x.com/rated_sm/status/2037865010320539854</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE My phone is broken and is pending repair with Apple. I need to make a payment and I logged into the website using OTP, but when attempting payment, its still asking for Smart Pass confirmation and no OTP option. Same when attempting to contact Whatsapp Support.</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>1774699854000</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>2037865010320539854</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>{'name': 'rated_sm', 'screenName': 'rated_sm', 'followersCount': 42, 'favouritesCount': 119, 'friendsCount': 122, 'description': ''}</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>1</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2037873211728081164</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2037873211728081164</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2037866970410811411</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2037866970410811411</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>@rated_sm We sincerely regret for the inconvenience To be able to assist further, we kindly request you to reach out to us at 
+social@emiratesnbd.com
+Quoting case #989891 in the subject line of the email from your registered email address We will make every effort to address the matter</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>1774700322000</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>2037865010320539854</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174061, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>1</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>2037865010320539854</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2037873211728081164</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2037873211728081164</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2037867679802122593</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>https://x.com/rated_sm/status/2037867679802122593</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE I was hoping for a more immediate support and solution cause inability to make this payment will cause me to incur a large overlimit fee.</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>1774700491000</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>2037865010320539854</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>{'name': 'rated_sm', 'screenName': 'rated_sm', 'followersCount': 42, 'favouritesCount': 119, 'friendsCount': 122, 'description': ''}</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>1</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>2037866970410811411</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2037873211728081164</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2037873211728081164</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2037873211728081164</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2037873211728081164</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>@rated_sm Please note that we don't have access to your profile from this channel due to security reasons, so kindly share the details through email, so we can check accordingly</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>1774701810000</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>2037865010320539854</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174061, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>2037867679802122593</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
           <t>https://x.com/EmiratesNBD_AE/status/2037895388909142325</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>2037895388909142325</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>2037895388909142325</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE/status/2037895388909142325</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>Get guaranteed vouchers worth of AED750
 Apply for Emirates NBD noon One Visa Credit Card and receive a guaranteed Majid Al Futtaim voucher worth AED 750.
 https://t.co/Rj1kVb2Rck https://t.co/MQajcVjmt6</t>
         </is>
       </c>
-      <c r="G21" t="n">
+      <c r="G29" t="n">
         <v>1774707097000</v>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>2037895388909142325</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEgPDX9WsAEtE9T.jpg', 'type': 'photo', 'id': '2037895382030528513'}]</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="K21" t="n">
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174061, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
         <v>2</v>
       </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
         <v>1</v>
       </c>
-      <c r="N21" t="n">
-        <v>2</v>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>652</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="B22" t="inlineStr">
+      <c r="N29" t="n">
+        <v>3</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>666</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE/status/2037895388909142325</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>2037895388909142325</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>2037955706662604958</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>https://x.com/Rita09729643/status/2037955706662604958</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>@EmiratesNBD_AE Hi I have a credit card of Emirates NBD, but I haven’t used it for many years, suddenly I received the email of statement that I need to pay 764.13AED as the total payment due, this is really unacceptable.</t>
         </is>
       </c>
-      <c r="G22" t="n">
+      <c r="G30" t="n">
         <v>1774721478000</v>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>2037895388909142325</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>{'name': 'Rita', 'screenName': 'Rita09729643', 'followersCount': 2, 'favouritesCount': 51, 'friendsCount': 24, 'description': 'Hi'}</t>
         </is>
       </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
         <v>1</v>
       </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
         <is>
           <t>2037895388909142325</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="B23" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE/status/2037895388909142325</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>2037895388909142325</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>2037801868244533349</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE/status/2037801868244533349</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>What’s more suspicious?
 Stay Safe, Stay Vigilant. #UnitedAgainstFraud
 https://t.co/YpRWtBZrhq</t>
         </is>
       </c>
-      <c r="G23" t="n">
+      <c r="G31" t="n">
         <v>1774684800000</v>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>2037801868244533349</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="K23" t="n">
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174061, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
         <v>2</v>
       </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>3</v>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>506</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>https://x.com/rated_sm/status/2037867679802122593</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>2037867679802122593</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>4</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>513</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2037866970410811411</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2037866970410811411</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
         <is>
           <t>2037865010320539854</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>https://x.com/rated_sm/status/2037865010320539854</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>@EmiratesNBD_AE My phone is broken and is pending repair with Apple. I need to make a payment and I logged into the website using OTP, but when attempting payment, its still asking for Smart Pass confirmation and no OTP option. Same when attempting to contact Whatsapp Support.</t>
         </is>
       </c>
-      <c r="G24" t="n">
+      <c r="G32" t="n">
         <v>1774699854000</v>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>2037865010320539854</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>{'name': 'rated_sm', 'screenName': 'rated_sm', 'followersCount': 42, 'favouritesCount': 119, 'friendsCount': 122, 'description': ''}</t>
         </is>
       </c>
-      <c r="K24" t="n">
+      <c r="K32" t="n">
         <v>1</v>
       </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>https://x.com/rated_sm/status/2037867679802122593</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>2037867679802122593</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2037866970410811411</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
         <is>
           <t>2037866970410811411</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2037866970410811411</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE/status/2037866970410811411</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>@rated_sm We sincerely regret for the inconvenience To be able to assist further, we kindly request you to reach out to us at 
 social@emiratesnbd.com
 Quoting case #989891 in the subject line of the email from your registered email address We will make every effort to address the matter</t>
         </is>
       </c>
-      <c r="G25" t="n">
+      <c r="G33" t="n">
         <v>1774700322000</v>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>2037865010320539854</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="K25" t="n">
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174061, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
         <v>1</v>
       </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="inlineStr">
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>2037865010320539854</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2037866970410811411</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2037866970410811411</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2037867679802122593</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>https://x.com/rated_sm/status/2037867679802122593</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE I was hoping for a more immediate support and solution cause inability to make this payment will cause me to incur a large overlimit fee.</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>1774700491000</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>2037865010320539854</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>{'name': 'rated_sm', 'screenName': 'rated_sm', 'followersCount': 42, 'favouritesCount': 119, 'friendsCount': 122, 'description': ''}</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>1</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>2037866970410811411</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>https://x.com/rated_sm/status/2037865010320539854</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
         <is>
           <t>2037865010320539854</t>
         </is>
       </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>https://x.com/rated_sm/status/2037867679802122593</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>2037867679802122593</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>2037867679802122593</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>https://x.com/rated_sm/status/2037867679802122593</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE I was hoping for a more immediate support and solution cause inability to make this payment will cause me to incur a large overlimit fee.</t>
-        </is>
-      </c>
-      <c r="G26" t="n">
-        <v>1774700491000</v>
-      </c>
-      <c r="H26" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>2037865010320539854</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>https://x.com/rated_sm/status/2037865010320539854</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE My phone is broken and is pending repair with Apple. I need to make a payment and I logged into the website using OTP, but when attempting payment, its still asking for Smart Pass confirmation and no OTP option. Same when attempting to contact Whatsapp Support.</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>1774699854000</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>2037865010320539854</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>{'name': 'rated_sm', 'screenName': 'rated_sm', 'followersCount': 42, 'favouritesCount': 119, 'friendsCount': 122, 'description': ''}</t>
         </is>
       </c>
-      <c r="K26" t="n">
+      <c r="K35" t="n">
         <v>1</v>
       </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>https://x.com/rated_sm/status/2037865010320539854</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2037865010320539854</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
         <is>
           <t>2037866970410811411</t>
         </is>
       </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>https://x.com/rated_sm/status/2037867679802122593</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>2037867679802122593</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>2037873211728081164</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037873211728081164</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>@rated_sm Please note that we don't have access to your profile from this channel due to security reasons, so kindly share the details through email, so we can check accordingly</t>
-        </is>
-      </c>
-      <c r="G27" t="n">
-        <v>1774701810000</v>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>2037865010320539854</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>2037867679802122593</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037873211728081164</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>2037873211728081164</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>2037865010320539854</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>https://x.com/rated_sm/status/2037865010320539854</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE My phone is broken and is pending repair with Apple. I need to make a payment and I logged into the website using OTP, but when attempting payment, its still asking for Smart Pass confirmation and no OTP option. Same when attempting to contact Whatsapp Support.</t>
-        </is>
-      </c>
-      <c r="G28" t="n">
-        <v>1774699854000</v>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>2037865010320539854</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>{'name': 'rated_sm', 'screenName': 'rated_sm', 'followersCount': 42, 'favouritesCount': 119, 'friendsCount': 122, 'description': ''}</t>
-        </is>
-      </c>
-      <c r="K28" t="n">
-        <v>1</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037873211728081164</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>2037873211728081164</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>2037866970410811411</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE/status/2037866970410811411</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>@rated_sm We sincerely regret for the inconvenience To be able to assist further, we kindly request you to reach out to us at 
 social@emiratesnbd.com
 Quoting case #989891 in the subject line of the email from your registered email address We will make every effort to address the matter</t>
         </is>
       </c>
-      <c r="G29" t="n">
-        <v>1774700322000</v>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>2037865010320539854</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="K29" t="n">
-        <v>1</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>2037865010320539854</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="n">
-        <v>28</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037873211728081164</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>2037873211728081164</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>2037867679802122593</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>https://x.com/rated_sm/status/2037867679802122593</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE I was hoping for a more immediate support and solution cause inability to make this payment will cause me to incur a large overlimit fee.</t>
-        </is>
-      </c>
-      <c r="G30" t="n">
-        <v>1774700491000</v>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>2037865010320539854</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>{'name': 'rated_sm', 'screenName': 'rated_sm', 'followersCount': 42, 'favouritesCount': 119, 'friendsCount': 122, 'description': ''}</t>
-        </is>
-      </c>
-      <c r="K30" t="n">
-        <v>1</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>2037866970410811411</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="n">
-        <v>29</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037873211728081164</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>2037873211728081164</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>2037873211728081164</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037873211728081164</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>@rated_sm Please note that we don't have access to your profile from this channel due to security reasons, so kindly share the details through email, so we can check accordingly</t>
-        </is>
-      </c>
-      <c r="G31" t="n">
-        <v>1774701810000</v>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>2037865010320539854</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>2037867679802122593</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="n">
-        <v>30</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037866970410811411</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>2037866970410811411</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>2037865010320539854</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>https://x.com/rated_sm/status/2037865010320539854</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE My phone is broken and is pending repair with Apple. I need to make a payment and I logged into the website using OTP, but when attempting payment, its still asking for Smart Pass confirmation and no OTP option. Same when attempting to contact Whatsapp Support.</t>
-        </is>
-      </c>
-      <c r="G32" t="n">
-        <v>1774699854000</v>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>2037865010320539854</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>{'name': 'rated_sm', 'screenName': 'rated_sm', 'followersCount': 42, 'favouritesCount': 119, 'friendsCount': 122, 'description': ''}</t>
-        </is>
-      </c>
-      <c r="K32" t="n">
-        <v>1</v>
-      </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="n">
-        <v>31</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037866970410811411</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>2037866970410811411</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>2037866970410811411</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037866970410811411</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>@rated_sm We sincerely regret for the inconvenience To be able to assist further, we kindly request you to reach out to us at 
-social@emiratesnbd.com
-Quoting case #989891 in the subject line of the email from your registered email address We will make every effort to address the matter</t>
-        </is>
-      </c>
-      <c r="G33" t="n">
-        <v>1774700322000</v>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>2037865010320539854</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="K33" t="n">
-        <v>1</v>
-      </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>2037865010320539854</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="n">
-        <v>32</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037866970410811411</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>2037866970410811411</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>2037867679802122593</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>https://x.com/rated_sm/status/2037867679802122593</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE I was hoping for a more immediate support and solution cause inability to make this payment will cause me to incur a large overlimit fee.</t>
-        </is>
-      </c>
-      <c r="G34" t="n">
-        <v>1774700491000</v>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>2037865010320539854</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>{'name': 'rated_sm', 'screenName': 'rated_sm', 'followersCount': 42, 'favouritesCount': 119, 'friendsCount': 122, 'description': ''}</t>
-        </is>
-      </c>
-      <c r="K34" t="n">
-        <v>1</v>
-      </c>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>2037866970410811411</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="n">
-        <v>33</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>https://x.com/rated_sm/status/2037865010320539854</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>2037865010320539854</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>2037865010320539854</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>https://x.com/rated_sm/status/2037865010320539854</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE My phone is broken and is pending repair with Apple. I need to make a payment and I logged into the website using OTP, but when attempting payment, its still asking for Smart Pass confirmation and no OTP option. Same when attempting to contact Whatsapp Support.</t>
-        </is>
-      </c>
-      <c r="G35" t="n">
-        <v>1774699854000</v>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>2037865010320539854</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>{'name': 'rated_sm', 'screenName': 'rated_sm', 'followersCount': 42, 'favouritesCount': 119, 'friendsCount': 122, 'description': ''}</t>
-        </is>
-      </c>
-      <c r="K35" t="n">
-        <v>1</v>
-      </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="n">
-        <v>34</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>https://x.com/rated_sm/status/2037865010320539854</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>2037865010320539854</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>2037866970410811411</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037866970410811411</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>@rated_sm We sincerely regret for the inconvenience To be able to assist further, we kindly request you to reach out to us at 
-social@emiratesnbd.com
-Quoting case #989891 in the subject line of the email from your registered email address We will make every effort to address the matter</t>
-        </is>
-      </c>
       <c r="G36" t="n">
         <v>1774700322000</v>
       </c>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174061, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="K36" t="n">
@@ -2988,7 +2988,7 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -3003,49 +3003,50 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>https://x.com/eazyislit/status/2037804608517509572</t>
+          <t>https://x.com/Talal_Hus/status/2037818020597215557</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2037804608517509572</t>
+          <t>2037818020597215557</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2037804608517509572</t>
+          <t>2037818020597215557</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://x.com/eazyislit/status/2037804608517509572</t>
+          <t>https://x.com/Talal_Hus/status/2037818020597215557</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>THE WOMAN DAT CARRIED YOU FOR 9 MONTHS MAY SHE LIVE LONG AND WITNESS YOU SUCCEED 🤍 https://t.co/0XDJyqkART</t>
+          <t>@EmiratesNBD_KSA بالنسبة للتقسيط بدون هامش ربح هل لو سددت من خلال الفيزا ابل باي اقدر استفيد من العرض ؟ 
+يعني ععندب في نون اشتري ابل باي وبعدها اقسطها ؟</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>1774685453000</v>
+        <v>1774688651000</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2037804608517509572</t>
+          <t>2037818020597215557</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/tweet_video_thumb/HEe8fFcXcAAIJKZ.jpg', 'type': 'animated_gif', 'id': '2037804598631559168'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>{'name': 'Dat Dark Rich Dude 💎🇳🇬🇬🇧', 'screenName': 'eazyislit', 'followersCount': 66, 'favouritesCount': 752, 'friendsCount': 238, 'description': 'Best in Maintaining Maximum 🕴🏽Composure 🥇🇺🇸🇳🇬 I Love Peace 🤍🛐Graphics Designer 👩\u200d🎤  A product of Grace 🕊️❤️✝️'}</t>
+          <t>{'name': 'T.A', 'screenName': 'Talal_Hus', 'followersCount': 57, 'favouritesCount': 741, 'friendsCount': 983, 'description': '👷🏻\u200d♂️⏳🏗 ——— ✈️'}</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
@@ -3058,7 +3059,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>22</t>
         </is>
       </c>
       <c r="P37" t="inlineStr"/>
@@ -3069,35 +3070,35 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>https://x.com/eazyislit/status/2037804608517509572</t>
+          <t>https://x.com/Talal_Hus/status/2037818020597215557</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2037804608517509572</t>
+          <t>2037818020597215557</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2037855319393464474</t>
+          <t>2037827252075839770</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://x.com/eazyislit/status/2037855319393464474</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2037827252075839770</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>I claim it 🙏🏼🙏🏼🙏🏼</t>
+          <t>@Talal_Hus نعم يمكنك تقسيط المبلغ, لطلب التقسيط وتفاصيل أكثر قبل إجراء المعاملة يرجى الاتصال بنا على الرقم المجاني 8007547777</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>1774697544000</v>
+        <v>1774690852000</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2037855319393464474</t>
+          <t>2037818020597215557</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3107,7 +3108,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>{'name': 'Dat Dark Rich Dude 💎🇳🇬🇬🇧', 'screenName': 'eazyislit', 'followersCount': 66, 'favouritesCount': 752, 'friendsCount': 238, 'description': 'Best in Maintaining Maximum 🕴🏽Composure 🥇🇺🇸🇳🇬 I Love Peace 🤍🛐Graphics Designer 👩\u200d🎤  A product of Grace 🕊️❤️✝️'}</t>
+          <t>{'name': 'EmiratesNBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17238, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
       <c r="K38" t="n">
@@ -3124,10 +3125,14 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr"/>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>2037818020597215557</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
@@ -3191,7 +3196,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="P39" t="inlineStr"/>
@@ -3257,7 +3262,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>32</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -3272,162 +3277,25 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>https://x.com/Talal_Hus/status/2037818020597215557</t>
+          <t>https://x.com/argosaki/status/2037799000171216897</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2037818020597215557</t>
+          <t>2037799000171216897</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2037818020597215557</t>
+          <t>2037799000171216897</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://x.com/Talal_Hus/status/2037818020597215557</t>
+          <t>https://x.com/argosaki/status/2037799000171216897</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_KSA بالنسبة للتقسيط بدون هامش ربح هل لو سددت من خلال الفيزا ابل باي اقدر استفيد من العرض ؟ 
-يعني ععندب في نون اشتري ابل باي وبعدها اقسطها ؟</t>
-        </is>
-      </c>
-      <c r="G41" t="n">
-        <v>1774688651000</v>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>2037818020597215557</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>{'name': 'T.A', 'screenName': 'Talal_Hus', 'followersCount': 57, 'favouritesCount': 741, 'friendsCount': 983, 'description': '👷🏻\u200d♂️⏳🏗 ——— ✈️'}</t>
-        </is>
-      </c>
-      <c r="K41" t="n">
-        <v>1</v>
-      </c>
-      <c r="L41" t="n">
-        <v>0</v>
-      </c>
-      <c r="M41" t="n">
-        <v>0</v>
-      </c>
-      <c r="N41" t="n">
-        <v>0</v>
-      </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="P41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="n">
-        <v>40</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>https://x.com/Talal_Hus/status/2037818020597215557</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>2037818020597215557</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>2037827252075839770</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2037827252075839770</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>@Talal_Hus نعم يمكنك تقسيط المبلغ, لطلب التقسيط وتفاصيل أكثر قبل إجراء المعاملة يرجى الاتصال بنا على الرقم المجاني 8007547777</t>
-        </is>
-      </c>
-      <c r="G42" t="n">
-        <v>1774690852000</v>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>2037818020597215557</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>{'name': 'EmiratesNBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17238, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
-        </is>
-      </c>
-      <c r="K42" t="n">
-        <v>0</v>
-      </c>
-      <c r="L42" t="n">
-        <v>0</v>
-      </c>
-      <c r="M42" t="n">
-        <v>0</v>
-      </c>
-      <c r="N42" t="n">
-        <v>0</v>
-      </c>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>2037818020597215557</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="1" t="n">
-        <v>41</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>https://x.com/argosaki/status/2037799000171216897</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>2037799000171216897</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>2037799000171216897</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>https://x.com/argosaki/status/2037799000171216897</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
         <is>
           <t>SOUNDS LIKE … QUANTUM 
 Emirates NBD enables instant trading account top-ups for UAE investors
@@ -3435,12 +3303,146 @@
 https://t.co/qE71v9rmUv</t>
         </is>
       </c>
+      <c r="G41" t="n">
+        <v>1774684116000</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>2037799000171216897</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>{'name': 'GP Q', 'screenName': 'argosaki', 'followersCount': 111376, 'favouritesCount': 302141, 'friendsCount': 1637, 'description': 'Special? Mmmmm not really, just me :). *Standard disclaimer that nothing in these posts should be used as a substitute for financial or medical advice*'}</t>
+        </is>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>1</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>431</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>https://x.com/argosaki/status/2037799000171216897</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2037799000171216897</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2038054346693435744</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>https://x.com/argosaki/status/2038054346693435744</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>.👇♥️🙏 https://t.co/k2P5WezRfZ</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>1774744996000</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>2038054346693435744</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEifoD5b0AEmFq5.jpg', 'type': 'photo', 'id': '2038054341974937601'}]</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>{'name': 'GP Q', 'screenName': 'argosaki', 'followersCount': 111376, 'favouritesCount': 302141, 'friendsCount': 1637, 'description': 'Special? Mmmmm not really, just me :). *Standard disclaimer that nothing in these posts should be used as a substitute for financial or medical advice*'}</t>
+        </is>
+      </c>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>4</v>
+      </c>
+      <c r="N42" t="n">
+        <v>29</v>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>691</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2037801868244533349</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2037801868244533349</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2037801868244533349</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2037801868244533349</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>What’s more suspicious?
+Stay Safe, Stay Vigilant. #UnitedAgainstFraud
+https://t.co/YpRWtBZrhq</t>
+        </is>
+      </c>
       <c r="G43" t="n">
-        <v>1774684116000</v>
+        <v>1774684800000</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2037799000171216897</t>
+          <t>2037801868244533349</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3450,24 +3452,24 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>{'name': 'GP Q', 'screenName': 'argosaki', 'followersCount': 111374, 'favouritesCount': 302141, 'friendsCount': 1637, 'description': 'Special? Mmmmm not really, just me :). *Standard disclaimer that nothing in these posts should be used as a substitute for financial or medical advice*'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174061, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>514</t>
         </is>
       </c>
       <c r="P43" t="inlineStr"/>
@@ -3478,62 +3480,64 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>https://x.com/argosaki/status/2037799000171216897</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2037801868244533349</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2037799000171216897</t>
+          <t>2037801868244533349</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2038054346693435744</t>
+          <t>2037895388909142325</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://x.com/argosaki/status/2038054346693435744</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2037895388909142325</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>.👇♥️🙏 https://t.co/k2P5WezRfZ</t>
+          <t>Get guaranteed vouchers worth of AED750
+Apply for Emirates NBD noon One Visa Credit Card and receive a guaranteed Majid Al Futtaim voucher worth AED 750.
+https://t.co/Rj1kVb2Rck https://t.co/MQajcVjmt6</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>1774744996000</v>
+        <v>1774707097000</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2038054346693435744</t>
+          <t>2037895388909142325</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEifoD5b0AEmFq5.jpg', 'type': 'photo', 'id': '2038054341974937601'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEgPDX9WsAEtE9T.jpg', 'type': 'photo', 'id': '2037895382030528513'}]</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>{'name': 'GP Q', 'screenName': 'argosaki', 'followersCount': 111374, 'favouritesCount': 302141, 'friendsCount': 1637, 'description': 'Special? Mmmmm not really, just me :). *Standard disclaimer that nothing in these posts should be used as a substitute for financial or medical advice*'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174061, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N44" t="n">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>667</t>
         </is>
       </c>
       <c r="P44" t="inlineStr"/>
@@ -3544,37 +3548,37 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037801868244533349</t>
+          <t>https://x.com/ZaibKang/status/2037796434725269639</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2037801868244533349</t>
+          <t>2037796434725269639</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2037801868244533349</t>
+          <t>2037784344333275440</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037801868244533349</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2037784344333275440</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>What’s more suspicious?
+          <t>Before clicking a link, what do you do?
 Stay Safe, Stay Vigilant. #UnitedAgainstFraud
 https://t.co/YpRWtBZrhq</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>1774684800000</v>
+        <v>1774680622000</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2037801868244533349</t>
+          <t>2037784344333275440</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3584,11 +3588,11 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174061, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="K45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
@@ -3601,7 +3605,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>507</t>
+          <t>532</t>
         </is>
       </c>
       <c r="P45" t="inlineStr"/>
@@ -3612,67 +3616,71 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037801868244533349</t>
+          <t>https://x.com/ZaibKang/status/2037796434725269639</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2037801868244533349</t>
+          <t>2037796434725269639</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
+          <t>2037785874474430532</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>https://x.com/ZaibKang/status/2037785874474430532</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE I applied for liv X account Still not received any response 
+Reference number 
+2026038379331830</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>1774680987000</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
           <t>2037784344333275440</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037784344333275440</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Before clicking a link, what do you do?
-Stay Safe, Stay Vigilant. #UnitedAgainstFraud
-https://t.co/YpRWtBZrhq</t>
-        </is>
-      </c>
-      <c r="G46" t="n">
-        <v>1774680622000</v>
-      </c>
-      <c r="H46" t="inlineStr">
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>{'name': 'Jahan Zaib Akbar Kang', 'screenName': 'ZaibKang', 'followersCount': 599, 'favouritesCount': 4475, 'friendsCount': 18, 'description': 'سُبْحَانَ اللَّهِ ، وَالْحَمْدُ لِلَّهِ ، وَلَا إِلَهَ إِلَّا اللَّهُ ، وَاللَّهُ أَكْبَرُ\nEntrepreneur &amp; investor'}</t>
+        </is>
+      </c>
+      <c r="K46" t="n">
+        <v>1</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
         <is>
           <t>2037784344333275440</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="K46" t="n">
-        <v>3</v>
-      </c>
-      <c r="L46" t="n">
-        <v>0</v>
-      </c>
-      <c r="M46" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" t="n">
-        <v>3</v>
-      </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>525</t>
-        </is>
-      </c>
-      <c r="P46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
@@ -3690,29 +3698,27 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
+          <t>2037792667782824069</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2037792667782824069</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>@ZaibKang We are so sorry to hear you had an unpleasant experience, please share with us your concern from your registered email address for further communication to social@emiratesnbd.com and tag the case reference number #989763 in the subject line.</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>1774682607000</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
           <t>2037784344333275440</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037784344333275440</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Before clicking a link, what do you do?
-Stay Safe, Stay Vigilant. #UnitedAgainstFraud
-https://t.co/YpRWtBZrhq</t>
-        </is>
-      </c>
-      <c r="G47" t="n">
-        <v>1774680622000</v>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>2037784344333275440</t>
-        </is>
-      </c>
       <c r="I47" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3720,11 +3726,11 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174061, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="K47" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
@@ -3733,14 +3739,18 @@
         <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>526</t>
-        </is>
-      </c>
-      <c r="P47" t="inlineStr"/>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>2037785874474430532</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
@@ -3758,23 +3768,21 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2037785874474430532</t>
+          <t>2037796434725269639</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://x.com/ZaibKang/status/2037785874474430532</t>
+          <t>https://x.com/ZaibKang/status/2037796434725269639</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE I applied for liv X account Still not received any response 
-Reference number 
-2026038379331830</t>
+          <t>@EmiratesNBD_AE Thanks for your timely response.</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>1774680987000</v>
+        <v>1774683505000</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -3792,7 +3800,7 @@
         </is>
       </c>
       <c r="K48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
@@ -3805,12 +3813,12 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>14</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>2037784344333275440</t>
+          <t>2037792667782824069</t>
         </is>
       </c>
     </row>
@@ -3820,165 +3828,25 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>https://x.com/ZaibKang/status/2037796434725269639</t>
+          <t>https://x.com/MazBalushi35285/status/2037796009921900610</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2037796434725269639</t>
+          <t>2037796009921900610</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2037792667782824069</t>
+          <t>2035436745538281762</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037792667782824069</t>
+          <t>https://x.com/RotanaLive/status/2035436745538281762</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
-        <is>
-          <t>@ZaibKang We are so sorry to hear you had an unpleasant experience, please share with us your concern from your registered email address for further communication to social@emiratesnbd.com and tag the case reference number #989763 in the subject line.</t>
-        </is>
-      </c>
-      <c r="G49" t="n">
-        <v>1774682607000</v>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>2037784344333275440</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="K49" t="n">
-        <v>1</v>
-      </c>
-      <c r="L49" t="n">
-        <v>0</v>
-      </c>
-      <c r="M49" t="n">
-        <v>0</v>
-      </c>
-      <c r="N49" t="n">
-        <v>1</v>
-      </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>2037785874474430532</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="1" t="n">
-        <v>48</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>https://x.com/ZaibKang/status/2037796434725269639</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>2037796434725269639</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>2037796434725269639</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>https://x.com/ZaibKang/status/2037796434725269639</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE Thanks for your timely response.</t>
-        </is>
-      </c>
-      <c r="G50" t="n">
-        <v>1774683505000</v>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>2037784344333275440</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>{'name': 'Jahan Zaib Akbar Kang', 'screenName': 'ZaibKang', 'followersCount': 599, 'favouritesCount': 4475, 'friendsCount': 18, 'description': 'سُبْحَانَ اللَّهِ ، وَالْحَمْدُ لِلَّهِ ، وَلَا إِلَهَ إِلَّا اللَّهُ ، وَاللَّهُ أَكْبَرُ\nEntrepreneur &amp; investor'}</t>
-        </is>
-      </c>
-      <c r="K50" t="n">
-        <v>0</v>
-      </c>
-      <c r="L50" t="n">
-        <v>0</v>
-      </c>
-      <c r="M50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N50" t="n">
-        <v>0</v>
-      </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>2037792667782824069</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="1" t="n">
-        <v>49</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>https://x.com/MazBalushi35285/status/2037796009921900610</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>2037796009921900610</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>2035436745538281762</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>https://x.com/RotanaLive/status/2035436745538281762</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
         <is>
           <t>جمهور الصقر جاهزين لحفل العيد مع صقر الأغنية الخليجية #رابح_صقر ؟🦅🎶
 #روتانا_لايف
@@ -3992,39 +3860,177 @@
 @EmiratesNBD_KSA https://t.co/0V3B6UgNKV</t>
         </is>
       </c>
+      <c r="G49" t="n">
+        <v>1774120911000</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>2035436745538281762</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2035436341970788352/img/OfSY4fBJEacp25TH.jpg', 'type': 'video', 'id': '2035436341970788352'}]</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>{'name': 'Rotana Live', 'screenName': 'RotanaLive', 'followersCount': 193210, 'favouritesCount': 7051, 'friendsCount': 147, 'description': 'روتانا لايف الحساب الرسمي لحفلات روتانا | Rotana events https://t.co/wTAoLH4wPm'}</t>
+        </is>
+      </c>
+      <c r="K49" t="n">
+        <v>3</v>
+      </c>
+      <c r="L49" t="n">
+        <v>1</v>
+      </c>
+      <c r="M49" t="n">
+        <v>6</v>
+      </c>
+      <c r="N49" t="n">
+        <v>28</v>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>7291</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="n">
+        <v>48</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>https://x.com/MazBalushi35285/status/2037796009921900610</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>2037796009921900610</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2037796009921900610</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>https://x.com/MazBalushi35285/status/2037796009921900610</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>@RotanaLive @Turki_alalshikh @RabehSaqer @GEA_SA @EidSeason @Mabdoarena @EmiratesNBD_KSA 🥳مزيد من النواة الفн على مسابقة رابح صقر! راحت لكم الحفل العيد في الرياض! 🎉 فوق_النهاية فقط</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>1774683403000</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>2035436745538281762</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>{'name': 'مازن البلوشي', 'screenName': 'MazBalushi35285', 'followersCount': 1, 'favouritesCount': 458, 'friendsCount': 1, 'description': 'عربي. رجل أعمال. أبني المستقبل خطوة بخطوة.'}</t>
+        </is>
+      </c>
+      <c r="K50" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>2035436745538281762</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="n">
+        <v>49</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2037792667782824069</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2037792667782824069</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2037784344333275440</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2037784344333275440</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Before clicking a link, what do you do?
+Stay Safe, Stay Vigilant. #UnitedAgainstFraud
+https://t.co/YpRWtBZrhq</t>
+        </is>
+      </c>
       <c r="G51" t="n">
-        <v>1774120911000</v>
+        <v>1774680622000</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2035436745538281762</t>
+          <t>2037784344333275440</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2035436341970788352/img/OfSY4fBJEacp25TH.jpg', 'type': 'video', 'id': '2035436341970788352'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>{'name': 'Rotana Live', 'screenName': 'RotanaLive', 'followersCount': 193214, 'favouritesCount': 7051, 'friendsCount': 147, 'description': 'روتانا لايف الحساب الرسمي لحفلات روتانا | Rotana events https://t.co/wTAoLH4wPm'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174061, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="K51" t="n">
         <v>3</v>
       </c>
       <c r="L51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>7289</t>
+          <t>532</t>
         </is>
       </c>
       <c r="P51" t="inlineStr"/>
@@ -4035,35 +4041,37 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>https://x.com/MazBalushi35285/status/2037796009921900610</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2037792667782824069</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2037796009921900610</t>
+          <t>2037792667782824069</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2037796009921900610</t>
+          <t>2037785874474430532</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>https://x.com/MazBalushi35285/status/2037796009921900610</t>
+          <t>https://x.com/ZaibKang/status/2037785874474430532</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>@RotanaLive @Turki_alalshikh @RabehSaqer @GEA_SA @EidSeason @Mabdoarena @EmiratesNBD_KSA 🥳مزيد من النواة الفн على مسابقة رابح صقر! راحت لكم الحفل العيد في الرياض! 🎉 فوق_النهاية فقط</t>
+          <t>@EmiratesNBD_AE I applied for liv X account Still not received any response 
+Reference number 
+2026038379331830</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>1774683403000</v>
+        <v>1774680987000</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2035436745538281762</t>
+          <t>2037784344333275440</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -4073,11 +4081,11 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>{'name': 'مازن البلوشي', 'screenName': 'MazBalushi35285', 'followersCount': 1, 'favouritesCount': 458, 'friendsCount': 1, 'description': 'عربي. رجل أعمال. أبني المستقبل خطوة بخطوة.'}</t>
+          <t>{'name': 'Jahan Zaib Akbar Kang', 'screenName': 'ZaibKang', 'followersCount': 599, 'favouritesCount': 4475, 'friendsCount': 18, 'description': 'سُبْحَانَ اللَّهِ ، وَالْحَمْدُ لِلَّهِ ، وَلَا إِلَهَ إِلَّا اللَّهُ ، وَاللَّهُ أَكْبَرُ\nEntrepreneur &amp; investor'}</t>
         </is>
       </c>
       <c r="K52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
@@ -4090,12 +4098,12 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>33</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>2035436745538281762</t>
+          <t>2037784344333275440</t>
         </is>
       </c>
     </row>
@@ -4115,29 +4123,27 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
+          <t>2037792667782824069</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2037792667782824069</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>@ZaibKang We are so sorry to hear you had an unpleasant experience, please share with us your concern from your registered email address for further communication to social@emiratesnbd.com and tag the case reference number #989763 in the subject line.</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>1774682607000</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
           <t>2037784344333275440</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037784344333275440</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Before clicking a link, what do you do?
-Stay Safe, Stay Vigilant. #UnitedAgainstFraud
-https://t.co/YpRWtBZrhq</t>
-        </is>
-      </c>
-      <c r="G53" t="n">
-        <v>1774680622000</v>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>2037784344333275440</t>
-        </is>
-      </c>
       <c r="I53" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4145,11 +4151,11 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174061, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="K53" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
@@ -4158,14 +4164,18 @@
         <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>526</t>
-        </is>
-      </c>
-      <c r="P53" t="inlineStr"/>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>2037785874474430532</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
@@ -4183,23 +4193,21 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2037785874474430532</t>
+          <t>2037796434725269639</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://x.com/ZaibKang/status/2037785874474430532</t>
+          <t>https://x.com/ZaibKang/status/2037796434725269639</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE I applied for liv X account Still not received any response 
-Reference number 
-2026038379331830</t>
+          <t>@EmiratesNBD_AE Thanks for your timely response.</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>1774680987000</v>
+        <v>1774683505000</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -4217,7 +4225,7 @@
         </is>
       </c>
       <c r="K54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
@@ -4230,12 +4238,12 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>14</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>2037784344333275440</t>
+          <t>2037792667782824069</t>
         </is>
       </c>
     </row>
@@ -4245,165 +4253,25 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037792667782824069</t>
+          <t>https://x.com/SelmaRomola/status/2037790087141101872</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2037792667782824069</t>
+          <t>2037790087141101872</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2037792667782824069</t>
+          <t>2031673422921564269</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037792667782824069</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2031673422921564269</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
-        <is>
-          <t>@ZaibKang We are so sorry to hear you had an unpleasant experience, please share with us your concern from your registered email address for further communication to social@emiratesnbd.com and tag the case reference number #989763 in the subject line.</t>
-        </is>
-      </c>
-      <c r="G55" t="n">
-        <v>1774682607000</v>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>2037784344333275440</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="K55" t="n">
-        <v>1</v>
-      </c>
-      <c r="L55" t="n">
-        <v>0</v>
-      </c>
-      <c r="M55" t="n">
-        <v>0</v>
-      </c>
-      <c r="N55" t="n">
-        <v>1</v>
-      </c>
-      <c r="O55" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>2037785874474430532</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="1" t="n">
-        <v>54</v>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037792667782824069</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>2037792667782824069</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>2037796434725269639</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>https://x.com/ZaibKang/status/2037796434725269639</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE Thanks for your timely response.</t>
-        </is>
-      </c>
-      <c r="G56" t="n">
-        <v>1774683505000</v>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>2037784344333275440</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>{'name': 'Jahan Zaib Akbar Kang', 'screenName': 'ZaibKang', 'followersCount': 599, 'favouritesCount': 4475, 'friendsCount': 18, 'description': 'سُبْحَانَ اللَّهِ ، وَالْحَمْدُ لِلَّهِ ، وَلَا إِلَهَ إِلَّا اللَّهُ ، وَاللَّهُ أَكْبَرُ\nEntrepreneur &amp; investor'}</t>
-        </is>
-      </c>
-      <c r="K56" t="n">
-        <v>0</v>
-      </c>
-      <c r="L56" t="n">
-        <v>0</v>
-      </c>
-      <c r="M56" t="n">
-        <v>0</v>
-      </c>
-      <c r="N56" t="n">
-        <v>0</v>
-      </c>
-      <c r="O56" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>2037792667782824069</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="1" t="n">
-        <v>55</v>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>https://x.com/SelmaRomola/status/2037790087141101872</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>2037790087141101872</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>2031673422921564269</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2031673422921564269</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
         <is>
           <t>نفذت أموال أم خماس قبل نهاية الشهر.
 هناك قاعدة بسيطة تُساعدها على إدارة أموالها بحكمة:
@@ -4430,68 +4298,68 @@
 - Drop your answer below for a chance to win AED 10,000</t>
         </is>
       </c>
-      <c r="G57" t="n">
+      <c r="G55" t="n">
         <v>1773223665000</v>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="H55" t="inlineStr">
         <is>
           <t>2031673422921564269</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="I55" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HDH0NZXWQAAnKTa.jpg', 'type': 'video', 'id': '2031673271423295488'}]</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="K57" t="n">
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174061, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="K55" t="n">
         <v>128</v>
       </c>
-      <c r="L57" t="n">
-        <v>0</v>
-      </c>
-      <c r="M57" t="n">
+      <c r="L55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" t="n">
         <v>40</v>
       </c>
-      <c r="N57" t="n">
+      <c r="N55" t="n">
         <v>53</v>
       </c>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t>2345</t>
-        </is>
-      </c>
-      <c r="P57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="1" t="n">
-        <v>56</v>
-      </c>
-      <c r="B58" t="inlineStr">
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>2349</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="n">
+        <v>54</v>
+      </c>
+      <c r="B56" t="inlineStr">
         <is>
           <t>https://x.com/SelmaRomola/status/2037790087141101872</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>2037790087141101872</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>2037790087141101872</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="E56" t="inlineStr">
         <is>
           <t>https://x.com/SelmaRomola/status/2037790087141101872</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>@EmiratesNBD_AE Fin well Financial well-being program with Emirates NBD 
 @Sabaashraff
@@ -4499,72 +4367,72 @@
 @Amanekhattab1</t>
         </is>
       </c>
-      <c r="G58" t="n">
+      <c r="G56" t="n">
         <v>1774681991000</v>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="H56" t="inlineStr">
         <is>
           <t>2031673422921564269</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
+      <c r="J56" t="inlineStr">
         <is>
           <t>{'name': 'Selma Romola', 'screenName': 'SelmaRomola', 'followersCount': 1152, 'favouritesCount': 19738, 'friendsCount': 1787, 'description': ''}</t>
         </is>
       </c>
-      <c r="K58" t="n">
-        <v>0</v>
-      </c>
-      <c r="L58" t="n">
-        <v>0</v>
-      </c>
-      <c r="M58" t="n">
-        <v>0</v>
-      </c>
-      <c r="N58" t="n">
-        <v>0</v>
-      </c>
-      <c r="O58" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="P58" t="inlineStr">
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
         <is>
           <t>2031673422921564269</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="1" t="n">
-        <v>57</v>
-      </c>
-      <c r="B59" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="B57" t="inlineStr">
         <is>
           <t>https://x.com/SelmaRomola/status/2037789707321622955</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>2037789707321622955</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>2034225946308358408</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE/status/2034225946308358408</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>اجعل مفاجآت العيد أكثر قيمة.
 من الفضة إلى الذهب، اكتشف طريقة أذكى لامتلاك أو إهداء شيء ثمين بحق.
@@ -4576,68 +4444,68 @@
 اكتب إجابتك في التعليقات أدناه لفرصة ربح 10,000 درهم</t>
         </is>
       </c>
-      <c r="G59" t="n">
+      <c r="G57" t="n">
         <v>1773832234000</v>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="H57" t="inlineStr">
         <is>
           <t>2034225946308358408</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2034225772156563456/img/fizQ3vAEH0uqiLix.jpg', 'type': 'video', 'id': '2034225772156563456'}]</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="K59" t="n">
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174061, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="K57" t="n">
         <v>91</v>
       </c>
-      <c r="L59" t="n">
+      <c r="L57" t="n">
         <v>1</v>
       </c>
-      <c r="M59" t="n">
+      <c r="M57" t="n">
         <v>39</v>
       </c>
-      <c r="N59" t="n">
+      <c r="N57" t="n">
         <v>50</v>
       </c>
-      <c r="O59" t="inlineStr">
-        <is>
-          <t>2638</t>
-        </is>
-      </c>
-      <c r="P59" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="1" t="n">
-        <v>58</v>
-      </c>
-      <c r="B60" t="inlineStr">
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>2642</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="n">
+        <v>56</v>
+      </c>
+      <c r="B58" t="inlineStr">
         <is>
           <t>https://x.com/SelmaRomola/status/2037789707321622955</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>2037789707321622955</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>2037789707321622955</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>https://x.com/SelmaRomola/status/2037789707321622955</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>@EmiratesNBD_AE To buy gold and silver through Emirates NBD, the fastest way is using the ENBD X mobile app. 
 Tagging 
@@ -4646,72 +4514,72 @@
 @Bushrasabih2</t>
         </is>
       </c>
-      <c r="G60" t="n">
+      <c r="G58" t="n">
         <v>1774681901000</v>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="H58" t="inlineStr">
         <is>
           <t>2034225946308358408</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
+      <c r="I58" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr">
+      <c r="J58" t="inlineStr">
         <is>
           <t>{'name': 'Selma Romola', 'screenName': 'SelmaRomola', 'followersCount': 1152, 'favouritesCount': 19738, 'friendsCount': 1787, 'description': ''}</t>
         </is>
       </c>
-      <c r="K60" t="n">
-        <v>0</v>
-      </c>
-      <c r="L60" t="n">
-        <v>0</v>
-      </c>
-      <c r="M60" t="n">
-        <v>0</v>
-      </c>
-      <c r="N60" t="n">
-        <v>0</v>
-      </c>
-      <c r="O60" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="P60" t="inlineStr">
+      <c r="K58" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
         <is>
           <t>2034225946308358408</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="1" t="n">
-        <v>59</v>
-      </c>
-      <c r="B61" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="1" t="n">
+        <v>57</v>
+      </c>
+      <c r="B59" t="inlineStr">
         <is>
           <t>https://x.com/SelmaRomola/status/2037788447910564341</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>2037788447910564341</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>2034225964863893587</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE/status/2034225964863893587</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>Make Eid surprises even more valuable.
 From silver to gold, discover a smarter way to own or gift something truly precious.
@@ -4723,68 +4591,68 @@
 Drop your answer below for a chance to win AED 10,000</t>
         </is>
       </c>
-      <c r="G61" t="n">
+      <c r="G59" t="n">
         <v>1773832238000</v>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="H59" t="inlineStr">
         <is>
           <t>2034225964863893587</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2034225751092822016/img/ppYucbpuWh6bd_l0.jpg', 'type': 'video', 'id': '2034225751092822016'}]</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="K61" t="n">
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174061, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="K59" t="n">
         <v>72</v>
       </c>
-      <c r="L61" t="n">
-        <v>0</v>
-      </c>
-      <c r="M61" t="n">
+      <c r="L59" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" t="n">
         <v>29</v>
       </c>
-      <c r="N61" t="n">
+      <c r="N59" t="n">
         <v>46</v>
       </c>
-      <c r="O61" t="inlineStr">
-        <is>
-          <t>1678</t>
-        </is>
-      </c>
-      <c r="P61" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="1" t="n">
-        <v>60</v>
-      </c>
-      <c r="B62" t="inlineStr">
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>1681</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="n">
+        <v>58</v>
+      </c>
+      <c r="B60" t="inlineStr">
         <is>
           <t>https://x.com/SelmaRomola/status/2037788447910564341</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C60" t="inlineStr">
         <is>
           <t>2037788447910564341</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="D60" t="inlineStr">
         <is>
           <t>2037788447910564341</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="E60" t="inlineStr">
         <is>
           <t>https://x.com/SelmaRomola/status/2037788447910564341</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="F60" t="inlineStr">
         <is>
           <t>@EmiratesNBD_AE To buy gold and silver through Emirates NBD, the fastest way is using the ENBD X mobile app. 
 Tagging 
@@ -4793,282 +4661,72 @@
 @Sosomostafa729S</t>
         </is>
       </c>
-      <c r="G62" t="n">
+      <c r="G60" t="n">
         <v>1774681600000</v>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="H60" t="inlineStr">
         <is>
           <t>2034225964863893587</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
+      <c r="I60" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr">
+      <c r="J60" t="inlineStr">
         <is>
           <t>{'name': 'Selma Romola', 'screenName': 'SelmaRomola', 'followersCount': 1152, 'favouritesCount': 19738, 'friendsCount': 1787, 'description': ''}</t>
         </is>
       </c>
-      <c r="K62" t="n">
-        <v>0</v>
-      </c>
-      <c r="L62" t="n">
-        <v>0</v>
-      </c>
-      <c r="M62" t="n">
-        <v>0</v>
-      </c>
-      <c r="N62" t="n">
-        <v>0</v>
-      </c>
-      <c r="O62" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="P62" t="inlineStr">
+      <c r="K60" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
         <is>
           <t>2034225964863893587</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="1" t="n">
-        <v>61</v>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>https://x.com/ZaibKang/status/2037785874474430532</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>2037785874474430532</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>2037784344333275440</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037784344333275440</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Before clicking a link, what do you do?
-Stay Safe, Stay Vigilant. #UnitedAgainstFraud
-https://t.co/YpRWtBZrhq</t>
-        </is>
-      </c>
-      <c r="G63" t="n">
-        <v>1774680622000</v>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>2037784344333275440</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="K63" t="n">
-        <v>3</v>
-      </c>
-      <c r="L63" t="n">
-        <v>0</v>
-      </c>
-      <c r="M63" t="n">
-        <v>0</v>
-      </c>
-      <c r="N63" t="n">
-        <v>3</v>
-      </c>
-      <c r="O63" t="inlineStr">
-        <is>
-          <t>526</t>
-        </is>
-      </c>
-      <c r="P63" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="1" t="n">
-        <v>62</v>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>https://x.com/ZaibKang/status/2037785874474430532</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>2037785874474430532</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>2037785874474430532</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>https://x.com/ZaibKang/status/2037785874474430532</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE I applied for liv X account Still not received any response 
-Reference number 
-2026038379331830</t>
-        </is>
-      </c>
-      <c r="G64" t="n">
-        <v>1774680987000</v>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>2037784344333275440</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>{'name': 'Jahan Zaib Akbar Kang', 'screenName': 'ZaibKang', 'followersCount': 599, 'favouritesCount': 4475, 'friendsCount': 18, 'description': 'سُبْحَانَ اللَّهِ ، وَالْحَمْدُ لِلَّهِ ، وَلَا إِلَهَ إِلَّا اللَّهُ ، وَاللَّهُ أَكْبَرُ\nEntrepreneur &amp; investor'}</t>
-        </is>
-      </c>
-      <c r="K64" t="n">
-        <v>1</v>
-      </c>
-      <c r="L64" t="n">
-        <v>0</v>
-      </c>
-      <c r="M64" t="n">
-        <v>0</v>
-      </c>
-      <c r="N64" t="n">
-        <v>0</v>
-      </c>
-      <c r="O64" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="P64" t="inlineStr">
-        <is>
-          <t>2037784344333275440</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="1" t="n">
-        <v>63</v>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>https://x.com/ZaibKang/status/2037785874474430532</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>2037785874474430532</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>2037792667782824069</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037792667782824069</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>@ZaibKang We are so sorry to hear you had an unpleasant experience, please share with us your concern from your registered email address for further communication to social@emiratesnbd.com and tag the case reference number #989763 in the subject line.</t>
-        </is>
-      </c>
-      <c r="G65" t="n">
-        <v>1774682607000</v>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>2037784344333275440</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="K65" t="n">
-        <v>1</v>
-      </c>
-      <c r="L65" t="n">
-        <v>0</v>
-      </c>
-      <c r="M65" t="n">
-        <v>0</v>
-      </c>
-      <c r="N65" t="n">
-        <v>1</v>
-      </c>
-      <c r="O65" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="P65" t="inlineStr">
-        <is>
-          <t>2037785874474430532</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="1" t="n">
-        <v>64</v>
-      </c>
-      <c r="B66" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="B61" t="inlineStr">
         <is>
           <t>https://x.com/SelmaRomola/status/2037789510478843981</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>2037789510478843981</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="D61" t="inlineStr">
         <is>
           <t>2034225946308358408</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="E61" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE/status/2034225946308358408</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="F61" t="inlineStr">
         <is>
           <t>اجعل مفاجآت العيد أكثر قيمة.
 من الفضة إلى الذهب، اكتشف طريقة أذكى لامتلاك أو إهداء شيء ثمين بحق.
@@ -5080,68 +4738,68 @@
 اكتب إجابتك في التعليقات أدناه لفرصة ربح 10,000 درهم</t>
         </is>
       </c>
-      <c r="G66" t="n">
+      <c r="G61" t="n">
         <v>1773832234000</v>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="H61" t="inlineStr">
         <is>
           <t>2034225946308358408</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
+      <c r="I61" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2034225772156563456/img/fizQ3vAEH0uqiLix.jpg', 'type': 'video', 'id': '2034225772156563456'}]</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="K66" t="n">
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174061, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="K61" t="n">
         <v>91</v>
       </c>
-      <c r="L66" t="n">
+      <c r="L61" t="n">
         <v>1</v>
       </c>
-      <c r="M66" t="n">
+      <c r="M61" t="n">
         <v>39</v>
       </c>
-      <c r="N66" t="n">
+      <c r="N61" t="n">
         <v>50</v>
       </c>
-      <c r="O66" t="inlineStr">
-        <is>
-          <t>2639</t>
-        </is>
-      </c>
-      <c r="P66" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="1" t="n">
-        <v>65</v>
-      </c>
-      <c r="B67" t="inlineStr">
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>2642</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="B62" t="inlineStr">
         <is>
           <t>https://x.com/SelmaRomola/status/2037789510478843981</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="C62" t="inlineStr">
         <is>
           <t>2037789510478843981</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="D62" t="inlineStr">
         <is>
           <t>2037789510478843981</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="E62" t="inlineStr">
         <is>
           <t>https://x.com/SelmaRomola/status/2037789510478843981</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="F62" t="inlineStr">
         <is>
           <t>@EmiratesNBD_AE To buy gold and silver through Emirates NBD, the fastest way is using the ENBD X mobile app. 
 Tagging 
@@ -5150,22 +4808,370 @@
 @yasar8212</t>
         </is>
       </c>
+      <c r="G62" t="n">
+        <v>1774681854000</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>2034225946308358408</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>{'name': 'Selma Romola', 'screenName': 'SelmaRomola', 'followersCount': 1152, 'favouritesCount': 19738, 'friendsCount': 1787, 'description': ''}</t>
+        </is>
+      </c>
+      <c r="K62" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>2034225946308358408</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="n">
+        <v>61</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>https://x.com/ZaibKang/status/2037785874474430532</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>2037785874474430532</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2037784344333275440</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2037784344333275440</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Before clicking a link, what do you do?
+Stay Safe, Stay Vigilant. #UnitedAgainstFraud
+https://t.co/YpRWtBZrhq</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>1774680622000</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>2037784344333275440</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174061, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="K63" t="n">
+        <v>3</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" t="n">
+        <v>3</v>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>532</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="n">
+        <v>62</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>https://x.com/ZaibKang/status/2037785874474430532</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>2037785874474430532</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2037785874474430532</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>https://x.com/ZaibKang/status/2037785874474430532</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE I applied for liv X account Still not received any response 
+Reference number 
+2026038379331830</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
+        <v>1774680987000</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>2037784344333275440</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>{'name': 'Jahan Zaib Akbar Kang', 'screenName': 'ZaibKang', 'followersCount': 599, 'favouritesCount': 4475, 'friendsCount': 18, 'description': 'سُبْحَانَ اللَّهِ ، وَالْحَمْدُ لِلَّهِ ، وَلَا إِلَهَ إِلَّا اللَّهُ ، وَاللَّهُ أَكْبَرُ\nEntrepreneur &amp; investor'}</t>
+        </is>
+      </c>
+      <c r="K64" t="n">
+        <v>1</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" t="n">
+        <v>0</v>
+      </c>
+      <c r="N64" t="n">
+        <v>0</v>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>2037784344333275440</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="n">
+        <v>63</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>https://x.com/ZaibKang/status/2037785874474430532</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>2037785874474430532</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2037792667782824069</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2037792667782824069</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>@ZaibKang We are so sorry to hear you had an unpleasant experience, please share with us your concern from your registered email address for further communication to social@emiratesnbd.com and tag the case reference number #989763 in the subject line.</t>
+        </is>
+      </c>
+      <c r="G65" t="n">
+        <v>1774682607000</v>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>2037784344333275440</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174061, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="K65" t="n">
+        <v>1</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" t="n">
+        <v>0</v>
+      </c>
+      <c r="N65" t="n">
+        <v>1</v>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>2037785874474430532</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="n">
+        <v>64</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>https://x.com/ZaibKang/status/2037785071189671937</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>2037785071189671937</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2037784344333275440</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2037784344333275440</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Before clicking a link, what do you do?
+Stay Safe, Stay Vigilant. #UnitedAgainstFraud
+https://t.co/YpRWtBZrhq</t>
+        </is>
+      </c>
+      <c r="G66" t="n">
+        <v>1774680622000</v>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>2037784344333275440</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174061, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="K66" t="n">
+        <v>3</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N66" t="n">
+        <v>3</v>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>532</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="n">
+        <v>65</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>https://x.com/ZaibKang/status/2037785071189671937</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>2037785071189671937</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2037785071189671937</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>https://x.com/ZaibKang/status/2037785071189671937</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE @EmiratesNBD_AE I applied for liv X account 3 days ago still not received any response please Check and respond as soon as possible https://t.co/LXfxy0AGqW</t>
+        </is>
+      </c>
       <c r="G67" t="n">
-        <v>1774681854000</v>
+        <v>1774680795000</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2034225946308358408</t>
+          <t>2037784344333275440</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEequS2a4AAftLC.jpg', 'type': 'photo', 'id': '2037785068719235072'}]</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>{'name': 'Selma Romola', 'screenName': 'SelmaRomola', 'followersCount': 1152, 'favouritesCount': 19738, 'friendsCount': 1787, 'description': ''}</t>
+          <t>{'name': 'Jahan Zaib Akbar Kang', 'screenName': 'ZaibKang', 'followersCount': 599, 'favouritesCount': 4475, 'friendsCount': 18, 'description': 'سُبْحَانَ اللَّهِ ، وَالْحَمْدُ لِلَّهِ ، وَلَا إِلَهَ إِلَّا اللَّهُ ، وَاللَّهُ أَكْبَرُ\nEntrepreneur &amp; investor'}</t>
         </is>
       </c>
       <c r="K67" t="n">
@@ -5182,12 +5188,12 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>2034225946308358408</t>
+          <t>2037784344333275440</t>
         </is>
       </c>
     </row>
@@ -5197,64 +5203,66 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>https://x.com/ZaibKang/status/2037785071189671937</t>
+          <t>https://x.com/Sosomostafa729S/status/2037784853866029145</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2037785071189671937</t>
+          <t>2037784853866029145</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2037784344333275440</t>
+          <t>2025123939970584932</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037784344333275440</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2025123939970584932</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Before clicking a link, what do you do?
-Stay Safe, Stay Vigilant. #UnitedAgainstFraud
-https://t.co/YpRWtBZrhq</t>
+          <t>حل اللغز واربح 10,000 درهم.💰
+أم علاوي تعبت من مشاكل السيارة، ومستعدة لسيارة جديدة بفضل قرض السيارات السريع من بنك الإمارات دبي الوطني، من خلال طلب سهل وسريع عبر الإنترنت.
+تابع @EmiratesNBD_ae
+قم بالإشارة إلى 3 من أصدقائك
+حل اللغز لفرصة الفوز بـ 10 آلاف درهم. https://t.co/NBQE3PzfgZ</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>1774680622000</v>
+        <v>1771662146000</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2037784344333275440</t>
+          <t>2025123939970584932</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2025123808986718208/img/anriFRhFhmo7262r.jpg', 'type': 'video', 'id': '2025123808986718208'}]</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174061, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="K68" t="n">
+        <v>857</v>
+      </c>
+      <c r="L68" t="n">
         <v>3</v>
       </c>
-      <c r="L68" t="n">
-        <v>0</v>
-      </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>183</v>
       </c>
       <c r="N68" t="n">
-        <v>3</v>
+        <v>191</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>526</t>
+          <t>9399</t>
         </is>
       </c>
       <c r="P68" t="inlineStr"/>
@@ -5265,45 +5273,45 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>https://x.com/ZaibKang/status/2037785071189671937</t>
+          <t>https://x.com/Sosomostafa729S/status/2037784853866029145</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2037785071189671937</t>
+          <t>2037784853866029145</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2037785071189671937</t>
+          <t>2037784853866029145</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>https://x.com/ZaibKang/status/2037785071189671937</t>
+          <t>https://x.com/Sosomostafa729S/status/2037784853866029145</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE @EmiratesNBD_AE I applied for liv X account 3 days ago still not received any response please Check and respond as soon as possible https://t.co/LXfxy0AGqW</t>
+          <t>@EmiratesNBD_AE B- 1.89% @zeynp_qas @Salma2232019 @semeet 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="G69" t="n">
-        <v>1774680795000</v>
+        <v>1774680744000</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2037784344333275440</t>
+          <t>2025123939970584932</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEequS2a4AAftLC.jpg', 'type': 'photo', 'id': '2037785068719235072'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>{'name': 'Jahan Zaib Akbar Kang', 'screenName': 'ZaibKang', 'followersCount': 599, 'favouritesCount': 4475, 'friendsCount': 18, 'description': 'سُبْحَانَ اللَّهِ ، وَالْحَمْدُ لِلَّهِ ، وَلَا إِلَهَ إِلَّا اللَّهُ ، وَاللَّهُ أَكْبَرُ\nEntrepreneur &amp; investor'}</t>
+          <t>{'name': 'Soha.mostafa77', 'screenName': 'Sosomostafa729S', 'followersCount': 345, 'favouritesCount': 22185, 'friendsCount': 968, 'description': 'Moom of 2 🙍\u200d♂️🙍\u200d♀️\nShopping 🛍 food 😋 traveling \nLive in UAE 🇦🇪🕊💕'}</t>
         </is>
       </c>
       <c r="K69" t="n">
@@ -5320,12 +5328,12 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>2037784344333275440</t>
+          <t>2025123939970584932</t>
         </is>
       </c>
     </row>
@@ -5379,7 +5387,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174061, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="K70" t="n">
@@ -5396,7 +5404,7 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>10504</t>
+          <t>10508</t>
         </is>
       </c>
       <c r="P70" t="inlineStr"/>
@@ -5451,7 +5459,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174061, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="K71" t="n">
@@ -5468,7 +5476,7 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>2289</t>
+          <t>2293</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -5539,7 +5547,7 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -5596,7 +5604,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174061, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="K73" t="n">
@@ -5613,7 +5621,7 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>9397</t>
+          <t>9400</t>
         </is>
       </c>
       <c r="P73" t="inlineStr"/>
@@ -5679,7 +5687,7 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
@@ -5736,7 +5744,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174061, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="K75" t="n">
@@ -5753,7 +5761,7 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>9397</t>
+          <t>9400</t>
         </is>
       </c>
       <c r="P75" t="inlineStr"/>
@@ -5819,7 +5827,7 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -5834,233 +5842,25 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037784344333275440</t>
+          <t>https://x.com/Sosomostafa729S/status/2037784405700419683</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2037784344333275440</t>
+          <t>2037784405700419683</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2037784344333275440</t>
+          <t>2027634643315404863</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037784344333275440</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2027634643315404863</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
-        <is>
-          <t>Before clicking a link, what do you do?
-Stay Safe, Stay Vigilant. #UnitedAgainstFraud
-https://t.co/YpRWtBZrhq</t>
-        </is>
-      </c>
-      <c r="G77" t="n">
-        <v>1774680622000</v>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>2037784344333275440</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="K77" t="n">
-        <v>3</v>
-      </c>
-      <c r="L77" t="n">
-        <v>0</v>
-      </c>
-      <c r="M77" t="n">
-        <v>0</v>
-      </c>
-      <c r="N77" t="n">
-        <v>3</v>
-      </c>
-      <c r="O77" t="inlineStr">
-        <is>
-          <t>528</t>
-        </is>
-      </c>
-      <c r="P77" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="1" t="n">
-        <v>76</v>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037784344333275440</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>2037784344333275440</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>2037785874474430532</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>https://x.com/ZaibKang/status/2037785874474430532</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE I applied for liv X account Still not received any response 
-Reference number 
-2026038379331830</t>
-        </is>
-      </c>
-      <c r="G78" t="n">
-        <v>1774680987000</v>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>2037784344333275440</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>{'name': 'Jahan Zaib Akbar Kang', 'screenName': 'ZaibKang', 'followersCount': 599, 'favouritesCount': 4475, 'friendsCount': 18, 'description': 'سُبْحَانَ اللَّهِ ، وَالْحَمْدُ لِلَّهِ ، وَلَا إِلَهَ إِلَّا اللَّهُ ، وَاللَّهُ أَكْبَرُ\nEntrepreneur &amp; investor'}</t>
-        </is>
-      </c>
-      <c r="K78" t="n">
-        <v>1</v>
-      </c>
-      <c r="L78" t="n">
-        <v>0</v>
-      </c>
-      <c r="M78" t="n">
-        <v>0</v>
-      </c>
-      <c r="N78" t="n">
-        <v>0</v>
-      </c>
-      <c r="O78" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="P78" t="inlineStr">
-        <is>
-          <t>2037784344333275440</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="1" t="n">
-        <v>77</v>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037784344333275440</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>2037784344333275440</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>2037801868244533349</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037801868244533349</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>What’s more suspicious?
-Stay Safe, Stay Vigilant. #UnitedAgainstFraud
-https://t.co/YpRWtBZrhq</t>
-        </is>
-      </c>
-      <c r="G79" t="n">
-        <v>1774684800000</v>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>2037801868244533349</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="K79" t="n">
-        <v>2</v>
-      </c>
-      <c r="L79" t="n">
-        <v>0</v>
-      </c>
-      <c r="M79" t="n">
-        <v>0</v>
-      </c>
-      <c r="N79" t="n">
-        <v>3</v>
-      </c>
-      <c r="O79" t="inlineStr">
-        <is>
-          <t>508</t>
-        </is>
-      </c>
-      <c r="P79" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="1" t="n">
-        <v>78</v>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784405700419683</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>2037784405700419683</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>2027634643315404863</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2027634643315404863</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
         <is>
           <t>حلّ فزورة رمضان واربح 10,000 درهم.
 من توزيع الوجبات، إلى دعم العاملين وقضاء الوقت مع كبار المواطنين، يجمع برنامج واحد كل ذلك تحت مظلًة واحدة.
@@ -6071,68 +5871,68 @@
 3.اكتب إجابتك في التعليقات أدناه https://t.co/aADoQF5a2E</t>
         </is>
       </c>
-      <c r="G80" t="n">
+      <c r="G77" t="n">
         <v>1772260745000</v>
       </c>
-      <c r="H80" t="inlineStr">
+      <c r="H77" t="inlineStr">
         <is>
           <t>2027634643315404863</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
+      <c r="I77" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2027634528185901056/img/L9yGlrO1upMqeKpB.jpg', 'type': 'video', 'id': '2027634528185901056'}]</t>
         </is>
       </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="K80" t="n">
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174061, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="K77" t="n">
         <v>366</v>
       </c>
-      <c r="L80" t="n">
+      <c r="L77" t="n">
         <v>2</v>
       </c>
-      <c r="M80" t="n">
+      <c r="M77" t="n">
         <v>154</v>
       </c>
-      <c r="N80" t="n">
+      <c r="N77" t="n">
         <v>183</v>
       </c>
-      <c r="O80" t="inlineStr">
-        <is>
-          <t>10505</t>
-        </is>
-      </c>
-      <c r="P80" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="1" t="n">
-        <v>79</v>
-      </c>
-      <c r="B81" t="inlineStr">
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>10508</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="n">
+        <v>76</v>
+      </c>
+      <c r="B78" t="inlineStr">
         <is>
           <t>https://x.com/Sosomostafa729S/status/2037784405700419683</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
+      <c r="C78" t="inlineStr">
         <is>
           <t>2037784405700419683</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
+      <c r="D78" t="inlineStr">
         <is>
           <t>2027634776555872373</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
+      <c r="E78" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE/status/2027634776555872373</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
+      <c r="F78" t="inlineStr">
         <is>
           <t>Solve this Ramadan riddle and win AED 10,000.
 From food distribution to supporting workers and spending time with senior citizens, one program brings it all together.
@@ -6143,44 +5943,254 @@
 3.Drop your answer below https://t.co/PDRSppGlrJ</t>
         </is>
       </c>
+      <c r="G78" t="n">
+        <v>1772260777000</v>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>2027634643315404863</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2027634660532973568/img/NcwS9qq5kEQQ1U9q.jpg', 'type': 'video', 'id': '2027634660532973568'}]</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174061, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="K78" t="n">
+        <v>100</v>
+      </c>
+      <c r="L78" t="n">
+        <v>2</v>
+      </c>
+      <c r="M78" t="n">
+        <v>38</v>
+      </c>
+      <c r="N78" t="n">
+        <v>46</v>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>2293</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>2027634643315404863</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="n">
+        <v>77</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2037784405700419683</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>2037784405700419683</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2037784405700419683</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2037784405700419683</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE Exchanger volunteer program @semeet @zeynp_qas @SelmaRomola 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="G79" t="n">
+        <v>1774680637000</v>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>2027634643315404863</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>{'name': 'Soha.mostafa77', 'screenName': 'Sosomostafa729S', 'followersCount': 345, 'favouritesCount': 22185, 'friendsCount': 968, 'description': 'Moom of 2 🙍\u200d♂️🙍\u200d♀️\nShopping 🛍 food 😋 traveling \nLive in UAE 🇦🇪🕊💕'}</t>
+        </is>
+      </c>
+      <c r="K79" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" t="n">
+        <v>0</v>
+      </c>
+      <c r="N79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>2027634776555872373</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="n">
+        <v>78</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2037784344333275440</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>2037784344333275440</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2037784344333275440</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2037784344333275440</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Before clicking a link, what do you do?
+Stay Safe, Stay Vigilant. #UnitedAgainstFraud
+https://t.co/YpRWtBZrhq</t>
+        </is>
+      </c>
+      <c r="G80" t="n">
+        <v>1774680622000</v>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>2037784344333275440</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174061, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="K80" t="n">
+        <v>3</v>
+      </c>
+      <c r="L80" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" t="n">
+        <v>0</v>
+      </c>
+      <c r="N80" t="n">
+        <v>3</v>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>534</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="n">
+        <v>79</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2037784344333275440</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>2037784344333275440</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2037785874474430532</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>https://x.com/ZaibKang/status/2037785874474430532</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE I applied for liv X account Still not received any response 
+Reference number 
+2026038379331830</t>
+        </is>
+      </c>
       <c r="G81" t="n">
-        <v>1772260777000</v>
+        <v>1774680987000</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2027634643315404863</t>
+          <t>2037784344333275440</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2027634660532973568/img/NcwS9qq5kEQQ1U9q.jpg', 'type': 'video', 'id': '2027634660532973568'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Jahan Zaib Akbar Kang', 'screenName': 'ZaibKang', 'followersCount': 599, 'favouritesCount': 4475, 'friendsCount': 18, 'description': 'سُبْحَانَ اللَّهِ ، وَالْحَمْدُ لِلَّهِ ، وَلَا إِلَهَ إِلَّا اللَّهُ ، وَاللَّهُ أَكْبَرُ\nEntrepreneur &amp; investor'}</t>
         </is>
       </c>
       <c r="K81" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="L81" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>2290</t>
+          <t>34</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>2027634643315404863</t>
+          <t>2037784344333275440</t>
         </is>
       </c>
     </row>
@@ -6190,35 +6200,37 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784405700419683</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2037784344333275440</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2037784405700419683</t>
+          <t>2037784344333275440</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2037784405700419683</t>
+          <t>2037801868244533349</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784405700419683</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2037801868244533349</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Exchanger volunteer program @semeet @zeynp_qas @SelmaRomola 🌿🇦🇪❤️</t>
+          <t>What’s more suspicious?
+Stay Safe, Stay Vigilant. #UnitedAgainstFraud
+https://t.co/YpRWtBZrhq</t>
         </is>
       </c>
       <c r="G82" t="n">
-        <v>1774680637000</v>
+        <v>1774684800000</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2027634643315404863</t>
+          <t>2037801868244533349</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -6228,11 +6240,11 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>{'name': 'Soha.mostafa77', 'screenName': 'Sosomostafa729S', 'followersCount': 345, 'favouritesCount': 22185, 'friendsCount': 968, 'description': 'Moom of 2 🙍\u200d♂️🙍\u200d♀️\nShopping 🛍 food 😋 traveling \nLive in UAE 🇦🇪🕊💕'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174061, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="K82" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L82" t="n">
         <v>0</v>
@@ -6241,18 +6253,14 @@
         <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="P82" t="inlineStr">
-        <is>
-          <t>2027634776555872373</t>
-        </is>
-      </c>
+          <t>516</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
@@ -6304,7 +6312,7 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174061, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="K83" t="n">
@@ -6321,7 +6329,7 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>10505</t>
+          <t>10509</t>
         </is>
       </c>
       <c r="P83" t="inlineStr"/>
@@ -6376,7 +6384,7 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174061, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="K84" t="n">
@@ -6393,7 +6401,7 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>2290</t>
+          <t>2295</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -6463,7 +6471,7 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -6522,7 +6530,7 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174061, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="K86" t="n">
@@ -6539,7 +6547,7 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>10505</t>
+          <t>10509</t>
         </is>
       </c>
       <c r="P86" t="inlineStr"/>
@@ -6594,7 +6602,7 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174061, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="K87" t="n">
@@ -6611,7 +6619,7 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>2290</t>
+          <t>2295</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -6681,7 +6689,7 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -6740,7 +6748,7 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174061, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="K89" t="n">
@@ -6757,7 +6765,7 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>10505</t>
+          <t>10512</t>
         </is>
       </c>
       <c r="P89" t="inlineStr"/>
@@ -6812,7 +6820,7 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174061, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="K90" t="n">
@@ -6829,7 +6837,7 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>2290</t>
+          <t>2295</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
@@ -6900,7 +6908,7 @@
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
@@ -6975,7 +6983,7 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174061, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="K92" t="n">
@@ -6992,7 +7000,7 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>2346</t>
+          <t>2350</t>
         </is>
       </c>
       <c r="P92" t="inlineStr"/>
@@ -7058,7 +7066,7 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
@@ -7133,7 +7141,7 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174061, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="K94" t="n">
@@ -7150,7 +7158,7 @@
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>2350</t>
         </is>
       </c>
       <c r="P94" t="inlineStr"/>
@@ -7217,7 +7225,7 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
@@ -7232,25 +7240,168 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
+          <t>https://x.com/Sosomostafa729S/status/2037783477979091314</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>2037783477979091314</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>2034225946308358408</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2034225946308358408</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>اجعل مفاجآت العيد أكثر قيمة.
+من الفضة إلى الذهب، اكتشف طريقة أذكى لامتلاك أو إهداء شيء ثمين بحق.
+شاهد هذه الحلقة وأخبرنا:
+كيف يمكنك شراء الذهب والفضه من البنك؟
+للمشاركة:
+تابع حساب بنك الإمارات دبي الوطني 
+قم بالإشارة إلى 3 من أصدقائك
+اكتب إجابتك في التعليقات أدناه لفرصة ربح 10,000 درهم</t>
+        </is>
+      </c>
+      <c r="G96" t="n">
+        <v>1773832234000</v>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>2034225946308358408</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2034225772156563456/img/fizQ3vAEH0uqiLix.jpg', 'type': 'video', 'id': '2034225772156563456'}]</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174061, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="K96" t="n">
+        <v>91</v>
+      </c>
+      <c r="L96" t="n">
+        <v>1</v>
+      </c>
+      <c r="M96" t="n">
+        <v>39</v>
+      </c>
+      <c r="N96" t="n">
+        <v>50</v>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>2644</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2037783477979091314</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>2037783477979091314</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>2037783477979091314</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2037783477979091314</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE Through ENBD X Mobile Banking's App @parulghalout @semeet @Emy191990 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="G97" t="n">
+        <v>1774680415000</v>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>2034225946308358408</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>{'name': 'Soha.mostafa77', 'screenName': 'Sosomostafa729S', 'followersCount': 345, 'favouritesCount': 22185, 'friendsCount': 968, 'description': 'Moom of 2 🙍\u200d♂️🙍\u200d♀️\nShopping 🛍 food 😋 traveling \nLive in UAE 🇦🇪🕊💕'}</t>
+        </is>
+      </c>
+      <c r="K97" t="n">
+        <v>0</v>
+      </c>
+      <c r="L97" t="n">
+        <v>0</v>
+      </c>
+      <c r="M97" t="n">
+        <v>0</v>
+      </c>
+      <c r="N97" t="n">
+        <v>0</v>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>2034225946308358408</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="n">
+        <v>96</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
           <t>https://x.com/Sosomostafa729S/status/2037783775896313876</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr">
+      <c r="C98" t="inlineStr">
         <is>
           <t>2037783775896313876</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr">
+      <c r="D98" t="inlineStr">
         <is>
           <t>2031673422921564269</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr">
+      <c r="E98" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE/status/2031673422921564269</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr">
+      <c r="F98" t="inlineStr">
         <is>
           <t>نفذت أموال أم خماس قبل نهاية الشهر.
 هناك قاعدة بسيطة تُساعدها على إدارة أموالها بحكمة:
@@ -7277,138 +7428,138 @@
 - Drop your answer below for a chance to win AED 10,000</t>
         </is>
       </c>
-      <c r="G96" t="n">
+      <c r="G98" t="n">
         <v>1773223665000</v>
       </c>
-      <c r="H96" t="inlineStr">
+      <c r="H98" t="inlineStr">
         <is>
           <t>2031673422921564269</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr">
+      <c r="I98" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HDH0NZXWQAAnKTa.jpg', 'type': 'video', 'id': '2031673271423295488'}]</t>
         </is>
       </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="K96" t="n">
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174061, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="K98" t="n">
         <v>128</v>
       </c>
-      <c r="L96" t="n">
-        <v>0</v>
-      </c>
-      <c r="M96" t="n">
+      <c r="L98" t="n">
+        <v>0</v>
+      </c>
+      <c r="M98" t="n">
         <v>40</v>
       </c>
-      <c r="N96" t="n">
+      <c r="N98" t="n">
         <v>53</v>
       </c>
-      <c r="O96" t="inlineStr">
-        <is>
-          <t>2347</t>
-        </is>
-      </c>
-      <c r="P96" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="1" t="n">
-        <v>95</v>
-      </c>
-      <c r="B97" t="inlineStr">
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>2350</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="n">
+        <v>97</v>
+      </c>
+      <c r="B99" t="inlineStr">
         <is>
           <t>https://x.com/Sosomostafa729S/status/2037783775896313876</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr">
+      <c r="C99" t="inlineStr">
         <is>
           <t>2037783775896313876</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr">
+      <c r="D99" t="inlineStr">
         <is>
           <t>2037783775896313876</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr">
+      <c r="E99" t="inlineStr">
         <is>
           <t>https://x.com/Sosomostafa729S/status/2037783775896313876</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr">
+      <c r="F99" t="inlineStr">
         <is>
           <t>@EmiratesNBD_AE FINWELL ( Financial Well-being program) with Emirates NBD @SelmaRomola @Emy191990 @parulghalout 🌿🇦🇪❤️</t>
         </is>
       </c>
-      <c r="G97" t="n">
+      <c r="G99" t="n">
         <v>1774680487000</v>
       </c>
-      <c r="H97" t="inlineStr">
+      <c r="H99" t="inlineStr">
         <is>
           <t>2031673422921564269</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr">
+      <c r="I99" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="J97" t="inlineStr">
+      <c r="J99" t="inlineStr">
         <is>
           <t>{'name': 'Soha.mostafa77', 'screenName': 'Sosomostafa729S', 'followersCount': 345, 'favouritesCount': 22185, 'friendsCount': 968, 'description': 'Moom of 2 🙍\u200d♂️🙍\u200d♀️\nShopping 🛍 food 😋 traveling \nLive in UAE 🇦🇪🕊💕'}</t>
         </is>
       </c>
-      <c r="K97" t="n">
-        <v>0</v>
-      </c>
-      <c r="L97" t="n">
-        <v>0</v>
-      </c>
-      <c r="M97" t="n">
-        <v>0</v>
-      </c>
-      <c r="N97" t="n">
-        <v>0</v>
-      </c>
-      <c r="O97" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="P97" t="inlineStr">
+      <c r="K99" t="n">
+        <v>0</v>
+      </c>
+      <c r="L99" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" t="n">
+        <v>0</v>
+      </c>
+      <c r="N99" t="n">
+        <v>0</v>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
         <is>
           <t>2031673422921564269</t>
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="1" t="n">
-        <v>96</v>
-      </c>
-      <c r="B98" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="B100" t="inlineStr">
         <is>
           <t>https://x.com/Sosomostafa729S/status/2037783335389540775</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr">
+      <c r="C100" t="inlineStr">
         <is>
           <t>2037783335389540775</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr">
+      <c r="D100" t="inlineStr">
         <is>
           <t>2034225946308358408</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr">
+      <c r="E100" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE/status/2034225946308358408</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr">
+      <c r="F100" t="inlineStr">
         <is>
           <t>اجعل مفاجآت العيد أكثر قيمة.
 من الفضة إلى الذهب، اكتشف طريقة أذكى لامتلاك أو إهداء شيء ثمين بحق.
@@ -7420,138 +7571,138 @@
 اكتب إجابتك في التعليقات أدناه لفرصة ربح 10,000 درهم</t>
         </is>
       </c>
-      <c r="G98" t="n">
+      <c r="G100" t="n">
         <v>1773832234000</v>
       </c>
-      <c r="H98" t="inlineStr">
+      <c r="H100" t="inlineStr">
         <is>
           <t>2034225946308358408</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr">
+      <c r="I100" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2034225772156563456/img/fizQ3vAEH0uqiLix.jpg', 'type': 'video', 'id': '2034225772156563456'}]</t>
         </is>
       </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="K98" t="n">
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174061, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="K100" t="n">
         <v>91</v>
       </c>
-      <c r="L98" t="n">
+      <c r="L100" t="n">
         <v>1</v>
       </c>
-      <c r="M98" t="n">
+      <c r="M100" t="n">
         <v>39</v>
       </c>
-      <c r="N98" t="n">
+      <c r="N100" t="n">
         <v>50</v>
       </c>
-      <c r="O98" t="inlineStr">
-        <is>
-          <t>2640</t>
-        </is>
-      </c>
-      <c r="P98" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="1" t="n">
-        <v>97</v>
-      </c>
-      <c r="B99" t="inlineStr">
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>2644</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="n">
+        <v>99</v>
+      </c>
+      <c r="B101" t="inlineStr">
         <is>
           <t>https://x.com/Sosomostafa729S/status/2037783335389540775</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
+      <c r="C101" t="inlineStr">
         <is>
           <t>2037783335389540775</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr">
+      <c r="D101" t="inlineStr">
         <is>
           <t>2037783335389540775</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr">
+      <c r="E101" t="inlineStr">
         <is>
           <t>https://x.com/Sosomostafa729S/status/2037783335389540775</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr">
+      <c r="F101" t="inlineStr">
         <is>
           <t>@EmiratesNBD_AE Through ENBD X Mobile Banking's App @Emy191990 @parulghalout @ibushra_03 🌿🇦🇪❤️</t>
         </is>
       </c>
-      <c r="G99" t="n">
+      <c r="G101" t="n">
         <v>1774680381000</v>
       </c>
-      <c r="H99" t="inlineStr">
+      <c r="H101" t="inlineStr">
         <is>
           <t>2034225946308358408</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr">
+      <c r="I101" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="J99" t="inlineStr">
+      <c r="J101" t="inlineStr">
         <is>
           <t>{'name': 'Soha.mostafa77', 'screenName': 'Sosomostafa729S', 'followersCount': 345, 'favouritesCount': 22185, 'friendsCount': 968, 'description': 'Moom of 2 🙍\u200d♂️🙍\u200d♀️\nShopping 🛍 food 😋 traveling \nLive in UAE 🇦🇪🕊💕'}</t>
         </is>
       </c>
-      <c r="K99" t="n">
-        <v>0</v>
-      </c>
-      <c r="L99" t="n">
-        <v>0</v>
-      </c>
-      <c r="M99" t="n">
-        <v>0</v>
-      </c>
-      <c r="N99" t="n">
-        <v>0</v>
-      </c>
-      <c r="O99" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="P99" t="inlineStr">
+      <c r="K101" t="n">
+        <v>0</v>
+      </c>
+      <c r="L101" t="n">
+        <v>0</v>
+      </c>
+      <c r="M101" t="n">
+        <v>0</v>
+      </c>
+      <c r="N101" t="n">
+        <v>0</v>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
         <is>
           <t>2034225946308358408</t>
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="1" t="n">
-        <v>98</v>
-      </c>
-      <c r="B100" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="B102" t="inlineStr">
         <is>
           <t>https://x.com/Sosomostafa729S/status/2037783402758508685</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr">
+      <c r="C102" t="inlineStr">
         <is>
           <t>2037783402758508685</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr">
+      <c r="D102" t="inlineStr">
         <is>
           <t>2034225946308358408</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr">
+      <c r="E102" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE/status/2034225946308358408</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr">
+      <c r="F102" t="inlineStr">
         <is>
           <t>اجعل مفاجآت العيد أكثر قيمة.
 من الفضة إلى الذهب، اكتشف طريقة أذكى لامتلاك أو إهداء شيء ثمين بحق.
@@ -7563,176 +7714,39 @@
 اكتب إجابتك في التعليقات أدناه لفرصة ربح 10,000 درهم</t>
         </is>
       </c>
-      <c r="G100" t="n">
+      <c r="G102" t="n">
         <v>1773832234000</v>
       </c>
-      <c r="H100" t="inlineStr">
+      <c r="H102" t="inlineStr">
         <is>
           <t>2034225946308358408</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr">
+      <c r="I102" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2034225772156563456/img/fizQ3vAEH0uqiLix.jpg', 'type': 'video', 'id': '2034225772156563456'}]</t>
         </is>
       </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="K100" t="n">
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174061, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="K102" t="n">
         <v>91</v>
       </c>
-      <c r="L100" t="n">
+      <c r="L102" t="n">
         <v>1</v>
       </c>
-      <c r="M100" t="n">
+      <c r="M102" t="n">
         <v>39</v>
       </c>
-      <c r="N100" t="n">
+      <c r="N102" t="n">
         <v>50</v>
       </c>
-      <c r="O100" t="inlineStr">
-        <is>
-          <t>2640</t>
-        </is>
-      </c>
-      <c r="P100" t="inlineStr"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="1" t="n">
-        <v>99</v>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2037783402758508685</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>2037783402758508685</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>2037783402758508685</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2037783402758508685</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE Through ENBD X Mobile Banking's App @zeynp_qas @SelmaRomola @Salma2232019 🌿🇦🇪❤️</t>
-        </is>
-      </c>
-      <c r="G101" t="n">
-        <v>1774680398000</v>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>2034225946308358408</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>{'name': 'Soha.mostafa77', 'screenName': 'Sosomostafa729S', 'followersCount': 345, 'favouritesCount': 22185, 'friendsCount': 968, 'description': 'Moom of 2 🙍\u200d♂️🙍\u200d♀️\nShopping 🛍 food 😋 traveling \nLive in UAE 🇦🇪🕊💕'}</t>
-        </is>
-      </c>
-      <c r="K101" t="n">
-        <v>0</v>
-      </c>
-      <c r="L101" t="n">
-        <v>0</v>
-      </c>
-      <c r="M101" t="n">
-        <v>0</v>
-      </c>
-      <c r="N101" t="n">
-        <v>0</v>
-      </c>
-      <c r="O101" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="P101" t="inlineStr">
-        <is>
-          <t>2034225946308358408</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>https://x.com/wil3020/status/2037730056920088898</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>2037730056920088898</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>2037432200166277382</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037432200166277382</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>Stay safe and bank with ease with ENBD X and businessONLINE 
-Visit https://t.co/0Z1tddYvqD https://t.co/l7XrKjfHOu</t>
-        </is>
-      </c>
-      <c r="G102" t="n">
-        <v>1774596664000</v>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>2037432200166277382</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEZpyN2aMAAR1EU.jpg', 'type': 'photo', 'id': '2037432192863973376'}]</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="K102" t="n">
-        <v>2</v>
-      </c>
-      <c r="L102" t="n">
-        <v>0</v>
-      </c>
-      <c r="M102" t="n">
-        <v>1</v>
-      </c>
-      <c r="N102" t="n">
-        <v>9</v>
-      </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>945</t>
+          <t>2644</t>
         </is>
       </c>
       <c r="P102" t="inlineStr"/>
@@ -7743,35 +7757,35 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>https://x.com/wil3020/status/2037730056920088898</t>
+          <t>https://x.com/Sosomostafa729S/status/2037783402758508685</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2037730056920088898</t>
+          <t>2037783402758508685</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2037730056920088898</t>
+          <t>2037783402758508685</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>https://x.com/wil3020/status/2037730056920088898</t>
+          <t>https://x.com/Sosomostafa729S/status/2037783402758508685</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE The UAE is no longer safe Continuous and comprehensive bombing of the UAE now</t>
+          <t>@EmiratesNBD_AE Through ENBD X Mobile Banking's App @zeynp_qas @SelmaRomola @Salma2232019 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="G103" t="n">
-        <v>1774667679000</v>
+        <v>1774680398000</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2037432200166277382</t>
+          <t>2034225946308358408</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -7781,7 +7795,7 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>{'name': 'wiil', 'screenName': 'wil3020', 'followersCount': 49, 'favouritesCount': 1810, 'friendsCount': 24, 'description': 'تهوى العين من يعجبها، ويهوى العقل من يفهمه، أمّا الروح فلا تهوى إلاّ من يُشبهها.'}</t>
+          <t>{'name': 'Soha.mostafa77', 'screenName': 'Sosomostafa729S', 'followersCount': 345, 'favouritesCount': 22185, 'friendsCount': 968, 'description': 'Moom of 2 🙍\u200d♂️🙍\u200d♀️\nShopping 🛍 food 😋 traveling \nLive in UAE 🇦🇪🕊💕'}</t>
         </is>
       </c>
       <c r="K103" t="n">
@@ -7798,12 +7812,12 @@
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>2037432200166277382</t>
+          <t>2034225946308358408</t>
         </is>
       </c>
     </row>
@@ -7813,12 +7827,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037783049065390446</t>
+          <t>https://x.com/Sosomostafa729S/status/2037783125854679453</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2037783049065390446</t>
+          <t>2037783125854679453</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -7858,7 +7872,7 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174061, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="K104" t="n">
@@ -7875,7 +7889,7 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>1679</t>
+          <t>1682</t>
         </is>
       </c>
       <c r="P104" t="inlineStr"/>
@@ -7886,32 +7900,31 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037783049065390446</t>
+          <t>https://x.com/Sosomostafa729S/status/2037783125854679453</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2037783049065390446</t>
+          <t>2037783125854679453</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2037783049065390446</t>
+          <t>2037783125854679453</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037783049065390446</t>
+          <t>https://x.com/Sosomostafa729S/status/2037783125854679453</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Through ENBD X Mobile Banking's App 
-@Emy191990 @ibushra_03 @semeet 🌿🇦🇪❤️</t>
+          <t>@EmiratesNBD_AE Through ENBD X Mobile Banking's App @parulghalout @Salma2232019 @semeet 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="G105" t="n">
-        <v>1774680313000</v>
+        <v>1774680332000</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
@@ -7942,7 +7955,7 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
@@ -7957,25 +7970,162 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037783125854679453</t>
+          <t>https://x.com/wil3020/status/2037730056920088898</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2037783125854679453</t>
+          <t>2037730056920088898</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
+          <t>2037432200166277382</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2037432200166277382</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Stay safe and bank with ease with ENBD X and businessONLINE 
+Visit https://t.co/0Z1tddYvqD https://t.co/l7XrKjfHOu</t>
+        </is>
+      </c>
+      <c r="G106" t="n">
+        <v>1774596664000</v>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>2037432200166277382</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEZpyN2aMAAR1EU.jpg', 'type': 'photo', 'id': '2037432192863973376'}]</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174061, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="K106" t="n">
+        <v>2</v>
+      </c>
+      <c r="L106" t="n">
+        <v>0</v>
+      </c>
+      <c r="M106" t="n">
+        <v>1</v>
+      </c>
+      <c r="N106" t="n">
+        <v>9</v>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>946</t>
+        </is>
+      </c>
+      <c r="P106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="n">
+        <v>105</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>https://x.com/wil3020/status/2037730056920088898</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>2037730056920088898</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>2037730056920088898</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>https://x.com/wil3020/status/2037730056920088898</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE The UAE is no longer safe Continuous and comprehensive bombing of the UAE now</t>
+        </is>
+      </c>
+      <c r="G107" t="n">
+        <v>1774667679000</v>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>2037432200166277382</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>{'name': 'wiil', 'screenName': 'wil3020', 'followersCount': 49, 'favouritesCount': 1811, 'friendsCount': 24, 'description': 'تهوى العين من يعجبها، ويهوى العقل من يفهمه، أمّا الروح فلا تهوى إلاّ من يُشبهها.'}</t>
+        </is>
+      </c>
+      <c r="K107" t="n">
+        <v>0</v>
+      </c>
+      <c r="L107" t="n">
+        <v>0</v>
+      </c>
+      <c r="M107" t="n">
+        <v>0</v>
+      </c>
+      <c r="N107" t="n">
+        <v>0</v>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>2037432200166277382</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="n">
+        <v>106</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2037783049065390446</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>2037783049065390446</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
           <t>2034225964863893587</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr">
+      <c r="E108" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE/status/2034225964863893587</t>
         </is>
       </c>
-      <c r="F106" t="inlineStr">
+      <c r="F108" t="inlineStr">
         <is>
           <t>Make Eid surprises even more valuable.
 From silver to gold, discover a smarter way to own or gift something truly precious.
@@ -7987,108 +8137,109 @@
 Drop your answer below for a chance to win AED 10,000</t>
         </is>
       </c>
-      <c r="G106" t="n">
+      <c r="G108" t="n">
         <v>1773832238000</v>
       </c>
-      <c r="H106" t="inlineStr">
+      <c r="H108" t="inlineStr">
         <is>
           <t>2034225964863893587</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr">
+      <c r="I108" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2034225751092822016/img/ppYucbpuWh6bd_l0.jpg', 'type': 'video', 'id': '2034225751092822016'}]</t>
         </is>
       </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="K106" t="n">
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174061, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="K108" t="n">
         <v>72</v>
       </c>
-      <c r="L106" t="n">
-        <v>0</v>
-      </c>
-      <c r="M106" t="n">
+      <c r="L108" t="n">
+        <v>0</v>
+      </c>
+      <c r="M108" t="n">
         <v>29</v>
       </c>
-      <c r="N106" t="n">
+      <c r="N108" t="n">
         <v>46</v>
       </c>
-      <c r="O106" t="inlineStr">
-        <is>
-          <t>1679</t>
-        </is>
-      </c>
-      <c r="P106" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="1" t="n">
-        <v>105</v>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2037783125854679453</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>2037783125854679453</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>2037783125854679453</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2037783125854679453</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE Through ENBD X Mobile Banking's App @parulghalout @Salma2232019 @semeet 🌿🇦🇪❤️</t>
-        </is>
-      </c>
-      <c r="G107" t="n">
-        <v>1774680332000</v>
-      </c>
-      <c r="H107" t="inlineStr">
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>1682</t>
+        </is>
+      </c>
+      <c r="P108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="n">
+        <v>107</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2037783049065390446</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>2037783049065390446</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>2037783049065390446</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2037783049065390446</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE Through ENBD X Mobile Banking's App 
+@Emy191990 @ibushra_03 @semeet 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="G109" t="n">
+        <v>1774680313000</v>
+      </c>
+      <c r="H109" t="inlineStr">
         <is>
           <t>2034225964863893587</t>
         </is>
       </c>
-      <c r="I107" t="inlineStr">
+      <c r="I109" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="J107" t="inlineStr">
+      <c r="J109" t="inlineStr">
         <is>
           <t>{'name': 'Soha.mostafa77', 'screenName': 'Sosomostafa729S', 'followersCount': 345, 'favouritesCount': 22185, 'friendsCount': 968, 'description': 'Moom of 2 🙍\u200d♂️🙍\u200d♀️\nShopping 🛍 food 😋 traveling \nLive in UAE 🇦🇪🕊💕'}</t>
         </is>
       </c>
-      <c r="K107" t="n">
-        <v>0</v>
-      </c>
-      <c r="L107" t="n">
-        <v>0</v>
-      </c>
-      <c r="M107" t="n">
-        <v>0</v>
-      </c>
-      <c r="N107" t="n">
-        <v>0</v>
-      </c>
-      <c r="O107" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="P107" t="inlineStr">
+      <c r="K109" t="n">
+        <v>0</v>
+      </c>
+      <c r="L109" t="n">
+        <v>0</v>
+      </c>
+      <c r="M109" t="n">
+        <v>0</v>
+      </c>
+      <c r="N109" t="n">
+        <v>0</v>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P109" t="inlineStr">
         <is>
           <t>2034225964863893587</t>
         </is>

--- a/Xpost_df_comments.xlsx
+++ b/Xpost_df_comments.xlsx
@@ -567,7 +567,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>159</t>
         </is>
       </c>
       <c r="P2" t="inlineStr"/>
@@ -636,7 +636,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>98</t>
         </is>
       </c>
       <c r="P3" t="inlineStr"/>
@@ -691,7 +691,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>{'name': 'Rotana Live', 'screenName': 'RotanaLive', 'followersCount': 193532, 'favouritesCount': 7072, 'friendsCount': 149, 'description': 'روتانا لايف الحساب الرسمي لحفلات روتانا | Rotana events https://t.co/wTAoLH4wPm'}</t>
+          <t>{'name': 'Rotana Live', 'screenName': 'RotanaLive', 'followersCount': 193533, 'favouritesCount': 7072, 'friendsCount': 149, 'description': 'روتانا لايف الحساب الرسمي لحفلات روتانا | Rotana events https://t.co/wTAoLH4wPm'}</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -708,7 +708,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>6604</t>
+          <t>6605</t>
         </is>
       </c>
       <c r="P4" t="inlineStr"/>
@@ -774,7 +774,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -805,7 +805,7 @@
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="n">
-        <v>1776223385969</v>
+        <v>1776225794636</v>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>1344</t>
+          <t>1350</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2006,7 +2006,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>96</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>99</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>{'name': 'Chirin Al Asadi', 'screenName': 'ChirinAsadi', 'followersCount': 3881, 'favouritesCount': 2850, 'friendsCount': 237, 'description': 'كل الكتابات والافكار هنا 👇🏻أصلية.. أغرد بأفكاري الخاصة بي .. أيضا: قرارك الاستثماري يخصك وحدك🤍 لا تأخذ بأرائي - اسأل مستشارك'}</t>
+          <t>{'name': 'Chirin Al Asadi', 'screenName': 'ChirinAsadi', 'followersCount': 3884, 'favouritesCount': 2850, 'friendsCount': 237, 'description': 'كل الكتابات والافكار هنا 👇🏻أصلية.. أغرد بأفكاري الخاصة بي .. أيضا: قرارك الاستثماري يخصك وحدك🤍 لا تأخذ بأرائي - اسأل مستشارك'}</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -2224,7 +2224,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>2522</t>
+          <t>2561</t>
         </is>
       </c>
       <c r="P26" t="inlineStr"/>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>96</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -2344,7 +2344,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>{'name': 'Chirin Al Asadi', 'screenName': 'ChirinAsadi', 'followersCount': 3881, 'favouritesCount': 2850, 'friendsCount': 237, 'description': 'كل الكتابات والافكار هنا 👇🏻أصلية.. أغرد بأفكاري الخاصة بي .. أيضا: قرارك الاستثماري يخصك وحدك🤍 لا تأخذ بأرائي - اسأل مستشارك'}</t>
+          <t>{'name': 'Chirin Al Asadi', 'screenName': 'ChirinAsadi', 'followersCount': 3884, 'favouritesCount': 2850, 'friendsCount': 237, 'description': 'كل الكتابات والافكار هنا 👇🏻أصلية.. أغرد بأفكاري الخاصة بي .. أيضا: قرارك الاستثماري يخصك وحدك🤍 لا تأخذ بأرائي - اسأل مستشارك'}</t>
         </is>
       </c>
       <c r="K28" t="n">
@@ -2361,7 +2361,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>94</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -2431,7 +2431,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P29" t="inlineStr"/>
@@ -2497,7 +2497,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -2512,12 +2512,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044077090039873867</t>
+          <t>https://x.com/attas_2010/status/2044078376982319373</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2044077090039873867</t>
+          <t>2044078376982319373</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2570,7 +2570,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>2533</t>
+          <t>2535</t>
         </is>
       </c>
       <c r="P31" t="inlineStr"/>
@@ -2581,12 +2581,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044077090039873867</t>
+          <t>https://x.com/attas_2010/status/2044078376982319373</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2044077090039873867</t>
+          <t>2044078376982319373</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2636,7 +2636,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>1009</t>
+          <t>1010</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -2651,12 +2651,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044077090039873867</t>
+          <t>https://x.com/attas_2010/status/2044078376982319373</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2044077090039873867</t>
+          <t>2044078376982319373</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>142</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -2721,12 +2721,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044077090039873867</t>
+          <t>https://x.com/attas_2010/status/2044078376982319373</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2044077090039873867</t>
+          <t>2044078376982319373</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2777,7 +2777,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>83</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044077090039873867</t>
+          <t>https://x.com/attas_2010/status/2044078376982319373</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2044077090039873867</t>
+          <t>2044078376982319373</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2847,7 +2847,7 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>112</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044077090039873867</t>
+          <t>https://x.com/attas_2010/status/2044078376982319373</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2044077090039873867</t>
+          <t>2044078376982319373</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2917,7 +2917,7 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>63</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -2940,17 +2940,171 @@
           <t>2044078376982319373</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>https://x.com/undefined/status/undefined</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="n">
+        <v>1776225826173</v>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>https://x.com/attas_2010/status/2044078376982319373</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2044078376982319373</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>https://x.com/undefined/status/undefined</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="n">
+        <v>1776225826173</v>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>https://x.com/attas_2010/status/2044078376982319373</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2044078376982319373</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2044078376982319373</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>https://x.com/attas_2010/status/2044078376982319373</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>@KhalidSaeedR @amsh75 @alrajhibank @BSF_sa @alinma @BankAlbilad @snbalahli @GulfIntlBank @EmiratesNBD_AE @BankAlJazira @RiyadBank @alawwalsab @SAIBLIVE فوق ١٠ مرات ارفع شكاوي هذا الرد</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>1776181236000</v>
+      </c>
+      <c r="H39" t="inlineStr">
         <is>
           <t>1962127907049930843</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>{'name': 'محمد', 'screenName': 'attas_2010', 'followersCount': 2342, 'favouritesCount': 3675, 'friendsCount': 4836, 'description': 'لا إله إلا الله محمد رسول الله\nتابعني وأتابعك'}</t>
+        </is>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>2044078181662019702</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>https://x.com/attas_2010/status/2044077341328957795</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2044077341328957795</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>1962127907049930843</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
         <is>
           <t>https://x.com/amsh75/status/1962127907049930843</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>سؤال:
 ماهو افضل بنك يشتري مديونية ؟!
@@ -2958,253 +3112,42 @@
 @alrajhibank @BSF_sa @alinma @BankAlbilad @snbalahli @GulfIntlBank @EmiratesNBD_AE @BankAlJazira @RiyadBank @alawwalsab @SAIBLIVE</t>
         </is>
       </c>
-      <c r="G37" t="n">
+      <c r="G40" t="n">
         <v>1756642722000</v>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>1962127907049930843</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>{'name': 'علي محمد الضبعان', 'screenName': 'amsh75', 'followersCount': 32674, 'favouritesCount': 2853, 'friendsCount': 6053, 'description': 'حاصل على وسام الملك عبدالعزيز من الدرجة الثالثة/ مدير فرع @Trahum_sa بالمنطقة الشرقية/ عضو لجنة الاسكان التنموي بالمنطقة الشرقية / رئيس مجلس إدارة @tadom_sa'}</t>
         </is>
       </c>
-      <c r="K37" t="n">
+      <c r="K40" t="n">
         <v>13</v>
       </c>
-      <c r="L37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M37" t="n">
-        <v>0</v>
-      </c>
-      <c r="N37" t="n">
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
         <v>2</v>
       </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>2533</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="n">
-        <v>36</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>https://x.com/attas_2010/status/2044078376982319373</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>2044078376982319373</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>1962458003224854945</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>https://x.com/KhalidSaeedR/status/1962458003224854945</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>@amsh75 @alrajhibank @BSF_sa @alinma @BankAlbilad @snbalahli @GulfIntlBank @EmiratesNBD_AE @BankAlJazira @RiyadBank @alawwalsab @SAIBLIVE انا ابحث ايضا عن شراء المديونيه قرض عقاري قرض شخصي،،،</t>
-        </is>
-      </c>
-      <c r="G38" t="n">
-        <v>1756721423000</v>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>1962127907049930843</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>{'name': 'خالد سعيد اليْمِنِي (أبو مشاري)', 'screenName': 'KhalidSaeedR', 'followersCount': 11096, 'favouritesCount': 6906, 'friendsCount': 1130, 'description': 'صحافي ومذيع  تلفزيوني   ومقدم حفلات رسميه،،،\nأخصائي وممارس العلاقات العامه،،'}</t>
-        </is>
-      </c>
-      <c r="K38" t="n">
-        <v>11</v>
-      </c>
-      <c r="L38" t="n">
-        <v>0</v>
-      </c>
-      <c r="M38" t="n">
-        <v>0</v>
-      </c>
-      <c r="N38" t="n">
-        <v>1</v>
-      </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>1009</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>1962127907049930843</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="n">
-        <v>37</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>https://x.com/attas_2010/status/2044078376982319373</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>2044078376982319373</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>2044075725334954107</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>https://x.com/attas_2010/status/2044075725334954107</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>@KhalidSaeedR @amsh75 @alrajhibank @BSF_sa @alinma @BankAlbilad @snbalahli @GulfIntlBank @EmiratesNBD_AE @BankAlJazira @RiyadBank @alawwalsab @SAIBLIVE والله من خلال تجربتي مع البنك السعودي الفرنسي لا انصح ابدا بشراء مديونية منه اتفقت مع الموظف على اعادة تمويل وكنت في بنك الرياض علي قرض شخصي وعقاري اتفقت مع الموظف بعد ماشاف راتبي والعقار المرهون لبنك الرياض قيمته ٣ مليون  قدروه عمارة ٢٥ شقة المهم موظف البنك الفرنسي</t>
-        </is>
-      </c>
-      <c r="G39" t="n">
-        <v>1776180604000</v>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>1962127907049930843</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>{'name': 'محمد', 'screenName': 'attas_2010', 'followersCount': 2342, 'favouritesCount': 3675, 'friendsCount': 4836, 'description': 'لا إله إلا الله محمد رسول الله\nتابعني وأتابعك'}</t>
-        </is>
-      </c>
-      <c r="K39" t="n">
-        <v>2</v>
-      </c>
-      <c r="L39" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" t="n">
-        <v>0</v>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>1962458003224854945</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="n">
-        <v>38</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>https://x.com/attas_2010/status/2044078376982319373</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>2044078376982319373</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>2044076340891009154</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>https://x.com/attas_2010/status/2044076340891009154</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>@KhalidSaeedR @amsh75 @alrajhibank @BSF_sa @alinma @BankAlbilad @snbalahli @GulfIntlBank @EmiratesNBD_AE @BankAlJazira @RiyadBank @alawwalsab @SAIBLIVE موظف البنك الفرنسي قال نعطيك اعادة تمويل ويطلع لك فائض بالشخصي٧٥٠٠٠ وفعلا تحولت لي والعقاري قال يفيض لك٢٥٥٠٠٠ وسحب علي وماعاد يرد وحتى اليوم فوق ١٠ مرات احاول ارفع شكوى من التطبيق مايقبلون الشكوى 
-اصلا</t>
-        </is>
-      </c>
-      <c r="G40" t="n">
-        <v>1776180751000</v>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>1962127907049930843</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>{'name': 'محمد', 'screenName': 'attas_2010', 'followersCount': 2342, 'favouritesCount': 3675, 'friendsCount': 4836, 'description': 'لا إله إلا الله محمد رسول الله\nتابعني وأتابعك'}</t>
-        </is>
-      </c>
-      <c r="K40" t="n">
-        <v>1</v>
-      </c>
-      <c r="L40" t="n">
-        <v>0</v>
-      </c>
-      <c r="M40" t="n">
-        <v>0</v>
-      </c>
-      <c r="N40" t="n">
-        <v>0</v>
-      </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>2044075725334954107</t>
-        </is>
-      </c>
+          <t>2535</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
@@ -3212,31 +3155,31 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044078376982319373</t>
+          <t>https://x.com/attas_2010/status/2044077341328957795</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2044078376982319373</t>
+          <t>2044077341328957795</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2044077090039873867</t>
+          <t>1962458003224854945</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044077090039873867</t>
+          <t>https://x.com/KhalidSaeedR/status/1962458003224854945</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>@KhalidSaeedR @amsh75 @alrajhibank @BSF_sa @alinma @BankAlbilad @snbalahli @GulfIntlBank @EmiratesNBD_AE @BankAlJazira @RiyadBank @alawwalsab @SAIBLIVE وحاليا بعد ماكان عندي قرض عقاري في بنك الرياض راح ارجعه مليون٦٠٠ ألف على ١٥ سنةصرت مديون للبنك الفرنسي مليونين ٣٠٠ ألف والصك مرهون عندهم وكل الي سوه سددو لبنك الرياض مليون ٧٠الف قيمة السداد المبكر فقط والفائض الي وعدني فيه سحب علي ومايرد</t>
+          <t>@amsh75 @alrajhibank @BSF_sa @alinma @BankAlbilad @snbalahli @GulfIntlBank @EmiratesNBD_AE @BankAlJazira @RiyadBank @alawwalsab @SAIBLIVE انا ابحث ايضا عن شراء المديونيه قرض عقاري قرض شخصي،،،</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>1776180930000</v>
+        <v>1756721423000</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -3250,11 +3193,11 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>{'name': 'محمد', 'screenName': 'attas_2010', 'followersCount': 2342, 'favouritesCount': 3675, 'friendsCount': 4836, 'description': 'لا إله إلا الله محمد رسول الله\nتابعني وأتابعك'}</t>
+          <t>{'name': 'خالد سعيد اليْمِنِي (أبو مشاري)', 'screenName': 'KhalidSaeedR', 'followersCount': 11096, 'favouritesCount': 6906, 'friendsCount': 1130, 'description': 'صحافي ومذيع  تلفزيوني   ومقدم حفلات رسميه،،،\nأخصائي وممارس العلاقات العامه،،'}</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -3263,16 +3206,16 @@
         <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>1010</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>2044076340891009154</t>
+          <t>1962127907049930843</t>
         </is>
       </c>
     </row>
@@ -3282,31 +3225,31 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044078376982319373</t>
+          <t>https://x.com/attas_2010/status/2044077341328957795</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2044078376982319373</t>
+          <t>2044077341328957795</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2044077341328957795</t>
+          <t>2044075725334954107</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044077341328957795</t>
+          <t>https://x.com/attas_2010/status/2044075725334954107</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>@KhalidSaeedR @amsh75 @alrajhibank @BSF_sa @alinma @BankAlbilad @snbalahli @GulfIntlBank @EmiratesNBD_AE @BankAlJazira @RiyadBank @alawwalsab @SAIBLIVE والله كاننا نتعامل مع عصابة مو موظف بنك لي ١٧ سنة اتعامل مع البنوك عمري ماشفت تعامل مثل البنك الفرنسي</t>
+          <t>@KhalidSaeedR @amsh75 @alrajhibank @BSF_sa @alinma @BankAlbilad @snbalahli @GulfIntlBank @EmiratesNBD_AE @BankAlJazira @RiyadBank @alawwalsab @SAIBLIVE والله من خلال تجربتي مع البنك السعودي الفرنسي لا انصح ابدا بشراء مديونية منه اتفقت مع الموظف على اعادة تمويل وكنت في بنك الرياض علي قرض شخصي وعقاري اتفقت مع الموظف بعد ماشاف راتبي والعقار المرهون لبنك الرياض قيمته ٣ مليون  قدروه عمارة ٢٥ شقة المهم موظف البنك الفرنسي</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>1776180989000</v>
+        <v>1776180604000</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -3324,7 +3267,7 @@
         </is>
       </c>
       <c r="K42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
@@ -3337,12 +3280,12 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>142</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>2044077090039873867</t>
+          <t>1962458003224854945</t>
         </is>
       </c>
     </row>
@@ -3352,25 +3295,38 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044078376982319373</t>
+          <t>https://x.com/attas_2010/status/2044077341328957795</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2044078376982319373</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
+          <t>2044077341328957795</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2044076340891009154</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://x.com/undefined/status/undefined</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr"/>
+          <t>https://x.com/attas_2010/status/2044076340891009154</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>@KhalidSaeedR @amsh75 @alrajhibank @BSF_sa @alinma @BankAlbilad @snbalahli @GulfIntlBank @EmiratesNBD_AE @BankAlJazira @RiyadBank @alawwalsab @SAIBLIVE موظف البنك الفرنسي قال نعطيك اعادة تمويل ويطلع لك فائض بالشخصي٧٥٠٠٠ وفعلا تحولت لي والعقاري قال يفيض لك٢٥٥٠٠٠ وسحب علي وماعاد يرد وحتى اليوم فوق ١٠ مرات احاول ارفع شكوى من التطبيق مايقبلون الشكوى 
+اصلا</t>
+        </is>
+      </c>
       <c r="G43" t="n">
-        <v>1776223418005</v>
-      </c>
-      <c r="H43" t="inlineStr"/>
+        <v>1776180751000</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>1962127907049930843</t>
+        </is>
+      </c>
       <c r="I43" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3378,15 +3334,31 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr"/>
+          <t>{'name': 'محمد', 'screenName': 'attas_2010', 'followersCount': 2342, 'favouritesCount': 3675, 'friendsCount': 4836, 'description': 'لا إله إلا الله محمد رسول الله\nتابعني وأتابعك'}</t>
+        </is>
+      </c>
+      <c r="K43" t="n">
+        <v>1</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>2044075725334954107</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
@@ -3394,25 +3366,37 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044078376982319373</t>
+          <t>https://x.com/attas_2010/status/2044077341328957795</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2044078376982319373</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr"/>
+          <t>2044077341328957795</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2044077090039873867</t>
+        </is>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://x.com/undefined/status/undefined</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr"/>
+          <t>https://x.com/attas_2010/status/2044077090039873867</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>@KhalidSaeedR @amsh75 @alrajhibank @BSF_sa @alinma @BankAlbilad @snbalahli @GulfIntlBank @EmiratesNBD_AE @BankAlJazira @RiyadBank @alawwalsab @SAIBLIVE وحاليا بعد ماكان عندي قرض عقاري في بنك الرياض راح ارجعه مليون٦٠٠ ألف على ١٥ سنةصرت مديون للبنك الفرنسي مليونين ٣٠٠ ألف والصك مرهون عندهم وكل الي سوه سددو لبنك الرياض مليون ٧٠الف قيمة السداد المبكر فقط والفائض الي وعدني فيه سحب علي ومايرد</t>
+        </is>
+      </c>
       <c r="G44" t="n">
-        <v>1776223418005</v>
-      </c>
-      <c r="H44" t="inlineStr"/>
+        <v>1776180930000</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>1962127907049930843</t>
+        </is>
+      </c>
       <c r="I44" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3420,15 +3404,31 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr"/>
+          <t>{'name': 'محمد', 'screenName': 'attas_2010', 'followersCount': 2342, 'favouritesCount': 3675, 'friendsCount': 4836, 'description': 'لا إله إلا الله محمد رسول الله\nتابعني وأتابعك'}</t>
+        </is>
+      </c>
+      <c r="K44" t="n">
+        <v>1</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>2044076340891009154</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
@@ -3436,31 +3436,31 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044078376982319373</t>
+          <t>https://x.com/attas_2010/status/2044077341328957795</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2044078376982319373</t>
+          <t>2044077341328957795</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2044078376982319373</t>
+          <t>2044077341328957795</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044078376982319373</t>
+          <t>https://x.com/attas_2010/status/2044077341328957795</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>@KhalidSaeedR @amsh75 @alrajhibank @BSF_sa @alinma @BankAlbilad @snbalahli @GulfIntlBank @EmiratesNBD_AE @BankAlJazira @RiyadBank @alawwalsab @SAIBLIVE فوق ١٠ مرات ارفع شكاوي هذا الرد</t>
+          <t>@KhalidSaeedR @amsh75 @alrajhibank @BSF_sa @alinma @BankAlbilad @snbalahli @GulfIntlBank @EmiratesNBD_AE @BankAlJazira @RiyadBank @alawwalsab @SAIBLIVE والله كاننا نتعامل مع عصابة مو موظف بنك لي ١٧ سنة اتعامل مع البنوك عمري ماشفت تعامل مثل البنك الفرنسي</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>1776181236000</v>
+        <v>1776180989000</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         </is>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
@@ -3491,12 +3491,12 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>63</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>2044078181662019702</t>
+          <t>2044077090039873867</t>
         </is>
       </c>
     </row>
@@ -3506,12 +3506,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044077341328957795</t>
+          <t>https://x.com/attas_2010/status/2044077090039873867</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2044077341328957795</t>
+          <t>2044077090039873867</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>2533</t>
+          <t>2535</t>
         </is>
       </c>
       <c r="P46" t="inlineStr"/>
@@ -3575,12 +3575,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044077341328957795</t>
+          <t>https://x.com/attas_2010/status/2044077090039873867</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2044077341328957795</t>
+          <t>2044077090039873867</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>1009</t>
+          <t>1010</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044077341328957795</t>
+          <t>https://x.com/attas_2010/status/2044077090039873867</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2044077341328957795</t>
+          <t>2044077090039873867</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3700,7 +3700,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>142</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044077341328957795</t>
+          <t>https://x.com/attas_2010/status/2044077090039873867</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2044077341328957795</t>
+          <t>2044077090039873867</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3771,7 +3771,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>83</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044077341328957795</t>
+          <t>https://x.com/attas_2010/status/2044077090039873867</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2044077341328957795</t>
+          <t>2044077090039873867</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3841,7 +3841,7 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>112</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -3856,12 +3856,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044077341328957795</t>
+          <t>https://x.com/attas_2010/status/2044077090039873867</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2044077341328957795</t>
+          <t>2044077090039873867</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3911,7 +3911,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>63</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -3984,7 +3984,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>2533</t>
+          <t>2535</t>
         </is>
       </c>
       <c r="P52" t="inlineStr"/>
@@ -4050,7 +4050,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>1009</t>
+          <t>1010</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>142</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>83</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -4261,7 +4261,7 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>112</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -4334,7 +4334,7 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>2533</t>
+          <t>2535</t>
         </is>
       </c>
       <c r="P57" t="inlineStr"/>
@@ -4400,7 +4400,7 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>1009</t>
+          <t>1010</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -4470,7 +4470,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>142</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -4541,7 +4541,7 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>83</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -4613,7 +4613,7 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -4628,35 +4628,37 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>https://x.com/dcgguide/status/2044025847523487886</t>
+          <t>https://x.com/biztoday_intl/status/2044047297034760542</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2044025847523487886</t>
+          <t>2044047297034760542</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2044025847523487886</t>
+          <t>2044047297034760542</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>https://x.com/dcgguide/status/2044025847523487886</t>
+          <t>https://x.com/biztoday_intl/status/2044047297034760542</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Emirates NBD And Sobha Realty Partner To Offer Integrated Home Financing Solutions For Off-Plan Projects In Dubai https://t.co/fVBST6NQ7A</t>
+          <t>@EmiratesNBD_AE and @SobhaRealtyDXB partner to offer integrated home financing solutions for off-plan projects in #Dubai .
+#EmiratesNBD #SobhaRealty #UAE #Dubairealestate #realestate
+https://t.co/ukweMYki3P</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>1776168712000</v>
+        <v>1776173826000</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2044025847523487886</t>
+          <t>2044047297034760542</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4666,7 +4668,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>{'name': 'DUBAI CITY GUIDE from Cyber Gear', 'screenName': 'dcgguide', 'followersCount': 93486, 'favouritesCount': 19465, 'friendsCount': 106588, 'description': 'DCG is a https://t.co/bmR4jltJAW e-venture. We publish guest posts at https://t.co/EISzXb0O0y Learn AI at https://t.co/YcnxpXcCNU'}</t>
+          <t>{'name': 'Biz Today Intl', 'screenName': 'biztoday_intl', 'followersCount': 469, 'favouritesCount': 969, 'friendsCount': 107, 'description': "Biz Today is the World's preeminent 24-hour English language business, economics, technology and finance to travel, fashion and lifestyle publication"}</t>
         </is>
       </c>
       <c r="K62" t="n">
@@ -4676,14 +4678,14 @@
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>49</t>
         </is>
       </c>
       <c r="P62" t="inlineStr"/>
@@ -4694,35 +4696,37 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>https://x.com/dcgguide/status/2044025847523487886</t>
+          <t>https://x.com/biztoday_intl/status/2044047297034760542</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2044025847523487886</t>
+          <t>2044047297034760542</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2044038292707143832</t>
+          <t>2044060507603382318</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>https://x.com/dcgguide/status/2044038292707143832</t>
+          <t>https://x.com/biztoday_intl/status/2044060507603382318</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Presenting Project Nightingale: A Coachbuild Collection https://t.co/KEb4FjZgsI</t>
+          <t>#DaherAircraft strengthens its customer support and distributor Network by adding the Kodiak to Columbia Air’s portfolio.
+@DAHER_official #aircraft #aviation #NicolasChabbert #MelissaDuzguner
+https://t.co/tFtCpJWMU9</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>1776171680000</v>
+        <v>1776176976000</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2044038292707143832</t>
+          <t>2044060507603382318</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4732,7 +4736,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>{'name': 'DUBAI CITY GUIDE from Cyber Gear', 'screenName': 'dcgguide', 'followersCount': 93486, 'favouritesCount': 19465, 'friendsCount': 106588, 'description': 'DCG is a https://t.co/bmR4jltJAW e-venture. We publish guest posts at https://t.co/EISzXb0O0y Learn AI at https://t.co/YcnxpXcCNU'}</t>
+          <t>{'name': 'Biz Today Intl', 'screenName': 'biztoday_intl', 'followersCount': 469, 'favouritesCount': 969, 'friendsCount': 107, 'description': "Biz Today is the World's preeminent 24-hour English language business, economics, technology and finance to travel, fashion and lifestyle publication"}</t>
         </is>
       </c>
       <c r="K63" t="n">
@@ -4745,11 +4749,11 @@
         <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P63" t="inlineStr"/>
@@ -4760,37 +4764,35 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>https://x.com/biztoday_intl/status/2044047297034760542</t>
+          <t>https://x.com/dcgguide/status/2044025847523487886</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2044047297034760542</t>
+          <t>2044025847523487886</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2044047297034760542</t>
+          <t>2044025847523487886</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>https://x.com/biztoday_intl/status/2044047297034760542</t>
+          <t>https://x.com/dcgguide/status/2044025847523487886</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE and @SobhaRealtyDXB partner to offer integrated home financing solutions for off-plan projects in #Dubai .
-#EmiratesNBD #SobhaRealty #UAE #Dubairealestate #realestate
-https://t.co/ukweMYki3P</t>
+          <t>Emirates NBD And Sobha Realty Partner To Offer Integrated Home Financing Solutions For Off-Plan Projects In Dubai https://t.co/fVBST6NQ7A</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>1776173826000</v>
+        <v>1776168712000</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2044047297034760542</t>
+          <t>2044025847523487886</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4800,7 +4802,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>{'name': 'Biz Today Intl', 'screenName': 'biztoday_intl', 'followersCount': 469, 'favouritesCount': 969, 'friendsCount': 107, 'description': "Biz Today is the World's preeminent 24-hour English language business, economics, technology and finance to travel, fashion and lifestyle publication"}</t>
+          <t>{'name': 'DUBAI CITY GUIDE from Cyber Gear', 'screenName': 'dcgguide', 'followersCount': 93486, 'favouritesCount': 19465, 'friendsCount': 106588, 'description': 'DCG is a https://t.co/bmR4jltJAW e-venture. We publish guest posts at https://t.co/EISzXb0O0y Learn AI at https://t.co/YcnxpXcCNU'}</t>
         </is>
       </c>
       <c r="K64" t="n">
@@ -4810,14 +4812,14 @@
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>45</t>
         </is>
       </c>
       <c r="P64" t="inlineStr"/>
@@ -4828,37 +4830,35 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>https://x.com/biztoday_intl/status/2044047297034760542</t>
+          <t>https://x.com/dcgguide/status/2044025847523487886</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2044047297034760542</t>
+          <t>2044025847523487886</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2043584275161977015</t>
+          <t>2044038581161996359</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>https://x.com/biztoday_intl/status/2043584275161977015</t>
+          <t>https://x.com/dcgguide/status/2044038581161996359</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>#DWTCFreeZone Partners with @WioBank to Provide Digital Banking Solutions for Businesses.
-#DWTC #WioBank #Dubai #UAE #DXB @DWTCOfficial
-https://t.co/GIjGf2VZ0q</t>
+          <t>EWEC Opens Q2 2026 Clean Energy Certificates Auction To Empower Organisations To Lead Global Energy Transition https://t.co/wXSWsOlKcV</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>1776063433000</v>
+        <v>1776171748000</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2043584275161977015</t>
+          <t>2044038581161996359</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>{'name': 'Biz Today Intl', 'screenName': 'biztoday_intl', 'followersCount': 469, 'favouritesCount': 969, 'friendsCount': 107, 'description': "Biz Today is the World's preeminent 24-hour English language business, economics, technology and finance to travel, fashion and lifestyle publication"}</t>
+          <t>{'name': 'DUBAI CITY GUIDE from Cyber Gear', 'screenName': 'dcgguide', 'followersCount': 93486, 'favouritesCount': 19465, 'friendsCount': 106588, 'description': 'DCG is a https://t.co/bmR4jltJAW e-venture. We publish guest posts at https://t.co/EISzXb0O0y Learn AI at https://t.co/YcnxpXcCNU'}</t>
         </is>
       </c>
       <c r="K65" t="n">
@@ -4881,11 +4881,11 @@
         <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>48</t>
         </is>
       </c>
       <c r="P65" t="inlineStr"/>
@@ -4896,58 +4896,47 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>https://x.com/Net_eqtisad/status/2044043515546800261</t>
+          <t>https://x.com/OneVilleNews/status/2044022292972482932</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2044043515546800261</t>
+          <t>2044022292972482932</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2044043515546800261</t>
+          <t>2044022292972482932</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>https://x.com/Net_eqtisad/status/2044043515546800261</t>
+          <t>https://x.com/OneVilleNews/status/2044022292972482932</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>القيمة السوقية لأكبر 10 شركات عامة في الإمارات تبلغ 692.3 مليار دولار في 2026، تتصدرها "الشركة العالمية القابضة" مستحوذة وحدها على نحو 34% من إجمالي القيمة السوقية.
-@ihc__official
-@TAQAGroup
-@ADNOCGas
-@FABConnects
-@EmiratesNBD_AE
-@eAndUAE
-@DEWAOfficial
-@emaardubai
-@OfficialADCB
-@adhuae
-@ADX_AE
-@DFMalerts
-#الإمارات #أدنوك #الطاقة #IHC  #الشبكة_الاقتصادية</t>
+          <t>Emirates NBD and Sobha Realty partner to offer integrated home financing solutions for off-plan projects in Dubai 
+#EmiratesNBD #SobhaRealty #Dubai #UAE #Business #Partnership @SobhaRealtyDXB #OneVilleNews
+https://t.co/rQ8bwNlb8E via @onevillenews https://t.co/uuh2N7Ktl1</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>1776172925000</v>
+        <v>1776167865000</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2044043515546800261</t>
+          <t>2044022292972482932</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF3mvnXaMAAc5dn.jpg', 'type': 'photo', 'id': '2044043511591481344'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF3Tb09bMAAglq0.jpg', 'type': 'photo', 'id': '2044022280922279936'}]</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>{'name': 'الشبكة الاقتصادية', 'screenName': 'Net_eqtisad', 'followersCount': 347, 'favouritesCount': 645, 'friendsCount': 24, 'description': 'أرقام..احصائيات..اقتصاد واكثر!'}</t>
+          <t>{'name': 'One Ville News', 'screenName': 'OneVilleNews', 'followersCount': 45, 'favouritesCount': 8, 'friendsCount': 39, 'description': 'All of One Ville, all in one place.'}</t>
         </is>
       </c>
       <c r="K66" t="n">
@@ -4964,7 +4953,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>37</t>
         </is>
       </c>
       <c r="P66" t="inlineStr"/>
@@ -4975,47 +4964,47 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>https://x.com/Net_eqtisad/status/2044043515546800261</t>
+          <t>https://x.com/OneVilleNews/status/2044022292972482932</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2044043515546800261</t>
+          <t>2044022292972482932</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2044029975376855339</t>
+          <t>2043769833955917928</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>https://x.com/Net_eqtisad/status/2044029975376855339</t>
+          <t>https://x.com/OneVilleNews/status/2043769833955917928</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>التقى سمو الشيخ خالد بن محمد بن زايد آل نهيان قادة شركات صينية، في إطار تعزيز الشراكة الاستراتيجية بين البلدين.
-📌 ركزت اللقاءات على استكشاف فرص جديدة للتعاون الاقتصادي والتنموي، بما يدعم توسيع الاستثمارات وتعزيز العلاقات الثنائية.
-#الإمارات #الصين #الاستثمار #الاقتصاد #الشبكة_الاقتصادية</t>
+          <t>“Ya Biladi”… A Song That Feels Like Home, Bringing the UAE’s Spirit to Life 
+#YaBiladi #UAE #Dubai #Song #HussainAlJassmi @7sainaljassmi #محمد_بن_زايد #الامارات_العربية_المتحدة 
+https://t.co/TqZCzfMs1b via @onevillenews https://t.co/lrW3u4M1bq</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>1776169697000</v>
+        <v>1776107674000</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2044029975376855339</t>
+          <t>2043769833955917928</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF3abgLagAAnLi2.jpg', 'type': 'photo', 'id': '2044029971925204992'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HFztt94bcAAnViP.jpg', 'type': 'photo', 'id': '2043769704880500736'}]</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>{'name': 'الشبكة الاقتصادية', 'screenName': 'Net_eqtisad', 'followersCount': 347, 'favouritesCount': 645, 'friendsCount': 24, 'description': 'أرقام..احصائيات..اقتصاد واكثر!'}</t>
+          <t>{'name': 'One Ville News', 'screenName': 'OneVilleNews', 'followersCount': 45, 'favouritesCount': 8, 'friendsCount': 39, 'description': 'All of One Ville, all in one place.'}</t>
         </is>
       </c>
       <c r="K67" t="n">
@@ -5025,14 +5014,14 @@
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>2706</t>
         </is>
       </c>
       <c r="P67" t="inlineStr"/>
@@ -5098,7 +5087,7 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>148</t>
         </is>
       </c>
       <c r="P68" t="inlineStr"/>
@@ -5147,7 +5136,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>{'name': 'Nabil Smarter', 'screenName': 'nabilal_rawi', 'followersCount': 30, 'favouritesCount': 16972, 'friendsCount': 335, 'description': 'المستقبل ليس مكاناً نكسبه، بل مكاناً يجب أن نحميه.'}</t>
+          <t>{'name': 'Nabil Smarter', 'screenName': 'nabilal_rawi', 'followersCount': 30, 'favouritesCount': 16975, 'friendsCount': 335, 'description': 'المستقبل ليس مكاناً نكسبه، بل مكاناً يجب أن نحميه.'}</t>
         </is>
       </c>
       <c r="K69" t="n">
@@ -5164,7 +5153,7 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -5235,7 +5224,7 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P70" t="inlineStr"/>
@@ -5303,7 +5292,7 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>158</t>
         </is>
       </c>
       <c r="P71" t="inlineStr"/>
@@ -5358,7 +5347,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>{'name': 'Rotana Live', 'screenName': 'RotanaLive', 'followersCount': 193532, 'favouritesCount': 7072, 'friendsCount': 149, 'description': 'روتانا لايف الحساب الرسمي لحفلات روتانا | Rotana events https://t.co/wTAoLH4wPm'}</t>
+          <t>{'name': 'Rotana Live', 'screenName': 'RotanaLive', 'followersCount': 193533, 'favouritesCount': 7072, 'friendsCount': 149, 'description': 'روتانا لايف الحساب الرسمي لحفلات روتانا | Rotana events https://t.co/wTAoLH4wPm'}</t>
         </is>
       </c>
       <c r="K72" t="n">
@@ -5375,7 +5364,7 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>8830</t>
+          <t>8833</t>
         </is>
       </c>
       <c r="P72" t="inlineStr"/>
@@ -5424,7 +5413,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>{'name': 'فراس علي', 'screenName': 'FirasAlin3va', 'followersCount': 27, 'favouritesCount': 188, 'friendsCount': 8, 'description': 'أنا لاعب كرة قدم ملتزم وأحب التحدي والتركيز على تطوير مهاراتي دائماً.'}</t>
+          <t>{'name': 'فراس علي', 'screenName': 'FirasAlin3va', 'followersCount': 27, 'favouritesCount': 189, 'friendsCount': 8, 'description': 'أنا لاعب كرة قدم ملتزم وأحب التحدي والتركيز على تطوير مهاراتي دائماً.'}</t>
         </is>
       </c>
       <c r="K73" t="n">
@@ -5441,7 +5430,7 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -5511,7 +5500,7 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>101</t>
         </is>
       </c>
       <c r="P74" t="inlineStr"/>
@@ -5577,7 +5566,7 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>83</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -5923,7 +5912,7 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -5993,7 +5982,7 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -6065,7 +6054,7 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>52</t>
         </is>
       </c>
       <c r="P82" t="inlineStr"/>
@@ -6133,7 +6122,7 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>91</t>
         </is>
       </c>
       <c r="P83" t="inlineStr"/>
@@ -6199,7 +6188,7 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>102</t>
         </is>
       </c>
       <c r="P84" t="inlineStr"/>
@@ -6265,7 +6254,7 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>83</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -6359,777 +6348,15 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2043932263725854816</t>
+          <t>2043932263386157239</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2043932263725854816</t>
+          <t>https://x.com/emiratesislamic/status/2043932263386157239</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
-        <is>
-          <t>Money grows best when given time, balance, and the right mix.
-Spreading investments and thinking long term can help create steadier progress along the way.
-Small steps today can support stronger outcomes tomorrow.</t>
-        </is>
-      </c>
-      <c r="G87" t="n">
-        <v>1776146400000</v>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>2043932263725854816</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="K87" t="n">
-        <v>1</v>
-      </c>
-      <c r="L87" t="n">
-        <v>0</v>
-      </c>
-      <c r="M87" t="n">
-        <v>0</v>
-      </c>
-      <c r="N87" t="n">
-        <v>0</v>
-      </c>
-      <c r="O87" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="P87" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="1" t="n">
-        <v>86</v>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2043955058459467807</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>2043955058459467807</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>2042145058133307907</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>https://x.com/aswanikumartst5/status/2042145058133307907</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>@emiratesislamic I have already cleared a personal loan and approached your Phone Banking &amp;amp; WhatsApp channel for issue of NIL LIABILITY LETTER..but no concrete response .Not feasible to obtain through your application as well.Can u please check&amp;amp; revert ASAP. Thank You.</t>
-        </is>
-      </c>
-      <c r="G88" t="n">
-        <v>1775720297000</v>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>2042145058133307907</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>{'name': 'TS Aswani Kumar', 'screenName': 'aswanikumartst5', 'followersCount': 10, 'favouritesCount': 181, 'friendsCount': 25, 'description': ''}</t>
-        </is>
-      </c>
-      <c r="K88" t="n">
-        <v>1</v>
-      </c>
-      <c r="L88" t="n">
-        <v>0</v>
-      </c>
-      <c r="M88" t="n">
-        <v>0</v>
-      </c>
-      <c r="N88" t="n">
-        <v>0</v>
-      </c>
-      <c r="O88" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="P88" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="1" t="n">
-        <v>87</v>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2043955058459467807</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>2043955058459467807</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>2042152553400385940</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2042152553400385940</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>@aswanikumartst5 Dear customer, we will connect with you on private messaging to serve you better</t>
-        </is>
-      </c>
-      <c r="G89" t="n">
-        <v>1775722084000</v>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>2042145058133307907</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="K89" t="n">
-        <v>1</v>
-      </c>
-      <c r="L89" t="n">
-        <v>0</v>
-      </c>
-      <c r="M89" t="n">
-        <v>0</v>
-      </c>
-      <c r="N89" t="n">
-        <v>0</v>
-      </c>
-      <c r="O89" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="P89" t="inlineStr">
-        <is>
-          <t>2042145058133307907</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="1" t="n">
-        <v>88</v>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2043955058459467807</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>2043955058459467807</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>2042853514049917277</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>https://x.com/aswanikumartst5/status/2042853514049917277</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>@emiratesislamic So far nobody has contacted me in connection with this query nor any mail from your end .</t>
-        </is>
-      </c>
-      <c r="G90" t="n">
-        <v>1775889206000</v>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>2042145058133307907</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>{'name': 'TS Aswani Kumar', 'screenName': 'aswanikumartst5', 'followersCount': 10, 'favouritesCount': 181, 'friendsCount': 25, 'description': ''}</t>
-        </is>
-      </c>
-      <c r="K90" t="n">
-        <v>1</v>
-      </c>
-      <c r="L90" t="n">
-        <v>0</v>
-      </c>
-      <c r="M90" t="n">
-        <v>0</v>
-      </c>
-      <c r="N90" t="n">
-        <v>0</v>
-      </c>
-      <c r="O90" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="P90" t="inlineStr">
-        <is>
-          <t>2042152553400385940</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="1" t="n">
-        <v>89</v>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2043955058459467807</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>2043955058459467807</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>2043560931511189651</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2043560931511189651</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>@aswanikumartst5 Dear customer, we will connect with you on private messaging to serve you better.</t>
-        </is>
-      </c>
-      <c r="G91" t="n">
-        <v>1776057868000</v>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>2042145058133307907</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="K91" t="n">
-        <v>1</v>
-      </c>
-      <c r="L91" t="n">
-        <v>0</v>
-      </c>
-      <c r="M91" t="n">
-        <v>0</v>
-      </c>
-      <c r="N91" t="n">
-        <v>0</v>
-      </c>
-      <c r="O91" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="P91" t="inlineStr">
-        <is>
-          <t>2042853514049917277</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="1" t="n">
-        <v>90</v>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2043955058459467807</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>2043955058459467807</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>2043951228640747823</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>https://x.com/aswanikumartst5/status/2043951228640747823</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>@emiratesislamic How many days more you require to issue a NIL LIABILITY LETTER...?</t>
-        </is>
-      </c>
-      <c r="G92" t="n">
-        <v>1776150922000</v>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>2042145058133307907</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>{'name': 'TS Aswani Kumar', 'screenName': 'aswanikumartst5', 'followersCount': 10, 'favouritesCount': 181, 'friendsCount': 25, 'description': ''}</t>
-        </is>
-      </c>
-      <c r="K92" t="n">
-        <v>1</v>
-      </c>
-      <c r="L92" t="n">
-        <v>0</v>
-      </c>
-      <c r="M92" t="n">
-        <v>0</v>
-      </c>
-      <c r="N92" t="n">
-        <v>0</v>
-      </c>
-      <c r="O92" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="P92" t="inlineStr">
-        <is>
-          <t>2043560931511189651</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="1" t="n">
-        <v>91</v>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2043955058459467807</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>2043955058459467807</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>2043955058459467807</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2043955058459467807</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>@aswanikumartst5 Dear customer, we will connect with you on private messaging to serve you better.</t>
-        </is>
-      </c>
-      <c r="G93" t="n">
-        <v>1776151835000</v>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>2042145058133307907</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="K93" t="n">
-        <v>0</v>
-      </c>
-      <c r="L93" t="n">
-        <v>0</v>
-      </c>
-      <c r="M93" t="n">
-        <v>0</v>
-      </c>
-      <c r="N93" t="n">
-        <v>0</v>
-      </c>
-      <c r="O93" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="P93" t="inlineStr">
-        <is>
-          <t>2043951228640747823</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="1" t="n">
-        <v>92</v>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2043932266456367150</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>2043932266456367150</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>2043932263725854816</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2043932263725854816</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>Money grows best when given time, balance, and the right mix.
-Spreading investments and thinking long term can help create steadier progress along the way.
-Small steps today can support stronger outcomes tomorrow.</t>
-        </is>
-      </c>
-      <c r="G94" t="n">
-        <v>1776146400000</v>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>2043932263725854816</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="K94" t="n">
-        <v>1</v>
-      </c>
-      <c r="L94" t="n">
-        <v>0</v>
-      </c>
-      <c r="M94" t="n">
-        <v>0</v>
-      </c>
-      <c r="N94" t="n">
-        <v>0</v>
-      </c>
-      <c r="O94" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="P94" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="1" t="n">
-        <v>93</v>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2043932266456367150</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>2043932266456367150</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>2043932266456367150</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2043932266456367150</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>To know more:
-https://t.co/XvyZgR87nM</t>
-        </is>
-      </c>
-      <c r="G95" t="n">
-        <v>1776146401000</v>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>2043932263725854816</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="K95" t="n">
-        <v>0</v>
-      </c>
-      <c r="L95" t="n">
-        <v>0</v>
-      </c>
-      <c r="M95" t="n">
-        <v>0</v>
-      </c>
-      <c r="N95" t="n">
-        <v>0</v>
-      </c>
-      <c r="O95" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="P95" t="inlineStr">
-        <is>
-          <t>2043932263725854816</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="1" t="n">
-        <v>94</v>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2043932263725854816</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>2043932263725854816</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>2043932263725854816</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2043932263725854816</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>Money grows best when given time, balance, and the right mix.
-Spreading investments and thinking long term can help create steadier progress along the way.
-Small steps today can support stronger outcomes tomorrow.</t>
-        </is>
-      </c>
-      <c r="G96" t="n">
-        <v>1776146400000</v>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>2043932263725854816</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="K96" t="n">
-        <v>1</v>
-      </c>
-      <c r="L96" t="n">
-        <v>0</v>
-      </c>
-      <c r="M96" t="n">
-        <v>0</v>
-      </c>
-      <c r="N96" t="n">
-        <v>0</v>
-      </c>
-      <c r="O96" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="P96" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="1" t="n">
-        <v>95</v>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2043932263725854816</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>2043932263725854816</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>2043932266456367150</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2043932266456367150</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>To know more:
-https://t.co/XvyZgR87nM</t>
-        </is>
-      </c>
-      <c r="G97" t="n">
-        <v>1776146401000</v>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>2043932263725854816</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="K97" t="n">
-        <v>0</v>
-      </c>
-      <c r="L97" t="n">
-        <v>0</v>
-      </c>
-      <c r="M97" t="n">
-        <v>0</v>
-      </c>
-      <c r="N97" t="n">
-        <v>0</v>
-      </c>
-      <c r="O97" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="P97" t="inlineStr">
-        <is>
-          <t>2043932263725854816</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="1" t="n">
-        <v>96</v>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2043932263725854816</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>2043932263725854816</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>2043932263386157239</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2043932263386157239</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
         <is>
           <t>ينمو المال بشكل أفضل مع الوقت، والتوازن، والتنوّع المناسب.
 تنويع الاستثمارات والتفكير على المدى الطويل يساعدان على تحقيق استقرار أكبر.
@@ -7138,68 +6365,623 @@
 https://t.co/mgtIcQsyLZ https://t.co/Eh7yupmtiG</t>
         </is>
       </c>
-      <c r="G98" t="n">
+      <c r="G87" t="n">
         <v>1776146400000</v>
       </c>
-      <c r="H98" t="inlineStr">
+      <c r="H87" t="inlineStr">
         <is>
           <t>2043932263386157239</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr">
+      <c r="I87" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/ext_tw_video_thumb/2043692933543550976/pu/img/DwmJr4WPQRT9Ka0q.jpg', 'type': 'video', 'id': '2043692933543550976'}]</t>
         </is>
       </c>
-      <c r="J98" t="inlineStr">
+      <c r="J87" t="inlineStr">
         <is>
           <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
-      <c r="K98" t="n">
-        <v>0</v>
-      </c>
-      <c r="L98" t="n">
-        <v>0</v>
-      </c>
-      <c r="M98" t="n">
-        <v>0</v>
-      </c>
-      <c r="N98" t="n">
-        <v>0</v>
-      </c>
-      <c r="O98" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="P98" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="1" t="n">
-        <v>97</v>
-      </c>
-      <c r="B99" t="inlineStr">
+      <c r="K87" t="n">
+        <v>0</v>
+      </c>
+      <c r="L87" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" t="n">
+        <v>0</v>
+      </c>
+      <c r="N87" t="n">
+        <v>0</v>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="n">
+        <v>86</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2043955058459467807</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>2043955058459467807</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>2042145058133307907</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>https://x.com/aswanikumartst5/status/2042145058133307907</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>@emiratesislamic I have already cleared a personal loan and approached your Phone Banking &amp;amp; WhatsApp channel for issue of NIL LIABILITY LETTER..but no concrete response .Not feasible to obtain through your application as well.Can u please check&amp;amp; revert ASAP. Thank You.</t>
+        </is>
+      </c>
+      <c r="G88" t="n">
+        <v>1775720297000</v>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>2042145058133307907</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>{'name': 'TS Aswani Kumar', 'screenName': 'aswanikumartst5', 'followersCount': 10, 'favouritesCount': 181, 'friendsCount': 25, 'description': ''}</t>
+        </is>
+      </c>
+      <c r="K88" t="n">
+        <v>1</v>
+      </c>
+      <c r="L88" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" t="n">
+        <v>0</v>
+      </c>
+      <c r="N88" t="n">
+        <v>0</v>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="n">
+        <v>87</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2043955058459467807</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>2043955058459467807</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>2042152553400385940</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2042152553400385940</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>@aswanikumartst5 Dear customer, we will connect with you on private messaging to serve you better</t>
+        </is>
+      </c>
+      <c r="G89" t="n">
+        <v>1775722084000</v>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>2042145058133307907</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="K89" t="n">
+        <v>1</v>
+      </c>
+      <c r="L89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>2042145058133307907</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="n">
+        <v>88</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2043955058459467807</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>2043955058459467807</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>2042853514049917277</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>https://x.com/aswanikumartst5/status/2042853514049917277</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>@emiratesislamic So far nobody has contacted me in connection with this query nor any mail from your end .</t>
+        </is>
+      </c>
+      <c r="G90" t="n">
+        <v>1775889206000</v>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>2042145058133307907</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>{'name': 'TS Aswani Kumar', 'screenName': 'aswanikumartst5', 'followersCount': 10, 'favouritesCount': 181, 'friendsCount': 25, 'description': ''}</t>
+        </is>
+      </c>
+      <c r="K90" t="n">
+        <v>1</v>
+      </c>
+      <c r="L90" t="n">
+        <v>0</v>
+      </c>
+      <c r="M90" t="n">
+        <v>0</v>
+      </c>
+      <c r="N90" t="n">
+        <v>0</v>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>2042152553400385940</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="n">
+        <v>89</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2043955058459467807</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>2043955058459467807</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>2043560931511189651</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2043560931511189651</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>@aswanikumartst5 Dear customer, we will connect with you on private messaging to serve you better.</t>
+        </is>
+      </c>
+      <c r="G91" t="n">
+        <v>1776057868000</v>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>2042145058133307907</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="K91" t="n">
+        <v>1</v>
+      </c>
+      <c r="L91" t="n">
+        <v>0</v>
+      </c>
+      <c r="M91" t="n">
+        <v>0</v>
+      </c>
+      <c r="N91" t="n">
+        <v>0</v>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>2042853514049917277</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="n">
+        <v>90</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2043955058459467807</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>2043955058459467807</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>2043951228640747823</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>https://x.com/aswanikumartst5/status/2043951228640747823</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>@emiratesislamic How many days more you require to issue a NIL LIABILITY LETTER...?</t>
+        </is>
+      </c>
+      <c r="G92" t="n">
+        <v>1776150922000</v>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>2042145058133307907</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>{'name': 'TS Aswani Kumar', 'screenName': 'aswanikumartst5', 'followersCount': 10, 'favouritesCount': 181, 'friendsCount': 25, 'description': ''}</t>
+        </is>
+      </c>
+      <c r="K92" t="n">
+        <v>1</v>
+      </c>
+      <c r="L92" t="n">
+        <v>0</v>
+      </c>
+      <c r="M92" t="n">
+        <v>0</v>
+      </c>
+      <c r="N92" t="n">
+        <v>0</v>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>2043560931511189651</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="n">
+        <v>91</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2043955058459467807</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>2043955058459467807</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>2043955058459467807</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2043955058459467807</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>@aswanikumartst5 Dear customer, we will connect with you on private messaging to serve you better.</t>
+        </is>
+      </c>
+      <c r="G93" t="n">
+        <v>1776151835000</v>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>2042145058133307907</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="K93" t="n">
+        <v>0</v>
+      </c>
+      <c r="L93" t="n">
+        <v>0</v>
+      </c>
+      <c r="M93" t="n">
+        <v>0</v>
+      </c>
+      <c r="N93" t="n">
+        <v>0</v>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>2043951228640747823</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="n">
+        <v>92</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2043932266456367150</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>2043932266456367150</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>2043932263725854816</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2043932263725854816</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Money grows best when given time, balance, and the right mix.
+Spreading investments and thinking long term can help create steadier progress along the way.
+Small steps today can support stronger outcomes tomorrow.</t>
+        </is>
+      </c>
+      <c r="G94" t="n">
+        <v>1776146400000</v>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>2043932263725854816</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="K94" t="n">
+        <v>1</v>
+      </c>
+      <c r="L94" t="n">
+        <v>0</v>
+      </c>
+      <c r="M94" t="n">
+        <v>0</v>
+      </c>
+      <c r="N94" t="n">
+        <v>0</v>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="n">
+        <v>93</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2043932266456367150</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>2043932266456367150</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>2043932266456367150</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2043932266456367150</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>To know more:
+https://t.co/XvyZgR87nM</t>
+        </is>
+      </c>
+      <c r="G95" t="n">
+        <v>1776146401000</v>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>2043932263725854816</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="K95" t="n">
+        <v>0</v>
+      </c>
+      <c r="L95" t="n">
+        <v>0</v>
+      </c>
+      <c r="M95" t="n">
+        <v>0</v>
+      </c>
+      <c r="N95" t="n">
+        <v>0</v>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>2043932263725854816</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="n">
+        <v>94</v>
+      </c>
+      <c r="B96" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2043932263386157239</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
+      <c r="C96" t="inlineStr">
         <is>
           <t>2043932263386157239</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr">
+      <c r="D96" t="inlineStr">
         <is>
           <t>2043932263386157239</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr">
+      <c r="E96" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2043932263386157239</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr">
+      <c r="F96" t="inlineStr">
         <is>
           <t>ينمو المال بشكل أفضل مع الوقت، والتوازن، والتنوّع المناسب.
 تنويع الاستثمارات والتفكير على المدى الطويل يساعدان على تحقيق استقرار أكبر.
@@ -7208,17 +6990,221 @@
 https://t.co/mgtIcQsyLZ https://t.co/Eh7yupmtiG</t>
         </is>
       </c>
+      <c r="G96" t="n">
+        <v>1776146400000</v>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>2043932263386157239</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/ext_tw_video_thumb/2043692933543550976/pu/img/DwmJr4WPQRT9Ka0q.jpg', 'type': 'video', 'id': '2043692933543550976'}]</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="K96" t="n">
+        <v>0</v>
+      </c>
+      <c r="L96" t="n">
+        <v>0</v>
+      </c>
+      <c r="M96" t="n">
+        <v>0</v>
+      </c>
+      <c r="N96" t="n">
+        <v>0</v>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2043932263386157239</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>2043932263386157239</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>2043932263449006494</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2043932263449006494</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>كيف تدفع نفقاتك عادةً؟
+#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
+https://t.co/mgtIcQsyLZ</t>
+        </is>
+      </c>
+      <c r="G97" t="n">
+        <v>1776146400000</v>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>2043932263449006494</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="K97" t="n">
+        <v>0</v>
+      </c>
+      <c r="L97" t="n">
+        <v>0</v>
+      </c>
+      <c r="M97" t="n">
+        <v>0</v>
+      </c>
+      <c r="N97" t="n">
+        <v>0</v>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="n">
+        <v>96</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2043932263449006494</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>2043932263449006494</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>2043932263449006494</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2043932263449006494</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>كيف تدفع نفقاتك عادةً؟
+#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
+https://t.co/mgtIcQsyLZ</t>
+        </is>
+      </c>
+      <c r="G98" t="n">
+        <v>1776146400000</v>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>2043932263449006494</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="K98" t="n">
+        <v>0</v>
+      </c>
+      <c r="L98" t="n">
+        <v>0</v>
+      </c>
+      <c r="M98" t="n">
+        <v>0</v>
+      </c>
+      <c r="N98" t="n">
+        <v>0</v>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="n">
+        <v>97</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2043932263449006494</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>2043932263449006494</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>2043932263725854816</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2043932263725854816</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Money grows best when given time, balance, and the right mix.
+Spreading investments and thinking long term can help create steadier progress along the way.
+Small steps today can support stronger outcomes tomorrow.</t>
+        </is>
+      </c>
       <c r="G99" t="n">
         <v>1776146400000</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2043932263386157239</t>
+          <t>2043932263725854816</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/ext_tw_video_thumb/2043692933543550976/pu/img/DwmJr4WPQRT9Ka0q.jpg', 'type': 'video', 'id': '2043692933543550976'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -7227,7 +7213,7 @@
         </is>
       </c>
       <c r="K99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L99" t="n">
         <v>0</v>
@@ -7240,7 +7226,7 @@
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>92</t>
         </is>
       </c>
       <c r="P99" t="inlineStr"/>
@@ -7251,12 +7237,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2043932263386157239</t>
+          <t>https://x.com/emiratesislamic/status/2043932263725854816</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2043932263386157239</t>
+          <t>2043932263725854816</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -7308,7 +7294,7 @@
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>92</t>
         </is>
       </c>
       <c r="P100" t="inlineStr"/>
@@ -7319,37 +7305,36 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2043932263449006494</t>
+          <t>https://x.com/emiratesislamic/status/2043932263725854816</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2043932263449006494</t>
+          <t>2043932263725854816</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2043932263449006494</t>
+          <t>2043932266456367150</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2043932263449006494</t>
+          <t>https://x.com/emiratesislamic/status/2043932266456367150</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>كيف تدفع نفقاتك عادةً؟
-#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
-https://t.co/mgtIcQsyLZ</t>
+          <t>To know more:
+https://t.co/XvyZgR87nM</t>
         </is>
       </c>
       <c r="G101" t="n">
-        <v>1776146400000</v>
+        <v>1776146401000</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2043932263449006494</t>
+          <t>2043932263725854816</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -7376,10 +7361,14 @@
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="P101" t="inlineStr"/>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>2043932263725854816</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
@@ -7387,29 +7376,31 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2043932263449006494</t>
+          <t>https://x.com/emiratesislamic/status/2043932263725854816</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2043932263449006494</t>
+          <t>2043932263725854816</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2043932263725854816</t>
+          <t>2043932263386157239</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2043932263725854816</t>
+          <t>https://x.com/emiratesislamic/status/2043932263386157239</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Money grows best when given time, balance, and the right mix.
-Spreading investments and thinking long term can help create steadier progress along the way.
-Small steps today can support stronger outcomes tomorrow.</t>
+          <t>ينمو المال بشكل أفضل مع الوقت، والتوازن، والتنوّع المناسب.
+تنويع الاستثمارات والتفكير على المدى الطويل يساعدان على تحقيق استقرار أكبر.
+خطوات صغيرة اليوم قد تصنع نتائج أقوى في المستقبل.
+للمزيد: 
+https://t.co/mgtIcQsyLZ https://t.co/Eh7yupmtiG</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -7417,12 +7408,12 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2043932263725854816</t>
+          <t>2043932263386157239</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/ext_tw_video_thumb/2043692933543550976/pu/img/DwmJr4WPQRT9Ka0q.jpg', 'type': 'video', 'id': '2043692933543550976'}]</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -7431,7 +7422,7 @@
         </is>
       </c>
       <c r="K102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L102" t="n">
         <v>0</v>
@@ -7444,7 +7435,7 @@
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>55</t>
         </is>
       </c>
       <c r="P102" t="inlineStr"/>

--- a/Xpost_df_comments.xlsx
+++ b/Xpost_df_comments.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P102"/>
+  <dimension ref="A1:P76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,36 +511,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://x.com/metrixyo/status/2044132083443155222</t>
+          <t>https://x.com/DustshotW/status/2044612515498496366</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2044132083443155222</t>
+          <t>2044612515498496366</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2044132083443155222</t>
+          <t>2044517451078197394</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://x.com/metrixyo/status/2044132083443155222</t>
+          <t>https://x.com/DustshotW/status/2044517451078197394</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Pattern Day Trader (PDT) rule is soon going. No 25K USD limit for day trading : SEC
-#WIO #NASDAQ #ROBINHOOD #ENBD #NYSE #IG #IBKR</t>
+          <t>anyone.....olease ......</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1776194041000</v>
+        <v>1776285920000</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2044132083443155222</t>
+          <t>2044517451078197394</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -550,11 +549,11 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>{'name': 'Metrix', 'screenName': 'metrixyo', 'followersCount': 91, 'favouritesCount': 385, 'friendsCount': 266, 'description': 'Background in Data &amp; AI  | Earning Money with AI &amp; Science |\nData Driven Analysis on Crypto, Stocks, Metals &amp; Real Estate Assets'}</t>
+          <t>{'name': 'justice gaming', 'screenName': 'DustshotW', 'followersCount': 1065, 'favouritesCount': 25613, 'friendsCount': 229, 'description': 'call me justice or 正凱 // 中文/English // 🇭🇰// i do like nothing but draw yuri\n\nhttps://t.co/wisNUqvSX2'}</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -563,11 +562,11 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>309</t>
         </is>
       </c>
       <c r="P2" t="inlineStr"/>
@@ -578,38 +577,35 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://x.com/metrixyo/status/2044132083443155222</t>
+          <t>https://x.com/DustshotW/status/2044612515498496366</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2044132083443155222</t>
+          <t>2044612515498496366</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2044068136115417120</t>
+          <t>2044610910640361699</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://x.com/metrixyo/status/2044068136115417120</t>
+          <t>https://x.com/dorienotfish/status/2044610910640361699</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>$QBTS 16% ⬆️ 
-$BE 21% ⬆️
-💵💵💵💵💵💵💵💵💵💵💵💵
-#qbts #quantum #dwave #Bloom #NASdaq #Nyse</t>
+          <t>@DustshotW can i try</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1776178795000</v>
+        <v>1776308202000</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2044068136115417120</t>
+          <t>2044517451078197394</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -619,11 +615,11 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>{'name': 'Metrix', 'screenName': 'metrixyo', 'followersCount': 91, 'favouritesCount': 385, 'friendsCount': 266, 'description': 'Background in Data &amp; AI  | Earning Money with AI &amp; Science |\nData Driven Analysis on Crypto, Stocks, Metals &amp; Real Estate Assets'}</t>
+          <t>{'name': 'dorion', 'screenName': 'dorienotfish', 'followersCount': 68, 'favouritesCount': 39809, 'friendsCount': 522, 'description': 'steine sind steine ohne rotes blut'}</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -636,10 +632,14 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr"/>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2044517451078197394</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -647,71 +647,69 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://x.com/AlAjlansambrfi/status/2044090446926823921</t>
+          <t>https://x.com/DustshotW/status/2044612515498496366</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2044090446926823921</t>
+          <t>2044612515498496366</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2042680872118174012</t>
+          <t>2044612515498496366</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://x.com/RotanaLive/status/2042680872118174012</t>
+          <t>https://x.com/DustshotW/status/2044612515498496366</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>جمهور جدة غير ومع الصقر غير🦅
-#رابح_صقر_في_جدة
-#موسم_جدة
-#روتانا_لايف
-@RabehSaqer 
-@JEDCalendar 
-@EmiratesNBD_KSA https://t.co/3mI6SdN1pE</t>
+          <t>@dorienotfish s enbd</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1775848045000</v>
+        <v>1776308585000</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2042680872118174012</t>
+          <t>2044517451078197394</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2042680331732684801/img/ZnKpK7bzPoCB7Knz.jpg', 'type': 'video', 'id': '2042680331732684801'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>{'name': 'Rotana Live', 'screenName': 'RotanaLive', 'followersCount': 193533, 'favouritesCount': 7072, 'friendsCount': 149, 'description': 'روتانا لايف الحساب الرسمي لحفلات روتانا | Rotana events https://t.co/wTAoLH4wPm'}</t>
+          <t>{'name': 'justice gaming', 'screenName': 'DustshotW', 'followersCount': 1065, 'favouritesCount': 25613, 'friendsCount': 229, 'description': 'call me justice or 正凱 // 中文/English // 🇭🇰// i do like nothing but draw yuri\n\nhttps://t.co/wisNUqvSX2'}</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>6605</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr"/>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2044610910640361699</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -719,49 +717,49 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://x.com/AlAjlansambrfi/status/2044090446926823921</t>
+          <t>https://x.com/DustshotW/status/2044612515498496366</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2044090446926823921</t>
+          <t>2044612515498496366</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2044090446926823921</t>
+          <t>2044613234427383893</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://x.com/AlAjlansambrfi/status/2044090446926823921</t>
+          <t>https://x.com/dorienotfish/status/2044613234427383893</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>@RotanaLive @RabehSaqer @JEDCalendar @EmiratesNBD_KSA رائع، الجوهرة تتألق في جدة! 🦅</t>
+          <t>@DustshotW sorry at first i though u said 'skibdi' mb✌🏻✌🏻✌🏻 ok here https://t.co/DsboMnkCKn</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1776184114000</v>
+        <v>1776308756000</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2042680872118174012</t>
+          <t>2044517451078197394</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF_s4_pbAAANiPL.jpg', 'type': 'photo', 'id': '2044613219751493632'}]</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>{'name': 'طموح العجلان', 'screenName': 'AlAjlansambrfi', 'followersCount': 9, 'favouritesCount': 222, 'friendsCount': 164, 'description': 'طموح في عالم الأعمال بالمدينة، أحب التقنية والمشاريع الكبرى.'}</t>
+          <t>{'name': 'dorion', 'screenName': 'dorienotfish', 'followersCount': 68, 'favouritesCount': 39809, 'friendsCount': 522, 'description': 'steine sind steine ohne rotes blut'}</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -774,12 +772,12 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>19</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2042680872118174012</t>
+          <t>2044612515498496366</t>
         </is>
       </c>
     </row>
@@ -789,25 +787,44 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044134219362779352</t>
+          <t>https://x.com/BehindNums/status/2044611289733878057</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2044134219362779352</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>2044611289733878057</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2044611289733878057</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://x.com/undefined/status/undefined</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
+          <t>https://x.com/BehindNums/status/2044611289733878057</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Top 5 Richest Companies in the Middle East 
+1️⃣ Saudi Aramco — ~$1.5T+
+2️⃣ International Holding Co (UAE) — ~$240B+
+3️⃣ QNB (Qatar National Bank) — ~$150B+
+4️⃣ Al Rajhi Bank (Saudi) — ~$100B+
+5️⃣ Emirates NBD (UAE) — ~$80B+
+Oil wealth meets financial power.
+@BehindNums</t>
+        </is>
+      </c>
       <c r="G6" t="n">
-        <v>1776225794636</v>
-      </c>
-      <c r="H6" t="inlineStr"/>
+        <v>1776308293000</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2044611289733878057</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr">
         <is>
           <t>[]</t>
@@ -815,14 +832,26 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
+          <t>{'name': 'BehindNums | Business &amp; Data', 'screenName': 'BehindNums', 'followersCount': 1, 'favouritesCount': 0, 'friendsCount': 1, 'description': 'Business. Wealth. Power. We decode the numbers behind it. Data-driven insights daily'}</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
@@ -831,69 +860,72 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044134219362779352</t>
+          <t>https://x.com/BehindNums/status/2044611289733878057</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2044134219362779352</t>
+          <t>2044611289733878057</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2044119073538113567</t>
+          <t>2044611048305574280</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044119073538113567</t>
+          <t>https://x.com/BehindNums/status/2044611048305574280</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ÖKKEŞ ŞAHİN'S INTERNATIONAL RECIPE: POWER SOUP. YOU WILL BOIL ONE CARROT, ONE GREEN PEPPER, AND ONE RED ONION. YOU WILL EAT IT LIKE THIS FOR A WHILE. LATER, YOU CAN ADD MEAT, FISH, AND CHICKEN TO IT. @LeaderOkkes @RoyalFamily @MonarchieBe @koninklijkhuis @KensingtonRoyal @X https://t.co/UBoi80xAg0</t>
+          <t>Top 5 Companies by Revenue 
+By Revenue (annual)
+1️⃣ Walmart — ~$650B
+2️⃣ Amazon — ~$575B
+3️⃣ Saudi Aramco — ~$500B
+4️⃣ China State Grid — ~$480B
+5️⃣ Apple — ~$390B
+@BehindNums</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1776190939000</v>
+        <v>1776308235000</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2021899533345841203</t>
+          <t>2044611048305574280</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF4rcsJX0AE0m43.jpg', 'type': 'photo', 'id': '2044119052759584769'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HF4rcsJWkAARX1r.jpg', 'type': 'photo', 'id': '2044119052759502848'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>{'name': 'THE REAL KING OF THE WORLD: ÖKKEŞ ŞAHİN', 'screenName': 'LeaderOkkes', 'followersCount': 1, 'favouritesCount': 1722, 'friendsCount': 37, 'description': ''}</t>
+          <t>{'name': 'BehindNums | Business &amp; Data', 'screenName': 'BehindNums', 'followersCount': 1, 'favouritesCount': 0, 'friendsCount': 1, 'description': 'Business. Wealth. Power. We decode the numbers behind it. Data-driven insights daily'}</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>1350</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2021899533345841203</t>
-        </is>
-      </c>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -901,69 +933,66 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044134219362779352</t>
+          <t>https://x.com/zaydaklabhoqx/status/2044582261102956879</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2044134219362779352</t>
+          <t>2044582261102956879</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2044120061124698315</t>
+          <t>2029869216254341430</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044120061124698315</t>
+          <t>https://x.com/CryptoNewsHntrs/status/2029869216254341430</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>@RoyalFamily @MonarchieBe @koninklijkhuis @KensingtonRoyal @X MY INTERNATIONAL RECIPE: POWER SOUP. @LeaderOkkes @DefensieMin @FratellidItalia @GiorgiaMeloni @Pontifex @MarkJCarney @EmmanuelMacron @PrimeministerGR @netanyahu @LulaOficial @JMilei @Jaemyung_Lee @chrisluxonmp @ParmelinG @scotgov @SwissGov @lemondefr @TheEconomist @iaeaorg @wef https://t.co/wJsGrMVAFs</t>
+          <t>🚨 JUST IN: 🇦🇪 EMIRATES NBD ELIMINATES ATM WITHDRAWAL &amp;amp; DEBIT CARD FEES ACROSS THE UAE &amp;amp; GCC UNTIL MARCH 31, 2026! 💳🔥
+#UAE #EmiratesNBD #Banking #Finance #ATM #NoFees #GCC #MoneySmart https://t.co/aI9H5crVgx</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1776191175000</v>
+        <v>1772793508000</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2021899533345841203</t>
+          <t>2029869216254341430</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF4sWL8XkAAwsHK.jpg', 'type': 'photo', 'id': '2044120040547520512'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HF4sWMZW8AAJzDO.jpg', 'type': 'photo', 'id': '2044120040669114368'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HCuLS2CXkAATb_t.jpg', 'type': 'photo', 'id': '2029869212919894016'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HCuLS2eXwAA68mZ.jpg', 'type': 'photo', 'id': '2029869213037346816'}]</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>{'name': 'THE REAL KING OF THE WORLD: ÖKKEŞ ŞAHİN', 'screenName': 'LeaderOkkes', 'followersCount': 1, 'favouritesCount': 1722, 'friendsCount': 37, 'description': ''}</t>
+          <t>{'name': 'Crypto News Hunters 🎯', 'screenName': 'CryptoNewsHntrs', 'followersCount': 28363, 'favouritesCount': 314597, 'friendsCount': 138, 'description': 'Crypto News 🌐 Financial Markets 📈 Memes &amp; Hopium 🔥 Not Financial Advice 🚫'}</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2044119073538113567</t>
-        </is>
-      </c>
+          <t>738</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -971,49 +1000,49 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044134219362779352</t>
+          <t>https://x.com/zaydaklabhoqx/status/2044582261102956879</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2044134219362779352</t>
+          <t>2044582261102956879</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2044121269105275233</t>
+          <t>2044582261102956879</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044121269105275233</t>
+          <t>https://x.com/zaydaklabhoqx/status/2044582261102956879</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>@RoyalFamily @MonarchieBe @koninklijkhuis @KensingtonRoyal @X @DefensieMin @FratellidItalia @GiorgiaMeloni @Pontifex @MarkJCarney @EmmanuelMacron @PrimeministerGR @netanyahu @LulaOficial @JMilei @Jaemyung_Lee @chrisluxonmp @ParmelinG @scotgov @SwissGov @lemondefr @TheEconomist @iaeaorg @wef MY INTERNATIONAL RECIPE: POWER SOUP. @LeaderOkkes @wef @wto @IMFNews @WorldBankGroup @Davos @nikkei @NYSE @Nasdaq @Poloniex @WazirXIndia @tadawul @Cryptopia_NZ @binance @dogecoin @bankofengland @bankofcanada @BankofIndia_IN @Banxico @Bancolombia @BancoCentralBR @BankofAmerica https://t.co/FmIt0fuKbt</t>
+          <t>@CryptoNewsHntrs ماذا عن مجانيّة سحب النقود؟ مبروك لعملاء Emirates NBD في الإمارات ودول الخليج</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1776191463000</v>
+        <v>1776301372000</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2021899533345841203</t>
+          <t>2029869216254341430</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF4tcaOW8AI_KR0.jpg', 'type': 'photo', 'id': '2044121246971916290'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HF4tcbqasAQGqbQ.jpg', 'type': 'photo', 'id': '2044121247358038020'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>{'name': 'THE REAL KING OF THE WORLD: ÖKKEŞ ŞAHİN', 'screenName': 'LeaderOkkes', 'followersCount': 1, 'favouritesCount': 1722, 'friendsCount': 37, 'description': ''}</t>
+          <t>{'name': 'زيد أكلب', 'screenName': 'zaydaklabhoqx', 'followersCount': 30, 'favouritesCount': 301, 'friendsCount': 48, 'description': 'مدير آي تي في دبي، أحب التقنية والسيارات والكرة. أعزب ومستمتع بالحياة الفاخرة.'}</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -1026,12 +1055,12 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2044120061124698315</t>
+          <t>2029869216254341430</t>
         </is>
       </c>
     </row>
@@ -1041,69 +1070,68 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044134219362779352</t>
+          <t>https://x.com/STFU1346/status/2044433219693466085</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2044134219362779352</t>
+          <t>2044433219693466085</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2044122040836206849</t>
+          <t>2043970652697211186</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044122040836206849</t>
+          <t>https://x.com/Brockutd/status/2043970652697211186</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>@RoyalFamily @MonarchieBe @koninklijkhuis @KensingtonRoyal @X @DefensieMin @FratellidItalia @GiorgiaMeloni @Pontifex @MarkJCarney @EmmanuelMacron @PrimeministerGR @netanyahu @LulaOficial @JMilei @Jaemyung_Lee @chrisluxonmp @ParmelinG @scotgov @SwissGov @lemondefr @TheEconomist @iaeaorg @wef @wto @IMFNews @WorldBankGroup @Davos @nikkei @NYSE @Nasdaq MY INTERNATIONAL RECIPE: POWER SOUP. @LeaderOkkes @MonarchieBe @RoyalFamily @koninklijkhuis @KingSalman @takaichi_sanae @kantei @Kantei_Saigai @DefensieMin @OPRArgentina @presidencia_BR @CancilleriaPeru @Cancilleria_Ar @cancilleriasv @wef @wto @IMFNews @EU_Commission @iaeaorg https://t.co/NfbvQKMl3H</t>
+          <t>🚨 Mark Clattenburg on Lisandro Martínez’s red card:
+“I was surprised that such an experienced referee considered this a red card offence. It was clearly a 50/50 challenge for the ball. 
+I think the referee’s seniority within the VAR group may have made others hesitant to overturn his on-field decision.
+In my opinion, this was a clear mistake. When we talk about ‘clear and obvious errors’, most referees would not have sent him off for that challenge.”</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1776191647000</v>
+        <v>1776155553000</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2021899533345841203</t>
+          <t>2043970652697211186</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF4uJcxX0AApkCR.jpg', 'type': 'photo', 'id': '2044122020749758464'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HF4uJczXkAACxrB.jpg', 'type': 'photo', 'id': '2044122020758130688'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF2kdMfXYAA7k8w.jpg', 'type': 'photo', 'id': '2043970627372015616'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HF2kdM8asAEzRR_.jpg', 'type': 'photo', 'id': '2043970627493867521'}]</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>{'name': 'THE REAL KING OF THE WORLD: ÖKKEŞ ŞAHİN', 'screenName': 'LeaderOkkes', 'followersCount': 1, 'favouritesCount': 1722, 'friendsCount': 37, 'description': ''}</t>
+          <t>{'name': 'BROCK(fan)', 'screenName': 'Brockutd', 'followersCount': 6684, 'favouritesCount': 145265, 'friendsCount': 791, 'description': 'Face of Pogba Fc •|• @manutd •|• Fan account •|• @Roobet'}</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>150</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1037</v>
       </c>
       <c r="N10" t="n">
-        <v>1</v>
+        <v>9501</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>2044121269105275233</t>
-        </is>
-      </c>
+          <t>428722</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -1111,67 +1139,69 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044134219362779352</t>
+          <t>https://x.com/STFU1346/status/2044433219693466085</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2044134219362779352</t>
+          <t>2044433219693466085</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2044123427083083921</t>
+          <t>2043989823325716661</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044123427083083921</t>
+          <t>https://x.com/STFU1346/status/2043989823325716661</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>@RoyalFamily @MonarchieBe @koninklijkhuis @KensingtonRoyal @X @DefensieMin @FratellidItalia @GiorgiaMeloni @Pontifex @MarkJCarney @EmmanuelMacron @PrimeministerGR @netanyahu @LulaOficial @JMilei @Jaemyung_Lee @chrisluxonmp @ParmelinG @scotgov @SwissGov @lemondefr @TheEconomist @iaeaorg @wef @wto @IMFNews @WorldBankGroup @Davos @nikkei @NYSE @Nasdaq @KingSalman @takaichi_sanae @kantei @Kantei_Saigai MY INTERNATIONAL RECIPE: POWER SOUP. MA RECETTE INTERNATIONALE : SOUPE ÉNERGISANTE. @LeaderOkkes @EmmanuelMacron @Elysee @francediplo @francediplo_EN @lemondefr @FranceoSenegal @FratellidItalia @GiorgiaMeloni @ItalyMFA @Gazzetta_it @Pontifex @VaticanNews @netanyahu @IsraelMFA https://t.co/AOXivIo2V8</t>
+          <t>@Brockutd Man U had it easy for years, now maybe karma is at play.
+I think it was soft, but the rules are the rules.
+Man U were shite last night, and should've been down by 3 or more before they woke up.</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1776191977000</v>
+        <v>1776160124000</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2021899533345841203</t>
+          <t>2043970652697211186</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF4vaMGXEAEjj03.jpg', 'type': 'photo', 'id': '2044123407843790849'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HF4vaMQasAEPCjo.jpg', 'type': 'photo', 'id': '2044123407885971457'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>{'name': 'THE REAL KING OF THE WORLD: ÖKKEŞ ŞAHİN', 'screenName': 'LeaderOkkes', 'followersCount': 1, 'favouritesCount': 1722, 'friendsCount': 37, 'description': ''}</t>
+          <t>{'name': 'BraveFart🏴\U000e0067\U000e0062\U000e0073\U000e0063\U000e0074\U000e007f', 'screenName': 'STFU1346', 'followersCount': 1646, 'favouritesCount': 16513, 'friendsCount': 1654, 'description': 'Scottish. NUFC mad. If you steal any of my memes, show a bit of common courtesy and like it first.'}</t>
         </is>
       </c>
       <c r="K11" t="n">
+        <v>7</v>
+      </c>
+      <c r="L11" t="n">
         <v>1</v>
       </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
       <c r="M11" t="n">
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>4746</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2044122040836206849</t>
+          <t>2043970652697211186</t>
         </is>
       </c>
     </row>
@@ -1181,45 +1211,45 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044134219362779352</t>
+          <t>https://x.com/STFU1346/status/2044433219693466085</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2044134219362779352</t>
+          <t>2044433219693466085</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2044124392943137264</t>
+          <t>2044040984212758846</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044124392943137264</t>
+          <t>https://x.com/JeetyJeeterson/status/2044040984212758846</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>@RoyalFamily @MonarchieBe @koninklijkhuis @KensingtonRoyal @X @DefensieMin @FratellidItalia @GiorgiaMeloni @Pontifex @MarkJCarney @EmmanuelMacron @PrimeministerGR @netanyahu @LulaOficial @JMilei @Jaemyung_Lee @chrisluxonmp @ParmelinG @scotgov @SwissGov @lemondefr @TheEconomist @iaeaorg @wef @wto @IMFNews @WorldBankGroup @Davos @nikkei @NYSE @Nasdaq @KingSalman @takaichi_sanae @kantei MY INTERNATIONAL RECIPE: POWER SOUP. המתכון הבינלאומי שלי: מרק עוצמתי. @LeaderOkkes @netanyahu @YairNetanyahu @IDF @IsraeliPM @IAFsite @IsraelMFA @Isaac_Herzog @TimesofIsrael @Jerusalem_Post @usembassyjlm @IsraelinUSA @IsraelinSpanish @IsraelinUK @IsraelinGermany @TelAvivUni https://t.co/1J3VzW57FV</t>
+          <t>@STFU1346 @Brockutd This narrative that United got all the decisions in the past is a complete lie. United are on the wrong end of poor decisions more than anybody, this lie was started by rival fans with zero evidence. We used to get alot of pens, as were attacking twice as much as everybody else</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1776192207000</v>
+        <v>1776172321000</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2021899533345841203</t>
+          <t>2043970652697211186</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF4wSRlWoAAL2qo.jpg', 'type': 'photo', 'id': '2044124371388637184'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HF4wSRlXEAAQXCy.jpg', 'type': 'photo', 'id': '2044124371388665856'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>{'name': 'THE REAL KING OF THE WORLD: ÖKKEŞ ŞAHİN', 'screenName': 'LeaderOkkes', 'followersCount': 1, 'favouritesCount': 1722, 'friendsCount': 37, 'description': ''}</t>
+          <t>{'name': 'Jeety', 'screenName': 'JeetyJeeterson', 'followersCount': 416, 'favouritesCount': 667, 'friendsCount': 1554, 'description': "Whatever people say I am, that's what I'm not"}</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1232,16 +1262,16 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>58</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2044123427083083921</t>
+          <t>2043989823325716661</t>
         </is>
       </c>
     </row>
@@ -1251,45 +1281,47 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044134219362779352</t>
+          <t>https://x.com/STFU1346/status/2044433219693466085</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2044134219362779352</t>
+          <t>2044433219693466085</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2044125532476821949</t>
+          <t>2044048198029742561</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044125532476821949</t>
+          <t>https://x.com/STFU1346/status/2044048198029742561</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>@RoyalFamily @MonarchieBe @koninklijkhuis @KensingtonRoyal @X @DefensieMin @FratellidItalia @GiorgiaMeloni @Pontifex @MarkJCarney @EmmanuelMacron @PrimeministerGR @netanyahu @LulaOficial @JMilei @Jaemyung_Lee @chrisluxonmp @ParmelinG @scotgov @SwissGov @lemondefr @TheEconomist @iaeaorg @wef @wto @IMFNews @WorldBankGroup @Davos @nikkei @NYSE 我的國際食譜能量湯. MY INTERNATIONAL RECIPE: POWER SOUP. @LeaderOkkes @BentleyMotors @Toyota @TOYOTA_PR @MitsubishiKaden @MHI_Group @RollsRoyce @LandRover @RangeRover @astonmartin @F1 @MercedesBenz @MercedesAMGF1 @BMW @Peugeot @Ford @FordMustang @VolvoCarUSA @renaultgroup @Tesla https://t.co/0QaF62lMwZ</t>
+          <t>@JeetyJeeterson @Brockutd No, none, nada, zilch,  penalties against Man U under Ferguson at Old Trafford during their purple.. Give your head a shake man.
+Look at Sky Sports and the coverage you's get. Be as well call it Man U TV.
+The "Red Cartel" is no conspiracy theory, Man U are the head of the gang.</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>1776192479000</v>
+        <v>1776174041000</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2021899533345841203</t>
+          <t>2043970652697211186</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF4xUs2aMAA5imS.jpg', 'type': 'photo', 'id': '2044125512579297280'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HF4xUsPWAAA7hU8.jpg', 'type': 'photo', 'id': '2044125512415444992'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>{'name': 'THE REAL KING OF THE WORLD: ÖKKEŞ ŞAHİN', 'screenName': 'LeaderOkkes', 'followersCount': 1, 'favouritesCount': 1722, 'friendsCount': 37, 'description': ''}</t>
+          <t>{'name': 'BraveFart🏴\U000e0067\U000e0062\U000e0073\U000e0063\U000e0074\U000e007f', 'screenName': 'STFU1346', 'followersCount': 1646, 'favouritesCount': 16513, 'friendsCount': 1654, 'description': 'Scottish. NUFC mad. If you steal any of my memes, show a bit of common courtesy and like it first.'}</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1299,19 +1331,19 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>69</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2044124392943137264</t>
+          <t>2044040984212758846</t>
         </is>
       </c>
     </row>
@@ -1321,45 +1353,45 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044134219362779352</t>
+          <t>https://x.com/STFU1346/status/2044433219693466085</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2044134219362779352</t>
+          <t>2044433219693466085</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2044126467026497799</t>
+          <t>2044431315555024909</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044126467026497799</t>
+          <t>https://x.com/Cle_Etc/status/2044431315555024909</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>@RoyalFamily @MonarchieBe @koninklijkhuis @KensingtonRoyal @X @DefensieMin @FratellidItalia @GiorgiaMeloni @Pontifex @MarkJCarney @EmmanuelMacron @PrimeministerGR @netanyahu @LulaOficial @JMilei @Jaemyung_Lee @chrisluxonmp @ParmelinG @scotgov @SwissGov @lemondefr @TheEconomist @iaeaorg @wef @wto @IMFNews @WorldBankGroup @Davos @nikkei @NYSE @BentleyMotors @Toyota @TOYOTA_PR @MitsubishiKaden 私の国際レシピ：パワースープ. MY INTERNATIONAL RECIPE: POWER SOUP. LOOK AT. @LeaderOkkes @SwissMFA @DanishMFA @BelgiumMFA @FCDOGovUK @MofaJapan_jp @KSAMOFA @CanadaFP @IsraelMFA @MFA_China  @ItalyMFA_int @francediplo_EN @DutchMFA @GreeceMFA @ArgentinaMFA @ItamaratyGovBr https://t.co/0q2rnxRjDF</t>
+          <t>@STFU1346 @JeetyJeeterson @Brockutd Hmmm, from an Oil Money Club.</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1776192702000</v>
+        <v>1776265383000</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2021899533345841203</t>
+          <t>2043970652697211186</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF4yLLEWEAEAEqo.jpg', 'type': 'photo', 'id': '2044126448403746817'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HF4yLLRXYAABkRi.jpg', 'type': 'photo', 'id': '2044126448458358784'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>{'name': 'THE REAL KING OF THE WORLD: ÖKKEŞ ŞAHİN', 'screenName': 'LeaderOkkes', 'followersCount': 1, 'favouritesCount': 1722, 'friendsCount': 37, 'description': ''}</t>
+          <t>{'name': 'Cle Etc.', 'screenName': 'Cle_Etc', 'followersCount': 186, 'favouritesCount': 21460, 'friendsCount': 42, 'description': 'Married. Dad. Irish. Musician. Songwriter. Producer. Teacher. Believer. Cynic. Man United supporter. Dyslexic. Dreamer. Likes a laugh.'}</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1372,16 +1404,16 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2044125532476821949</t>
+          <t>2044048198029742561</t>
         </is>
       </c>
     </row>
@@ -1391,45 +1423,48 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044134219362779352</t>
+          <t>https://x.com/STFU1346/status/2044433219693466085</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2044134219362779352</t>
+          <t>2044433219693466085</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2044127070410674226</t>
+          <t>2044432755811860595</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044127070410674226</t>
+          <t>https://x.com/STFU1346/status/2044432755811860595</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>@RoyalFamily @MonarchieBe @koninklijkhuis @KensingtonRoyal @X @DefensieMin @FratellidItalia @GiorgiaMeloni @Pontifex @MarkJCarney @EmmanuelMacron @PrimeministerGR @netanyahu @LulaOficial @JMilei @Jaemyung_Lee @chrisluxonmp @ParmelinG @scotgov @SwissGov @lemondefr @TheEconomist @iaeaorg @wef @wto @IMFNews @WorldBankGroup @Davos @nikkei @NYSE @BentleyMotors @Toyota @TOYOTA_PR MY INTERNATIONAL RECIPE: POWER SOUP. @LeaderOkkes @infopresidencia @Presidencia_Ec @presidenciaperu @PresidenciaSV @presidencia_BR @SecPrensaSV @PresidenciaCuba @PresidenciaPy @presidenciacr @PresidenciaCPNL @MonarchieBe @koninklijkhuis @RoyalFamily @IsraeliPM @SwissGov @GOVUK https://t.co/vaMTYIPN32</t>
+          <t>@Cle_Etc @JeetyJeeterson @Brockutd Here are your sponsors:
+Commercial Bank of Qatar: A Financial Services Affinity Partner for Qatar.
+VIVA: An integrated telecommunications partner for Bahrain and Kuwait. 
+TM: An integrated telecommunications partner for Malaysia (often grouped with regional Asian/Middle Eastern</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1776192846000</v>
+        <v>1776265727000</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2021899533345841203</t>
+          <t>2043970652697211186</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF4yuKsXEAAC63S.jpg', 'type': 'photo', 'id': '2044127049598570496'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HF4yuKzWEAArvi3.jpg', 'type': 'photo', 'id': '2044127049627865088'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>{'name': 'THE REAL KING OF THE WORLD: ÖKKEŞ ŞAHİN', 'screenName': 'LeaderOkkes', 'followersCount': 1, 'favouritesCount': 1722, 'friendsCount': 37, 'description': ''}</t>
+          <t>{'name': 'BraveFart🏴\U000e0067\U000e0062\U000e0073\U000e0063\U000e0074\U000e007f', 'screenName': 'STFU1346', 'followersCount': 1646, 'favouritesCount': 16513, 'friendsCount': 1654, 'description': 'Scottish. NUFC mad. If you steal any of my memes, show a bit of common courtesy and like it first.'}</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1442,16 +1477,16 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>28</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2044126467026497799</t>
+          <t>2044431315555024909</t>
         </is>
       </c>
     </row>
@@ -1461,45 +1496,48 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044134219362779352</t>
+          <t>https://x.com/STFU1346/status/2044433219693466085</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2044134219362779352</t>
+          <t>2044433219693466085</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2044127797086446009</t>
+          <t>2044433219693466085</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044127797086446009</t>
+          <t>https://x.com/STFU1346/status/2044433219693466085</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>@RoyalFamily @MonarchieBe @koninklijkhuis @KensingtonRoyal @X @DefensieMin @FratellidItalia @GiorgiaMeloni @Pontifex @MarkJCarney @EmmanuelMacron @PrimeministerGR @netanyahu @LulaOficial @JMilei @Jaemyung_Lee @chrisluxonmp @ParmelinG @scotgov @SwissGov @lemondefr @TheEconomist @iaeaorg @wef @wto @IMFNews @WorldBankGroup @Davos @nikkei @NYSE @BentleyMotors MY INTERNATIONAL RECIPE: POWER SOUP.A MINHA RECEITA INTERNACIONAL:SOPA ENERGÉTICA. @LeaderOkkes @Walmart @Apple @AppleMusic @Microsoft @Google @SpaceX @X @Oracle @OracleDatabase @Huawei_Europe @Tesla  @Xiaomi @XiaomiIndonesia @McDonalds @BurgerKingUK @CocaCola @pepsi @RollsRoyce https://t.co/Pkuk6ynj28</t>
+          <t>@Cle_Etc @JeetyJeeterson @Brockutd PepsiCo: Noted for regional arrangements in the Middle East and Asia. 
+Emirates NBD for the United Arab Emirates.
+Saudi Telecom Co.
+So, what's your point?</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1776193019000</v>
+        <v>1776265837000</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2021899533345841203</t>
+          <t>2043970652697211186</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF4zYgqboAAYu-e.jpg', 'type': 'photo', 'id': '2044127777050566656'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HF4zYgcaUAAEnpW.jpg', 'type': 'photo', 'id': '2044127776991760384'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>{'name': 'THE REAL KING OF THE WORLD: ÖKKEŞ ŞAHİN', 'screenName': 'LeaderOkkes', 'followersCount': 1, 'favouritesCount': 1722, 'friendsCount': 37, 'description': ''}</t>
+          <t>{'name': 'BraveFart🏴\U000e0067\U000e0062\U000e0073\U000e0063\U000e0074\U000e007f', 'screenName': 'STFU1346', 'followersCount': 1646, 'favouritesCount': 16513, 'friendsCount': 1654, 'description': 'Scottish. NUFC mad. If you steal any of my memes, show a bit of common courtesy and like it first.'}</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1512,16 +1550,16 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>28</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2044127070410674226</t>
+          <t>2044432755811860595</t>
         </is>
       </c>
     </row>
@@ -1531,45 +1569,45 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044134219362779352</t>
+          <t>https://x.com/STFU1346/status/2044433219693466085</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2044134219362779352</t>
+          <t>2044433219693466085</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2044128711998411106</t>
+          <t>2044459400069357578</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044128711998411106</t>
+          <t>https://x.com/Cle_Etc/status/2044459400069357578</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>@RoyalFamily @MonarchieBe @koninklijkhuis @KensingtonRoyal @X @DefensieMin @FratellidItalia @GiorgiaMeloni @Pontifex @MarkJCarney @EmmanuelMacron @PrimeministerGR @netanyahu @LulaOficial @JMilei @Jaemyung_Lee @chrisluxonmp @ParmelinG @scotgov @SwissGov @lemondefr @TheEconomist @iaeaorg @wef @wto @IMFNews @WorldBankGroup @Davos @nikkei @NYSE @BentleyMotors @Walmart @Apple @AppleMusic @Microsoft MY INTERNATIONAL RECIPE: POWER SOUP. LA MIA RICETTA INTERNAZIONALE: ZUPPA ENERGETICA. @LeaderOkkes @GiorgiaMeloni @FratellidItalia @ItalyMFA @Jaemyung_Lee @SamsungKorea @VogueKorea @kantei @bankofengland @TheEconomist @lemondefr @folha @DefensieMin @DilanYesilgoz @koninklijkhuis https://t.co/yZXs4ltxR4</t>
+          <t>@STFU1346 @JeetyJeeterson @Brockutd Awe, you worked really hard for that. My point is that there are a handful of states sports washing, pumping billions into their purchased clubs… but we still have to listen to the fans complaining about imaginary cartels that control referees.</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1776193237000</v>
+        <v>1776272079000</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2021899533345841203</t>
+          <t>2043970652697211186</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF40N6HasAQaFiL.jpg', 'type': 'photo', 'id': '2044128694416093188'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HF40N50WwAA9QJR.jpg', 'type': 'photo', 'id': '2044128694336143360'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>{'name': 'THE REAL KING OF THE WORLD: ÖKKEŞ ŞAHİN', 'screenName': 'LeaderOkkes', 'followersCount': 1, 'favouritesCount': 1722, 'friendsCount': 37, 'description': ''}</t>
+          <t>{'name': 'Cle Etc.', 'screenName': 'Cle_Etc', 'followersCount': 186, 'favouritesCount': 21460, 'friendsCount': 42, 'description': 'Married. Dad. Irish. Musician. Songwriter. Producer. Teacher. Believer. Cynic. Man United supporter. Dyslexic. Dreamer. Likes a laugh.'}</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1582,16 +1620,16 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2044127797086446009</t>
+          <t>2044433219693466085</t>
         </is>
       </c>
     </row>
@@ -1601,49 +1639,50 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044134219362779352</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2044430548727128554</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2044134219362779352</t>
+          <t>2044430548727128554</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2044129315659345996</t>
+          <t>2044430548727128554</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044129315659345996</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2044430548727128554</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>@RoyalFamily @MonarchieBe @koninklijkhuis @KensingtonRoyal @X @DefensieMin @FratellidItalia @GiorgiaMeloni @Pontifex @MarkJCarney @EmmanuelMacron @PrimeministerGR @netanyahu @LulaOficial @JMilei @Jaemyung_Lee @chrisluxonmp @ParmelinG @scotgov @SwissGov @lemondefr @TheEconomist @iaeaorg @wef @wto @IMFNews @WorldBankGroup @Davos @nikkei @NYSE @BentleyMotors @Walmart MY INTERNATIONAL RECIPE: POWER SOUP. MEUM COQUENDI INTERNATIONALE: IUS ENERGETICUM. I’M KING - BARON OF THE WORLD. @LeaderOkkes @spagov @Reuters @NatGeo @Forbes @TIME @FT @TheEconomist @MarketWatch @MorganStanley @jpmorgan @NYSE @Nasdaq @BBCWorld @SkyNews @cnni @FoxNews @Nike https://t.co/645SVweoGN</t>
+          <t>Manage your wealth with expertise you can trust. Contact us today https://t.co/XmTzVbwpLQ
+#EmiratesNBD #WealthManagement https://t.co/1RVFBUcixf</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>1776193381000</v>
+        <v>1776265201000</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2021899533345841203</t>
+          <t>2044430548727128554</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF40w1xbYAAHhrr.jpg', 'type': 'photo', 'id': '2044129294545543168'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HF40w0_XwAA1srp.jpg', 'type': 'photo', 'id': '2044129294335590400'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF8-vnKWcAAQyPA.jpg', 'type': 'video', 'id': '2044421704122798080'}]</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>{'name': 'THE REAL KING OF THE WORLD: ÖKKEŞ ŞAHİN', 'screenName': 'LeaderOkkes', 'followersCount': 1, 'favouritesCount': 1722, 'friendsCount': 37, 'description': ''}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174062, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -1652,18 +1691,14 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>2044128711998411106</t>
-        </is>
-      </c>
+          <t>1286</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
@@ -1671,45 +1706,45 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044134219362779352</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2044430548727128554</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2044134219362779352</t>
+          <t>2044430548727128554</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2044130108303085904</t>
+          <t>2043932263717482626</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044130108303085904</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2043932263717482626</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>@RoyalFamily @MonarchieBe @koninklijkhuis @KensingtonRoyal @X @DefensieMin @FratellidItalia @GiorgiaMeloni @Pontifex @MarkJCarney @EmmanuelMacron @PrimeministerGR @netanyahu @LulaOficial @JMilei @Jaemyung_Lee @chrisluxonmp @ParmelinG @scotgov @SwissGov @lemondefr @TheEconomist @iaeaorg @wef @wto @IMFNews @WorldBankGroup @Davos @nikkei @NYSE @BentleyMotors @Walmart @spagov MY INTERNATIONAL RECIPE: POWER SOUP - IUS POTENTIA - SOUPE PUISSANTE - パワースープ. I’M BARON - KING OF THE WORLD. @LeaderOkkes @Walmart @Apple  @Microsoft @Google @SpaceX @X @Oracle @Huawei_Europe @Tesla @TeslaAUNZ @Xiaomi  @McDonaldsJapan @BurgerKingUK @CocaCola @pepsi @Meta https://t.co/rRQOciWTn0</t>
+          <t>We are together against Fraud. @UAEBF #FightFraud #UAEBF #togetheragainstfraud #UnitedAgainstFraud https://t.co/CqApZaCAFO</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>1776193570000</v>
+        <v>1776146400000</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2021899533345841203</t>
+          <t>2043932263717482626</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF41e7mXYAA1rfh.jpg', 'type': 'photo', 'id': '2044130086383738880'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HF41e8TasAId-9v.jpg', 'type': 'photo', 'id': '2044130086572699650'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2043610882656059392/img/HaP0BSdqwFktNLDX.jpg', 'type': 'video', 'id': '2043610882656059392'}]</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>{'name': 'THE REAL KING OF THE WORLD: ÖKKEŞ ŞAHİN', 'screenName': 'LeaderOkkes', 'followersCount': 1, 'favouritesCount': 1722, 'friendsCount': 37, 'description': ''}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174062, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -1719,21 +1754,17 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N19" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>2044129315659345996</t>
-        </is>
-      </c>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
@@ -1741,49 +1772,52 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044134219362779352</t>
+          <t>https://x.com/khir_llnas/status/2044377290952364098</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2044134219362779352</t>
+          <t>2044377290952364098</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2044130932110626901</t>
+          <t>2044377290952364098</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044130932110626901</t>
+          <t>https://x.com/khir_llnas/status/2044377290952364098</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>@RoyalFamily @MonarchieBe @koninklijkhuis @KensingtonRoyal @X @DefensieMin @FratellidItalia @GiorgiaMeloni @Pontifex @MarkJCarney @EmmanuelMacron @PrimeministerGR @netanyahu @LulaOficial @JMilei @Jaemyung_Lee @chrisluxonmp @ParmelinG @scotgov @SwissGov @lemondefr @TheEconomist @iaeaorg @wef @wto @IMFNews @WorldBankGroup @Davos @nikkei @NYSE @BentleyMotors ནུས་ཤུགས་ཐང་།. MY POWER SOUP. I’M KING OF THE WORLD. @LeaderOkkes @NASA @SpaceX @teslaeurope @Tesla_Asia @amazon @alibaba_cloud @msdev @ApplePodcasts @FCDOGovUK @ChinaMusicData @GovernmentRF @MichSoS @DefenceHQ @RoyalFamily @GiorgiaMeloni @EmmanuelMacron @francediplo @elonmusk https://t.co/hBU5y91OWL</t>
+          <t>شكرا Emirates NBD بنك الإمارات دبي الوطني
+على دعمكم الإنساني في نجاح أنشطة المؤسسة لدعم الأسر المحتاجة..
+#متبرعين_خير_للناس
+#مؤسسة_خير_للناس https://t.co/5PUxmmX1mn</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>1776193766000</v>
+        <v>1776252503000</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2021899533345841203</t>
+          <t>2044377290952364098</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF42PP_XcAEKunC.jpg', 'type': 'photo', 'id': '2044130916491030529'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HF42PP_XAAA-k6v.jpg', 'type': 'photo', 'id': '2044130916491001856'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF8VrwnXkAApAXH.jpg', 'type': 'photo', 'id': '2044376597378076672'}]</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>{'name': 'THE REAL KING OF THE WORLD: ÖKKEŞ ŞAHİN', 'screenName': 'LeaderOkkes', 'followersCount': 1, 'favouritesCount': 1722, 'friendsCount': 37, 'description': ''}</t>
+          <t>{'name': 'خير للناس للتنمية', 'screenName': 'khir_llnas', 'followersCount': 3, 'favouritesCount': 0, 'friendsCount': 3, 'description': ''}</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -1792,18 +1826,14 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>2044130108303085904</t>
-        </is>
-      </c>
+      <c r="P20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
@@ -1811,49 +1841,50 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044134219362779352</t>
+          <t>https://x.com/khir_llnas/status/2044377290952364098</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2044134219362779352</t>
+          <t>2044377290952364098</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2044132642241568996</t>
+          <t>2044440524782764312</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044132642241568996</t>
+          <t>https://x.com/khir_llnas/status/2044440524782764312</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>@RoyalFamily @MonarchieBe @koninklijkhuis @KensingtonRoyal @X @DefensieMin @FratellidItalia @GiorgiaMeloni @Pontifex @MarkJCarney @EmmanuelMacron @PrimeministerGR @netanyahu @LulaOficial @JMilei @Jaemyung_Lee @chrisluxonmp @ParmelinG @scotgov @SwissGov @lemondefr @TheEconomist @iaeaorg @wef @wto @IMFNews @WorldBankGroup @Davos @nikkei @NYSE @BentleyMotors MY POWER SOUP. पावर सूप. I’M KING OF THE WORLD. @LeaderOkkes @UniofOxford @OUPAcademic @Harvard @Stanford @Cambridge_Uni @Yale @WHU_1893 @universityofky @MIT @techreview @WashInstitute @ForeignPolicy @ForeignAffairs @CFR_org @ChathamHouse @BrookingsInst @McKinsey_MGI @TelAvivUni https://t.co/Gv1O15jASP</t>
+          <t>تبرع الآن
+https://t.co/sk7px2ePBH https://t.co/lsrrrAISd0</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>1776194174000</v>
+        <v>1776267579000</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2021899533345841203</t>
+          <t>2044440524782764312</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF43yDhasAE0J8P.jpg', 'type': 'photo', 'id': '2044132613951238145'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HF43yDZWAAA220e.jpg', 'type': 'photo', 'id': '2044132613917376512'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF9PwRYXUAAfgil.jpg', 'type': 'photo', 'id': '2044440446567403520'}]</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>{'name': 'THE REAL KING OF THE WORLD: ÖKKEŞ ŞAHİN', 'screenName': 'LeaderOkkes', 'followersCount': 1, 'favouritesCount': 1722, 'friendsCount': 37, 'description': ''}</t>
+          <t>{'name': 'خير للناس للتنمية', 'screenName': 'khir_llnas', 'followersCount': 3, 'favouritesCount': 0, 'friendsCount': 3, 'description': ''}</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -1862,18 +1893,14 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>2044130932110626901</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
@@ -1881,49 +1908,54 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044134219362779352</t>
+          <t>https://x.com/ibmag_magazine/status/2044410083262734349</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2044134219362779352</t>
+          <t>2044410083262734349</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2044133212385874152</t>
+          <t>2044410083262734349</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044133212385874152</t>
+          <t>https://x.com/ibmag_magazine/status/2044410083262734349</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>@RoyalFamily @MonarchieBe @koninklijkhuis @KensingtonRoyal @X @DefensieMin @FratellidItalia @GiorgiaMeloni @Pontifex @MarkJCarney @EmmanuelMacron @PrimeministerGR @netanyahu @LulaOficial @JMilei @Jaemyung_Lee @chrisluxonmp @ParmelinG @scotgov @SwissGov @lemondefr @TheEconomist @iaeaorg @wef @wto @IMFNews @WorldBankGroup @Davos @nikkei @NYSE @BentleyMotors @UniofOxford MY POWER SOUP. MIJN KRACHTSOEP. I’M KING OF THE WORLD. @LeaderOkkes @DefenceU @DefesaGovBr @DefenceHQ @Defensoria_Peru @DefensaSV @Defensagob @Defensie @DefensieMin @DefensieStas @DHQNigeria @kdfinfo @RwandaMoD  @DefensoriaCol @ArmedForcesJO @CanadianForces @IDF @Armees_Gouv https://t.co/j9UW8NkvCJ</t>
+          <t>To find the trending news on Real estate, finance, and Technology for April 15, check the news links and the video link below:
+https://t.co/AuS5pOClPI
+https://t.co/uOBF8Ce7As
+https://t.co/0Q3Pd23x0U
+https://t.co/QMIfzjAAnq
+#INTLBM  #Sohar #EToro #EmiratesNBD #Sobha #Headlines</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>1776194310000</v>
+        <v>1776260321000</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2021899533345841203</t>
+          <t>2044410083262734349</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF44TxYXQAALIb0.jpg', 'type': 'photo', 'id': '2044133193196978176'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HF44TxXWgAA_cP6.jpg', 'type': 'photo', 'id': '2044133193192734720'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>{'name': 'THE REAL KING OF THE WORLD: ÖKKEŞ ŞAHİN', 'screenName': 'LeaderOkkes', 'followersCount': 1, 'favouritesCount': 1722, 'friendsCount': 37, 'description': ''}</t>
+          <t>{'name': 'International Business Magazine', 'screenName': 'ibmag_magazine', 'followersCount': 1537, 'favouritesCount': 2080, 'friendsCount': 1003, 'description': 'International Business Magazine is a Dubai, UAE based publication.'}</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -1936,14 +1968,10 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>2044132642241568996</t>
-        </is>
-      </c>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
@@ -1951,49 +1979,54 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044134219362779352</t>
+          <t>https://x.com/ibmag_magazine/status/2044410083262734349</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2044134219362779352</t>
+          <t>2044410083262734349</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2044133751009997207</t>
+          <t>2043999660285862211</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044133751009997207</t>
+          <t>https://x.com/ibmag_magazine/status/2043999660285862211</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>@RoyalFamily @MonarchieBe @koninklijkhuis @KensingtonRoyal @X @DefensieMin @FratellidItalia @GiorgiaMeloni @Pontifex @MarkJCarney @EmmanuelMacron @PrimeministerGR @netanyahu @LulaOficial @JMilei @Jaemyung_Lee @chrisluxonmp @ParmelinG @scotgov @SwissGov @lemondefr @TheEconomist @iaeaorg @wef @wto @IMFNews @WorldBankGroup @Davos @nikkei @NYSE @BentleyMotors @UniofOxford @DefenceU MIN KRAFTSOPPA. MY POWER SOUP. @LeaderOkkes @BankofAmerica @bankofengland @bankofcanada @BankofIndia_IN @bankofthailand @BankOfTanzania @bankofmaldives @BcodeVenezuela @Banxico @BancoMundialLAC @Bancolombia @el_BID @BancoMundial @BancoCentralBR @BancoCentral_AR @BancoCentralRD https://t.co/tHfR0Eljxf</t>
+          <t>To find the trending news on Corporate, Technology, Banking and Finance for #April14, check the links below:
+https://t.co/wCnnEeLf7A
+https://t.co/5jczPIqAT3
+https://t.co/X0IupL4wiw
+https://t.co/amPUbrkpdI
+#Intlbm #telecoms #Investment #MiddleEast #Banking #Finance #Innovation</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>1776194439000</v>
+        <v>1776162469000</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2021899533345841203</t>
+          <t>2043999660285862211</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF44y-vasAANkaM.jpg', 'type': 'photo', 'id': '2044133729359278080'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HF44y-RWQAA5RfD.jpg', 'type': 'photo', 'id': '2044133729233158144'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>{'name': 'THE REAL KING OF THE WORLD: ÖKKEŞ ŞAHİN', 'screenName': 'LeaderOkkes', 'followersCount': 1, 'favouritesCount': 1722, 'friendsCount': 37, 'description': ''}</t>
+          <t>{'name': 'International Business Magazine', 'screenName': 'ibmag_magazine', 'followersCount': 1537, 'favouritesCount': 2080, 'friendsCount': 1003, 'description': 'International Business Magazine is a Dubai, UAE based publication.'}</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -2006,14 +2039,10 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>2044133212385874152</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
@@ -2021,69 +2050,67 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044134219362779352</t>
+          <t>https://x.com/Gulf_const/status/2044390258528395378</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2044134219362779352</t>
+          <t>2044390258528395378</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2044134219362779352</t>
+          <t>2044390258528395378</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044134219362779352</t>
+          <t>https://x.com/Gulf_const/status/2044390258528395378</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>@RoyalFamily @MonarchieBe @koninklijkhuis @KensingtonRoyal @X @DefensieMin @FratellidItalia @GiorgiaMeloni @Pontifex @MarkJCarney @EmmanuelMacron @PrimeministerGR @netanyahu @LulaOficial @JMilei @Jaemyung_Lee @chrisluxonmp @ParmelinG @scotgov @SwissGov @lemondefr @TheEconomist @iaeaorg @wef @wto @IMFNews @WorldBankGroup @Davos @nikkei @NYSE @BentleyMotors @UniofOxford A MINHA SOPA DE PODER. MY POWER SOUP. I’M KING OF THE WORLD. @LeaderOkkes @airasia_indo @IAF_MCC @CebuPacificAir @airasia @usairforce @airtelindia @British_Airways @KenyaAirways @etihad @flysaa @EmiratesNBD_AE @emirates @AmericanAir @AirCanada @airserbia @SaudiAirlinesEn @X https://t.co/8qnHpREKqV</t>
+          <t>Emirates NBD has announced a strategic partnership with Sobha Realty to provide integrated home financing solutions for buyers of the premium luxury developer’s off-plan residential developments across Dubai.
+Read more on https://t.co/966sAK8POe
+#GCnews #emirates #MENA https://t.co/B6wVnQqtgg</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>1776194550000</v>
+        <v>1776255595000</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2021899533345841203</t>
+          <t>2044390258528395378</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF45OSkbEAAvVjg.jpg', 'type': 'photo', 'id': '2044134198538342400'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HF45OTeXYAA1oKr.jpg', 'type': 'photo', 'id': '2044134198781370368'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF8h57OawAA3WNa.jpg', 'type': 'photo', 'id': '2044390034883919872'}]</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>{'name': 'THE REAL KING OF THE WORLD: ÖKKEŞ ŞAHİN', 'screenName': 'LeaderOkkes', 'followersCount': 1, 'favouritesCount': 1722, 'friendsCount': 37, 'description': ''}</t>
+          <t>{'name': 'Gulf Construction', 'screenName': 'Gulf_const', 'followersCount': 3304, 'favouritesCount': 338, 'friendsCount': 334, 'description': 'We are an authoritative, respected journal with unmatched coverage of the Gulf region’s building and construction industries.'}</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>2044133751009997207</t>
-        </is>
-      </c>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
@@ -2091,49 +2118,51 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044134219362779352</t>
+          <t>https://x.com/Gulf_const/status/2044390258528395378</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2044134219362779352</t>
+          <t>2044390258528395378</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2044134999616549139</t>
+          <t>2044017573616893963</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044134999616549139</t>
+          <t>https://x.com/Gulf_const/status/2044017573616893963</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>@RoyalFamily @MonarchieBe @koninklijkhuis @KensingtonRoyal @X @DefensieMin @FratellidItalia @GiorgiaMeloni @Pontifex @MarkJCarney @EmmanuelMacron @PrimeministerGR @netanyahu @LulaOficial @JMilei @Jaemyung_Lee @chrisluxonmp @ParmelinG @scotgov @SwissGov @lemondefr @TheEconomist @iaeaorg @wef @wto @IMFNews @WorldBankGroup @Davos @nikkei MY INTERNATIONAL RECIPE. MEUM RECEPTUM INTERNATIONALE. EGO SUM: ÖKKEŞ. @LeaderOkkes @nvidia @amazon @Apple @aramco @Broadcom @Tesla @Walmart @Walmart @Disney @Meta @NetflixKR @EliLillyandCo @jpmorgan @exxonmobil @Oracle @Roche @AstraZeneca @Shell @MorganStanley @lorealparisfr https://t.co/WRKhLq07T0</t>
+          <t>Mered, the award-winning developer based in UAE, has announced that main piling operations are now progressing at Riviera Residences, a waterfront residential tower in Abu Dhabi, Al Reem Island.
+Read more on https://t.co/xGW6cvJ1Nc
+#GCnews #developer #UAE #residences https://t.co/bFrmFMn6HS</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>1776194736000</v>
+        <v>1776166740000</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2021899533345841203</t>
+          <t>2044017573616893963</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF45710WwAAMkZ5.jpg', 'type': 'photo', 'id': '2044134981094522880'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HF4572xasAA1gCB.jpg', 'type': 'photo', 'id': '2044134981350633472'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HFxca_0aMAAamjh.jpg', 'type': 'photo', 'id': '2043609949796970496'}]</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>{'name': 'THE REAL KING OF THE WORLD: ÖKKEŞ ŞAHİN', 'screenName': 'LeaderOkkes', 'followersCount': 1, 'favouritesCount': 1722, 'friendsCount': 37, 'description': ''}</t>
+          <t>{'name': 'Gulf Construction', 'screenName': 'Gulf_const', 'followersCount': 3304, 'favouritesCount': 338, 'friendsCount': 334, 'description': 'We are an authoritative, respected journal with unmatched coverage of the Gulf region’s building and construction industries.'}</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -2146,14 +2175,10 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>2044134219362779352</t>
-        </is>
-      </c>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
@@ -2161,43 +2186,38 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>https://x.com/ChirinAsadi/status/2044082310447018168</t>
+          <t>https://x.com/iRonyForChange/status/2044369434362753181</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2044082310447018168</t>
+          <t>2044369434362753181</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2044064867896963237</t>
+          <t>2044369434362753181</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://x.com/ChirinAsadi/status/2044064867896963237</t>
+          <t>https://x.com/iRonyForChange/status/2044369434362753181</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>أعزائي ..
-السبب الوحيد للارتفاعات في الاسواق 
-هو دخول سيولة قوية ( بغض النظر عن الآلية) 
-تتزامن مع نتائج الشركات
-وهي الفترة التي لا يفوتها السوق أبداً
-لا في سراء ولا في ضراء 
-عُدْ إلي بعد أسبوعين،
-حتى نتحدث عن " زلزال المنطق "
-أضف الى ذلك .. أنا بِنْت ☹️</t>
+          <t>@EmiratesNBD_AE 
+You kept pushing to take the Share Credit Card,finally I applied and then you rejected citing “internal policies” despite having higher eligibility than required.
+Now your agents are calling and saying it’s a miss &amp;amp; to resubmit documents.
+Are you serious?</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>1776178016000</v>
+        <v>1776250630000</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2044064867896963237</t>
+          <t>2044369434362753181</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2207,24 +2227,24 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>{'name': 'Chirin Al Asadi', 'screenName': 'ChirinAsadi', 'followersCount': 3884, 'favouritesCount': 2850, 'friendsCount': 237, 'description': 'كل الكتابات والافكار هنا 👇🏻أصلية.. أغرد بأفكاري الخاصة بي .. أيضا: قرارك الاستثماري يخصك وحدك🤍 لا تأخذ بأرائي - اسأل مستشارك'}</t>
+          <t>{'name': 'Preetam Chakraborty', 'screenName': 'iRonyForChange', 'followersCount': 42, 'favouritesCount': 1281, 'friendsCount': 193, 'description': 'Work &amp; live in 🇦🇪 | Strong political opinions | Anti-establishment'}</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>2561</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P26" t="inlineStr"/>
@@ -2235,35 +2255,35 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>https://x.com/ChirinAsadi/status/2044082310447018168</t>
+          <t>https://x.com/iRonyForChange/status/2044369434362753181</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2044082310447018168</t>
+          <t>2044369434362753181</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2044071581186699505</t>
+          <t>2044371163166466284</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://x.com/alnuaimi_bader/status/2044071581186699505</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2044371163166466284</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>@ChirinAsadi ما شاء الله عليكم اخت شيرين. دائماً تثبتين بُعد النظر والفهم العميق للأسواق. أتوقع تألُّق قطاع البنوك عندنا في الإمارات وحتى قطاع العقارات بتكون نتائجه مميزة بإذن الله تعالى.</t>
+          <t>Hi, thank you for sharing your feedback. We’re sorry that you had experienced this, it is not what we expect our customers to feel nor see. We kindly request you to send us more details and your registered mobile number via social@emiratesnbd.com and quote Case #997789 for us to assist you better. Thanks.</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>1776179616000</v>
+        <v>1776251042000</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2044064867896963237</t>
+          <t>2044369434362753181</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2273,11 +2293,11 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>{'name': 'bader_alain', 'screenName': 'alnuaimi_bader', 'followersCount': 47, 'favouritesCount': 5559, 'friendsCount': 217, 'description': 'Power of simplicity'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174062, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -2286,16 +2306,16 @@
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2044064867896963237</t>
+          <t>2044369434362753181</t>
         </is>
       </c>
     </row>
@@ -2305,38 +2325,25 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>https://x.com/ChirinAsadi/status/2044082310447018168</t>
+          <t>https://x.com/Sems3499/status/2044363346460172688</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2044082310447018168</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>2044082310447018168</t>
-        </is>
-      </c>
+          <t>2044363346460172688</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://x.com/ChirinAsadi/status/2044082310447018168</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>@alnuaimi_bader اعتقد بنك دبي الامارات الوطني ENBD استفاد من اللخبطة التي حصلت في مارس
-بينما كان دبي الاسلامي DIB محافظاً في الانتقاء</t>
-        </is>
-      </c>
+          <t>https://x.com/undefined/status/undefined</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
       <c r="G28" t="n">
-        <v>1776182174000</v>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>2044064867896963237</t>
-        </is>
-      </c>
+        <v>1776312254982</v>
+      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2344,31 +2351,15 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>{'name': 'Chirin Al Asadi', 'screenName': 'ChirinAsadi', 'followersCount': 3884, 'favouritesCount': 2850, 'friendsCount': 237, 'description': 'كل الكتابات والافكار هنا 👇🏻أصلية.. أغرد بأفكاري الخاصة بي .. أيضا: قرارك الاستثماري يخصك وحدك🤍 لا تأخذ بأرائي - اسأل مستشارك'}</t>
-        </is>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>2044071581186699505</t>
-        </is>
-      </c>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
@@ -2376,35 +2367,35 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>https://x.com/SunnyLusty/status/2044082383205609853</t>
+          <t>https://x.com/Sems3499/status/2044363346460172688</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2044082383205609853</t>
+          <t>2044363346460172688</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2044082383205609853</t>
+          <t>2044363346460172688</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://x.com/SunnyLusty/status/2044082383205609853</t>
+          <t>https://x.com/Sems3499/status/2044363346460172688</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Is there any updates or changes regarding Installment deferment for the personal loan due to current geopolitical circumstances,</t>
+          <t>@nurkanaydogan Enbd bankalarında çalışanlar için 1. Şık olduğunu düşünüyorum (:</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>1776182192000</v>
+        <v>1776249178000</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2044082383205609853</t>
+          <t>2044358706846941680</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2414,27 +2405,31 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>{'name': 'आदियोगी', 'screenName': 'SunnyLusty', 'followersCount': 78, 'favouritesCount': 224, 'friendsCount': 39, 'description': 'Not related to any Political Party, but can’t close eyes if someone tries to fool, It’s can be any1'}</t>
+          <t>{'name': 'Sem', 'screenName': 'Sems3499', 'followersCount': 4, 'favouritesCount': 275, 'friendsCount': 7, 'description': ''}</t>
         </is>
       </c>
       <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
         <v>1</v>
       </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr"/>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>2044358706846941680</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
@@ -2442,35 +2437,36 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>https://x.com/SunnyLusty/status/2044082383205609853</t>
+          <t>https://x.com/metakixakbar/status/2044307778140025041</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2044082383205609853</t>
+          <t>2044307778140025041</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2044085223952900599</t>
+          <t>2044307778140025041</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2044085223952900599</t>
+          <t>https://x.com/metakixakbar/status/2044307778140025041</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>@SunnyLusty Hello, we have replied to you privately.</t>
+          <t>@ENBDdeals
+Took a Takaful policy from ENBD back in 2012. 15 year policy. Was supposed to mature in 2027. Policy was issued from Aman insurances. ENBD was distributor. Being told now to contact Aman insurance directly. Aman is as good as closed. ENBD is not taking responsibility.</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>1776182869000</v>
+        <v>1776235930000</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2044082383205609853</t>
+          <t>2044307778140025041</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2480,11 +2476,11 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174047, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Akbar Syed', 'screenName': 'metakixakbar', 'followersCount': 0, 'favouritesCount': 88, 'friendsCount': 25, 'description': ''}</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -2497,14 +2493,10 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>2044082383205609853</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
@@ -2512,38 +2504,35 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044078376982319373</t>
+          <t>https://x.com/metakixakbar/status/2044307778140025041</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2044078376982319373</t>
+          <t>2044307778140025041</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1962127907049930843</t>
+          <t>2044310308068425734</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://x.com/amsh75/status/1962127907049930843</t>
+          <t>https://x.com/ENBDdeals/status/2044310308068425734</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>سؤال:
-ماهو افضل بنك يشتري مديونية ؟!
-قرض عقاري + قرض شخصي .
-@alrajhibank @BSF_sa @alinma @BankAlbilad @snbalahli @GulfIntlBank @EmiratesNBD_AE @BankAlJazira @RiyadBank @alawwalsab @SAIBLIVE</t>
+          <t>@metakixakbar Quoting case #997567 in the subject line of the email from your registered email address We will make every effort to address the matter promptly and provide the necessary support. Thanks</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>1756642722000</v>
+        <v>1776236533000</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>1962127907049930843</t>
+          <t>2044307778140025041</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2553,11 +2542,11 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>{'name': 'علي محمد الضبعان', 'screenName': 'amsh75', 'followersCount': 32674, 'favouritesCount': 2853, 'friendsCount': 6053, 'description': 'حاصل على وسام الملك عبدالعزيز من الدرجة الثالثة/ مدير فرع @Trahum_sa بالمنطقة الشرقية/ عضو لجنة الاسكان التنموي بالمنطقة الشرقية / رئيس مجلس إدارة @tadom_sa'}</t>
+          <t>{'name': 'Emirates NBD Deals', 'screenName': 'ENBDdeals', 'followersCount': 39129, 'favouritesCount': 61, 'friendsCount': 4, 'description': 'Welcome to the official account for Emirates NBD Deals. نرحب بكم في الحساب الرسمي لعروض بنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -2566,14 +2555,18 @@
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>2535</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>2044307778140025041</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
@@ -2581,35 +2574,36 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044078376982319373</t>
+          <t>https://x.com/metakixakbar/status/2044307778140025041</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2044078376982319373</t>
+          <t>2044307778140025041</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1962458003224854945</t>
+          <t>2044310246277967968</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://x.com/KhalidSaeedR/status/1962458003224854945</t>
+          <t>https://x.com/ENBDdeals/status/2044310246277967968</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>@amsh75 @alrajhibank @BSF_sa @alinma @BankAlbilad @snbalahli @GulfIntlBank @EmiratesNBD_AE @BankAlJazira @RiyadBank @alawwalsab @SAIBLIVE انا ابحث ايضا عن شراء المديونيه قرض عقاري قرض شخصي،،،</t>
+          <t>@metakixakbar We sincerely regret for the inconvenience To be able to assist further, we kindly request you to reach out to us at
+ social@emiratesnbd.com</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>1756721423000</v>
+        <v>1776236518000</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>1962127907049930843</t>
+          <t>2044307778140025041</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2619,11 +2613,11 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>{'name': 'خالد سعيد اليْمِنِي (أبو مشاري)', 'screenName': 'KhalidSaeedR', 'followersCount': 11096, 'favouritesCount': 6906, 'friendsCount': 1130, 'description': 'صحافي ومذيع  تلفزيوني   ومقدم حفلات رسميه،،،\nأخصائي وممارس العلاقات العامه،،'}</t>
+          <t>{'name': 'Emirates NBD Deals', 'screenName': 'ENBDdeals', 'followersCount': 39129, 'favouritesCount': 61, 'friendsCount': 4, 'description': 'Welcome to the official account for Emirates NBD Deals. نرحب بكم في الحساب الرسمي لعروض بنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -2632,16 +2626,16 @@
         <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>1010</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>1962127907049930843</t>
+          <t>2044307778140025041</t>
         </is>
       </c>
     </row>
@@ -2651,35 +2645,38 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044078376982319373</t>
+          <t>https://x.com/HarshGada76429/status/2044356621351149946</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2044078376982319373</t>
+          <t>2044356621351149946</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2044075725334954107</t>
+          <t>2038970719238045794</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044075725334954107</t>
+          <t>https://x.com/HarshGada76429/status/2038970719238045794</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>@KhalidSaeedR @amsh75 @alrajhibank @BSF_sa @alinma @BankAlbilad @snbalahli @GulfIntlBank @EmiratesNBD_AE @BankAlJazira @RiyadBank @alawwalsab @SAIBLIVE والله من خلال تجربتي مع البنك السعودي الفرنسي لا انصح ابدا بشراء مديونية منه اتفقت مع الموظف على اعادة تمويل وكنت في بنك الرياض علي قرض شخصي وعقاري اتفقت مع الموظف بعد ماشاف راتبي والعقار المرهون لبنك الرياض قيمته ٣ مليون  قدروه عمارة ٢٥ شقة المهم موظف البنك الفرنسي</t>
+          <t>@RBLBankCares
+@rblbank
+I have been a loyal customer for last 3yrs using your world safari credit card I have achieved the milestone but missed the redemption date by 7 days 
+Request you to send me new redemption link for 10000rs voucher or I will have to end the relationship now</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>1776180604000</v>
+        <v>1774963476000</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>1962127907049930843</t>
+          <t>2038970719238045794</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2689,31 +2686,27 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>{'name': 'محمد', 'screenName': 'attas_2010', 'followersCount': 2342, 'favouritesCount': 3675, 'friendsCount': 4836, 'description': 'لا إله إلا الله محمد رسول الله\nتابعني وأتابعك'}</t>
+          <t>{'name': 'Harsh Gada', 'screenName': 'HarshGada76429', 'followersCount': 0, 'favouritesCount': 0, 'friendsCount': 21, 'description': ''}</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N33" t="n">
         <v>0</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>142</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>1962458003224854945</t>
-        </is>
-      </c>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
@@ -2721,36 +2714,39 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044078376982319373</t>
+          <t>https://x.com/HarshGada76429/status/2044356621351149946</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2044078376982319373</t>
+          <t>2044356621351149946</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2044076340891009154</t>
+          <t>2044356621351149946</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044076340891009154</t>
+          <t>https://x.com/HarshGada76429/status/2044356621351149946</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>@KhalidSaeedR @amsh75 @alrajhibank @BSF_sa @alinma @BankAlbilad @snbalahli @GulfIntlBank @EmiratesNBD_AE @BankAlJazira @RiyadBank @alawwalsab @SAIBLIVE موظف البنك الفرنسي قال نعطيك اعادة تمويل ويطلع لك فائض بالشخصي٧٥٠٠٠ وفعلا تحولت لي والعقاري قال يفيض لك٢٥٥٠٠٠ وسحب علي وماعاد يرد وحتى اليوم فوق ١٠ مرات احاول ارفع شكوى من التطبيق مايقبلون الشكوى 
-اصلا</t>
+          <t>@RBLBankCares @rblbank I haven't got the resolution yet 
+On technical terms you are denying me the voucher
+What about last 3 years of harassment where you guys were denying for voucher which i have earned by reaching milestone?
+@EmiratesNBD_AE   be careful with tie up with
+RBL Bank</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>1776180751000</v>
+        <v>1776247575000</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>1962127907049930843</t>
+          <t>2038970719238045794</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2760,7 +2756,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>{'name': 'محمد', 'screenName': 'attas_2010', 'followersCount': 2342, 'favouritesCount': 3675, 'friendsCount': 4836, 'description': 'لا إله إلا الله محمد رسول الله\nتابعني وأتابعك'}</t>
+          <t>{'name': 'Harsh Gada', 'screenName': 'HarshGada76429', 'followersCount': 0, 'favouritesCount': 0, 'friendsCount': 21, 'description': ''}</t>
         </is>
       </c>
       <c r="K34" t="n">
@@ -2777,12 +2773,12 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2044075725334954107</t>
+          <t>2038970719238045794</t>
         </is>
       </c>
     </row>
@@ -2792,35 +2788,35 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044078376982319373</t>
+          <t>https://x.com/HarshGada76429/status/2044356621351149946</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2044078376982319373</t>
+          <t>2044356621351149946</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2044077090039873867</t>
+          <t>2044364006027403737</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044077090039873867</t>
+          <t>https://x.com/RBLBankCares/status/2044364006027403737</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>@KhalidSaeedR @amsh75 @alrajhibank @BSF_sa @alinma @BankAlbilad @snbalahli @GulfIntlBank @EmiratesNBD_AE @BankAlJazira @RiyadBank @alawwalsab @SAIBLIVE وحاليا بعد ماكان عندي قرض عقاري في بنك الرياض راح ارجعه مليون٦٠٠ ألف على ١٥ سنةصرت مديون للبنك الفرنسي مليونين ٣٠٠ ألف والصك مرهون عندهم وكل الي سوه سددو لبنك الرياض مليون ٧٠الف قيمة السداد المبكر فقط والفائض الي وعدني فيه سحب علي ومايرد</t>
+          <t>@HarshGada76429 Hello, our representative will get in touch with you at the earliest to address your query. Regards, RBL Bank.</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>1776180930000</v>
+        <v>1776249336000</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>1962127907049930843</t>
+          <t>2038970719238045794</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2830,11 +2826,11 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>{'name': 'محمد', 'screenName': 'attas_2010', 'followersCount': 2342, 'favouritesCount': 3675, 'friendsCount': 4836, 'description': 'لا إله إلا الله محمد رسول الله\nتابعني وأتابعك'}</t>
+          <t>{'name': 'RBL Bank Cares', 'screenName': 'RBLBankCares', 'followersCount': 15139, 'favouritesCount': 107, 'friendsCount': 1, 'description': 'Welcome to the official service handle of RBL Bank for addressing your queries. The Bank’s social media guidelines are available on: https://t.co/4latICF1Kx'}</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -2847,12 +2843,12 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2044076340891009154</t>
+          <t>2044356621351149946</t>
         </is>
       </c>
     </row>
@@ -2862,69 +2858,67 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044078376982319373</t>
+          <t>https://x.com/titledeednews/status/2044351837869105398</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2044078376982319373</t>
+          <t>2044351837869105398</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2044077341328957795</t>
+          <t>2044351837869105398</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044077341328957795</t>
+          <t>https://x.com/titledeednews/status/2044351837869105398</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>@KhalidSaeedR @amsh75 @alrajhibank @BSF_sa @alinma @BankAlbilad @snbalahli @GulfIntlBank @EmiratesNBD_AE @BankAlJazira @RiyadBank @alawwalsab @SAIBLIVE والله كاننا نتعامل مع عصابة مو موظف بنك لي ١٧ سنة اتعامل مع البنوك عمري ماشفت تعامل مثل البنك الفرنسي</t>
+          <t>Sobha Realty is making off-plan investing in Dubai more accessible.
+In partnership with Emirates NBD, Sobha Realty introduces flexible financing solutions, giving investors easier access to high-potential opportunities.
+#DubaiInvestors #OffPlanDubai #RealEstateInvesting #Dubai https://t.co/yHBmK8RVEk</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>1776180989000</v>
+        <v>1776246435000</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>1962127907049930843</t>
+          <t>2044351837869105398</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF7_CgOb0AAEGFF.jpg', 'type': 'photo', 'id': '2044351699348082688'}]</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>{'name': 'محمد', 'screenName': 'attas_2010', 'followersCount': 2342, 'favouritesCount': 3675, 'friendsCount': 4836, 'description': 'لا إله إلا الله محمد رسول الله\nتابعني وأتابعك'}</t>
+          <t>{'name': 'The Title Deed', 'screenName': 'titledeednews', 'followersCount': 0, 'favouritesCount': 0, 'friendsCount': 10, 'description': ''}</t>
         </is>
       </c>
       <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
         <v>1</v>
       </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0</v>
-      </c>
       <c r="N36" t="n">
         <v>0</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>2044077090039873867</t>
-        </is>
-      </c>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
@@ -2932,40 +2926,65 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044078376982319373</t>
+          <t>https://x.com/titledeednews/status/2044351837869105398</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2044078376982319373</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
+          <t>2044351837869105398</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2044042548185010299</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://x.com/undefined/status/undefined</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr"/>
+          <t>https://x.com/titledeednews/status/2044042548185010299</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Al Habtoor Group is committing over AED 5 billion to a new commercial tower in Dubai. Another strong indicator of sustained demand for Grade A office space and long-term market confidence.
+#DubaiRealEstate #CommercialRealEstate #InvestInDubai #DubaiBrokers #RealEstateNews https://t.co/kHUr6Xe7wr</t>
+        </is>
+      </c>
       <c r="G37" t="n">
-        <v>1776225826173</v>
-      </c>
-      <c r="H37" t="inlineStr"/>
+        <v>1776172694000</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>2044042548185010299</t>
+        </is>
+      </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF3loHrbsAAWgHC.jpg', 'type': 'photo', 'id': '2044042283314819072'}]</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
+          <t>{'name': 'The Title Deed', 'screenName': 'titledeednews', 'followersCount': 0, 'favouritesCount': 0, 'friendsCount': 10, 'description': ''}</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>1</v>
+      </c>
+      <c r="N37" t="n">
+        <v>1</v>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr"/>
     </row>
     <row r="38">
@@ -2974,25 +2993,37 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044078376982319373</t>
+          <t>https://x.com/oras_2030/status/2044301025142513927</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2044078376982319373</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
+          <t>2044301025142513927</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2039084064070623329</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://x.com/undefined/status/undefined</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr"/>
+          <t>https://x.com/AliAhmedk66633/status/2039084064070623329</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_KSA اسوء تجربة من البنك في خدمة العملاء ولا ادارة التحصيل الي اسلوبه زي الزفت تخيلو طلبت خطاب عدم مومانعه  من شراء المديونية لك وشو يسوي البنك يتصل على البنك الثاني ويتاكد متى تتغير النسبه ويتاخر الطلب لي ثلاث ايام وانا اتصل على ادارة التحصيل وخدمه العملاء اخر شي</t>
+        </is>
+      </c>
       <c r="G38" t="n">
-        <v>1776225826173</v>
-      </c>
-      <c r="H38" t="inlineStr"/>
+        <v>1774990499000</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>2039084064070623329</t>
+        </is>
+      </c>
       <c r="I38" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3000,14 +3031,26 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
+          <t>{'name': 'Ali Ahmed', 'screenName': 'AliAhmedk66633', 'followersCount': 0, 'favouritesCount': 0, 'friendsCount': 6, 'description': ''}</t>
+        </is>
+      </c>
+      <c r="K38" t="n">
+        <v>2</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr"/>
     </row>
     <row r="39">
@@ -3016,35 +3059,35 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044078376982319373</t>
+          <t>https://x.com/oras_2030/status/2044301025142513927</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2044078376982319373</t>
+          <t>2044301025142513927</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2044078376982319373</t>
+          <t>2044301025142513927</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044078376982319373</t>
+          <t>https://x.com/oras_2030/status/2044301025142513927</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>@KhalidSaeedR @amsh75 @alrajhibank @BSF_sa @alinma @BankAlbilad @snbalahli @GulfIntlBank @EmiratesNBD_AE @BankAlJazira @RiyadBank @alawwalsab @SAIBLIVE فوق ١٠ مرات ارفع شكاوي هذا الرد</t>
+          <t>@AliAhmedk66633 @EmiratesNBD_KSA هل تنصح اخ علي@ انقل راتبي عندهم عشان قرض شخصي لان نسبتهم اقل من البنوك الاخرى؟</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>1776181236000</v>
+        <v>1776234320000</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>1962127907049930843</t>
+          <t>2039084064070623329</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -3054,7 +3097,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>{'name': 'محمد', 'screenName': 'attas_2010', 'followersCount': 2342, 'favouritesCount': 3675, 'friendsCount': 4836, 'description': 'لا إله إلا الله محمد رسول الله\nتابعني وأتابعك'}</t>
+          <t>{'name': 'oras2030', 'screenName': 'oras_2030', 'followersCount': 0, 'favouritesCount': 133, 'friendsCount': 126, 'description': 'سبحان الله وبحمده سبحان الله العظيم'}</t>
         </is>
       </c>
       <c r="K39" t="n">
@@ -3071,12 +3114,12 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>2044078181662019702</t>
+          <t>2039084064070623329</t>
         </is>
       </c>
     </row>
@@ -3086,38 +3129,35 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044077341328957795</t>
+          <t>https://x.com/Eisa_Shj/status/2044283005183857003</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2044077341328957795</t>
+          <t>2044283005183857003</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1962127907049930843</t>
+          <t>2044283005183857003</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://x.com/amsh75/status/1962127907049930843</t>
+          <t>https://x.com/Eisa_Shj/status/2044283005183857003</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>سؤال:
-ماهو افضل بنك يشتري مديونية ؟!
-قرض عقاري + قرض شخصي .
-@alrajhibank @BSF_sa @alinma @BankAlbilad @snbalahli @GulfIntlBank @EmiratesNBD_AE @BankAlJazira @RiyadBank @alawwalsab @SAIBLIVE</t>
+          <t>ماعرف ليش اغلب الناس لين الحين تفتح عندهم و هم من اكثر البنوك في تعقيد الامور الحمدالله على نعمه ENBD الصراحة🦦</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>1756642722000</v>
+        <v>1776230024000</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>1962127907049930843</t>
+          <t>2044283005183857003</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -3127,11 +3167,11 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>{'name': 'علي محمد الضبعان', 'screenName': 'amsh75', 'followersCount': 32674, 'favouritesCount': 2853, 'friendsCount': 6053, 'description': 'حاصل على وسام الملك عبدالعزيز من الدرجة الثالثة/ مدير فرع @Trahum_sa بالمنطقة الشرقية/ عضو لجنة الاسكان التنموي بالمنطقة الشرقية / رئيس مجلس إدارة @tadom_sa'}</t>
+          <t>{'name': 'عـيـســى الأمـيــري', 'screenName': 'Eisa_Shj', 'followersCount': 74, 'favouritesCount': 40740, 'friendsCount': 404, 'description': 'Don’t be sorry, BE BETTER ✨'}</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
@@ -3140,11 +3180,11 @@
         <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>2535</t>
+          <t>77</t>
         </is>
       </c>
       <c r="P40" t="inlineStr"/>
@@ -3155,35 +3195,35 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044077341328957795</t>
+          <t>https://x.com/dcgguide/status/2044340590037655768</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2044077341328957795</t>
+          <t>2044340590037655768</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1962458003224854945</t>
+          <t>2044340590037655768</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://x.com/KhalidSaeedR/status/1962458003224854945</t>
+          <t>https://x.com/dcgguide/status/2044340590037655768</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>@amsh75 @alrajhibank @BSF_sa @alinma @BankAlbilad @snbalahli @GulfIntlBank @EmiratesNBD_AE @BankAlJazira @RiyadBank @alawwalsab @SAIBLIVE انا ابحث ايضا عن شراء المديونيه قرض عقاري قرض شخصي،،،</t>
+          <t>Emirates Islamic Drives SME Growth And Engagement Through AED 1 Million Business Banking Campaign https://t.co/lYSRNGGq3N</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>1756721423000</v>
+        <v>1776243753000</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>1962127907049930843</t>
+          <t>2044340590037655768</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3193,11 +3233,11 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>{'name': 'خالد سعيد اليْمِنِي (أبو مشاري)', 'screenName': 'KhalidSaeedR', 'followersCount': 11096, 'favouritesCount': 6906, 'friendsCount': 1130, 'description': 'صحافي ومذيع  تلفزيوني   ومقدم حفلات رسميه،،،\nأخصائي وممارس العلاقات العامه،،'}</t>
+          <t>{'name': 'DUBAI CITY GUIDE from Cyber Gear', 'screenName': 'dcgguide', 'followersCount': 93487, 'favouritesCount': 19475, 'friendsCount': 106586, 'description': 'DCG is a https://t.co/bmR4jltJAW e-venture. We publish guest posts at https://t.co/EISzXb0O0y Learn AI at https://t.co/YcnxpXcCNU'}</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -3210,14 +3250,10 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>1010</t>
-        </is>
-      </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>1962127907049930843</t>
-        </is>
-      </c>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
@@ -3225,35 +3261,35 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044077341328957795</t>
+          <t>https://x.com/dcgguide/status/2044340590037655768</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2044077341328957795</t>
+          <t>2044340590037655768</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2044075725334954107</t>
+          <t>2044619960383848830</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044075725334954107</t>
+          <t>https://x.com/dcgguide/status/2044619960383848830</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>@KhalidSaeedR @amsh75 @alrajhibank @BSF_sa @alinma @BankAlbilad @snbalahli @GulfIntlBank @EmiratesNBD_AE @BankAlJazira @RiyadBank @alawwalsab @SAIBLIVE والله من خلال تجربتي مع البنك السعودي الفرنسي لا انصح ابدا بشراء مديونية منه اتفقت مع الموظف على اعادة تمويل وكنت في بنك الرياض علي قرض شخصي وعقاري اتفقت مع الموظف بعد ماشاف راتبي والعقار المرهون لبنك الرياض قيمته ٣ مليون  قدروه عمارة ٢٥ شقة المهم موظف البنك الفرنسي</t>
+          <t>Soulland Arrives In Dubai, Marking Its First Entry Into The Middle East https://t.co/lNcIEXHcGK</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>1776180604000</v>
+        <v>1776310360000</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>1962127907049930843</t>
+          <t>2044619960383848830</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3263,11 +3299,11 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>{'name': 'محمد', 'screenName': 'attas_2010', 'followersCount': 2342, 'favouritesCount': 3675, 'friendsCount': 4836, 'description': 'لا إله إلا الله محمد رسول الله\nتابعني وأتابعك'}</t>
+          <t>{'name': 'DUBAI CITY GUIDE from Cyber Gear', 'screenName': 'dcgguide', 'followersCount': 93487, 'favouritesCount': 19475, 'friendsCount': 106586, 'description': 'DCG is a https://t.co/bmR4jltJAW e-venture. We publish guest posts at https://t.co/EISzXb0O0y Learn AI at https://t.co/YcnxpXcCNU'}</t>
         </is>
       </c>
       <c r="K42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
@@ -3276,18 +3312,14 @@
         <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>142</t>
-        </is>
-      </c>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>1962458003224854945</t>
-        </is>
-      </c>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
@@ -3295,36 +3327,37 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044077341328957795</t>
+          <t>https://x.com/EntAlArabiya/status/2044341445717610661</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2044077341328957795</t>
+          <t>2044341445717610661</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2044076340891009154</t>
+          <t>2044341445717610661</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044076340891009154</t>
+          <t>https://x.com/EntAlArabiya/status/2044341445717610661</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>@KhalidSaeedR @amsh75 @alrajhibank @BSF_sa @alinma @BankAlbilad @snbalahli @GulfIntlBank @EmiratesNBD_AE @BankAlJazira @RiyadBank @alawwalsab @SAIBLIVE موظف البنك الفرنسي قال نعطيك اعادة تمويل ويطلع لك فائض بالشخصي٧٥٠٠٠ وفعلا تحولت لي والعقاري قال يفيض لك٢٥٥٠٠٠ وسحب علي وماعاد يرد وحتى اليوم فوق ١٠ مرات احاول ارفع شكوى من التطبيق مايقبلون الشكوى 
-اصلا</t>
+          <t>الإمارات الإسلامي @emiratesislamic  يعزز قطاع الأعمال بحملة للشركات الصغيرة
+#الإمارات #دبي #بنوك #شركات #مشاريع_صغيرة #تمويل #اقتصاد #استثمار #نمو #entalarabiya
+https://t.co/XNTvseOsQ0</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>1776180751000</v>
+        <v>1776243957000</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>1962127907049930843</t>
+          <t>2044341445717610661</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3334,31 +3367,27 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>{'name': 'محمد', 'screenName': 'attas_2010', 'followersCount': 2342, 'favouritesCount': 3675, 'friendsCount': 4836, 'description': 'لا إله إلا الله محمد رسول الله\nتابعني وأتابعك'}</t>
+          <t>{'name': 'Entrepreneur العربية', 'screenName': 'EntAlArabiya', 'followersCount': 15614, 'favouritesCount': 5008, 'friendsCount': 796, 'description': 'لمتابعة آخر أخبار عالم ريادة الأعمال في منطقة الشرق الأوسط وشمال إفريقيا، الحساب الرسمي لمجلة Entrepreneur العربية'}</t>
         </is>
       </c>
       <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
         <v>1</v>
       </c>
-      <c r="L43" t="n">
-        <v>0</v>
-      </c>
-      <c r="M43" t="n">
-        <v>0</v>
-      </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>2044075725334954107</t>
-        </is>
-      </c>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
@@ -3366,35 +3395,37 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044077341328957795</t>
+          <t>https://x.com/EntAlArabiya/status/2044341445717610661</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2044077341328957795</t>
+          <t>2044341445717610661</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2044077090039873867</t>
+          <t>2044366042470977758</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044077090039873867</t>
+          <t>https://x.com/EntAlArabiya/status/2044366042470977758</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>@KhalidSaeedR @amsh75 @alrajhibank @BSF_sa @alinma @BankAlbilad @snbalahli @GulfIntlBank @EmiratesNBD_AE @BankAlJazira @RiyadBank @alawwalsab @SAIBLIVE وحاليا بعد ماكان عندي قرض عقاري في بنك الرياض راح ارجعه مليون٦٠٠ ألف على ١٥ سنةصرت مديون للبنك الفرنسي مليونين ٣٠٠ ألف والصك مرهون عندهم وكل الي سوه سددو لبنك الرياض مليون ٧٠الف قيمة السداد المبكر فقط والفائض الي وعدني فيه سحب علي ومايرد</t>
+          <t>شراكة بين RGB وBNC Publishing لتعزيز الوصول إلى المحتوى الصحي الموثوق في المنطقة @EntMagazineME  
+#الإمارات #صحة #توعية #طب #إعلام #شركات #محتوى #رفاهية #ابتكار #entalarabiya
+https://t.co/PFB5U9YnOG</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>1776180930000</v>
+        <v>1776249821000</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>1962127907049930843</t>
+          <t>2044366042470977758</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3404,31 +3435,27 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>{'name': 'محمد', 'screenName': 'attas_2010', 'followersCount': 2342, 'favouritesCount': 3675, 'friendsCount': 4836, 'description': 'لا إله إلا الله محمد رسول الله\nتابعني وأتابعك'}</t>
+          <t>{'name': 'Entrepreneur العربية', 'screenName': 'EntAlArabiya', 'followersCount': 15614, 'favouritesCount': 5008, 'friendsCount': 796, 'description': 'لمتابعة آخر أخبار عالم ريادة الأعمال في منطقة الشرق الأوسط وشمال إفريقيا، الحساب الرسمي لمجلة Entrepreneur العربية'}</t>
         </is>
       </c>
       <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
         <v>1</v>
       </c>
-      <c r="L44" t="n">
-        <v>0</v>
-      </c>
-      <c r="M44" t="n">
-        <v>0</v>
-      </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>2044076340891009154</t>
-        </is>
-      </c>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
@@ -3436,35 +3463,35 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044077341328957795</t>
+          <t>https://x.com/gold_hadas/status/2044447495619547616</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2044077341328957795</t>
+          <t>2044447495619547616</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2044077341328957795</t>
+          <t>2044447495619547616</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044077341328957795</t>
+          <t>https://x.com/gold_hadas/status/2044447495619547616</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>@KhalidSaeedR @amsh75 @alrajhibank @BSF_sa @alinma @BankAlbilad @snbalahli @GulfIntlBank @EmiratesNBD_AE @BankAlJazira @RiyadBank @alawwalsab @SAIBLIVE والله كاننا نتعامل مع عصابة مو موظف بنك لي ١٧ سنة اتعامل مع البنوك عمري ماشفت تعامل مثل البنك الفرنسي</t>
+          <t>Emirates Islamic launches AED1m campaign for SME customers  https://t.co/7gX7HHRcOh</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>1776180989000</v>
+        <v>1776269241000</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>1962127907049930843</t>
+          <t>2044447495619547616</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3474,11 +3501,11 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>{'name': 'محمد', 'screenName': 'attas_2010', 'followersCount': 2342, 'favouritesCount': 3675, 'friendsCount': 4836, 'description': 'لا إله إلا الله محمد رسول الله\nتابعني وأتابعك'}</t>
+          <t>{'name': 'Nicholas MOLODYKO, writer', 'screenName': 'gold_hadas', 'followersCount': 1108, 'favouritesCount': 23737, 'friendsCount': 301, 'description': "Agency (individual free will) is the collective spiritual value of an individual's words and actions—Existence of free will is central to the U.S. Constitution."}</t>
         </is>
       </c>
       <c r="K45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
@@ -3491,14 +3518,10 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>2044077090039873867</t>
-        </is>
-      </c>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
@@ -3506,52 +3529,49 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044077090039873867</t>
+          <t>https://x.com/gold_hadas/status/2044447495619547616</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2044077090039873867</t>
+          <t>2044447495619547616</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1962127907049930843</t>
+          <t>2044582960431554593</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://x.com/amsh75/status/1962127907049930843</t>
+          <t>https://x.com/gold_hadas/status/2044582960431554593</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>سؤال:
-ماهو افضل بنك يشتري مديونية ؟!
-قرض عقاري + قرض شخصي .
-@alrajhibank @BSF_sa @alinma @BankAlbilad @snbalahli @GulfIntlBank @EmiratesNBD_AE @BankAlJazira @RiyadBank @alawwalsab @SAIBLIVE</t>
+          <t>Modesty is a defining element of a Muslim’s “style” — a “less is more” philosophy that prioritizes spirituality and personal comfort over overt attention seeking. Identity is both internal and external. Modesty is a conscious choice —and a powerful one. https://t.co/hcxLG2j35s https://t.co/V2EWTgPYbW</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>1756642722000</v>
+        <v>1776301538000</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>1962127907049930843</t>
+          <t>2044582960431554593</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF_RXPNWoAA_0TN.jpg', 'type': 'photo', 'id': '2044582952999231488'}]</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>{'name': 'علي محمد الضبعان', 'screenName': 'amsh75', 'followersCount': 32674, 'favouritesCount': 2853, 'friendsCount': 6053, 'description': 'حاصل على وسام الملك عبدالعزيز من الدرجة الثالثة/ مدير فرع @Trahum_sa بالمنطقة الشرقية/ عضو لجنة الاسكان التنموي بالمنطقة الشرقية / رئيس مجلس إدارة @tadom_sa'}</t>
+          <t>{'name': 'Nicholas MOLODYKO, writer', 'screenName': 'gold_hadas', 'followersCount': 1108, 'favouritesCount': 23737, 'friendsCount': 301, 'description': "Agency (individual free will) is the collective spiritual value of an individual's words and actions—Existence of free will is central to the U.S. Constitution."}</t>
         </is>
       </c>
       <c r="K46" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
@@ -3560,11 +3580,11 @@
         <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>2535</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P46" t="inlineStr"/>
@@ -3575,35 +3595,37 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044077090039873867</t>
+          <t>https://x.com/emiratesislamic/status/2044294659795513346</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2044077090039873867</t>
+          <t>2044294659795513346</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1962458003224854945</t>
+          <t>2044294653097156714</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://x.com/KhalidSaeedR/status/1962458003224854945</t>
+          <t>https://x.com/emiratesislamic/status/2044294653097156714</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>@amsh75 @alrajhibank @BSF_sa @alinma @BankAlbilad @snbalahli @GulfIntlBank @EmiratesNBD_AE @BankAlJazira @RiyadBank @alawwalsab @SAIBLIVE انا ابحث ايضا عن شراء المديونيه قرض عقاري قرض شخصي،،،</t>
+          <t>من “يوماً ما” إلى يوم الانتقال!
+التمويل السكني من الإمارات الإسلامي يجعل حلم امتلاك منزلك حقيقة، مع المرونة والوضوح في كل خطوة من رحلتك.
+استمتع بحلول تمويلية مصممة خصيصاً لك، ودعم متكامل طوال الطريق، لتصبح تجربة امتلاك المنزل سلسة وميسرة.</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>1756721423000</v>
+        <v>1776232801000</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>1962127907049930843</t>
+          <t>2044294653097156714</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3613,11 +3635,11 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>{'name': 'خالد سعيد اليْمِنِي (أبو مشاري)', 'screenName': 'KhalidSaeedR', 'followersCount': 11096, 'favouritesCount': 6906, 'friendsCount': 1130, 'description': 'صحافي ومذيع  تلفزيوني   ومقدم حفلات رسميه،،،\nأخصائي وممارس العلاقات العامه،،'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="K47" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
@@ -3626,18 +3648,14 @@
         <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>1010</t>
-        </is>
-      </c>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>1962127907049930843</t>
-        </is>
-      </c>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
@@ -3645,35 +3663,36 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044077090039873867</t>
+          <t>https://x.com/emiratesislamic/status/2044294659795513346</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2044077090039873867</t>
+          <t>2044294659795513346</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2044075725334954107</t>
+          <t>2044294656716836969</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044075725334954107</t>
+          <t>https://x.com/emiratesislamic/status/2044294656716836969</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>@KhalidSaeedR @amsh75 @alrajhibank @BSF_sa @alinma @BankAlbilad @snbalahli @GulfIntlBank @EmiratesNBD_AE @BankAlJazira @RiyadBank @alawwalsab @SAIBLIVE والله من خلال تجربتي مع البنك السعودي الفرنسي لا انصح ابدا بشراء مديونية منه اتفقت مع الموظف على اعادة تمويل وكنت في بنك الرياض علي قرض شخصي وعقاري اتفقت مع الموظف بعد ماشاف راتبي والعقار المرهون لبنك الرياض قيمته ٣ مليون  قدروه عمارة ٢٥ شقة المهم موظف البنك الفرنسي</t>
+          <t>ابدأ رحلتك نحو منزل أحلامك اليوم.
+https://t.co/lQDtk9615Y</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>1776180604000</v>
+        <v>1776232801000</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>1962127907049930843</t>
+          <t>2044294653097156714</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3683,11 +3702,11 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>{'name': 'محمد', 'screenName': 'attas_2010', 'followersCount': 2342, 'favouritesCount': 3675, 'friendsCount': 4836, 'description': 'لا إله إلا الله محمد رسول الله\nتابعني وأتابعك'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="K48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
@@ -3700,12 +3719,12 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>127</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>1962458003224854945</t>
+          <t>2044294653097156714</t>
         </is>
       </c>
     </row>
@@ -3715,36 +3734,39 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044077090039873867</t>
+          <t>https://x.com/emiratesislamic/status/2044294659795513346</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2044077090039873867</t>
+          <t>2044294659795513346</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2044076340891009154</t>
+          <t>2044294659795513346</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044076340891009154</t>
+          <t>https://x.com/emiratesislamic/status/2044294659795513346</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>@KhalidSaeedR @amsh75 @alrajhibank @BSF_sa @alinma @BankAlbilad @snbalahli @GulfIntlBank @EmiratesNBD_AE @BankAlJazira @RiyadBank @alawwalsab @SAIBLIVE موظف البنك الفرنسي قال نعطيك اعادة تمويل ويطلع لك فائض بالشخصي٧٥٠٠٠ وفعلا تحولت لي والعقاري قال يفيض لك٢٥٥٠٠٠ وسحب علي وماعاد يرد وحتى اليوم فوق ١٠ مرات احاول ارفع شكوى من التطبيق مايقبلون الشكوى 
-اصلا</t>
+          <t>From “one day” to move-in day.
+Emirates Islamic Home Finance helps turn home ownership into reality, with the flexibility and clarity you need at every step.
+With tailored finance solutions and guided support throughout,
+Your home journey starts here.
+https://t.co/XwkOLamNf0</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>1776180751000</v>
+        <v>1776232802000</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>1962127907049930843</t>
+          <t>2044294653097156714</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3754,11 +3776,11 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>{'name': 'محمد', 'screenName': 'attas_2010', 'followersCount': 2342, 'favouritesCount': 3675, 'friendsCount': 4836, 'description': 'لا إله إلا الله محمد رسول الله\nتابعني وأتابعك'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="K49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
@@ -3771,12 +3793,12 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>119</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>2044075725334954107</t>
+          <t>2044294656716836969</t>
         </is>
       </c>
     </row>
@@ -3786,69 +3808,68 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044077090039873867</t>
+          <t>https://x.com/EntMagazineME/status/2044312732879728677</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2044077090039873867</t>
+          <t>2044312732879728677</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2044077090039873867</t>
+          <t>2044312732879728677</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044077090039873867</t>
+          <t>https://x.com/EntMagazineME/status/2044312732879728677</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>@KhalidSaeedR @amsh75 @alrajhibank @BSF_sa @alinma @BankAlbilad @snbalahli @GulfIntlBank @EmiratesNBD_AE @BankAlJazira @RiyadBank @alawwalsab @SAIBLIVE وحاليا بعد ماكان عندي قرض عقاري في بنك الرياض راح ارجعه مليون٦٠٠ ألف على ١٥ سنةصرت مديون للبنك الفرنسي مليونين ٣٠٠ ألف والصك مرهون عندهم وكل الي سوه سددو لبنك الرياض مليون ٧٠الف قيمة السداد المبكر فقط والفائض الي وعدني فيه سحب علي ومايرد</t>
+          <t>@emiratesislamic has announced the launch of a new Business Banking campaign aimed at supporting 3SME customers and strengthening #business resilience across the #UAE.
+Running until June 30, 2026, the campaign allows businesses to participate by increasing and maintaining their average balances in their Business Banking Accounts.
+The initiative offers a total prize pool of AED1 million and will reward 55 winners over three months, providing multiple opportunities for customers to win cash prizes while encouraging sustainable growth.
+🔗Read more HERE: https://t.co/j0Wq0RjPdm</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>1776180930000</v>
+        <v>1776237111000</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>1962127907049930843</t>
+          <t>2044312732879728677</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF7bgFgb0AArMEW.jpg', 'type': 'photo', 'id': '2044312625153298432'}]</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>{'name': 'محمد', 'screenName': 'attas_2010', 'followersCount': 2342, 'favouritesCount': 3675, 'friendsCount': 4836, 'description': 'لا إله إلا الله محمد رسول الله\nتابعني وأتابعك'}</t>
+          <t>{'name': 'Entrepreneur Middle East', 'screenName': 'EntMagazineME', 'followersCount': 178521, 'favouritesCount': 30182, 'friendsCount': 622, 'description': 'The official Twitter of Entrepreneur Middle East: inspiring, informing, and celebrating entrepreneurs in the Middle East, and beyond.'}</t>
         </is>
       </c>
       <c r="K50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>2044076340891009154</t>
-        </is>
-      </c>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
@@ -3856,69 +3877,69 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044077090039873867</t>
+          <t>https://x.com/EntMagazineME/status/2044312732879728677</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2044077090039873867</t>
+          <t>2044312732879728677</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2044077341328957795</t>
+          <t>2044354972473766389</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044077341328957795</t>
+          <t>https://x.com/EntMagazineME/status/2044354972473766389</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>@KhalidSaeedR @amsh75 @alrajhibank @BSF_sa @alinma @BankAlbilad @snbalahli @GulfIntlBank @EmiratesNBD_AE @BankAlJazira @RiyadBank @alawwalsab @SAIBLIVE والله كاننا نتعامل مع عصابة مو موظف بنك لي ١٧ سنة اتعامل مع البنوك عمري ماشفت تعامل مثل البنك الفرنسي</t>
+          <t>RGB (@RGBDubai), a #Dubai-based broadcasting and content production company known for its cutting-edge output and expertise in branding and identity since 2006, and the creator of The Health Community—a digital platform focused on verified medical knowledge—has entered a strategic media partnership with Dubai-headquartered regional media company BNC Publishing.
+The collaboration aims to expand access to credible, expert-led health content across the Middle East, leveraging Entrepreneur’s bilingual platforms and established regional audience.
+Designed as more than a content platform, The Health Community seeks to create a connected ecosystem where reliable #healthcare knowledge can be shared in ways that are practical and accessible for everyday life.
+Under the partnership, Entrepreneur Middle East (@EntMagazineME) and Entrepreneur Al Arabiya will collaborate with RGB to develop bilingual editorial features, #expert insights, and multimedia storytelling that elevate conversations around prevention, wellbeing, and human performance across the region.
+Read more HERE: https://t.co/KBGmbzdXAG</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>1776180989000</v>
+        <v>1776247182000</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>1962127907049930843</t>
+          <t>2044354972473766389</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF8B64ZaYAECgQU.jpg', 'type': 'photo', 'id': '2044354866932506625'}]</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>{'name': 'محمد', 'screenName': 'attas_2010', 'followersCount': 2342, 'favouritesCount': 3675, 'friendsCount': 4836, 'description': 'لا إله إلا الله محمد رسول الله\nتابعني وأتابعك'}</t>
+          <t>{'name': 'Entrepreneur Middle East', 'screenName': 'EntMagazineME', 'followersCount': 178521, 'favouritesCount': 30182, 'friendsCount': 622, 'description': 'The official Twitter of Entrepreneur Middle East: inspiring, informing, and celebrating entrepreneurs in the Middle East, and beyond.'}</t>
         </is>
       </c>
       <c r="K51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>2044077090039873867</t>
-        </is>
-      </c>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
@@ -3926,52 +3947,50 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044076340891009154</t>
+          <t>https://x.com/emiratesislamic/status/2044471342880170391</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2044076340891009154</t>
+          <t>2044471342880170391</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>1962127907049930843</t>
+          <t>2044471339784810653</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>https://x.com/amsh75/status/1962127907049930843</t>
+          <t>https://x.com/emiratesislamic/status/2044471339784810653</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>سؤال:
-ماهو افضل بنك يشتري مديونية ؟!
-قرض عقاري + قرض شخصي .
-@alrajhibank @BSF_sa @alinma @BankAlbilad @snbalahli @GulfIntlBank @EmiratesNBD_AE @BankAlJazira @RiyadBank @alawwalsab @SAIBLIVE</t>
+          <t>احصل على فرصة الفوز بحصة من الجوائز النقدية قيمتها تصل إلى 1,000,000 درهم. كل زيادة بقيمة 100,000 درهم في حسابك المصرفي للأعمال تمنحك فرصة واحدة للدخول في السحب.
+اجعل شركتك إحدى الشركات الـ 55 الفائزة. فهل ستكون من بينها؟ https://t.co/zGFXn2y3iT</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>1756642722000</v>
+        <v>1776274926000</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>1962127907049930843</t>
+          <t>2044471339784810653</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF9r2SlXIAA7IEH.jpg', 'type': 'photo', 'id': '2044471336295145472'}]</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>{'name': 'علي محمد الضبعان', 'screenName': 'amsh75', 'followersCount': 32674, 'favouritesCount': 2853, 'friendsCount': 6053, 'description': 'حاصل على وسام الملك عبدالعزيز من الدرجة الثالثة/ مدير فرع @Trahum_sa بالمنطقة الشرقية/ عضو لجنة الاسكان التنموي بالمنطقة الشرقية / رئيس مجلس إدارة @tadom_sa'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="K52" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
@@ -3980,11 +3999,11 @@
         <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>2535</t>
+          <t>147</t>
         </is>
       </c>
       <c r="P52" t="inlineStr"/>
@@ -3995,35 +4014,40 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044076340891009154</t>
+          <t>https://x.com/emiratesislamic/status/2044471342880170391</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2044076340891009154</t>
+          <t>2044471342880170391</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>1962458003224854945</t>
+          <t>2044471342880170391</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://x.com/KhalidSaeedR/status/1962458003224854945</t>
+          <t>https://x.com/emiratesislamic/status/2044471342880170391</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>@amsh75 @alrajhibank @BSF_sa @alinma @BankAlbilad @snbalahli @GulfIntlBank @EmiratesNBD_AE @BankAlJazira @RiyadBank @alawwalsab @SAIBLIVE انا ابحث ايضا عن شراء المديونيه قرض عقاري قرض شخصي،،،</t>
+          <t>الجائزة النقدية الكبرى: 250,000 درهم (فائز واحد) 
+الجائزة النقدية الثانية: 100,000 درهم (فائزان اثنان)
+الجوائز النقدية الشهرية: تصل إلى 25 ألف درهم (52 فائز)
+يسري العرض لغاية 30 يونيو 2026.
+تطبق الشروط والأحكام.
+https://t.co/RWuJWfhfUm</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>1756721423000</v>
+        <v>1776274927000</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>1962127907049930843</t>
+          <t>2044471339784810653</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -4033,11 +4057,11 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>{'name': 'خالد سعيد اليْمِنِي (أبو مشاري)', 'screenName': 'KhalidSaeedR', 'followersCount': 11096, 'favouritesCount': 6906, 'friendsCount': 1130, 'description': 'صحافي ومذيع  تلفزيوني   ومقدم حفلات رسميه،،،\nأخصائي وممارس العلاقات العامه،،'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="K53" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
@@ -4046,16 +4070,16 @@
         <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>1010</t>
+          <t>147</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>1962127907049930843</t>
+          <t>2044471339784810653</t>
         </is>
       </c>
     </row>
@@ -4065,49 +4089,50 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044076340891009154</t>
+          <t>https://x.com/emiratesislamic/status/2044471339784810653</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2044076340891009154</t>
+          <t>2044471339784810653</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2044075725334954107</t>
+          <t>2044471339784810653</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044075725334954107</t>
+          <t>https://x.com/emiratesislamic/status/2044471339784810653</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>@KhalidSaeedR @amsh75 @alrajhibank @BSF_sa @alinma @BankAlbilad @snbalahli @GulfIntlBank @EmiratesNBD_AE @BankAlJazira @RiyadBank @alawwalsab @SAIBLIVE والله من خلال تجربتي مع البنك السعودي الفرنسي لا انصح ابدا بشراء مديونية منه اتفقت مع الموظف على اعادة تمويل وكنت في بنك الرياض علي قرض شخصي وعقاري اتفقت مع الموظف بعد ماشاف راتبي والعقار المرهون لبنك الرياض قيمته ٣ مليون  قدروه عمارة ٢٥ شقة المهم موظف البنك الفرنسي</t>
+          <t>احصل على فرصة الفوز بحصة من الجوائز النقدية قيمتها تصل إلى 1,000,000 درهم. كل زيادة بقيمة 100,000 درهم في حسابك المصرفي للأعمال تمنحك فرصة واحدة للدخول في السحب.
+اجعل شركتك إحدى الشركات الـ 55 الفائزة. فهل ستكون من بينها؟ https://t.co/zGFXn2y3iT</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>1776180604000</v>
+        <v>1776274926000</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>1962127907049930843</t>
+          <t>2044471339784810653</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF9r2SlXIAA7IEH.jpg', 'type': 'photo', 'id': '2044471336295145472'}]</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>{'name': 'محمد', 'screenName': 'attas_2010', 'followersCount': 2342, 'favouritesCount': 3675, 'friendsCount': 4836, 'description': 'لا إله إلا الله محمد رسول الله\nتابعني وأتابعك'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="K54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
@@ -4116,18 +4141,14 @@
         <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>142</t>
-        </is>
-      </c>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>1962458003224854945</t>
-        </is>
-      </c>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
@@ -4135,36 +4156,40 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044076340891009154</t>
+          <t>https://x.com/emiratesislamic/status/2044471339784810653</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2044076340891009154</t>
+          <t>2044471339784810653</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2044076340891009154</t>
+          <t>2044471342880170391</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044076340891009154</t>
+          <t>https://x.com/emiratesislamic/status/2044471342880170391</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>@KhalidSaeedR @amsh75 @alrajhibank @BSF_sa @alinma @BankAlbilad @snbalahli @GulfIntlBank @EmiratesNBD_AE @BankAlJazira @RiyadBank @alawwalsab @SAIBLIVE موظف البنك الفرنسي قال نعطيك اعادة تمويل ويطلع لك فائض بالشخصي٧٥٠٠٠ وفعلا تحولت لي والعقاري قال يفيض لك٢٥٥٠٠٠ وسحب علي وماعاد يرد وحتى اليوم فوق ١٠ مرات احاول ارفع شكوى من التطبيق مايقبلون الشكوى 
-اصلا</t>
+          <t>الجائزة النقدية الكبرى: 250,000 درهم (فائز واحد) 
+الجائزة النقدية الثانية: 100,000 درهم (فائزان اثنان)
+الجوائز النقدية الشهرية: تصل إلى 25 ألف درهم (52 فائز)
+يسري العرض لغاية 30 يونيو 2026.
+تطبق الشروط والأحكام.
+https://t.co/RWuJWfhfUm</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>1776180751000</v>
+        <v>1776274927000</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>1962127907049930843</t>
+          <t>2044471339784810653</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -4174,11 +4199,11 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>{'name': 'محمد', 'screenName': 'attas_2010', 'followersCount': 2342, 'favouritesCount': 3675, 'friendsCount': 4836, 'description': 'لا إله إلا الله محمد رسول الله\nتابعني وأتابعك'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="K55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
@@ -4191,12 +4216,12 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>147</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>2044075725334954107</t>
+          <t>2044471339784810653</t>
         </is>
       </c>
     </row>
@@ -4206,45 +4231,47 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044076340891009154</t>
+          <t>https://x.com/emiratesislamic/status/2044471339784810653</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2044076340891009154</t>
+          <t>2044471339784810653</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2044077090039873867</t>
+          <t>2044322412007735394</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044077090039873867</t>
+          <t>https://x.com/emiratesislamic/status/2044322412007735394</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>@KhalidSaeedR @amsh75 @alrajhibank @BSF_sa @alinma @BankAlbilad @snbalahli @GulfIntlBank @EmiratesNBD_AE @BankAlJazira @RiyadBank @alawwalsab @SAIBLIVE وحاليا بعد ماكان عندي قرض عقاري في بنك الرياض راح ارجعه مليون٦٠٠ ألف على ١٥ سنةصرت مديون للبنك الفرنسي مليونين ٣٠٠ ألف والصك مرهون عندهم وكل الي سوه سددو لبنك الرياض مليون ٧٠الف قيمة السداد المبكر فقط والفائض الي وعدني فيه سحب علي ومايرد</t>
+          <t>Invest in gold and silver, easily and digitally with the EI + Mobile Banking App
+⭐️Access the Wealth tab through the EI + Mobile Banking App and start investing securely and seamlessly.
+⭐️Shariah-compliant offering https://t.co/lsN56x6Joc</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>1776180930000</v>
+        <v>1776239419000</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>1962127907049930843</t>
+          <t>2044322412007735394</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF7kZnMXwAAJGag.jpg', 'type': 'photo', 'id': '2044322409541517312'}]</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>{'name': 'محمد', 'screenName': 'attas_2010', 'followersCount': 2342, 'favouritesCount': 3675, 'friendsCount': 4836, 'description': 'لا إله إلا الله محمد رسول الله\nتابعني وأتابعك'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="K56" t="n">
@@ -4257,18 +4284,14 @@
         <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>2044076340891009154</t>
-        </is>
-      </c>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
@@ -4276,52 +4299,51 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044075725334954107</t>
+          <t>https://x.com/emiratesislamic/status/2044471329382900119</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2044075725334954107</t>
+          <t>2044471329382900119</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>1962127907049930843</t>
+          <t>2044471327159996698</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://x.com/amsh75/status/1962127907049930843</t>
+          <t>https://x.com/emiratesislamic/status/2044471327159996698</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>سؤال:
-ماهو افضل بنك يشتري مديونية ؟!
-قرض عقاري + قرض شخصي .
-@alrajhibank @BSF_sa @alinma @BankAlbilad @snbalahli @GulfIntlBank @EmiratesNBD_AE @BankAlJazira @RiyadBank @alawwalsab @SAIBLIVE</t>
+          <t>Get a chance to win a total of AED 1,000,000 in cash prizes! Every AED 100,000 increase in your Business Banking account earns you one entry into the draw.
+55 businesses will be winners. Will you be one of them?
+Grand cash prize: AED 250,000 (1 winner) https://t.co/PtTMEJsQ5k</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>1756642722000</v>
+        <v>1776274923000</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>1962127907049930843</t>
+          <t>2044471327159996698</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF9r1lyXAAANAJs.jpg', 'type': 'photo', 'id': '2044471324270067712'}]</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>{'name': 'علي محمد الضبعان', 'screenName': 'amsh75', 'followersCount': 32674, 'favouritesCount': 2853, 'friendsCount': 6053, 'description': 'حاصل على وسام الملك عبدالعزيز من الدرجة الثالثة/ مدير فرع @Trahum_sa بالمنطقة الشرقية/ عضو لجنة الاسكان التنموي بالمنطقة الشرقية / رئيس مجلس إدارة @tadom_sa'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="K57" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
@@ -4330,11 +4352,11 @@
         <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>2535</t>
+          <t>83</t>
         </is>
       </c>
       <c r="P57" t="inlineStr"/>
@@ -4345,35 +4367,39 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044075725334954107</t>
+          <t>https://x.com/emiratesislamic/status/2044471329382900119</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2044075725334954107</t>
+          <t>2044471329382900119</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>1962458003224854945</t>
+          <t>2044471329382900119</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://x.com/KhalidSaeedR/status/1962458003224854945</t>
+          <t>https://x.com/emiratesislamic/status/2044471329382900119</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>@amsh75 @alrajhibank @BSF_sa @alinma @BankAlbilad @snbalahli @GulfIntlBank @EmiratesNBD_AE @BankAlJazira @RiyadBank @alawwalsab @SAIBLIVE انا ابحث ايضا عن شراء المديونيه قرض عقاري قرض شخصي،،،</t>
+          <t>Second cash prize: AED 100,000 each (2 winners)
+Monthly cash prizes: up to AED 25,000 (52 winners)
+Valid until 30 June 2026.
+Terms and conditions apply.
+https://t.co/FsXr2qXw7K</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>1756721423000</v>
+        <v>1776274924000</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>1962127907049930843</t>
+          <t>2044471327159996698</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4383,11 +4409,11 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>{'name': 'خالد سعيد اليْمِنِي (أبو مشاري)', 'screenName': 'KhalidSaeedR', 'followersCount': 11096, 'favouritesCount': 6906, 'friendsCount': 1130, 'description': 'صحافي ومذيع  تلفزيوني   ومقدم حفلات رسميه،،،\nأخصائي وممارس العلاقات العامه،،'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="K58" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
@@ -4396,16 +4422,16 @@
         <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>1010</t>
+          <t>73</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>1962127907049930843</t>
+          <t>2044471327159996698</t>
         </is>
       </c>
     </row>
@@ -4415,49 +4441,51 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044075725334954107</t>
+          <t>https://x.com/emiratesislamic/status/2044471327159996698</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2044075725334954107</t>
+          <t>2044471327159996698</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2044075725334954107</t>
+          <t>2044471327159996698</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044075725334954107</t>
+          <t>https://x.com/emiratesislamic/status/2044471327159996698</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>@KhalidSaeedR @amsh75 @alrajhibank @BSF_sa @alinma @BankAlbilad @snbalahli @GulfIntlBank @EmiratesNBD_AE @BankAlJazira @RiyadBank @alawwalsab @SAIBLIVE والله من خلال تجربتي مع البنك السعودي الفرنسي لا انصح ابدا بشراء مديونية منه اتفقت مع الموظف على اعادة تمويل وكنت في بنك الرياض علي قرض شخصي وعقاري اتفقت مع الموظف بعد ماشاف راتبي والعقار المرهون لبنك الرياض قيمته ٣ مليون  قدروه عمارة ٢٥ شقة المهم موظف البنك الفرنسي</t>
+          <t>Get a chance to win a total of AED 1,000,000 in cash prizes! Every AED 100,000 increase in your Business Banking account earns you one entry into the draw.
+55 businesses will be winners. Will you be one of them?
+Grand cash prize: AED 250,000 (1 winner) https://t.co/PtTMEJsQ5k</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>1776180604000</v>
+        <v>1776274923000</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>1962127907049930843</t>
+          <t>2044471327159996698</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF9r1lyXAAANAJs.jpg', 'type': 'photo', 'id': '2044471324270067712'}]</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>{'name': 'محمد', 'screenName': 'attas_2010', 'followersCount': 2342, 'favouritesCount': 3675, 'friendsCount': 4836, 'description': 'لا إله إلا الله محمد رسول الله\nتابعني وأتابعك'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="K59" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
@@ -4470,14 +4498,10 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>142</t>
-        </is>
-      </c>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>1962458003224854945</t>
-        </is>
-      </c>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
@@ -4485,36 +4509,39 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044075725334954107</t>
+          <t>https://x.com/emiratesislamic/status/2044471327159996698</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2044075725334954107</t>
+          <t>2044471327159996698</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2044076340891009154</t>
+          <t>2044471329382900119</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044076340891009154</t>
+          <t>https://x.com/emiratesislamic/status/2044471329382900119</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>@KhalidSaeedR @amsh75 @alrajhibank @BSF_sa @alinma @BankAlbilad @snbalahli @GulfIntlBank @EmiratesNBD_AE @BankAlJazira @RiyadBank @alawwalsab @SAIBLIVE موظف البنك الفرنسي قال نعطيك اعادة تمويل ويطلع لك فائض بالشخصي٧٥٠٠٠ وفعلا تحولت لي والعقاري قال يفيض لك٢٥٥٠٠٠ وسحب علي وماعاد يرد وحتى اليوم فوق ١٠ مرات احاول ارفع شكوى من التطبيق مايقبلون الشكوى 
-اصلا</t>
+          <t>Second cash prize: AED 100,000 each (2 winners)
+Monthly cash prizes: up to AED 25,000 (52 winners)
+Valid until 30 June 2026.
+Terms and conditions apply.
+https://t.co/FsXr2qXw7K</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>1776180751000</v>
+        <v>1776274924000</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>1962127907049930843</t>
+          <t>2044471327159996698</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4524,11 +4551,11 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>{'name': 'محمد', 'screenName': 'attas_2010', 'followersCount': 2342, 'favouritesCount': 3675, 'friendsCount': 4836, 'description': 'لا إله إلا الله محمد رسول الله\nتابعني وأتابعك'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="K60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
@@ -4541,12 +4568,12 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>73</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>2044075725334954107</t>
+          <t>2044471327159996698</t>
         </is>
       </c>
     </row>
@@ -4556,47 +4583,46 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044075725334954107</t>
+          <t>https://x.com/emiratesislamic/status/2044471327159996698</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2044075725334954107</t>
+          <t>2044471327159996698</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2044084483222127002</t>
+          <t>2044471339784810653</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>https://x.com/BSF_help/status/2044084483222127002</t>
+          <t>https://x.com/emiratesislamic/status/2044471339784810653</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>عميلنا العزيز ، نود التوضيح بأن منصات التواصل الاجتماعي مخصصة للاستفسارات العامة فقط.
-ولضمان خصوصيتكم وحماية بياناتكم، نرجو عدم مشاركة أي معلومات شخصية أو مصرفية (مثل رقم الهوية، رقم الحساب، كلمة المرور، رقم الجوال أو الأرقام السرية) عبر هذه المنصات.
-يرجى استخدام البريد الإلكتروني أو القنوات الرسمية للبنك لمعالجة الطلبات بأمان وسرية تامة.</t>
+          <t>احصل على فرصة الفوز بحصة من الجوائز النقدية قيمتها تصل إلى 1,000,000 درهم. كل زيادة بقيمة 100,000 درهم في حسابك المصرفي للأعمال تمنحك فرصة واحدة للدخول في السحب.
+اجعل شركتك إحدى الشركات الـ 55 الفائزة. فهل ستكون من بينها؟ https://t.co/zGFXn2y3iT</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>1776182692000</v>
+        <v>1776274926000</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>1962127907049930843</t>
+          <t>2044471339784810653</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF9r2SlXIAA7IEH.jpg', 'type': 'photo', 'id': '2044471336295145472'}]</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>{'name': 'BSF Help', 'screenName': 'BSF_help', 'followersCount': 56031, 'favouritesCount': 1, 'friendsCount': 1, 'description': 'مرحبًا بكم في الحساب الرسمي BSF Help، المصدر المعتمد للإجابة على استفساراتكم المصرفية. تابعوا حسابنا @BSF_sa لمعرفة آخر الأخبار'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="K61" t="n">
@@ -4609,18 +4635,14 @@
         <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="P61" t="inlineStr">
-        <is>
-          <t>2044075725334954107</t>
-        </is>
-      </c>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
@@ -4628,64 +4650,64 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>https://x.com/biztoday_intl/status/2044047297034760542</t>
+          <t>https://x.com/emiratesislamic/status/2044322414310367621</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2044047297034760542</t>
+          <t>2044322414310367621</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2044047297034760542</t>
+          <t>2044322412007735394</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>https://x.com/biztoday_intl/status/2044047297034760542</t>
+          <t>https://x.com/emiratesislamic/status/2044322412007735394</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE and @SobhaRealtyDXB partner to offer integrated home financing solutions for off-plan projects in #Dubai .
-#EmiratesNBD #SobhaRealty #UAE #Dubairealestate #realestate
-https://t.co/ukweMYki3P</t>
+          <t>Invest in gold and silver, easily and digitally with the EI + Mobile Banking App
+⭐️Access the Wealth tab through the EI + Mobile Banking App and start investing securely and seamlessly.
+⭐️Shariah-compliant offering https://t.co/lsN56x6Joc</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>1776173826000</v>
+        <v>1776239419000</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2044047297034760542</t>
+          <t>2044322412007735394</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF7kZnMXwAAJGag.jpg', 'type': 'photo', 'id': '2044322409541517312'}]</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>{'name': 'Biz Today Intl', 'screenName': 'biztoday_intl', 'followersCount': 469, 'favouritesCount': 969, 'friendsCount': 107, 'description': "Biz Today is the World's preeminent 24-hour English language business, economics, technology and finance to travel, fashion and lifestyle publication"}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="K62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
         <v>1</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>204</t>
         </is>
       </c>
       <c r="P62" t="inlineStr"/>
@@ -4696,37 +4718,38 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>https://x.com/biztoday_intl/status/2044047297034760542</t>
+          <t>https://x.com/emiratesislamic/status/2044322414310367621</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2044047297034760542</t>
+          <t>2044322414310367621</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2044060507603382318</t>
+          <t>2044322414310367621</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>https://x.com/biztoday_intl/status/2044060507603382318</t>
+          <t>https://x.com/emiratesislamic/status/2044322414310367621</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>#DaherAircraft strengthens its customer support and distributor Network by adding the Kodiak to Columbia Air’s portfolio.
-@DAHER_official #aircraft #aviation #NicolasChabbert #MelissaDuzguner
-https://t.co/tFtCpJWMU9</t>
+          <t>⭐️Certified gold bars meeting London Bullion Market Association (LBMA) and Dubai Good Delivery (DGD) standards
+⭐️Certified silver bars compliant with UAE Good Delivery (UAE GD) standards
+Terms and conditions apply.
+https://t.co/w5RtLlrqm8</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>1776176976000</v>
+        <v>1776239419000</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2044060507603382318</t>
+          <t>2044322412007735394</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4736,7 +4759,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>{'name': 'Biz Today Intl', 'screenName': 'biztoday_intl', 'followersCount': 469, 'favouritesCount': 969, 'friendsCount': 107, 'description': "Biz Today is the World's preeminent 24-hour English language business, economics, technology and finance to travel, fashion and lifestyle publication"}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="K63" t="n">
@@ -4753,10 +4776,14 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="P63" t="inlineStr"/>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>2044322412007735394</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
@@ -4764,49 +4791,52 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>https://x.com/dcgguide/status/2044025847523487886</t>
+          <t>https://x.com/emiratesislamic/status/2044322401052250291</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2044025847523487886</t>
+          <t>2044322401052250291</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2044025847523487886</t>
+          <t>2044322401052250291</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>https://x.com/dcgguide/status/2044025847523487886</t>
+          <t>https://x.com/emiratesislamic/status/2044322401052250291</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Emirates NBD And Sobha Realty Partner To Offer Integrated Home Financing Solutions For Off-Plan Projects In Dubai https://t.co/fVBST6NQ7A</t>
+          <t>استثمر في الذهب والفضة رقمياً وبكل سهولة على تطبيق
+EI + للخدمات المصرفية عبر الهاتف المتحرك
+⭐️ادخل إلى منصة "الثروات" في تطبيق + EI  للخدمات المصرفية عبر الهاتف المتحرك وابدأ في لاستثمار بمنتهى السهولة والأمان.
+⭐️منتج متوافق مع أحكام الشريعة الإسلامية https://t.co/CZe51naJfQ</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>1776168712000</v>
+        <v>1776239416000</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2044025847523487886</t>
+          <t>2044322401052250291</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF7kY9tWoAAk87F.jpg', 'type': 'photo', 'id': '2044322398405566464'}]</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>{'name': 'DUBAI CITY GUIDE from Cyber Gear', 'screenName': 'dcgguide', 'followersCount': 93486, 'favouritesCount': 19465, 'friendsCount': 106588, 'description': 'DCG is a https://t.co/bmR4jltJAW e-venture. We publish guest posts at https://t.co/EISzXb0O0y Learn AI at https://t.co/YcnxpXcCNU'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
@@ -4815,11 +4845,11 @@
         <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>202</t>
         </is>
       </c>
       <c r="P64" t="inlineStr"/>
@@ -4830,35 +4860,38 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>https://x.com/dcgguide/status/2044025847523487886</t>
+          <t>https://x.com/emiratesislamic/status/2044322401052250291</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2044025847523487886</t>
+          <t>2044322401052250291</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2044038581161996359</t>
+          <t>2044322403761697193</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>https://x.com/dcgguide/status/2044038581161996359</t>
+          <t>https://x.com/emiratesislamic/status/2044322403761697193</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>EWEC Opens Q2 2026 Clean Energy Certificates Auction To Empower Organisations To Lead Global Energy Transition https://t.co/wXSWsOlKcV</t>
+          <t>⭐️سبائك ذهب معتمدة ومطابقة لمعايير جمعية سوق لندن للسبائك ودبي للتسليم الجيد
+⭐️سبائك فضة معتمدة ومتوافقة مع معايير الإمارات للتسليم الجيد
+تطبق الشروط والأحكام.
+https://t.co/WN0tZk19JS</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>1776171748000</v>
+        <v>1776239417000</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2044038581161996359</t>
+          <t>2044322401052250291</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4868,7 +4901,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>{'name': 'DUBAI CITY GUIDE from Cyber Gear', 'screenName': 'dcgguide', 'followersCount': 93486, 'favouritesCount': 19465, 'friendsCount': 106588, 'description': 'DCG is a https://t.co/bmR4jltJAW e-venture. We publish guest posts at https://t.co/EISzXb0O0y Learn AI at https://t.co/YcnxpXcCNU'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="K65" t="n">
@@ -4881,14 +4914,18 @@
         <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="P65" t="inlineStr"/>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>2044322401052250291</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
@@ -4896,51 +4933,52 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>https://x.com/OneVilleNews/status/2044022292972482932</t>
+          <t>https://x.com/emiratesislamic/status/2044322403761697193</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2044022292972482932</t>
+          <t>2044322403761697193</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2044022292972482932</t>
+          <t>2044322401052250291</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>https://x.com/OneVilleNews/status/2044022292972482932</t>
+          <t>https://x.com/emiratesislamic/status/2044322401052250291</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Emirates NBD and Sobha Realty partner to offer integrated home financing solutions for off-plan projects in Dubai 
-#EmiratesNBD #SobhaRealty #Dubai #UAE #Business #Partnership @SobhaRealtyDXB #OneVilleNews
-https://t.co/rQ8bwNlb8E via @onevillenews https://t.co/uuh2N7Ktl1</t>
+          <t>استثمر في الذهب والفضة رقمياً وبكل سهولة على تطبيق
+EI + للخدمات المصرفية عبر الهاتف المتحرك
+⭐️ادخل إلى منصة "الثروات" في تطبيق + EI  للخدمات المصرفية عبر الهاتف المتحرك وابدأ في لاستثمار بمنتهى السهولة والأمان.
+⭐️منتج متوافق مع أحكام الشريعة الإسلامية https://t.co/CZe51naJfQ</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>1776167865000</v>
+        <v>1776239416000</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2044022292972482932</t>
+          <t>2044322401052250291</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF3Tb09bMAAglq0.jpg', 'type': 'photo', 'id': '2044022280922279936'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF7kY9tWoAAk87F.jpg', 'type': 'photo', 'id': '2044322398405566464'}]</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>{'name': 'One Ville News', 'screenName': 'OneVilleNews', 'followersCount': 45, 'favouritesCount': 8, 'friendsCount': 39, 'description': 'All of One Ville, all in one place.'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="K66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
@@ -4949,11 +4987,11 @@
         <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>202</t>
         </is>
       </c>
       <c r="P66" t="inlineStr"/>
@@ -4964,47 +5002,48 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>https://x.com/OneVilleNews/status/2044022292972482932</t>
+          <t>https://x.com/emiratesislamic/status/2044322403761697193</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2044022292972482932</t>
+          <t>2044322403761697193</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2043769833955917928</t>
+          <t>2044322403761697193</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>https://x.com/OneVilleNews/status/2043769833955917928</t>
+          <t>https://x.com/emiratesislamic/status/2044322403761697193</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>“Ya Biladi”… A Song That Feels Like Home, Bringing the UAE’s Spirit to Life 
-#YaBiladi #UAE #Dubai #Song #HussainAlJassmi @7sainaljassmi #محمد_بن_زايد #الامارات_العربية_المتحدة 
-https://t.co/TqZCzfMs1b via @onevillenews https://t.co/lrW3u4M1bq</t>
+          <t>⭐️سبائك ذهب معتمدة ومطابقة لمعايير جمعية سوق لندن للسبائك ودبي للتسليم الجيد
+⭐️سبائك فضة معتمدة ومتوافقة مع معايير الإمارات للتسليم الجيد
+تطبق الشروط والأحكام.
+https://t.co/WN0tZk19JS</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>1776107674000</v>
+        <v>1776239417000</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2043769833955917928</t>
+          <t>2044322401052250291</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HFztt94bcAAnViP.jpg', 'type': 'photo', 'id': '2043769704880500736'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>{'name': 'One Ville News', 'screenName': 'OneVilleNews', 'followersCount': 45, 'favouritesCount': 8, 'friendsCount': 39, 'description': 'All of One Ville, all in one place.'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="K67" t="n">
@@ -5014,17 +5053,21 @@
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>2706</t>
-        </is>
-      </c>
-      <c r="P67" t="inlineStr"/>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>2044322401052250291</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
@@ -5032,45 +5075,47 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>https://x.com/nabilal_rawi/status/2044003893114232972</t>
+          <t>https://x.com/emiratesislamic/status/2044322412007735394</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2044003893114232972</t>
+          <t>2044322412007735394</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2044002065840521609</t>
+          <t>2044322412007735394</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>https://x.com/Zawya/status/2044002065840521609</t>
+          <t>https://x.com/emiratesislamic/status/2044322412007735394</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>While regional tensions are driving higher volatility and risk premiums, the #banking sector in the GCC remains fundamentally sound, with Saudi and UAE institutions still offering upside even under adverse scenarios, according to CI Capital https://t.co/BjQ424Gns3</t>
+          <t>Invest in gold and silver, easily and digitally with the EI + Mobile Banking App
+⭐️Access the Wealth tab through the EI + Mobile Banking App and start investing securely and seamlessly.
+⭐️Shariah-compliant offering https://t.co/lsN56x6Joc</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>1776163042000</v>
+        <v>1776239419000</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2044002065840521609</t>
+          <t>2044322412007735394</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF7kZnMXwAAJGag.jpg', 'type': 'photo', 'id': '2044322409541517312'}]</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>{'name': 'Zawya', 'screenName': 'Zawya', 'followersCount': 26278, 'favouritesCount': 259, 'friendsCount': 94, 'description': 'https://t.co/zY3tN9MLkQ, by @LSEGplc, is a leading source of regional news and intelligence. Retweets are not endorsements.'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="K68" t="n">
@@ -5080,14 +5125,14 @@
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>205</t>
         </is>
       </c>
       <c r="P68" t="inlineStr"/>
@@ -5098,35 +5143,38 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>https://x.com/nabilal_rawi/status/2044003893114232972</t>
+          <t>https://x.com/emiratesislamic/status/2044322412007735394</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2044003893114232972</t>
+          <t>2044322412007735394</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2044003893114232972</t>
+          <t>2044322414310367621</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>https://x.com/nabilal_rawi/status/2044003893114232972</t>
+          <t>https://x.com/emiratesislamic/status/2044322414310367621</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>@Zawya Emirates NBD and ADCB demonstrate the UAE's institutional strength. Free zones and global market access create a financial anchor for entrepreneurs navigating regional volatility.</t>
+          <t>⭐️Certified gold bars meeting London Bullion Market Association (LBMA) and Dubai Good Delivery (DGD) standards
+⭐️Certified silver bars compliant with UAE Good Delivery (UAE GD) standards
+Terms and conditions apply.
+https://t.co/w5RtLlrqm8</t>
         </is>
       </c>
       <c r="G69" t="n">
-        <v>1776163478000</v>
+        <v>1776239419000</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2044002065840521609</t>
+          <t>2044322412007735394</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -5136,7 +5184,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>{'name': 'Nabil Smarter', 'screenName': 'nabilal_rawi', 'followersCount': 30, 'favouritesCount': 16975, 'friendsCount': 335, 'description': 'المستقبل ليس مكاناً نكسبه، بل مكاناً يجب أن نحميه.'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="K69" t="n">
@@ -5153,12 +5201,12 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>142</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>2044002065840521609</t>
+          <t>2044322412007735394</t>
         </is>
       </c>
     </row>
@@ -5168,50 +5216,50 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>https://x.com/GidwaniHero/status/2044143965486948528</t>
+          <t>https://x.com/emiratesislamic/status/2044322412007735394</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2044143965486948528</t>
+          <t>2044322412007735394</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2044143965486948528</t>
+          <t>2044471339784810653</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>https://x.com/GidwaniHero/status/2044143965486948528</t>
+          <t>https://x.com/emiratesislamic/status/2044471339784810653</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>@HHShkMohd @ENBDdeals @FABConnects @MashreqTweets @emiratesislamic 
-Dear uae government what is daily lime to deposit in machine if I have 100k to deposit and machine is slow and behind me standing In Q Are arguing what to do who deposit black money no one question them why</t>
+          <t>احصل على فرصة الفوز بحصة من الجوائز النقدية قيمتها تصل إلى 1,000,000 درهم. كل زيادة بقيمة 100,000 درهم في حسابك المصرفي للأعمال تمنحك فرصة واحدة للدخول في السحب.
+اجعل شركتك إحدى الشركات الـ 55 الفائزة. فهل ستكون من بينها؟ https://t.co/zGFXn2y3iT</t>
         </is>
       </c>
       <c r="G70" t="n">
-        <v>1776196874000</v>
+        <v>1776274926000</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2044143965486948528</t>
+          <t>2044471339784810653</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF9r2SlXIAA7IEH.jpg', 'type': 'photo', 'id': '2044471336295145472'}]</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>{'name': 'Hero Gidwani', 'screenName': 'GidwaniHero', 'followersCount': 19, 'favouritesCount': 24, 'friendsCount': 154, 'description': ''}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="K70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
@@ -5220,11 +5268,11 @@
         <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>148</t>
         </is>
       </c>
       <c r="P70" t="inlineStr"/>
@@ -5235,51 +5283,51 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>https://x.com/ENBDdeals/status/2043984421192077650</t>
+          <t>https://x.com/emiratesislamic/status/2044294656716836969</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2043984421192077650</t>
+          <t>2044294656716836969</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2043984421192077650</t>
+          <t>2044294653097156714</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>https://x.com/ENBDdeals/status/2043984421192077650</t>
+          <t>https://x.com/emiratesislamic/status/2044294653097156714</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Travel more, earn more miles ✈️
-Earn bonus Skywards Miles on Emirates Holidays bookings when you pay with your Emirates NBD card. Offer valid until 30 April 2026. T&amp;amp;Cs apply.
-https://t.co/HWEZythYdM https://t.co/z5yAeQRQdC</t>
+          <t>من “يوماً ما” إلى يوم الانتقال!
+التمويل السكني من الإمارات الإسلامي يجعل حلم امتلاك منزلك حقيقة، مع المرونة والوضوح في كل خطوة من رحلتك.
+استمتع بحلول تمويلية مصممة خصيصاً لك، ودعم متكامل طوال الطريق، لتصبح تجربة امتلاك المنزل سلسة وميسرة.</t>
         </is>
       </c>
       <c r="G71" t="n">
-        <v>1776158836000</v>
+        <v>1776232801000</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2043984421192077650</t>
+          <t>2044294653097156714</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF2w_zAWYAA52Xp.jpg', 'type': 'photo', 'id': '2043984415965995008'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD Deals', 'screenName': 'ENBDdeals', 'followersCount': 39131, 'favouritesCount': 61, 'friendsCount': 4, 'description': 'Welcome to the official account for Emirates NBD Deals. نرحب بكم في الحساب الرسمي لعروض بنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="K71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L71" t="n">
         <v>0</v>
@@ -5288,11 +5336,11 @@
         <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>195</t>
         </is>
       </c>
       <c r="P71" t="inlineStr"/>
@@ -5303,71 +5351,70 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>https://x.com/FirasAlin3va/status/2043855961165623417</t>
+          <t>https://x.com/emiratesislamic/status/2044294656716836969</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2043855961165623417</t>
+          <t>2044294656716836969</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2043039035585700343</t>
+          <t>2044294656716836969</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>https://x.com/RotanaLive/status/2043039035585700343</t>
+          <t>https://x.com/emiratesislamic/status/2044294656716836969</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>ليلة استثنائية حلق فيها صقر الغناء في #موسم_جدة 🦅
-والجمهور ولعها حماس من أول لحظة لآخرها 🔥
-#رابح_صقر
-#روتانا_لايف
-@RabehSaqer 
-@JEDCalendar 
-@EmiratesNBD_KSA https://t.co/2PHoXVNSf7</t>
+          <t>ابدأ رحلتك نحو منزل أحلامك اليوم.
+https://t.co/lQDtk9615Y</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>1775933438000</v>
+        <v>1776232801000</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2043039035585700343</t>
+          <t>2044294653097156714</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2043038860767068160/img/roy7XPjYQBFoKXUJ.jpg', 'type': 'video', 'id': '2043038860767068160'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>{'name': 'Rotana Live', 'screenName': 'RotanaLive', 'followersCount': 193533, 'favouritesCount': 7072, 'friendsCount': 149, 'description': 'روتانا لايف الحساب الرسمي لحفلات روتانا | Rotana events https://t.co/wTAoLH4wPm'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="K72" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L72" t="n">
         <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>8833</t>
-        </is>
-      </c>
-      <c r="P72" t="inlineStr"/>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>2044294653097156714</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
@@ -5375,35 +5422,39 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>https://x.com/FirasAlin3va/status/2043855961165623417</t>
+          <t>https://x.com/emiratesislamic/status/2044294656716836969</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2043855961165623417</t>
+          <t>2044294656716836969</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2043855961165623417</t>
+          <t>2044294659795513346</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>https://x.com/FirasAlin3va/status/2043855961165623417</t>
+          <t>https://x.com/emiratesislamic/status/2044294659795513346</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>@RotanaLive @RabehSaqer @JEDCalendar @EmiratesNBD_KSA أداء ساحر لطيور الغناء في موسم جدة!</t>
+          <t>From “one day” to move-in day.
+Emirates Islamic Home Finance helps turn home ownership into reality, with the flexibility and clarity you need at every step.
+With tailored finance solutions and guided support throughout,
+Your home journey starts here.
+https://t.co/XwkOLamNf0</t>
         </is>
       </c>
       <c r="G73" t="n">
-        <v>1776128208000</v>
+        <v>1776232802000</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2043039035585700343</t>
+          <t>2044294653097156714</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -5413,7 +5464,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>{'name': 'فراس علي', 'screenName': 'FirasAlin3va', 'followersCount': 27, 'favouritesCount': 189, 'friendsCount': 8, 'description': 'أنا لاعب كرة قدم ملتزم وأحب التحدي والتركيز على تطوير مهاراتي دائماً.'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="K73" t="n">
@@ -5430,12 +5481,12 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>120</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>2043039035585700343</t>
+          <t>2044294656716836969</t>
         </is>
       </c>
     </row>
@@ -5445,35 +5496,37 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>https://x.com/ZaharaMMalik/status/2044011613422834071</t>
+          <t>https://x.com/emiratesislamic/status/2044294653097156714</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2044011613422834071</t>
+          <t>2044294653097156714</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2044011613422834071</t>
+          <t>2044294653097156714</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>https://x.com/ZaharaMMalik/status/2044011613422834071</t>
+          <t>https://x.com/emiratesislamic/status/2044294653097156714</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Really struggling to get hold of @emiratesislamic I’ve called the international line and emailed and really need to get hold of someone. Please help 😭</t>
+          <t>من “يوماً ما” إلى يوم الانتقال!
+التمويل السكني من الإمارات الإسلامي يجعل حلم امتلاك منزلك حقيقة، مع المرونة والوضوح في كل خطوة من رحلتك.
+استمتع بحلول تمويلية مصممة خصيصاً لك، ودعم متكامل طوال الطريق، لتصبح تجربة امتلاك المنزل سلسة وميسرة.</t>
         </is>
       </c>
       <c r="G74" t="n">
-        <v>1776165319000</v>
+        <v>1776232801000</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2044011613422834071</t>
+          <t>2044294653097156714</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -5483,7 +5536,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>{'name': 'Zahara Sadiq', 'screenName': 'ZaharaMMalik', 'followersCount': 741, 'favouritesCount': 827, 'friendsCount': 564, 'description': 'Impact Investing | Entrepreneur | Driven by Building Bridges Globally | Serial Tea Drinker | Part Time Wisdom Coach'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="K74" t="n">
@@ -5496,11 +5549,11 @@
         <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>195</t>
         </is>
       </c>
       <c r="P74" t="inlineStr"/>
@@ -5511,35 +5564,36 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>https://x.com/ZaharaMMalik/status/2044011613422834071</t>
+          <t>https://x.com/emiratesislamic/status/2044294653097156714</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2044011613422834071</t>
+          <t>2044294653097156714</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2044023053797953761</t>
+          <t>2044294656716836969</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2044023053797953761</t>
+          <t>https://x.com/emiratesislamic/status/2044294656716836969</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>@ZaharaMMalik Dear Zahara,we have tried to reach you through the direct Message, unfortunately we were not successful due to the direct message (Not Following our page). Please DM us back in order to assist you better.</t>
+          <t>ابدأ رحلتك نحو منزل أحلامك اليوم.
+https://t.co/lQDtk9615Y</t>
         </is>
       </c>
       <c r="G75" t="n">
-        <v>1776168046000</v>
+        <v>1776232801000</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2044011613422834071</t>
+          <t>2044294653097156714</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5553,7 +5607,7 @@
         </is>
       </c>
       <c r="K75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L75" t="n">
         <v>0</v>
@@ -5566,12 +5620,12 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>127</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>2044011613422834071</t>
+          <t>2044294653097156714</t>
         </is>
       </c>
     </row>
@@ -5581,45 +5635,46 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>https://x.com/aswanikumartst5/status/2043951228640747823</t>
+          <t>https://x.com/emiratesislamic/status/2044294653097156714</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2043951228640747823</t>
+          <t>2044294653097156714</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2042145058133307907</t>
+          <t>2044471339784810653</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>https://x.com/aswanikumartst5/status/2042145058133307907</t>
+          <t>https://x.com/emiratesislamic/status/2044471339784810653</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>@emiratesislamic I have already cleared a personal loan and approached your Phone Banking &amp;amp; WhatsApp channel for issue of NIL LIABILITY LETTER..but no concrete response .Not feasible to obtain through your application as well.Can u please check&amp;amp; revert ASAP. Thank You.</t>
+          <t>احصل على فرصة الفوز بحصة من الجوائز النقدية قيمتها تصل إلى 1,000,000 درهم. كل زيادة بقيمة 100,000 درهم في حسابك المصرفي للأعمال تمنحك فرصة واحدة للدخول في السحب.
+اجعل شركتك إحدى الشركات الـ 55 الفائزة. فهل ستكون من بينها؟ https://t.co/zGFXn2y3iT</t>
         </is>
       </c>
       <c r="G76" t="n">
-        <v>1775720297000</v>
+        <v>1776274926000</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2042145058133307907</t>
+          <t>2044471339784810653</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF9r2SlXIAA7IEH.jpg', 'type': 'photo', 'id': '2044471336295145472'}]</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>{'name': 'TS Aswani Kumar', 'screenName': 'aswanikumartst5', 'followersCount': 10, 'favouritesCount': 181, 'friendsCount': 25, 'description': ''}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="K76" t="n">
@@ -5632,1813 +5687,14 @@
         <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>148</t>
         </is>
       </c>
       <c r="P76" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="1" t="n">
-        <v>75</v>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>https://x.com/aswanikumartst5/status/2043951228640747823</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>2043951228640747823</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>2042152553400385940</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2042152553400385940</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>@aswanikumartst5 Dear customer, we will connect with you on private messaging to serve you better</t>
-        </is>
-      </c>
-      <c r="G77" t="n">
-        <v>1775722084000</v>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>2042145058133307907</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="K77" t="n">
-        <v>1</v>
-      </c>
-      <c r="L77" t="n">
-        <v>0</v>
-      </c>
-      <c r="M77" t="n">
-        <v>0</v>
-      </c>
-      <c r="N77" t="n">
-        <v>0</v>
-      </c>
-      <c r="O77" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="P77" t="inlineStr">
-        <is>
-          <t>2042145058133307907</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="1" t="n">
-        <v>76</v>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>https://x.com/aswanikumartst5/status/2043951228640747823</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>2043951228640747823</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>2042853514049917277</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>https://x.com/aswanikumartst5/status/2042853514049917277</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>@emiratesislamic So far nobody has contacted me in connection with this query nor any mail from your end .</t>
-        </is>
-      </c>
-      <c r="G78" t="n">
-        <v>1775889206000</v>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>2042145058133307907</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>{'name': 'TS Aswani Kumar', 'screenName': 'aswanikumartst5', 'followersCount': 10, 'favouritesCount': 181, 'friendsCount': 25, 'description': ''}</t>
-        </is>
-      </c>
-      <c r="K78" t="n">
-        <v>1</v>
-      </c>
-      <c r="L78" t="n">
-        <v>0</v>
-      </c>
-      <c r="M78" t="n">
-        <v>0</v>
-      </c>
-      <c r="N78" t="n">
-        <v>0</v>
-      </c>
-      <c r="O78" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="P78" t="inlineStr">
-        <is>
-          <t>2042152553400385940</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="1" t="n">
-        <v>77</v>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>https://x.com/aswanikumartst5/status/2043951228640747823</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>2043951228640747823</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>2043560931511189651</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2043560931511189651</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>@aswanikumartst5 Dear customer, we will connect with you on private messaging to serve you better.</t>
-        </is>
-      </c>
-      <c r="G79" t="n">
-        <v>1776057868000</v>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>2042145058133307907</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="K79" t="n">
-        <v>1</v>
-      </c>
-      <c r="L79" t="n">
-        <v>0</v>
-      </c>
-      <c r="M79" t="n">
-        <v>0</v>
-      </c>
-      <c r="N79" t="n">
-        <v>0</v>
-      </c>
-      <c r="O79" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="P79" t="inlineStr">
-        <is>
-          <t>2042853514049917277</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="1" t="n">
-        <v>78</v>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>https://x.com/aswanikumartst5/status/2043951228640747823</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>2043951228640747823</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>2043951228640747823</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>https://x.com/aswanikumartst5/status/2043951228640747823</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>@emiratesislamic How many days more you require to issue a NIL LIABILITY LETTER...?</t>
-        </is>
-      </c>
-      <c r="G80" t="n">
-        <v>1776150922000</v>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>2042145058133307907</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>{'name': 'TS Aswani Kumar', 'screenName': 'aswanikumartst5', 'followersCount': 10, 'favouritesCount': 181, 'friendsCount': 25, 'description': ''}</t>
-        </is>
-      </c>
-      <c r="K80" t="n">
-        <v>1</v>
-      </c>
-      <c r="L80" t="n">
-        <v>0</v>
-      </c>
-      <c r="M80" t="n">
-        <v>0</v>
-      </c>
-      <c r="N80" t="n">
-        <v>0</v>
-      </c>
-      <c r="O80" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="P80" t="inlineStr">
-        <is>
-          <t>2043560931511189651</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="1" t="n">
-        <v>79</v>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>https://x.com/aswanikumartst5/status/2043951228640747823</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>2043951228640747823</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>2043955058459467807</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2043955058459467807</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>@aswanikumartst5 Dear customer, we will connect with you on private messaging to serve you better.</t>
-        </is>
-      </c>
-      <c r="G81" t="n">
-        <v>1776151835000</v>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>2042145058133307907</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="K81" t="n">
-        <v>0</v>
-      </c>
-      <c r="L81" t="n">
-        <v>0</v>
-      </c>
-      <c r="M81" t="n">
-        <v>0</v>
-      </c>
-      <c r="N81" t="n">
-        <v>0</v>
-      </c>
-      <c r="O81" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="P81" t="inlineStr">
-        <is>
-          <t>2043951228640747823</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="1" t="n">
-        <v>80</v>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2043932263390310621</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>2043932263390310621</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>2043932263390310621</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2043932263390310621</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>How do you usually pay for your expenses?
-#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic
-https://t.co/XvyZgR87nM</t>
-        </is>
-      </c>
-      <c r="G82" t="n">
-        <v>1776146400000</v>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>2043932263390310621</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="K82" t="n">
-        <v>0</v>
-      </c>
-      <c r="L82" t="n">
-        <v>0</v>
-      </c>
-      <c r="M82" t="n">
-        <v>0</v>
-      </c>
-      <c r="N82" t="n">
-        <v>0</v>
-      </c>
-      <c r="O82" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="P82" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="1" t="n">
-        <v>81</v>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2043932263390310621</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>2043932263390310621</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>2043932263725854816</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2043932263725854816</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>Money grows best when given time, balance, and the right mix.
-Spreading investments and thinking long term can help create steadier progress along the way.
-Small steps today can support stronger outcomes tomorrow.</t>
-        </is>
-      </c>
-      <c r="G83" t="n">
-        <v>1776146400000</v>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>2043932263725854816</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="K83" t="n">
-        <v>1</v>
-      </c>
-      <c r="L83" t="n">
-        <v>0</v>
-      </c>
-      <c r="M83" t="n">
-        <v>0</v>
-      </c>
-      <c r="N83" t="n">
-        <v>0</v>
-      </c>
-      <c r="O83" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="P83" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="1" t="n">
-        <v>82</v>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2044023053797953761</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>2044023053797953761</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>2044011613422834071</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>https://x.com/ZaharaMMalik/status/2044011613422834071</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>Really struggling to get hold of @emiratesislamic I’ve called the international line and emailed and really need to get hold of someone. Please help 😭</t>
-        </is>
-      </c>
-      <c r="G84" t="n">
-        <v>1776165319000</v>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>2044011613422834071</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>{'name': 'Zahara Sadiq', 'screenName': 'ZaharaMMalik', 'followersCount': 741, 'favouritesCount': 827, 'friendsCount': 564, 'description': 'Impact Investing | Entrepreneur | Driven by Building Bridges Globally | Serial Tea Drinker | Part Time Wisdom Coach'}</t>
-        </is>
-      </c>
-      <c r="K84" t="n">
-        <v>1</v>
-      </c>
-      <c r="L84" t="n">
-        <v>0</v>
-      </c>
-      <c r="M84" t="n">
-        <v>0</v>
-      </c>
-      <c r="N84" t="n">
-        <v>1</v>
-      </c>
-      <c r="O84" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="P84" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="1" t="n">
-        <v>83</v>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2044023053797953761</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>2044023053797953761</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>2044023053797953761</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2044023053797953761</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>@ZaharaMMalik Dear Zahara,we have tried to reach you through the direct Message, unfortunately we were not successful due to the direct message (Not Following our page). Please DM us back in order to assist you better.</t>
-        </is>
-      </c>
-      <c r="G85" t="n">
-        <v>1776168046000</v>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>2044011613422834071</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="K85" t="n">
-        <v>0</v>
-      </c>
-      <c r="L85" t="n">
-        <v>0</v>
-      </c>
-      <c r="M85" t="n">
-        <v>0</v>
-      </c>
-      <c r="N85" t="n">
-        <v>0</v>
-      </c>
-      <c r="O85" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="P85" t="inlineStr">
-        <is>
-          <t>2044011613422834071</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="1" t="n">
-        <v>84</v>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2043917165502316982</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>2043917165502316982</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>2043917165502316982</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2043917165502316982</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>نظرتك الأسبوعية… لحياة أكثر وعياً واتزاناً مالياً.
-#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
-Your Weekly Perspective. A step toward a more mindful financial week.
-#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic https://t.co/48pYcSntb5</t>
-        </is>
-      </c>
-      <c r="G86" t="n">
-        <v>1776142801000</v>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>2043917165502316982</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HFw707XWcAAVI5E.jpg', 'type': 'photo', 'id': '2043574111394230272'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HFw71ETXwAAPour.jpg', 'type': 'photo', 'id': '2043574113793458176'}]</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="K86" t="n">
-        <v>0</v>
-      </c>
-      <c r="L86" t="n">
-        <v>0</v>
-      </c>
-      <c r="M86" t="n">
-        <v>0</v>
-      </c>
-      <c r="N86" t="n">
-        <v>0</v>
-      </c>
-      <c r="O86" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="P86" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="1" t="n">
-        <v>85</v>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2043917165502316982</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>2043917165502316982</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>2043932263386157239</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2043932263386157239</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>ينمو المال بشكل أفضل مع الوقت، والتوازن، والتنوّع المناسب.
-تنويع الاستثمارات والتفكير على المدى الطويل يساعدان على تحقيق استقرار أكبر.
-خطوات صغيرة اليوم قد تصنع نتائج أقوى في المستقبل.
-للمزيد: 
-https://t.co/mgtIcQsyLZ https://t.co/Eh7yupmtiG</t>
-        </is>
-      </c>
-      <c r="G87" t="n">
-        <v>1776146400000</v>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>2043932263386157239</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/ext_tw_video_thumb/2043692933543550976/pu/img/DwmJr4WPQRT9Ka0q.jpg', 'type': 'video', 'id': '2043692933543550976'}]</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="K87" t="n">
-        <v>0</v>
-      </c>
-      <c r="L87" t="n">
-        <v>0</v>
-      </c>
-      <c r="M87" t="n">
-        <v>0</v>
-      </c>
-      <c r="N87" t="n">
-        <v>0</v>
-      </c>
-      <c r="O87" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="P87" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="1" t="n">
-        <v>86</v>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2043955058459467807</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>2043955058459467807</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>2042145058133307907</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>https://x.com/aswanikumartst5/status/2042145058133307907</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>@emiratesislamic I have already cleared a personal loan and approached your Phone Banking &amp;amp; WhatsApp channel for issue of NIL LIABILITY LETTER..but no concrete response .Not feasible to obtain through your application as well.Can u please check&amp;amp; revert ASAP. Thank You.</t>
-        </is>
-      </c>
-      <c r="G88" t="n">
-        <v>1775720297000</v>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>2042145058133307907</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>{'name': 'TS Aswani Kumar', 'screenName': 'aswanikumartst5', 'followersCount': 10, 'favouritesCount': 181, 'friendsCount': 25, 'description': ''}</t>
-        </is>
-      </c>
-      <c r="K88" t="n">
-        <v>1</v>
-      </c>
-      <c r="L88" t="n">
-        <v>0</v>
-      </c>
-      <c r="M88" t="n">
-        <v>0</v>
-      </c>
-      <c r="N88" t="n">
-        <v>0</v>
-      </c>
-      <c r="O88" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="P88" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="1" t="n">
-        <v>87</v>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2043955058459467807</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>2043955058459467807</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>2042152553400385940</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2042152553400385940</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>@aswanikumartst5 Dear customer, we will connect with you on private messaging to serve you better</t>
-        </is>
-      </c>
-      <c r="G89" t="n">
-        <v>1775722084000</v>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>2042145058133307907</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="K89" t="n">
-        <v>1</v>
-      </c>
-      <c r="L89" t="n">
-        <v>0</v>
-      </c>
-      <c r="M89" t="n">
-        <v>0</v>
-      </c>
-      <c r="N89" t="n">
-        <v>0</v>
-      </c>
-      <c r="O89" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="P89" t="inlineStr">
-        <is>
-          <t>2042145058133307907</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="1" t="n">
-        <v>88</v>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2043955058459467807</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>2043955058459467807</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>2042853514049917277</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>https://x.com/aswanikumartst5/status/2042853514049917277</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>@emiratesislamic So far nobody has contacted me in connection with this query nor any mail from your end .</t>
-        </is>
-      </c>
-      <c r="G90" t="n">
-        <v>1775889206000</v>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>2042145058133307907</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>{'name': 'TS Aswani Kumar', 'screenName': 'aswanikumartst5', 'followersCount': 10, 'favouritesCount': 181, 'friendsCount': 25, 'description': ''}</t>
-        </is>
-      </c>
-      <c r="K90" t="n">
-        <v>1</v>
-      </c>
-      <c r="L90" t="n">
-        <v>0</v>
-      </c>
-      <c r="M90" t="n">
-        <v>0</v>
-      </c>
-      <c r="N90" t="n">
-        <v>0</v>
-      </c>
-      <c r="O90" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="P90" t="inlineStr">
-        <is>
-          <t>2042152553400385940</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="1" t="n">
-        <v>89</v>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2043955058459467807</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>2043955058459467807</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>2043560931511189651</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2043560931511189651</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>@aswanikumartst5 Dear customer, we will connect with you on private messaging to serve you better.</t>
-        </is>
-      </c>
-      <c r="G91" t="n">
-        <v>1776057868000</v>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>2042145058133307907</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="K91" t="n">
-        <v>1</v>
-      </c>
-      <c r="L91" t="n">
-        <v>0</v>
-      </c>
-      <c r="M91" t="n">
-        <v>0</v>
-      </c>
-      <c r="N91" t="n">
-        <v>0</v>
-      </c>
-      <c r="O91" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="P91" t="inlineStr">
-        <is>
-          <t>2042853514049917277</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="1" t="n">
-        <v>90</v>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2043955058459467807</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>2043955058459467807</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>2043951228640747823</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>https://x.com/aswanikumartst5/status/2043951228640747823</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>@emiratesislamic How many days more you require to issue a NIL LIABILITY LETTER...?</t>
-        </is>
-      </c>
-      <c r="G92" t="n">
-        <v>1776150922000</v>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>2042145058133307907</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>{'name': 'TS Aswani Kumar', 'screenName': 'aswanikumartst5', 'followersCount': 10, 'favouritesCount': 181, 'friendsCount': 25, 'description': ''}</t>
-        </is>
-      </c>
-      <c r="K92" t="n">
-        <v>1</v>
-      </c>
-      <c r="L92" t="n">
-        <v>0</v>
-      </c>
-      <c r="M92" t="n">
-        <v>0</v>
-      </c>
-      <c r="N92" t="n">
-        <v>0</v>
-      </c>
-      <c r="O92" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="P92" t="inlineStr">
-        <is>
-          <t>2043560931511189651</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="1" t="n">
-        <v>91</v>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2043955058459467807</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>2043955058459467807</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>2043955058459467807</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2043955058459467807</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>@aswanikumartst5 Dear customer, we will connect with you on private messaging to serve you better.</t>
-        </is>
-      </c>
-      <c r="G93" t="n">
-        <v>1776151835000</v>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>2042145058133307907</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="K93" t="n">
-        <v>0</v>
-      </c>
-      <c r="L93" t="n">
-        <v>0</v>
-      </c>
-      <c r="M93" t="n">
-        <v>0</v>
-      </c>
-      <c r="N93" t="n">
-        <v>0</v>
-      </c>
-      <c r="O93" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="P93" t="inlineStr">
-        <is>
-          <t>2043951228640747823</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="1" t="n">
-        <v>92</v>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2043932266456367150</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>2043932266456367150</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>2043932263725854816</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2043932263725854816</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>Money grows best when given time, balance, and the right mix.
-Spreading investments and thinking long term can help create steadier progress along the way.
-Small steps today can support stronger outcomes tomorrow.</t>
-        </is>
-      </c>
-      <c r="G94" t="n">
-        <v>1776146400000</v>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>2043932263725854816</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="K94" t="n">
-        <v>1</v>
-      </c>
-      <c r="L94" t="n">
-        <v>0</v>
-      </c>
-      <c r="M94" t="n">
-        <v>0</v>
-      </c>
-      <c r="N94" t="n">
-        <v>0</v>
-      </c>
-      <c r="O94" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="P94" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="1" t="n">
-        <v>93</v>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2043932266456367150</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>2043932266456367150</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>2043932266456367150</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2043932266456367150</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>To know more:
-https://t.co/XvyZgR87nM</t>
-        </is>
-      </c>
-      <c r="G95" t="n">
-        <v>1776146401000</v>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>2043932263725854816</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="K95" t="n">
-        <v>0</v>
-      </c>
-      <c r="L95" t="n">
-        <v>0</v>
-      </c>
-      <c r="M95" t="n">
-        <v>0</v>
-      </c>
-      <c r="N95" t="n">
-        <v>0</v>
-      </c>
-      <c r="O95" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="P95" t="inlineStr">
-        <is>
-          <t>2043932263725854816</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="1" t="n">
-        <v>94</v>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2043932263386157239</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>2043932263386157239</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>2043932263386157239</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2043932263386157239</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>ينمو المال بشكل أفضل مع الوقت، والتوازن، والتنوّع المناسب.
-تنويع الاستثمارات والتفكير على المدى الطويل يساعدان على تحقيق استقرار أكبر.
-خطوات صغيرة اليوم قد تصنع نتائج أقوى في المستقبل.
-للمزيد: 
-https://t.co/mgtIcQsyLZ https://t.co/Eh7yupmtiG</t>
-        </is>
-      </c>
-      <c r="G96" t="n">
-        <v>1776146400000</v>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>2043932263386157239</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/ext_tw_video_thumb/2043692933543550976/pu/img/DwmJr4WPQRT9Ka0q.jpg', 'type': 'video', 'id': '2043692933543550976'}]</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="K96" t="n">
-        <v>0</v>
-      </c>
-      <c r="L96" t="n">
-        <v>0</v>
-      </c>
-      <c r="M96" t="n">
-        <v>0</v>
-      </c>
-      <c r="N96" t="n">
-        <v>0</v>
-      </c>
-      <c r="O96" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="P96" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="1" t="n">
-        <v>95</v>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2043932263386157239</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>2043932263386157239</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>2043932263449006494</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2043932263449006494</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>كيف تدفع نفقاتك عادةً؟
-#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
-https://t.co/mgtIcQsyLZ</t>
-        </is>
-      </c>
-      <c r="G97" t="n">
-        <v>1776146400000</v>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>2043932263449006494</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="K97" t="n">
-        <v>0</v>
-      </c>
-      <c r="L97" t="n">
-        <v>0</v>
-      </c>
-      <c r="M97" t="n">
-        <v>0</v>
-      </c>
-      <c r="N97" t="n">
-        <v>0</v>
-      </c>
-      <c r="O97" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="P97" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="1" t="n">
-        <v>96</v>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2043932263449006494</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>2043932263449006494</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>2043932263449006494</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2043932263449006494</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>كيف تدفع نفقاتك عادةً؟
-#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
-https://t.co/mgtIcQsyLZ</t>
-        </is>
-      </c>
-      <c r="G98" t="n">
-        <v>1776146400000</v>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>2043932263449006494</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="K98" t="n">
-        <v>0</v>
-      </c>
-      <c r="L98" t="n">
-        <v>0</v>
-      </c>
-      <c r="M98" t="n">
-        <v>0</v>
-      </c>
-      <c r="N98" t="n">
-        <v>0</v>
-      </c>
-      <c r="O98" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="P98" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="1" t="n">
-        <v>97</v>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2043932263449006494</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>2043932263449006494</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>2043932263725854816</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2043932263725854816</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>Money grows best when given time, balance, and the right mix.
-Spreading investments and thinking long term can help create steadier progress along the way.
-Small steps today can support stronger outcomes tomorrow.</t>
-        </is>
-      </c>
-      <c r="G99" t="n">
-        <v>1776146400000</v>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>2043932263725854816</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="K99" t="n">
-        <v>1</v>
-      </c>
-      <c r="L99" t="n">
-        <v>0</v>
-      </c>
-      <c r="M99" t="n">
-        <v>0</v>
-      </c>
-      <c r="N99" t="n">
-        <v>0</v>
-      </c>
-      <c r="O99" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="P99" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="1" t="n">
-        <v>98</v>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2043932263725854816</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>2043932263725854816</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>2043932263725854816</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2043932263725854816</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>Money grows best when given time, balance, and the right mix.
-Spreading investments and thinking long term can help create steadier progress along the way.
-Small steps today can support stronger outcomes tomorrow.</t>
-        </is>
-      </c>
-      <c r="G100" t="n">
-        <v>1776146400000</v>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>2043932263725854816</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="K100" t="n">
-        <v>1</v>
-      </c>
-      <c r="L100" t="n">
-        <v>0</v>
-      </c>
-      <c r="M100" t="n">
-        <v>0</v>
-      </c>
-      <c r="N100" t="n">
-        <v>0</v>
-      </c>
-      <c r="O100" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="P100" t="inlineStr"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="1" t="n">
-        <v>99</v>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2043932263725854816</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>2043932263725854816</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>2043932266456367150</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2043932266456367150</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>To know more:
-https://t.co/XvyZgR87nM</t>
-        </is>
-      </c>
-      <c r="G101" t="n">
-        <v>1776146401000</v>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>2043932263725854816</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="K101" t="n">
-        <v>0</v>
-      </c>
-      <c r="L101" t="n">
-        <v>0</v>
-      </c>
-      <c r="M101" t="n">
-        <v>0</v>
-      </c>
-      <c r="N101" t="n">
-        <v>0</v>
-      </c>
-      <c r="O101" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="P101" t="inlineStr">
-        <is>
-          <t>2043932263725854816</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2043932263725854816</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>2043932263725854816</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>2043932263386157239</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2043932263386157239</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>ينمو المال بشكل أفضل مع الوقت، والتوازن، والتنوّع المناسب.
-تنويع الاستثمارات والتفكير على المدى الطويل يساعدان على تحقيق استقرار أكبر.
-خطوات صغيرة اليوم قد تصنع نتائج أقوى في المستقبل.
-للمزيد: 
-https://t.co/mgtIcQsyLZ https://t.co/Eh7yupmtiG</t>
-        </is>
-      </c>
-      <c r="G102" t="n">
-        <v>1776146400000</v>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>2043932263386157239</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/ext_tw_video_thumb/2043692933543550976/pu/img/DwmJr4WPQRT9Ka0q.jpg', 'type': 'video', 'id': '2043692933543550976'}]</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="K102" t="n">
-        <v>0</v>
-      </c>
-      <c r="L102" t="n">
-        <v>0</v>
-      </c>
-      <c r="M102" t="n">
-        <v>0</v>
-      </c>
-      <c r="N102" t="n">
-        <v>0</v>
-      </c>
-      <c r="O102" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="P102" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Xpost_df_comments.xlsx
+++ b/Xpost_df_comments.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P76"/>
+  <dimension ref="A1:P128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,62 +511,69 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://x.com/DustshotW/status/2044612515498496366</t>
+          <t>https://x.com/Anakbrv_/status/2044884248746705270</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2044612515498496366</t>
+          <t>2044884248746705270</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2044517451078197394</t>
+          <t>2044528693268074976</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://x.com/DustshotW/status/2044517451078197394</t>
+          <t>https://x.com/iFood/status/2044528693268074976</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>anyone.....olease ......</t>
+          <t>Quer ganhar R$5 MIL no iFood? ✨
+As regras são simples: 
+1.⁠ ⁠dê RT nesse tweet.
+2.⁠ ⁠comente MUITO com as tags #iFoodNoBBB26 e #BBB26 respondendo este tweet.
+O @ com MAIS COMENTÁRIOS neste post é o ganhador!
+Bora? Valendooo! Amanhã já teremos o campeão
+Consulte regulamento na bio.
+Comentários válidos até 16/04/2026 às 18:30</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1776285920000</v>
+        <v>1776288600000</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2044517451078197394</t>
+          <t>2044528693268074976</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF-aj8zbsAAPd23.jpg', 'type': 'photo', 'id': '2044522698257444864'}]</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>{'name': 'justice gaming', 'screenName': 'DustshotW', 'followersCount': 1065, 'favouritesCount': 25613, 'friendsCount': 229, 'description': 'call me justice or 正凱 // 中文/English // 🇭🇰// i do like nothing but draw yuri\n\nhttps://t.co/wisNUqvSX2'}</t>
+          <t>{'name': 'iFood', 'screenName': 'iFood', 'followersCount': 355139, 'favouritesCount': 27799, 'friendsCount': 9398, 'description': '100 dias de oferta para quem manja de BBB: Brasileiro, Bom e Barato ❤️ #iFoodNoBBB26'}</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>5</v>
+        <v>56138</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="N2" t="n">
-        <v>10</v>
+        <v>62</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>309</t>
+          <t>12064</t>
         </is>
       </c>
       <c r="P2" t="inlineStr"/>
@@ -577,35 +584,36 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://x.com/DustshotW/status/2044612515498496366</t>
+          <t>https://x.com/Anakbrv_/status/2044884248746705270</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2044612515498496366</t>
+          <t>2044884248746705270</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2044610910640361699</t>
+          <t>2044884248746705270</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://x.com/dorienotfish/status/2044610910640361699</t>
+          <t>https://x.com/Anakbrv_/status/2044884248746705270</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>@DustshotW can i try</t>
+          <t>@iFood Comprar tudo que eu quero sem me preocupar com p preço  
+#iFoodNoBBB26 #BBB26  hehe enbd dh</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1776308202000</v>
+        <v>1776373371000</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2044517451078197394</t>
+          <t>2044528693268074976</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -615,11 +623,11 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>{'name': 'dorion', 'screenName': 'dorienotfish', 'followersCount': 68, 'favouritesCount': 39809, 'friendsCount': 522, 'description': 'steine sind steine ohne rotes blut'}</t>
+          <t>{'name': 'Ana que ainda não superou o cancelamento de JATP', 'screenName': 'Anakbrv_', 'followersCount': 319, 'favouritesCount': 63841, 'friendsCount': 711, 'description': 'Órfã de Julie and the phantoms'}</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -632,12 +640,12 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>24</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2044517451078197394</t>
+          <t>2044528693268074976</t>
         </is>
       </c>
     </row>
@@ -647,35 +655,36 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://x.com/DustshotW/status/2044612515498496366</t>
+          <t>https://x.com/Kyodonews_JBN/status/2044955402941673971</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2044612515498496366</t>
+          <t>2044955402941673971</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2044612515498496366</t>
+          <t>2044955402941673971</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://x.com/DustshotW/status/2044612515498496366</t>
+          <t>https://x.com/Kyodonews_JBN/status/2044955402941673971</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>@dorienotfish s enbd</t>
+          <t>Emirates NBD successfully executes USD 250 Million Syndicated Term Loan facility for Dar Global, Accelerating Global Growth and Expansion【Dar Global】
+https://t.co/ILzW7B8sby</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1776308585000</v>
+        <v>1776390336000</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2044517451078197394</t>
+          <t>2044955402941673971</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -685,11 +694,11 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>{'name': 'justice gaming', 'screenName': 'DustshotW', 'followersCount': 1065, 'favouritesCount': 25613, 'friendsCount': 229, 'description': 'call me justice or 正凱 // 中文/English // 🇭🇰// i do like nothing but draw yuri\n\nhttps://t.co/wisNUqvSX2'}</t>
+          <t>{'name': 'KYODONEWS JBN', 'screenName': 'Kyodonews_JBN', 'followersCount': 18, 'favouritesCount': 5, 'friendsCount': 2, 'description': '株式会社共同通信社 ジャパンビジネス広報センター'}</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -702,14 +711,10 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2044610910640361699</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -717,69 +722,66 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://x.com/DustshotW/status/2044612515498496366</t>
+          <t>https://x.com/Kyodonews_JBN/status/2044955402941673971</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2044612515498496366</t>
+          <t>2044955402941673971</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2044613234427383893</t>
+          <t>2044967082945888595</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://x.com/dorienotfish/status/2044613234427383893</t>
+          <t>https://x.com/Kyodonews_JBN/status/2044967082945888595</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>@DustshotW sorry at first i though u said 'skibdi' mb✌🏻✌🏻✌🏻 ok here https://t.co/DsboMnkCKn</t>
+          <t>Cainiao、ラッククライミング式ロボット「ZeeBot」を発表 保管・出庫の生産性が最大100％向上【Cainiao】
+https://t.co/luFsWSpvPE</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1776308756000</v>
+        <v>1776393120000</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2044517451078197394</t>
+          <t>2044967082945888595</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF_s4_pbAAANiPL.jpg', 'type': 'photo', 'id': '2044613219751493632'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>{'name': 'dorion', 'screenName': 'dorienotfish', 'followersCount': 68, 'favouritesCount': 39809, 'friendsCount': 522, 'description': 'steine sind steine ohne rotes blut'}</t>
+          <t>{'name': 'KYODONEWS JBN', 'screenName': 'Kyodonews_JBN', 'followersCount': 18, 'favouritesCount': 5, 'friendsCount': 2, 'description': '株式会社共同通信社 ジャパンビジネス広報センター'}</t>
         </is>
       </c>
       <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
         <v>1</v>
       </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2044612515498496366</t>
-        </is>
-      </c>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -787,52 +789,47 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>https://x.com/BehindNums/status/2044611289733878057</t>
+          <t>https://x.com/F44195Faleh/status/2044915426291826845</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2044611289733878057</t>
+          <t>2044915426291826845</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2044611289733878057</t>
+          <t>2044743177412722931</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://x.com/BehindNums/status/2044611289733878057</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2044743177412722931</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Top 5 Richest Companies in the Middle East 
-1️⃣ Saudi Aramco — ~$1.5T+
-2️⃣ International Holding Co (UAE) — ~$240B+
-3️⃣ QNB (Qatar National Bank) — ~$150B+
-4️⃣ Al Rajhi Bank (Saudi) — ~$100B+
-5️⃣ Emirates NBD (UAE) — ~$80B+
-Oil wealth meets financial power.
-@BehindNums</t>
+          <t>طموحاتك تحتاج سند مالي قوي
+ اكتشف منتجاتنا الادخارية وخصص جزء من دخلك لبناء مستقبلك مع #بنك_الإمارات_دبي_الوطني 💙
+للتفاصيل:https://t.co/oeE4XrSB6s https://t.co/QYrpXupJen</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1776308293000</v>
+        <v>1776339737000</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2044611289733878057</t>
+          <t>2044743177412722931</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGBjFKZXEAAVUtq.jpg', 'type': 'photo', 'id': '2044743171167424512'}]</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>{'name': 'BehindNums | Business &amp; Data', 'screenName': 'BehindNums', 'followersCount': 1, 'favouritesCount': 0, 'friendsCount': 1, 'description': 'Business. Wealth. Power. We decode the numbers behind it. Data-driven insights daily'}</t>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17269, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -849,7 +846,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>375</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
@@ -860,42 +857,35 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://x.com/BehindNums/status/2044611289733878057</t>
+          <t>https://x.com/F44195Faleh/status/2044915426291826845</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2044611289733878057</t>
+          <t>2044915426291826845</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2044611048305574280</t>
+          <t>2044915426291826845</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://x.com/BehindNums/status/2044611048305574280</t>
+          <t>https://x.com/F44195Faleh/status/2044915426291826845</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Top 5 Companies by Revenue 
-By Revenue (annual)
-1️⃣ Walmart — ~$650B
-2️⃣ Amazon — ~$575B
-3️⃣ Saudi Aramco — ~$500B
-4️⃣ China State Grid — ~$480B
-5️⃣ Apple — ~$390B
-@BehindNums</t>
+          <t>@EmiratesNBD_KSA عندكم شراء مديونيه</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1776308235000</v>
+        <v>1776380804000</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2044611048305574280</t>
+          <t>2044743177412722931</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -905,7 +895,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>{'name': 'BehindNums | Business &amp; Data', 'screenName': 'BehindNums', 'followersCount': 1, 'favouritesCount': 0, 'friendsCount': 1, 'description': 'Business. Wealth. Power. We decode the numbers behind it. Data-driven insights daily'}</t>
+          <t>{'name': 'F', 'screenName': 'F44195Faleh', 'followersCount': 2, 'favouritesCount': 32, 'friendsCount': 2, 'description': 'حساب جديد الاول طار 🛫'}</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -922,10 +912,14 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr"/>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2044743177412722931</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -933,63 +927,63 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>https://x.com/zaydaklabhoqx/status/2044582261102956879</t>
+          <t>https://x.com/Barigiin7m/status/2044849789800505744</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2044582261102956879</t>
+          <t>2044849789800505744</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2029869216254341430</t>
+          <t>2042645533164999079</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://x.com/CryptoNewsHntrs/status/2029869216254341430</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2042645533164999079</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>🚨 JUST IN: 🇦🇪 EMIRATES NBD ELIMINATES ATM WITHDRAWAL &amp;amp; DEBIT CARD FEES ACROSS THE UAE &amp;amp; GCC UNTIL MARCH 31, 2026! 💳🔥
-#UAE #EmiratesNBD #Banking #Finance #ATM #NoFees #GCC #MoneySmart https://t.co/aI9H5crVgx</t>
+          <t>سيارة حلمك تقدر تتملكها
+جديدة ولا مستعملة نمولها لك مع التمويل التأجيري للسيارات من بنك الإمارات دبي الوطني</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1772793508000</v>
+        <v>1775839620000</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2029869216254341430</t>
+          <t>2042645533164999079</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HCuLS2CXkAATb_t.jpg', 'type': 'photo', 'id': '2029869212919894016'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HCuLS2eXwAA68mZ.jpg', 'type': 'photo', 'id': '2029869213037346816'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>{'name': 'Crypto News Hunters 🎯', 'screenName': 'CryptoNewsHntrs', 'followersCount': 28363, 'favouritesCount': 314597, 'friendsCount': 138, 'description': 'Crypto News 🌐 Financial Markets 📈 Memes &amp; Hopium 🔥 Not Financial Advice 🚫'}</t>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17269, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>738</t>
+          <t>1462</t>
         </is>
       </c>
       <c r="P8" t="inlineStr"/>
@@ -1000,35 +994,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>https://x.com/zaydaklabhoqx/status/2044582261102956879</t>
+          <t>https://x.com/Barigiin7m/status/2044849789800505744</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2044582261102956879</t>
+          <t>2044849789800505744</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2044582261102956879</t>
+          <t>2044849789800505744</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://x.com/zaydaklabhoqx/status/2044582261102956879</t>
+          <t>https://x.com/Barigiin7m/status/2044849789800505744</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>@CryptoNewsHntrs ماذا عن مجانيّة سحب النقود؟ مبروك لعملاء Emirates NBD في الإمارات ودول الخليج</t>
+          <t>@EmiratesNBD_KSA كم النسبه</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1776301372000</v>
+        <v>1776365156000</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2029869216254341430</t>
+          <t>2042645533164999079</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1038,7 +1032,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>{'name': 'زيد أكلب', 'screenName': 'zaydaklabhoqx', 'followersCount': 30, 'favouritesCount': 301, 'friendsCount': 48, 'description': 'مدير آي تي في دبي، أحب التقنية والسيارات والكرة. أعزب ومستمتع بالحياة الفاخرة.'}</t>
+          <t>{'name': 'Barigi', 'screenName': 'Barigiin7m', 'followersCount': 0, 'favouritesCount': 0, 'friendsCount': 102, 'description': ''}</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -1051,16 +1045,16 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2029869216254341430</t>
+          <t>2042645533164999079</t>
         </is>
       </c>
     </row>
@@ -1070,65 +1064,63 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>https://x.com/STFU1346/status/2044433219693466085</t>
+          <t>https://x.com/RehmaniBahi/status/2044868531251245548</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2044433219693466085</t>
+          <t>2044868531251245548</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2043970652697211186</t>
+          <t>2044868531251245548</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://x.com/Brockutd/status/2043970652697211186</t>
+          <t>https://x.com/RehmaniBahi/status/2044868531251245548</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>🚨 Mark Clattenburg on Lisandro Martínez’s red card:
-“I was surprised that such an experienced referee considered this a red card offence. It was clearly a 50/50 challenge for the ball. 
-I think the referee’s seniority within the VAR group may have made others hesitant to overturn his on-field decision.
-In my opinion, this was a clear mistake. When we talk about ‘clear and obvious errors’, most referees would not have sent him off for that challenge.”</t>
+          <t>Dear @EmiratesNBD_AE please help and guide is it possible to convert my current account which was recently created to "Current/Salary Account" which I had mistakenly created as "Millionaire Savings Account"
+Your positive response will be appreciated! Thanks https://t.co/vNHoHSkhCl</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1776155553000</v>
+        <v>1776369624000</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2043970652697211186</t>
+          <t>2044868531251245548</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF2kdMfXYAA7k8w.jpg', 'type': 'photo', 'id': '2043970627372015616'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HF2kdM8asAEzRR_.jpg', 'type': 'photo', 'id': '2043970627493867521'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGDVF64agAAEcd6.jpg', 'type': 'photo', 'id': '2044868528508141568'}]</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>{'name': 'BROCK(fan)', 'screenName': 'Brockutd', 'followersCount': 6684, 'favouritesCount': 145265, 'friendsCount': 791, 'description': 'Face of Pogba Fc •|• @manutd •|• Fan account •|• @Roobet'}</t>
+          <t>{'name': 'Usman Bahi 🕊️🍁🇵🇰', 'screenName': 'RehmaniBahi', 'followersCount': 12, 'favouritesCount': 622, 'friendsCount': 822, 'description': 'I am raising social issues on social media for the sake of humanity and I am not a part of any political party or wing/social group or social wing.'}</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1037</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>9501</v>
+        <v>0</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>428722</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P10" t="inlineStr"/>
@@ -1139,37 +1131,37 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>https://x.com/STFU1346/status/2044433219693466085</t>
+          <t>https://x.com/RehmaniBahi/status/2044868531251245548</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2044433219693466085</t>
+          <t>2044868531251245548</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2043989823325716661</t>
+          <t>2044855091828756893</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://x.com/STFU1346/status/2043989823325716661</t>
+          <t>https://x.com/RehmaniBahi/status/2044855091828756893</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>@Brockutd Man U had it easy for years, now maybe karma is at play.
-I think it was soft, but the rules are the rules.
-Man U were shite last night, and should've been down by 3 or more before they woke up.</t>
+          <t>I am new here in Dubai @DubaiPoliceHQ, @DXBMediaOffice Please inform guide If someone use a VPN to call home country on WhatsApp because of restrictions, is that illegal? and there a penalty for it?
+or only there is penalties when someone use VPN for illegal activities?
+Thank you</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1776160124000</v>
+        <v>1776366420000</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2043970652697211186</t>
+          <t>2044855091828756893</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1179,31 +1171,27 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>{'name': 'BraveFart🏴\U000e0067\U000e0062\U000e0073\U000e0063\U000e0074\U000e007f', 'screenName': 'STFU1346', 'followersCount': 1646, 'favouritesCount': 16513, 'friendsCount': 1654, 'description': 'Scottish. NUFC mad. If you steal any of my memes, show a bit of common courtesy and like it first.'}</t>
+          <t>{'name': 'Usman Bahi 🕊️🍁🇵🇰', 'screenName': 'RehmaniBahi', 'followersCount': 12, 'favouritesCount': 622, 'friendsCount': 822, 'description': 'I am raising social issues on social media for the sake of humanity and I am not a part of any political party or wing/social group or social wing.'}</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>4746</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2043970652697211186</t>
-        </is>
-      </c>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
@@ -1211,35 +1199,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>https://x.com/STFU1346/status/2044433219693466085</t>
+          <t>https://x.com/mohamed50575321/status/2044777257898578369</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2044433219693466085</t>
+          <t>2044777257898578369</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2044040984212758846</t>
+          <t>2044777257898578369</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://x.com/JeetyJeeterson/status/2044040984212758846</t>
+          <t>https://x.com/mohamed50575321/status/2044777257898578369</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>@STFU1346 @Brockutd This narrative that United got all the decisions in the past is a complete lie. United are on the wrong end of poor decisions more than anybody, this lie was started by rival fans with zero evidence. We used to get alot of pens, as were attacking twice as much as everybody else</t>
+          <t>@EmiratesNBD_AE تواصلت مع visa airport campain
+و اكدوا عدم خصم اى رسوم من قبلهم
+ليكون الرسوم من راس البنك للاحتيال على شروط فيزا
+ارجو التحقيق من البنك المركزى
+لانه البنك الوحيد اللى فعل هذا</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1776172321000</v>
+        <v>1776347863000</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2043970652697211186</t>
+          <t>2044777257898578369</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1249,7 +1241,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>{'name': 'Jeety', 'screenName': 'JeetyJeeterson', 'followersCount': 416, 'favouritesCount': 667, 'friendsCount': 1554, 'description': "Whatever people say I am, that's what I'm not"}</t>
+          <t>{'name': 'Alaa', 'screenName': 'mohamed50575321', 'followersCount': 0, 'favouritesCount': 2, 'friendsCount': 1, 'description': ''}</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1262,18 +1254,14 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2043989823325716661</t>
-        </is>
-      </c>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
@@ -1281,37 +1269,35 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>https://x.com/STFU1346/status/2044433219693466085</t>
+          <t>https://x.com/mohamed50575321/status/2044777257898578369</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2044433219693466085</t>
+          <t>2044777257898578369</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2044048198029742561</t>
+          <t>2044777613521006775</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://x.com/STFU1346/status/2044048198029742561</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2044777613521006775</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>@JeetyJeeterson @Brockutd No, none, nada, zilch,  penalties against Man U under Ferguson at Old Trafford during their purple.. Give your head a shake man.
-Look at Sky Sports and the coverage you's get. Be as well call it Man U TV.
-The "Red Cartel" is no conspiracy theory, Man U are the head of the gang.</t>
+          <t>@mohamed50575321 مرحبًا، ،نأسف لأنك واجهت هذا، ليس هذا ما نتوقع أن يشعر به أو يراه عملاؤنا. سنقوم بالتأكيد بمراجعة الأمر. نطلب منك إرسال المزيد من التفاصيل ورقم هاتفك المسجل و رقم الهوية عبر social@emiratesnbd.com وذكر رقم الحالة #998439 ليمكننا من مساعدتك بشكل أفضل. شكرًا.</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>1776174041000</v>
+        <v>1776347947000</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2043970652697211186</t>
+          <t>2044777257898578369</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1321,11 +1307,11 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>{'name': 'BraveFart🏴\U000e0067\U000e0062\U000e0073\U000e0063\U000e0074\U000e007f', 'screenName': 'STFU1346', 'followersCount': 1646, 'favouritesCount': 16513, 'friendsCount': 1654, 'description': 'Scottish. NUFC mad. If you steal any of my memes, show a bit of common courtesy and like it first.'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174081, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1338,12 +1324,12 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>13</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2044040984212758846</t>
+          <t>2044777257898578369</t>
         </is>
       </c>
     </row>
@@ -1353,35 +1339,41 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>https://x.com/STFU1346/status/2044433219693466085</t>
+          <t>https://x.com/mohamed50575321/status/2044777257898578369</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2044433219693466085</t>
+          <t>2044777257898578369</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2044431315555024909</t>
+          <t>2044776755207057813</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://x.com/Cle_Etc/status/2044431315555024909</t>
+          <t>https://x.com/mohamed50575321/status/2044776755207057813</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>@STFU1346 @JeetyJeeterson @Brockutd Hmmm, from an Oil Money Club.</t>
+          <t>@EmiratesNBD_SA
+حدد visa campain
+شرط دخول الصالات بانفاق ١٠٠ دولار
+لتكون البطاقه صالحه لمده ٩٠ يوم لدخول صالات
+بينما بنك الامارات دبى الوطنى السعوديه وضع شرطا من راسه بانفاق ٣٠٠٠ ريال فى نفس ذات الشهر
+بينما البنك فرض عليا رسوم ٣٢ دولار بظون وجه حق
+طريقه احتيال يجب فيها التحقيق</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1776265383000</v>
+        <v>1776347743000</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2043970652697211186</t>
+          <t>2044776755207057813</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1391,11 +1383,11 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>{'name': 'Cle Etc.', 'screenName': 'Cle_Etc', 'followersCount': 186, 'favouritesCount': 21460, 'friendsCount': 42, 'description': 'Married. Dad. Irish. Musician. Songwriter. Producer. Teacher. Believer. Cynic. Man United supporter. Dyslexic. Dreamer. Likes a laugh.'}</t>
+          <t>{'name': 'Alaa', 'screenName': 'mohamed50575321', 'followersCount': 0, 'favouritesCount': 2, 'friendsCount': 1, 'description': ''}</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -1408,14 +1400,10 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>2044048198029742561</t>
-        </is>
-      </c>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
@@ -1423,38 +1411,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>https://x.com/STFU1346/status/2044433219693466085</t>
+          <t>https://x.com/TheJerzWay/status/2044788706364592302</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2044433219693466085</t>
+          <t>2044788706364592302</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2044432755811860595</t>
+          <t>2044786874955280730</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://x.com/STFU1346/status/2044432755811860595</t>
+          <t>https://x.com/TheJerzWay/status/2044786874955280730</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>@Cle_Etc @JeetyJeeterson @Brockutd Here are your sponsors:
-Commercial Bank of Qatar: A Financial Services Affinity Partner for Qatar.
-VIVA: An integrated telecommunications partner for Bahrain and Kuwait. 
-TM: An integrated telecommunications partner for Malaysia (often grouped with regional Asian/Middle Eastern</t>
+          <t>30,000 people just fled Dubai.
+The expat influencers are suddenly quiet.
+Here's what actually happened and where the smart money went instead:
+🧵</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1776265727000</v>
+        <v>1776350155000</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2043970652697211186</t>
+          <t>2044786874955280730</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1464,31 +1452,27 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>{'name': 'BraveFart🏴\U000e0067\U000e0062\U000e0073\U000e0063\U000e0074\U000e007f', 'screenName': 'STFU1346', 'followersCount': 1646, 'favouritesCount': 16513, 'friendsCount': 1654, 'description': 'Scottish. NUFC mad. If you steal any of my memes, show a bit of common courtesy and like it first.'}</t>
+          <t>{'name': 'The Way of Jerz', 'screenName': 'TheJerzWay', 'followersCount': 28573, 'favouritesCount': 57295, 'friendsCount': 1031, 'description': 'Helped 1,000+ protect assets &amp; go offshore. Pay LESS tax and build WEALTH. Second passports ▪️ Residencies ▪️ Structures 👉 https://t.co/3hDl1SmAoF'}</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>866</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>2044431315555024909</t>
-        </is>
-      </c>
+          <t>165960</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
@@ -1496,38 +1480,40 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>https://x.com/STFU1346/status/2044433219693466085</t>
+          <t>https://x.com/TheJerzWay/status/2044788706364592302</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2044433219693466085</t>
+          <t>2044788706364592302</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2044433219693466085</t>
+          <t>2044787195072938463</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://x.com/STFU1346/status/2044433219693466085</t>
+          <t>https://x.com/TheJerzWay/status/2044787195072938463</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>@Cle_Etc @JeetyJeeterson @Brockutd PepsiCo: Noted for regional arrangements in the Middle East and Asia. 
-Emirates NBD for the United Arab Emirates.
-Saudi Telecom Co.
-So, what's your point?</t>
+          <t>For years, Dubai was THE move.
+"Zero tax bro"
+"Lambos everywhere"
+"Just get a freelancer visa"
+Social media made it look easy.
+Reality was different.</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1776265837000</v>
+        <v>1776350232000</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2043970652697211186</t>
+          <t>2044786874955280730</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1537,7 +1523,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>{'name': 'BraveFart🏴\U000e0067\U000e0062\U000e0073\U000e0063\U000e0074\U000e007f', 'screenName': 'STFU1346', 'followersCount': 1646, 'favouritesCount': 16513, 'friendsCount': 1654, 'description': 'Scottish. NUFC mad. If you steal any of my memes, show a bit of common courtesy and like it first.'}</t>
+          <t>{'name': 'The Way of Jerz', 'screenName': 'TheJerzWay', 'followersCount': 28573, 'favouritesCount': 57295, 'friendsCount': 1031, 'description': 'Helped 1,000+ protect assets &amp; go offshore. Pay LESS tax and build WEALTH. Second passports ▪️ Residencies ▪️ Structures 👉 https://t.co/3hDl1SmAoF'}</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1547,19 +1533,19 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>24294</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2044432755811860595</t>
+          <t>2044786874955280730</t>
         </is>
       </c>
     </row>
@@ -1569,35 +1555,40 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>https://x.com/STFU1346/status/2044433219693466085</t>
+          <t>https://x.com/TheJerzWay/status/2044788706364592302</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2044433219693466085</t>
+          <t>2044788706364592302</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2044459400069357578</t>
+          <t>2044787700503318732</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://x.com/Cle_Etc/status/2044459400069357578</t>
+          <t>https://x.com/TheJerzWay/status/2044787700503318732</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>@STFU1346 @JeetyJeeterson @Brockutd Awe, you worked really hard for that. My point is that there are a handful of states sports washing, pumping billions into their purchased clubs… but we still have to listen to the fans complaining about imaginary cartels that control referees.</t>
+          <t>The truth about Dubai's "0% tax":
+• You need perfect structure (most didn't have it)
+• Your home country can still tax you
+• UAE ≠ automatic tax freedom
+• No tax treaty with most countries
+People moved for the aesthetic. Got audited for the structure.</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1776272079000</v>
+        <v>1776350352000</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2043970652697211186</t>
+          <t>2044786874955280730</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1607,29 +1598,29 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>{'name': 'Cle Etc.', 'screenName': 'Cle_Etc', 'followersCount': 186, 'favouritesCount': 21460, 'friendsCount': 42, 'description': 'Married. Dad. Irish. Musician. Songwriter. Producer. Teacher. Believer. Cynic. Man United supporter. Dyslexic. Dreamer. Likes a laugh.'}</t>
+          <t>{'name': 'The Way of Jerz', 'screenName': 'TheJerzWay', 'followersCount': 28573, 'favouritesCount': 57295, 'friendsCount': 1031, 'description': 'Helped 1,000+ protect assets &amp; go offshore. Pay LESS tax and build WEALTH. Second passports ▪️ Residencies ▪️ Structures 👉 https://t.co/3hDl1SmAoF'}</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>23907</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2044433219693466085</t>
+          <t>2044787195072938463</t>
         </is>
       </c>
     </row>
@@ -1639,66 +1630,74 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2044430548727128554</t>
+          <t>https://x.com/TheJerzWay/status/2044788706364592302</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2044430548727128554</t>
+          <t>2044788706364592302</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2044430548727128554</t>
+          <t>2044788201395564940</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2044430548727128554</t>
+          <t>https://x.com/TheJerzWay/status/2044788201395564940</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Manage your wealth with expertise you can trust. Contact us today https://t.co/XmTzVbwpLQ
-#EmiratesNBD #WealthManagement https://t.co/1RVFBUcixf</t>
+          <t>Then the costs exploded:
+• Rent up 50-80% in 2 years
+• School fees: $30-50K/year
+• Health insurance: $15K+/family
+• Visa costs increasing
+The "cheap Dubai life" became $200K/year minimum to live well.</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>1776265201000</v>
+        <v>1776350472000</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2044430548727128554</t>
+          <t>2044786874955280730</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF8-vnKWcAAQyPA.jpg', 'type': 'video', 'id': '2044421704122798080'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174062, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'The Way of Jerz', 'screenName': 'TheJerzWay', 'followersCount': 28573, 'favouritesCount': 57295, 'friendsCount': 1031, 'description': 'Helped 1,000+ protect assets &amp; go offshore. Pay LESS tax and build WEALTH. Second passports ▪️ Residencies ▪️ Structures 👉 https://t.co/3hDl1SmAoF'}</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N18" t="n">
-        <v>8</v>
+        <v>104</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>1286</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr"/>
+          <t>22964</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>2044787700503318732</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
@@ -1706,65 +1705,74 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2044430548727128554</t>
+          <t>https://x.com/TheJerzWay/status/2044788706364592302</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2044430548727128554</t>
+          <t>2044788706364592302</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2043932263717482626</t>
+          <t>2044788706364592302</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2043932263717482626</t>
+          <t>https://x.com/TheJerzWay/status/2044788706364592302</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>We are together against Fraud. @UAEBF #FightFraud #UAEBF #togetheragainstfraud #UnitedAgainstFraud https://t.co/CqApZaCAFO</t>
+          <t>Meanwhile, the banking got harder:
+• Emirates NBD closing accounts
+• Compliance questions on every transaction
+• "Source of funds" requests monthly
+• Crypto? Good luck.
+The "business-friendly" paradise started feeling a lot like everywhere else.</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>1776146400000</v>
+        <v>1776350592000</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2043932263717482626</t>
+          <t>2044786874955280730</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2043610882656059392/img/HaP0BSdqwFktNLDX.jpg', 'type': 'video', 'id': '2043610882656059392'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174062, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'The Way of Jerz', 'screenName': 'TheJerzWay', 'followersCount': 28573, 'favouritesCount': 57295, 'friendsCount': 1031, 'description': 'Helped 1,000+ protect assets &amp; go offshore. Pay LESS tax and build WEALTH. Second passports ▪️ Residencies ▪️ Structures 👉 https://t.co/3hDl1SmAoF'}</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N19" t="n">
-        <v>12</v>
+        <v>87</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>1234</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr"/>
+          <t>22095</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>2044788201395564940</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
@@ -1772,68 +1780,71 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>https://x.com/khir_llnas/status/2044377290952364098</t>
+          <t>https://x.com/TheJerzWay/status/2044788706364592302</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2044377290952364098</t>
+          <t>2044788706364592302</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2044377290952364098</t>
+          <t>2044789210507264373</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://x.com/khir_llnas/status/2044377290952364098</t>
+          <t>https://x.com/TheJerzWay/status/2044789210507264373</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>شكرا Emirates NBD بنك الإمارات دبي الوطني
-على دعمكم الإنساني في نجاح أنشطة المؤسسة لدعم الأسر المحتاجة..
-#متبرعين_خير_للناس
-#مؤسسة_خير_للناس https://t.co/5PUxmmX1mn</t>
+          <t>So where did the smart money actually go?
+They never went to Dubai in the first place.
+They went where the structure actually works:</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>1776252503000</v>
+        <v>1776350712000</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2044377290952364098</t>
+          <t>2044786874955280730</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF8VrwnXkAApAXH.jpg', 'type': 'photo', 'id': '2044376597378076672'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>{'name': 'خير للناس للتنمية', 'screenName': 'khir_llnas', 'followersCount': 3, 'favouritesCount': 0, 'friendsCount': 3, 'description': ''}</t>
+          <t>{'name': 'The Way of Jerz', 'screenName': 'TheJerzWay', 'followersCount': 28573, 'favouritesCount': 57295, 'friendsCount': 1031, 'description': 'Helped 1,000+ protect assets &amp; go offshore. Pay LESS tax and build WEALTH. Second passports ▪️ Residencies ▪️ Structures 👉 https://t.co/3hDl1SmAoF'}</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr"/>
+          <t>20893</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>2044788706364592302</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
@@ -1841,46 +1852,45 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>https://x.com/khir_llnas/status/2044377290952364098</t>
+          <t>https://x.com/TheJerzWay/status/2044788706364592302</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2044377290952364098</t>
+          <t>2044788706364592302</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2044440524782764312</t>
+          <t>2044967280467923140</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://x.com/khir_llnas/status/2044440524782764312</t>
+          <t>https://x.com/PegasusIzmirTR/status/2044967280467923140</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>تبرع الآن
-https://t.co/sk7px2ePBH https://t.co/lsrrrAISd0</t>
+          <t>@TheJerzWay To compare to Europe lets say Germany, banking here is a different dimention, for tiny 50k eur asset you have named contact via whatsapp, most of the stuff is via selfservice or whatsapp; credit cards delivered within 2-3 days from application same for loans.</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>1776267579000</v>
+        <v>1776393167000</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2044440524782764312</t>
+          <t>2044786874955280730</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF9PwRYXUAAfgil.jpg', 'type': 'photo', 'id': '2044440446567403520'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>{'name': 'خير للناس للتنمية', 'screenName': 'khir_llnas', 'followersCount': 3, 'favouritesCount': 0, 'friendsCount': 3, 'description': ''}</t>
+          <t>{'name': 'Göcmen Pegasus', 'screenName': 'PegasusIzmirTR', 'followersCount': 249, 'favouritesCount': 1983, 'friendsCount': 833, 'description': 'yazdiklarimi yatirim tavsiyesi olarak kullanani allah islah etsin"Domuzla boğuşma,birlikte kirlenirsiniz ve sadece o zevk alır" Simdilik 57 ülkeyi gezen gezgin.'}</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -1897,10 +1907,14 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>2044788706364592302</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
@@ -1908,40 +1922,35 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>https://x.com/ibmag_magazine/status/2044410083262734349</t>
+          <t>https://x.com/TheJerzWay/status/2044788706364592302</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2044410083262734349</t>
+          <t>2044788706364592302</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2044410083262734349</t>
+          <t>2044834096652657020</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://x.com/ibmag_magazine/status/2044410083262734349</t>
+          <t>https://x.com/jdpcasey/status/2044834096652657020</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>To find the trending news on Real estate, finance, and Technology for April 15, check the news links and the video link below:
-https://t.co/AuS5pOClPI
-https://t.co/uOBF8Ce7As
-https://t.co/0Q3Pd23x0U
-https://t.co/QMIfzjAAnq
-#INTLBM  #Sohar #EToro #EmiratesNBD #Sobha #Headlines</t>
+          <t>@TheJerzWay What on earth are you talking about?</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>1776260321000</v>
+        <v>1776361414000</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2044410083262734349</t>
+          <t>2044786874955280730</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1951,7 +1960,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>{'name': 'International Business Magazine', 'screenName': 'ibmag_magazine', 'followersCount': 1537, 'favouritesCount': 2080, 'friendsCount': 1003, 'description': 'International Business Magazine is a Dubai, UAE based publication.'}</t>
+          <t>{'name': 'Jak Casey', 'screenName': 'jdpcasey', 'followersCount': 7, 'favouritesCount': 7, 'friendsCount': 78, 'description': 'engineer @maplefinance\n\nshaping intent to sculpt compute'}</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -1968,10 +1977,14 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr"/>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>2044788706364592302</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
@@ -1979,40 +1992,35 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>https://x.com/ibmag_magazine/status/2044410083262734349</t>
+          <t>https://x.com/TheJerzWay/status/2044788706364592302</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2044410083262734349</t>
+          <t>2044788706364592302</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2043999660285862211</t>
+          <t>2044885650290180319</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://x.com/ibmag_magazine/status/2043999660285862211</t>
+          <t>https://x.com/FCACF17/status/2044885650290180319</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>To find the trending news on Corporate, Technology, Banking and Finance for #April14, check the links below:
-https://t.co/wCnnEeLf7A
-https://t.co/5jczPIqAT3
-https://t.co/X0IupL4wiw
-https://t.co/amPUbrkpdI
-#Intlbm #telecoms #Investment #MiddleEast #Banking #Finance #Innovation</t>
+          <t>@TheJerzWay Utter shite.</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>1776162469000</v>
+        <v>1776373705000</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2043999660285862211</t>
+          <t>2044786874955280730</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2022,7 +2030,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>{'name': 'International Business Magazine', 'screenName': 'ibmag_magazine', 'followersCount': 1537, 'favouritesCount': 2080, 'friendsCount': 1003, 'description': 'International Business Magazine is a Dubai, UAE based publication.'}</t>
+          <t>{'name': 'Vern', 'screenName': 'FCACF17', 'followersCount': 826, 'favouritesCount': 26811, 'friendsCount': 4706, 'description': 'Worked in the Oil &amp; Gas industry for over 30 yrs &amp; proud of it! IWCF Level 4 🏴\U000e0067\U000e0062\U000e0065\U000e006e\U000e0067\U000e007f 🇬🇧 🇺🇸'}</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -2035,14 +2043,18 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr"/>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>2044788706364592302</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
@@ -2050,51 +2062,51 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>https://x.com/Gulf_const/status/2044390258528395378</t>
+          <t>https://x.com/M17322417/status/2044796762028691877</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2044390258528395378</t>
+          <t>2044796762028691877</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2044390258528395378</t>
+          <t>2043309453412380893</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://x.com/Gulf_const/status/2044390258528395378</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2043309453412380893</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Emirates NBD has announced a strategic partnership with Sobha Realty to provide integrated home financing solutions for buyers of the premium luxury developer’s off-plan residential developments across Dubai.
-Read more on https://t.co/966sAK8POe
-#GCnews #emirates #MENA https://t.co/B6wVnQqtgg</t>
+          <t>رجّع 5% من مقاضي البقالة 😎 
+باستخدام بطاقة مزيد الائتمانية من #بنك_الإمارات_دبي_الوطني 
+للتفاصيل:https://t.co/b8HVJdpuqK https://t.co/kVUdwtCbBa</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>1776255595000</v>
+        <v>1775997911000</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2044390258528395378</t>
+          <t>2043309453412380893</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF8h57OawAA3WNa.jpg', 'type': 'photo', 'id': '2044390034883919872'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HFtLHljXAAAYJkf.jpg', 'type': 'photo', 'id': '2043309449654239232'}]</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>{'name': 'Gulf Construction', 'screenName': 'Gulf_const', 'followersCount': 3304, 'favouritesCount': 338, 'friendsCount': 334, 'description': 'We are an authoritative, respected journal with unmatched coverage of the Gulf region’s building and construction industries.'}</t>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17269, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -2107,7 +2119,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>1019</t>
         </is>
       </c>
       <c r="P24" t="inlineStr"/>
@@ -2118,47 +2130,45 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>https://x.com/Gulf_const/status/2044390258528395378</t>
+          <t>https://x.com/M17322417/status/2044796762028691877</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2044390258528395378</t>
+          <t>2044796762028691877</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2044017573616893963</t>
+          <t>2044796762028691877</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://x.com/Gulf_const/status/2044017573616893963</t>
+          <t>https://x.com/M17322417/status/2044796762028691877</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mered, the award-winning developer based in UAE, has announced that main piling operations are now progressing at Riviera Residences, a waterfront residential tower in Abu Dhabi, Al Reem Island.
-Read more on https://t.co/xGW6cvJ1Nc
-#GCnews #developer #UAE #residences https://t.co/bFrmFMn6HS</t>
+          <t>@EmiratesNBD_KSA الغوا شرط صرف ١٠٠٠ ريال شهريا واموركم تزين</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>1776166740000</v>
+        <v>1776352513000</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2044017573616893963</t>
+          <t>2043309453412380893</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HFxca_0aMAAamjh.jpg', 'type': 'photo', 'id': '2043609949796970496'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>{'name': 'Gulf Construction', 'screenName': 'Gulf_const', 'followersCount': 3304, 'favouritesCount': 338, 'friendsCount': 334, 'description': 'We are an authoritative, respected journal with unmatched coverage of the Gulf region’s building and construction industries.'}</t>
+          <t>{'name': 'M - #يارب_بلايستيشن5', 'screenName': 'M17322417', 'followersCount': 61, 'favouritesCount': 3568, 'friendsCount': 1971, 'description': ''}</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -2171,14 +2181,18 @@
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>2043309453412380893</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
@@ -2186,52 +2200,51 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>https://x.com/iRonyForChange/status/2044369434362753181</t>
+          <t>https://x.com/HomszRami/status/2044758697386348926</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2044369434362753181</t>
+          <t>2044758697386348926</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2044369434362753181</t>
+          <t>2044657039834550600</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://x.com/iRonyForChange/status/2044369434362753181</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2044657039834550600</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE 
-You kept pushing to take the Share Credit Card,finally I applied and then you rejected citing “internal policies” despite having higher eligibility than required.
-Now your agents are calling and saying it’s a miss &amp;amp; to resubmit documents.
-Are you serious?</t>
+          <t>ليست كل أنواع الفوائد متشابهة — فبعضها بسيط.
+هل تستطيع تسمية هذا النوع؟ شاركنا إجابتك.
+#لغز_الأسبوع_ENBD #أساسيات_المال #تعلم_المالية https://t.co/gAgAYclmU0</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>1776250630000</v>
+        <v>1776319200000</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2044369434362753181</t>
+          <t>2044657039834550600</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF7Zip7WsAAdNSe.jpg', 'type': 'photo', 'id': '2044310470266368000'}]</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>{'name': 'Preetam Chakraborty', 'screenName': 'iRonyForChange', 'followersCount': 42, 'favouritesCount': 1281, 'friendsCount': 193, 'description': 'Work &amp; live in 🇦🇪 | Strong political opinions | Anti-establishment'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174081, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -2240,11 +2253,11 @@
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>422</t>
         </is>
       </c>
       <c r="P26" t="inlineStr"/>
@@ -2255,35 +2268,35 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>https://x.com/iRonyForChange/status/2044369434362753181</t>
+          <t>https://x.com/HomszRami/status/2044758697386348926</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2044369434362753181</t>
+          <t>2044758697386348926</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2044371163166466284</t>
+          <t>2044758697386348926</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2044371163166466284</t>
+          <t>https://x.com/HomszRami/status/2044758697386348926</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Hi, thank you for sharing your feedback. We’re sorry that you had experienced this, it is not what we expect our customers to feel nor see. We kindly request you to send us more details and your registered mobile number via social@emiratesnbd.com and quote Case #997789 for us to assist you better. Thanks.</t>
+          <t>@EmiratesNBD_AE الإجابة هي الفائدة البسيطة #لغز_الأسبوع_للحاصلين_على_شهادة_الهندسة_المدنية #تعلم_المالية #أساسيات_المال</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>1776251042000</v>
+        <v>1776343437000</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2044369434362753181</t>
+          <t>2044657039834550600</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2293,7 +2306,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174062, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Rami Almsri', 'screenName': 'HomszRami', 'followersCount': 0, 'favouritesCount': 154, 'friendsCount': 31, 'description': ''}</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -2306,16 +2319,16 @@
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2044369434362753181</t>
+          <t>2044657039834550600</t>
         </is>
       </c>
     </row>
@@ -2325,40 +2338,65 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>https://x.com/Sems3499/status/2044363346460172688</t>
+          <t>https://x.com/masryeng/status/2044733124177743954</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2044363346460172688</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
+          <t>2044733124177743954</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2044430548727128554</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://x.com/undefined/status/undefined</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr"/>
+          <t>https://x.com/EmiratesNBD_AE/status/2044430548727128554</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Manage your wealth with expertise you can trust. Contact us today https://t.co/XmTzVbwpLQ
+#EmiratesNBD #WealthManagement https://t.co/1RVFBUcixf</t>
+        </is>
+      </c>
       <c r="G28" t="n">
-        <v>1776312254982</v>
-      </c>
-      <c r="H28" t="inlineStr"/>
+        <v>1776265201000</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>2044430548727128554</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF8-vnKWcAAQyPA.jpg', 'type': 'video', 'id': '2044421704122798080'}]</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174080, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>1</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>9</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>1444</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr"/>
     </row>
     <row r="29">
@@ -2367,35 +2405,36 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>https://x.com/Sems3499/status/2044363346460172688</t>
+          <t>https://x.com/masryeng/status/2044733124177743954</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2044363346460172688</t>
+          <t>2044733124177743954</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2044363346460172688</t>
+          <t>2044733124177743954</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://x.com/Sems3499/status/2044363346460172688</t>
+          <t>https://x.com/masryeng/status/2044733124177743954</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>@nurkanaydogan Enbd bankalarında çalışanlar için 1. Şık olduğunu düşünüyorum (:</t>
+          <t>@EmiratesNBD_AE عندي بطاقه ائتمانية ونزلتوا عليها مبلغ غرامه غير مستحقه ورفعت لكم ايميل ولا ردتوا علي الايميل 
+لا انصح بالتعامل معاهم</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>1776249178000</v>
+        <v>1776337340000</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2044358706846941680</t>
+          <t>2044430548727128554</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2405,7 +2444,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>{'name': 'Sem', 'screenName': 'Sems3499', 'followersCount': 4, 'favouritesCount': 275, 'friendsCount': 7, 'description': ''}</t>
+          <t>{'name': 'El-Sayed El-Masry', 'screenName': 'masryeng', 'followersCount': 214, 'favouritesCount': 312, 'friendsCount': 2291, 'description': 'Engineer | Founder | Investor'}</t>
         </is>
       </c>
       <c r="K29" t="n">
@@ -2418,16 +2457,16 @@
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>63</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2044358706846941680</t>
+          <t>2044430548727128554</t>
         </is>
       </c>
     </row>
@@ -2437,63 +2476,64 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>https://x.com/metakixakbar/status/2044307778140025041</t>
+          <t>https://x.com/masryeng/status/2044734491336282349</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2044307778140025041</t>
+          <t>2044734491336282349</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2044307778140025041</t>
+          <t>2044657039872245768</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://x.com/metakixakbar/status/2044307778140025041</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2044657039872245768</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>@ENBDdeals
-Took a Takaful policy from ENBD back in 2012. 15 year policy. Was supposed to mature in 2027. Policy was issued from Aman insurances. ENBD was distributor. Being told now to contact Aman insurance directly. Aman is as good as closed. ENBD is not taking responsibility.</t>
+          <t>Not all interests work the same way — some are simple.
+Can you name this type? Comment your answer.
+#ENBDRiddleOfTheWeek #MoneyBasics #LearnFinance https://t.co/05i14Flw98</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>1776235930000</v>
+        <v>1776319200000</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2044307778140025041</t>
+          <t>2044657039872245768</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF8tUJpWsAAqygG.jpg', 'type': 'photo', 'id': '2044402580059500544'}]</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>{'name': 'Akbar Syed', 'screenName': 'metakixakbar', 'followersCount': 0, 'favouritesCount': 88, 'friendsCount': 25, 'description': ''}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174080, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="K30" t="n">
+        <v>3</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
         <v>2</v>
       </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>478</t>
         </is>
       </c>
       <c r="P30" t="inlineStr"/>
@@ -2504,35 +2544,36 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>https://x.com/metakixakbar/status/2044307778140025041</t>
+          <t>https://x.com/masryeng/status/2044734491336282349</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2044307778140025041</t>
+          <t>2044734491336282349</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2044310308068425734</t>
+          <t>2044734491336282349</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://x.com/ENBDdeals/status/2044310308068425734</t>
+          <t>https://x.com/masryeng/status/2044734491336282349</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>@metakixakbar Quoting case #997567 in the subject line of the email from your registered email address We will make every effort to address the matter promptly and provide the necessary support. Thanks</t>
+          <t>@EmiratesNBD_AE نزلتوا غرامه غير مستحقه علي بطاقة فيزا الائتمانية ورفعت ايميل بالمشكلة ولا تن الرد 
+لا انصح بالتعامل معهم</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>1776236533000</v>
+        <v>1776337666000</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2044307778140025041</t>
+          <t>2044657039872245768</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2542,11 +2583,11 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD Deals', 'screenName': 'ENBDdeals', 'followersCount': 39129, 'favouritesCount': 61, 'friendsCount': 4, 'description': 'Welcome to the official account for Emirates NBD Deals. نرحب بكم في الحساب الرسمي لعروض بنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'El-Sayed El-Masry', 'screenName': 'masryeng', 'followersCount': 214, 'favouritesCount': 312, 'friendsCount': 2291, 'description': 'Engineer | Founder | Investor'}</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -2559,12 +2600,12 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>17</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2044307778140025041</t>
+          <t>2044657039872245768</t>
         </is>
       </c>
     </row>
@@ -2574,36 +2615,35 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>https://x.com/metakixakbar/status/2044307778140025041</t>
+          <t>https://x.com/masryeng/status/2044734491336282349</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2044307778140025041</t>
+          <t>2044734491336282349</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2044310246277967968</t>
+          <t>2044734607183036713</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://x.com/ENBDdeals/status/2044310246277967968</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2044734607183036713</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>@metakixakbar We sincerely regret for the inconvenience To be able to assist further, we kindly request you to reach out to us at
- social@emiratesnbd.com</t>
+          <t>@masryeng مرحبا, تم الرد على الخاص.</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>1776236518000</v>
+        <v>1776337694000</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2044307778140025041</t>
+          <t>2044657039872245768</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2613,7 +2653,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD Deals', 'screenName': 'ENBDdeals', 'followersCount': 39129, 'favouritesCount': 61, 'friendsCount': 4, 'description': 'Welcome to the official account for Emirates NBD Deals. نرحب بكم في الحساب الرسمي لعروض بنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174080, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -2626,16 +2666,16 @@
         <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2044307778140025041</t>
+          <t>2044734491336282349</t>
         </is>
       </c>
     </row>
@@ -2645,65 +2685,70 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>https://x.com/HarshGada76429/status/2044356621351149946</t>
+          <t>https://x.com/AyshaMoham64638/status/2044728681705390440</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2044356621351149946</t>
+          <t>2044728681705390440</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2038970719238045794</t>
+          <t>2041837196030705976</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://x.com/HarshGada76429/status/2038970719238045794</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2041837196030705976</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>@RBLBankCares
-@rblbank
-I have been a loyal customer for last 3yrs using your world safari credit card I have achieved the milestone but missed the redemption date by 7 days 
-Request you to send me new redemption link for 10000rs voucher or I will have to end the relationship now</t>
+          <t>Three messages say your Emirates ID or residence visa needs to be renewed. 
+Two are genuine and one is a trap designed to steal your data. Can you spot the fake message? 
+Share your answer in the comments, put your scam detection skills to the test and stand the chance to win AED 2,000.
+#UnitedAgainstFraud 
+تصلك ثلاث رسائل تفيد بأن هويتك الإماراتية أو تأشيرة إقامتك بحاجة إلى تجديد.
+اثنتان منهما حقيقيتان، وواحدة فخ احتيالي صُمّم لسرقة بياناتك.
+هل تستطيع كشف الرسالة المزيّفة؟ 
+شارك إجابتك في التعليقات، اختبر مهاراتك في كشف الاحتيال، واحصل على فرصة ربح 2,000 درهم.
+ #متحدون_ضد_الاحتيال</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>1774963476000</v>
+        <v>1775646897000</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2038970719238045794</t>
+          <t>2041837196030705976</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HFYQG8IXAAAIRz6.jpg', 'type': 'video', 'id': '2041837143132106752'}]</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>{'name': 'Harsh Gada', 'screenName': 'HarshGada76429', 'followersCount': 0, 'favouritesCount': 0, 'friendsCount': 21, 'description': ''}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174080, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>957</t>
         </is>
       </c>
       <c r="P33" t="inlineStr"/>
@@ -2714,39 +2759,35 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>https://x.com/HarshGada76429/status/2044356621351149946</t>
+          <t>https://x.com/AyshaMoham64638/status/2044728681705390440</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2044356621351149946</t>
+          <t>2044728681705390440</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2044356621351149946</t>
+          <t>2044728681705390440</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://x.com/HarshGada76429/status/2044356621351149946</t>
+          <t>https://x.com/AyshaMoham64638/status/2044728681705390440</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>@RBLBankCares @rblbank I haven't got the resolution yet 
-On technical terms you are denying me the voucher
-What about last 3 years of harassment where you guys were denying for voucher which i have earned by reaching milestone?
-@EmiratesNBD_AE   be careful with tie up with
-RBL Bank</t>
+          <t>@EmiratesNBD_AE SMS2 .</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>1776247575000</v>
+        <v>1776336281000</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2038970719238045794</t>
+          <t>2041837196030705976</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2756,11 +2797,11 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>{'name': 'Harsh Gada', 'screenName': 'HarshGada76429', 'followersCount': 0, 'favouritesCount': 0, 'friendsCount': 21, 'description': ''}</t>
+          <t>{'name': 'Aysha Mohammad', 'screenName': 'AyshaMoham64638', 'followersCount': 20, 'favouritesCount': 624, 'friendsCount': 86, 'description': 'Success is in my veins✨'}</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -2773,12 +2814,12 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2038970719238045794</t>
+          <t>2041837196030705976</t>
         </is>
       </c>
     </row>
@@ -2788,45 +2829,45 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>https://x.com/HarshGada76429/status/2044356621351149946</t>
+          <t>https://x.com/dar_global/status/2044730856070144064</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2044356621351149946</t>
+          <t>2044730856070144064</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2044364006027403737</t>
+          <t>2044730856070144064</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://x.com/RBLBankCares/status/2044364006027403737</t>
+          <t>https://x.com/dar_global/status/2044730856070144064</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>@HarshGada76429 Hello, our representative will get in touch with you at the earliest to address your query. Regards, RBL Bank.</t>
+          <t>Emirates NBD successfully executes USD 250 Million Syndicated Term Loan facility for Darglobal, Accelerating Global Growth and Expansion https://t.co/EnXMEkr31m https://t.co/CkhOYQYv3e</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>1776249336000</v>
+        <v>1776336800000</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2038970719238045794</t>
+          <t>2044730856070144064</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGBX38sXMAEnGkw.jpg', 'type': 'photo', 'id': '2044730849522823169'}]</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>{'name': 'RBL Bank Cares', 'screenName': 'RBLBankCares', 'followersCount': 15139, 'favouritesCount': 107, 'friendsCount': 1, 'description': 'Welcome to the official service handle of RBL Bank for addressing your queries. The Bank’s social media guidelines are available on: https://t.co/4latICF1Kx'}</t>
+          <t>{'name': 'DarGlobal', 'screenName': 'dar_global', 'followersCount': 4796, 'favouritesCount': 211, 'friendsCount': 19, 'description': 'Live All In'}</t>
         </is>
       </c>
       <c r="K35" t="n">
@@ -2836,21 +2877,17 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>2044356621351149946</t>
-        </is>
-      </c>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
@@ -2858,47 +2895,45 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>https://x.com/titledeednews/status/2044351837869105398</t>
+          <t>https://x.com/dar_global/status/2044730856070144064</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2044351837869105398</t>
+          <t>2044730856070144064</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2044351837869105398</t>
+          <t>2044860550589427947</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://x.com/titledeednews/status/2044351837869105398</t>
+          <t>https://x.com/dar_global/status/2044860550589427947</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sobha Realty is making off-plan investing in Dubai more accessible.
-In partnership with Emirates NBD, Sobha Realty introduces flexible financing solutions, giving investors easier access to high-potential opportunities.
-#DubaiInvestors #OffPlanDubai #RealEstateInvesting #Dubai https://t.co/yHBmK8RVEk</t>
+          <t>LSE-listed Dar Global secures $250mln term loan https://t.co/6wbMOXS2Dg</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>1776246435000</v>
+        <v>1776367721000</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2044351837869105398</t>
+          <t>2044860550589427947</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF7_CgOb0AAEGFF.jpg', 'type': 'photo', 'id': '2044351699348082688'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>{'name': 'The Title Deed', 'screenName': 'titledeednews', 'followersCount': 0, 'favouritesCount': 0, 'friendsCount': 10, 'description': ''}</t>
+          <t>{'name': 'DarGlobal', 'screenName': 'dar_global', 'followersCount': 4796, 'favouritesCount': 211, 'friendsCount': 19, 'description': 'Live All In'}</t>
         </is>
       </c>
       <c r="K36" t="n">
@@ -2908,14 +2943,14 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
         <v>0</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>54</t>
         </is>
       </c>
       <c r="P36" t="inlineStr"/>
@@ -2926,63 +2961,70 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>https://x.com/titledeednews/status/2044351837869105398</t>
+          <t>https://x.com/AyshaMoham64638/status/2044728654954111007</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2044351837869105398</t>
+          <t>2044728654954111007</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2044042548185010299</t>
+          <t>2041837196030705976</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://x.com/titledeednews/status/2044042548185010299</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2041837196030705976</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Al Habtoor Group is committing over AED 5 billion to a new commercial tower in Dubai. Another strong indicator of sustained demand for Grade A office space and long-term market confidence.
-#DubaiRealEstate #CommercialRealEstate #InvestInDubai #DubaiBrokers #RealEstateNews https://t.co/kHUr6Xe7wr</t>
+          <t>Three messages say your Emirates ID or residence visa needs to be renewed. 
+Two are genuine and one is a trap designed to steal your data. Can you spot the fake message? 
+Share your answer in the comments, put your scam detection skills to the test and stand the chance to win AED 2,000.
+#UnitedAgainstFraud 
+تصلك ثلاث رسائل تفيد بأن هويتك الإماراتية أو تأشيرة إقامتك بحاجة إلى تجديد.
+اثنتان منهما حقيقيتان، وواحدة فخ احتيالي صُمّم لسرقة بياناتك.
+هل تستطيع كشف الرسالة المزيّفة؟ 
+شارك إجابتك في التعليقات، اختبر مهاراتك في كشف الاحتيال، واحصل على فرصة ربح 2,000 درهم.
+ #متحدون_ضد_الاحتيال</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>1776172694000</v>
+        <v>1775646897000</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2044042548185010299</t>
+          <t>2041837196030705976</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF3loHrbsAAWgHC.jpg', 'type': 'photo', 'id': '2044042283314819072'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HFYQG8IXAAAIRz6.jpg', 'type': 'video', 'id': '2041837143132106752'}]</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>{'name': 'The Title Deed', 'screenName': 'titledeednews', 'followersCount': 0, 'favouritesCount': 0, 'friendsCount': 10, 'description': ''}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174080, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="N37" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>958</t>
         </is>
       </c>
       <c r="P37" t="inlineStr"/>
@@ -2993,35 +3035,35 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>https://x.com/oras_2030/status/2044301025142513927</t>
+          <t>https://x.com/AyshaMoham64638/status/2044728654954111007</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2044301025142513927</t>
+          <t>2044728654954111007</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2039084064070623329</t>
+          <t>2044728654954111007</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://x.com/AliAhmedk66633/status/2039084064070623329</t>
+          <t>https://x.com/AyshaMoham64638/status/2044728654954111007</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA اسوء تجربة من البنك في خدمة العملاء ولا ادارة التحصيل الي اسلوبه زي الزفت تخيلو طلبت خطاب عدم مومانعه  من شراء المديونية لك وشو يسوي البنك يتصل على البنك الثاني ويتاكد متى تتغير النسبه ويتاخر الطلب لي ثلاث ايام وانا اتصل على ادارة التحصيل وخدمه العملاء اخر شي</t>
+          <t>@EmiratesNBD_AE SMS2</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>1774990499000</v>
+        <v>1776336275000</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2039084064070623329</t>
+          <t>2041837196030705976</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3031,11 +3073,11 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>{'name': 'Ali Ahmed', 'screenName': 'AliAhmedk66633', 'followersCount': 0, 'favouritesCount': 0, 'friendsCount': 6, 'description': ''}</t>
+          <t>{'name': 'Aysha Mohammad', 'screenName': 'AyshaMoham64638', 'followersCount': 20, 'favouritesCount': 624, 'friendsCount': 86, 'description': 'Success is in my veins✨'}</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
@@ -3048,10 +3090,14 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>157</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>2041837196030705976</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
@@ -3059,45 +3105,50 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>https://x.com/oras_2030/status/2044301025142513927</t>
+          <t>https://x.com/FintechGate1/status/2044721846457655694</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2044301025142513927</t>
+          <t>2044721846457655694</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2044301025142513927</t>
+          <t>2044721846457655694</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://x.com/oras_2030/status/2044301025142513927</t>
+          <t>https://x.com/FintechGate1/status/2044721846457655694</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>@AliAhmedk66633 @EmiratesNBD_KSA هل تنصح اخ علي@ انقل راتبي عندهم عشان قرض شخصي لان نسبتهم اقل من البنوك الاخرى؟</t>
+          <t>«الإمارات دبي الوطني» ينفذ تسهيلات قرض مشترك بقيمة 250 مليون دولار لصالح «دار جلوبال»
+https://t.co/t5ea8OOIgX | التفاصيل 
+@EmiratesNBD_AE
+@dar_global
+#fintech_gate
+#الإمارات_دبي_الوطني #دار_جلوبال https://t.co/o7GYOB2HP9</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>1776234320000</v>
+        <v>1776334651000</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2039084064070623329</t>
+          <t>2044721846457655694</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGBPrv_WgAACCKx.jpg', 'type': 'photo', 'id': '2044721843861356544'}]</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>{'name': 'oras2030', 'screenName': 'oras_2030', 'followersCount': 0, 'favouritesCount': 133, 'friendsCount': 126, 'description': 'سبحان الله وبحمده سبحان الله العظيم'}</t>
+          <t>{'name': 'FinTech Gate-بوابة التكنولوجيا المالية', 'screenName': 'FintechGate1', 'followersCount': 485, 'favouritesCount': 56, 'friendsCount': 331, 'description': 'منصة إخبارية مهتمة بكل ما يتعلق بالتكنولوجيا المالية والقطاعات التابعة لها التجارة الإلكترونية و المدفوعات والبنوك الرقمية والقطاع المالي غير المصرفي'}</t>
         </is>
       </c>
       <c r="K39" t="n">
@@ -3107,21 +3158,17 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N39" t="n">
         <v>0</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>2039084064070623329</t>
-        </is>
-      </c>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
@@ -3129,45 +3176,48 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>https://x.com/Eisa_Shj/status/2044283005183857003</t>
+          <t>https://x.com/FintechGate1/status/2044721846457655694</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2044283005183857003</t>
+          <t>2044721846457655694</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2044283005183857003</t>
+          <t>2044876376222654838</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://x.com/Eisa_Shj/status/2044283005183857003</t>
+          <t>https://x.com/FintechGate1/status/2044876376222654838</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>ماعرف ليش اغلب الناس لين الحين تفتح عندهم و هم من اكثر البنوك في تعقيد الامور الحمدالله على نعمه ENBD الصراحة🦦</t>
+          <t>«بورصة مصر» تربح 113 مليار جنيه خلال أسبوع
+https://t.co/7VTQKUKB0R  | التفاصيل 
+#fintech_gate
+#بورصة_مصر  #تعاملات #اسهم https://t.co/E8uEF2Kkpm</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>1776230024000</v>
+        <v>1776371494000</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2044283005183857003</t>
+          <t>2044876376222654838</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGDcOiFXgAAnoQT.jpg', 'type': 'photo', 'id': '2044876373051801600'}]</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>{'name': 'عـيـســى الأمـيــري', 'screenName': 'Eisa_Shj', 'followersCount': 74, 'favouritesCount': 40740, 'friendsCount': 404, 'description': 'Don’t be sorry, BE BETTER ✨'}</t>
+          <t>{'name': 'FinTech Gate-بوابة التكنولوجيا المالية', 'screenName': 'FintechGate1', 'followersCount': 485, 'favouritesCount': 56, 'friendsCount': 331, 'description': 'منصة إخبارية مهتمة بكل ما يتعلق بالتكنولوجيا المالية والقطاعات التابعة لها التجارة الإلكترونية و المدفوعات والبنوك الرقمية والقطاع المالي غير المصرفي'}</t>
         </is>
       </c>
       <c r="K40" t="n">
@@ -3184,7 +3234,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P40" t="inlineStr"/>
@@ -3195,45 +3245,47 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>https://x.com/dcgguide/status/2044340590037655768</t>
+          <t>https://x.com/GCCBusinessNews/status/2044715070912188821</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2044340590037655768</t>
+          <t>2044715070912188821</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2044340590037655768</t>
+          <t>2044715070912188821</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://x.com/dcgguide/status/2044340590037655768</t>
+          <t>https://x.com/GCCBusinessNews/status/2044715070912188821</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Emirates Islamic Drives SME Growth And Engagement Through AED 1 Million Business Banking Campaign https://t.co/lYSRNGGq3N</t>
+          <t>Dubai Holding Real Estate and Emirates NBD have signed an MoU to introduce integrated mortgage financing for off-plan developments in Dubai.
+https://t.co/7Rqdx9rNls
+#SaudiArabia #DigitalTransformation #DGA #GovTech #Innovation  #GCCBusinessNews @dubaiholding  @EmiratesNBD_AE https://t.co/SdUcJuRdBY</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>1776243753000</v>
+        <v>1776333036000</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2044340590037655768</t>
+          <t>2044715070912188821</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGBJgmkbIAAKaO6.jpg', 'type': 'photo', 'id': '2044715055284166656'}]</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>{'name': 'DUBAI CITY GUIDE from Cyber Gear', 'screenName': 'dcgguide', 'followersCount': 93487, 'favouritesCount': 19475, 'friendsCount': 106586, 'description': 'DCG is a https://t.co/bmR4jltJAW e-venture. We publish guest posts at https://t.co/EISzXb0O0y Learn AI at https://t.co/YcnxpXcCNU'}</t>
+          <t>{'name': 'GCC Business News', 'screenName': 'GCCBusinessNews', 'followersCount': 471, 'favouritesCount': 103, 'friendsCount': 20, 'description': 'GBN is an exclusive business news portal for entrepreneurs, businessmen, and trade enthusiasts of the GCC region.'}</t>
         </is>
       </c>
       <c r="K41" t="n">
@@ -3246,11 +3298,11 @@
         <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="P41" t="inlineStr"/>
@@ -3261,45 +3313,47 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>https://x.com/dcgguide/status/2044340590037655768</t>
+          <t>https://x.com/GCCBusinessNews/status/2044715070912188821</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2044340590037655768</t>
+          <t>2044715070912188821</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2044619960383848830</t>
+          <t>2044716585060069772</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://x.com/dcgguide/status/2044619960383848830</t>
+          <t>https://x.com/GCCBusinessNews/status/2044716585060069772</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Soulland Arrives In Dubai, Marking Its First Entry Into The Middle East https://t.co/lNcIEXHcGK</t>
+          <t>Tabby has secured a SVF license from the CBUAE, enabling the fintech company to offer spending accounts, payment cards, and money management tools.
+https://t.co/vAV5vsPqwg
+#TabbyUAE #SVFLicense #Fintech #DigitalBanking #GCCFintech #TabbyPayments #GCCBusinessNews @centralbankuae https://t.co/XEDSOgu4uG</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>1776310360000</v>
+        <v>1776333397000</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2044619960383848830</t>
+          <t>2044716585060069772</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGBK483a4AAYj4K.jpg', 'type': 'photo', 'id': '2044716573097910272'}]</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>{'name': 'DUBAI CITY GUIDE from Cyber Gear', 'screenName': 'dcgguide', 'followersCount': 93487, 'favouritesCount': 19475, 'friendsCount': 106586, 'description': 'DCG is a https://t.co/bmR4jltJAW e-venture. We publish guest posts at https://t.co/EISzXb0O0y Learn AI at https://t.co/YcnxpXcCNU'}</t>
+          <t>{'name': 'GCC Business News', 'screenName': 'GCCBusinessNews', 'followersCount': 471, 'favouritesCount': 103, 'friendsCount': 20, 'description': 'GBN is an exclusive business news portal for entrepreneurs, businessmen, and trade enthusiasts of the GCC region.'}</t>
         </is>
       </c>
       <c r="K42" t="n">
@@ -3316,7 +3370,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>21</t>
         </is>
       </c>
       <c r="P42" t="inlineStr"/>
@@ -3327,47 +3381,51 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>https://x.com/EntAlArabiya/status/2044341445717610661</t>
+          <t>https://x.com/OMFIF/status/2044709886311985369</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2044341445717610661</t>
+          <t>2044709886311985369</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2044341445717610661</t>
+          <t>2044709886311985369</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://x.com/EntAlArabiya/status/2044341445717610661</t>
+          <t>https://x.com/OMFIF/status/2044709886311985369</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>الإمارات الإسلامي @emiratesislamic  يعزز قطاع الأعمال بحملة للشركات الصغيرة
-#الإمارات #دبي #بنوك #شركات #مشاريع_صغيرة #تمويل #اقتصاد #استثمار #نمو #entalarabiya
-https://t.co/XNTvseOsQ0</t>
+          <t>Last year, on OMFIF’s #GenderBalanceIndex, the least‑scoring commercial banks were:
+@HDFC_Bank 
+@EmiratesNBD_AE 
+@Bancolombia 
+@mizuhobank 
+@Bradesco 
+Want to see how commercial banks performed over the last 5 years? Explore it here: https://t.co/RKo9Ahvcg6 https://t.co/dHWnMtFIl6</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>1776243957000</v>
+        <v>1776331800000</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2044341445717610661</t>
+          <t>2044709886311985369</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2044695782427684864/img/zA_chf-DgPi1Wm22.jpg', 'type': 'video', 'id': '2044695782427684864'}]</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>{'name': 'Entrepreneur العربية', 'screenName': 'EntAlArabiya', 'followersCount': 15614, 'favouritesCount': 5008, 'friendsCount': 796, 'description': 'لمتابعة آخر أخبار عالم ريادة الأعمال في منطقة الشرق الأوسط وشمال إفريقيا، الحساب الرسمي لمجلة Entrepreneur العربية'}</t>
+          <t>{'name': 'OMFIF', 'screenName': 'OMFIF', 'followersCount': 9009, 'favouritesCount': 2226, 'friendsCount': 276, 'description': 'https://t.co/sI5QfywLi7\nVideos/podcasts: https://t.co/rujfGXEXAk\nEvents: https://t.co/vBPUnB1tEK\nReports: https://t.co/Hdfzo1M4V9'}</t>
         </is>
       </c>
       <c r="K43" t="n">
@@ -3377,14 +3435,14 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
         <v>1</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>171</t>
         </is>
       </c>
       <c r="P43" t="inlineStr"/>
@@ -3395,47 +3453,46 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>https://x.com/EntAlArabiya/status/2044341445717610661</t>
+          <t>https://x.com/OMFIF/status/2044709886311985369</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2044341445717610661</t>
+          <t>2044709886311985369</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2044366042470977758</t>
+          <t>2044349543429312913</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://x.com/EntAlArabiya/status/2044366042470977758</t>
+          <t>https://x.com/OMFIF/status/2044349543429312913</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>شراكة بين RGB وBNC Publishing لتعزيز الوصول إلى المحتوى الصحي الموثوق في المنطقة @EntMagazineME  
-#الإمارات #صحة #توعية #طب #إعلام #شركات #محتوى #رفاهية #ابتكار #entalarabiya
-https://t.co/PFB5U9YnOG</t>
+          <t>In 1989 #ViktorOrbán launched himself into the centre of Hungarian politics with an anti-Russia, pro-liberal speech. However, political support for Orbán has dwindled in the last few years, and this year’s election saw challenger #PéterMagyar win.
+https://t.co/awg2X83gbi https://t.co/myWYSUumtU</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>1776249821000</v>
+        <v>1776245887000</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2044366042470977758</t>
+          <t>2044349543429312913</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF79A5BW8AArj0w.jpg', 'type': 'photo', 'id': '2044349472621129728'}]</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>{'name': 'Entrepreneur العربية', 'screenName': 'EntAlArabiya', 'followersCount': 15614, 'favouritesCount': 5008, 'friendsCount': 796, 'description': 'لمتابعة آخر أخبار عالم ريادة الأعمال في منطقة الشرق الأوسط وشمال إفريقيا، الحساب الرسمي لمجلة Entrepreneur العربية'}</t>
+          <t>{'name': 'OMFIF', 'screenName': 'OMFIF', 'followersCount': 9009, 'favouritesCount': 2226, 'friendsCount': 276, 'description': 'https://t.co/sI5QfywLi7\nVideos/podcasts: https://t.co/rujfGXEXAk\nEvents: https://t.co/vBPUnB1tEK\nReports: https://t.co/Hdfzo1M4V9'}</t>
         </is>
       </c>
       <c r="K44" t="n">
@@ -3445,14 +3502,14 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>127</t>
         </is>
       </c>
       <c r="P44" t="inlineStr"/>
@@ -3463,35 +3520,36 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>https://x.com/gold_hadas/status/2044447495619547616</t>
+          <t>https://x.com/msa3474/status/2044694547498696848</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2044447495619547616</t>
+          <t>2044694547498696848</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2044447495619547616</t>
+          <t>2044375431952867780</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://x.com/gold_hadas/status/2044447495619547616</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2044375431952867780</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Emirates Islamic launches AED1m campaign for SME customers  https://t.co/7gX7HHRcOh</t>
+          <t>سافر لوجهتك، وقسط دفعاتها مع 0% هامش ربح ✈️
+على طيران الإمارات باستخدام بطاقات #بنك_الإمارات_دبي_الوطني الائتمانية</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>1776269241000</v>
+        <v>1776252060000</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2044447495619547616</t>
+          <t>2044375431952867780</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3501,11 +3559,11 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>{'name': 'Nicholas MOLODYKO, writer', 'screenName': 'gold_hadas', 'followersCount': 1108, 'favouritesCount': 23737, 'friendsCount': 301, 'description': "Agency (individual free will) is the collective spiritual value of an individual's words and actions—Existence of free will is central to the U.S. Constitution."}</t>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17269, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
@@ -3514,11 +3572,11 @@
         <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>642</t>
         </is>
       </c>
       <c r="P45" t="inlineStr"/>
@@ -3529,49 +3587,49 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>https://x.com/gold_hadas/status/2044447495619547616</t>
+          <t>https://x.com/msa3474/status/2044694547498696848</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2044447495619547616</t>
+          <t>2044694547498696848</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2044582960431554593</t>
+          <t>2044676172248690733</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://x.com/gold_hadas/status/2044582960431554593</t>
+          <t>https://x.com/msa3474/status/2044676172248690733</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Modesty is a defining element of a Muslim’s “style” — a “less is more” philosophy that prioritizes spirituality and personal comfort over overt attention seeking. Identity is both internal and external. Modesty is a conscious choice —and a powerful one. https://t.co/hcxLG2j35s https://t.co/V2EWTgPYbW</t>
+          <t>@EmiratesNBD_KSA السلام عليكم ورحمه الله وبركاته الساده بنك الإمارات دبي الوطني المحترمين الرجاء حل مشكلتي مع فرع شارع الامير سلطان بجدة حيث انني طلبت منهم إيصال سداد مديونية ولي الى الآن اسبوع كامل لم يصلني الرد.</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>1776301538000</v>
+        <v>1776323762000</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2044582960431554593</t>
+          <t>2044375431952867780</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF_RXPNWoAA_0TN.jpg', 'type': 'photo', 'id': '2044582952999231488'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>{'name': 'Nicholas MOLODYKO, writer', 'screenName': 'gold_hadas', 'followersCount': 1108, 'favouritesCount': 23737, 'friendsCount': 301, 'description': "Agency (individual free will) is the collective spiritual value of an individual's words and actions—Existence of free will is central to the U.S. Constitution."}</t>
+          <t>{'name': 'AHMARI', 'screenName': 'msa3474', 'followersCount': 36, 'favouritesCount': 2762, 'friendsCount': 150, 'description': ''}</t>
         </is>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
@@ -3584,10 +3642,14 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="P46" t="inlineStr"/>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>2044375431952867780</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
@@ -3595,37 +3657,35 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2044294659795513346</t>
+          <t>https://x.com/msa3474/status/2044694547498696848</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2044294659795513346</t>
+          <t>2044694547498696848</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2044294653097156714</t>
+          <t>2044679518741205412</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2044294653097156714</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2044679518741205412</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>من “يوماً ما” إلى يوم الانتقال!
-التمويل السكني من الإمارات الإسلامي يجعل حلم امتلاك منزلك حقيقة، مع المرونة والوضوح في كل خطوة من رحلتك.
-استمتع بحلول تمويلية مصممة خصيصاً لك، ودعم متكامل طوال الطريق، لتصبح تجربة امتلاك المنزل سلسة وميسرة.</t>
+          <t>@msa3474 مرحباً، نأسف لسماع أنك تواجه تجربة غير سارة. يسعدنا مساعدتك وحلها. يُرجى إرسال التفاصيل الخاصه بشكواك إلى رسائل الخاص حتي نتمكن من مساعدتك بشكل أفضل</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>1776232801000</v>
+        <v>1776324560000</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2044294653097156714</t>
+          <t>2044375431952867780</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3635,11 +3695,11 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17269, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
       <c r="K47" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
@@ -3652,10 +3712,14 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="P47" t="inlineStr"/>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>2044676172248690733</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
@@ -3663,36 +3727,35 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2044294659795513346</t>
+          <t>https://x.com/msa3474/status/2044694547498696848</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2044294659795513346</t>
+          <t>2044694547498696848</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2044294656716836969</t>
+          <t>2044694547498696848</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2044294656716836969</t>
+          <t>https://x.com/msa3474/status/2044694547498696848</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>ابدأ رحلتك نحو منزل أحلامك اليوم.
-https://t.co/lQDtk9615Y</t>
+          <t>@EmiratesNBD_KSA الرسائل الخاصه مقفله لديكم</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>1776232801000</v>
+        <v>1776328143000</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2044294653097156714</t>
+          <t>2044375431952867780</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3702,7 +3765,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+          <t>{'name': 'AHMARI', 'screenName': 'msa3474', 'followersCount': 36, 'favouritesCount': 2762, 'friendsCount': 150, 'description': ''}</t>
         </is>
       </c>
       <c r="K48" t="n">
@@ -3719,12 +3782,12 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>14</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>2044294653097156714</t>
+          <t>2044679518741205412</t>
         </is>
       </c>
     </row>
@@ -3734,39 +3797,35 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2044294659795513346</t>
+          <t>https://x.com/msa3474/status/2044694547498696848</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2044294659795513346</t>
+          <t>2044694547498696848</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2044294659795513346</t>
+          <t>2044694905054777447</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2044294659795513346</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2044694905054777447</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>From “one day” to move-in day.
-Emirates Islamic Home Finance helps turn home ownership into reality, with the flexibility and clarity you need at every step.
-With tailored finance solutions and guided support throughout,
-Your home journey starts here.
-https://t.co/XwkOLamNf0</t>
+          <t>@msa3474 مرحبا تم الرد عبر رسائل الخاص</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>1776232802000</v>
+        <v>1776328228000</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2044294653097156714</t>
+          <t>2044375431952867780</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3776,7 +3835,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17269, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
       <c r="K49" t="n">
@@ -3793,12 +3852,12 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>2044294656716836969</t>
+          <t>2044694547498696848</t>
         </is>
       </c>
     </row>
@@ -3808,65 +3867,63 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>https://x.com/EntMagazineME/status/2044312732879728677</t>
+          <t>https://x.com/msa3474/status/2044693858894700659</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2044312732879728677</t>
+          <t>2044693858894700659</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2044312732879728677</t>
+          <t>2044375431952867780</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://x.com/EntMagazineME/status/2044312732879728677</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2044375431952867780</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>@emiratesislamic has announced the launch of a new Business Banking campaign aimed at supporting 3SME customers and strengthening #business resilience across the #UAE.
-Running until June 30, 2026, the campaign allows businesses to participate by increasing and maintaining their average balances in their Business Banking Accounts.
-The initiative offers a total prize pool of AED1 million and will reward 55 winners over three months, providing multiple opportunities for customers to win cash prizes while encouraging sustainable growth.
-🔗Read more HERE: https://t.co/j0Wq0RjPdm</t>
+          <t>سافر لوجهتك، وقسط دفعاتها مع 0% هامش ربح ✈️
+على طيران الإمارات باستخدام بطاقات #بنك_الإمارات_دبي_الوطني الائتمانية</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>1776237111000</v>
+        <v>1776252060000</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2044312732879728677</t>
+          <t>2044375431952867780</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF7bgFgb0AArMEW.jpg', 'type': 'photo', 'id': '2044312625153298432'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>{'name': 'Entrepreneur Middle East', 'screenName': 'EntMagazineME', 'followersCount': 178521, 'favouritesCount': 30182, 'friendsCount': 622, 'description': 'The official Twitter of Entrepreneur Middle East: inspiring, informing, and celebrating entrepreneurs in the Middle East, and beyond.'}</t>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17269, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
       <c r="K50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>643</t>
         </is>
       </c>
       <c r="P50" t="inlineStr"/>
@@ -3877,69 +3934,69 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>https://x.com/EntMagazineME/status/2044312732879728677</t>
+          <t>https://x.com/msa3474/status/2044693858894700659</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2044312732879728677</t>
+          <t>2044693858894700659</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2044354972473766389</t>
+          <t>2044676172248690733</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://x.com/EntMagazineME/status/2044354972473766389</t>
+          <t>https://x.com/msa3474/status/2044676172248690733</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>RGB (@RGBDubai), a #Dubai-based broadcasting and content production company known for its cutting-edge output and expertise in branding and identity since 2006, and the creator of The Health Community—a digital platform focused on verified medical knowledge—has entered a strategic media partnership with Dubai-headquartered regional media company BNC Publishing.
-The collaboration aims to expand access to credible, expert-led health content across the Middle East, leveraging Entrepreneur’s bilingual platforms and established regional audience.
-Designed as more than a content platform, The Health Community seeks to create a connected ecosystem where reliable #healthcare knowledge can be shared in ways that are practical and accessible for everyday life.
-Under the partnership, Entrepreneur Middle East (@EntMagazineME) and Entrepreneur Al Arabiya will collaborate with RGB to develop bilingual editorial features, #expert insights, and multimedia storytelling that elevate conversations around prevention, wellbeing, and human performance across the region.
-Read more HERE: https://t.co/KBGmbzdXAG</t>
+          <t>@EmiratesNBD_KSA السلام عليكم ورحمه الله وبركاته الساده بنك الإمارات دبي الوطني المحترمين الرجاء حل مشكلتي مع فرع شارع الامير سلطان بجدة حيث انني طلبت منهم إيصال سداد مديونية ولي الى الآن اسبوع كامل لم يصلني الرد.</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>1776247182000</v>
+        <v>1776323762000</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2044354972473766389</t>
+          <t>2044375431952867780</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF8B64ZaYAECgQU.jpg', 'type': 'photo', 'id': '2044354866932506625'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>{'name': 'Entrepreneur Middle East', 'screenName': 'EntMagazineME', 'followersCount': 178521, 'favouritesCount': 30182, 'friendsCount': 622, 'description': 'The official Twitter of Entrepreneur Middle East: inspiring, informing, and celebrating entrepreneurs in the Middle East, and beyond.'}</t>
+          <t>{'name': 'AHMARI', 'screenName': 'msa3474', 'followersCount': 36, 'favouritesCount': 2762, 'friendsCount': 150, 'description': ''}</t>
         </is>
       </c>
       <c r="K51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>189</t>
-        </is>
-      </c>
-      <c r="P51" t="inlineStr"/>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>2044375431952867780</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
@@ -3947,50 +4004,49 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2044471342880170391</t>
+          <t>https://x.com/msa3474/status/2044693858894700659</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2044471342880170391</t>
+          <t>2044693858894700659</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2044471339784810653</t>
+          <t>2044679518741205412</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2044471339784810653</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2044679518741205412</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>احصل على فرصة الفوز بحصة من الجوائز النقدية قيمتها تصل إلى 1,000,000 درهم. كل زيادة بقيمة 100,000 درهم في حسابك المصرفي للأعمال تمنحك فرصة واحدة للدخول في السحب.
-اجعل شركتك إحدى الشركات الـ 55 الفائزة. فهل ستكون من بينها؟ https://t.co/zGFXn2y3iT</t>
+          <t>@msa3474 مرحباً، نأسف لسماع أنك تواجه تجربة غير سارة. يسعدنا مساعدتك وحلها. يُرجى إرسال التفاصيل الخاصه بشكواك إلى رسائل الخاص حتي نتمكن من مساعدتك بشكل أفضل</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>1776274926000</v>
+        <v>1776324560000</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2044471339784810653</t>
+          <t>2044375431952867780</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF9r2SlXIAA7IEH.jpg', 'type': 'photo', 'id': '2044471336295145472'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17269, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
       <c r="K52" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
@@ -3999,14 +4055,18 @@
         <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>147</t>
-        </is>
-      </c>
-      <c r="P52" t="inlineStr"/>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>2044676172248690733</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
@@ -4014,40 +4074,35 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2044471342880170391</t>
+          <t>https://x.com/msa3474/status/2044693858894700659</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2044471342880170391</t>
+          <t>2044693858894700659</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2044471342880170391</t>
+          <t>2044693858894700659</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2044471342880170391</t>
+          <t>https://x.com/msa3474/status/2044693858894700659</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>الجائزة النقدية الكبرى: 250,000 درهم (فائز واحد) 
-الجائزة النقدية الثانية: 100,000 درهم (فائزان اثنان)
-الجوائز النقدية الشهرية: تصل إلى 25 ألف درهم (52 فائز)
-يسري العرض لغاية 30 يونيو 2026.
-تطبق الشروط والأحكام.
-https://t.co/RWuJWfhfUm</t>
+          <t>@EmiratesNBD_KSA احاول ارسلها خاص لم يتم الارسال</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>1776274927000</v>
+        <v>1776327979000</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2044471339784810653</t>
+          <t>2044375431952867780</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -4057,7 +4112,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+          <t>{'name': 'AHMARI', 'screenName': 'msa3474', 'followersCount': 36, 'favouritesCount': 2762, 'friendsCount': 150, 'description': ''}</t>
         </is>
       </c>
       <c r="K53" t="n">
@@ -4074,12 +4129,12 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>2044471339784810653</t>
+          <t>2044679518741205412</t>
         </is>
       </c>
     </row>
@@ -4089,46 +4144,46 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2044471339784810653</t>
+          <t>https://x.com/msa3474/status/2044694249686323218</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2044471339784810653</t>
+          <t>2044694249686323218</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2044471339784810653</t>
+          <t>2044375431952867780</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2044471339784810653</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2044375431952867780</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>احصل على فرصة الفوز بحصة من الجوائز النقدية قيمتها تصل إلى 1,000,000 درهم. كل زيادة بقيمة 100,000 درهم في حسابك المصرفي للأعمال تمنحك فرصة واحدة للدخول في السحب.
-اجعل شركتك إحدى الشركات الـ 55 الفائزة. فهل ستكون من بينها؟ https://t.co/zGFXn2y3iT</t>
+          <t>سافر لوجهتك، وقسط دفعاتها مع 0% هامش ربح ✈️
+على طيران الإمارات باستخدام بطاقات #بنك_الإمارات_دبي_الوطني الائتمانية</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>1776274926000</v>
+        <v>1776252060000</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2044471339784810653</t>
+          <t>2044375431952867780</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF9r2SlXIAA7IEH.jpg', 'type': 'photo', 'id': '2044471336295145472'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17269, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
       <c r="K54" t="n">
@@ -4145,7 +4200,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>643</t>
         </is>
       </c>
       <c r="P54" t="inlineStr"/>
@@ -4156,40 +4211,35 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2044471339784810653</t>
+          <t>https://x.com/msa3474/status/2044694249686323218</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2044471339784810653</t>
+          <t>2044694249686323218</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2044471342880170391</t>
+          <t>2044676172248690733</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2044471342880170391</t>
+          <t>https://x.com/msa3474/status/2044676172248690733</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>الجائزة النقدية الكبرى: 250,000 درهم (فائز واحد) 
-الجائزة النقدية الثانية: 100,000 درهم (فائزان اثنان)
-الجوائز النقدية الشهرية: تصل إلى 25 ألف درهم (52 فائز)
-يسري العرض لغاية 30 يونيو 2026.
-تطبق الشروط والأحكام.
-https://t.co/RWuJWfhfUm</t>
+          <t>@EmiratesNBD_KSA السلام عليكم ورحمه الله وبركاته الساده بنك الإمارات دبي الوطني المحترمين الرجاء حل مشكلتي مع فرع شارع الامير سلطان بجدة حيث انني طلبت منهم إيصال سداد مديونية ولي الى الآن اسبوع كامل لم يصلني الرد.</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>1776274927000</v>
+        <v>1776323762000</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2044471339784810653</t>
+          <t>2044375431952867780</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -4199,11 +4249,11 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+          <t>{'name': 'AHMARI', 'screenName': 'msa3474', 'followersCount': 36, 'favouritesCount': 2762, 'friendsCount': 150, 'description': ''}</t>
         </is>
       </c>
       <c r="K55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
@@ -4216,12 +4266,12 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>73</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>2044471339784810653</t>
+          <t>2044375431952867780</t>
         </is>
       </c>
     </row>
@@ -4231,51 +4281,49 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2044471339784810653</t>
+          <t>https://x.com/msa3474/status/2044694249686323218</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2044471339784810653</t>
+          <t>2044694249686323218</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2044322412007735394</t>
+          <t>2044679518741205412</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2044322412007735394</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2044679518741205412</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Invest in gold and silver, easily and digitally with the EI + Mobile Banking App
-⭐️Access the Wealth tab through the EI + Mobile Banking App and start investing securely and seamlessly.
-⭐️Shariah-compliant offering https://t.co/lsN56x6Joc</t>
+          <t>@msa3474 مرحباً، نأسف لسماع أنك تواجه تجربة غير سارة. يسعدنا مساعدتك وحلها. يُرجى إرسال التفاصيل الخاصه بشكواك إلى رسائل الخاص حتي نتمكن من مساعدتك بشكل أفضل</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>1776239419000</v>
+        <v>1776324560000</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2044322412007735394</t>
+          <t>2044375431952867780</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF7kZnMXwAAJGag.jpg', 'type': 'photo', 'id': '2044322409541517312'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17269, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
       <c r="K56" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
@@ -4284,14 +4332,18 @@
         <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>204</t>
-        </is>
-      </c>
-      <c r="P56" t="inlineStr"/>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>2044676172248690733</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
@@ -4299,51 +4351,49 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2044471329382900119</t>
+          <t>https://x.com/msa3474/status/2044694249686323218</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2044471329382900119</t>
+          <t>2044694249686323218</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2044471327159996698</t>
+          <t>2044694249686323218</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2044471327159996698</t>
+          <t>https://x.com/msa3474/status/2044694249686323218</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Get a chance to win a total of AED 1,000,000 in cash prizes! Every AED 100,000 increase in your Business Banking account earns you one entry into the draw.
-55 businesses will be winners. Will you be one of them?
-Grand cash prize: AED 250,000 (1 winner) https://t.co/PtTMEJsQ5k</t>
+          <t>@EmiratesNBD_KSA الرجاء إرسال رسالة خاصة لكي ارد عليكم</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>1776274923000</v>
+        <v>1776328072000</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2044471327159996698</t>
+          <t>2044375431952867780</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF9r1lyXAAANAJs.jpg', 'type': 'photo', 'id': '2044471324270067712'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+          <t>{'name': 'AHMARI', 'screenName': 'msa3474', 'followersCount': 36, 'favouritesCount': 2762, 'friendsCount': 150, 'description': ''}</t>
         </is>
       </c>
       <c r="K57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
@@ -4356,10 +4406,14 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="P57" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>2044679518741205412</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
@@ -4367,73 +4421,66 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2044471329382900119</t>
+          <t>https://x.com/gulf_news/status/2044683879332589921</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2044471329382900119</t>
+          <t>2044683879332589921</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2044471329382900119</t>
+          <t>2044683879332589921</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2044471329382900119</t>
+          <t>https://x.com/gulf_news/status/2044683879332589921</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Second cash prize: AED 100,000 each (2 winners)
-Monthly cash prizes: up to AED 25,000 (52 winners)
-Valid until 30 June 2026.
-Terms and conditions apply.
-https://t.co/FsXr2qXw7K</t>
+          <t>Dubai opens earlier mortgage access for off-plan buyers as Dubai Holding Real Estate and Emirates NBD integrate financing at booking to boost homeownership.
+https://t.co/xizzcnP3Fc https://t.co/kKhMWzTJhW</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>1776274924000</v>
+        <v>1776325599000</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2044471327159996698</t>
+          <t>2044683879332589921</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGAtIjiXsAA97M-.jpg', 'type': 'photo', 'id': '2044683855827808256'}]</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+          <t>{'name': 'Gulf News', 'screenName': 'gulf_news', 'followersCount': 1535686, 'favouritesCount': 1073, 'friendsCount': 412, 'description': "We don't just cover the news - we uncover the truth. The official Twitter feed from Gulf News."}</t>
         </is>
       </c>
       <c r="K58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>2044471327159996698</t>
-        </is>
-      </c>
+          <t>19046</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
@@ -4441,67 +4488,69 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2044471327159996698</t>
+          <t>https://x.com/gulf_news/status/2044683879332589921</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2044471327159996698</t>
+          <t>2044683879332589921</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2044471327159996698</t>
+          <t>2044695927689298408</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2044471327159996698</t>
+          <t>https://x.com/moazzamhusain/status/2044695927689298408</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Get a chance to win a total of AED 1,000,000 in cash prizes! Every AED 100,000 increase in your Business Banking account earns you one entry into the draw.
-55 businesses will be winners. Will you be one of them?
-Grand cash prize: AED 250,000 (1 winner) https://t.co/PtTMEJsQ5k</t>
+          <t>@gulf_news This is the kind of stimulus which is needed in times like these. It is an initiative to spur demand which lowers the entry threshold for new buyers.</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>1776274923000</v>
+        <v>1776328472000</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2044471327159996698</t>
+          <t>2044683879332589921</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF9r1lyXAAANAJs.jpg', 'type': 'photo', 'id': '2044471324270067712'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+          <t>{'name': 'Dubai: The Fall', 'screenName': 'moazzamhusain', 'followersCount': 730, 'favouritesCount': 2410, 'friendsCount': 362, 'description': 'Author of the novel Dubai: The Fall — written while the Gulf war was unfolding\n30-page preview: https://t.co/WuUVMf9X4O\nPre-order on Amazon"'}</t>
         </is>
       </c>
       <c r="K59" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" t="n">
         <v>1</v>
       </c>
-      <c r="L59" t="n">
-        <v>0</v>
-      </c>
-      <c r="M59" t="n">
-        <v>0</v>
-      </c>
-      <c r="N59" t="n">
-        <v>0</v>
-      </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="P59" t="inlineStr"/>
+          <t>395</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>2044683879332589921</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
@@ -4509,73 +4558,65 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2044471327159996698</t>
+          <t>https://x.com/gulf_news/status/2044683879332589921</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2044471327159996698</t>
+          <t>2044683879332589921</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2044471329382900119</t>
+          <t>2044497028701401307</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2044471329382900119</t>
+          <t>https://x.com/center_getfit/status/2044497028701401307</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Second cash prize: AED 100,000 each (2 winners)
-Monthly cash prizes: up to AED 25,000 (52 winners)
-Valid until 30 June 2026.
-Terms and conditions apply.
-https://t.co/FsXr2qXw7K</t>
+          <t>Best Foods High in Fiber https://t.co/j3Qv2TBkZl</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>1776274924000</v>
+        <v>1776281051000</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2044471327159996698</t>
+          <t>2044497028701401307</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF-DJe1bEAAXDXT.jpg', 'type': 'photo', 'id': '2044496954768691200'}]</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+          <t>{'name': 'GetFIT CENTER', 'screenName': 'center_getfit', 'followersCount': 112725, 'favouritesCount': 20023, 'friendsCount': 25, 'description': 'Sharing home/gym workouts as well as nutritional nuggets to create sustainable solutions for lasting health, wellness and confidence to help you Get FIT.'}</t>
         </is>
       </c>
       <c r="K60" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>302</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="P60" t="inlineStr">
-        <is>
-          <t>2044471327159996698</t>
-        </is>
-      </c>
+          <t>8626</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
@@ -4583,50 +4624,53 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2044471327159996698</t>
+          <t>https://x.com/proptglobal/status/2044676629453213871</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2044471327159996698</t>
+          <t>2044676629453213871</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2044471339784810653</t>
+          <t>2044676629453213871</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2044471339784810653</t>
+          <t>https://x.com/proptglobal/status/2044676629453213871</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>احصل على فرصة الفوز بحصة من الجوائز النقدية قيمتها تصل إلى 1,000,000 درهم. كل زيادة بقيمة 100,000 درهم في حسابك المصرفي للأعمال تمنحك فرصة واحدة للدخول في السحب.
-اجعل شركتك إحدى الشركات الـ 55 الفائزة. فهل ستكون من بينها؟ https://t.co/zGFXn2y3iT</t>
+          <t>Dubai Holding Real Estate and Emirates NBD just teamed up to revolutionize off-plan mortgage financing🤝
+🔗Download the Propt!
+Appstore: https://t.co/sq8ARTKsof
+Playstore: https://t.co/Ju874t2DvN
+#HomeBuying #EmiratesNBD https://t.co/dSn1Zqufyh</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>1776274926000</v>
+        <v>1776323871000</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2044471339784810653</t>
+          <t>2044676629453213871</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF9r2SlXIAA7IEH.jpg', 'type': 'photo', 'id': '2044471336295145472'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGAmPfMa4AAvqEp.jpg', 'type': 'photo', 'id': '2044676278339690496'}]</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+          <t>{'name': 'PROPT', 'screenName': 'proptglobal', 'followersCount': 8, 'favouritesCount': 5, 'friendsCount': 6, 'description': 'Daily real estate news, project launches &amp; market insights | Covering UAE, KSA, Qatar, Bahrain, Oman &amp; Kuwait | Your trusted real estate news source'}</t>
         </is>
       </c>
       <c r="K61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
@@ -4639,7 +4683,7 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P61" t="inlineStr"/>
@@ -4650,51 +4694,53 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2044322414310367621</t>
+          <t>https://x.com/proptglobal/status/2044676629453213871</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2044322414310367621</t>
+          <t>2044676629453213871</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2044322412007735394</t>
+          <t>2044785383930777925</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2044322412007735394</t>
+          <t>https://x.com/proptglobal/status/2044785383930777925</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Invest in gold and silver, easily and digitally with the EI + Mobile Banking App
-⭐️Access the Wealth tab through the EI + Mobile Banking App and start investing securely and seamlessly.
-⭐️Shariah-compliant offering https://t.co/lsN56x6Joc</t>
+          <t>Don’t miss out on Abu Dhabi’s booming real estate market! 🚀
+🔗Download the Propt
+Appstore: https://t.co/sq8ARTKsof
+Playstore: https://t.co/Ju874t2DvN
+#GoldenVisa #YasIsland https://t.co/70xvtvnexQ</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>1776239419000</v>
+        <v>1776349800000</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2044322412007735394</t>
+          <t>2044785383930777925</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF7kZnMXwAAJGag.jpg', 'type': 'photo', 'id': '2044322409541517312'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGB9fBKbQAAKUii.jpg', 'type': 'photo', 'id': '2044772202667786240'}]</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+          <t>{'name': 'PROPT', 'screenName': 'proptglobal', 'followersCount': 8, 'favouritesCount': 5, 'friendsCount': 6, 'description': 'Daily real estate news, project launches &amp; market insights | Covering UAE, KSA, Qatar, Bahrain, Oman &amp; Kuwait | Your trusted real estate news source'}</t>
         </is>
       </c>
       <c r="K62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
@@ -4707,7 +4753,7 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P62" t="inlineStr"/>
@@ -4718,38 +4764,36 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2044322414310367621</t>
+          <t>https://x.com/msa3474/status/2044676172248690733</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2044322414310367621</t>
+          <t>2044676172248690733</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2044322414310367621</t>
+          <t>2044375431952867780</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2044322414310367621</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2044375431952867780</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>⭐️Certified gold bars meeting London Bullion Market Association (LBMA) and Dubai Good Delivery (DGD) standards
-⭐️Certified silver bars compliant with UAE Good Delivery (UAE GD) standards
-Terms and conditions apply.
-https://t.co/w5RtLlrqm8</t>
+          <t>سافر لوجهتك، وقسط دفعاتها مع 0% هامش ربح ✈️
+على طيران الإمارات باستخدام بطاقات #بنك_الإمارات_دبي_الوطني الائتمانية</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>1776239419000</v>
+        <v>1776252060000</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2044322412007735394</t>
+          <t>2044375431952867780</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4759,11 +4803,11 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17269, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
       <c r="K63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
@@ -4772,18 +4816,14 @@
         <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>142</t>
-        </is>
-      </c>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t>2044322412007735394</t>
-        </is>
-      </c>
+          <t>643</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
@@ -4791,48 +4831,45 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2044322401052250291</t>
+          <t>https://x.com/msa3474/status/2044676172248690733</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2044322401052250291</t>
+          <t>2044676172248690733</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2044322401052250291</t>
+          <t>2044676172248690733</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2044322401052250291</t>
+          <t>https://x.com/msa3474/status/2044676172248690733</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>استثمر في الذهب والفضة رقمياً وبكل سهولة على تطبيق
-EI + للخدمات المصرفية عبر الهاتف المتحرك
-⭐️ادخل إلى منصة "الثروات" في تطبيق + EI  للخدمات المصرفية عبر الهاتف المتحرك وابدأ في لاستثمار بمنتهى السهولة والأمان.
-⭐️منتج متوافق مع أحكام الشريعة الإسلامية https://t.co/CZe51naJfQ</t>
+          <t>@EmiratesNBD_KSA السلام عليكم ورحمه الله وبركاته الساده بنك الإمارات دبي الوطني المحترمين الرجاء حل مشكلتي مع فرع شارع الامير سلطان بجدة حيث انني طلبت منهم إيصال سداد مديونية ولي الى الآن اسبوع كامل لم يصلني الرد.</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>1776239416000</v>
+        <v>1776323762000</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2044322401052250291</t>
+          <t>2044375431952867780</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF7kY9tWoAAk87F.jpg', 'type': 'photo', 'id': '2044322398405566464'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+          <t>{'name': 'AHMARI', 'screenName': 'msa3474', 'followersCount': 36, 'favouritesCount': 2762, 'friendsCount': 150, 'description': ''}</t>
         </is>
       </c>
       <c r="K64" t="n">
@@ -4845,14 +4882,18 @@
         <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>202</t>
-        </is>
-      </c>
-      <c r="P64" t="inlineStr"/>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>2044375431952867780</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
@@ -4860,38 +4901,35 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2044322401052250291</t>
+          <t>https://x.com/msa3474/status/2044676172248690733</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2044322401052250291</t>
+          <t>2044676172248690733</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2044322403761697193</t>
+          <t>2044679518741205412</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2044322403761697193</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2044679518741205412</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>⭐️سبائك ذهب معتمدة ومطابقة لمعايير جمعية سوق لندن للسبائك ودبي للتسليم الجيد
-⭐️سبائك فضة معتمدة ومتوافقة مع معايير الإمارات للتسليم الجيد
-تطبق الشروط والأحكام.
-https://t.co/WN0tZk19JS</t>
+          <t>@msa3474 مرحباً، نأسف لسماع أنك تواجه تجربة غير سارة. يسعدنا مساعدتك وحلها. يُرجى إرسال التفاصيل الخاصه بشكواك إلى رسائل الخاص حتي نتمكن من مساعدتك بشكل أفضل</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>1776239417000</v>
+        <v>1776324560000</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2044322401052250291</t>
+          <t>2044375431952867780</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4901,11 +4939,11 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17269, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
       <c r="K65" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
@@ -4918,12 +4956,12 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>19</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>2044322401052250291</t>
+          <t>2044676172248690733</t>
         </is>
       </c>
     </row>
@@ -4933,52 +4971,51 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2044322403761697193</t>
+          <t>https://x.com/talent_folder/status/2044662520884179409</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2044322403761697193</t>
+          <t>2044662520884179409</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2044322401052250291</t>
+          <t>2044662520884179409</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2044322401052250291</t>
+          <t>https://x.com/talent_folder/status/2044662520884179409</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>استثمر في الذهب والفضة رقمياً وبكل سهولة على تطبيق
-EI + للخدمات المصرفية عبر الهاتف المتحرك
-⭐️ادخل إلى منصة "الثروات" في تطبيق + EI  للخدمات المصرفية عبر الهاتف المتحرك وابدأ في لاستثمار بمنتهى السهولة والأمان.
-⭐️منتج متوافق مع أحكام الشريعة الإسلامية https://t.co/CZe51naJfQ</t>
+          <t>Open Your Bank Account in Dubai Easily
+Looking to open a bank account in Dubai? We make it simple, fast, and stress-free!
+Whether you're a resident, investor, or business owner, our experts help you open accounts with top UAE banks like ADCB, FAB, Emirates NBD, and more. https://t.co/pae9jOcrIr</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>1776239416000</v>
+        <v>1776320507000</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2044322401052250291</t>
+          <t>2044662520884179409</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF7kY9tWoAAk87F.jpg', 'type': 'photo', 'id': '2044322398405566464'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGAZlV4aUAA3ZQl.jpg', 'type': 'photo', 'id': '2044662360145809408'}]</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+          <t>{'name': 'Talentfolder', 'screenName': 'talent_folder', 'followersCount': 9, 'favouritesCount': 9, 'friendsCount': 9, 'description': 'Our Resources Are Everything.'}</t>
         </is>
       </c>
       <c r="K66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
@@ -4987,11 +5024,11 @@
         <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>24</t>
         </is>
       </c>
       <c r="P66" t="inlineStr"/>
@@ -5002,48 +5039,50 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2044322403761697193</t>
+          <t>https://x.com/talent_folder/status/2044662520884179409</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2044322403761697193</t>
+          <t>2044662520884179409</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2044322403761697193</t>
+          <t>2044348407981228451</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2044322403761697193</t>
+          <t>https://x.com/talent_folder/status/2044348407981228451</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>⭐️سبائك ذهب معتمدة ومطابقة لمعايير جمعية سوق لندن للسبائك ودبي للتسليم الجيد
-⭐️سبائك فضة معتمدة ومتوافقة مع معايير الإمارات للتسليم الجيد
-تطبق الشروط والأحكام.
-https://t.co/WN0tZk19JS</t>
+          <t>At Talentfolder, we wish you and your loved ones a joyful and blessed Vishu! 🌼💛
+Let this new beginning open doors to success and brighter futures.
++971 52 158 3672
++971 58 513 8291
+https://t.co/npKFNyRFVV
+#HappyVishu #Vishu2026 #VishuCelebration #KeralaFestival #NewBeginnings https://t.co/tnPPiy9Gym</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>1776239417000</v>
+        <v>1776245617000</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2044322401052250291</t>
+          <t>2044348407981228451</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF77-aXbsAETo6U.jpg', 'type': 'photo', 'id': '2044348330520850433'}]</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+          <t>{'name': 'Talentfolder', 'screenName': 'talent_folder', 'followersCount': 9, 'favouritesCount': 9, 'friendsCount': 9, 'description': 'Our Resources Are Everything.'}</t>
         </is>
       </c>
       <c r="K67" t="n">
@@ -5060,14 +5099,10 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="P67" t="inlineStr">
-        <is>
-          <t>2044322401052250291</t>
-        </is>
-      </c>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
@@ -5075,51 +5110,51 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2044322412007735394</t>
+          <t>https://x.com/khushbuag88/status/2044659603196231971</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2044322412007735394</t>
+          <t>2044659603196231971</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2044322412007735394</t>
+          <t>2044657039834550600</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2044322412007735394</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2044657039834550600</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Invest in gold and silver, easily and digitally with the EI + Mobile Banking App
-⭐️Access the Wealth tab through the EI + Mobile Banking App and start investing securely and seamlessly.
-⭐️Shariah-compliant offering https://t.co/lsN56x6Joc</t>
+          <t>ليست كل أنواع الفوائد متشابهة — فبعضها بسيط.
+هل تستطيع تسمية هذا النوع؟ شاركنا إجابتك.
+#لغز_الأسبوع_ENBD #أساسيات_المال #تعلم_المالية https://t.co/gAgAYclmU0</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>1776239419000</v>
+        <v>1776319200000</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2044322412007735394</t>
+          <t>2044657039834550600</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF7kZnMXwAAJGag.jpg', 'type': 'photo', 'id': '2044322409541517312'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF7Zip7WsAAdNSe.jpg', 'type': 'photo', 'id': '2044310470266368000'}]</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174080, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="K68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
@@ -5128,11 +5163,11 @@
         <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>423</t>
         </is>
       </c>
       <c r="P68" t="inlineStr"/>
@@ -5143,38 +5178,35 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2044322412007735394</t>
+          <t>https://x.com/khushbuag88/status/2044659603196231971</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2044322412007735394</t>
+          <t>2044659603196231971</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2044322414310367621</t>
+          <t>2044659603196231971</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2044322414310367621</t>
+          <t>https://x.com/khushbuag88/status/2044659603196231971</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>⭐️Certified gold bars meeting London Bullion Market Association (LBMA) and Dubai Good Delivery (DGD) standards
-⭐️Certified silver bars compliant with UAE Good Delivery (UAE GD) standards
-Terms and conditions apply.
-https://t.co/w5RtLlrqm8</t>
+          <t>@EmiratesNBD_AE الإجابة هي الفائدة البسيطة #لغز_الأسبوع_للحاصلين_على_شهادة_الهندسة_المدنية #تعلم_المالية #أساسيات_المال</t>
         </is>
       </c>
       <c r="G69" t="n">
-        <v>1776239419000</v>
+        <v>1776319811000</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2044322412007735394</t>
+          <t>2044657039834550600</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -5184,7 +5216,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+          <t>{'name': 'Khushbu Agarwal', 'screenName': 'khushbuag88', 'followersCount': 13, 'favouritesCount': 376, 'friendsCount': 77, 'description': ''}</t>
         </is>
       </c>
       <c r="K69" t="n">
@@ -5201,12 +5233,12 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>2044322412007735394</t>
+          <t>2044657039834550600</t>
         </is>
       </c>
     </row>
@@ -5216,50 +5248,51 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2044322412007735394</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2044675073445871906</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2044322412007735394</t>
+          <t>2044675073445871906</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2044471339784810653</t>
+          <t>2044675073445871906</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2044471339784810653</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2044675073445871906</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>احصل على فرصة الفوز بحصة من الجوائز النقدية قيمتها تصل إلى 1,000,000 درهم. كل زيادة بقيمة 100,000 درهم في حسابك المصرفي للأعمال تمنحك فرصة واحدة للدخول في السحب.
-اجعل شركتك إحدى الشركات الـ 55 الفائزة. فهل ستكون من بينها؟ https://t.co/zGFXn2y3iT</t>
+          <t>We at Emirates NBD are on a mission to make financial wellness truly inclusive. On our recent visit to a women accommodation camp in the UAE, we introduced them to everything finance, from budgeting to saving. Interactive sessions, quizzes, prizes, an evening well spent.
+Catch the action here.
+https://t.co/UAuXxgtnH8</t>
         </is>
       </c>
       <c r="G70" t="n">
-        <v>1776274926000</v>
+        <v>1776323500000</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2044471339784810653</t>
+          <t>2044675073445871906</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF9r2SlXIAA7IEH.jpg', 'type': 'photo', 'id': '2044471336295145472'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2044674915350024192/img/-pcw_C3KhbKzMlgK.jpg', 'type': 'video', 'id': '2044674915350024192'}]</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174080, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="K70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
@@ -5268,11 +5301,11 @@
         <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>433</t>
         </is>
       </c>
       <c r="P70" t="inlineStr"/>
@@ -5283,64 +5316,64 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2044294656716836969</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2044675073445871906</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2044294656716836969</t>
+          <t>2044675073445871906</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2044294653097156714</t>
+          <t>2044657039872245768</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2044294653097156714</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2044657039872245768</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>من “يوماً ما” إلى يوم الانتقال!
-التمويل السكني من الإمارات الإسلامي يجعل حلم امتلاك منزلك حقيقة، مع المرونة والوضوح في كل خطوة من رحلتك.
-استمتع بحلول تمويلية مصممة خصيصاً لك، ودعم متكامل طوال الطريق، لتصبح تجربة امتلاك المنزل سلسة وميسرة.</t>
+          <t>Not all interests work the same way — some are simple.
+Can you name this type? Comment your answer.
+#ENBDRiddleOfTheWeek #MoneyBasics #LearnFinance https://t.co/05i14Flw98</t>
         </is>
       </c>
       <c r="G71" t="n">
-        <v>1776232801000</v>
+        <v>1776319200000</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2044294653097156714</t>
+          <t>2044657039872245768</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF8tUJpWsAAqygG.jpg', 'type': 'photo', 'id': '2044402580059500544'}]</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174080, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="K71" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L71" t="n">
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>195</t>
+          <t>478</t>
         </is>
       </c>
       <c r="P71" t="inlineStr"/>
@@ -5351,70 +5384,66 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2044294656716836969</t>
+          <t>https://x.com/CBN_ME/status/2044654528956682747</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2044294656716836969</t>
+          <t>2044654528956682747</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2044294656716836969</t>
+          <t>2044654528956682747</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2044294656716836969</t>
+          <t>https://x.com/CBN_ME/status/2044654528956682747</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>ابدأ رحلتك نحو منزل أحلامك اليوم.
-https://t.co/lQDtk9615Y</t>
+          <t>@dubaiholding and @EmiratesNBD_AE have signed an MoU to introduce integrated mortgage solutions for off-plan homes across @MeraasDubai, @NakheelOfficial and @DubaiProperties.
+https://t.co/NE9RbJAFPP https://t.co/P6urCIn0qy</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>1776232801000</v>
+        <v>1776318602000</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2044294653097156714</t>
+          <t>2044654528956682747</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGASVLrbwAAP6Tv.jpg', 'type': 'photo', 'id': '2044654385947721728'}]</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+          <t>{'name': 'Construction Business News ME', 'screenName': 'CBN_ME', 'followersCount': 5147, 'favouritesCount': 2782, 'friendsCount': 1391, 'description': 'Construction Business News ME - A definitive guide for the region’s construction professionals.'}</t>
         </is>
       </c>
       <c r="K72" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" t="n">
+        <v>0</v>
+      </c>
+      <c r="M72" t="n">
         <v>1</v>
       </c>
-      <c r="L72" t="n">
-        <v>0</v>
-      </c>
-      <c r="M72" t="n">
-        <v>0</v>
-      </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>127</t>
-        </is>
-      </c>
-      <c r="P72" t="inlineStr">
-        <is>
-          <t>2044294653097156714</t>
-        </is>
-      </c>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
@@ -5422,49 +5451,46 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2044294656716836969</t>
+          <t>https://x.com/CBN_ME/status/2044654528956682747</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2044294656716836969</t>
+          <t>2044654528956682747</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2044294659795513346</t>
+          <t>2044745005173252374</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2044294659795513346</t>
+          <t>https://x.com/CBN_ME/status/2044745005173252374</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>From “one day” to move-in day.
-Emirates Islamic Home Finance helps turn home ownership into reality, with the flexibility and clarity you need at every step.
-With tailored finance solutions and guided support throughout,
-Your home journey starts here.
-https://t.co/XwkOLamNf0</t>
+          <t>We are pleased to announce Turab Saleem, CEO, Perfetti Hospitality, as a speaker on Panel 3: Saudi Arabia’s Leisure and Hospitality Boom Opportunities, Challenges, and the Visitor Experience.
+https://t.co/hBAGIgH1Ju https://t.co/3sWGnco48j</t>
         </is>
       </c>
       <c r="G73" t="n">
-        <v>1776232802000</v>
+        <v>1776340173000</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2044294653097156714</t>
+          <t>2044745005173252374</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGBktEnbcAAo6bx.jpg', 'type': 'photo', 'id': '2044744956322213888'}]</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+          <t>{'name': 'Construction Business News ME', 'screenName': 'CBN_ME', 'followersCount': 5147, 'favouritesCount': 2782, 'friendsCount': 1391, 'description': 'Construction Business News ME - A definitive guide for the region’s construction professionals.'}</t>
         </is>
       </c>
       <c r="K73" t="n">
@@ -5477,18 +5503,14 @@
         <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="P73" t="inlineStr">
-        <is>
-          <t>2044294656716836969</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
@@ -5496,64 +5518,64 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2044294653097156714</t>
+          <t>https://x.com/khushbuag88/status/2044659438011961784</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2044294653097156714</t>
+          <t>2044659438011961784</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2044294653097156714</t>
+          <t>2044657039872245768</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2044294653097156714</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2044657039872245768</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>من “يوماً ما” إلى يوم الانتقال!
-التمويل السكني من الإمارات الإسلامي يجعل حلم امتلاك منزلك حقيقة، مع المرونة والوضوح في كل خطوة من رحلتك.
-استمتع بحلول تمويلية مصممة خصيصاً لك، ودعم متكامل طوال الطريق، لتصبح تجربة امتلاك المنزل سلسة وميسرة.</t>
+          <t>Not all interests work the same way — some are simple.
+Can you name this type? Comment your answer.
+#ENBDRiddleOfTheWeek #MoneyBasics #LearnFinance https://t.co/05i14Flw98</t>
         </is>
       </c>
       <c r="G74" t="n">
-        <v>1776232801000</v>
+        <v>1776319200000</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2044294653097156714</t>
+          <t>2044657039872245768</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF8tUJpWsAAqygG.jpg', 'type': 'photo', 'id': '2044402580059500544'}]</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174080, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="K74" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L74" t="n">
         <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>195</t>
+          <t>478</t>
         </is>
       </c>
       <c r="P74" t="inlineStr"/>
@@ -5564,36 +5586,35 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2044294653097156714</t>
+          <t>https://x.com/khushbuag88/status/2044659438011961784</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2044294653097156714</t>
+          <t>2044659438011961784</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2044294656716836969</t>
+          <t>2044659438011961784</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2044294656716836969</t>
+          <t>https://x.com/khushbuag88/status/2044659438011961784</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>ابدأ رحلتك نحو منزل أحلامك اليوم.
-https://t.co/lQDtk9615Y</t>
+          <t>@EmiratesNBD_AE Answer is Simple Interest     #ENBDRiddleOfTheWeek   #LearnFinance #MoneyBasics</t>
         </is>
       </c>
       <c r="G75" t="n">
-        <v>1776232801000</v>
+        <v>1776319772000</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2044294653097156714</t>
+          <t>2044657039872245768</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5603,11 +5624,11 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+          <t>{'name': 'Khushbu Agarwal', 'screenName': 'khushbuag88', 'followersCount': 13, 'favouritesCount': 376, 'friendsCount': 77, 'description': ''}</t>
         </is>
       </c>
       <c r="K75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L75" t="n">
         <v>0</v>
@@ -5620,12 +5641,12 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>2044294653097156714</t>
+          <t>2044657039872245768</t>
         </is>
       </c>
     </row>
@@ -5635,46 +5656,46 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2044294653097156714</t>
+          <t>https://x.com/AdityaD_Shah/status/2044647851410817502</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2044294653097156714</t>
+          <t>2044647851410817502</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2044471339784810653</t>
+          <t>2044647851410817502</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2044471339784810653</t>
+          <t>https://x.com/AdityaD_Shah/status/2044647851410817502</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>احصل على فرصة الفوز بحصة من الجوائز النقدية قيمتها تصل إلى 1,000,000 درهم. كل زيادة بقيمة 100,000 درهم في حسابك المصرفي للأعمال تمنحك فرصة واحدة للدخول في السحب.
-اجعل شركتك إحدى الشركات الـ 55 الفائزة. فهل ستكون من بينها؟ https://t.co/zGFXn2y3iT</t>
+          <t>Can Emirates NBD really change the fortunes of RBL Bank?
+The market really thinks so! https://t.co/EBFkHPBULm</t>
         </is>
       </c>
       <c r="G76" t="n">
-        <v>1776274926000</v>
+        <v>1776317010000</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2044471339784810653</t>
+          <t>2044647851410817502</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF9r2SlXIAA7IEH.jpg', 'type': 'photo', 'id': '2044471336295145472'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGAMQtfbsAEtw9n.jpg', 'type': 'photo', 'id': '2044647712055078913'}]</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+          <t>{'name': 'Aditya Shah', 'screenName': 'AdityaD_Shah', 'followersCount': 132977, 'favouritesCount': 23780, 'friendsCount': 638, 'description': 'Founder Hercules Advisors-Stocks,Financial Planning,Insurance and Mutual funds\n\nDM us for enquiries, or email at adityashah291@gmail.com'}</t>
         </is>
       </c>
       <c r="K76" t="n">
@@ -5684,17 +5705,3618 @@
         <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N76" t="n">
+        <v>57</v>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>6188</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="n">
+        <v>75</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>https://x.com/AdityaD_Shah/status/2044647851410817502</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>2044647851410817502</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2044660823801659442</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>https://x.com/Bunti2725/status/2044660823801659442</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>@AdityaD_Shah They will only survive with this funding. Because big banks are tightening competition.</t>
+        </is>
+      </c>
+      <c r="G77" t="n">
+        <v>1776320103000</v>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>2044647851410817502</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>{'name': 'SB', 'screenName': 'Bunti2725', 'followersCount': 225, 'favouritesCount': 99489, 'friendsCount': 1867, 'description': ''}</t>
+        </is>
+      </c>
+      <c r="K77" t="n">
+        <v>0</v>
+      </c>
+      <c r="L77" t="n">
+        <v>0</v>
+      </c>
+      <c r="M77" t="n">
+        <v>0</v>
+      </c>
+      <c r="N77" t="n">
+        <v>0</v>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>2044647851410817502</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="n">
+        <v>76</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>https://x.com/AdityaD_Shah/status/2044647851410817502</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>2044647851410817502</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>2044790855731675313</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>https://x.com/CNBCTV18Live/status/2044790855731675313</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>#4QWithCNBCTV18 | #AngelOne Announces Its Q4 Results;
+📈Net Profit Up 83.5% At ₹320 Cr Vs ₹175 Cr (YoY)
+📈Revenue Up 38.2% At ₹1,459 Cr Vs ₹1,056 Cr (YoY)
+📈EBITDA Up 74.6% At ₹598 Cr Vs ₹343 Cr (YoY)
+📈Margin At 41% Vs 32% (YoY)
+📈To Raise Funds Via NCDs Up To ₹1,500 Cr</t>
+        </is>
+      </c>
+      <c r="G78" t="n">
+        <v>1776351105000</v>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>2044790855731675313</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGCN1mVaEAIceSo.jpg', 'type': 'photo', 'id': '2044790182789124098'}]</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>{'name': 'CNBC-TV18', 'screenName': 'CNBCTV18Live', 'followersCount': 1419247, 'favouritesCount': 239, 'friendsCount': 532, 'description': 'The CNBC-TV18 news ticker on Twitter. The news breaks here first.\n\nWhatsApp:  https://t.co/7R212M4izl'}</t>
+        </is>
+      </c>
+      <c r="K78" t="n">
+        <v>4</v>
+      </c>
+      <c r="L78" t="n">
+        <v>4</v>
+      </c>
+      <c r="M78" t="n">
+        <v>22</v>
+      </c>
+      <c r="N78" t="n">
+        <v>228</v>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>23855</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="n">
+        <v>77</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>https://x.com/DustshotW/status/2044612515498496366</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>2044612515498496366</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2044517451078197394</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>https://x.com/DustshotW/status/2044517451078197394</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>anyone.....olease ......</t>
+        </is>
+      </c>
+      <c r="G79" t="n">
+        <v>1776285920000</v>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>2044517451078197394</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>{'name': 'justice gaming', 'screenName': 'DustshotW', 'followersCount': 1081, 'favouritesCount': 25654, 'friendsCount': 229, 'description': 'call me justice or 正凱 // 中文/English // 🇭🇰// i do like nothing but draw yuri\n\nhttps://t.co/wisNUqvSX2'}</t>
+        </is>
+      </c>
+      <c r="K79" t="n">
+        <v>5</v>
+      </c>
+      <c r="L79" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" t="n">
+        <v>0</v>
+      </c>
+      <c r="N79" t="n">
+        <v>11</v>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>485</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="n">
+        <v>78</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>https://x.com/DustshotW/status/2044612515498496366</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>2044612515498496366</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2044610910640361699</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>https://x.com/dorienotfish/status/2044610910640361699</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>@DustshotW can i try</t>
+        </is>
+      </c>
+      <c r="G80" t="n">
+        <v>1776308202000</v>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>2044517451078197394</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>{'name': 'dorion', 'screenName': 'dorienotfish', 'followersCount': 69, 'favouritesCount': 40093, 'friendsCount': 524, 'description': 'steine sind steine ohne rotes blut'}</t>
+        </is>
+      </c>
+      <c r="K80" t="n">
         <v>1</v>
       </c>
-      <c r="O76" t="inlineStr">
-        <is>
-          <t>148</t>
-        </is>
-      </c>
-      <c r="P76" t="inlineStr"/>
+      <c r="L80" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" t="n">
+        <v>0</v>
+      </c>
+      <c r="N80" t="n">
+        <v>0</v>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>2044517451078197394</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="n">
+        <v>79</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>https://x.com/DustshotW/status/2044612515498496366</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>2044612515498496366</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2044612515498496366</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>https://x.com/DustshotW/status/2044612515498496366</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>@dorienotfish s enbd</t>
+        </is>
+      </c>
+      <c r="G81" t="n">
+        <v>1776308585000</v>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>2044517451078197394</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>{'name': 'justice gaming', 'screenName': 'DustshotW', 'followersCount': 1081, 'favouritesCount': 25654, 'friendsCount': 229, 'description': 'call me justice or 正凱 // 中文/English // 🇭🇰// i do like nothing but draw yuri\n\nhttps://t.co/wisNUqvSX2'}</t>
+        </is>
+      </c>
+      <c r="K81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L81" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" t="n">
+        <v>0</v>
+      </c>
+      <c r="N81" t="n">
+        <v>0</v>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>2044610910640361699</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="n">
+        <v>80</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>https://x.com/DustshotW/status/2044612515498496366</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>2044612515498496366</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>2044613234427383893</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>https://x.com/dorienotfish/status/2044613234427383893</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>@DustshotW sorry at first i though u said 'skibdi' mb✌🏻✌🏻✌🏻 ok here https://t.co/DsboMnkCKn</t>
+        </is>
+      </c>
+      <c r="G82" t="n">
+        <v>1776308756000</v>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>2044517451078197394</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF_s4_pbAAANiPL.jpg', 'type': 'photo', 'id': '2044613219751493632'}]</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>{'name': 'dorion', 'screenName': 'dorienotfish', 'followersCount': 69, 'favouritesCount': 40093, 'friendsCount': 524, 'description': 'steine sind steine ohne rotes blut'}</t>
+        </is>
+      </c>
+      <c r="K82" t="n">
+        <v>1</v>
+      </c>
+      <c r="L82" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" t="n">
+        <v>0</v>
+      </c>
+      <c r="N82" t="n">
+        <v>0</v>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>2044612515498496366</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="n">
+        <v>81</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>https://x.com/zaydaklabhoqx/status/2044582261102956879</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>2044582261102956879</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>2029869216254341430</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>https://x.com/CryptoNewsHntrs/status/2029869216254341430</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>🚨 JUST IN: 🇦🇪 EMIRATES NBD ELIMINATES ATM WITHDRAWAL &amp;amp; DEBIT CARD FEES ACROSS THE UAE &amp;amp; GCC UNTIL MARCH 31, 2026! 💳🔥
+#UAE #EmiratesNBD #Banking #Finance #ATM #NoFees #GCC #MoneySmart https://t.co/aI9H5crVgx</t>
+        </is>
+      </c>
+      <c r="G83" t="n">
+        <v>1772793508000</v>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>2029869216254341430</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HCuLS2CXkAATb_t.jpg', 'type': 'photo', 'id': '2029869212919894016'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HCuLS2eXwAA68mZ.jpg', 'type': 'photo', 'id': '2029869213037346816'}]</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>{'name': 'Crypto News Hunters 🎯', 'screenName': 'CryptoNewsHntrs', 'followersCount': 28364, 'favouritesCount': 314750, 'friendsCount': 139, 'description': 'Crypto News 🌐 Financial Markets 📈 Memes &amp; Hopium 🔥 Not Financial Advice 🚫'}</t>
+        </is>
+      </c>
+      <c r="K83" t="n">
+        <v>5</v>
+      </c>
+      <c r="L83" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" t="n">
+        <v>20</v>
+      </c>
+      <c r="N83" t="n">
+        <v>50</v>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>744</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="n">
+        <v>82</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>https://x.com/zaydaklabhoqx/status/2044582261102956879</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>2044582261102956879</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>2044582261102956879</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>https://x.com/zaydaklabhoqx/status/2044582261102956879</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>@CryptoNewsHntrs ماذا عن مجانيّة سحب النقود؟ مبروك لعملاء Emirates NBD في الإمارات ودول الخليج</t>
+        </is>
+      </c>
+      <c r="G84" t="n">
+        <v>1776301372000</v>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>2029869216254341430</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>{'name': 'زيد أكلب', 'screenName': 'zaydaklabhoqx', 'followersCount': 30, 'favouritesCount': 313, 'friendsCount': 48, 'description': 'مدير آي تي في دبي، أحب التقنية والسيارات والكرة. أعزب ومستمتع بالحياة الفاخرة.'}</t>
+        </is>
+      </c>
+      <c r="K84" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" t="n">
+        <v>0</v>
+      </c>
+      <c r="N84" t="n">
+        <v>1</v>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>2029869216254341430</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="n">
+        <v>83</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>https://x.com/RakeshMavath/status/2044832798670995759</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>2044832798670995759</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>2044732404938702855</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>https://x.com/aaditsh/status/2044732404938702855</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>@emiratesislamic probably the worst customer experience I’ve had in my life.
+Tried cancelling my cards. Have received 10+ phone calls from them trying to retain. Confirmed each time that I want to cancel (on call and on email confirmation). It’s been 4-5 months since I raised this complaint. No resolution yet.
+Impressed with how difficult they make this process. Wow!</t>
+        </is>
+      </c>
+      <c r="G85" t="n">
+        <v>1776337169000</v>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>2044732404938702855</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>{'name': 'Aadit Sheth', 'screenName': 'aaditsh', 'followersCount': 522016, 'favouritesCount': 32068, 'friendsCount': 581, 'description': 'Co-founder, The Narrative Company. We help Fortune 500 C-suite engineer their biggest moments. Also write Neatprompts, 100K+ subscribers.'}</t>
+        </is>
+      </c>
+      <c r="K85" t="n">
+        <v>2</v>
+      </c>
+      <c r="L85" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" t="n">
+        <v>0</v>
+      </c>
+      <c r="N85" t="n">
+        <v>4</v>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>5717</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="n">
+        <v>84</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>https://x.com/RakeshMavath/status/2044832798670995759</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>2044832798670995759</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>2044758862017007662</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>https://x.com/RakeshMavath/status/2044758862017007662</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>@aaditsh @emiratesislamic especially now they are not going to let go of your business easily. you can raise the issue with UAECB who will in turn contact the bank</t>
+        </is>
+      </c>
+      <c r="G86" t="n">
+        <v>1776343477000</v>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>2044732404938702855</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>{'name': 'Rakesh Mavath', 'screenName': 'RakeshMavath', 'followersCount': 366, 'favouritesCount': 12484, 'friendsCount': 3077, 'description': 'Running two startups: one guarantees your rent @takeem_ai, the other guarantees your dignity. Still waiting for my guaranteed 8 hours of sleep.'}</t>
+        </is>
+      </c>
+      <c r="K86" t="n">
+        <v>1</v>
+      </c>
+      <c r="L86" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" t="n">
+        <v>0</v>
+      </c>
+      <c r="N86" t="n">
+        <v>1</v>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>2044732404938702855</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="n">
+        <v>85</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>https://x.com/RakeshMavath/status/2044832798670995759</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>2044832798670995759</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>2044759599656689929</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>https://x.com/aaditsh/status/2044759599656689929</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>@RakeshMavath @emiratesislamic Will do! So frustrating. They will call me, I’ll pick up. They will end the call within 10 seconds and message me “we called you. You didn’t pick up”.
+And it’s been extended like this for the past 4-5 months. What a joke.</t>
+        </is>
+      </c>
+      <c r="G87" t="n">
+        <v>1776343653000</v>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>2044732404938702855</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>{'name': 'Aadit Sheth', 'screenName': 'aaditsh', 'followersCount': 522016, 'favouritesCount': 32068, 'friendsCount': 581, 'description': 'Co-founder, The Narrative Company. We help Fortune 500 C-suite engineer their biggest moments. Also write Neatprompts, 100K+ subscribers.'}</t>
+        </is>
+      </c>
+      <c r="K87" t="n">
+        <v>1</v>
+      </c>
+      <c r="L87" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" t="n">
+        <v>0</v>
+      </c>
+      <c r="N87" t="n">
+        <v>1</v>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>2044758862017007662</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="n">
+        <v>86</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>https://x.com/RakeshMavath/status/2044832798670995759</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>2044832798670995759</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>2044832798670995759</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>https://x.com/RakeshMavath/status/2044832798670995759</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>@aaditsh @emiratesislamic Grab screenshots of when they have called you and the following messages include that to your complaint to UAECB and they will fine the bank</t>
+        </is>
+      </c>
+      <c r="G88" t="n">
+        <v>1776361105000</v>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>2044732404938702855</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>{'name': 'Rakesh Mavath', 'screenName': 'RakeshMavath', 'followersCount': 366, 'favouritesCount': 12484, 'friendsCount': 3077, 'description': 'Running two startups: one guarantees your rent @takeem_ai, the other guarantees your dignity. Still waiting for my guaranteed 8 hours of sleep.'}</t>
+        </is>
+      </c>
+      <c r="K88" t="n">
+        <v>0</v>
+      </c>
+      <c r="L88" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" t="n">
+        <v>0</v>
+      </c>
+      <c r="N88" t="n">
+        <v>0</v>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>2044759599656689929</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="n">
+        <v>87</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>https://x.com/aaditsh/status/2044784107352445179</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>2044784107352445179</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>2044732404938702855</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>https://x.com/aaditsh/status/2044732404938702855</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>@emiratesislamic probably the worst customer experience I’ve had in my life.
+Tried cancelling my cards. Have received 10+ phone calls from them trying to retain. Confirmed each time that I want to cancel (on call and on email confirmation). It’s been 4-5 months since I raised this complaint. No resolution yet.
+Impressed with how difficult they make this process. Wow!</t>
+        </is>
+      </c>
+      <c r="G89" t="n">
+        <v>1776337169000</v>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>2044732404938702855</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>{'name': 'Aadit Sheth', 'screenName': 'aaditsh', 'followersCount': 522016, 'favouritesCount': 32068, 'friendsCount': 581, 'description': 'Co-founder, The Narrative Company. We help Fortune 500 C-suite engineer their biggest moments. Also write Neatprompts, 100K+ subscribers.'}</t>
+        </is>
+      </c>
+      <c r="K89" t="n">
+        <v>2</v>
+      </c>
+      <c r="L89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N89" t="n">
+        <v>4</v>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>5718</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="n">
+        <v>88</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>https://x.com/aaditsh/status/2044784107352445179</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>2044784107352445179</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>2044781883184316706</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>https://x.com/huss23/status/2044781883184316706</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>@aaditsh @emiratesislamic I had the same issue. @emiratesislamic has the worst Customer service centre and its literally unreachable and unreliable. After 2 years of request, they still haven’t cancelled my Credit card.</t>
+        </is>
+      </c>
+      <c r="G90" t="n">
+        <v>1776348965000</v>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>2044732404938702855</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>{'name': 'Huss', 'screenName': 'huss23', 'followersCount': 105, 'favouritesCount': 5034, 'friendsCount': 291, 'description': 'Observations, Confessions, Criticism | Politics, Cricket, Books | Hates Bigotry and Extreme Views |'}</t>
+        </is>
+      </c>
+      <c r="K90" t="n">
+        <v>1</v>
+      </c>
+      <c r="L90" t="n">
+        <v>0</v>
+      </c>
+      <c r="M90" t="n">
+        <v>0</v>
+      </c>
+      <c r="N90" t="n">
+        <v>1</v>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>2044732404938702855</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="n">
+        <v>89</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>https://x.com/aaditsh/status/2044784107352445179</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>2044784107352445179</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>2044784107352445179</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>https://x.com/aaditsh/status/2044784107352445179</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>@huss23 @emiratesislamic Just unacceptable. They just auto-charge you without your permission?</t>
+        </is>
+      </c>
+      <c r="G91" t="n">
+        <v>1776349496000</v>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>2044732404938702855</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>{'name': 'Aadit Sheth', 'screenName': 'aaditsh', 'followersCount': 522016, 'favouritesCount': 32068, 'friendsCount': 581, 'description': 'Co-founder, The Narrative Company. We help Fortune 500 C-suite engineer their biggest moments. Also write Neatprompts, 100K+ subscribers.'}</t>
+        </is>
+      </c>
+      <c r="K91" t="n">
+        <v>0</v>
+      </c>
+      <c r="L91" t="n">
+        <v>0</v>
+      </c>
+      <c r="M91" t="n">
+        <v>0</v>
+      </c>
+      <c r="N91" t="n">
+        <v>0</v>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>2044781883184316706</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="n">
+        <v>90</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>https://x.com/huss23/status/2044781883184316706</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>2044781883184316706</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>2044732404938702855</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>https://x.com/aaditsh/status/2044732404938702855</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>@emiratesislamic probably the worst customer experience I’ve had in my life.
+Tried cancelling my cards. Have received 10+ phone calls from them trying to retain. Confirmed each time that I want to cancel (on call and on email confirmation). It’s been 4-5 months since I raised this complaint. No resolution yet.
+Impressed with how difficult they make this process. Wow!</t>
+        </is>
+      </c>
+      <c r="G92" t="n">
+        <v>1776337169000</v>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>2044732404938702855</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>{'name': 'Aadit Sheth', 'screenName': 'aaditsh', 'followersCount': 522016, 'favouritesCount': 32068, 'friendsCount': 581, 'description': 'Co-founder, The Narrative Company. We help Fortune 500 C-suite engineer their biggest moments. Also write Neatprompts, 100K+ subscribers.'}</t>
+        </is>
+      </c>
+      <c r="K92" t="n">
+        <v>2</v>
+      </c>
+      <c r="L92" t="n">
+        <v>0</v>
+      </c>
+      <c r="M92" t="n">
+        <v>0</v>
+      </c>
+      <c r="N92" t="n">
+        <v>4</v>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>5718</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="n">
+        <v>91</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>https://x.com/huss23/status/2044781883184316706</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>2044781883184316706</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>2044781883184316706</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>https://x.com/huss23/status/2044781883184316706</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>@aaditsh @emiratesislamic I had the same issue. @emiratesislamic has the worst Customer service centre and its literally unreachable and unreliable. After 2 years of request, they still haven’t cancelled my Credit card.</t>
+        </is>
+      </c>
+      <c r="G93" t="n">
+        <v>1776348965000</v>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>2044732404938702855</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>{'name': 'Huss', 'screenName': 'huss23', 'followersCount': 105, 'favouritesCount': 5034, 'friendsCount': 291, 'description': 'Observations, Confessions, Criticism | Politics, Cricket, Books | Hates Bigotry and Extreme Views |'}</t>
+        </is>
+      </c>
+      <c r="K93" t="n">
+        <v>1</v>
+      </c>
+      <c r="L93" t="n">
+        <v>0</v>
+      </c>
+      <c r="M93" t="n">
+        <v>0</v>
+      </c>
+      <c r="N93" t="n">
+        <v>1</v>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>2044732404938702855</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="n">
+        <v>92</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>https://x.com/huss23/status/2044781883184316706</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>2044781883184316706</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>2044784107352445179</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>https://x.com/aaditsh/status/2044784107352445179</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>@huss23 @emiratesislamic Just unacceptable. They just auto-charge you without your permission?</t>
+        </is>
+      </c>
+      <c r="G94" t="n">
+        <v>1776349496000</v>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>2044732404938702855</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>{'name': 'Aadit Sheth', 'screenName': 'aaditsh', 'followersCount': 522016, 'favouritesCount': 32068, 'friendsCount': 581, 'description': 'Co-founder, The Narrative Company. We help Fortune 500 C-suite engineer their biggest moments. Also write Neatprompts, 100K+ subscribers.'}</t>
+        </is>
+      </c>
+      <c r="K94" t="n">
+        <v>0</v>
+      </c>
+      <c r="L94" t="n">
+        <v>0</v>
+      </c>
+      <c r="M94" t="n">
+        <v>0</v>
+      </c>
+      <c r="N94" t="n">
+        <v>0</v>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>2044781883184316706</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="n">
+        <v>93</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>https://x.com/1ss9490ss1/status/2044805287459398125</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>2044805287459398125</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>2044717394669502695</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2044717394669502695</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Save and earn with your Emirates Islamic Super Savings Etihad Guest Account!
+💸 Get up to 750,000 Etihad Guest Miles every quarter and up to 3 million Etihad Guest Miles in a year https://t.co/y8cuMSrpQL</t>
+        </is>
+      </c>
+      <c r="G95" t="n">
+        <v>1776333590000</v>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>2044717394669502695</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGBLonrW4AARVnw.jpg', 'type': 'photo', 'id': '2044717392043892736'}]</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18419, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="K95" t="n">
+        <v>2</v>
+      </c>
+      <c r="L95" t="n">
+        <v>0</v>
+      </c>
+      <c r="M95" t="n">
+        <v>0</v>
+      </c>
+      <c r="N95" t="n">
+        <v>0</v>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="n">
+        <v>94</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>https://x.com/1ss9490ss1/status/2044805287459398125</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>2044805287459398125</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>2044805287459398125</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>https://x.com/1ss9490ss1/status/2044805287459398125</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>@emiratesislamic السلام عليكم ورحمه الله وبركاته 
+الرجاء التواصل بي باحد من خدمة العملاء.</t>
+        </is>
+      </c>
+      <c r="G96" t="n">
+        <v>1776354545000</v>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>2044717394669502695</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>{'name': 'بوالسلطان', 'screenName': '1ss9490ss1', 'followersCount': 50, 'favouritesCount': 2062, 'friendsCount': 337, 'description': 'لا يعترف بأن الحب لا يوجد له تاريخ انتهاء ويعترف انه تبقى المودة الأبدية بين المتعاشرين'}</t>
+        </is>
+      </c>
+      <c r="K96" t="n">
+        <v>0</v>
+      </c>
+      <c r="L96" t="n">
+        <v>0</v>
+      </c>
+      <c r="M96" t="n">
+        <v>0</v>
+      </c>
+      <c r="N96" t="n">
+        <v>0</v>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>2044717394669502695</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>https://x.com/aaditsh/status/2044759599656689929</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>2044759599656689929</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>2044732404938702855</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>https://x.com/aaditsh/status/2044732404938702855</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>@emiratesislamic probably the worst customer experience I’ve had in my life.
+Tried cancelling my cards. Have received 10+ phone calls from them trying to retain. Confirmed each time that I want to cancel (on call and on email confirmation). It’s been 4-5 months since I raised this complaint. No resolution yet.
+Impressed with how difficult they make this process. Wow!</t>
+        </is>
+      </c>
+      <c r="G97" t="n">
+        <v>1776337169000</v>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>2044732404938702855</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>{'name': 'Aadit Sheth', 'screenName': 'aaditsh', 'followersCount': 522016, 'favouritesCount': 32068, 'friendsCount': 581, 'description': 'Co-founder, The Narrative Company. We help Fortune 500 C-suite engineer their biggest moments. Also write Neatprompts, 100K+ subscribers.'}</t>
+        </is>
+      </c>
+      <c r="K97" t="n">
+        <v>2</v>
+      </c>
+      <c r="L97" t="n">
+        <v>0</v>
+      </c>
+      <c r="M97" t="n">
+        <v>0</v>
+      </c>
+      <c r="N97" t="n">
+        <v>4</v>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>5718</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="n">
+        <v>96</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>https://x.com/aaditsh/status/2044759599656689929</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>2044759599656689929</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>2044758862017007662</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>https://x.com/RakeshMavath/status/2044758862017007662</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>@aaditsh @emiratesislamic especially now they are not going to let go of your business easily. you can raise the issue with UAECB who will in turn contact the bank</t>
+        </is>
+      </c>
+      <c r="G98" t="n">
+        <v>1776343477000</v>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>2044732404938702855</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>{'name': 'Rakesh Mavath', 'screenName': 'RakeshMavath', 'followersCount': 366, 'favouritesCount': 12484, 'friendsCount': 3077, 'description': 'Running two startups: one guarantees your rent @takeem_ai, the other guarantees your dignity. Still waiting for my guaranteed 8 hours of sleep.'}</t>
+        </is>
+      </c>
+      <c r="K98" t="n">
+        <v>1</v>
+      </c>
+      <c r="L98" t="n">
+        <v>0</v>
+      </c>
+      <c r="M98" t="n">
+        <v>0</v>
+      </c>
+      <c r="N98" t="n">
+        <v>1</v>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>2044732404938702855</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="n">
+        <v>97</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>https://x.com/aaditsh/status/2044759599656689929</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>2044759599656689929</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>2044759599656689929</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>https://x.com/aaditsh/status/2044759599656689929</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>@RakeshMavath @emiratesislamic Will do! So frustrating. They will call me, I’ll pick up. They will end the call within 10 seconds and message me “we called you. You didn’t pick up”.
+And it’s been extended like this for the past 4-5 months. What a joke.</t>
+        </is>
+      </c>
+      <c r="G99" t="n">
+        <v>1776343653000</v>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>2044732404938702855</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>{'name': 'Aadit Sheth', 'screenName': 'aaditsh', 'followersCount': 522016, 'favouritesCount': 32068, 'friendsCount': 581, 'description': 'Co-founder, The Narrative Company. We help Fortune 500 C-suite engineer their biggest moments. Also write Neatprompts, 100K+ subscribers.'}</t>
+        </is>
+      </c>
+      <c r="K99" t="n">
+        <v>1</v>
+      </c>
+      <c r="L99" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" t="n">
+        <v>0</v>
+      </c>
+      <c r="N99" t="n">
+        <v>1</v>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>2044758862017007662</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>https://x.com/aaditsh/status/2044759599656689929</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>2044759599656689929</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>2044832798670995759</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>https://x.com/RakeshMavath/status/2044832798670995759</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>@aaditsh @emiratesislamic Grab screenshots of when they have called you and the following messages include that to your complaint to UAECB and they will fine the bank</t>
+        </is>
+      </c>
+      <c r="G100" t="n">
+        <v>1776361105000</v>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>2044732404938702855</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>{'name': 'Rakesh Mavath', 'screenName': 'RakeshMavath', 'followersCount': 366, 'favouritesCount': 12484, 'friendsCount': 3077, 'description': 'Running two startups: one guarantees your rent @takeem_ai, the other guarantees your dignity. Still waiting for my guaranteed 8 hours of sleep.'}</t>
+        </is>
+      </c>
+      <c r="K100" t="n">
+        <v>0</v>
+      </c>
+      <c r="L100" t="n">
+        <v>0</v>
+      </c>
+      <c r="M100" t="n">
+        <v>0</v>
+      </c>
+      <c r="N100" t="n">
+        <v>0</v>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>2044759599656689929</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="n">
+        <v>99</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>https://x.com/RakeshMavath/status/2044758862017007662</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>2044758862017007662</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>2044732404938702855</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>https://x.com/aaditsh/status/2044732404938702855</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>@emiratesislamic probably the worst customer experience I’ve had in my life.
+Tried cancelling my cards. Have received 10+ phone calls from them trying to retain. Confirmed each time that I want to cancel (on call and on email confirmation). It’s been 4-5 months since I raised this complaint. No resolution yet.
+Impressed with how difficult they make this process. Wow!</t>
+        </is>
+      </c>
+      <c r="G101" t="n">
+        <v>1776337169000</v>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>2044732404938702855</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>{'name': 'Aadit Sheth', 'screenName': 'aaditsh', 'followersCount': 522016, 'favouritesCount': 32068, 'friendsCount': 581, 'description': 'Co-founder, The Narrative Company. We help Fortune 500 C-suite engineer their biggest moments. Also write Neatprompts, 100K+ subscribers.'}</t>
+        </is>
+      </c>
+      <c r="K101" t="n">
+        <v>2</v>
+      </c>
+      <c r="L101" t="n">
+        <v>0</v>
+      </c>
+      <c r="M101" t="n">
+        <v>0</v>
+      </c>
+      <c r="N101" t="n">
+        <v>4</v>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>5718</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>https://x.com/RakeshMavath/status/2044758862017007662</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>2044758862017007662</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>2044758862017007662</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>https://x.com/RakeshMavath/status/2044758862017007662</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>@aaditsh @emiratesislamic especially now they are not going to let go of your business easily. you can raise the issue with UAECB who will in turn contact the bank</t>
+        </is>
+      </c>
+      <c r="G102" t="n">
+        <v>1776343477000</v>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>2044732404938702855</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>{'name': 'Rakesh Mavath', 'screenName': 'RakeshMavath', 'followersCount': 366, 'favouritesCount': 12484, 'friendsCount': 3077, 'description': 'Running two startups: one guarantees your rent @takeem_ai, the other guarantees your dignity. Still waiting for my guaranteed 8 hours of sleep.'}</t>
+        </is>
+      </c>
+      <c r="K102" t="n">
+        <v>1</v>
+      </c>
+      <c r="L102" t="n">
+        <v>0</v>
+      </c>
+      <c r="M102" t="n">
+        <v>0</v>
+      </c>
+      <c r="N102" t="n">
+        <v>1</v>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>2044732404938702855</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="n">
+        <v>101</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>https://x.com/RakeshMavath/status/2044758862017007662</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>2044758862017007662</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>2044759599656689929</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>https://x.com/aaditsh/status/2044759599656689929</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>@RakeshMavath @emiratesislamic Will do! So frustrating. They will call me, I’ll pick up. They will end the call within 10 seconds and message me “we called you. You didn’t pick up”.
+And it’s been extended like this for the past 4-5 months. What a joke.</t>
+        </is>
+      </c>
+      <c r="G103" t="n">
+        <v>1776343653000</v>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>2044732404938702855</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>{'name': 'Aadit Sheth', 'screenName': 'aaditsh', 'followersCount': 522016, 'favouritesCount': 32068, 'friendsCount': 581, 'description': 'Co-founder, The Narrative Company. We help Fortune 500 C-suite engineer their biggest moments. Also write Neatprompts, 100K+ subscribers.'}</t>
+        </is>
+      </c>
+      <c r="K103" t="n">
+        <v>1</v>
+      </c>
+      <c r="L103" t="n">
+        <v>0</v>
+      </c>
+      <c r="M103" t="n">
+        <v>0</v>
+      </c>
+      <c r="N103" t="n">
+        <v>1</v>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>2044758862017007662</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="n">
+        <v>102</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>https://x.com/startupsceneme/status/2044704123199554019</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>2044704123199554019</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>2044704123199554019</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>https://x.com/startupsceneme/status/2044704123199554019</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Emirates Islamic, a Dubai-based Islamic bank offering Sharia-compliant financial services, has launched a Business Banking campaign aimed at supporting small and medium enterprises in the United Arab Emirates, offering a total prize pool of Dhs 1 million.
+https://t.co/NGMGwUvZfs</t>
+        </is>
+      </c>
+      <c r="G104" t="n">
+        <v>1776330426000</v>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>2044704123199554019</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>{'name': 'Startup Scene ME', 'screenName': 'startupsceneme', 'followersCount': 3868, 'favouritesCount': 759, 'friendsCount': 1128, 'description': "They defy odds and champion change. #StartupScene is the story of the Middle East's fiercest entrepreneurs. A part of @MO4Network."}</t>
+        </is>
+      </c>
+      <c r="K104" t="n">
+        <v>0</v>
+      </c>
+      <c r="L104" t="n">
+        <v>0</v>
+      </c>
+      <c r="M104" t="n">
+        <v>2</v>
+      </c>
+      <c r="N104" t="n">
+        <v>0</v>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="n">
+        <v>103</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>https://x.com/startupsceneme/status/2044704123199554019</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>2044704123199554019</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>2044755794210492583</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>https://x.com/startupsceneme/status/2044755794210492583</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>INVIA, a Cairo-based fintech startup, has raised $1.2 million from angel investors and strategic supporters to develop an AI-powered platform designed to streamline operations for small and mid-sized businesses.
+https://t.co/xcogOK0kd4</t>
+        </is>
+      </c>
+      <c r="G105" t="n">
+        <v>1776342745000</v>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>2044755794210492583</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>{'name': 'Startup Scene ME', 'screenName': 'startupsceneme', 'followersCount': 3868, 'favouritesCount': 759, 'friendsCount': 1128, 'description': "They defy odds and champion change. #StartupScene is the story of the Middle East's fiercest entrepreneurs. A part of @MO4Network."}</t>
+        </is>
+      </c>
+      <c r="K105" t="n">
+        <v>0</v>
+      </c>
+      <c r="L105" t="n">
+        <v>0</v>
+      </c>
+      <c r="M105" t="n">
+        <v>1</v>
+      </c>
+      <c r="N105" t="n">
+        <v>1</v>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="n">
+        <v>104</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2044717394669502695</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>2044717394669502695</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>2044717394669502695</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2044717394669502695</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Save and earn with your Emirates Islamic Super Savings Etihad Guest Account!
+💸 Get up to 750,000 Etihad Guest Miles every quarter and up to 3 million Etihad Guest Miles in a year https://t.co/y8cuMSrpQL</t>
+        </is>
+      </c>
+      <c r="G106" t="n">
+        <v>1776333590000</v>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>2044717394669502695</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGBLonrW4AARVnw.jpg', 'type': 'photo', 'id': '2044717392043892736'}]</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18419, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="K106" t="n">
+        <v>2</v>
+      </c>
+      <c r="L106" t="n">
+        <v>0</v>
+      </c>
+      <c r="M106" t="n">
+        <v>0</v>
+      </c>
+      <c r="N106" t="n">
+        <v>0</v>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="P106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="n">
+        <v>105</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2044717394669502695</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>2044717394669502695</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>2044717396758303206</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2044717396758303206</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>💸 Save AED 20,000 or more to start earning miles based on your average quarterly savings
+🌟 Get a complimentary Debit Card that is internationally recognized
+Offer valid till 30 June 2026
+Terms &amp;amp; Conditions apply
+https://t.co/6VJUgOMZYN</t>
+        </is>
+      </c>
+      <c r="G107" t="n">
+        <v>1776333591000</v>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>2044717394669502695</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18419, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="K107" t="n">
+        <v>0</v>
+      </c>
+      <c r="L107" t="n">
+        <v>0</v>
+      </c>
+      <c r="M107" t="n">
+        <v>0</v>
+      </c>
+      <c r="N107" t="n">
+        <v>0</v>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>2044717394669502695</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="n">
+        <v>106</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2044657039872237722</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>2044657039872237722</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>2044657039872237722</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2044657039872237722</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>You don’t have a spending problem, you have invisible spending.
+Track what feels “too small to matter.”
+Because that’s usually where your money goes.
+#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic
+https://t.co/XvyZgR87nM"</t>
+        </is>
+      </c>
+      <c r="G108" t="n">
+        <v>1776319200000</v>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>2044657039872237722</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18419, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="K108" t="n">
+        <v>0</v>
+      </c>
+      <c r="L108" t="n">
+        <v>0</v>
+      </c>
+      <c r="M108" t="n">
+        <v>0</v>
+      </c>
+      <c r="N108" t="n">
+        <v>0</v>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="P108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="n">
+        <v>107</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2044657039872237722</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>2044657039872237722</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>2044717394669502695</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2044717394669502695</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Save and earn with your Emirates Islamic Super Savings Etihad Guest Account!
+💸 Get up to 750,000 Etihad Guest Miles every quarter and up to 3 million Etihad Guest Miles in a year https://t.co/y8cuMSrpQL</t>
+        </is>
+      </c>
+      <c r="G109" t="n">
+        <v>1776333590000</v>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>2044717394669502695</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGBLonrW4AARVnw.jpg', 'type': 'photo', 'id': '2044717392043892736'}]</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18419, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="K109" t="n">
+        <v>2</v>
+      </c>
+      <c r="L109" t="n">
+        <v>0</v>
+      </c>
+      <c r="M109" t="n">
+        <v>0</v>
+      </c>
+      <c r="N109" t="n">
+        <v>0</v>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="P109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="n">
+        <v>108</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2044701412848705623</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>2044701412848705623</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>2044701403591983546</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2044701403591983546</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>مع الإمارات الإسلامي، تتحوّل طموحات الشركات الصغيرة والمتوسطة إلى فرص حقيقية للنمو. من خلال إطلاق حملة جديدة تضيف قيمة ملموسة لمتعاملينا، نفتح الباب للفوز بجوائز يصل مجموعها إلى مليون درهم إماراتي. 
+نرافق رحلتكم، ندعم توسّعكم، ونمنح أفكاركم المساحة لتكبر.
+معا نصنع نجاح أعمالكم. https://t.co/0uN1xuq5rX</t>
+        </is>
+      </c>
+      <c r="G110" t="n">
+        <v>1776329777000</v>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>2044701403591983546</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGA9FkYXcAAK_jt.jpg', 'type': 'photo', 'id': '2044701396700721152'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGA9FxiXwAA7B7v.jpg', 'type': 'photo', 'id': '2044701400232345600'}]</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18419, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="K110" t="n">
+        <v>1</v>
+      </c>
+      <c r="L110" t="n">
+        <v>0</v>
+      </c>
+      <c r="M110" t="n">
+        <v>0</v>
+      </c>
+      <c r="N110" t="n">
+        <v>0</v>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="P110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="n">
+        <v>109</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2044701412848705623</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>2044701412848705623</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>2044701412848705623</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2044701412848705623</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Emirates Islamic empowers SME growth with a campaign that brings added value to customers and an opportunity to win from a total prize pool of AED 1 million. Driving ambition. Enabling expansion. Unlocking new opportunities.
+#SME #businessbanking #emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G111" t="n">
+        <v>1776329780000</v>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>2044701403591983546</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18419, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="K111" t="n">
+        <v>0</v>
+      </c>
+      <c r="L111" t="n">
+        <v>0</v>
+      </c>
+      <c r="M111" t="n">
+        <v>0</v>
+      </c>
+      <c r="N111" t="n">
+        <v>0</v>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>2044701403591983546</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="n">
+        <v>110</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2044836542028320968</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>2044836542028320968</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>2044836538958200892</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2044836538958200892</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>تشهد التحديثات الوهمية على أجهزة أندرويد تزايداً ملحوظاً، وقد تُستخدم لخداعك لتثبيت تطبيقات غير آمنة أو مشاركة البيانات.
+احم حسابك من خلال تفعيل ميزة اللمس الذكي والتعرّف على الوجه لتسجيل دخول أكثر أماناً. https://t.co/ZOt8O2bR9J</t>
+        </is>
+      </c>
+      <c r="G112" t="n">
+        <v>1776361996000</v>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>2044836538958200892</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGC3_GQWIAAxAQS.jpg', 'type': 'photo', 'id': '2044836525465018368'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGC3_SFXEAAobhw.jpg', 'type': 'photo', 'id': '2044836528640167936'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGC3_d1WcAABZL9.jpg', 'type': 'photo', 'id': '2044836531794243584'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGC3_rQXYAAwpP1.jpg', 'type': 'photo', 'id': '2044836535397212160'}]</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18419, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="K112" t="n">
+        <v>1</v>
+      </c>
+      <c r="L112" t="n">
+        <v>0</v>
+      </c>
+      <c r="M112" t="n">
+        <v>0</v>
+      </c>
+      <c r="N112" t="n">
+        <v>0</v>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="P112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="n">
+        <v>111</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2044836542028320968</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>2044836542028320968</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>2044836542028320968</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2044836542028320968</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Fake Android updates are rising. They can trick you into installing unsafe apps or sharing details.
+Turn on Smart Touch and Face Pass for secure login.</t>
+        </is>
+      </c>
+      <c r="G113" t="n">
+        <v>1776361997000</v>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>2044836538958200892</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18419, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="K113" t="n">
+        <v>0</v>
+      </c>
+      <c r="L113" t="n">
+        <v>0</v>
+      </c>
+      <c r="M113" t="n">
+        <v>0</v>
+      </c>
+      <c r="N113" t="n">
+        <v>0</v>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>2044836538958200892</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="n">
+        <v>112</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2044836538958200892</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>2044836538958200892</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>2044836538958200892</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2044836538958200892</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>تشهد التحديثات الوهمية على أجهزة أندرويد تزايداً ملحوظاً، وقد تُستخدم لخداعك لتثبيت تطبيقات غير آمنة أو مشاركة البيانات.
+احم حسابك من خلال تفعيل ميزة اللمس الذكي والتعرّف على الوجه لتسجيل دخول أكثر أماناً. https://t.co/ZOt8O2bR9J</t>
+        </is>
+      </c>
+      <c r="G114" t="n">
+        <v>1776361996000</v>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>2044836538958200892</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGC3_GQWIAAxAQS.jpg', 'type': 'photo', 'id': '2044836525465018368'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGC3_SFXEAAobhw.jpg', 'type': 'photo', 'id': '2044836528640167936'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGC3_d1WcAABZL9.jpg', 'type': 'photo', 'id': '2044836531794243584'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGC3_rQXYAAwpP1.jpg', 'type': 'photo', 'id': '2044836535397212160'}]</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18419, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="K114" t="n">
+        <v>1</v>
+      </c>
+      <c r="L114" t="n">
+        <v>0</v>
+      </c>
+      <c r="M114" t="n">
+        <v>0</v>
+      </c>
+      <c r="N114" t="n">
+        <v>0</v>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="P114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="n">
+        <v>113</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2044836538958200892</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>2044836538958200892</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>2044836542028320968</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2044836542028320968</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Fake Android updates are rising. They can trick you into installing unsafe apps or sharing details.
+Turn on Smart Touch and Face Pass for secure login.</t>
+        </is>
+      </c>
+      <c r="G115" t="n">
+        <v>1776361997000</v>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>2044836538958200892</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18419, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="K115" t="n">
+        <v>0</v>
+      </c>
+      <c r="L115" t="n">
+        <v>0</v>
+      </c>
+      <c r="M115" t="n">
+        <v>0</v>
+      </c>
+      <c r="N115" t="n">
+        <v>0</v>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>2044836538958200892</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="n">
+        <v>114</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2044836538958200892</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>2044836538958200892</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>2044717365380739467</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2044717365380739467</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>ادخر واكسب مع حساب ضيف الاتحاد سوبر للتوفير من الإمارات الإسلامي
+💸 اكسب ما يصل إلى 750,000 ميل من أميال ضيف الاتحاد كل ربع سنة ولغاية 3,000,000 ميل من أميال ضيف الاتحاد سنوياً https://t.co/QZie703oFv</t>
+        </is>
+      </c>
+      <c r="G116" t="n">
+        <v>1776333583000</v>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>2044717365380739467</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGBLm7KXsAAQep6.jpg', 'type': 'photo', 'id': '2044717362914504704'}]</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18419, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="K116" t="n">
+        <v>1</v>
+      </c>
+      <c r="L116" t="n">
+        <v>0</v>
+      </c>
+      <c r="M116" t="n">
+        <v>0</v>
+      </c>
+      <c r="N116" t="n">
+        <v>1</v>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="P116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="n">
+        <v>115</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2044717396758303206</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>2044717396758303206</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>2044717394669502695</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2044717394669502695</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Save and earn with your Emirates Islamic Super Savings Etihad Guest Account!
+💸 Get up to 750,000 Etihad Guest Miles every quarter and up to 3 million Etihad Guest Miles in a year https://t.co/y8cuMSrpQL</t>
+        </is>
+      </c>
+      <c r="G117" t="n">
+        <v>1776333590000</v>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>2044717394669502695</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGBLonrW4AARVnw.jpg', 'type': 'photo', 'id': '2044717392043892736'}]</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18419, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="K117" t="n">
+        <v>2</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0</v>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="P117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="n">
+        <v>116</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2044717396758303206</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>2044717396758303206</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>2044717396758303206</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2044717396758303206</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>💸 Save AED 20,000 or more to start earning miles based on your average quarterly savings
+🌟 Get a complimentary Debit Card that is internationally recognized
+Offer valid till 30 June 2026
+Terms &amp;amp; Conditions apply
+https://t.co/6VJUgOMZYN</t>
+        </is>
+      </c>
+      <c r="G118" t="n">
+        <v>1776333591000</v>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>2044717394669502695</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18419, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="K118" t="n">
+        <v>0</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0</v>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>2044717394669502695</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="n">
+        <v>117</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2044717367842816367</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>2044717367842816367</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>2044717365380739467</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2044717365380739467</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>ادخر واكسب مع حساب ضيف الاتحاد سوبر للتوفير من الإمارات الإسلامي
+💸 اكسب ما يصل إلى 750,000 ميل من أميال ضيف الاتحاد كل ربع سنة ولغاية 3,000,000 ميل من أميال ضيف الاتحاد سنوياً https://t.co/QZie703oFv</t>
+        </is>
+      </c>
+      <c r="G119" t="n">
+        <v>1776333583000</v>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>2044717365380739467</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGBLm7KXsAAQep6.jpg', 'type': 'photo', 'id': '2044717362914504704'}]</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18419, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="K119" t="n">
+        <v>1</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0</v>
+      </c>
+      <c r="N119" t="n">
+        <v>1</v>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="P119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="n">
+        <v>118</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2044717367842816367</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>2044717367842816367</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>2044717367842816367</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2044717367842816367</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>💸 ادخر 20,000 درهم أو أكثر للبدء باكتساب الأميال بناءً على متوسط مدخراتك ربع السنوي! 
+🌟 احصل على بطاقة خصم معترف بها دولياً
+يسري العرض لغاية 30 يونيو 2026
+تطبق الشروط والأحكام
+https://t.co/csC9BzTLNy</t>
+        </is>
+      </c>
+      <c r="G120" t="n">
+        <v>1776333584000</v>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>2044717365380739467</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18419, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="K120" t="n">
+        <v>0</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0</v>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>2044717365380739467</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="n">
+        <v>119</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2044701403591983546</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>2044701403591983546</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>2044701403591983546</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2044701403591983546</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>مع الإمارات الإسلامي، تتحوّل طموحات الشركات الصغيرة والمتوسطة إلى فرص حقيقية للنمو. من خلال إطلاق حملة جديدة تضيف قيمة ملموسة لمتعاملينا، نفتح الباب للفوز بجوائز يصل مجموعها إلى مليون درهم إماراتي. 
+نرافق رحلتكم، ندعم توسّعكم، ونمنح أفكاركم المساحة لتكبر.
+معا نصنع نجاح أعمالكم. https://t.co/0uN1xuq5rX</t>
+        </is>
+      </c>
+      <c r="G121" t="n">
+        <v>1776329777000</v>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>2044701403591983546</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGA9FkYXcAAK_jt.jpg', 'type': 'photo', 'id': '2044701396700721152'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGA9FxiXwAA7B7v.jpg', 'type': 'photo', 'id': '2044701400232345600'}]</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18419, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="K121" t="n">
+        <v>1</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0</v>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="P121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="n">
+        <v>120</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2044701403591983546</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>2044701403591983546</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>2044701412848705623</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2044701412848705623</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Emirates Islamic empowers SME growth with a campaign that brings added value to customers and an opportunity to win from a total prize pool of AED 1 million. Driving ambition. Enabling expansion. Unlocking new opportunities.
+#SME #businessbanking #emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G122" t="n">
+        <v>1776329780000</v>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>2044701403591983546</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18419, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="K122" t="n">
+        <v>0</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0</v>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>2044701403591983546</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="1" t="n">
+        <v>121</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2044701403591983546</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>2044701403591983546</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>2044717365380739467</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2044717365380739467</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>ادخر واكسب مع حساب ضيف الاتحاد سوبر للتوفير من الإمارات الإسلامي
+💸 اكسب ما يصل إلى 750,000 ميل من أميال ضيف الاتحاد كل ربع سنة ولغاية 3,000,000 ميل من أميال ضيف الاتحاد سنوياً https://t.co/QZie703oFv</t>
+        </is>
+      </c>
+      <c r="G123" t="n">
+        <v>1776333583000</v>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>2044717365380739467</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGBLm7KXsAAQep6.jpg', 'type': 'photo', 'id': '2044717362914504704'}]</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18419, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="K123" t="n">
+        <v>1</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0</v>
+      </c>
+      <c r="N123" t="n">
+        <v>1</v>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="P123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="n">
+        <v>122</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2044657039859757511</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>2044657039859757511</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>2044657039859757511</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2044657039859757511</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>ليست المشكلة فيما تنفقه، بل في ما يتسرّب منه بصمت.
+فالمبالغ الصغيرة التي نظنها "غير مهمّة"، هي غالباً ما تتراكم وتؤثر على ميزانيتك أكثر مما تتوقع.
+#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
+https://t.co/mgtIcQsyLZ</t>
+        </is>
+      </c>
+      <c r="G124" t="n">
+        <v>1776319200000</v>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>2044657039859757511</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18419, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="K124" t="n">
+        <v>0</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0</v>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="P124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="n">
+        <v>123</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2044657039859757511</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>2044657039859757511</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>2044717365380739467</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2044717365380739467</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>ادخر واكسب مع حساب ضيف الاتحاد سوبر للتوفير من الإمارات الإسلامي
+💸 اكسب ما يصل إلى 750,000 ميل من أميال ضيف الاتحاد كل ربع سنة ولغاية 3,000,000 ميل من أميال ضيف الاتحاد سنوياً https://t.co/QZie703oFv</t>
+        </is>
+      </c>
+      <c r="G125" t="n">
+        <v>1776333583000</v>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>2044717365380739467</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGBLm7KXsAAQep6.jpg', 'type': 'photo', 'id': '2044717362914504704'}]</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18419, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="K125" t="n">
+        <v>1</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0</v>
+      </c>
+      <c r="N125" t="n">
+        <v>1</v>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="P125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="n">
+        <v>124</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2044717365380739467</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>2044717365380739467</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>2044717365380739467</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2044717365380739467</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>ادخر واكسب مع حساب ضيف الاتحاد سوبر للتوفير من الإمارات الإسلامي
+💸 اكسب ما يصل إلى 750,000 ميل من أميال ضيف الاتحاد كل ربع سنة ولغاية 3,000,000 ميل من أميال ضيف الاتحاد سنوياً https://t.co/QZie703oFv</t>
+        </is>
+      </c>
+      <c r="G126" t="n">
+        <v>1776333583000</v>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>2044717365380739467</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGBLm7KXsAAQep6.jpg', 'type': 'photo', 'id': '2044717362914504704'}]</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18419, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="K126" t="n">
+        <v>1</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0</v>
+      </c>
+      <c r="N126" t="n">
+        <v>1</v>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="P126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="1" t="n">
+        <v>125</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2044717365380739467</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>2044717365380739467</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>2044717367842816367</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2044717367842816367</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>💸 ادخر 20,000 درهم أو أكثر للبدء باكتساب الأميال بناءً على متوسط مدخراتك ربع السنوي! 
+🌟 احصل على بطاقة خصم معترف بها دولياً
+يسري العرض لغاية 30 يونيو 2026
+تطبق الشروط والأحكام
+https://t.co/csC9BzTLNy</t>
+        </is>
+      </c>
+      <c r="G127" t="n">
+        <v>1776333584000</v>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>2044717365380739467</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18419, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="K127" t="n">
+        <v>0</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0</v>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>2044717365380739467</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="1" t="n">
+        <v>126</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2044717365380739467</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>2044717365380739467</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>2044836538958200892</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2044836538958200892</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>تشهد التحديثات الوهمية على أجهزة أندرويد تزايداً ملحوظاً، وقد تُستخدم لخداعك لتثبيت تطبيقات غير آمنة أو مشاركة البيانات.
+احم حسابك من خلال تفعيل ميزة اللمس الذكي والتعرّف على الوجه لتسجيل دخول أكثر أماناً. https://t.co/ZOt8O2bR9J</t>
+        </is>
+      </c>
+      <c r="G128" t="n">
+        <v>1776361996000</v>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>2044836538958200892</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGC3_GQWIAAxAQS.jpg', 'type': 'photo', 'id': '2044836525465018368'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGC3_SFXEAAobhw.jpg', 'type': 'photo', 'id': '2044836528640167936'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGC3_d1WcAABZL9.jpg', 'type': 'photo', 'id': '2044836531794243584'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGC3_rQXYAAwpP1.jpg', 'type': 'photo', 'id': '2044836535397212160'}]</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18419, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="K128" t="n">
+        <v>1</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0</v>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="P128" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Xpost_df_comments.xlsx
+++ b/Xpost_df_comments.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P48"/>
+  <dimension ref="A1:P108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,36 +511,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://x.com/ansariiarif/status/2045958337494143476</t>
+          <t>https://x.com/evocarsrental/status/2046283996015800804</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2045958337494143476</t>
+          <t>2046283996015800804</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2045958337494143476</t>
+          <t>2046283996015800804</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://x.com/ansariiarif/status/2045958337494143476</t>
+          <t>https://x.com/evocarsrental/status/2046283996015800804</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE 
-I have been chargd without any reason. Not expexted this from NDB as per their policy I have spent the required amount but still they have charged me for accessing the lounge which shouldn't be!!!</t>
+          <t>@EmiratesNBD_AE May i ask which email can be written to, for the purpose of assisting us in deferment on auto-loans. Based on the article - https://t.co/l4qu0XUPAx</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1776629454000</v>
+        <v>1776707097000</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2045958337494143476</t>
+          <t>2046283996015800804</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -550,11 +549,11 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>{'name': 'Arif', 'screenName': 'ansariiarif', 'followersCount': 0, 'favouritesCount': 31, 'friendsCount': 52, 'description': ''}</t>
+          <t>{'name': 'EVO Cars Rental', 'screenName': 'evocarsrental', 'followersCount': 34, 'favouritesCount': 7, 'friendsCount': 55, 'description': 'Go on! Drive your dream LUXURY car now!\nServices available for Individuals/Corporate Clients/Events/'}</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -567,7 +566,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P2" t="inlineStr"/>
@@ -578,36 +577,36 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://x.com/Kyodonews_JBN/status/2046033950339166455</t>
+          <t>https://x.com/evocarsrental/status/2046283996015800804</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2046033950339166455</t>
+          <t>2046283996015800804</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2046033950339166455</t>
+          <t>2046287756955930787</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://x.com/Kyodonews_JBN/status/2046033950339166455</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2046287756955930787</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Emirates NBD、Dar Global向け2億5,000万米ドルのシンジケート・タームローンを実行し、世界的な成長と事業拡大を加速【Dar Global】
-https://t.co/H82MnfRa04</t>
+          <t>@evocarsrental Thanks for writing to us, kindly visit the below link to review the terms and conditions then you can apply 
+https://t.co/ZUuqqadVdS</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1776647481000</v>
+        <v>1776707994000</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2046033950339166455</t>
+          <t>2046283996015800804</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -617,7 +616,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>{'name': 'KYODONEWS JBN', 'screenName': 'Kyodonews_JBN', 'followersCount': 21, 'favouritesCount': 6, 'friendsCount': 2, 'description': '株式会社共同通信社 ジャパンビジネス広報センター'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174304, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -637,7 +636,11 @@
           <t>4</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2046283996015800804</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -645,63 +648,62 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://x.com/Kyodonews_JBN/status/2046033950339166455</t>
+          <t>https://x.com/saigol7/status/2046285967863279687</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2046033950339166455</t>
+          <t>2046285967863279687</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2046074841544200528</t>
+          <t>2045203152040018428</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://x.com/Kyodonews_JBN/status/2046074841544200528</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2045203152040018428</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Train of Glamour Joins EHL Alliance as First Chinese Member, Marking New Era for Luxury Rail Travel【Train of Glamour】
-https://t.co/yerijBdY0c</t>
+          <t>We are extending our support to help you manage your finances with more confidence. https://t.co/EP2xuqo7Gb</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1776657231000</v>
+        <v>1776449404000</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2046074841544200528</t>
+          <t>2045203152040018428</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGIFa_XbAAAbdED.jpg', 'type': 'photo', 'id': '2045203142024036352'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGIFa_QaQAAmKGx.jpg', 'type': 'photo', 'id': '2045203141994627072'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGIFa_MbMAAD7Cp.jpg', 'type': 'photo', 'id': '2045203141977911296'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGIFa_kboAEToWB.jpg', 'type': 'photo', 'id': '2045203142078603265'}]</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>{'name': 'KYODONEWS JBN', 'screenName': 'Kyodonews_JBN', 'followersCount': 21, 'favouritesCount': 6, 'friendsCount': 2, 'description': '株式会社共同通信社 ジャパンビジネス広報センター'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174304, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>567313</t>
         </is>
       </c>
       <c r="P4" t="inlineStr"/>
@@ -712,25 +714,713 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://x.com/she7ii88/status/2046061240511082734</t>
+          <t>https://x.com/saigol7/status/2046285967863279687</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2046061240511082734</t>
+          <t>2046285967863279687</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>2046285967863279687</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>https://x.com/saigol7/status/2046285967863279687</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE Please launch prepaid debit card for tourists.</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>1776707567000</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2045203152040018428</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>{'name': 'Jeanvaljeanrambo', 'screenName': 'saigol7', 'followersCount': 98, 'favouritesCount': 801, 'friendsCount': 495, 'description': 'Planes,  automobiles, things that go fast and make a lot of noise. Also Linux, Unix and Android, Electronics, economics, astronomy, photography.'}</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>2</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2045203152040018428</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>https://x.com/saigol7/status/2046285967863279687</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2046285967863279687</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2046289305190953193</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2046289305190953193</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>@saigol7 For suggestions please visit the below link, We will make every effort to address the matter promptly and provide the necessary support.
+https://t.co/nfKBl3vphJ</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>1776708363000</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2045203152040018428</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174304, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2046285967863279687</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>https://x.com/saigol7/status/2046285967863279687</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2046285967863279687</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2046289251550044333</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2046289251550044333</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>@saigol7 Thanks for writing to us, please visit the below link to review the prepaid cards 
+https://t.co/6Lk5Jbb44I</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>1776708350000</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2045203152040018428</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174304, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2046285967863279687</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>https://x.com/khaleejtimes/status/2046263546024165797</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2046263546024165797</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2046263546024165797</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>https://x.com/khaleejtimes/status/2046263546024165797</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Emirates NBD extends fee waivers, 0% interest on credit card transfers for UAE customers
+https://t.co/sNYXzG1RYE</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>1776702221000</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2046263546024165797</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>{'name': 'Khaleej Times', 'screenName': 'khaleejtimes', 'followersCount': 1195567, 'favouritesCount': 43, 'friendsCount': 1565, 'description': "The official Twitter feed of Khaleej Times, the UAE's first and leading English daily\nhttps://t.co/bKx3o3oPhX"}</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2</v>
+      </c>
+      <c r="N8" t="n">
+        <v>34</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>7104</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>https://x.com/khaleejtimes/status/2046263546024165797</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2046263546024165797</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2046375898933231804</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>https://x.com/wallet/status/2046375898933231804</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Need this? Drop a GM below👇 https://t.co/XjAc2KdaHx</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>1776729008000</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2046375898933231804</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGYwBO5WgAEB478.jpg', 'type': 'photo', 'id': '2046375878423117825'}]</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>{'name': 'OKX Wallet', 'screenName': 'wallet', 'followersCount': 1929748, 'favouritesCount': 14748, 'friendsCount': 422, 'description': 'The crypto wallet for everything onchain. Self-custody is the future.\n\nEngagement is not endorsement.'}</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>500</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>16</v>
+      </c>
+      <c r="N9" t="n">
+        <v>547</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>24341</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>https://x.com/preeminentdxb/status/2046264235852718127</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2046264235852718127</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2046264189786714117</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>https://x.com/preeminentdxb/status/2046264189786714117</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>A quiet shift, but a powerful one.
+The gap between intent and ownership in Dubai just got smaller, and more predictable.
+Follow for perspective that stays ahead of the curve.
+#MarketMaturity #DubaiRealEstate #PropertyInvestment https://t.co/F1CLT9HxwK</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>1776702375000</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2046264189786714117</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGXKavSW8AAvugA.jpg', 'type': 'photo', 'id': '2046264166428635136'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGXKbQLWYAAjRuc.png', 'type': 'photo', 'id': '2046264175257608192'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGXKbh8WgAAvC6X.png', 'type': 'photo', 'id': '2046264180026540032'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGXKbz0W4AAHPcf.png', 'type': 'photo', 'id': '2046264184824848384'}]</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>{'name': 'Preeminent Properties', 'screenName': 'preeminentdxb', 'followersCount': 0, 'favouritesCount': 0, 'friendsCount': 2, 'description': "Unveiling UAE's finest real estate, where trust and satisfaction meet"}</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>https://x.com/preeminentdxb/status/2046264235852718127</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2046264235852718127</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2046264235852718127</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>https://x.com/preeminentdxb/status/2046264235852718127</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Backed by Emirates NBD and Dubai Holding Real Estate, this move signals a maturing market: one that's reducing friction, improving transparency, and making long-term planning far more structure https://t.co/ykGWWmVfrC</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>1776702386000</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2046264189786714117</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGXKda4WYAEW_JB.png', 'type': 'photo', 'id': '2046264212490444801'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGXKdvYXUAAyguF.png', 'type': 'photo', 'id': '2046264217993433088'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGXKeRWWcAEerrb.jpg', 'type': 'photo', 'id': '2046264227111792641'}]</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>{'name': 'Preeminent Properties', 'screenName': 'preeminentdxb', 'followersCount': 0, 'favouritesCount': 0, 'friendsCount': 2, 'description': "Unveiling UAE's finest real estate, where trust and satisfaction meet"}</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2046264189786714117</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>https://x.com/naveenthumala/status/2046198033738785046</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2046198033738785046</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2046198033738785046</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>https://x.com/naveenthumala/status/2046198033738785046</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>If someone experienced gulf banking understands  the importance of Emirates NBD acquiring RBL bank stake
+#RBLBank</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>1776686602000</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2046198033738785046</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>{'name': 'Naveen Reddy', 'screenName': 'naveenthumala', 'followersCount': 20, 'favouritesCount': 1498, 'friendsCount': 127, 'description': 'Remember you will die'}</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>https://x.com/ja2030ah/status/2046190505554321598</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2046190505554321598</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2046190505554321598</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>https://x.com/ja2030ah/status/2046190505554321598</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>@DFMalerts 
+I have old account with DFM and now dormant. 
+I talked to Emirates NBD Securities , they said to contact Dubai Financial Market. 
+I have the full details. I need your help to update my investor’s account.</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>1776684807000</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2046190505554321598</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>{'name': 'vision', 'screenName': 'ja2030ah', 'followersCount': 86, 'favouritesCount': 12, 'friendsCount': 597, 'description': 'وطني وقيادته خط أحمر'}</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>https://x.com/ENBDdeals/status/2046171931813011938</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2046171931813011938</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2046171931813011938</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>https://x.com/ENBDdeals/status/2046171931813011938</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Turn your bills into rewards
+Get AED 500 worth of noon credits + AED 500 welcome bonus when you apply for an Emirates NBD noon One Visa Credit Card.
+Apply Now: https://t.co/vPejTs11gM https://t.co/w4kHA8AtSA</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>1776680379000</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2046171931813011938</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGV2hzyXYAAiJn2.jpg', 'type': 'photo', 'id': '2046171928918974464'}]</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD Deals', 'screenName': 'ENBDdeals', 'followersCount': 39177, 'favouritesCount': 61, 'friendsCount': 4, 'description': 'Welcome to the official account for Emirates NBD Deals. نرحب بكم في الحساب الرسمي لعروض بنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>https://x.com/ATwo2/status/2046171233243541979</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2046171233243541979</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
           <t>2045093015459352679</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE/status/2045093015459352679</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>ندعم من يحمون الوطن
 مجموعة من مزايا الدعم المالي والخدمات المصرفية المخصصة للعاملين في الصفوف الأمامية
@@ -744,575 +1434,344 @@
 https://t.co/I7DGlib9vt</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="G15" t="n">
         <v>1776423145000</v>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>2045093015459352679</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGGhQnfXsAAHpYo.jpg', 'type': 'photo', 'id': '2045093012653453312'}]</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174302, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174304, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>19</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
+        <v>33</v>
+      </c>
+      <c r="N15" t="n">
+        <v>344</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>862354</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>https://x.com/ATwo2/status/2046171233243541979</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2046171233243541979</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2046171233243541979</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>https://x.com/ATwo2/status/2046171233243541979</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE شو ها العروض مع احترامي لكم. لا تستغلون حماة الوطن بهكذا عروض مخجله</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>1776680212000</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2045093015459352679</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>{'name': 'عبدالله ثاني الغاوي', 'screenName': 'ATwo2', 'followersCount': 444, 'favouritesCount': 4901, 'friendsCount': 480, 'description': 'رياضي، اقتصادي، #crypto$'}</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>2045093015459352679</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>https://x.com/ATwo2/status/2046171233243541979</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2046171233243541979</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2046175033328890208</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2046175033328890208</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>@ATwo2 مرحبًا، هل يمكننا معرفة سبب عدم رضاك؟ سيكون من المفيد جدًا إذا كان بإمكانك مشاركة المزيد من التفاصيل حول ذلك ورقم اتصالك معنا عبر الرسائل الخاصة.</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>1776681118000</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2045093015459352679</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174304, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>2046171233243541979</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>https://x.com/ArabiaCSR/status/2046167018303602898</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2046167018303602898</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2046167018303602898</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>https://x.com/ArabiaCSR/status/2046167018303602898</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Excited to announce Mr Vijay Bains, Group Head of ESG &amp;amp; CSO at Emirates NBD, as a plenary speaker for Climate Finance 2.0 at the Global Sustainability &amp;amp; CSR Forum!
+With 20+ years in sustainable finance &amp;amp; leadership in ESG councils, Vijay brings unmatched expertise. Don’t miss it! https://t.co/ApxeVy3ABX</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>1776679207000</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2046167018303602898</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGVyD6AaAAAN0zx.jpg', 'type': 'photo', 'id': '2046167017145892864'}]</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>{'name': 'Arabia CSR Network', 'screenName': 'ArabiaCSR', 'followersCount': 3122, 'favouritesCount': 2298, 'friendsCount': 595, 'description': 'We are one of the very first multi-stakeholder platforms contributing to CSR &amp; sustainable development across the Arab world. #HappinessInSustainability'}</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="L5" t="n">
-        <v>1</v>
-      </c>
-      <c r="M5" t="n">
-        <v>26</v>
-      </c>
-      <c r="N5" t="n">
-        <v>264</v>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>639239</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" t="inlineStr">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>https://x.com/ArabiaCSR/status/2046167018303602898</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2046167018303602898</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2046118862736003268</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>https://x.com/ArabiaCSR/status/2046118862736003268</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Arabia CSR Network – Driving sustainability and responsible business across the MENA region.
+Through research, insights, and collaboration, we empower organisations to create meaningful CSR impact and shape a sustainable future.
+admin@arabiacsrnetwork.com
+https://t.co/FXjp8HUpNf https://t.co/gpTUlQf79R</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>1776667726000</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>2046118862736003268</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGVGQ4CakAAF6bs.jpg', 'type': 'photo', 'id': '2046118861444124672'}]</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>{'name': 'Arabia CSR Network', 'screenName': 'ArabiaCSR', 'followersCount': 3122, 'favouritesCount': 2298, 'friendsCount': 595, 'description': 'We are one of the very first multi-stakeholder platforms contributing to CSR &amp; sustainable development across the Arab world. #HappinessInSustainability'}</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="inlineStr">
         <is>
           <t>https://x.com/she7ii88/status/2046061240511082734</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>2046061240511082734</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2046061240511082734</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>https://x.com/she7ii88/status/2046061240511082734</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE هذا عرض صدق ؟! 
-٦% ؟! سلامات البنوك الاسلاميه المرابحه الثابته ٢.٧% ؟! 
-ولو سمحتوا علم الامارات و لبس القوات المسلحه ... ليست دعايه</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>1776653988000</v>
-      </c>
-      <c r="H6" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>2045093015459352679</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>{'name': 'Rashed Sem', 'screenName': 'she7ii88', 'followersCount': 9, 'favouritesCount': 303, 'friendsCount': 49, 'description': ''}</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2045093015459352679</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>https://x.com/almidfa75/status/2045894623957278735</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>2045894623957278735</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2045894611756048610</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>https://x.com/almidfa75/status/2045894611756048610</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>🧵 1/
-في خطوة تعكس تطور المنتجات المالية في السوق العقاري بدولة الإمارات، أعلن بنك Emirates NBD عن إطلاق نموذج تمويل مبكر للعقارات قيد الإنشاء (Off-plan)، بالتعاون مع Dubai Holding Real Estate.
-#دبي #القطاع_العقاري #التمويل https://t.co/qdzz3FJ7io</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>1776614260000</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>2045894611756048610</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGR6QSzbsAAwqIY.jpg', 'type': 'photo', 'id': '2045894551077105664'}]</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>{'name': 'Faisal Al Midfa', 'screenName': 'almidfa75', 'followersCount': 492, 'favouritesCount': 71, 'friendsCount': 237, 'description': ''}</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>https://x.com/almidfa75/status/2045894623957278735</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>2045894623957278735</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2045894614973087782</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>https://x.com/almidfa75/status/2045894614973087782</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>🧵 2/
-يتيح النموذج الجديد للعملاء:
-الحصول على موافقة مبدئية للتمويل العقاري في مرحلة مبكرة من عملية الشراء، وتحديدًا عند حجز الوحدة، بدلاً من الانتظار حتى قرب التسليم.</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>1776614261000</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>2045894611756048610</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>{'name': 'Faisal Al Midfa', 'screenName': 'almidfa75', 'followersCount': 492, 'favouritesCount': 71, 'friendsCount': 237, 'description': ''}</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2045894611756048610</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>https://x.com/almidfa75/status/2045894623957278735</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>2045894623957278735</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2045894617548349695</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>https://x.com/almidfa75/status/2045894617548349695</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>🧵 3/
-📊 من المتوقع أن يسهم هذا التوجه في:
-• تعزيز وضوح القدرة التمويلية للمستثمرين
-• دعم اتخاذ القرار الشرائي في مراحل مبكرة
-• رفع كفاءة دورة المبيعات لدى المطورين
-• تعزيز ثقة المستثمرين في المشاريع قيد الإنشاء</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>1776614262000</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>2045894611756048610</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>{'name': 'Faisal Al Midfa', 'screenName': 'almidfa75', 'followersCount': 492, 'favouritesCount': 71, 'friendsCount': 237, 'description': ''}</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>1</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>2045894614973087782</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>https://x.com/almidfa75/status/2045894623957278735</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>2045894623957278735</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2045894619729412301</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>https://x.com/almidfa75/status/2045894619729412301</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>🧵 4/
-⚠️ تجدر الإشارة إلى أن:
-هذا التطور يأتي ضمن إطار تطوير المنتجات التمويلية، ولا يمثل تغييرًا في التشريعات أو الأنظمة المنظمة للتمويل العقاري في الدولة.</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>1776614262000</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>2045894611756048610</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>{'name': 'Faisal Al Midfa', 'screenName': 'almidfa75', 'followersCount': 492, 'favouritesCount': 71, 'friendsCount': 237, 'description': ''}</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>2045894617548349695</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>https://x.com/almidfa75/status/2045894623957278735</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>2045894623957278735</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2045894621834903822</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>https://x.com/almidfa75/status/2045894621834903822</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>🧵 5/
-📈 من منظور السوق، قد ينعكس هذا التوجه على:
-• زيادة الإقبال على العقارات قيد الإنشاء
-• تسريع وتيرة الصفقات العقارية
-• دعم النشاط العام في القطاع العقاري
-مع بقاء الأثر الفعلي مرتبطًا بآليات التطبيق وشروط التمويل.</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>1776614263000</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>2045894611756048610</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>{'name': 'Faisal Al Midfa', 'screenName': 'almidfa75', 'followersCount': 492, 'favouritesCount': 71, 'friendsCount': 237, 'description': ''}</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2045894619729412301</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>https://x.com/almidfa75/status/2045894623957278735</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>2045894623957278735</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2045894623957278735</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>https://x.com/almidfa75/status/2045894623957278735</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>🧵 6/
-🎯 خلاصة:
-يمثل هذا الإعلان خطوة نوعية في تطوير حلول التمويل العقاري، ويعكس توجه المؤسسات المالية نحو تقديم منتجات أكثر مرونة تدعم نمو واستدامة السوق العقاري في دولة الإمارات.
-#دبي #التمويل_العقاري #استثمار #EmiratesNBD #DubaiHolding</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
-        <v>1776614263000</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>2045894611756048610</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>{'name': 'Faisal Al Midfa', 'screenName': 'almidfa75', 'followersCount': 492, 'favouritesCount': 71, 'friendsCount': 237, 'description': ''}</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2045894621834903822</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>https://x.com/f3100000/status/2045922728868479327</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>2045922728868479327</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2045093015459352679</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE/status/2045093015459352679</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>ندعم من يحمون الوطن
 مجموعة من مزايا الدعم المالي والخدمات المصرفية المخصصة للعاملين في الصفوف الأمامية
@@ -1326,493 +1785,6 @@
 https://t.co/I7DGlib9vt</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>1776423145000</v>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>2045093015459352679</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGGhQnfXsAAHpYo.jpg', 'type': 'photo', 'id': '2045093012653453312'}]</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174302, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="K13" t="n">
-        <v>17</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>26</v>
-      </c>
-      <c r="N13" t="n">
-        <v>264</v>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>639313</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>https://x.com/f3100000/status/2045922728868479327</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>2045922728868479327</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2045922728868479327</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>https://x.com/f3100000/status/2045922728868479327</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE دعم من اي نوع هذا</t>
-        </is>
-      </c>
-      <c r="G14" t="n">
-        <v>1776620964000</v>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>2045093015459352679</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>{'name': 'F35', 'screenName': 'f3100000', 'followersCount': 13, 'favouritesCount': 1420, 'friendsCount': 94, 'description': 'Name'}</t>
-        </is>
-      </c>
-      <c r="K14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>2045093015459352679</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>https://x.com/f3100000/status/2045922728868479327</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>2045922728868479327</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2045925406272856232</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2045925406272856232</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>@f3100000 مرحباً، شكراً لتواصلكم معنا، يُرجى مراسلتنا عبر الرسائل الخاصة، كيف يُمكننا مساعدتكم؟ شكراً - زبير</t>
-        </is>
-      </c>
-      <c r="G15" t="n">
-        <v>1776621602000</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>2045093015459352679</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174302, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>2045922728868479327</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>https://x.com/almidfa75/status/2045894611756048610</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>2045894611756048610</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>2045894611756048610</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>https://x.com/almidfa75/status/2045894611756048610</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>🧵 1/
-في خطوة تعكس تطور المنتجات المالية في السوق العقاري بدولة الإمارات، أعلن بنك Emirates NBD عن إطلاق نموذج تمويل مبكر للعقارات قيد الإنشاء (Off-plan)، بالتعاون مع Dubai Holding Real Estate.
-#دبي #القطاع_العقاري #التمويل https://t.co/qdzz3FJ7io</t>
-        </is>
-      </c>
-      <c r="G16" t="n">
-        <v>1776614260000</v>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>2045894611756048610</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGR6QSzbsAAwqIY.jpg', 'type': 'photo', 'id': '2045894551077105664'}]</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>{'name': 'Faisal Al Midfa', 'screenName': 'almidfa75', 'followersCount': 492, 'favouritesCount': 71, 'friendsCount': 237, 'description': ''}</t>
-        </is>
-      </c>
-      <c r="K16" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>1</v>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>https://x.com/almidfa75/status/2045894611756048610</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>2045894611756048610</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>2045894614973087782</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>https://x.com/almidfa75/status/2045894614973087782</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>🧵 2/
-يتيح النموذج الجديد للعملاء:
-الحصول على موافقة مبدئية للتمويل العقاري في مرحلة مبكرة من عملية الشراء، وتحديدًا عند حجز الوحدة، بدلاً من الانتظار حتى قرب التسليم.</t>
-        </is>
-      </c>
-      <c r="G17" t="n">
-        <v>1776614261000</v>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>2045894611756048610</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>{'name': 'Faisal Al Midfa', 'screenName': 'almidfa75', 'followersCount': 492, 'favouritesCount': 71, 'friendsCount': 237, 'description': ''}</t>
-        </is>
-      </c>
-      <c r="K17" t="n">
-        <v>1</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>2045894611756048610</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>https://x.com/r35sk/status/2045850840196694451</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>2045850840196694451</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2045850840196694451</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>https://x.com/r35sk/status/2045850840196694451</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>الحمدلله الحمرا فيها صرافة enbd</t>
-        </is>
-      </c>
-      <c r="G18" t="n">
-        <v>1776603825000</v>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>2045850840196694451</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>{'name': 'ريم', 'screenName': 'r35sk', 'followersCount': 2561, 'favouritesCount': 14, 'friendsCount': 770, 'description': ''}</t>
-        </is>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>https://x.com/r35sk/status/2045850840196694451</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>2045850840196694451</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2045584134823870598</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>https://x.com/r35sk/status/2045584134823870598</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>الوداعيةةة https://t.co/p08tSNxQZ3</t>
-        </is>
-      </c>
-      <c r="G19" t="n">
-        <v>1776540237000</v>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>2045584134823870598</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGNf4JsaIAA3hjJ.jpg', 'type': 'photo', 'id': '2045584074035830784'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGNf4JhasAEZi4Z.jpg', 'type': 'photo', 'id': '2045584073989730305'}, {'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2045584074031648768/img/_lP3Wq_s_e6lrB7p.jpg', 'type': 'video', 'id': '2045584074031648768'}]</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>{'name': 'ريم', 'screenName': 'r35sk', 'followersCount': 2561, 'favouritesCount': 14, 'friendsCount': 770, 'description': ''}</t>
-        </is>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>2</v>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>https://x.com/AhmedAlhaq79518/status/2045850184811422052</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>2045850184811422052</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>2045093015459352679</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2045093015459352679</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>ندعم من يحمون الوطن
-مجموعة من مزايا الدعم المالي والخدمات المصرفية المخصصة للعاملين في الصفوف الأمامية
-•استرداد نقدي 10% بحد أقصى 400 درهم
-•سعر فائدة ثابت بنسبة 6% لجميع الموظفين الجدد الذي يقومون بتحويل رواتبهم
-•تمديد فترة تحويل الراتب
-•إعفاء من رسوم الحد الأدنى للرصيد للعملاء غير المحوّلة رواتبهم
-•إعفاءات على رسوم القروض مع أولوية معالجة الطلبات
-يسري العرض حتى 30 يونيو 2026.
-تُطبق الشروط والأحكام.
-https://t.co/I7DGlib9vt</t>
-        </is>
-      </c>
       <c r="G20" t="n">
         <v>1776423145000</v>
       </c>
@@ -1828,24 +1800,24 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174302, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174304, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L20" t="n">
         <v>1</v>
       </c>
       <c r="M20" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="N20" t="n">
-        <v>264</v>
+        <v>344</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>639367</t>
+          <t>862471</t>
         </is>
       </c>
       <c r="P20" t="inlineStr"/>
@@ -1856,31 +1828,33 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>https://x.com/AhmedAlhaq79518/status/2045850184811422052</t>
+          <t>https://x.com/she7ii88/status/2046061240511082734</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2045850184811422052</t>
+          <t>2046061240511082734</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2045850184811422052</t>
+          <t>2046061240511082734</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://x.com/AhmedAlhaq79518/status/2045850184811422052</t>
+          <t>https://x.com/she7ii88/status/2046061240511082734</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE فعلا بنك مميز بمعني الكلمه والصقه بهم متوفره عندي علاجه.</t>
+          <t>@EmiratesNBD_AE هذا عرض صدق ؟! 
+٦% ؟! سلامات البنوك الاسلاميه المرابحه الثابته ٢.٧% ؟! 
+ولو سمحتوا علم الامارات و لبس القوات المسلحه ... ليست دعايه</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>1776603668000</v>
+        <v>1776653988000</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1894,7 +1868,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>{'name': 'Ahmed Alhaìqi', 'screenName': 'AhmedAlhaq79518', 'followersCount': 63, 'favouritesCount': 4335, 'friendsCount': 154, 'description': 'عود لسانك بقول الحق تعداء به....\nان اللسان لما عودت تعداء به...'}</t>
+          <t>{'name': 'Rashed Sem', 'screenName': 'she7ii88', 'followersCount': 9, 'favouritesCount': 303, 'friendsCount': 49, 'description': ''}</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -1911,7 +1885,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>87</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -1926,35 +1900,36 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>https://x.com/m_azeemq/status/2045824669907845529</t>
+          <t>https://x.com/khaleejtimes/status/2046166030557614556</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2045824669907845529</t>
+          <t>2046166030557614556</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2045824669907845529</t>
+          <t>2046166030557614556</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://x.com/m_azeemq/status/2045824669907845529</t>
+          <t>https://x.com/khaleejtimes/status/2046166030557614556</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA ,It is extremely disappointing to experience such unprofessional customer support. Despite repeated attempts to contact you via email and phone, I have received no meaningful response/clarification on my issue which is pending now since more than 2.5 month</t>
+          <t>Emirates NBD extends fee waivers, 0% interest on credit card transfers for UAE customers
+https://t.co/sNYXzG1RYE</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>1776597585000</v>
+        <v>1776678972000</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2045824669907845529</t>
+          <t>2046166030557614556</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1964,24 +1939,24 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>{'name': 'Muhammad Azeem Qureshi', 'screenName': 'm_azeemq', 'followersCount': 3, 'favouritesCount': 5, 'friendsCount': 74, 'description': ''}</t>
+          <t>{'name': 'Khaleej Times', 'screenName': 'khaleejtimes', 'followersCount': 1195567, 'favouritesCount': 43, 'friendsCount': 1565, 'description': "The official Twitter feed of Khaleej Times, the UAE's first and leading English daily\nhttps://t.co/bKx3o3oPhX"}</t>
         </is>
       </c>
       <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
         <v>2</v>
       </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8330</t>
         </is>
       </c>
       <c r="P22" t="inlineStr"/>
@@ -1992,69 +1967,66 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>https://x.com/m_azeemq/status/2045824669907845529</t>
+          <t>https://x.com/khaleejtimes/status/2046166030557614556</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2045824669907845529</t>
+          <t>2046166030557614556</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2045825753510478080</t>
+          <t>2046265860453761085</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2045825753510478080</t>
+          <t>https://x.com/Cricket_bazball/status/2046265860453761085</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>@m_azeemq Hi Muhammad, we are extremely sorry for the delay, and we have sent followup email to our team to contact you as soon as possible with an update.</t>
+          <t>🚨 End of Mike Hesson 🚨
+- PCB has decided to sack Mike Hesson from the role of Pakistan team’s head coach and has decided to appoint Ottis Gibson as the new head coach for white-ball cricket. (Geo news) https://t.co/nvlKVuP4il</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>1776597843000</v>
+        <v>1776702773000</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2045824669907845529</t>
+          <t>2046265860453761085</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGXL9DraAAMigd2.jpg', 'type': 'photo', 'id': '2046265855529582595'}]</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17329, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
+          <t>{'name': 'junaid', 'screenName': 'Cricket_bazball', 'followersCount': 145, 'favouritesCount': 174811, 'friendsCount': 258, 'description': 'Cricket • Stats • Not affiliated with anyone'}</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>752</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>2045824669907845529</t>
-        </is>
-      </c>
+          <t>35692</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
@@ -2062,71 +2034,63 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>https://x.com/abasetaljanahi/status/2045805999718903933</t>
+          <t>https://x.com/Kyodonews_JBN/status/2046033950339166455</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2045805999718903933</t>
+          <t>2046033950339166455</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2045093015459352679</t>
+          <t>2046033950339166455</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2045093015459352679</t>
+          <t>https://x.com/Kyodonews_JBN/status/2046033950339166455</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ندعم من يحمون الوطن
-مجموعة من مزايا الدعم المالي والخدمات المصرفية المخصصة للعاملين في الصفوف الأمامية
-•استرداد نقدي 10% بحد أقصى 400 درهم
-•سعر فائدة ثابت بنسبة 6% لجميع الموظفين الجدد الذي يقومون بتحويل رواتبهم
-•تمديد فترة تحويل الراتب
-•إعفاء من رسوم الحد الأدنى للرصيد للعملاء غير المحوّلة رواتبهم
-•إعفاءات على رسوم القروض مع أولوية معالجة الطلبات
-يسري العرض حتى 30 يونيو 2026.
-تُطبق الشروط والأحكام.
-https://t.co/I7DGlib9vt</t>
+          <t>Emirates NBD、Dar Global向け2億5,000万米ドルのシンジケート・タームローンを実行し、世界的な成長と事業拡大を加速【Dar Global】
+https://t.co/H82MnfRa04</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>1776423145000</v>
+        <v>1776647481000</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2045093015459352679</t>
+          <t>2046033950339166455</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGGhQnfXsAAHpYo.jpg', 'type': 'photo', 'id': '2045093012653453312'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174302, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'KYODONEWS JBN', 'screenName': 'Kyodonews_JBN', 'followersCount': 22, 'favouritesCount': 6, 'friendsCount': 2, 'description': '株式会社共同通信社 ジャパンビジネス広報センター'}</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>264</v>
+        <v>0</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>639512</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P24" t="inlineStr"/>
@@ -2137,36 +2101,36 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>https://x.com/abasetaljanahi/status/2045805999718903933</t>
+          <t>https://x.com/Kyodonews_JBN/status/2046033950339166455</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2045805999718903933</t>
+          <t>2046033950339166455</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2045805999718903933</t>
+          <t>2046424774474391989</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://x.com/abasetaljanahi/status/2045805999718903933</t>
+          <t>https://x.com/Kyodonews_JBN/status/2046424774474391989</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE بس! 
-وايد عليكم</t>
+          <t>Singapore imagines new ways of living at Milan Design Week with the opening of Prototype Island【DesignSingapore Council】
+https://t.co/SxdfkcpvgF</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>1776593134000</v>
+        <v>1776740661000</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2045093015459352679</t>
+          <t>2046424774474391989</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2176,11 +2140,11 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>{'name': 'Abdulbaset Al Janahi', 'screenName': 'abasetaljanahi', 'followersCount': 5898, 'favouritesCount': 4331, 'friendsCount': 1383, 'description': ''}</t>
+          <t>{'name': 'KYODONEWS JBN', 'screenName': 'Kyodonews_JBN', 'followersCount': 22, 'favouritesCount': 6, 'friendsCount': 2, 'description': '株式会社共同通信社 ジャパンビジネス広報センター'}</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -2193,14 +2157,10 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>2045093015459352679</t>
-        </is>
-      </c>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
@@ -2208,69 +2168,78 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>https://x.com/abasetaljanahi/status/2045805999718903933</t>
+          <t>https://x.com/mohmd_moh/status/2046224051438526663</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2045805999718903933</t>
+          <t>2046224051438526663</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2045806421590110590</t>
+          <t>2044321422282240384</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2045806421590110590</t>
+          <t>https://x.com/ADIBTweets/status/2044321422282240384</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>@abasetaljanahi مرحبًا، هل يمكننا معرفة سبب عدم رضاك؟ سيكون من المفيد جدًا إذا كان بإمكانك مشاركة المزيد من التفاصيل حول ذلك ورقم اتصالك معنا عبر الرسائل الخاصة.</t>
+          <t>قد تكون رسالة من “قريب”... لكنها احتيال. 
+أجب واربح 
+تلقيت رسالة من صديقك يطلب منك بشكل عاجل تحويل مبلغ مالي إلى حسابه، مدّعياً أن هناك حالة طارئة. ماذا يجب أن تفعل؟
+أ. تحوّل المبلغ فوراً لمساعدة صديقك
+ب. تتحقّق من الأمر عبر الاتصال بصديقك
+ج. تثق بالرسالة لأنها واردة من حساب صديقك
+للمشاركة:
+أجب بشكل صحيح في التعليقات 
+قم بعمل منشن لشخصين 
+تابع حسابنا على X
+سيتم الإعلان عن الفائز بتاريخ 5 مايو 2026
+يرجى زيارة  https://t.co/4RkTsyGuDX للاطلاع على الشروط والأحكام
+تقتصر المشاركة على مواطني دولة الإمارات العربية المتحدة أو المقيمين في الدولة الذين يحملون بطاقة هوية سارية المفعول.
+مسابقة_مصرف_أبوظبي_الإسلامي</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>1776593234000</v>
+        <v>1776239183000</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2045093015459352679</t>
+          <t>2044321422282240384</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF7jf0ba0AAZFPu.jpg', 'type': 'photo', 'id': '2044321416661880832'}]</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174302, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'ADIB Tweets', 'screenName': 'ADIBTweets', 'followersCount': 137563, 'favouritesCount': 2888, 'friendsCount': 104, 'description': 'حياكم في الحساب الرسمي لمصرف أبوظبي الإسلامي، شركة مساهمة عامة. Welcome to Abu Dhabi Islamic Bank Public Joint Stock Company official account'}</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>393</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>206</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>196</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>2045805999718903933</t>
-        </is>
-      </c>
+          <t>1435284</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
@@ -2278,74 +2247,70 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>https://x.com/UaeAlteneiji/status/2045814764828516809</t>
+          <t>https://x.com/mohmd_moh/status/2046224051438526663</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2045814764828516809</t>
+          <t>2046224051438526663</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2045093015459352679</t>
+          <t>2045175695169732901</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2045093015459352679</t>
+          <t>https://x.com/mohmd_moh/status/2045175695169732901</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>ندعم من يحمون الوطن
-مجموعة من مزايا الدعم المالي والخدمات المصرفية المخصصة للعاملين في الصفوف الأمامية
-•استرداد نقدي 10% بحد أقصى 400 درهم
-•سعر فائدة ثابت بنسبة 6% لجميع الموظفين الجدد الذي يقومون بتحويل رواتبهم
-•تمديد فترة تحويل الراتب
-•إعفاء من رسوم الحد الأدنى للرصيد للعملاء غير المحوّلة رواتبهم
-•إعفاءات على رسوم القروض مع أولوية معالجة الطلبات
-يسري العرض حتى 30 يونيو 2026.
-تُطبق الشروط والأحكام.
-https://t.co/I7DGlib9vt</t>
+          <t>لماذ البنك لايتحمل المسوؤلية إذا تم اختراق الحساب الشخصي وتم سحب مبلغ من المال بدون اي ادارة امن الحسابات او عن طريق ارسال OTP ويدعي انه تم التحويل بالفعل والبنك غير قادر علي فعل شيي و يجب ان يتحمل صاحب الحساب تكاليف اصدار بطاقة جديده و تحمل المبلغ المسحوب و كأن الحسابات الشخصية سبيل متاح لاي عملية إحتيال وعلي صاحب الحساب تحمل كامل المسؤلية والبنك الذي من المفترض هو المؤتمن علي هذا المال لايتحمل إي مسؤلية.. علي فكره انتم من البنوك التي لاتهتم بحمايه العميل لكن هناك بنوك مثل الامارات الإسلامي له كل الشكر والامتنان لانه حدث معي عمليه احتيال و خلال اسبوع تحمل البنك المبلغ وتم إيداعه في حسابي وتم اصدار بطاقة جديده بدون اي تكلفة.
+كل الشكر الي بنك الإمارات الإسلامي @emiratesislamic</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>1776423145000</v>
+        <v>1776442857000</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2045093015459352679</t>
+          <t>2044321422282240384</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGGhQnfXsAAHpYo.jpg', 'type': 'photo', 'id': '2045093012653453312'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174302, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Mohamed Mohamed', 'screenName': 'mohmd_moh', 'followersCount': 195, 'favouritesCount': 6659, 'friendsCount': 1287, 'description': ''}</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="L27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>264</v>
+        <v>0</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>639512</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr"/>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>2044321422282240384</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
@@ -2353,39 +2318,35 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>https://x.com/UaeAlteneiji/status/2045814764828516809</t>
+          <t>https://x.com/mohmd_moh/status/2046224051438526663</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2045814764828516809</t>
+          <t>2046224051438526663</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2045814764828516809</t>
+          <t>2046125857643606493</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://x.com/UaeAlteneiji/status/2045814764828516809</t>
+          <t>https://x.com/emiratesislamic/status/2046125857643606493</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE من شكل الاعلان باين انه مجرد دعاية للبنك وليس دعماً لحماة الوطن
-اعلان غير موفق
-اعلان محدد بتاريخ صلاحية 
-اعلان تحكمه الشروط والاحكام المجهولة
-هنالك بنوك أخرى تقدم عروض تتافسية جذابة أكثر ومزايا أفضل وأحسن وتقدم لجميع العملاء ولعامة الشعب دون منية</t>
+          <t>@mohmd_moh مرحبا ، يأسفنا سماع تجربتك! فريقنا ملتزم بمعالجة هذا الأمر على الفور. لحماية خصوصيتك ، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل. رضاك أولويتنا.</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>1776595223000</v>
+        <v>1776669394000</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2045093015459352679</t>
+          <t>2044321422282240384</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2395,7 +2356,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>{'name': 'أبو عمر ، عبدالرحمن الطنيجي', 'screenName': 'UaeAlteneiji', 'followersCount': 2975, 'favouritesCount': 49730, 'friendsCount': 3074, 'description': 'يبقى الانسان في هذه الحياه مثل قلم الرصاص ! تبريه الأيام لـ يكتب بخط أجمل وهكذا حتى يفنى القلم فلا يبقى له إلا جميل ماكتب .الإمارات  خط أحمر🇦🇪'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="K28" t="n">
@@ -2412,12 +2373,12 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2045093015459352679</t>
+          <t>2045175695169732901</t>
         </is>
       </c>
     </row>
@@ -2427,35 +2388,37 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>https://x.com/UaeAlteneiji/status/2045814764828516809</t>
+          <t>https://x.com/mohmd_moh/status/2046224051438526663</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2045814764828516809</t>
+          <t>2046224051438526663</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2045815303024545800</t>
+          <t>2046224051438526663</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2045815303024545800</t>
+          <t>https://x.com/mohmd_moh/status/2046224051438526663</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>@UaeAlteneiji مرحبًا، هل يمكننا معرفة سبب عدم رضاك؟ سيكون من المفيد جدًا إذا كان بإمكانك مشاركة المزيد من التفاصيل حول ذلك ورقم اتصالك معنا عبر الرسائل الخاصة.</t>
+          <t>الشكر الجزيل لكم .  ليس لدي اي مشكلة حاليا أنا فقط ذكرت ماحدث معي للإشادة بكم علي سرعة الحل المقدم من طرفكم وسرعة استجابتكم وتحملكم المسؤلية تجاه العملاء .
+تعامل راقي وليس هدفكم المكسب فقط ولكن هدفكم الاول هو ارضاء العميل وهذا ذكاء منكم لأنكم بهذا الأسلوب سوف تكسبوا ثقة العملاء وبالتالي زيادة العملاء ويأتي المكسب مضاعف لاحقا . 
+كلمة حق تقال ان نهج الإمارات الإسلامي يستحق ان يقتدي به جميع البنوك.</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>1776595352000</v>
+        <v>1776692805000</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2045093015459352679</t>
+          <t>2044321422282240384</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2465,7 +2428,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174302, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Mohamed Mohamed', 'screenName': 'mohmd_moh', 'followersCount': 195, 'favouritesCount': 6659, 'friendsCount': 1287, 'description': ''}</t>
         </is>
       </c>
       <c r="K29" t="n">
@@ -2482,12 +2445,12 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>23</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2045814764828516809</t>
+          <t>2046125857643606493</t>
         </is>
       </c>
     </row>
@@ -2497,37 +2460,37 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>https://x.com/CWSaudi/status/2045821589539733783</t>
+          <t>https://x.com/aaditsh/status/2046217543870738694</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2045821589539733783</t>
+          <t>2046217543870738694</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2045821589539733783</t>
+          <t>2044732404938702855</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://x.com/CWSaudi/status/2045821589539733783</t>
+          <t>https://x.com/aaditsh/status/2044732404938702855</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>. @dar_global  has secured a $250M loan arranged by @EmiratesNBD_AE , as the #London -listed developer behind @realDonaldTrump -branded projects expands its pipeline.
-Read more:
-https://t.co/fLtvZJMVhg</t>
+          <t>@emiratesislamic probably the worst customer experience I’ve had in my life.
+Tried cancelling my cards. Have received 10+ phone calls from them trying to retain. Confirmed each time that I want to cancel (on call and on email confirmation). It’s been 4-5 months since I raised this complaint. No resolution yet.
+Impressed with how difficult they make this process. Wow!</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>1776596851000</v>
+        <v>1776337169000</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2045821589539733783</t>
+          <t>2044732404938702855</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2537,11 +2500,11 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>{'name': 'Construction Week Saudi', 'screenName': 'CWSaudi', 'followersCount': 309, 'favouritesCount': 11, 'friendsCount': 6, 'description': 'A digital B2B platform catering to the construction and engineering industry in the Kingdom of Saudi Arabia.\nAn @itpmediagroup publication.'}</t>
+          <t>{'name': 'Aadit Sheth', 'screenName': 'aaditsh', 'followersCount': 523004, 'favouritesCount': 32071, 'friendsCount': 588, 'description': 'Co-founder, The Narrative Company. We help Fortune 500 C-suite engineer their biggest moments. Also write Neatprompts, 100K+ subscribers.'}</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -2550,11 +2513,11 @@
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>6419</t>
         </is>
       </c>
       <c r="P30" t="inlineStr"/>
@@ -2565,37 +2528,35 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>https://x.com/CWSaudi/status/2045821589539733783</t>
+          <t>https://x.com/aaditsh/status/2046217543870738694</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2045821589539733783</t>
+          <t>2046217543870738694</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2045736398255194361</t>
+          <t>2044758862017007662</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://x.com/CWSaudi/status/2045736398255194361</t>
+          <t>https://x.com/RakeshMavath/status/2044758862017007662</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>#SaudiArabia extends the Landbridge rail bid deadline to April 29 as #Hormuz disruptions highlight its lack of a direct east–west freight rail link.
-Read more ll
-https://t.co/UvrhC24nWJ</t>
+          <t>@aaditsh @emiratesislamic especially now they are not going to let go of your business easily. you can raise the issue with UAECB who will in turn contact the bank</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>1776576539000</v>
+        <v>1776343477000</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2045736398255194361</t>
+          <t>2044732404938702855</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2605,27 +2566,31 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>{'name': 'Construction Week Saudi', 'screenName': 'CWSaudi', 'followersCount': 309, 'favouritesCount': 11, 'friendsCount': 6, 'description': 'A digital B2B platform catering to the construction and engineering industry in the Kingdom of Saudi Arabia.\nAn @itpmediagroup publication.'}</t>
+          <t>{'name': 'Rakesh Mavath', 'screenName': 'RakeshMavath', 'followersCount': 367, 'favouritesCount': 12526, 'friendsCount': 3077, 'description': 'Running two startups: one guarantees your rent @takeem_ai, the other guarantees your dignity. Still waiting for my guaranteed 8 hours of sleep.'}</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>303</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr"/>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>2044732404938702855</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
@@ -2633,35 +2598,36 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>https://x.com/SultanAbdu70381/status/2045786366504796559</t>
+          <t>https://x.com/aaditsh/status/2046217543870738694</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2045786366504796559</t>
+          <t>2046217543870738694</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2045776312099656112</t>
+          <t>2044759599656689929</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://x.com/SultanAbdu70381/status/2045776312099656112</t>
+          <t>https://x.com/aaditsh/status/2044759599656689929</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>نحتاج تأجيل 3 شهور للازمه</t>
+          <t>@RakeshMavath @emiratesislamic Will do! So frustrating. They will call me, I’ll pick up. They will end the call within 10 seconds and message me “we called you. You didn’t pick up”.
+And it’s been extended like this for the past 4-5 months. What a joke.</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>1776586056000</v>
+        <v>1776343653000</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2045776312099656112</t>
+          <t>2044732404938702855</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2671,7 +2637,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>{'name': 'Sultan Abdullah', 'screenName': 'SultanAbdu70381', 'followersCount': 25, 'favouritesCount': 1922, 'friendsCount': 28, 'description': 'هلا'}</t>
+          <t>{'name': 'Aadit Sheth', 'screenName': 'aaditsh', 'followersCount': 523004, 'favouritesCount': 32071, 'friendsCount': 588, 'description': 'Co-founder, The Narrative Company. We help Fortune 500 C-suite engineer their biggest moments. Also write Neatprompts, 100K+ subscribers.'}</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -2684,14 +2650,18 @@
         <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>430</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr"/>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>2044758862017007662</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
@@ -2699,35 +2669,35 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>https://x.com/SultanAbdu70381/status/2045786366504796559</t>
+          <t>https://x.com/aaditsh/status/2046217543870738694</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2045786366504796559</t>
+          <t>2046217543870738694</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2045784123353034764</t>
+          <t>2044832798670995759</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2045784123353034764</t>
+          <t>https://x.com/RakeshMavath/status/2044832798670995759</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>@SultanAbdu70381 مرحباً بك، شكراً لتواصلك معنا. لضمان تجربة مصرفية سلسة وآمنة، يرجى التواصل مع دعم العملاء على مدار الساعة عبر الهاتف أو واتساب على الرقم 971600540000 لمساعدتك في استفسارك. يساعدنا هذا في الحفاظ على أعلى معايير الأمان لحسابك. شكراً لتفهمك.</t>
+          <t>@aaditsh @emiratesislamic Grab screenshots of when they have called you and the following messages include that to your complaint to UAECB and they will fine the bank</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>1776587918000</v>
+        <v>1776361105000</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2045776312099656112</t>
+          <t>2044732404938702855</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2737,11 +2707,11 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174302, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Rakesh Mavath', 'screenName': 'RakeshMavath', 'followersCount': 367, 'favouritesCount': 12526, 'friendsCount': 3077, 'description': 'Running two startups: one guarantees your rent @takeem_ai, the other guarantees your dignity. Still waiting for my guaranteed 8 hours of sleep.'}</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -2750,16 +2720,16 @@
         <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>35</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2045776312099656112</t>
+          <t>2044759599656689929</t>
         </is>
       </c>
     </row>
@@ -2769,35 +2739,35 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>https://x.com/SultanAbdu70381/status/2045786366504796559</t>
+          <t>https://x.com/aaditsh/status/2046217543870738694</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2045786366504796559</t>
+          <t>2046217543870738694</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2045786366504796559</t>
+          <t>2046217543870738694</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://x.com/SultanAbdu70381/status/2045786366504796559</t>
+          <t>https://x.com/aaditsh/status/2046217543870738694</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE اكثر البنوك فالدولة تساهلت مع متعامليها لتوفير راحتهم واحتياجاتهم وليس لزياده ضغط عليهم حيث قامو بتأجيل قروض لهم ٣ اشهر مساعده لهم لضروفهم خاصه دفاع الأول وشكرا لكم</t>
+          <t>@RakeshMavath @emiratesislamic Alright. Will do! Thanks.</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>1776588453000</v>
+        <v>1776691253000</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2045776312099656112</t>
+          <t>2044732404938702855</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2807,7 +2777,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>{'name': 'Sultan Abdullah', 'screenName': 'SultanAbdu70381', 'followersCount': 25, 'favouritesCount': 1922, 'friendsCount': 28, 'description': 'هلا'}</t>
+          <t>{'name': 'Aadit Sheth', 'screenName': 'aaditsh', 'followersCount': 523004, 'favouritesCount': 32071, 'friendsCount': 588, 'description': 'Co-founder, The Narrative Company. We help Fortune 500 C-suite engineer their biggest moments. Also write Neatprompts, 100K+ subscribers.'}</t>
         </is>
       </c>
       <c r="K34" t="n">
@@ -2820,16 +2790,16 @@
         <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2045784123353034764</t>
+          <t>2044832798670995759</t>
         </is>
       </c>
     </row>
@@ -2839,71 +2809,63 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>https://x.com/amerbinhraiz/status/2045801203934925261</t>
+          <t>https://x.com/emiratesislamic/status/2046148194392740002</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2045801203934925261</t>
+          <t>2046148194392740002</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2045093015459352679</t>
+          <t>2046148156560121974</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2045093015459352679</t>
+          <t>https://x.com/emiratesislamic/status/2046148156560121974</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>ندعم من يحمون الوطن
-مجموعة من مزايا الدعم المالي والخدمات المصرفية المخصصة للعاملين في الصفوف الأمامية
-•استرداد نقدي 10% بحد أقصى 400 درهم
-•سعر فائدة ثابت بنسبة 6% لجميع الموظفين الجدد الذي يقومون بتحويل رواتبهم
-•تمديد فترة تحويل الراتب
-•إعفاء من رسوم الحد الأدنى للرصيد للعملاء غير المحوّلة رواتبهم
-•إعفاءات على رسوم القروض مع أولوية معالجة الطلبات
-يسري العرض حتى 30 يونيو 2026.
-تُطبق الشروط والأحكام.
-https://t.co/I7DGlib9vt</t>
+          <t>امنح أبنائك انطلاقة مبكرة نحو الوعي المالي الذكي
+ #الإمارات_الإسلامي https://t.co/xdFKEhpKDT</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>1776423145000</v>
+        <v>1776674710000</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2045093015459352679</t>
+          <t>2046148156560121974</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGGhQnfXsAAHpYo.jpg', 'type': 'photo', 'id': '2045093012653453312'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/ext_tw_video_thumb/2046148122250809344/pu/img/WEGHCsaWoyjDb-ot.jpg', 'type': 'video', 'id': '2046148122250809344'}]</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174302, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="L35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>264</v>
+        <v>0</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>639595</t>
+          <t>54</t>
         </is>
       </c>
       <c r="P35" t="inlineStr"/>
@@ -2914,48 +2876,46 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>https://x.com/amerbinhraiz/status/2045801203934925261</t>
+          <t>https://x.com/emiratesislamic/status/2046148194392740002</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2045801203934925261</t>
+          <t>2046148194392740002</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2045801203934925261</t>
+          <t>2046148194392740002</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://x.com/amerbinhraiz/status/2045801203934925261</t>
+          <t>https://x.com/emiratesislamic/status/2046148194392740002</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE نريدكم تلغون الفايدة من اصحاب 
-المديونيات الطويلة القديمة
-كل شي واقف عليهم وماخذين فايدة
- عليهم ضعف قيمة القرض !</t>
+          <t>Your child's smart money journey starts here. Empower your kids to take their first steps toward financial independence. 
+#EmiratesIslamic #AlphaYouth https://t.co/udWgfz8rNb</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>1776591990000</v>
+        <v>1776674719000</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2045093015459352679</t>
+          <t>2046148156560121974</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/ext_tw_video_thumb/2046148161090068480/pu/img/GpPJv5a4DR5wZAQc.jpg', 'type': 'video', 'id': '2046148161090068480'}]</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>{'name': 'بـتـال | Batal', 'screenName': 'amerbinhraiz', 'followersCount': 1084, 'favouritesCount': 1309, 'friendsCount': 349, 'description': 'يرحل الأشخاص ويبقى الوطن يساراً جهة القلب'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="K36" t="n">
@@ -2972,12 +2932,12 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>46</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2045093015459352679</t>
+          <t>2046148156560121974</t>
         </is>
       </c>
     </row>
@@ -2987,49 +2947,52 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>https://x.com/SultanAbdu70381/status/2045785730023301620</t>
+          <t>https://x.com/gassann20203/status/2046215734481834418</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2045785730023301620</t>
+          <t>2046215734481834418</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2045776312099656112</t>
+          <t>2046215312949879234</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://x.com/SultanAbdu70381/status/2045776312099656112</t>
+          <t>https://x.com/emiratesislamic/status/2046215312949879234</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>نحتاج تأجيل 3 شهور للازمه</t>
+          <t>Exclusively for Emaratis. Apply for an Emarati Credit Card &amp;amp; get a welcome bonus of up to 150,000 EI SmartMiles worth AED 1,500
+✅ No annual membership fee
+📈 Earn up to 3.75 EI SmartMiles back per AED spend
+🍔 50% discount on talabat https://t.co/pIT39d8ym8</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>1776586056000</v>
+        <v>1776690722000</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2045776312099656112</t>
+          <t>2046215312949879234</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGWd-66WYAAChSk.jpg', 'type': 'photo', 'id': '2046215310001201152'}]</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>{'name': 'Sultan Abdullah', 'screenName': 'SultanAbdu70381', 'followersCount': 25, 'favouritesCount': 1922, 'friendsCount': 28, 'description': 'هلا'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
@@ -3042,7 +3005,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>60</t>
         </is>
       </c>
       <c r="P37" t="inlineStr"/>
@@ -3053,35 +3016,35 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>https://x.com/SultanAbdu70381/status/2045785730023301620</t>
+          <t>https://x.com/gassann20203/status/2046215734481834418</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2045785730023301620</t>
+          <t>2046215734481834418</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2045784123353034764</t>
+          <t>2046215734481834418</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2045784123353034764</t>
+          <t>https://x.com/gassann20203/status/2046215734481834418</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>@SultanAbdu70381 مرحباً بك، شكراً لتواصلك معنا. لضمان تجربة مصرفية سلسة وآمنة، يرجى التواصل مع دعم العملاء على مدار الساعة عبر الهاتف أو واتساب على الرقم 971600540000 لمساعدتك في استفسارك. يساعدنا هذا في الحفاظ على أعلى معايير الأمان لحسابك. شكراً لتفهمك.</t>
+          <t>@emiratesislamic انتم بس لا تسرقونا واكفوناةشركمةزخيركم</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>1776587918000</v>
+        <v>1776690822000</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2045776312099656112</t>
+          <t>2046215312949879234</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3091,11 +3054,11 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174302, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'gazan', 'screenName': 'gassann20203', 'followersCount': 36, 'favouritesCount': 17, 'friendsCount': 35, 'description': 'Bloch chain expert'}</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
@@ -3108,12 +3071,12 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>2045776312099656112</t>
+          <t>2046215312949879234</t>
         </is>
       </c>
     </row>
@@ -3123,35 +3086,39 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>https://x.com/SultanAbdu70381/status/2045785730023301620</t>
+          <t>https://x.com/emiratesislamic/status/2046106592232214645</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2045785730023301620</t>
+          <t>2046106592232214645</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2045785730023301620</t>
+          <t>2046106592232214645</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://x.com/SultanAbdu70381/status/2045785730023301620</t>
+          <t>https://x.com/emiratesislamic/status/2046106592232214645</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE عند الإعلان يجب وضع التوضيح وليس وضع إعلان بموضوع واتخاذ إجراءات وأوامر أخرى شكرا لكم</t>
+          <t>Legitimate delivery companies don’t ask for extra payments through unsecured links.
+Do not fall for the traps. Stay alert to scams.
+#EIAgainstFraud with Emirates Islamic.
+#TogetherAgainstFraud
+https://t.co/y7eSpGNdfk</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>1776588301000</v>
+        <v>1776664801000</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2045776312099656112</t>
+          <t>2046106592232214645</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -3161,7 +3128,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>{'name': 'Sultan Abdullah', 'screenName': 'SultanAbdu70381', 'followersCount': 25, 'favouritesCount': 1922, 'friendsCount': 28, 'description': 'هلا'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="K39" t="n">
@@ -3178,14 +3145,10 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>2045784123353034764</t>
-        </is>
-      </c>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
@@ -3193,71 +3156,65 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>https://x.com/bu_rashed98/status/2045729029614129456</t>
+          <t>https://x.com/emiratesislamic/status/2046106592232214645</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2045729029614129456</t>
+          <t>2046106592232214645</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2045093015459352679</t>
+          <t>2046215312949879234</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2045093015459352679</t>
+          <t>https://x.com/emiratesislamic/status/2046215312949879234</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>ندعم من يحمون الوطن
-مجموعة من مزايا الدعم المالي والخدمات المصرفية المخصصة للعاملين في الصفوف الأمامية
-•استرداد نقدي 10% بحد أقصى 400 درهم
-•سعر فائدة ثابت بنسبة 6% لجميع الموظفين الجدد الذي يقومون بتحويل رواتبهم
-•تمديد فترة تحويل الراتب
-•إعفاء من رسوم الحد الأدنى للرصيد للعملاء غير المحوّلة رواتبهم
-•إعفاءات على رسوم القروض مع أولوية معالجة الطلبات
-يسري العرض حتى 30 يونيو 2026.
-تُطبق الشروط والأحكام.
-https://t.co/I7DGlib9vt</t>
+          <t>Exclusively for Emaratis. Apply for an Emarati Credit Card &amp;amp; get a welcome bonus of up to 150,000 EI SmartMiles worth AED 1,500
+✅ No annual membership fee
+📈 Earn up to 3.75 EI SmartMiles back per AED spend
+🍔 50% discount on talabat https://t.co/pIT39d8ym8</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>1776423145000</v>
+        <v>1776690722000</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2045093015459352679</t>
+          <t>2046215312949879234</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGGhQnfXsAAHpYo.jpg', 'type': 'photo', 'id': '2045093012653453312'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGWd-66WYAAChSk.jpg', 'type': 'photo', 'id': '2046215310001201152'}]</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174302, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="L40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>264</v>
+        <v>0</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>639672</t>
+          <t>60</t>
         </is>
       </c>
       <c r="P40" t="inlineStr"/>
@@ -3268,35 +3225,37 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>https://x.com/bu_rashed98/status/2045729029614129456</t>
+          <t>https://x.com/emiratesislamic/status/2046106598221746656</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2045729029614129456</t>
+          <t>2046106598221746656</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2045729029614129456</t>
+          <t>2046106592114856006</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://x.com/bu_rashed98/status/2045729029614129456</t>
+          <t>https://x.com/emiratesislamic/status/2046106592114856006</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE أنا وياهم 😁</t>
+          <t>الاستثمار ليس معقداً، بل يحتاج إلى تخطيط ذكي.
+مع منصة الثروات الرقمية من الإمارات الإسلامي، يمكنك البدء بثقة عبر تجربة رقمية سلسة ومتوافقة مع الشريعة الإسلامية، صُممت لمساعدتك على:
+✔️ الوصول إلى مجموعة واسعة من خيارات الاستثمار المتوافقة مع الشريعة الإسلامية</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>1776574783000</v>
+        <v>1776664801000</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2045093015459352679</t>
+          <t>2046106592114856006</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3306,11 +3265,11 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>{'name': '﮼💛🇦🇪الامبراطور 🇦🇪💛', 'screenName': 'bu_rashed98', 'followersCount': 480, 'favouritesCount': 4057, 'friendsCount': 212, 'description': '🤍'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -3323,14 +3282,10 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>141</t>
-        </is>
-      </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>2045093015459352679</t>
-        </is>
-      </c>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
@@ -3338,74 +3293,74 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>https://x.com/girluae11/status/2045755517948272900</t>
+          <t>https://x.com/emiratesislamic/status/2046106598221746656</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2045755517948272900</t>
+          <t>2046106598221746656</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2045093015459352679</t>
+          <t>2046106595369615672</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2045093015459352679</t>
+          <t>https://x.com/emiratesislamic/status/2046106595369615672</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>ندعم من يحمون الوطن
-مجموعة من مزايا الدعم المالي والخدمات المصرفية المخصصة للعاملين في الصفوف الأمامية
-•استرداد نقدي 10% بحد أقصى 400 درهم
-•سعر فائدة ثابت بنسبة 6% لجميع الموظفين الجدد الذي يقومون بتحويل رواتبهم
-•تمديد فترة تحويل الراتب
-•إعفاء من رسوم الحد الأدنى للرصيد للعملاء غير المحوّلة رواتبهم
-•إعفاءات على رسوم القروض مع أولوية معالجة الطلبات
-يسري العرض حتى 30 يونيو 2026.
-تُطبق الشروط والأحكام.
-https://t.co/I7DGlib9vt</t>
+          <t>✔️ متابعة استثماراتك لحظة بلحظة
+✔️ الحصول على إرشادات ذكية لدعم قراراتك المالية
+✔️ الاستمتاع بتجربة رقمية متكاملة وسهلة
+ابدأ بمبلغ صغير، ضع أهدافاً بعيدة المدى، والتزم بالانضباط لتحقيق نتائج ملموسة.
+للمزيد من المعلومات، تفضل بزيارة الرابط التالي:
+https://t.co/PgcKVmrsKA</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>1776423145000</v>
+        <v>1776664801000</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2045093015459352679</t>
+          <t>2046106592114856006</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGGhQnfXsAAHpYo.jpg', 'type': 'photo', 'id': '2045093012653453312'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174302, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="K42" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="L42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>264</v>
+        <v>0</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>639672</t>
-        </is>
-      </c>
-      <c r="P42" t="inlineStr"/>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>2046106592114856006</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
@@ -3413,35 +3368,36 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>https://x.com/girluae11/status/2045755517948272900</t>
+          <t>https://x.com/emiratesislamic/status/2046106598221746656</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2045755517948272900</t>
+          <t>2046106598221746656</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2045755517948272900</t>
+          <t>2046106598221746656</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://x.com/girluae11/status/2045755517948272900</t>
+          <t>https://x.com/emiratesislamic/status/2046106598221746656</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE من هم حماه الوطن؟ الفئات ؟</t>
+          <t>Investing doesn’t have to be complicated. It just has to be well-planned. With Emirates Islamic Digital Wealth, start investing confidently through a seamless, Shariah-compliant digital experience designed to help you:
+✔️ Access a range of Shariah-compliant investment options</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>1776581098000</v>
+        <v>1776664802000</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2045093015459352679</t>
+          <t>2046106592114856006</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3451,11 +3407,11 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>{'name': 'girl', 'screenName': 'girluae11', 'followersCount': 134, 'favouritesCount': 1542, 'friendsCount': 195, 'description': '🇦🇪 متفائلين أنا وقلبي'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -3468,12 +3424,12 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>42</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>2045093015459352679</t>
+          <t>2046106595369615672</t>
         </is>
       </c>
     </row>
@@ -3483,36 +3439,40 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>https://x.com/firstdiver4ever/status/2045771180469272971</t>
+          <t>https://x.com/emiratesislamic/status/2046106598221746656</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2045771180469272971</t>
+          <t>2046106598221746656</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2045771180469272971</t>
+          <t>2046106600142725209</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://x.com/firstdiver4ever/status/2045771180469272971</t>
+          <t>https://x.com/emiratesislamic/status/2046106600142725209</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>@emiratesislamic أتقدم لجميع العاملين في مصرف الإمارات الإسلامي بجزيل الشكر والتقدير على جهودهم وعملهم الدؤوب الذي قاموا به ، حيث تم مشكلتي في زمن قياسي بالوقت الذي كان من المفروض ان يتم انجازه خلال سبعة ايام عمل .
-شكرا من القلب مرة اخرى .</t>
+          <t>✔️ Track your investments in real time
+✔️ Get smart insights to guide your decisions
+✔️ Enjoy a fully digital experience
+Start small. Think long-term. Stay disciplined.
+To know more, visit:
+https://t.co/BZed26iXDD</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>1776584832000</v>
+        <v>1776664802000</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2045771180469272971</t>
+          <t>2046106592114856006</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3522,7 +3482,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>{'name': 'اماراتى وافتخر', 'screenName': 'firstdiver4ever', 'followersCount': 933, 'favouritesCount': 4615, 'friendsCount': 1840, 'description': 'الله ثم الوطن ثم رئيس الدوله'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="K44" t="n">
@@ -3539,10 +3499,14 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="P44" t="inlineStr"/>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>2046106598221746656</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
@@ -3550,45 +3514,43 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2045744202382807549</t>
+          <t>https://x.com/emiratesislamic/status/2046215315273486655</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2045744202382807549</t>
+          <t>2046215315273486655</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2045744202382807549</t>
+          <t>2046215312949879234</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2045744202382807549</t>
+          <t>https://x.com/emiratesislamic/status/2046215312949879234</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Outstanding payments = constant stress.
-💡 Tip:
-Write everything down in one place
-Clarity makes it feel manageable.
-#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic
-https://t.co/XvyZgR87nM</t>
+          <t>Exclusively for Emaratis. Apply for an Emarati Credit Card &amp;amp; get a welcome bonus of up to 150,000 EI SmartMiles worth AED 1,500
+✅ No annual membership fee
+📈 Earn up to 3.75 EI SmartMiles back per AED spend
+🍔 50% discount on talabat https://t.co/pIT39d8ym8</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>1776578400000</v>
+        <v>1776690722000</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2045744202382807549</t>
+          <t>2046215312949879234</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGWd-66WYAAChSk.jpg', 'type': 'photo', 'id': '2046215310001201152'}]</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3597,7 +3559,7 @@
         </is>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
@@ -3610,7 +3572,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>60</t>
         </is>
       </c>
       <c r="P45" t="inlineStr"/>
@@ -3621,25 +3583,2891 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2045744202382807549</t>
+          <t>https://x.com/emiratesislamic/status/2046215315273486655</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2045744202382807549</t>
+          <t>2046215315273486655</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
+          <t>2046215315273486655</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046215315273486655</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>🚗 Complimentary valet parking
+✈️ Complimentary airport lounge access
+💳 Metal Card with unique design
+And much more!
+📅 Offer valid till 31 May 2026
+https://t.co/Rcpj14D3rn</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>1776690722000</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>2046215312949879234</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>2046215312949879234</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="n">
+        <v>45</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046215063929749703</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2046215063929749703</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2046215061186683019</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046215061186683019</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>حصرياً للإماراتيين. تقدم بطلب بطاقة إماراتي الائتمانية واحصل على مكافأة ترحيبية تصل الى 150,000 ميل من أميال سمارت مايلز بقيمة 1,500 درهم
+✅ بدون رسوم عضوية سنوية
+📈استرداد لغاية 3.75 ميل من أميال سمارت مايلز مقابل كل درهم إماراتي تنفقه
+🍔 خصم لغاية %50 على طلبات https://t.co/X996FmddPk</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>1776690662000</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>2046215061186683019</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGWdwRrWMAARNF5.jpg', 'type': 'photo', 'id': '2046215058414252032'}]</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="K47" t="n">
+        <v>1</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="n">
+        <v>46</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046215063929749703</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2046215063929749703</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2046215063929749703</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046215063929749703</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>🚗 خدمة صف السيارات
+🛫 الدخول إلى صالات المطارات
+💳 بطاقة معدنية بتصميم فريد
+وغير ذلك الكثير
+📅 يسري العرض لغاية 31 مايو 2026
+https://t.co/WJhVBxsiSW</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>1776690662000</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>2046215061186683019</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>2046215061186683019</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="n">
+        <v>47</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046215312949879234</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>2046215312949879234</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2046215312949879234</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046215312949879234</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Exclusively for Emaratis. Apply for an Emarati Credit Card &amp;amp; get a welcome bonus of up to 150,000 EI SmartMiles worth AED 1,500
+✅ No annual membership fee
+📈 Earn up to 3.75 EI SmartMiles back per AED spend
+🍔 50% discount on talabat https://t.co/pIT39d8ym8</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>1776690722000</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>2046215312949879234</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGWd-66WYAAChSk.jpg', 'type': 'photo', 'id': '2046215310001201152'}]</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="K49" t="n">
+        <v>2</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="n">
+        <v>48</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046215312949879234</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>2046215312949879234</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2046215315273486655</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046215315273486655</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>🚗 Complimentary valet parking
+✈️ Complimentary airport lounge access
+💳 Metal Card with unique design
+And much more!
+📅 Offer valid till 31 May 2026
+https://t.co/Rcpj14D3rn</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>1776690722000</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>2046215312949879234</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="K50" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>2046215312949879234</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="n">
+        <v>49</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046215312949879234</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2046215312949879234</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2046215061186683019</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046215061186683019</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>حصرياً للإماراتيين. تقدم بطلب بطاقة إماراتي الائتمانية واحصل على مكافأة ترحيبية تصل الى 150,000 ميل من أميال سمارت مايلز بقيمة 1,500 درهم
+✅ بدون رسوم عضوية سنوية
+📈استرداد لغاية 3.75 ميل من أميال سمارت مايلز مقابل كل درهم إماراتي تنفقه
+🍔 خصم لغاية %50 على طلبات https://t.co/X996FmddPk</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>1776690662000</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>2046215061186683019</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGWdwRrWMAARNF5.jpg', 'type': 'photo', 'id': '2046215058414252032'}]</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="K51" t="n">
+        <v>1</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046200685037830312</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>2046200685037830312</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2044702429464441285</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>https://x.com/alsajwani1/status/2044702429464441285</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>@emiratesislamic 
+السلام عليكم
+زرت فرع 06 مول يوم الثلاثاء الماضى من اجل كسر الوديعة ودفع مبلغ القرض المتبقي علي
+أخبرتني الموظفة المحترمة بانه سوف يتم إرسال أميل الى الإدارة  لمعرفة الخطوات
+والى اليوم الخميس الإدارة لم ترد عليهم 
+هل هذ التأخير له مبرر
+او عدم هو اهتمام بالعملاء</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>1776330022000</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>2044702429464441285</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>{'name': 'عبدالصاحب السجواني', 'screenName': 'alsajwani1', 'followersCount': 622, 'favouritesCount': 55, 'friendsCount': 2015, 'description': '\u200fمدرب ومستشار ريادة الأعمال  trainer and adviser Entrepreneurs'}</t>
+        </is>
+      </c>
+      <c r="K52" t="n">
+        <v>1</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="n">
+        <v>51</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046200685037830312</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2046200685037830312</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2044734739718824109</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2044734739718824109</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>@alsajwani1 مرحبا ، يأسفنا سماع تجربتك! فريقنا ملتزم بمعالجة هذا الأمر على الفور. لحماية خصوصيتك ، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل. رضاك أولويتنا.</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>1776337725000</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>2044702429464441285</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="K53" t="n">
+        <v>1</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>2044702429464441285</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="n">
+        <v>52</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046200685037830312</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2046200685037830312</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2045014720416186802</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>https://x.com/alsajwani1/status/2045014720416186802</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>@emiratesislamic تم امس التواصل معي من عندكم
+سألني عن تاريخ الميلاد
+أعطيته 
+ثم سألني عن رقم الجواز
+قلت له لا احفظه ونا حاليا أسوق السيارة
+قال لي سوف اتصل لاحقاً
+قلت له الان انت متصل عشان معرفة المشكلة ولا داعي لهذه الاسئلة لأنني لن أطب اي خدمة؟
+قال هذا هو النظام
+أخبرته بالمشكلة
+في انتظار الحل!!!</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>1776404478000</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>2044702429464441285</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>{'name': 'عبدالصاحب السجواني', 'screenName': 'alsajwani1', 'followersCount': 622, 'favouritesCount': 55, 'friendsCount': 2015, 'description': '\u200fمدرب ومستشار ريادة الأعمال  trainer and adviser Entrepreneurs'}</t>
+        </is>
+      </c>
+      <c r="K54" t="n">
+        <v>1</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>2044734739718824109</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="n">
+        <v>53</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046200685037830312</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2046200685037830312</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2045035981535912006</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2045035981535912006</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>@alsajwani1 مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
+رسالتك الخاصه.</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>1776409547000</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>2044702429464441285</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="K55" t="n">
+        <v>1</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>2045014720416186802</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="n">
+        <v>54</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046200685037830312</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2046200685037830312</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2045418169452695808</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>https://x.com/alsajwani1/status/2045418169452695808</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>@emiratesislamic ولكن إلى اليوم لم يتم إنهاء الإجراء 
+مع الأسف لايوجد متابعة لطلب من الفرع
+ولايوجد اهتمام من الإدارة في مساعدة الفروع لخدمة العملاء
+اكرر سوالي هل من المعقول عدم معرفة الإجراء لدي الفرع؟
+ وهل الإدارة لاتبالي في الرد على الفروع عند الاستفسار لخدمة العملاء؟
+متى ستنتهي المأساة؟ https://t.co/rFW4GdBPlY</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>1776500668000</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>2044702429464441285</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGLI-x3aUAA7Qsp.jpg', 'type': 'photo', 'id': '2045418161642819584'}]</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>{'name': 'عبدالصاحب السجواني', 'screenName': 'alsajwani1', 'followersCount': 622, 'favouritesCount': 55, 'friendsCount': 2015, 'description': '\u200fمدرب ومستشار ريادة الأعمال  trainer and adviser Entrepreneurs'}</t>
+        </is>
+      </c>
+      <c r="K56" t="n">
+        <v>1</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>2045035981535912006</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046200685037830312</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2046200685037830312</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2046133214998114511</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046133214998114511</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>@alsajwani1 مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
+رسالتك الخاصه.</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>1776671148000</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>2044702429464441285</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="K57" t="n">
+        <v>2</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>2045418169452695808</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="n">
+        <v>56</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046200685037830312</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2046200685037830312</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2046181231432495104</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>https://x.com/alsajwani1/status/2046181231432495104</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>@emiratesislamic ردكم لم يحرك ساكن 
+ إنجاز المعاملة إلى اليوم صفر</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>1776682596000</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>2044702429464441285</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>{'name': 'عبدالصاحب السجواني', 'screenName': 'alsajwani1', 'followersCount': 622, 'favouritesCount': 55, 'friendsCount': 2015, 'description': '\u200fمدرب ومستشار ريادة الأعمال  trainer and adviser Entrepreneurs'}</t>
+        </is>
+      </c>
+      <c r="K58" t="n">
+        <v>1</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>2046133214998114511</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="n">
+        <v>57</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046200685037830312</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>2046200685037830312</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2046200685037830312</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046200685037830312</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>@alsajwani1 مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
+رسالتك الخاصه.</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>1776687234000</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>2044702429464441285</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="K59" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>2046181231432495104</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="n">
+        <v>58</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046215061186683019</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2046215061186683019</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2046215061186683019</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046215061186683019</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>حصرياً للإماراتيين. تقدم بطلب بطاقة إماراتي الائتمانية واحصل على مكافأة ترحيبية تصل الى 150,000 ميل من أميال سمارت مايلز بقيمة 1,500 درهم
+✅ بدون رسوم عضوية سنوية
+📈استرداد لغاية 3.75 ميل من أميال سمارت مايلز مقابل كل درهم إماراتي تنفقه
+🍔 خصم لغاية %50 على طلبات https://t.co/X996FmddPk</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
+        <v>1776690662000</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>2046215061186683019</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGWdwRrWMAARNF5.jpg', 'type': 'photo', 'id': '2046215058414252032'}]</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="K60" t="n">
+        <v>1</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046215061186683019</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2046215061186683019</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2046215063929749703</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046215063929749703</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>🚗 خدمة صف السيارات
+🛫 الدخول إلى صالات المطارات
+💳 بطاقة معدنية بتصميم فريد
+وغير ذلك الكثير
+📅 يسري العرض لغاية 31 مايو 2026
+https://t.co/WJhVBxsiSW</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
+        <v>1776690662000</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>2046215061186683019</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="K61" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" t="n">
+        <v>0</v>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>2046215061186683019</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046215061186683019</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>2046215061186683019</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2046215312949879234</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046215312949879234</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Exclusively for Emaratis. Apply for an Emarati Credit Card &amp;amp; get a welcome bonus of up to 150,000 EI SmartMiles worth AED 1,500
+✅ No annual membership fee
+📈 Earn up to 3.75 EI SmartMiles back per AED spend
+🍔 50% discount on talabat https://t.co/pIT39d8ym8</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
+        <v>1776690722000</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>2046215312949879234</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGWd-66WYAAChSk.jpg', 'type': 'photo', 'id': '2046215310001201152'}]</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="K62" t="n">
+        <v>2</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="n">
+        <v>61</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046200603928338537</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>2046200603928338537</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2046139112361717905</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>https://x.com/alsajwani1/status/2046139112361717905</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>@emiratesislamic 
+منذ أسبوع قدمت على طلب كسر الوديعة وتسديد قيمة القرض  من الوديعة فرعكم في 06 مول في الشارقة ومن أسبوع وموظفين الفرع لا علم لهم بالإجراء ويتواصلون عبر الإميل مع الإدارة لمعرفة الخطوات والإدارة لاحياة لمن تنادي
+هل تتوقعون من هذه الخدمة تدخلون في حلبة المنافسة</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>1776672554000</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>2046139112361717905</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>{'name': 'عبدالصاحب السجواني', 'screenName': 'alsajwani1', 'followersCount': 622, 'favouritesCount': 55, 'friendsCount': 2015, 'description': '\u200fمدرب ومستشار ريادة الأعمال  trainer and adviser Entrepreneurs'}</t>
+        </is>
+      </c>
+      <c r="K63" t="n">
+        <v>1</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="n">
+        <v>62</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046200603928338537</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>2046200603928338537</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2046200603928338537</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046200603928338537</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>@alsajwani1 مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
+رسالتك الخاصه.</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
+        <v>1776687215000</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>2046139112361717905</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="K64" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" t="n">
+        <v>0</v>
+      </c>
+      <c r="N64" t="n">
+        <v>0</v>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>2046139112361717905</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="n">
+        <v>63</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046164985571598514</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>2046164985571598514</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2045771180469272971</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>https://x.com/firstdiver4ever/status/2045771180469272971</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>@emiratesislamic أتقدم لجميع العاملين في مصرف الإمارات الإسلامي بجزيل الشكر والتقدير على جهودهم وعملهم الدؤوب الذي قاموا به ، حيث تم مشكلتي في زمن قياسي بالوقت الذي كان من المفروض ان يتم انجازه خلال سبعة ايام عمل .
+شكرا من القلب مرة اخرى .</t>
+        </is>
+      </c>
+      <c r="G65" t="n">
+        <v>1776584832000</v>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>2045771180469272971</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>{'name': 'اماراتى وافتخر', 'screenName': 'firstdiver4ever', 'followersCount': 934, 'favouritesCount': 4614, 'friendsCount': 1841, 'description': 'الله ثم الوطن ثم رئيس الدوله'}</t>
+        </is>
+      </c>
+      <c r="K65" t="n">
+        <v>1</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" t="n">
+        <v>0</v>
+      </c>
+      <c r="N65" t="n">
+        <v>0</v>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="n">
+        <v>64</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046164985571598514</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>2046164985571598514</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2046164985571598514</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046164985571598514</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>@firstdiver4ever عزيزنا المتعامل، يسرنا أن نعرب لك عن جزيل شكرنا لهذه الكلمات الطيبة. كما أننا نقدر الوقت والجهد الذي بذلته لارسال هذا التقدير.</t>
+        </is>
+      </c>
+      <c r="G66" t="n">
+        <v>1776678723000</v>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>2045771180469272971</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="K66" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N66" t="n">
+        <v>0</v>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>2045771180469272971</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="n">
+        <v>65</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046200645498130445</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>2046200645498130445</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2044702429464441285</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>https://x.com/alsajwani1/status/2044702429464441285</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>@emiratesislamic 
+السلام عليكم
+زرت فرع 06 مول يوم الثلاثاء الماضى من اجل كسر الوديعة ودفع مبلغ القرض المتبقي علي
+أخبرتني الموظفة المحترمة بانه سوف يتم إرسال أميل الى الإدارة  لمعرفة الخطوات
+والى اليوم الخميس الإدارة لم ترد عليهم 
+هل هذ التأخير له مبرر
+او عدم هو اهتمام بالعملاء</t>
+        </is>
+      </c>
+      <c r="G67" t="n">
+        <v>1776330022000</v>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>2044702429464441285</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>{'name': 'عبدالصاحب السجواني', 'screenName': 'alsajwani1', 'followersCount': 622, 'favouritesCount': 55, 'friendsCount': 2015, 'description': '\u200fمدرب ومستشار ريادة الأعمال  trainer and adviser Entrepreneurs'}</t>
+        </is>
+      </c>
+      <c r="K67" t="n">
+        <v>1</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0</v>
+      </c>
+      <c r="M67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N67" t="n">
+        <v>0</v>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="n">
+        <v>66</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046200645498130445</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>2046200645498130445</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2044734739718824109</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2044734739718824109</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>@alsajwani1 مرحبا ، يأسفنا سماع تجربتك! فريقنا ملتزم بمعالجة هذا الأمر على الفور. لحماية خصوصيتك ، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل. رضاك أولويتنا.</t>
+        </is>
+      </c>
+      <c r="G68" t="n">
+        <v>1776337725000</v>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>2044702429464441285</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="K68" t="n">
+        <v>1</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" t="n">
+        <v>0</v>
+      </c>
+      <c r="N68" t="n">
+        <v>0</v>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>2044702429464441285</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="n">
+        <v>67</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046200645498130445</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>2046200645498130445</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2045014720416186802</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>https://x.com/alsajwani1/status/2045014720416186802</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>@emiratesislamic تم امس التواصل معي من عندكم
+سألني عن تاريخ الميلاد
+أعطيته 
+ثم سألني عن رقم الجواز
+قلت له لا احفظه ونا حاليا أسوق السيارة
+قال لي سوف اتصل لاحقاً
+قلت له الان انت متصل عشان معرفة المشكلة ولا داعي لهذه الاسئلة لأنني لن أطب اي خدمة؟
+قال هذا هو النظام
+أخبرته بالمشكلة
+في انتظار الحل!!!</t>
+        </is>
+      </c>
+      <c r="G69" t="n">
+        <v>1776404478000</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>2044702429464441285</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>{'name': 'عبدالصاحب السجواني', 'screenName': 'alsajwani1', 'followersCount': 622, 'favouritesCount': 55, 'friendsCount': 2015, 'description': '\u200fمدرب ومستشار ريادة الأعمال  trainer and adviser Entrepreneurs'}</t>
+        </is>
+      </c>
+      <c r="K69" t="n">
+        <v>1</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N69" t="n">
+        <v>0</v>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>2044734739718824109</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="n">
+        <v>68</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046200645498130445</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>2046200645498130445</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2045035981535912006</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2045035981535912006</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>@alsajwani1 مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
+رسالتك الخاصه.</t>
+        </is>
+      </c>
+      <c r="G70" t="n">
+        <v>1776409547000</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>2044702429464441285</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="K70" t="n">
+        <v>1</v>
+      </c>
+      <c r="L70" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" t="n">
+        <v>0</v>
+      </c>
+      <c r="N70" t="n">
+        <v>0</v>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>2045014720416186802</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="n">
+        <v>69</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046200645498130445</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>2046200645498130445</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2045418169452695808</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>https://x.com/alsajwani1/status/2045418169452695808</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>@emiratesislamic ولكن إلى اليوم لم يتم إنهاء الإجراء 
+مع الأسف لايوجد متابعة لطلب من الفرع
+ولايوجد اهتمام من الإدارة في مساعدة الفروع لخدمة العملاء
+اكرر سوالي هل من المعقول عدم معرفة الإجراء لدي الفرع؟
+ وهل الإدارة لاتبالي في الرد على الفروع عند الاستفسار لخدمة العملاء؟
+متى ستنتهي المأساة؟ https://t.co/rFW4GdBPlY</t>
+        </is>
+      </c>
+      <c r="G71" t="n">
+        <v>1776500668000</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>2044702429464441285</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGLI-x3aUAA7Qsp.jpg', 'type': 'photo', 'id': '2045418161642819584'}]</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>{'name': 'عبدالصاحب السجواني', 'screenName': 'alsajwani1', 'followersCount': 622, 'favouritesCount': 55, 'friendsCount': 2015, 'description': '\u200fمدرب ومستشار ريادة الأعمال  trainer and adviser Entrepreneurs'}</t>
+        </is>
+      </c>
+      <c r="K71" t="n">
+        <v>1</v>
+      </c>
+      <c r="L71" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" t="n">
+        <v>0</v>
+      </c>
+      <c r="N71" t="n">
+        <v>0</v>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>2045035981535912006</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="n">
+        <v>70</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046200645498130445</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>2046200645498130445</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2046133214998114511</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046133214998114511</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>@alsajwani1 مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
+رسالتك الخاصه.</t>
+        </is>
+      </c>
+      <c r="G72" t="n">
+        <v>1776671148000</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>2044702429464441285</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="K72" t="n">
+        <v>2</v>
+      </c>
+      <c r="L72" t="n">
+        <v>0</v>
+      </c>
+      <c r="M72" t="n">
+        <v>0</v>
+      </c>
+      <c r="N72" t="n">
+        <v>0</v>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>2045418169452695808</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="n">
+        <v>71</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046200645498130445</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>2046200645498130445</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>2046154630548402178</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>https://x.com/alsajwani1/status/2046154630548402178</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>@emiratesislamic أنا اريد إنهاء الإجراء ولا اريد رد كلمات</t>
+        </is>
+      </c>
+      <c r="G73" t="n">
+        <v>1776676254000</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>2044702429464441285</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>{'name': 'عبدالصاحب السجواني', 'screenName': 'alsajwani1', 'followersCount': 622, 'favouritesCount': 55, 'friendsCount': 2015, 'description': '\u200fمدرب ومستشار ريادة الأعمال  trainer and adviser Entrepreneurs'}</t>
+        </is>
+      </c>
+      <c r="K73" t="n">
+        <v>1</v>
+      </c>
+      <c r="L73" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" t="n">
+        <v>0</v>
+      </c>
+      <c r="N73" t="n">
+        <v>0</v>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>2046133214998114511</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="n">
+        <v>72</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046200645498130445</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>2046200645498130445</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>2046200645498130445</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046200645498130445</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>@alsajwani1 مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
+رسالتك الخاصه.</t>
+        </is>
+      </c>
+      <c r="G74" t="n">
+        <v>1776687225000</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>2044702429464441285</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="K74" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" t="n">
+        <v>0</v>
+      </c>
+      <c r="M74" t="n">
+        <v>0</v>
+      </c>
+      <c r="N74" t="n">
+        <v>0</v>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>2046154630548402178</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="n">
+        <v>73</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046148156560121974</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>2046148156560121974</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>2046148156560121974</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046148156560121974</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>امنح أبنائك انطلاقة مبكرة نحو الوعي المالي الذكي
+ #الإمارات_الإسلامي https://t.co/xdFKEhpKDT</t>
+        </is>
+      </c>
+      <c r="G75" t="n">
+        <v>1776674710000</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>2046148156560121974</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/ext_tw_video_thumb/2046148122250809344/pu/img/WEGHCsaWoyjDb-ot.jpg', 'type': 'video', 'id': '2046148122250809344'}]</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="K75" t="n">
+        <v>1</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0</v>
+      </c>
+      <c r="N75" t="n">
+        <v>0</v>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="n">
+        <v>74</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046148156560121974</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>2046148156560121974</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>2046148194392740002</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046148194392740002</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Your child's smart money journey starts here. Empower your kids to take their first steps toward financial independence. 
+#EmiratesIslamic #AlphaYouth https://t.co/udWgfz8rNb</t>
+        </is>
+      </c>
+      <c r="G76" t="n">
+        <v>1776674719000</v>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>2046148156560121974</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/ext_tw_video_thumb/2046148161090068480/pu/img/GpPJv5a4DR5wZAQc.jpg', 'type': 'video', 'id': '2046148161090068480'}]</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="K76" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" t="n">
+        <v>0</v>
+      </c>
+      <c r="M76" t="n">
+        <v>0</v>
+      </c>
+      <c r="N76" t="n">
+        <v>0</v>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>2046148156560121974</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="n">
+        <v>75</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046148156560121974</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>2046148156560121974</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2046215312949879234</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046215312949879234</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Exclusively for Emaratis. Apply for an Emarati Credit Card &amp;amp; get a welcome bonus of up to 150,000 EI SmartMiles worth AED 1,500
+✅ No annual membership fee
+📈 Earn up to 3.75 EI SmartMiles back per AED spend
+🍔 50% discount on talabat https://t.co/pIT39d8ym8</t>
+        </is>
+      </c>
+      <c r="G77" t="n">
+        <v>1776690722000</v>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>2046215312949879234</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGWd-66WYAAChSk.jpg', 'type': 'photo', 'id': '2046215310001201152'}]</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="K77" t="n">
+        <v>2</v>
+      </c>
+      <c r="L77" t="n">
+        <v>0</v>
+      </c>
+      <c r="M77" t="n">
+        <v>0</v>
+      </c>
+      <c r="N77" t="n">
+        <v>0</v>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="n">
+        <v>76</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046133214998114511</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>2046133214998114511</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>2044702429464441285</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>https://x.com/alsajwani1/status/2044702429464441285</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>@emiratesislamic 
+السلام عليكم
+زرت فرع 06 مول يوم الثلاثاء الماضى من اجل كسر الوديعة ودفع مبلغ القرض المتبقي علي
+أخبرتني الموظفة المحترمة بانه سوف يتم إرسال أميل الى الإدارة  لمعرفة الخطوات
+والى اليوم الخميس الإدارة لم ترد عليهم 
+هل هذ التأخير له مبرر
+او عدم هو اهتمام بالعملاء</t>
+        </is>
+      </c>
+      <c r="G78" t="n">
+        <v>1776330022000</v>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>2044702429464441285</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>{'name': 'عبدالصاحب السجواني', 'screenName': 'alsajwani1', 'followersCount': 622, 'favouritesCount': 55, 'friendsCount': 2015, 'description': '\u200fمدرب ومستشار ريادة الأعمال  trainer and adviser Entrepreneurs'}</t>
+        </is>
+      </c>
+      <c r="K78" t="n">
+        <v>1</v>
+      </c>
+      <c r="L78" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" t="n">
+        <v>0</v>
+      </c>
+      <c r="N78" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="n">
+        <v>77</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046133214998114511</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>2046133214998114511</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2044734739718824109</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2044734739718824109</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>@alsajwani1 مرحبا ، يأسفنا سماع تجربتك! فريقنا ملتزم بمعالجة هذا الأمر على الفور. لحماية خصوصيتك ، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل. رضاك أولويتنا.</t>
+        </is>
+      </c>
+      <c r="G79" t="n">
+        <v>1776337725000</v>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>2044702429464441285</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="K79" t="n">
+        <v>1</v>
+      </c>
+      <c r="L79" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" t="n">
+        <v>0</v>
+      </c>
+      <c r="N79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>2044702429464441285</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="n">
+        <v>78</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046133214998114511</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>2046133214998114511</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2045014720416186802</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>https://x.com/alsajwani1/status/2045014720416186802</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>@emiratesislamic تم امس التواصل معي من عندكم
+سألني عن تاريخ الميلاد
+أعطيته 
+ثم سألني عن رقم الجواز
+قلت له لا احفظه ونا حاليا أسوق السيارة
+قال لي سوف اتصل لاحقاً
+قلت له الان انت متصل عشان معرفة المشكلة ولا داعي لهذه الاسئلة لأنني لن أطب اي خدمة؟
+قال هذا هو النظام
+أخبرته بالمشكلة
+في انتظار الحل!!!</t>
+        </is>
+      </c>
+      <c r="G80" t="n">
+        <v>1776404478000</v>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>2044702429464441285</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>{'name': 'عبدالصاحب السجواني', 'screenName': 'alsajwani1', 'followersCount': 622, 'favouritesCount': 55, 'friendsCount': 2015, 'description': '\u200fمدرب ومستشار ريادة الأعمال  trainer and adviser Entrepreneurs'}</t>
+        </is>
+      </c>
+      <c r="K80" t="n">
+        <v>1</v>
+      </c>
+      <c r="L80" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" t="n">
+        <v>0</v>
+      </c>
+      <c r="N80" t="n">
+        <v>0</v>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>2044734739718824109</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="n">
+        <v>79</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046133214998114511</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>2046133214998114511</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2045035981535912006</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2045035981535912006</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>@alsajwani1 مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
+رسالتك الخاصه.</t>
+        </is>
+      </c>
+      <c r="G81" t="n">
+        <v>1776409547000</v>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>2044702429464441285</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="K81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L81" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" t="n">
+        <v>0</v>
+      </c>
+      <c r="N81" t="n">
+        <v>0</v>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>2045014720416186802</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="n">
+        <v>80</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046133214998114511</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>2046133214998114511</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>2045418169452695808</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>https://x.com/alsajwani1/status/2045418169452695808</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>@emiratesislamic ولكن إلى اليوم لم يتم إنهاء الإجراء 
+مع الأسف لايوجد متابعة لطلب من الفرع
+ولايوجد اهتمام من الإدارة في مساعدة الفروع لخدمة العملاء
+اكرر سوالي هل من المعقول عدم معرفة الإجراء لدي الفرع؟
+ وهل الإدارة لاتبالي في الرد على الفروع عند الاستفسار لخدمة العملاء؟
+متى ستنتهي المأساة؟ https://t.co/rFW4GdBPlY</t>
+        </is>
+      </c>
+      <c r="G82" t="n">
+        <v>1776500668000</v>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>2044702429464441285</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGLI-x3aUAA7Qsp.jpg', 'type': 'photo', 'id': '2045418161642819584'}]</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>{'name': 'عبدالصاحب السجواني', 'screenName': 'alsajwani1', 'followersCount': 622, 'favouritesCount': 55, 'friendsCount': 2015, 'description': '\u200fمدرب ومستشار ريادة الأعمال  trainer and adviser Entrepreneurs'}</t>
+        </is>
+      </c>
+      <c r="K82" t="n">
+        <v>1</v>
+      </c>
+      <c r="L82" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" t="n">
+        <v>0</v>
+      </c>
+      <c r="N82" t="n">
+        <v>0</v>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>2045035981535912006</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="n">
+        <v>81</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046133214998114511</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>2046133214998114511</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>2046133214998114511</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046133214998114511</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>@alsajwani1 مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
+رسالتك الخاصه.</t>
+        </is>
+      </c>
+      <c r="G83" t="n">
+        <v>1776671148000</v>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>2044702429464441285</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="K83" t="n">
+        <v>2</v>
+      </c>
+      <c r="L83" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" t="n">
+        <v>0</v>
+      </c>
+      <c r="N83" t="n">
+        <v>0</v>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>2045418169452695808</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="n">
+        <v>82</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046133214998114511</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>2046133214998114511</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>2046181231432495104</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>https://x.com/alsajwani1/status/2046181231432495104</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>@emiratesislamic ردكم لم يحرك ساكن 
+ إنجاز المعاملة إلى اليوم صفر</t>
+        </is>
+      </c>
+      <c r="G84" t="n">
+        <v>1776682596000</v>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>2044702429464441285</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>{'name': 'عبدالصاحب السجواني', 'screenName': 'alsajwani1', 'followersCount': 622, 'favouritesCount': 55, 'friendsCount': 2015, 'description': '\u200fمدرب ومستشار ريادة الأعمال  trainer and adviser Entrepreneurs'}</t>
+        </is>
+      </c>
+      <c r="K84" t="n">
+        <v>1</v>
+      </c>
+      <c r="L84" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" t="n">
+        <v>0</v>
+      </c>
+      <c r="N84" t="n">
+        <v>0</v>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>2046133214998114511</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="n">
+        <v>83</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046133214998114511</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>2046133214998114511</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>2046154630548402178</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>https://x.com/alsajwani1/status/2046154630548402178</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>@emiratesislamic أنا اريد إنهاء الإجراء ولا اريد رد كلمات</t>
+        </is>
+      </c>
+      <c r="G85" t="n">
+        <v>1776676254000</v>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>2044702429464441285</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>{'name': 'عبدالصاحب السجواني', 'screenName': 'alsajwani1', 'followersCount': 622, 'favouritesCount': 55, 'friendsCount': 2015, 'description': '\u200fمدرب ومستشار ريادة الأعمال  trainer and adviser Entrepreneurs'}</t>
+        </is>
+      </c>
+      <c r="K85" t="n">
+        <v>1</v>
+      </c>
+      <c r="L85" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" t="n">
+        <v>0</v>
+      </c>
+      <c r="N85" t="n">
+        <v>0</v>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>2046133214998114511</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="n">
+        <v>84</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046125833811615920</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>2046125833811615920</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
           <t>2045083218303402442</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E86" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2045083218303402442</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F86" t="inlineStr">
         <is>
           <t>Get a chance to win a total of AED 1,000,000 in cash prizes.
 55 businesses will be winners. Will you be one of them?
@@ -3647,138 +6475,573 @@
 💸 Second cash prize: AED 100,000 each (2 winners) https://t.co/V52QeTxHT6</t>
         </is>
       </c>
-      <c r="G46" t="n">
+      <c r="G86" t="n">
         <v>1776420809000</v>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="H86" t="inlineStr">
         <is>
           <t>2045083218303402442</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="I86" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGGYWVTWUAEdJxW.jpg', 'type': 'photo', 'id': '2045083215245758465'}]</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="J86" t="inlineStr">
         <is>
           <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
-      <c r="K46" t="n">
+      <c r="K86" t="n">
         <v>2</v>
       </c>
-      <c r="L46" t="n">
-        <v>0</v>
-      </c>
-      <c r="M46" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" t="n">
+      <c r="L86" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" t="n">
+        <v>0</v>
+      </c>
+      <c r="N86" t="n">
         <v>1</v>
       </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>166</t>
-        </is>
-      </c>
-      <c r="P46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="1" t="n">
-        <v>45</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2045744202651226430</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>2045744202651226430</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>2045744202651226430</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2045744202651226430</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>المدفوعات المستحقة تعني ضغطاً مستمراً.
-💡نصيحة: دوّن كل مدفوعاتك في مكان واحد.
-الوضوح يجعل الأمر أسهل في الإدارة. 
-#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
-https://t.co/mgtIcQsyLZ</t>
-        </is>
-      </c>
-      <c r="G47" t="n">
-        <v>1776578400000</v>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>2045744202651226430</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="n">
+        <v>85</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046125833811615920</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>2046125833811615920</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>2045083221952532551</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2045083221952532551</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>💸 Monthly cash prizes: from AED 5,000 up to AED 25,000 (52 winners)
+Valid until 30 June 2026.
+Terms and conditions apply.
+https://t.co/FsXr2qXw7K</t>
+        </is>
+      </c>
+      <c r="G87" t="n">
+        <v>1776420810000</v>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>2045083218303402442</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
+      <c r="J87" t="inlineStr">
         <is>
           <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
-      <c r="K47" t="n">
-        <v>0</v>
-      </c>
-      <c r="L47" t="n">
-        <v>0</v>
-      </c>
-      <c r="M47" t="n">
-        <v>0</v>
-      </c>
-      <c r="N47" t="n">
-        <v>0</v>
-      </c>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="P47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="1" t="n">
-        <v>46</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2045744202651226430</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>2045744202651226430</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
+      <c r="K87" t="n">
+        <v>1</v>
+      </c>
+      <c r="L87" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" t="n">
+        <v>0</v>
+      </c>
+      <c r="N87" t="n">
+        <v>0</v>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
         <is>
           <t>2045083218303402442</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="n">
+        <v>86</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046125833811615920</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>2046125833811615920</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>2045521200613560345</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>https://x.com/gassann20203/status/2045521200613560345</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>@emiratesislamic It's fake prize from 15 year u have account with u never ever I trusted u and today after removing otp u start steel the money from account</t>
+        </is>
+      </c>
+      <c r="G88" t="n">
+        <v>1776525232000</v>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>2045083218303402442</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>{'name': 'gazan', 'screenName': 'gassann20203', 'followersCount': 36, 'favouritesCount': 17, 'friendsCount': 35, 'description': 'Bloch chain expert'}</t>
+        </is>
+      </c>
+      <c r="K88" t="n">
+        <v>1</v>
+      </c>
+      <c r="L88" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" t="n">
+        <v>0</v>
+      </c>
+      <c r="N88" t="n">
+        <v>0</v>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>2045083221952532551</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="n">
+        <v>87</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046125833811615920</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>2046125833811615920</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>2046125833811615920</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046125833811615920</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>@gassann20203 Dear customer, we will connect with you on private messaging to serve you better</t>
+        </is>
+      </c>
+      <c r="G89" t="n">
+        <v>1776669388000</v>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>2045083218303402442</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="K89" t="n">
+        <v>0</v>
+      </c>
+      <c r="L89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>2045521200613560345</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="n">
+        <v>88</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046125857643606493</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>2046125857643606493</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>2044321422282240384</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>https://x.com/ADIBTweets/status/2044321422282240384</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>قد تكون رسالة من “قريب”... لكنها احتيال. 
+أجب واربح 
+تلقيت رسالة من صديقك يطلب منك بشكل عاجل تحويل مبلغ مالي إلى حسابه، مدّعياً أن هناك حالة طارئة. ماذا يجب أن تفعل؟
+أ. تحوّل المبلغ فوراً لمساعدة صديقك
+ب. تتحقّق من الأمر عبر الاتصال بصديقك
+ج. تثق بالرسالة لأنها واردة من حساب صديقك
+للمشاركة:
+أجب بشكل صحيح في التعليقات 
+قم بعمل منشن لشخصين 
+تابع حسابنا على X
+سيتم الإعلان عن الفائز بتاريخ 5 مايو 2026
+يرجى زيارة  https://t.co/4RkTsyGuDX للاطلاع على الشروط والأحكام
+تقتصر المشاركة على مواطني دولة الإمارات العربية المتحدة أو المقيمين في الدولة الذين يحملون بطاقة هوية سارية المفعول.
+مسابقة_مصرف_أبوظبي_الإسلامي</t>
+        </is>
+      </c>
+      <c r="G90" t="n">
+        <v>1776239183000</v>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>2044321422282240384</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF7jf0ba0AAZFPu.jpg', 'type': 'photo', 'id': '2044321416661880832'}]</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>{'name': 'ADIB Tweets', 'screenName': 'ADIBTweets', 'followersCount': 137563, 'favouritesCount': 2888, 'friendsCount': 104, 'description': 'حياكم في الحساب الرسمي لمصرف أبوظبي الإسلامي، شركة مساهمة عامة. Welcome to Abu Dhabi Islamic Bank Public Joint Stock Company official account'}</t>
+        </is>
+      </c>
+      <c r="K90" t="n">
+        <v>393</v>
+      </c>
+      <c r="L90" t="n">
+        <v>0</v>
+      </c>
+      <c r="M90" t="n">
+        <v>69</v>
+      </c>
+      <c r="N90" t="n">
+        <v>206</v>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>1435558</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="n">
+        <v>89</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046125857643606493</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>2046125857643606493</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>2045175695169732901</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>https://x.com/mohmd_moh/status/2045175695169732901</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>لماذ البنك لايتحمل المسوؤلية إذا تم اختراق الحساب الشخصي وتم سحب مبلغ من المال بدون اي ادارة امن الحسابات او عن طريق ارسال OTP ويدعي انه تم التحويل بالفعل والبنك غير قادر علي فعل شيي و يجب ان يتحمل صاحب الحساب تكاليف اصدار بطاقة جديده و تحمل المبلغ المسحوب و كأن الحسابات الشخصية سبيل متاح لاي عملية إحتيال وعلي صاحب الحساب تحمل كامل المسؤلية والبنك الذي من المفترض هو المؤتمن علي هذا المال لايتحمل إي مسؤلية.. علي فكره انتم من البنوك التي لاتهتم بحمايه العميل لكن هناك بنوك مثل الامارات الإسلامي له كل الشكر والامتنان لانه حدث معي عمليه احتيال و خلال اسبوع تحمل البنك المبلغ وتم إيداعه في حسابي وتم اصدار بطاقة جديده بدون اي تكلفة.
+كل الشكر الي بنك الإمارات الإسلامي @emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G91" t="n">
+        <v>1776442857000</v>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>2044321422282240384</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>{'name': 'Mohamed Mohamed', 'screenName': 'mohmd_moh', 'followersCount': 195, 'favouritesCount': 6659, 'friendsCount': 1287, 'description': ''}</t>
+        </is>
+      </c>
+      <c r="K91" t="n">
+        <v>3</v>
+      </c>
+      <c r="L91" t="n">
+        <v>0</v>
+      </c>
+      <c r="M91" t="n">
+        <v>0</v>
+      </c>
+      <c r="N91" t="n">
+        <v>0</v>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>2044321422282240384</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="n">
+        <v>90</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046125857643606493</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>2046125857643606493</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>2046125857643606493</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046125857643606493</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>@mohmd_moh مرحبا ، يأسفنا سماع تجربتك! فريقنا ملتزم بمعالجة هذا الأمر على الفور. لحماية خصوصيتك ، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل. رضاك أولويتنا.</t>
+        </is>
+      </c>
+      <c r="G92" t="n">
+        <v>1776669394000</v>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>2044321422282240384</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="K92" t="n">
+        <v>1</v>
+      </c>
+      <c r="L92" t="n">
+        <v>0</v>
+      </c>
+      <c r="M92" t="n">
+        <v>0</v>
+      </c>
+      <c r="N92" t="n">
+        <v>0</v>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>2045175695169732901</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="n">
+        <v>91</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046125857643606493</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>2046125857643606493</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>2046224051438526663</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>https://x.com/mohmd_moh/status/2046224051438526663</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>الشكر الجزيل لكم .  ليس لدي اي مشكلة حاليا أنا فقط ذكرت ماحدث معي للإشادة بكم علي سرعة الحل المقدم من طرفكم وسرعة استجابتكم وتحملكم المسؤلية تجاه العملاء .
+تعامل راقي وليس هدفكم المكسب فقط ولكن هدفكم الاول هو ارضاء العميل وهذا ذكاء منكم لأنكم بهذا الأسلوب سوف تكسبوا ثقة العملاء وبالتالي زيادة العملاء ويأتي المكسب مضاعف لاحقا . 
+كلمة حق تقال ان نهج الإمارات الإسلامي يستحق ان يقتدي به جميع البنوك.</t>
+        </is>
+      </c>
+      <c r="G93" t="n">
+        <v>1776692805000</v>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>2044321422282240384</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>{'name': 'Mohamed Mohamed', 'screenName': 'mohmd_moh', 'followersCount': 195, 'favouritesCount': 6659, 'friendsCount': 1287, 'description': ''}</t>
+        </is>
+      </c>
+      <c r="K93" t="n">
+        <v>0</v>
+      </c>
+      <c r="L93" t="n">
+        <v>0</v>
+      </c>
+      <c r="M93" t="n">
+        <v>0</v>
+      </c>
+      <c r="N93" t="n">
+        <v>0</v>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>2046125857643606493</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="n">
+        <v>92</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046125792552222931</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>2046125792552222931</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>2045083218303402442</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2045083218303402442</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="F94" t="inlineStr">
         <is>
           <t>Get a chance to win a total of AED 1,000,000 in cash prizes.
 55 businesses will be winners. Will you be one of them?
@@ -3786,42 +7049,1035 @@
 💸 Second cash prize: AED 100,000 each (2 winners) https://t.co/V52QeTxHT6</t>
         </is>
       </c>
-      <c r="G48" t="n">
+      <c r="G94" t="n">
         <v>1776420809000</v>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="H94" t="inlineStr">
         <is>
           <t>2045083218303402442</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="I94" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGGYWVTWUAEdJxW.jpg', 'type': 'photo', 'id': '2045083215245758465'}]</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
+      <c r="J94" t="inlineStr">
         <is>
           <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
-      <c r="K48" t="n">
+      <c r="K94" t="n">
         <v>2</v>
       </c>
-      <c r="L48" t="n">
-        <v>0</v>
-      </c>
-      <c r="M48" t="n">
-        <v>0</v>
-      </c>
-      <c r="N48" t="n">
+      <c r="L94" t="n">
+        <v>0</v>
+      </c>
+      <c r="M94" t="n">
+        <v>0</v>
+      </c>
+      <c r="N94" t="n">
         <v>1</v>
       </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
-      <c r="P48" t="inlineStr"/>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="n">
+        <v>93</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046125792552222931</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>2046125792552222931</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>2045520833406464393</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>https://x.com/gassann20203/status/2045520833406464393</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>@emiratesislamic Before few days u stopped the otp which was protecting our account from any fake or steeling money then we star receiving  withdraw from our account without permission I think u stolen our money</t>
+        </is>
+      </c>
+      <c r="G95" t="n">
+        <v>1776525145000</v>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>2045083218303402442</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>{'name': 'gazan', 'screenName': 'gassann20203', 'followersCount': 36, 'favouritesCount': 17, 'friendsCount': 35, 'description': 'Bloch chain expert'}</t>
+        </is>
+      </c>
+      <c r="K95" t="n">
+        <v>1</v>
+      </c>
+      <c r="L95" t="n">
+        <v>0</v>
+      </c>
+      <c r="M95" t="n">
+        <v>0</v>
+      </c>
+      <c r="N95" t="n">
+        <v>0</v>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>2045083218303402442</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="n">
+        <v>94</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046125792552222931</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>2046125792552222931</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>2046125792552222931</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046125792552222931</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>@gassann20203 Dear customer, we will connect with you on private messaging to serve you better</t>
+        </is>
+      </c>
+      <c r="G96" t="n">
+        <v>1776669378000</v>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>2045083218303402442</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="K96" t="n">
+        <v>0</v>
+      </c>
+      <c r="L96" t="n">
+        <v>0</v>
+      </c>
+      <c r="M96" t="n">
+        <v>0</v>
+      </c>
+      <c r="N96" t="n">
+        <v>0</v>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>2045520833406464393</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046106595369615672</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>2046106595369615672</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>2046106592114856006</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046106592114856006</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>الاستثمار ليس معقداً، بل يحتاج إلى تخطيط ذكي.
+مع منصة الثروات الرقمية من الإمارات الإسلامي، يمكنك البدء بثقة عبر تجربة رقمية سلسة ومتوافقة مع الشريعة الإسلامية، صُممت لمساعدتك على:
+✔️ الوصول إلى مجموعة واسعة من خيارات الاستثمار المتوافقة مع الشريعة الإسلامية</t>
+        </is>
+      </c>
+      <c r="G97" t="n">
+        <v>1776664801000</v>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>2046106592114856006</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="K97" t="n">
+        <v>1</v>
+      </c>
+      <c r="L97" t="n">
+        <v>0</v>
+      </c>
+      <c r="M97" t="n">
+        <v>0</v>
+      </c>
+      <c r="N97" t="n">
+        <v>0</v>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="n">
+        <v>96</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046106595369615672</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>2046106595369615672</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>2046106595369615672</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046106595369615672</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>✔️ متابعة استثماراتك لحظة بلحظة
+✔️ الحصول على إرشادات ذكية لدعم قراراتك المالية
+✔️ الاستمتاع بتجربة رقمية متكاملة وسهلة
+ابدأ بمبلغ صغير، ضع أهدافاً بعيدة المدى، والتزم بالانضباط لتحقيق نتائج ملموسة.
+للمزيد من المعلومات، تفضل بزيارة الرابط التالي:
+https://t.co/PgcKVmrsKA</t>
+        </is>
+      </c>
+      <c r="G98" t="n">
+        <v>1776664801000</v>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>2046106592114856006</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="K98" t="n">
+        <v>1</v>
+      </c>
+      <c r="L98" t="n">
+        <v>0</v>
+      </c>
+      <c r="M98" t="n">
+        <v>0</v>
+      </c>
+      <c r="N98" t="n">
+        <v>0</v>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>2046106592114856006</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="n">
+        <v>97</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046106595369615672</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>2046106595369615672</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>2046106598221746656</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046106598221746656</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Investing doesn’t have to be complicated. It just has to be well-planned. With Emirates Islamic Digital Wealth, start investing confidently through a seamless, Shariah-compliant digital experience designed to help you:
+✔️ Access a range of Shariah-compliant investment options</t>
+        </is>
+      </c>
+      <c r="G99" t="n">
+        <v>1776664802000</v>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>2046106592114856006</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="K99" t="n">
+        <v>1</v>
+      </c>
+      <c r="L99" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" t="n">
+        <v>0</v>
+      </c>
+      <c r="N99" t="n">
+        <v>0</v>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>2046106595369615672</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046106600142725209</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>2046106600142725209</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>2046106592114856006</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046106592114856006</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>الاستثمار ليس معقداً، بل يحتاج إلى تخطيط ذكي.
+مع منصة الثروات الرقمية من الإمارات الإسلامي، يمكنك البدء بثقة عبر تجربة رقمية سلسة ومتوافقة مع الشريعة الإسلامية، صُممت لمساعدتك على:
+✔️ الوصول إلى مجموعة واسعة من خيارات الاستثمار المتوافقة مع الشريعة الإسلامية</t>
+        </is>
+      </c>
+      <c r="G100" t="n">
+        <v>1776664801000</v>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>2046106592114856006</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="K100" t="n">
+        <v>1</v>
+      </c>
+      <c r="L100" t="n">
+        <v>0</v>
+      </c>
+      <c r="M100" t="n">
+        <v>0</v>
+      </c>
+      <c r="N100" t="n">
+        <v>0</v>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="n">
+        <v>99</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046106600142725209</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>2046106600142725209</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>2046106595369615672</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046106595369615672</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>✔️ متابعة استثماراتك لحظة بلحظة
+✔️ الحصول على إرشادات ذكية لدعم قراراتك المالية
+✔️ الاستمتاع بتجربة رقمية متكاملة وسهلة
+ابدأ بمبلغ صغير، ضع أهدافاً بعيدة المدى، والتزم بالانضباط لتحقيق نتائج ملموسة.
+للمزيد من المعلومات، تفضل بزيارة الرابط التالي:
+https://t.co/PgcKVmrsKA</t>
+        </is>
+      </c>
+      <c r="G101" t="n">
+        <v>1776664801000</v>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>2046106592114856006</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="K101" t="n">
+        <v>1</v>
+      </c>
+      <c r="L101" t="n">
+        <v>0</v>
+      </c>
+      <c r="M101" t="n">
+        <v>0</v>
+      </c>
+      <c r="N101" t="n">
+        <v>0</v>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>2046106592114856006</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046106600142725209</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>2046106600142725209</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>2046106598221746656</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046106598221746656</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Investing doesn’t have to be complicated. It just has to be well-planned. With Emirates Islamic Digital Wealth, start investing confidently through a seamless, Shariah-compliant digital experience designed to help you:
+✔️ Access a range of Shariah-compliant investment options</t>
+        </is>
+      </c>
+      <c r="G102" t="n">
+        <v>1776664802000</v>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>2046106592114856006</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="K102" t="n">
+        <v>1</v>
+      </c>
+      <c r="L102" t="n">
+        <v>0</v>
+      </c>
+      <c r="M102" t="n">
+        <v>0</v>
+      </c>
+      <c r="N102" t="n">
+        <v>0</v>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>2046106595369615672</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="n">
+        <v>101</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046106600142725209</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>2046106600142725209</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>2046106600142725209</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046106600142725209</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>✔️ Track your investments in real time
+✔️ Get smart insights to guide your decisions
+✔️ Enjoy a fully digital experience
+Start small. Think long-term. Stay disciplined.
+To know more, visit:
+https://t.co/BZed26iXDD</t>
+        </is>
+      </c>
+      <c r="G103" t="n">
+        <v>1776664802000</v>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>2046106592114856006</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="K103" t="n">
+        <v>0</v>
+      </c>
+      <c r="L103" t="n">
+        <v>0</v>
+      </c>
+      <c r="M103" t="n">
+        <v>0</v>
+      </c>
+      <c r="N103" t="n">
+        <v>0</v>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>2046106598221746656</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="n">
+        <v>102</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046106592135831614</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>2046106592135831614</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>2046106592135831614</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046106592135831614</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>شركات التوصيل الموثوقة لا تطلب دفعات إضافية عبر روابط غير آمنة.
+لا تقع في الفخ. احذر الاحتيال.
+#متحّدون_ضد_الاحتيال مع الإمارات الإسلامي.
+https://t.co/ltnxcRlBOA</t>
+        </is>
+      </c>
+      <c r="G104" t="n">
+        <v>1776664801000</v>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>2046106592135831614</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="K104" t="n">
+        <v>0</v>
+      </c>
+      <c r="L104" t="n">
+        <v>0</v>
+      </c>
+      <c r="M104" t="n">
+        <v>0</v>
+      </c>
+      <c r="N104" t="n">
+        <v>0</v>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="n">
+        <v>103</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046106592135831614</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>2046106592135831614</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>2046215312949879234</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046215312949879234</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Exclusively for Emaratis. Apply for an Emarati Credit Card &amp;amp; get a welcome bonus of up to 150,000 EI SmartMiles worth AED 1,500
+✅ No annual membership fee
+📈 Earn up to 3.75 EI SmartMiles back per AED spend
+🍔 50% discount on talabat https://t.co/pIT39d8ym8</t>
+        </is>
+      </c>
+      <c r="G105" t="n">
+        <v>1776690722000</v>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>2046215312949879234</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGWd-66WYAAChSk.jpg', 'type': 'photo', 'id': '2046215310001201152'}]</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="K105" t="n">
+        <v>2</v>
+      </c>
+      <c r="L105" t="n">
+        <v>0</v>
+      </c>
+      <c r="M105" t="n">
+        <v>0</v>
+      </c>
+      <c r="N105" t="n">
+        <v>0</v>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="n">
+        <v>104</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046106592114856006</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>2046106592114856006</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>2046106592114856006</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046106592114856006</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>الاستثمار ليس معقداً، بل يحتاج إلى تخطيط ذكي.
+مع منصة الثروات الرقمية من الإمارات الإسلامي، يمكنك البدء بثقة عبر تجربة رقمية سلسة ومتوافقة مع الشريعة الإسلامية، صُممت لمساعدتك على:
+✔️ الوصول إلى مجموعة واسعة من خيارات الاستثمار المتوافقة مع الشريعة الإسلامية</t>
+        </is>
+      </c>
+      <c r="G106" t="n">
+        <v>1776664801000</v>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>2046106592114856006</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="K106" t="n">
+        <v>1</v>
+      </c>
+      <c r="L106" t="n">
+        <v>0</v>
+      </c>
+      <c r="M106" t="n">
+        <v>0</v>
+      </c>
+      <c r="N106" t="n">
+        <v>0</v>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="P106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="n">
+        <v>105</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046106592114856006</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>2046106592114856006</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>2046106595369615672</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046106595369615672</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>✔️ متابعة استثماراتك لحظة بلحظة
+✔️ الحصول على إرشادات ذكية لدعم قراراتك المالية
+✔️ الاستمتاع بتجربة رقمية متكاملة وسهلة
+ابدأ بمبلغ صغير، ضع أهدافاً بعيدة المدى، والتزم بالانضباط لتحقيق نتائج ملموسة.
+للمزيد من المعلومات، تفضل بزيارة الرابط التالي:
+https://t.co/PgcKVmrsKA</t>
+        </is>
+      </c>
+      <c r="G107" t="n">
+        <v>1776664801000</v>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>2046106592114856006</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="K107" t="n">
+        <v>1</v>
+      </c>
+      <c r="L107" t="n">
+        <v>0</v>
+      </c>
+      <c r="M107" t="n">
+        <v>0</v>
+      </c>
+      <c r="N107" t="n">
+        <v>0</v>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>2046106592114856006</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="n">
+        <v>106</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046106592114856006</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>2046106592114856006</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>2046215312949879234</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046215312949879234</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Exclusively for Emaratis. Apply for an Emarati Credit Card &amp;amp; get a welcome bonus of up to 150,000 EI SmartMiles worth AED 1,500
+✅ No annual membership fee
+📈 Earn up to 3.75 EI SmartMiles back per AED spend
+🍔 50% discount on talabat https://t.co/pIT39d8ym8</t>
+        </is>
+      </c>
+      <c r="G108" t="n">
+        <v>1776690722000</v>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>2046215312949879234</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGWd-66WYAAChSk.jpg', 'type': 'photo', 'id': '2046215310001201152'}]</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="K108" t="n">
+        <v>2</v>
+      </c>
+      <c r="L108" t="n">
+        <v>0</v>
+      </c>
+      <c r="M108" t="n">
+        <v>0</v>
+      </c>
+      <c r="N108" t="n">
+        <v>0</v>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="P108" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Xpost_df_comments.xlsx
+++ b/Xpost_df_comments.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P108"/>
+  <dimension ref="A1:P105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,62 +511,62 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://x.com/evocarsrental/status/2046283996015800804</t>
+          <t>https://x.com/saigol7/status/2046285967863279687</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2046283996015800804</t>
+          <t>2046285967863279687</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2046283996015800804</t>
+          <t>2045203152040018428</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://x.com/evocarsrental/status/2046283996015800804</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2045203152040018428</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE May i ask which email can be written to, for the purpose of assisting us in deferment on auto-loans. Based on the article - https://t.co/l4qu0XUPAx</t>
+          <t>We are extending our support to help you manage your finances with more confidence. https://t.co/EP2xuqo7Gb</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1776707097000</v>
+        <v>1776449404000</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2046283996015800804</t>
+          <t>2045203152040018428</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGIFa_XbAAAbdED.jpg', 'type': 'photo', 'id': '2045203142024036352'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGIFa_QaQAAmKGx.jpg', 'type': 'photo', 'id': '2045203141994627072'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGIFa_MbMAAD7Cp.jpg', 'type': 'photo', 'id': '2045203141977911296'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGIFa_kboAEToWB.jpg', 'type': 'photo', 'id': '2045203142078603265'}]</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>{'name': 'EVO Cars Rental', 'screenName': 'evocarsrental', 'followersCount': 34, 'favouritesCount': 7, 'friendsCount': 55, 'description': 'Go on! Drive your dream LUXURY car now!\nServices available for Individuals/Corporate Clients/Events/'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174305, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>573195</t>
         </is>
       </c>
       <c r="P2" t="inlineStr"/>
@@ -577,36 +577,35 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://x.com/evocarsrental/status/2046283996015800804</t>
+          <t>https://x.com/saigol7/status/2046285967863279687</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2046283996015800804</t>
+          <t>2046285967863279687</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2046287756955930787</t>
+          <t>2046285967863279687</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2046287756955930787</t>
+          <t>https://x.com/saigol7/status/2046285967863279687</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>@evocarsrental Thanks for writing to us, kindly visit the below link to review the terms and conditions then you can apply 
-https://t.co/ZUuqqadVdS</t>
+          <t>@EmiratesNBD_AE Please launch prepaid debit card for tourists.</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1776707994000</v>
+        <v>1776707567000</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2046283996015800804</t>
+          <t>2045203152040018428</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -616,11 +615,11 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174304, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Jeanvaljeanrambo', 'screenName': 'saigol7', 'followersCount': 98, 'favouritesCount': 801, 'friendsCount': 495, 'description': 'Planes,  automobiles, things that go fast and make a lot of noise. Also Linux, Unix and Android, Electronics, economics, astronomy, photography.'}</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -633,12 +632,12 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>109</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2046283996015800804</t>
+          <t>2045203152040018428</t>
         </is>
       </c>
     </row>
@@ -658,55 +657,60 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>2046289305190953193</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2046289305190953193</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>@saigol7 For suggestions please visit the below link, We will make every effort to address the matter promptly and provide the necessary support.
+https://t.co/nfKBl3vphJ</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>1776708363000</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
           <t>2045203152040018428</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2045203152040018428</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>We are extending our support to help you manage your finances with more confidence. https://t.co/EP2xuqo7Gb</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>1776449404000</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>2045203152040018428</t>
-        </is>
-      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGIFa_XbAAAbdED.jpg', 'type': 'photo', 'id': '2045203142024036352'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGIFa_QaQAAmKGx.jpg', 'type': 'photo', 'id': '2045203141994627072'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGIFa_MbMAAD7Cp.jpg', 'type': 'photo', 'id': '2045203141977911296'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGIFa_kboAEToWB.jpg', 'type': 'photo', 'id': '2045203142078603265'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174304, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174305, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>567313</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr"/>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2046285967863279687</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -724,57 +728,58 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>2046289251550044333</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2046289251550044333</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>@saigol7 Thanks for writing to us, please visit the below link to review the prepaid cards 
+https://t.co/6Lk5Jbb44I</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>1776708350000</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2045203152040018428</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174305, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
           <t>2046285967863279687</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>https://x.com/saigol7/status/2046285967863279687</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE Please launch prepaid debit card for tourists.</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>1776707567000</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>2045203152040018428</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>{'name': 'Jeanvaljeanrambo', 'screenName': 'saigol7', 'followersCount': 98, 'favouritesCount': 801, 'friendsCount': 495, 'description': 'Planes,  automobiles, things that go fast and make a lot of noise. Also Linux, Unix and Android, Electronics, economics, astronomy, photography.'}</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>2</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2045203152040018428</t>
         </is>
       </c>
     </row>
@@ -784,36 +789,36 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>https://x.com/saigol7/status/2046285967863279687</t>
+          <t>https://x.com/khaleejtimes/status/2046263546024165797</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2046285967863279687</t>
+          <t>2046263546024165797</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2046289305190953193</t>
+          <t>2046263546024165797</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2046289305190953193</t>
+          <t>https://x.com/khaleejtimes/status/2046263546024165797</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>@saigol7 For suggestions please visit the below link, We will make every effort to address the matter promptly and provide the necessary support.
-https://t.co/nfKBl3vphJ</t>
+          <t>Emirates NBD extends fee waivers, 0% interest on credit card transfers for UAE customers
+https://t.co/sNYXzG1RYE</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1776708363000</v>
+        <v>1776702221000</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2045203152040018428</t>
+          <t>2046263546024165797</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -823,7 +828,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174304, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Khaleej Times', 'screenName': 'khaleejtimes', 'followersCount': 1195570, 'favouritesCount': 43, 'friendsCount': 1565, 'description': "The official Twitter feed of Khaleej Times, the UAE's first and leading English daily\nhttps://t.co/bKx3o3oPhX"}</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -833,21 +838,17 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2046285967863279687</t>
-        </is>
-      </c>
+          <t>7175</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -855,70 +856,65 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://x.com/saigol7/status/2046285967863279687</t>
+          <t>https://x.com/khaleejtimes/status/2046263546024165797</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2046285967863279687</t>
+          <t>2046263546024165797</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2046289251550044333</t>
+          <t>2046375898933231804</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2046289251550044333</t>
+          <t>https://x.com/wallet/status/2046375898933231804</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>@saigol7 Thanks for writing to us, please visit the below link to review the prepaid cards 
-https://t.co/6Lk5Jbb44I</t>
+          <t>Need this? Drop a GM below👇 https://t.co/XjAc2KdaHx</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1776708350000</v>
+        <v>1776729008000</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2045203152040018428</t>
+          <t>2046375898933231804</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGYwBO5WgAEB478.jpg', 'type': 'photo', 'id': '2046375878423117825'}]</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174304, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'OKX Wallet', 'screenName': 'wallet', 'followersCount': 1929766, 'favouritesCount': 14748, 'friendsCount': 422, 'description': 'The crypto wallet for everything onchain. Self-custody is the future.\n\nEngagement is not endorsement.'}</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>555</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>609</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2046285967863279687</t>
-        </is>
-      </c>
+          <t>27261</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -926,36 +922,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>https://x.com/khaleejtimes/status/2046263546024165797</t>
+          <t>https://x.com/yallaweb/status/2046418526051684674</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2046263546024165797</t>
+          <t>2046418526051684674</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2046263546024165797</t>
+          <t>2046418526051684674</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://x.com/khaleejtimes/status/2046263546024165797</t>
+          <t>https://x.com/yallaweb/status/2046418526051684674</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Emirates NBD extends fee waivers, 0% interest on credit card transfers for UAE customers
-https://t.co/sNYXzG1RYE</t>
+          <t>#EmiratesNBD @EmiratesNBD_AE Sent Me An Account Statement,They Owe Me 200000AED Which They Won't Pay.@HHShkMohd @MohamedBinZayed
+#Lebanese #Banks Stole My Money @FransabankGroup @EmmanuelMacron.
+#Emirates @emirates &amp;amp; @BarackObama
+ Owe Me 2 Years Pay
+I Am Just Too Tired To Give Up</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1776702221000</v>
+        <v>1776739171000</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2046263546024165797</t>
+          <t>2046418526051684674</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -965,24 +964,24 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>{'name': 'Khaleej Times', 'screenName': 'khaleejtimes', 'followersCount': 1195567, 'favouritesCount': 43, 'friendsCount': 1565, 'description': "The official Twitter feed of Khaleej Times, the UAE's first and leading English daily\nhttps://t.co/bKx3o3oPhX"}</t>
+          <t>{'name': 'M.G.', 'screenName': 'yallaweb', 'followersCount': 597, 'favouritesCount': 13, 'friendsCount': 446, 'description': 'Digital Marketer,Startup Founder, Almost Homeless Accidental Activist Against Corrupt Corporations,zionistLobby WarCrimes,GayLobby Pedophiles &amp; CIA Cockroaches.'}</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>7104</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P8" t="inlineStr"/>
@@ -993,65 +992,65 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>https://x.com/khaleejtimes/status/2046263546024165797</t>
+          <t>https://x.com/yallaweb/status/2046418526051684674</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2046263546024165797</t>
+          <t>2046418526051684674</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2046375898933231804</t>
+          <t>2046433498962026756</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://x.com/wallet/status/2046375898933231804</t>
+          <t>https://x.com/Mario_thomas_y/status/2046433498962026756</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Need this? Drop a GM below👇 https://t.co/XjAc2KdaHx</t>
+          <t>@yallaweb Were you able to file a legal complaint @yallaweb ?</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1776729008000</v>
+        <v>1776742741000</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2046375898933231804</t>
+          <t>2046418526051684674</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGYwBO5WgAEB478.jpg', 'type': 'photo', 'id': '2046375878423117825'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>{'name': 'OKX Wallet', 'screenName': 'wallet', 'followersCount': 1929748, 'favouritesCount': 14748, 'friendsCount': 422, 'description': 'The crypto wallet for everything onchain. Self-custody is the future.\n\nEngagement is not endorsement.'}</t>
+          <t>{'name': 'Mario Thomas', 'screenName': 'Mario_thomas_y', 'followersCount': 1643, 'favouritesCount': 2658, 'friendsCount': 236, 'description': 'Victim of Elon scams.'}</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>547</v>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>24341</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2046418526051684674</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -1059,25 +1058,93 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>https://x.com/yallaweb/status/2046418526051684674</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2046418526051684674</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2046311476127023142</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>https://x.com/yallaweb/status/2046311476127023142</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>#God I Hate Slow #Internet,it's Killer Of  #Productivity
+Had 1000Mbps In #MexicoCity,But #GenocidalJews &amp;amp; #GenocidalGays Did    #Sabotage That,As They Thought My #highspeed Can Hinder/Expose/Endanger Their Crimes &amp;amp; Conspiracies.
+#EconomicSiege #Mexico #CDMX #Islamophobia #USA</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>1776713649000</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2046311476127023142</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>{'name': 'M.G.', 'screenName': 'yallaweb', 'followersCount': 597, 'favouritesCount': 13, 'friendsCount': 446, 'description': 'Digital Marketer,Startup Founder, Almost Homeless Accidental Activist Against Corrupt Corporations,zionistLobby WarCrimes,GayLobby Pedophiles &amp; CIA Cockroaches.'}</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>https://x.com/preeminentdxb/status/2046264235852718127</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>2046264235852718127</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>2046264189786714117</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>https://x.com/preeminentdxb/status/2046264189786714117</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>A quiet shift, but a powerful one.
 The gap between intent and ownership in Dubai just got smaller, and more predictable.
@@ -1085,93 +1152,27 @@
 #MarketMaturity #DubaiRealEstate #PropertyInvestment https://t.co/F1CLT9HxwK</t>
         </is>
       </c>
-      <c r="G10" t="n">
+      <c r="G11" t="n">
         <v>1776702375000</v>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>2046264189786714117</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGXKavSW8AAvugA.jpg', 'type': 'photo', 'id': '2046264166428635136'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGXKbQLWYAAjRuc.png', 'type': 'photo', 'id': '2046264175257608192'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGXKbh8WgAAvC6X.png', 'type': 'photo', 'id': '2046264180026540032'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGXKbz0W4AAHPcf.png', 'type': 'photo', 'id': '2046264184824848384'}]</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>{'name': 'Preeminent Properties', 'screenName': 'preeminentdxb', 'followersCount': 0, 'favouritesCount': 0, 'friendsCount': 2, 'description': "Unveiling UAE's finest real estate, where trust and satisfaction meet"}</t>
         </is>
       </c>
-      <c r="K10" t="n">
+      <c r="K11" t="n">
         <v>1</v>
       </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>https://x.com/preeminentdxb/status/2046264235852718127</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>2046264235852718127</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2046264235852718127</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>https://x.com/preeminentdxb/status/2046264235852718127</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Backed by Emirates NBD and Dubai Holding Real Estate, this move signals a maturing market: one that's reducing friction, improving transparency, and making long-term planning far more structure https://t.co/ykGWWmVfrC</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>1776702386000</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>2046264189786714117</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGXKda4WYAEW_JB.png', 'type': 'photo', 'id': '2046264212490444801'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGXKdvYXUAAyguF.png', 'type': 'photo', 'id': '2046264217993433088'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGXKeRWWcAEerrb.jpg', 'type': 'photo', 'id': '2046264227111792641'}]</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>{'name': 'Preeminent Properties', 'screenName': 'preeminentdxb', 'followersCount': 0, 'favouritesCount': 0, 'friendsCount': 2, 'description': "Unveiling UAE's finest real estate, where trust and satisfaction meet"}</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
@@ -1183,14 +1184,10 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2046264189786714117</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
@@ -1198,46 +1195,45 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>https://x.com/naveenthumala/status/2046198033738785046</t>
+          <t>https://x.com/preeminentdxb/status/2046264235852718127</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2046198033738785046</t>
+          <t>2046264235852718127</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2046198033738785046</t>
+          <t>2046264235852718127</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://x.com/naveenthumala/status/2046198033738785046</t>
+          <t>https://x.com/preeminentdxb/status/2046264235852718127</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>If someone experienced gulf banking understands  the importance of Emirates NBD acquiring RBL bank stake
-#RBLBank</t>
+          <t>Backed by Emirates NBD and Dubai Holding Real Estate, this move signals a maturing market: one that's reducing friction, improving transparency, and making long-term planning far more structure https://t.co/ykGWWmVfrC</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1776686602000</v>
+        <v>1776702386000</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2046198033738785046</t>
+          <t>2046264189786714117</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGXKda4WYAEW_JB.png', 'type': 'photo', 'id': '2046264212490444801'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGXKdvYXUAAyguF.png', 'type': 'photo', 'id': '2046264217993433088'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGXKeRWWcAEerrb.jpg', 'type': 'photo', 'id': '2046264227111792641'}]</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>{'name': 'Naveen Reddy', 'screenName': 'naveenthumala', 'followersCount': 20, 'favouritesCount': 1498, 'friendsCount': 127, 'description': 'Remember you will die'}</t>
+          <t>{'name': 'Preeminent Properties', 'screenName': 'preeminentdxb', 'followersCount': 0, 'favouritesCount': 0, 'friendsCount': 2, 'description': "Unveiling UAE's finest real estate, where trust and satisfaction meet"}</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1254,10 +1250,14 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2046264189786714117</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
@@ -1265,38 +1265,36 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>https://x.com/ja2030ah/status/2046190505554321598</t>
+          <t>https://x.com/naveenthumala/status/2046198033738785046</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2046190505554321598</t>
+          <t>2046198033738785046</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2046190505554321598</t>
+          <t>2046198033738785046</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://x.com/ja2030ah/status/2046190505554321598</t>
+          <t>https://x.com/naveenthumala/status/2046198033738785046</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>@DFMalerts 
-I have old account with DFM and now dormant. 
-I talked to Emirates NBD Securities , they said to contact Dubai Financial Market. 
-I have the full details. I need your help to update my investor’s account.</t>
+          <t>If someone experienced gulf banking understands  the importance of Emirates NBD acquiring RBL bank stake
+#RBLBank</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>1776684807000</v>
+        <v>1776686602000</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2046190505554321598</t>
+          <t>2046198033738785046</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1306,7 +1304,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>{'name': 'vision', 'screenName': 'ja2030ah', 'followersCount': 86, 'favouritesCount': 12, 'friendsCount': 597, 'description': 'وطني وقيادته خط أحمر'}</t>
+          <t>{'name': 'Naveen Reddy', 'screenName': 'naveenthumala', 'followersCount': 20, 'favouritesCount': 1498, 'friendsCount': 127, 'description': 'Remember you will die'}</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1323,7 +1321,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>18</t>
         </is>
       </c>
       <c r="P13" t="inlineStr"/>
@@ -1334,93 +1332,25 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>https://x.com/ENBDdeals/status/2046171931813011938</t>
+          <t>https://x.com/GaminNiukkua/status/2046173095581647055</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2046171931813011938</t>
+          <t>2046173095581647055</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2046171931813011938</t>
+          <t>2045093015459352679</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://x.com/ENBDdeals/status/2046171931813011938</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2045093015459352679</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
-        <is>
-          <t>Turn your bills into rewards
-Get AED 500 worth of noon credits + AED 500 welcome bonus when you apply for an Emirates NBD noon One Visa Credit Card.
-Apply Now: https://t.co/vPejTs11gM https://t.co/w4kHA8AtSA</t>
-        </is>
-      </c>
-      <c r="G14" t="n">
-        <v>1776680379000</v>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>2046171931813011938</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGV2hzyXYAAiJn2.jpg', 'type': 'photo', 'id': '2046171928918974464'}]</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD Deals', 'screenName': 'ENBDdeals', 'followersCount': 39177, 'favouritesCount': 61, 'friendsCount': 4, 'description': 'Welcome to the official account for Emirates NBD Deals. نرحب بكم في الحساب الرسمي لعروض بنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>1</v>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>https://x.com/ATwo2/status/2046171233243541979</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>2046171233243541979</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2045093015459352679</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2045093015459352679</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
         <is>
           <t>ندعم من يحمون الوطن
 مجموعة من مزايا الدعم المالي والخدمات المصرفية المخصصة للعاملين في الصفوف الأمامية
@@ -1434,8 +1364,74 @@
 https://t.co/I7DGlib9vt</t>
         </is>
       </c>
+      <c r="G14" t="n">
+        <v>1776423145000</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2045093015459352679</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGGhQnfXsAAHpYo.jpg', 'type': 'photo', 'id': '2045093012653453312'}]</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174305, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>19</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>35</v>
+      </c>
+      <c r="N14" t="n">
+        <v>346</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>866700</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>https://x.com/GaminNiukkua/status/2046173095581647055</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2046173095581647055</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2046173095581647055</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>https://x.com/GaminNiukkua/status/2046173095581647055</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE حرام ولا حلال؟</t>
+        </is>
+      </c>
       <c r="G15" t="n">
-        <v>1776423145000</v>
+        <v>1776680656000</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1444,32 +1440,36 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGGhQnfXsAAHpYo.jpg', 'type': 'photo', 'id': '2045093012653453312'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174304, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Gamin Niu', 'screenName': 'GaminNiukkua', 'followersCount': 2, 'favouritesCount': 941, 'friendsCount': 16, 'description': ''}</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>344</v>
+        <v>0</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>862354</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr"/>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>2045093015459352679</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
@@ -1477,31 +1477,32 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>https://x.com/ATwo2/status/2046171233243541979</t>
+          <t>https://x.com/GaminNiukkua/status/2046173095581647055</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2046171233243541979</t>
+          <t>2046173095581647055</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2046171233243541979</t>
+          <t>2046176687994376576</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://x.com/ATwo2/status/2046171233243541979</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2046176687994376576</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE شو ها العروض مع احترامي لكم. لا تستغلون حماة الوطن بهكذا عروض مخجله</t>
+          <t>@GaminNiukkua مرحبا شكرا لتواصلك معنا يمكنك مراجعه التفاصيل من خلال زياره هذا الرابط 
+https://t.co/7964Z6bRKk</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1776680212000</v>
+        <v>1776681513000</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1515,11 +1516,11 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>{'name': 'عبدالله ثاني الغاوي', 'screenName': 'ATwo2', 'followersCount': 444, 'favouritesCount': 4901, 'friendsCount': 480, 'description': 'رياضي، اقتصادي، #crypto$'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174305, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -1532,12 +1533,12 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>137</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2045093015459352679</t>
+          <t>2046173095581647055</t>
         </is>
       </c>
     </row>
@@ -1547,35 +1548,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>https://x.com/ATwo2/status/2046171233243541979</t>
+          <t>https://x.com/ja2030ah/status/2046190505554321598</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2046171233243541979</t>
+          <t>2046190505554321598</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2046175033328890208</t>
+          <t>2046190505554321598</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2046175033328890208</t>
+          <t>https://x.com/ja2030ah/status/2046190505554321598</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>@ATwo2 مرحبًا، هل يمكننا معرفة سبب عدم رضاك؟ سيكون من المفيد جدًا إذا كان بإمكانك مشاركة المزيد من التفاصيل حول ذلك ورقم اتصالك معنا عبر الرسائل الخاصة.</t>
+          <t>@DFMalerts 
+I have old account with DFM and now dormant. 
+I talked to Emirates NBD Securities , they said to contact Dubai Financial Market. 
+I have the full details. I need your help to update my investor’s account.</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1776681118000</v>
+        <v>1776684807000</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2045093015459352679</t>
+          <t>2046190505554321598</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1585,7 +1589,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174304, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'vision', 'screenName': 'ja2030ah', 'followersCount': 86, 'favouritesCount': 12, 'friendsCount': 597, 'description': 'وطني وقيادته خط أحمر'}</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1602,14 +1606,10 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>2046171233243541979</t>
-        </is>
-      </c>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
@@ -1617,46 +1617,47 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>https://x.com/ArabiaCSR/status/2046167018303602898</t>
+          <t>https://x.com/ENBDdeals/status/2046171931813011938</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2046167018303602898</t>
+          <t>2046171931813011938</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2046167018303602898</t>
+          <t>2046171931813011938</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://x.com/ArabiaCSR/status/2046167018303602898</t>
+          <t>https://x.com/ENBDdeals/status/2046171931813011938</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Excited to announce Mr Vijay Bains, Group Head of ESG &amp;amp; CSO at Emirates NBD, as a plenary speaker for Climate Finance 2.0 at the Global Sustainability &amp;amp; CSR Forum!
-With 20+ years in sustainable finance &amp;amp; leadership in ESG councils, Vijay brings unmatched expertise. Don’t miss it! https://t.co/ApxeVy3ABX</t>
+          <t>Turn your bills into rewards
+Get AED 500 worth of noon credits + AED 500 welcome bonus when you apply for an Emirates NBD noon One Visa Credit Card.
+Apply Now: https://t.co/vPejTs11gM https://t.co/w4kHA8AtSA</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>1776679207000</v>
+        <v>1776680379000</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2046167018303602898</t>
+          <t>2046171931813011938</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGVyD6AaAAAN0zx.jpg', 'type': 'photo', 'id': '2046167017145892864'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGV2hzyXYAAiJn2.jpg', 'type': 'photo', 'id': '2046171928918974464'}]</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>{'name': 'Arabia CSR Network', 'screenName': 'ArabiaCSR', 'followersCount': 3122, 'favouritesCount': 2298, 'friendsCount': 595, 'description': 'We are one of the very first multi-stakeholder platforms contributing to CSR &amp; sustainable development across the Arab world. #HappinessInSustainability'}</t>
+          <t>{'name': 'Emirates NBD Deals', 'screenName': 'ENBDdeals', 'followersCount': 39177, 'favouritesCount': 61, 'friendsCount': 4, 'description': 'Welcome to the official account for Emirates NBD Deals. نرحب بكم في الحساب الرسمي لعروض بنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -1669,11 +1670,11 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>73</t>
         </is>
       </c>
       <c r="P18" t="inlineStr"/>
@@ -1684,94 +1685,25 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>https://x.com/ArabiaCSR/status/2046167018303602898</t>
+          <t>https://x.com/ATwo2/status/2046171233243541979</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2046167018303602898</t>
+          <t>2046171233243541979</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2046118862736003268</t>
+          <t>2045093015459352679</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://x.com/ArabiaCSR/status/2046118862736003268</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2045093015459352679</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
-        <is>
-          <t>Arabia CSR Network – Driving sustainability and responsible business across the MENA region.
-Through research, insights, and collaboration, we empower organisations to create meaningful CSR impact and shape a sustainable future.
-admin@arabiacsrnetwork.com
-https://t.co/FXjp8HUpNf https://t.co/gpTUlQf79R</t>
-        </is>
-      </c>
-      <c r="G19" t="n">
-        <v>1776667726000</v>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>2046118862736003268</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGVGQ4CakAAF6bs.jpg', 'type': 'photo', 'id': '2046118861444124672'}]</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>{'name': 'Arabia CSR Network', 'screenName': 'ArabiaCSR', 'followersCount': 3122, 'favouritesCount': 2298, 'friendsCount': 595, 'description': 'We are one of the very first multi-stakeholder platforms contributing to CSR &amp; sustainable development across the Arab world. #HappinessInSustainability'}</t>
-        </is>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>https://x.com/she7ii88/status/2046061240511082734</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>2046061240511082734</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>2045093015459352679</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2045093015459352679</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
         <is>
           <t>ندعم من يحمون الوطن
 مجموعة من مزايا الدعم المالي والخدمات المصرفية المخصصة للعاملين في الصفوف الأمامية
@@ -1785,8 +1717,74 @@
 https://t.co/I7DGlib9vt</t>
         </is>
       </c>
+      <c r="G19" t="n">
+        <v>1776423145000</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>2045093015459352679</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGGhQnfXsAAHpYo.jpg', 'type': 'photo', 'id': '2045093012653453312'}]</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174305, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>19</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" t="n">
+        <v>35</v>
+      </c>
+      <c r="N19" t="n">
+        <v>346</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>866700</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>https://x.com/ATwo2/status/2046171233243541979</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2046171233243541979</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2046171233243541979</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>https://x.com/ATwo2/status/2046171233243541979</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE شو ها العروض مع احترامي لكم. لا تستغلون حماة الوطن بهكذا عروض مخجله</t>
+        </is>
+      </c>
       <c r="G20" t="n">
-        <v>1776423145000</v>
+        <v>1776680212000</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1795,32 +1793,36 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGGhQnfXsAAHpYo.jpg', 'type': 'photo', 'id': '2045093012653453312'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174304, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'عبدالله ثاني الغاوي', 'screenName': 'ATwo2', 'followersCount': 444, 'favouritesCount': 4901, 'friendsCount': 480, 'description': 'رياضي، اقتصادي، #crypto$'}</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="L20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>344</v>
+        <v>0</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>862471</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr"/>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>2045093015459352679</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
@@ -1828,33 +1830,31 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>https://x.com/she7ii88/status/2046061240511082734</t>
+          <t>https://x.com/ATwo2/status/2046171233243541979</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2046061240511082734</t>
+          <t>2046171233243541979</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2046061240511082734</t>
+          <t>2046175033328890208</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://x.com/she7ii88/status/2046061240511082734</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2046175033328890208</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE هذا عرض صدق ؟! 
-٦% ؟! سلامات البنوك الاسلاميه المرابحه الثابته ٢.٧% ؟! 
-ولو سمحتوا علم الامارات و لبس القوات المسلحه ... ليست دعايه</t>
+          <t>@ATwo2 مرحبًا، هل يمكننا معرفة سبب عدم رضاك؟ سيكون من المفيد جدًا إذا كان بإمكانك مشاركة المزيد من التفاصيل حول ذلك ورقم اتصالك معنا عبر الرسائل الخاصة.</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>1776653988000</v>
+        <v>1776681118000</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>{'name': 'Rashed Sem', 'screenName': 'she7ii88', 'followersCount': 9, 'favouritesCount': 303, 'friendsCount': 49, 'description': ''}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174305, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>70</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2045093015459352679</t>
+          <t>2046171233243541979</t>
         </is>
       </c>
     </row>
@@ -1900,46 +1900,46 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>https://x.com/khaleejtimes/status/2046166030557614556</t>
+          <t>https://x.com/ArabiaCSR/status/2046167018303602898</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2046166030557614556</t>
+          <t>2046167018303602898</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2046166030557614556</t>
+          <t>2046167018303602898</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://x.com/khaleejtimes/status/2046166030557614556</t>
+          <t>https://x.com/ArabiaCSR/status/2046167018303602898</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Emirates NBD extends fee waivers, 0% interest on credit card transfers for UAE customers
-https://t.co/sNYXzG1RYE</t>
+          <t>Excited to announce Mr Vijay Bains, Group Head of ESG &amp;amp; CSO at Emirates NBD, as a plenary speaker for Climate Finance 2.0 at the Global Sustainability &amp;amp; CSR Forum!
+With 20+ years in sustainable finance &amp;amp; leadership in ESG councils, Vijay brings unmatched expertise. Don’t miss it! https://t.co/ApxeVy3ABX</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>1776678972000</v>
+        <v>1776679207000</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2046166030557614556</t>
+          <t>2046167018303602898</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGVyD6AaAAAN0zx.jpg', 'type': 'photo', 'id': '2046167017145892864'}]</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>{'name': 'Khaleej Times', 'screenName': 'khaleejtimes', 'followersCount': 1195567, 'favouritesCount': 43, 'friendsCount': 1565, 'description': "The official Twitter feed of Khaleej Times, the UAE's first and leading English daily\nhttps://t.co/bKx3o3oPhX"}</t>
+          <t>{'name': 'Arabia CSR Network', 'screenName': 'ArabiaCSR', 'followersCount': 3122, 'favouritesCount': 2298, 'friendsCount': 595, 'description': 'We are one of the very first multi-stakeholder platforms contributing to CSR &amp; sustainable development across the Arab world. #HappinessInSustainability'}</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -1949,14 +1949,14 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>8330</t>
+          <t>21</t>
         </is>
       </c>
       <c r="P22" t="inlineStr"/>
@@ -1967,63 +1967,65 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>https://x.com/khaleejtimes/status/2046166030557614556</t>
+          <t>https://x.com/ArabiaCSR/status/2046167018303602898</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2046166030557614556</t>
+          <t>2046167018303602898</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2046265860453761085</t>
+          <t>2046118862736003268</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://x.com/Cricket_bazball/status/2046265860453761085</t>
+          <t>https://x.com/ArabiaCSR/status/2046118862736003268</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>🚨 End of Mike Hesson 🚨
-- PCB has decided to sack Mike Hesson from the role of Pakistan team’s head coach and has decided to appoint Ottis Gibson as the new head coach for white-ball cricket. (Geo news) https://t.co/nvlKVuP4il</t>
+          <t>Arabia CSR Network – Driving sustainability and responsible business across the MENA region.
+Through research, insights, and collaboration, we empower organisations to create meaningful CSR impact and shape a sustainable future.
+admin@arabiacsrnetwork.com
+https://t.co/FXjp8HUpNf https://t.co/gpTUlQf79R</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>1776702773000</v>
+        <v>1776667726000</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2046265860453761085</t>
+          <t>2046118862736003268</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGXL9DraAAMigd2.jpg', 'type': 'photo', 'id': '2046265855529582595'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGVGQ4CakAAF6bs.jpg', 'type': 'photo', 'id': '2046118861444124672'}]</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>{'name': 'junaid', 'screenName': 'Cricket_bazball', 'followersCount': 145, 'favouritesCount': 174811, 'friendsCount': 258, 'description': 'Cricket • Stats • Not affiliated with anyone'}</t>
+          <t>{'name': 'Arabia CSR Network', 'screenName': 'ArabiaCSR', 'followersCount': 3122, 'favouritesCount': 2298, 'friendsCount': 595, 'description': 'We are one of the very first multi-stakeholder platforms contributing to CSR &amp; sustainable development across the Arab world. #HappinessInSustainability'}</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>752</v>
+        <v>0</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>35692</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P23" t="inlineStr"/>
@@ -2034,36 +2036,36 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>https://x.com/Kyodonews_JBN/status/2046033950339166455</t>
+          <t>https://x.com/khaleejtimes/status/2046166030557614556</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2046033950339166455</t>
+          <t>2046166030557614556</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2046033950339166455</t>
+          <t>2046166030557614556</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://x.com/Kyodonews_JBN/status/2046033950339166455</t>
+          <t>https://x.com/khaleejtimes/status/2046166030557614556</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Emirates NBD、Dar Global向け2億5,000万米ドルのシンジケート・タームローンを実行し、世界的な成長と事業拡大を加速【Dar Global】
-https://t.co/H82MnfRa04</t>
+          <t>Emirates NBD extends fee waivers, 0% interest on credit card transfers for UAE customers
+https://t.co/sNYXzG1RYE</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>1776647481000</v>
+        <v>1776678972000</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2046033950339166455</t>
+          <t>2046166030557614556</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2073,7 +2075,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>{'name': 'KYODONEWS JBN', 'screenName': 'Kyodonews_JBN', 'followersCount': 22, 'favouritesCount': 6, 'friendsCount': 2, 'description': '株式会社共同通信社 ジャパンビジネス広報センター'}</t>
+          <t>{'name': 'Khaleej Times', 'screenName': 'khaleejtimes', 'followersCount': 1195570, 'favouritesCount': 43, 'friendsCount': 1565, 'description': "The official Twitter feed of Khaleej Times, the UAE's first and leading English daily\nhttps://t.co/bKx3o3oPhX"}</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -2083,14 +2085,14 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8379</t>
         </is>
       </c>
       <c r="P24" t="inlineStr"/>
@@ -2101,63 +2103,63 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>https://x.com/Kyodonews_JBN/status/2046033950339166455</t>
+          <t>https://x.com/khaleejtimes/status/2046166030557614556</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2046033950339166455</t>
+          <t>2046166030557614556</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2046424774474391989</t>
+          <t>2046265860453761085</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://x.com/Kyodonews_JBN/status/2046424774474391989</t>
+          <t>https://x.com/Cricket_bazball/status/2046265860453761085</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Singapore imagines new ways of living at Milan Design Week with the opening of Prototype Island【DesignSingapore Council】
-https://t.co/SxdfkcpvgF</t>
+          <t>🚨 End of Mike Hesson 🚨
+- PCB has decided to sack Mike Hesson from the role of Pakistan team’s head coach and has decided to appoint Ottis Gibson as the new head coach for white-ball cricket. (Geo news) https://t.co/nvlKVuP4il</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>1776740661000</v>
+        <v>1776702773000</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2046424774474391989</t>
+          <t>2046265860453761085</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGXL9DraAAMigd2.jpg', 'type': 'photo', 'id': '2046265855529582595'}]</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>{'name': 'KYODONEWS JBN', 'screenName': 'Kyodonews_JBN', 'followersCount': 22, 'favouritesCount': 6, 'friendsCount': 2, 'description': '株式会社共同通信社 ジャパンビジネス広報センター'}</t>
+          <t>{'name': 'junaid', 'screenName': 'Cricket_bazball', 'followersCount': 145, 'favouritesCount': 174811, 'friendsCount': 258, 'description': 'Cricket • Stats • Not affiliated with anyone'}</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>785</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>38069</t>
         </is>
       </c>
       <c r="P25" t="inlineStr"/>
@@ -2168,25 +2170,159 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
+          <t>https://x.com/Kyodonews_JBN/status/2046033950339166455</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2046033950339166455</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2046033950339166455</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>https://x.com/Kyodonews_JBN/status/2046033950339166455</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Emirates NBD、Dar Global向け2億5,000万米ドルのシンジケート・タームローンを実行し、世界的な成長と事業拡大を加速【Dar Global】
+https://t.co/H82MnfRa04</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>1776647481000</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>2046033950339166455</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>{'name': 'KYODONEWS JBN', 'screenName': 'Kyodonews_JBN', 'followersCount': 22, 'favouritesCount': 6, 'friendsCount': 2, 'description': '株式会社共同通信社 ジャパンビジネス広報センター'}</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>https://x.com/Kyodonews_JBN/status/2046033950339166455</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2046033950339166455</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2046424774474391989</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>https://x.com/Kyodonews_JBN/status/2046424774474391989</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Singapore imagines new ways of living at Milan Design Week with the opening of Prototype Island【DesignSingapore Council】
+https://t.co/SxdfkcpvgF</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>1776740661000</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>2046424774474391989</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>{'name': 'KYODONEWS JBN', 'screenName': 'Kyodonews_JBN', 'followersCount': 22, 'favouritesCount': 6, 'friendsCount': 2, 'description': '株式会社共同通信社 ジャパンビジネス広報センター'}</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
           <t>https://x.com/mohmd_moh/status/2046224051438526663</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>2046224051438526663</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>2044321422282240384</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>https://x.com/ADIBTweets/status/2044321422282240384</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>قد تكون رسالة من “قريب”... لكنها احتيال. 
 أجب واربح 
@@ -2204,183 +2340,42 @@
 مسابقة_مصرف_أبوظبي_الإسلامي</t>
         </is>
       </c>
-      <c r="G26" t="n">
+      <c r="G28" t="n">
         <v>1776239183000</v>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>2044321422282240384</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF7jf0ba0AAZFPu.jpg', 'type': 'photo', 'id': '2044321416661880832'}]</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>{'name': 'ADIB Tweets', 'screenName': 'ADIBTweets', 'followersCount': 137563, 'favouritesCount': 2888, 'friendsCount': 104, 'description': 'حياكم في الحساب الرسمي لمصرف أبوظبي الإسلامي، شركة مساهمة عامة. Welcome to Abu Dhabi Islamic Bank Public Joint Stock Company official account'}</t>
-        </is>
-      </c>
-      <c r="K26" t="n">
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>{'name': 'ADIB Tweets', 'screenName': 'ADIBTweets', 'followersCount': 137558, 'favouritesCount': 2888, 'friendsCount': 104, 'description': 'حياكم في الحساب الرسمي لمصرف أبوظبي الإسلامي، شركة مساهمة عامة. Welcome to Abu Dhabi Islamic Bank Public Joint Stock Company official account'}</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
         <v>393</v>
       </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
         <v>69</v>
       </c>
-      <c r="N26" t="n">
+      <c r="N28" t="n">
         <v>206</v>
       </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>1435284</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>https://x.com/mohmd_moh/status/2046224051438526663</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>2046224051438526663</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>2045175695169732901</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>https://x.com/mohmd_moh/status/2045175695169732901</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>لماذ البنك لايتحمل المسوؤلية إذا تم اختراق الحساب الشخصي وتم سحب مبلغ من المال بدون اي ادارة امن الحسابات او عن طريق ارسال OTP ويدعي انه تم التحويل بالفعل والبنك غير قادر علي فعل شيي و يجب ان يتحمل صاحب الحساب تكاليف اصدار بطاقة جديده و تحمل المبلغ المسحوب و كأن الحسابات الشخصية سبيل متاح لاي عملية إحتيال وعلي صاحب الحساب تحمل كامل المسؤلية والبنك الذي من المفترض هو المؤتمن علي هذا المال لايتحمل إي مسؤلية.. علي فكره انتم من البنوك التي لاتهتم بحمايه العميل لكن هناك بنوك مثل الامارات الإسلامي له كل الشكر والامتنان لانه حدث معي عمليه احتيال و خلال اسبوع تحمل البنك المبلغ وتم إيداعه في حسابي وتم اصدار بطاقة جديده بدون اي تكلفة.
-كل الشكر الي بنك الإمارات الإسلامي @emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G27" t="n">
-        <v>1776442857000</v>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>2044321422282240384</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>{'name': 'Mohamed Mohamed', 'screenName': 'mohmd_moh', 'followersCount': 195, 'favouritesCount': 6659, 'friendsCount': 1287, 'description': ''}</t>
-        </is>
-      </c>
-      <c r="K27" t="n">
-        <v>3</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>2044321422282240384</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>https://x.com/mohmd_moh/status/2046224051438526663</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>2046224051438526663</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>2046125857643606493</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2046125857643606493</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>@mohmd_moh مرحبا ، يأسفنا سماع تجربتك! فريقنا ملتزم بمعالجة هذا الأمر على الفور. لحماية خصوصيتك ، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل. رضاك أولويتنا.</t>
-        </is>
-      </c>
-      <c r="G28" t="n">
-        <v>1776669394000</v>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>2044321422282240384</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="K28" t="n">
-        <v>1</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>2045175695169732901</t>
-        </is>
-      </c>
+          <t>1440032</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
@@ -2398,270 +2393,270 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
+          <t>2045175695169732901</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>https://x.com/mohmd_moh/status/2045175695169732901</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>لماذ البنك لايتحمل المسوؤلية إذا تم اختراق الحساب الشخصي وتم سحب مبلغ من المال بدون اي ادارة امن الحسابات او عن طريق ارسال OTP ويدعي انه تم التحويل بالفعل والبنك غير قادر علي فعل شيي و يجب ان يتحمل صاحب الحساب تكاليف اصدار بطاقة جديده و تحمل المبلغ المسحوب و كأن الحسابات الشخصية سبيل متاح لاي عملية إحتيال وعلي صاحب الحساب تحمل كامل المسؤلية والبنك الذي من المفترض هو المؤتمن علي هذا المال لايتحمل إي مسؤلية.. علي فكره انتم من البنوك التي لاتهتم بحمايه العميل لكن هناك بنوك مثل الامارات الإسلامي له كل الشكر والامتنان لانه حدث معي عمليه احتيال و خلال اسبوع تحمل البنك المبلغ وتم إيداعه في حسابي وتم اصدار بطاقة جديده بدون اي تكلفة.
+كل الشكر الي بنك الإمارات الإسلامي @emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>1776442857000</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>2044321422282240384</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>{'name': 'Mohamed Mohamed', 'screenName': 'mohmd_moh', 'followersCount': 195, 'favouritesCount': 6659, 'friendsCount': 1287, 'description': ''}</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>3</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>2044321422282240384</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>https://x.com/mohmd_moh/status/2046224051438526663</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
           <t>2046224051438526663</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2046125857643606493</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046125857643606493</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>@mohmd_moh مرحبا ، يأسفنا سماع تجربتك! فريقنا ملتزم بمعالجة هذا الأمر على الفور. لحماية خصوصيتك ، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل. رضاك أولويتنا.</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>1776669394000</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>2044321422282240384</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>1</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>2045175695169732901</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" t="inlineStr">
         <is>
           <t>https://x.com/mohmd_moh/status/2046224051438526663</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2046224051438526663</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2046224051438526663</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>https://x.com/mohmd_moh/status/2046224051438526663</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
         <is>
           <t>الشكر الجزيل لكم .  ليس لدي اي مشكلة حاليا أنا فقط ذكرت ماحدث معي للإشادة بكم علي سرعة الحل المقدم من طرفكم وسرعة استجابتكم وتحملكم المسؤلية تجاه العملاء .
 تعامل راقي وليس هدفكم المكسب فقط ولكن هدفكم الاول هو ارضاء العميل وهذا ذكاء منكم لأنكم بهذا الأسلوب سوف تكسبوا ثقة العملاء وبالتالي زيادة العملاء ويأتي المكسب مضاعف لاحقا . 
 كلمة حق تقال ان نهج الإمارات الإسلامي يستحق ان يقتدي به جميع البنوك.</t>
         </is>
       </c>
-      <c r="G29" t="n">
+      <c r="G31" t="n">
         <v>1776692805000</v>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>2044321422282240384</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>{'name': 'Mohamed Mohamed', 'screenName': 'mohmd_moh', 'followersCount': 195, 'favouritesCount': 6659, 'friendsCount': 1287, 'description': ''}</t>
         </is>
       </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
         <is>
           <t>2046125857643606493</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="1" t="n">
-        <v>28</v>
-      </c>
-      <c r="B30" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" t="inlineStr">
         <is>
           <t>https://x.com/aaditsh/status/2046217543870738694</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>2046217543870738694</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>2044732404938702855</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>https://x.com/aaditsh/status/2044732404938702855</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>@emiratesislamic probably the worst customer experience I’ve had in my life.
 Tried cancelling my cards. Have received 10+ phone calls from them trying to retain. Confirmed each time that I want to cancel (on call and on email confirmation). It’s been 4-5 months since I raised this complaint. No resolution yet.
 Impressed with how difficult they make this process. Wow!</t>
         </is>
       </c>
-      <c r="G30" t="n">
+      <c r="G32" t="n">
         <v>1776337169000</v>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>2044732404938702855</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>{'name': 'Aadit Sheth', 'screenName': 'aaditsh', 'followersCount': 523004, 'favouritesCount': 32071, 'friendsCount': 588, 'description': 'Co-founder, The Narrative Company. We help Fortune 500 C-suite engineer their biggest moments. Also write Neatprompts, 100K+ subscribers.'}</t>
-        </is>
-      </c>
-      <c r="K30" t="n">
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>{'name': 'Aadit Sheth', 'screenName': 'aaditsh', 'followersCount': 523000, 'favouritesCount': 32071, 'friendsCount': 588, 'description': 'Co-founder, The Narrative Company. We help Fortune 500 C-suite engineer their biggest moments. Also write Neatprompts, 100K+ subscribers.'}</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
         <v>2</v>
       </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" t="n">
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
         <v>4</v>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>6419</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="n">
-        <v>29</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>https://x.com/aaditsh/status/2046217543870738694</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>2046217543870738694</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>2044758862017007662</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>https://x.com/RakeshMavath/status/2044758862017007662</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>@aaditsh @emiratesislamic especially now they are not going to let go of your business easily. you can raise the issue with UAECB who will in turn contact the bank</t>
-        </is>
-      </c>
-      <c r="G31" t="n">
-        <v>1776343477000</v>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>2044732404938702855</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>{'name': 'Rakesh Mavath', 'screenName': 'RakeshMavath', 'followersCount': 367, 'favouritesCount': 12526, 'friendsCount': 3077, 'description': 'Running two startups: one guarantees your rent @takeem_ai, the other guarantees your dignity. Still waiting for my guaranteed 8 hours of sleep.'}</t>
-        </is>
-      </c>
-      <c r="K31" t="n">
-        <v>1</v>
-      </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="n">
-        <v>1</v>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>2044732404938702855</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="n">
-        <v>30</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>https://x.com/aaditsh/status/2046217543870738694</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>2046217543870738694</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>2044759599656689929</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>https://x.com/aaditsh/status/2044759599656689929</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>@RakeshMavath @emiratesislamic Will do! So frustrating. They will call me, I’ll pick up. They will end the call within 10 seconds and message me “we called you. You didn’t pick up”.
-And it’s been extended like this for the past 4-5 months. What a joke.</t>
-        </is>
-      </c>
-      <c r="G32" t="n">
-        <v>1776343653000</v>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>2044732404938702855</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>{'name': 'Aadit Sheth', 'screenName': 'aaditsh', 'followersCount': 523004, 'favouritesCount': 32071, 'friendsCount': 588, 'description': 'Co-founder, The Narrative Company. We help Fortune 500 C-suite engineer their biggest moments. Also write Neatprompts, 100K+ subscribers.'}</t>
-        </is>
-      </c>
-      <c r="K32" t="n">
-        <v>1</v>
-      </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" t="n">
-        <v>1</v>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>2044758862017007662</t>
-        </is>
-      </c>
+      <c r="P32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
@@ -2679,21 +2674,21 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2044832798670995759</t>
+          <t>2044758862017007662</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://x.com/RakeshMavath/status/2044832798670995759</t>
+          <t>https://x.com/RakeshMavath/status/2044758862017007662</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>@aaditsh @emiratesislamic Grab screenshots of when they have called you and the following messages include that to your complaint to UAECB and they will fine the bank</t>
+          <t>@aaditsh @emiratesislamic especially now they are not going to let go of your business easily. you can raise the issue with UAECB who will in turn contact the bank</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>1776361105000</v>
+        <v>1776343477000</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -2724,12 +2719,12 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>161</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2044759599656689929</t>
+          <t>2044732404938702855</t>
         </is>
       </c>
     </row>
@@ -2749,21 +2744,22 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2046217543870738694</t>
+          <t>2044759599656689929</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://x.com/aaditsh/status/2046217543870738694</t>
+          <t>https://x.com/aaditsh/status/2044759599656689929</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>@RakeshMavath @emiratesislamic Alright. Will do! Thanks.</t>
+          <t>@RakeshMavath @emiratesislamic Will do! So frustrating. They will call me, I’ll pick up. They will end the call within 10 seconds and message me “we called you. You didn’t pick up”.
+And it’s been extended like this for the past 4-5 months. What a joke.</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>1776691253000</v>
+        <v>1776343653000</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -2777,11 +2773,11 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>{'name': 'Aadit Sheth', 'screenName': 'aaditsh', 'followersCount': 523004, 'favouritesCount': 32071, 'friendsCount': 588, 'description': 'Co-founder, The Narrative Company. We help Fortune 500 C-suite engineer their biggest moments. Also write Neatprompts, 100K+ subscribers.'}</t>
+          <t>{'name': 'Aadit Sheth', 'screenName': 'aaditsh', 'followersCount': 523000, 'favouritesCount': 32071, 'friendsCount': 588, 'description': 'Co-founder, The Narrative Company. We help Fortune 500 C-suite engineer their biggest moments. Also write Neatprompts, 100K+ subscribers.'}</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -2794,12 +2790,12 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>228</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2044832798670995759</t>
+          <t>2044758862017007662</t>
         </is>
       </c>
     </row>
@@ -2809,46 +2805,45 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2046148194392740002</t>
+          <t>https://x.com/aaditsh/status/2046217543870738694</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2046148194392740002</t>
+          <t>2046217543870738694</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2046148156560121974</t>
+          <t>2044832798670995759</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2046148156560121974</t>
+          <t>https://x.com/RakeshMavath/status/2044832798670995759</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>امنح أبنائك انطلاقة مبكرة نحو الوعي المالي الذكي
- #الإمارات_الإسلامي https://t.co/xdFKEhpKDT</t>
+          <t>@aaditsh @emiratesislamic Grab screenshots of when they have called you and the following messages include that to your complaint to UAECB and they will fine the bank</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>1776674710000</v>
+        <v>1776361105000</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2046148156560121974</t>
+          <t>2044732404938702855</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/ext_tw_video_thumb/2046148122250809344/pu/img/WEGHCsaWoyjDb-ot.jpg', 'type': 'video', 'id': '2046148122250809344'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+          <t>{'name': 'Rakesh Mavath', 'screenName': 'RakeshMavath', 'followersCount': 367, 'favouritesCount': 12526, 'friendsCount': 3077, 'description': 'Running two startups: one guarantees your rent @takeem_ai, the other guarantees your dignity. Still waiting for my guaranteed 8 hours of sleep.'}</t>
         </is>
       </c>
       <c r="K35" t="n">
@@ -2861,14 +2856,18 @@
         <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr"/>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>2044759599656689929</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
@@ -2876,46 +2875,45 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2046148194392740002</t>
+          <t>https://x.com/aaditsh/status/2046217543870738694</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2046148194392740002</t>
+          <t>2046217543870738694</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2046148194392740002</t>
+          <t>2046217543870738694</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2046148194392740002</t>
+          <t>https://x.com/aaditsh/status/2046217543870738694</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Your child's smart money journey starts here. Empower your kids to take their first steps toward financial independence. 
-#EmiratesIslamic #AlphaYouth https://t.co/udWgfz8rNb</t>
+          <t>@RakeshMavath @emiratesislamic Alright. Will do! Thanks.</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>1776674719000</v>
+        <v>1776691253000</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2046148156560121974</t>
+          <t>2044732404938702855</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/ext_tw_video_thumb/2046148161090068480/pu/img/GpPJv5a4DR5wZAQc.jpg', 'type': 'video', 'id': '2046148161090068480'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+          <t>{'name': 'Aadit Sheth', 'screenName': 'aaditsh', 'followersCount': 523000, 'favouritesCount': 32071, 'friendsCount': 588, 'description': 'Co-founder, The Narrative Company. We help Fortune 500 C-suite engineer their biggest moments. Also write Neatprompts, 100K+ subscribers.'}</t>
         </is>
       </c>
       <c r="K36" t="n">
@@ -2928,16 +2926,16 @@
         <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>11</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2046148156560121974</t>
+          <t>2044832798670995759</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3003,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>64</t>
         </is>
       </c>
       <c r="P37" t="inlineStr"/>
@@ -3071,7 +3069,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -3086,25 +3084,163 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
+          <t>https://x.com/emiratesislamic/status/2046148194392740002</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2046148194392740002</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2046148156560121974</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046148156560121974</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>امنح أبنائك انطلاقة مبكرة نحو الوعي المالي الذكي
+ #الإمارات_الإسلامي https://t.co/xdFKEhpKDT</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>1776674710000</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>2046148156560121974</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/ext_tw_video_thumb/2046148122250809344/pu/img/WEGHCsaWoyjDb-ot.jpg', 'type': 'video', 'id': '2046148122250809344'}]</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="K39" t="n">
+        <v>1</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046148194392740002</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2046148194392740002</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2046148194392740002</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046148194392740002</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Your child's smart money journey starts here. Empower your kids to take their first steps toward financial independence. 
+#EmiratesIslamic #AlphaYouth https://t.co/udWgfz8rNb</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>1776674719000</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>2046148156560121974</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/ext_tw_video_thumb/2046148161090068480/pu/img/GpPJv5a4DR5wZAQc.jpg', 'type': 'video', 'id': '2046148161090068480'}]</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>2046148156560121974</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
           <t>https://x.com/emiratesislamic/status/2046106592232214645</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>2046106592232214645</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>2046106592232214645</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2046106592232214645</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>Legitimate delivery companies don’t ask for extra payments through unsecured links.
 Do not fall for the traps. Stay alert to scams.
@@ -3113,68 +3249,68 @@
 https://t.co/y7eSpGNdfk</t>
         </is>
       </c>
-      <c r="G39" t="n">
+      <c r="G41" t="n">
         <v>1776664801000</v>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>2046106592232214645</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
-      <c r="K39" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" t="n">
-        <v>0</v>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="P39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="n">
-        <v>38</v>
-      </c>
-      <c r="B40" t="inlineStr">
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2046106592232214645</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>2046106592232214645</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>2046215312949879234</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2046215312949879234</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>Exclusively for Emaratis. Apply for an Emarati Credit Card &amp;amp; get a welcome bonus of up to 150,000 EI SmartMiles worth AED 1,500
 ✅ No annual membership fee
@@ -3182,136 +3318,136 @@
 🍔 50% discount on talabat https://t.co/pIT39d8ym8</t>
         </is>
       </c>
-      <c r="G40" t="n">
+      <c r="G42" t="n">
         <v>1776690722000</v>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>2046215312949879234</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGWd-66WYAAChSk.jpg', 'type': 'photo', 'id': '2046215310001201152'}]</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
-      <c r="K40" t="n">
+      <c r="K42" t="n">
         <v>2</v>
       </c>
-      <c r="L40" t="n">
-        <v>0</v>
-      </c>
-      <c r="M40" t="n">
-        <v>0</v>
-      </c>
-      <c r="N40" t="n">
-        <v>0</v>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="P40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="n">
-        <v>39</v>
-      </c>
-      <c r="B41" t="inlineStr">
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2046106598221746656</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>2046106598221746656</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>2046106592114856006</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2046106592114856006</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>الاستثمار ليس معقداً، بل يحتاج إلى تخطيط ذكي.
 مع منصة الثروات الرقمية من الإمارات الإسلامي، يمكنك البدء بثقة عبر تجربة رقمية سلسة ومتوافقة مع الشريعة الإسلامية، صُممت لمساعدتك على:
 ✔️ الوصول إلى مجموعة واسعة من خيارات الاستثمار المتوافقة مع الشريعة الإسلامية</t>
         </is>
       </c>
-      <c r="G41" t="n">
+      <c r="G43" t="n">
         <v>1776664801000</v>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>2046106592114856006</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
-      <c r="K41" t="n">
+      <c r="K43" t="n">
         <v>1</v>
       </c>
-      <c r="L41" t="n">
-        <v>0</v>
-      </c>
-      <c r="M41" t="n">
-        <v>0</v>
-      </c>
-      <c r="N41" t="n">
-        <v>0</v>
-      </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="P41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="n">
-        <v>40</v>
-      </c>
-      <c r="B42" t="inlineStr">
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2046106598221746656</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>2046106598221746656</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>2046106595369615672</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2046106595369615672</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>✔️ متابعة استثماراتك لحظة بلحظة
 ✔️ الحصول على إرشادات ذكية لدعم قراراتك المالية
@@ -3321,143 +3457,143 @@
 https://t.co/PgcKVmrsKA</t>
         </is>
       </c>
-      <c r="G42" t="n">
+      <c r="G44" t="n">
         <v>1776664801000</v>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>2046106592114856006</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
-      <c r="K42" t="n">
+      <c r="K44" t="n">
         <v>1</v>
       </c>
-      <c r="L42" t="n">
-        <v>0</v>
-      </c>
-      <c r="M42" t="n">
-        <v>0</v>
-      </c>
-      <c r="N42" t="n">
-        <v>0</v>
-      </c>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="P42" t="inlineStr">
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
         <is>
           <t>2046106592114856006</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="1" t="n">
-        <v>41</v>
-      </c>
-      <c r="B43" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="1" t="n">
+        <v>43</v>
+      </c>
+      <c r="B45" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2046106598221746656</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>2046106598221746656</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>2046106598221746656</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2046106598221746656</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>Investing doesn’t have to be complicated. It just has to be well-planned. With Emirates Islamic Digital Wealth, start investing confidently through a seamless, Shariah-compliant digital experience designed to help you:
 ✔️ Access a range of Shariah-compliant investment options</t>
         </is>
       </c>
-      <c r="G43" t="n">
+      <c r="G45" t="n">
         <v>1776664802000</v>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>2046106592114856006</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
-      <c r="K43" t="n">
+      <c r="K45" t="n">
         <v>1</v>
       </c>
-      <c r="L43" t="n">
-        <v>0</v>
-      </c>
-      <c r="M43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N43" t="n">
-        <v>0</v>
-      </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="P43" t="inlineStr">
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
         <is>
           <t>2046106595369615672</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="1" t="n">
-        <v>42</v>
-      </c>
-      <c r="B44" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="1" t="n">
+        <v>44</v>
+      </c>
+      <c r="B46" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2046106598221746656</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>2046106598221746656</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>2046106600142725209</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2046106600142725209</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>✔️ Track your investments in real time
 ✔️ Get smart insights to guide your decisions
@@ -3467,72 +3603,72 @@
 https://t.co/BZed26iXDD</t>
         </is>
       </c>
-      <c r="G44" t="n">
+      <c r="G46" t="n">
         <v>1776664802000</v>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>2046106592114856006</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
-      <c r="K44" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" t="n">
-        <v>0</v>
-      </c>
-      <c r="M44" t="n">
-        <v>0</v>
-      </c>
-      <c r="N44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="P44" t="inlineStr">
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
         <is>
           <t>2046106598221746656</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="1" t="n">
-        <v>43</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2046215315273486655</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>2046215315273486655</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="1" t="n">
+        <v>45</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046215312949879234</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
         <is>
           <t>2046215312949879234</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2046215312949879234</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2046215312949879234</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>Exclusively for Emaratis. Apply for an Emarati Credit Card &amp;amp; get a welcome bonus of up to 150,000 EI SmartMiles worth AED 1,500
 ✅ No annual membership fee
@@ -3540,68 +3676,68 @@
 🍔 50% discount on talabat https://t.co/pIT39d8ym8</t>
         </is>
       </c>
-      <c r="G45" t="n">
+      <c r="G47" t="n">
         <v>1776690722000</v>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>2046215312949879234</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGWd-66WYAAChSk.jpg', 'type': 'photo', 'id': '2046215310001201152'}]</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
-      <c r="K45" t="n">
+      <c r="K47" t="n">
         <v>2</v>
       </c>
-      <c r="L45" t="n">
-        <v>0</v>
-      </c>
-      <c r="M45" t="n">
-        <v>0</v>
-      </c>
-      <c r="N45" t="n">
-        <v>0</v>
-      </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="P45" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="1" t="n">
-        <v>44</v>
-      </c>
-      <c r="B46" t="inlineStr">
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="n">
+        <v>46</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046215312949879234</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2046215312949879234</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2046215315273486655</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2046215315273486655</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>2046215315273486655</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>2046215315273486655</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2046215315273486655</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>🚗 Complimentary valet parking
 ✈️ Complimentary airport lounge access
@@ -3611,72 +3747,72 @@
 https://t.co/Rcpj14D3rn</t>
         </is>
       </c>
-      <c r="G46" t="n">
+      <c r="G48" t="n">
         <v>1776690722000</v>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>2046215312949879234</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
-      <c r="K46" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" t="n">
-        <v>0</v>
-      </c>
-      <c r="M46" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" t="n">
-        <v>0</v>
-      </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="P46" t="inlineStr">
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
         <is>
           <t>2046215312949879234</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="1" t="n">
-        <v>45</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2046215063929749703</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>2046215063929749703</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="1" t="n">
+        <v>47</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046215312949879234</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>2046215312949879234</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
         <is>
           <t>2046215061186683019</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2046215061186683019</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>حصرياً للإماراتيين. تقدم بطلب بطاقة إماراتي الائتمانية واحصل على مكافأة ترحيبية تصل الى 150,000 ميل من أميال سمارت مايلز بقيمة 1,500 درهم
 ✅ بدون رسوم عضوية سنوية
@@ -3684,68 +3820,281 @@
 🍔 خصم لغاية %50 على طلبات https://t.co/X996FmddPk</t>
         </is>
       </c>
-      <c r="G47" t="n">
+      <c r="G49" t="n">
         <v>1776690662000</v>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>2046215061186683019</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGWdwRrWMAARNF5.jpg', 'type': 'photo', 'id': '2046215058414252032'}]</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
-      <c r="K47" t="n">
+      <c r="K49" t="n">
         <v>1</v>
       </c>
-      <c r="L47" t="n">
-        <v>0</v>
-      </c>
-      <c r="M47" t="n">
-        <v>0</v>
-      </c>
-      <c r="N47" t="n">
-        <v>0</v>
-      </c>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="P47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="1" t="n">
-        <v>46</v>
-      </c>
-      <c r="B48" t="inlineStr">
+      <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="n">
+        <v>48</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046215315273486655</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>2046215315273486655</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2046215312949879234</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046215312949879234</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Exclusively for Emaratis. Apply for an Emarati Credit Card &amp;amp; get a welcome bonus of up to 150,000 EI SmartMiles worth AED 1,500
+✅ No annual membership fee
+📈 Earn up to 3.75 EI SmartMiles back per AED spend
+🍔 50% discount on talabat https://t.co/pIT39d8ym8</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>1776690722000</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>2046215312949879234</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGWd-66WYAAChSk.jpg', 'type': 'photo', 'id': '2046215310001201152'}]</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="K50" t="n">
+        <v>2</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="n">
+        <v>49</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046215315273486655</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2046215315273486655</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2046215315273486655</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046215315273486655</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>🚗 Complimentary valet parking
+✈️ Complimentary airport lounge access
+💳 Metal Card with unique design
+And much more!
+📅 Offer valid till 31 May 2026
+https://t.co/Rcpj14D3rn</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>1776690722000</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>2046215312949879234</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>2046215312949879234</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046215061186683019</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>2046215061186683019</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2046215061186683019</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046215061186683019</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>حصرياً للإماراتيين. تقدم بطلب بطاقة إماراتي الائتمانية واحصل على مكافأة ترحيبية تصل الى 150,000 ميل من أميال سمارت مايلز بقيمة 1,500 درهم
+✅ بدون رسوم عضوية سنوية
+📈استرداد لغاية 3.75 ميل من أميال سمارت مايلز مقابل كل درهم إماراتي تنفقه
+🍔 خصم لغاية %50 على طلبات https://t.co/X996FmddPk</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>1776690662000</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>2046215061186683019</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGWdwRrWMAARNF5.jpg', 'type': 'photo', 'id': '2046215058414252032'}]</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="K52" t="n">
+        <v>1</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="n">
+        <v>51</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046215061186683019</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2046215061186683019</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2046215063929749703</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2046215063929749703</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>2046215063929749703</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>2046215063929749703</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2046215063929749703</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>🚗 خدمة صف السيارات
 🛫 الدخول إلى صالات المطارات
@@ -3755,72 +4104,72 @@
 https://t.co/WJhVBxsiSW</t>
         </is>
       </c>
-      <c r="G48" t="n">
+      <c r="G53" t="n">
         <v>1776690662000</v>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="H53" t="inlineStr">
         <is>
           <t>2046215061186683019</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
+      <c r="J53" t="inlineStr">
         <is>
           <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
-      <c r="K48" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" t="n">
-        <v>0</v>
-      </c>
-      <c r="M48" t="n">
-        <v>0</v>
-      </c>
-      <c r="N48" t="n">
-        <v>0</v>
-      </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="P48" t="inlineStr">
+      <c r="K53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
         <is>
           <t>2046215061186683019</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="1" t="n">
-        <v>47</v>
-      </c>
-      <c r="B49" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="1" t="n">
+        <v>52</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046215061186683019</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2046215061186683019</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2046215312949879234</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2046215312949879234</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>2046215312949879234</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>2046215312949879234</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2046215312949879234</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>Exclusively for Emaratis. Apply for an Emarati Credit Card &amp;amp; get a welcome bonus of up to 150,000 EI SmartMiles worth AED 1,500
 ✅ No annual membership fee
@@ -3828,212 +4177,68 @@
 🍔 50% discount on talabat https://t.co/pIT39d8ym8</t>
         </is>
       </c>
-      <c r="G49" t="n">
+      <c r="G54" t="n">
         <v>1776690722000</v>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="H54" t="inlineStr">
         <is>
           <t>2046215312949879234</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="I54" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGWd-66WYAAChSk.jpg', 'type': 'photo', 'id': '2046215310001201152'}]</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="J54" t="inlineStr">
         <is>
           <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
-      <c r="K49" t="n">
+      <c r="K54" t="n">
         <v>2</v>
       </c>
-      <c r="L49" t="n">
-        <v>0</v>
-      </c>
-      <c r="M49" t="n">
-        <v>0</v>
-      </c>
-      <c r="N49" t="n">
-        <v>0</v>
-      </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="P49" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="1" t="n">
-        <v>48</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2046215312949879234</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>2046215312949879234</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>2046215315273486655</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2046215315273486655</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>🚗 Complimentary valet parking
-✈️ Complimentary airport lounge access
-💳 Metal Card with unique design
-And much more!
-📅 Offer valid till 31 May 2026
-https://t.co/Rcpj14D3rn</t>
-        </is>
-      </c>
-      <c r="G50" t="n">
-        <v>1776690722000</v>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>2046215312949879234</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="K50" t="n">
-        <v>0</v>
-      </c>
-      <c r="L50" t="n">
-        <v>0</v>
-      </c>
-      <c r="M50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N50" t="n">
-        <v>0</v>
-      </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>2046215312949879234</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="1" t="n">
-        <v>49</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2046215312949879234</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>2046215312949879234</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>2046215061186683019</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2046215061186683019</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>حصرياً للإماراتيين. تقدم بطلب بطاقة إماراتي الائتمانية واحصل على مكافأة ترحيبية تصل الى 150,000 ميل من أميال سمارت مايلز بقيمة 1,500 درهم
-✅ بدون رسوم عضوية سنوية
-📈استرداد لغاية 3.75 ميل من أميال سمارت مايلز مقابل كل درهم إماراتي تنفقه
-🍔 خصم لغاية %50 على طلبات https://t.co/X996FmddPk</t>
-        </is>
-      </c>
-      <c r="G51" t="n">
-        <v>1776690662000</v>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>2046215061186683019</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGWdwRrWMAARNF5.jpg', 'type': 'photo', 'id': '2046215058414252032'}]</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="K51" t="n">
-        <v>1</v>
-      </c>
-      <c r="L51" t="n">
-        <v>0</v>
-      </c>
-      <c r="M51" t="n">
-        <v>0</v>
-      </c>
-      <c r="N51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="P51" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="B52" t="inlineStr">
+      <c r="L54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="n">
+        <v>53</v>
+      </c>
+      <c r="B55" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2046200685037830312</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>2046200685037830312</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>2044702429464441285</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>https://x.com/alsajwani1/status/2044702429464441285</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>@emiratesislamic 
 السلام عليكم
@@ -4044,138 +4249,138 @@
 او عدم هو اهتمام بالعملاء</t>
         </is>
       </c>
-      <c r="G52" t="n">
+      <c r="G55" t="n">
         <v>1776330022000</v>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="H55" t="inlineStr">
         <is>
           <t>2044702429464441285</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
+      <c r="I55" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
+      <c r="J55" t="inlineStr">
         <is>
           <t>{'name': 'عبدالصاحب السجواني', 'screenName': 'alsajwani1', 'followersCount': 622, 'favouritesCount': 55, 'friendsCount': 2015, 'description': '\u200fمدرب ومستشار ريادة الأعمال  trainer and adviser Entrepreneurs'}</t>
         </is>
       </c>
-      <c r="K52" t="n">
+      <c r="K55" t="n">
         <v>1</v>
       </c>
-      <c r="L52" t="n">
-        <v>0</v>
-      </c>
-      <c r="M52" t="n">
-        <v>0</v>
-      </c>
-      <c r="N52" t="n">
-        <v>0</v>
-      </c>
-      <c r="O52" t="inlineStr">
+      <c r="L55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="P52" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="1" t="n">
-        <v>51</v>
-      </c>
-      <c r="B53" t="inlineStr">
+      <c r="P55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="n">
+        <v>54</v>
+      </c>
+      <c r="B56" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2046200685037830312</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>2046200685037830312</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>2044734739718824109</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="E56" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2044734739718824109</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>@alsajwani1 مرحبا ، يأسفنا سماع تجربتك! فريقنا ملتزم بمعالجة هذا الأمر على الفور. لحماية خصوصيتك ، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل. رضاك أولويتنا.</t>
         </is>
       </c>
-      <c r="G53" t="n">
+      <c r="G56" t="n">
         <v>1776337725000</v>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="H56" t="inlineStr">
         <is>
           <t>2044702429464441285</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="J56" t="inlineStr">
         <is>
           <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
-      <c r="K53" t="n">
+      <c r="K56" t="n">
         <v>1</v>
       </c>
-      <c r="L53" t="n">
-        <v>0</v>
-      </c>
-      <c r="M53" t="n">
-        <v>0</v>
-      </c>
-      <c r="N53" t="n">
-        <v>0</v>
-      </c>
-      <c r="O53" t="inlineStr">
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="P53" t="inlineStr">
+      <c r="P56" t="inlineStr">
         <is>
           <t>2044702429464441285</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="1" t="n">
-        <v>52</v>
-      </c>
-      <c r="B54" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="B57" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2046200685037830312</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>2046200685037830312</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>2045014720416186802</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>https://x.com/alsajwani1/status/2045014720416186802</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>@emiratesislamic تم امس التواصل معي من عندكم
 سألني عن تاريخ الميلاد
@@ -4189,143 +4394,143 @@
 في انتظار الحل!!!</t>
         </is>
       </c>
-      <c r="G54" t="n">
+      <c r="G57" t="n">
         <v>1776404478000</v>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="H57" t="inlineStr">
         <is>
           <t>2044702429464441285</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
+      <c r="J57" t="inlineStr">
         <is>
           <t>{'name': 'عبدالصاحب السجواني', 'screenName': 'alsajwani1', 'followersCount': 622, 'favouritesCount': 55, 'friendsCount': 2015, 'description': '\u200fمدرب ومستشار ريادة الأعمال  trainer and adviser Entrepreneurs'}</t>
         </is>
       </c>
-      <c r="K54" t="n">
+      <c r="K57" t="n">
         <v>1</v>
       </c>
-      <c r="L54" t="n">
-        <v>0</v>
-      </c>
-      <c r="M54" t="n">
-        <v>0</v>
-      </c>
-      <c r="N54" t="n">
-        <v>0</v>
-      </c>
-      <c r="O54" t="inlineStr">
+      <c r="L57" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="P54" t="inlineStr">
+      <c r="P57" t="inlineStr">
         <is>
           <t>2044734739718824109</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="1" t="n">
-        <v>53</v>
-      </c>
-      <c r="B55" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="1" t="n">
+        <v>56</v>
+      </c>
+      <c r="B58" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2046200685037830312</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>2046200685037830312</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>2045035981535912006</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2045035981535912006</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>@alsajwani1 مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
 رسالتك الخاصه.</t>
         </is>
       </c>
-      <c r="G55" t="n">
+      <c r="G58" t="n">
         <v>1776409547000</v>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="H58" t="inlineStr">
         <is>
           <t>2044702429464441285</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
+      <c r="I58" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
+      <c r="J58" t="inlineStr">
         <is>
           <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
-      <c r="K55" t="n">
+      <c r="K58" t="n">
         <v>1</v>
       </c>
-      <c r="L55" t="n">
-        <v>0</v>
-      </c>
-      <c r="M55" t="n">
-        <v>0</v>
-      </c>
-      <c r="N55" t="n">
-        <v>0</v>
-      </c>
-      <c r="O55" t="inlineStr">
+      <c r="L58" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="P55" t="inlineStr">
+      <c r="P58" t="inlineStr">
         <is>
           <t>2045014720416186802</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="1" t="n">
-        <v>54</v>
-      </c>
-      <c r="B56" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="1" t="n">
+        <v>57</v>
+      </c>
+      <c r="B59" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2046200685037830312</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>2046200685037830312</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>2045418169452695808</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>https://x.com/alsajwani1/status/2045418169452695808</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>@emiratesislamic ولكن إلى اليوم لم يتم إنهاء الإجراء 
 مع الأسف لايوجد متابعة لطلب من الفرع
@@ -4335,257 +4540,44 @@
 متى ستنتهي المأساة؟ https://t.co/rFW4GdBPlY</t>
         </is>
       </c>
-      <c r="G56" t="n">
+      <c r="G59" t="n">
         <v>1776500668000</v>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="H59" t="inlineStr">
         <is>
           <t>2044702429464441285</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGLI-x3aUAA7Qsp.jpg', 'type': 'photo', 'id': '2045418161642819584'}]</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
+      <c r="J59" t="inlineStr">
         <is>
           <t>{'name': 'عبدالصاحب السجواني', 'screenName': 'alsajwani1', 'followersCount': 622, 'favouritesCount': 55, 'friendsCount': 2015, 'description': '\u200fمدرب ومستشار ريادة الأعمال  trainer and adviser Entrepreneurs'}</t>
         </is>
       </c>
-      <c r="K56" t="n">
+      <c r="K59" t="n">
         <v>1</v>
       </c>
-      <c r="L56" t="n">
-        <v>0</v>
-      </c>
-      <c r="M56" t="n">
-        <v>0</v>
-      </c>
-      <c r="N56" t="n">
-        <v>0</v>
-      </c>
-      <c r="O56" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="P56" t="inlineStr">
+      <c r="L59" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
         <is>
           <t>2045035981535912006</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="1" t="n">
-        <v>55</v>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2046200685037830312</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>2046200685037830312</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>2046133214998114511</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2046133214998114511</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>@alsajwani1 مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
-رسالتك الخاصه.</t>
-        </is>
-      </c>
-      <c r="G57" t="n">
-        <v>1776671148000</v>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>2044702429464441285</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="K57" t="n">
-        <v>2</v>
-      </c>
-      <c r="L57" t="n">
-        <v>0</v>
-      </c>
-      <c r="M57" t="n">
-        <v>0</v>
-      </c>
-      <c r="N57" t="n">
-        <v>0</v>
-      </c>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>2045418169452695808</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="1" t="n">
-        <v>56</v>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2046200685037830312</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>2046200685037830312</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>2046181231432495104</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>https://x.com/alsajwani1/status/2046181231432495104</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>@emiratesislamic ردكم لم يحرك ساكن 
- إنجاز المعاملة إلى اليوم صفر</t>
-        </is>
-      </c>
-      <c r="G58" t="n">
-        <v>1776682596000</v>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>2044702429464441285</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>{'name': 'عبدالصاحب السجواني', 'screenName': 'alsajwani1', 'followersCount': 622, 'favouritesCount': 55, 'friendsCount': 2015, 'description': '\u200fمدرب ومستشار ريادة الأعمال  trainer and adviser Entrepreneurs'}</t>
-        </is>
-      </c>
-      <c r="K58" t="n">
-        <v>1</v>
-      </c>
-      <c r="L58" t="n">
-        <v>0</v>
-      </c>
-      <c r="M58" t="n">
-        <v>0</v>
-      </c>
-      <c r="N58" t="n">
-        <v>0</v>
-      </c>
-      <c r="O58" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>2046133214998114511</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="1" t="n">
-        <v>57</v>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2046200685037830312</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>2046200685037830312</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>2046200685037830312</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2046200685037830312</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>@alsajwani1 مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
-رسالتك الخاصه.</t>
-        </is>
-      </c>
-      <c r="G59" t="n">
-        <v>1776687234000</v>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>2044702429464441285</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="K59" t="n">
-        <v>0</v>
-      </c>
-      <c r="L59" t="n">
-        <v>0</v>
-      </c>
-      <c r="M59" t="n">
-        <v>0</v>
-      </c>
-      <c r="N59" t="n">
-        <v>0</v>
-      </c>
-      <c r="O59" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>2046181231432495104</t>
         </is>
       </c>
     </row>
@@ -4595,43 +4587,41 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2046215061186683019</t>
+          <t>https://x.com/emiratesislamic/status/2046200685037830312</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2046215061186683019</t>
+          <t>2046200685037830312</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2046215061186683019</t>
+          <t>2046133214998114511</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2046215061186683019</t>
+          <t>https://x.com/emiratesislamic/status/2046133214998114511</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>حصرياً للإماراتيين. تقدم بطلب بطاقة إماراتي الائتمانية واحصل على مكافأة ترحيبية تصل الى 150,000 ميل من أميال سمارت مايلز بقيمة 1,500 درهم
-✅ بدون رسوم عضوية سنوية
-📈استرداد لغاية 3.75 ميل من أميال سمارت مايلز مقابل كل درهم إماراتي تنفقه
-🍔 خصم لغاية %50 على طلبات https://t.co/X996FmddPk</t>
+          <t>@alsajwani1 مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
+رسالتك الخاصه.</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>1776690662000</v>
+        <v>1776671148000</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2046215061186683019</t>
+          <t>2044702429464441285</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGWdwRrWMAARNF5.jpg', 'type': 'photo', 'id': '2046215058414252032'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -4640,7 +4630,7 @@
         </is>
       </c>
       <c r="K60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
@@ -4653,10 +4643,14 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="P60" t="inlineStr"/>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>2045418169452695808</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
@@ -4664,40 +4658,36 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2046215061186683019</t>
+          <t>https://x.com/emiratesislamic/status/2046200685037830312</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2046215061186683019</t>
+          <t>2046200685037830312</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2046215063929749703</t>
+          <t>2046181231432495104</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2046215063929749703</t>
+          <t>https://x.com/alsajwani1/status/2046181231432495104</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>🚗 خدمة صف السيارات
-🛫 الدخول إلى صالات المطارات
-💳 بطاقة معدنية بتصميم فريد
-وغير ذلك الكثير
-📅 يسري العرض لغاية 31 مايو 2026
-https://t.co/WJhVBxsiSW</t>
+          <t>@emiratesislamic ردكم لم يحرك ساكن 
+ إنجاز المعاملة إلى اليوم صفر</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>1776690662000</v>
+        <v>1776682596000</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2046215061186683019</t>
+          <t>2044702429464441285</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4707,11 +4697,11 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+          <t>{'name': 'عبدالصاحب السجواني', 'screenName': 'alsajwani1', 'followersCount': 622, 'favouritesCount': 55, 'friendsCount': 2015, 'description': '\u200fمدرب ومستشار ريادة الأعمال  trainer and adviser Entrepreneurs'}</t>
         </is>
       </c>
       <c r="K61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
@@ -4724,12 +4714,12 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>2046215061186683019</t>
+          <t>2046133214998114511</t>
         </is>
       </c>
     </row>
@@ -4739,43 +4729,41 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2046215061186683019</t>
+          <t>https://x.com/emiratesislamic/status/2046200685037830312</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2046215061186683019</t>
+          <t>2046200685037830312</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2046215312949879234</t>
+          <t>2046200685037830312</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2046215312949879234</t>
+          <t>https://x.com/emiratesislamic/status/2046200685037830312</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Exclusively for Emaratis. Apply for an Emarati Credit Card &amp;amp; get a welcome bonus of up to 150,000 EI SmartMiles worth AED 1,500
-✅ No annual membership fee
-📈 Earn up to 3.75 EI SmartMiles back per AED spend
-🍔 50% discount on talabat https://t.co/pIT39d8ym8</t>
+          <t>@alsajwani1 مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
+رسالتك الخاصه.</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>1776690722000</v>
+        <v>1776687234000</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2046215312949879234</t>
+          <t>2044702429464441285</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGWd-66WYAAChSk.jpg', 'type': 'photo', 'id': '2046215310001201152'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -4784,7 +4772,7 @@
         </is>
       </c>
       <c r="K62" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
@@ -4797,10 +4785,14 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="P62" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>2046181231432495104</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
@@ -4808,185 +4800,184 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
+          <t>https://x.com/emiratesislamic/status/2046164985571598514</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>2046164985571598514</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2045771180469272971</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>https://x.com/firstdiver4ever/status/2045771180469272971</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>@emiratesislamic أتقدم لجميع العاملين في مصرف الإمارات الإسلامي بجزيل الشكر والتقدير على جهودهم وعملهم الدؤوب الذي قاموا به ، حيث تم مشكلتي في زمن قياسي بالوقت الذي كان من المفروض ان يتم انجازه خلال سبعة ايام عمل .
+شكرا من القلب مرة اخرى .</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>1776584832000</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>2045771180469272971</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>{'name': 'اماراتى وافتخر', 'screenName': 'firstdiver4ever', 'followersCount': 934, 'favouritesCount': 4615, 'friendsCount': 1841, 'description': 'الله ثم الوطن ثم رئيس الدوله'}</t>
+        </is>
+      </c>
+      <c r="K63" t="n">
+        <v>1</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="n">
+        <v>62</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046164985571598514</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>2046164985571598514</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2046164985571598514</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046164985571598514</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>@firstdiver4ever عزيزنا المتعامل، يسرنا أن نعرب لك عن جزيل شكرنا لهذه الكلمات الطيبة. كما أننا نقدر الوقت والجهد الذي بذلته لارسال هذا التقدير.</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
+        <v>1776678723000</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>2045771180469272971</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="K64" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" t="n">
+        <v>0</v>
+      </c>
+      <c r="N64" t="n">
+        <v>0</v>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>2045771180469272971</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="n">
+        <v>63</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
           <t>https://x.com/emiratesislamic/status/2046200603928338537</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C65" t="inlineStr">
         <is>
           <t>2046200603928338537</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="D65" t="inlineStr">
         <is>
           <t>2046139112361717905</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="E65" t="inlineStr">
         <is>
           <t>https://x.com/alsajwani1/status/2046139112361717905</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="F65" t="inlineStr">
         <is>
           <t>@emiratesislamic 
 منذ أسبوع قدمت على طلب كسر الوديعة وتسديد قيمة القرض  من الوديعة فرعكم في 06 مول في الشارقة ومن أسبوع وموظفين الفرع لا علم لهم بالإجراء ويتواصلون عبر الإميل مع الإدارة لمعرفة الخطوات والإدارة لاحياة لمن تنادي
 هل تتوقعون من هذه الخدمة تدخلون في حلبة المنافسة</t>
         </is>
       </c>
-      <c r="G63" t="n">
+      <c r="G65" t="n">
         <v>1776672554000</v>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="H65" t="inlineStr">
         <is>
           <t>2046139112361717905</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr">
+      <c r="J65" t="inlineStr">
         <is>
           <t>{'name': 'عبدالصاحب السجواني', 'screenName': 'alsajwani1', 'followersCount': 622, 'favouritesCount': 55, 'friendsCount': 2015, 'description': '\u200fمدرب ومستشار ريادة الأعمال  trainer and adviser Entrepreneurs'}</t>
-        </is>
-      </c>
-      <c r="K63" t="n">
-        <v>1</v>
-      </c>
-      <c r="L63" t="n">
-        <v>0</v>
-      </c>
-      <c r="M63" t="n">
-        <v>0</v>
-      </c>
-      <c r="N63" t="n">
-        <v>0</v>
-      </c>
-      <c r="O63" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="P63" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="1" t="n">
-        <v>62</v>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2046200603928338537</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>2046200603928338537</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>2046200603928338537</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2046200603928338537</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>@alsajwani1 مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
-رسالتك الخاصه.</t>
-        </is>
-      </c>
-      <c r="G64" t="n">
-        <v>1776687215000</v>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>2046139112361717905</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="K64" t="n">
-        <v>0</v>
-      </c>
-      <c r="L64" t="n">
-        <v>0</v>
-      </c>
-      <c r="M64" t="n">
-        <v>0</v>
-      </c>
-      <c r="N64" t="n">
-        <v>0</v>
-      </c>
-      <c r="O64" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="P64" t="inlineStr">
-        <is>
-          <t>2046139112361717905</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="1" t="n">
-        <v>63</v>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2046164985571598514</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>2046164985571598514</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>2045771180469272971</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>https://x.com/firstdiver4ever/status/2045771180469272971</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>@emiratesislamic أتقدم لجميع العاملين في مصرف الإمارات الإسلامي بجزيل الشكر والتقدير على جهودهم وعملهم الدؤوب الذي قاموا به ، حيث تم مشكلتي في زمن قياسي بالوقت الذي كان من المفروض ان يتم انجازه خلال سبعة ايام عمل .
-شكرا من القلب مرة اخرى .</t>
-        </is>
-      </c>
-      <c r="G65" t="n">
-        <v>1776584832000</v>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>2045771180469272971</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>{'name': 'اماراتى وافتخر', 'screenName': 'firstdiver4ever', 'followersCount': 934, 'favouritesCount': 4614, 'friendsCount': 1841, 'description': 'الله ثم الوطن ثم رئيس الدوله'}</t>
         </is>
       </c>
       <c r="K65" t="n">
@@ -5003,7 +4994,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>23</t>
         </is>
       </c>
       <c r="P65" t="inlineStr"/>
@@ -5014,35 +5005,36 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2046164985571598514</t>
+          <t>https://x.com/emiratesislamic/status/2046200603928338537</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2046164985571598514</t>
+          <t>2046200603928338537</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2046164985571598514</t>
+          <t>2046200603928338537</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2046164985571598514</t>
+          <t>https://x.com/emiratesislamic/status/2046200603928338537</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>@firstdiver4ever عزيزنا المتعامل، يسرنا أن نعرب لك عن جزيل شكرنا لهذه الكلمات الطيبة. كما أننا نقدر الوقت والجهد الذي بذلته لارسال هذا التقدير.</t>
+          <t>@alsajwani1 مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
+رسالتك الخاصه.</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>1776678723000</v>
+        <v>1776687215000</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2045771180469272971</t>
+          <t>2046139112361717905</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -5069,12 +5061,12 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>2045771180469272971</t>
+          <t>2046139112361717905</t>
         </is>
       </c>
     </row>
@@ -5436,7 +5428,7 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -5507,7 +5499,7 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -5577,7 +5569,7 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -5648,7 +5640,7 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
@@ -5663,232 +5655,25 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2046148156560121974</t>
+          <t>https://x.com/emiratesislamic/status/2046133214998114511</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2046148156560121974</t>
+          <t>2046133214998114511</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2046148156560121974</t>
+          <t>2044702429464441285</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2046148156560121974</t>
+          <t>https://x.com/alsajwani1/status/2044702429464441285</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
-        <is>
-          <t>امنح أبنائك انطلاقة مبكرة نحو الوعي المالي الذكي
- #الإمارات_الإسلامي https://t.co/xdFKEhpKDT</t>
-        </is>
-      </c>
-      <c r="G75" t="n">
-        <v>1776674710000</v>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>2046148156560121974</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/ext_tw_video_thumb/2046148122250809344/pu/img/WEGHCsaWoyjDb-ot.jpg', 'type': 'video', 'id': '2046148122250809344'}]</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="K75" t="n">
-        <v>1</v>
-      </c>
-      <c r="L75" t="n">
-        <v>0</v>
-      </c>
-      <c r="M75" t="n">
-        <v>0</v>
-      </c>
-      <c r="N75" t="n">
-        <v>0</v>
-      </c>
-      <c r="O75" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="P75" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="1" t="n">
-        <v>74</v>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2046148156560121974</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>2046148156560121974</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>2046148194392740002</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2046148194392740002</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>Your child's smart money journey starts here. Empower your kids to take their first steps toward financial independence. 
-#EmiratesIslamic #AlphaYouth https://t.co/udWgfz8rNb</t>
-        </is>
-      </c>
-      <c r="G76" t="n">
-        <v>1776674719000</v>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>2046148156560121974</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/ext_tw_video_thumb/2046148161090068480/pu/img/GpPJv5a4DR5wZAQc.jpg', 'type': 'video', 'id': '2046148161090068480'}]</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="K76" t="n">
-        <v>0</v>
-      </c>
-      <c r="L76" t="n">
-        <v>0</v>
-      </c>
-      <c r="M76" t="n">
-        <v>0</v>
-      </c>
-      <c r="N76" t="n">
-        <v>0</v>
-      </c>
-      <c r="O76" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="P76" t="inlineStr">
-        <is>
-          <t>2046148156560121974</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="1" t="n">
-        <v>75</v>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2046148156560121974</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>2046148156560121974</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>2046215312949879234</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2046215312949879234</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>Exclusively for Emaratis. Apply for an Emarati Credit Card &amp;amp; get a welcome bonus of up to 150,000 EI SmartMiles worth AED 1,500
-✅ No annual membership fee
-📈 Earn up to 3.75 EI SmartMiles back per AED spend
-🍔 50% discount on talabat https://t.co/pIT39d8ym8</t>
-        </is>
-      </c>
-      <c r="G77" t="n">
-        <v>1776690722000</v>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>2046215312949879234</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGWd-66WYAAChSk.jpg', 'type': 'photo', 'id': '2046215310001201152'}]</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="K77" t="n">
-        <v>2</v>
-      </c>
-      <c r="L77" t="n">
-        <v>0</v>
-      </c>
-      <c r="M77" t="n">
-        <v>0</v>
-      </c>
-      <c r="N77" t="n">
-        <v>0</v>
-      </c>
-      <c r="O77" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="P77" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="1" t="n">
-        <v>76</v>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2046133214998114511</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>2046133214998114511</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>2044702429464441285</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>https://x.com/alsajwani1/status/2044702429464441285</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
         <is>
           <t>@emiratesislamic 
 السلام عليكم
@@ -5899,138 +5684,138 @@
 او عدم هو اهتمام بالعملاء</t>
         </is>
       </c>
-      <c r="G78" t="n">
+      <c r="G75" t="n">
         <v>1776330022000</v>
       </c>
-      <c r="H78" t="inlineStr">
+      <c r="H75" t="inlineStr">
         <is>
           <t>2044702429464441285</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
+      <c r="I75" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="J78" t="inlineStr">
+      <c r="J75" t="inlineStr">
         <is>
           <t>{'name': 'عبدالصاحب السجواني', 'screenName': 'alsajwani1', 'followersCount': 622, 'favouritesCount': 55, 'friendsCount': 2015, 'description': '\u200fمدرب ومستشار ريادة الأعمال  trainer and adviser Entrepreneurs'}</t>
         </is>
       </c>
-      <c r="K78" t="n">
+      <c r="K75" t="n">
         <v>1</v>
       </c>
-      <c r="L78" t="n">
-        <v>0</v>
-      </c>
-      <c r="M78" t="n">
-        <v>0</v>
-      </c>
-      <c r="N78" t="n">
-        <v>0</v>
-      </c>
-      <c r="O78" t="inlineStr">
+      <c r="L75" t="n">
+        <v>0</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0</v>
+      </c>
+      <c r="N75" t="n">
+        <v>0</v>
+      </c>
+      <c r="O75" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="P78" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="1" t="n">
-        <v>77</v>
-      </c>
-      <c r="B79" t="inlineStr">
+      <c r="P75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="n">
+        <v>74</v>
+      </c>
+      <c r="B76" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2046133214998114511</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="C76" t="inlineStr">
         <is>
           <t>2046133214998114511</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
+      <c r="D76" t="inlineStr">
         <is>
           <t>2044734739718824109</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="E76" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2044734739718824109</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
+      <c r="F76" t="inlineStr">
         <is>
           <t>@alsajwani1 مرحبا ، يأسفنا سماع تجربتك! فريقنا ملتزم بمعالجة هذا الأمر على الفور. لحماية خصوصيتك ، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل. رضاك أولويتنا.</t>
         </is>
       </c>
-      <c r="G79" t="n">
+      <c r="G76" t="n">
         <v>1776337725000</v>
       </c>
-      <c r="H79" t="inlineStr">
+      <c r="H76" t="inlineStr">
         <is>
           <t>2044702429464441285</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
+      <c r="I76" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="J79" t="inlineStr">
+      <c r="J76" t="inlineStr">
         <is>
           <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
-      <c r="K79" t="n">
+      <c r="K76" t="n">
         <v>1</v>
       </c>
-      <c r="L79" t="n">
-        <v>0</v>
-      </c>
-      <c r="M79" t="n">
-        <v>0</v>
-      </c>
-      <c r="N79" t="n">
-        <v>0</v>
-      </c>
-      <c r="O79" t="inlineStr">
+      <c r="L76" t="n">
+        <v>0</v>
+      </c>
+      <c r="M76" t="n">
+        <v>0</v>
+      </c>
+      <c r="N76" t="n">
+        <v>0</v>
+      </c>
+      <c r="O76" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="P79" t="inlineStr">
+      <c r="P76" t="inlineStr">
         <is>
           <t>2044702429464441285</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="1" t="n">
-        <v>78</v>
-      </c>
-      <c r="B80" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="1" t="n">
+        <v>75</v>
+      </c>
+      <c r="B77" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2046133214998114511</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
+      <c r="C77" t="inlineStr">
         <is>
           <t>2046133214998114511</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
+      <c r="D77" t="inlineStr">
         <is>
           <t>2045014720416186802</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="E77" t="inlineStr">
         <is>
           <t>https://x.com/alsajwani1/status/2045014720416186802</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
+      <c r="F77" t="inlineStr">
         <is>
           <t>@emiratesislamic تم امس التواصل معي من عندكم
 سألني عن تاريخ الميلاد
@@ -6044,143 +5829,143 @@
 في انتظار الحل!!!</t>
         </is>
       </c>
-      <c r="G80" t="n">
+      <c r="G77" t="n">
         <v>1776404478000</v>
       </c>
-      <c r="H80" t="inlineStr">
+      <c r="H77" t="inlineStr">
         <is>
           <t>2044702429464441285</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
+      <c r="I77" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="J80" t="inlineStr">
+      <c r="J77" t="inlineStr">
         <is>
           <t>{'name': 'عبدالصاحب السجواني', 'screenName': 'alsajwani1', 'followersCount': 622, 'favouritesCount': 55, 'friendsCount': 2015, 'description': '\u200fمدرب ومستشار ريادة الأعمال  trainer and adviser Entrepreneurs'}</t>
         </is>
       </c>
-      <c r="K80" t="n">
+      <c r="K77" t="n">
         <v>1</v>
       </c>
-      <c r="L80" t="n">
-        <v>0</v>
-      </c>
-      <c r="M80" t="n">
-        <v>0</v>
-      </c>
-      <c r="N80" t="n">
-        <v>0</v>
-      </c>
-      <c r="O80" t="inlineStr">
+      <c r="L77" t="n">
+        <v>0</v>
+      </c>
+      <c r="M77" t="n">
+        <v>0</v>
+      </c>
+      <c r="N77" t="n">
+        <v>0</v>
+      </c>
+      <c r="O77" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="P80" t="inlineStr">
+      <c r="P77" t="inlineStr">
         <is>
           <t>2044734739718824109</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="1" t="n">
-        <v>79</v>
-      </c>
-      <c r="B81" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="1" t="n">
+        <v>76</v>
+      </c>
+      <c r="B78" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2046133214998114511</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
+      <c r="C78" t="inlineStr">
         <is>
           <t>2046133214998114511</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
+      <c r="D78" t="inlineStr">
         <is>
           <t>2045035981535912006</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
+      <c r="E78" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2045035981535912006</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
+      <c r="F78" t="inlineStr">
         <is>
           <t>@alsajwani1 مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
 رسالتك الخاصه.</t>
         </is>
       </c>
-      <c r="G81" t="n">
+      <c r="G78" t="n">
         <v>1776409547000</v>
       </c>
-      <c r="H81" t="inlineStr">
+      <c r="H78" t="inlineStr">
         <is>
           <t>2044702429464441285</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
+      <c r="I78" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="J81" t="inlineStr">
+      <c r="J78" t="inlineStr">
         <is>
           <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
-      <c r="K81" t="n">
+      <c r="K78" t="n">
         <v>1</v>
       </c>
-      <c r="L81" t="n">
-        <v>0</v>
-      </c>
-      <c r="M81" t="n">
-        <v>0</v>
-      </c>
-      <c r="N81" t="n">
-        <v>0</v>
-      </c>
-      <c r="O81" t="inlineStr">
+      <c r="L78" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" t="n">
+        <v>0</v>
+      </c>
+      <c r="N78" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="P81" t="inlineStr">
+      <c r="P78" t="inlineStr">
         <is>
           <t>2045014720416186802</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="1" t="n">
-        <v>80</v>
-      </c>
-      <c r="B82" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="1" t="n">
+        <v>77</v>
+      </c>
+      <c r="B79" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2046133214998114511</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
+      <c r="C79" t="inlineStr">
         <is>
           <t>2046133214998114511</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
+      <c r="D79" t="inlineStr">
         <is>
           <t>2045418169452695808</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
+      <c r="E79" t="inlineStr">
         <is>
           <t>https://x.com/alsajwani1/status/2045418169452695808</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
+      <c r="F79" t="inlineStr">
         <is>
           <t>@emiratesislamic ولكن إلى اليوم لم يتم إنهاء الإجراء 
 مع الأسف لايوجد متابعة لطلب من الفرع
@@ -6190,8 +5975,220 @@
 متى ستنتهي المأساة؟ https://t.co/rFW4GdBPlY</t>
         </is>
       </c>
+      <c r="G79" t="n">
+        <v>1776500668000</v>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>2044702429464441285</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGLI-x3aUAA7Qsp.jpg', 'type': 'photo', 'id': '2045418161642819584'}]</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>{'name': 'عبدالصاحب السجواني', 'screenName': 'alsajwani1', 'followersCount': 622, 'favouritesCount': 55, 'friendsCount': 2015, 'description': '\u200fمدرب ومستشار ريادة الأعمال  trainer and adviser Entrepreneurs'}</t>
+        </is>
+      </c>
+      <c r="K79" t="n">
+        <v>1</v>
+      </c>
+      <c r="L79" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" t="n">
+        <v>0</v>
+      </c>
+      <c r="N79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>2045035981535912006</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="n">
+        <v>78</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046133214998114511</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>2046133214998114511</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2046133214998114511</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046133214998114511</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>@alsajwani1 مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
+رسالتك الخاصه.</t>
+        </is>
+      </c>
+      <c r="G80" t="n">
+        <v>1776671148000</v>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>2044702429464441285</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="K80" t="n">
+        <v>2</v>
+      </c>
+      <c r="L80" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" t="n">
+        <v>0</v>
+      </c>
+      <c r="N80" t="n">
+        <v>0</v>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>2045418169452695808</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="n">
+        <v>79</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046133214998114511</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>2046133214998114511</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2046181231432495104</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>https://x.com/alsajwani1/status/2046181231432495104</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>@emiratesislamic ردكم لم يحرك ساكن 
+ إنجاز المعاملة إلى اليوم صفر</t>
+        </is>
+      </c>
+      <c r="G81" t="n">
+        <v>1776682596000</v>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>2044702429464441285</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>{'name': 'عبدالصاحب السجواني', 'screenName': 'alsajwani1', 'followersCount': 622, 'favouritesCount': 55, 'friendsCount': 2015, 'description': '\u200fمدرب ومستشار ريادة الأعمال  trainer and adviser Entrepreneurs'}</t>
+        </is>
+      </c>
+      <c r="K81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L81" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" t="n">
+        <v>0</v>
+      </c>
+      <c r="N81" t="n">
+        <v>0</v>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>2046133214998114511</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="n">
+        <v>80</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046133214998114511</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>2046133214998114511</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>2046154630548402178</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>https://x.com/alsajwani1/status/2046154630548402178</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>@emiratesislamic أنا اريد إنهاء الإجراء ولا اريد رد كلمات</t>
+        </is>
+      </c>
       <c r="G82" t="n">
-        <v>1776500668000</v>
+        <v>1776676254000</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
@@ -6200,7 +6197,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGLI-x3aUAA7Qsp.jpg', 'type': 'photo', 'id': '2045418161642819584'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -6222,12 +6219,12 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>2045035981535912006</t>
+          <t>2046133214998114511</t>
         </is>
       </c>
     </row>
@@ -6237,41 +6234,41 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2046133214998114511</t>
+          <t>https://x.com/emiratesislamic/status/2046148156560121974</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2046133214998114511</t>
+          <t>2046148156560121974</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2046133214998114511</t>
+          <t>2046148156560121974</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2046133214998114511</t>
+          <t>https://x.com/emiratesislamic/status/2046148156560121974</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>@alsajwani1 مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
-رسالتك الخاصه.</t>
+          <t>امنح أبنائك انطلاقة مبكرة نحو الوعي المالي الذكي
+ #الإمارات_الإسلامي https://t.co/xdFKEhpKDT</t>
         </is>
       </c>
       <c r="G83" t="n">
-        <v>1776671148000</v>
+        <v>1776674710000</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2044702429464441285</t>
+          <t>2046148156560121974</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/ext_tw_video_thumb/2046148122250809344/pu/img/WEGHCsaWoyjDb-ot.jpg', 'type': 'video', 'id': '2046148122250809344'}]</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -6280,7 +6277,7 @@
         </is>
       </c>
       <c r="K83" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L83" t="n">
         <v>0</v>
@@ -6293,14 +6290,10 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="P83" t="inlineStr">
-        <is>
-          <t>2045418169452695808</t>
-        </is>
-      </c>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
@@ -6308,50 +6301,50 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2046133214998114511</t>
+          <t>https://x.com/emiratesislamic/status/2046148156560121974</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2046133214998114511</t>
+          <t>2046148156560121974</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2046181231432495104</t>
+          <t>2046148194392740002</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>https://x.com/alsajwani1/status/2046181231432495104</t>
+          <t>https://x.com/emiratesislamic/status/2046148194392740002</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>@emiratesislamic ردكم لم يحرك ساكن 
- إنجاز المعاملة إلى اليوم صفر</t>
+          <t>Your child's smart money journey starts here. Empower your kids to take their first steps toward financial independence. 
+#EmiratesIslamic #AlphaYouth https://t.co/udWgfz8rNb</t>
         </is>
       </c>
       <c r="G84" t="n">
-        <v>1776682596000</v>
+        <v>1776674719000</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2044702429464441285</t>
+          <t>2046148156560121974</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/ext_tw_video_thumb/2046148161090068480/pu/img/GpPJv5a4DR5wZAQc.jpg', 'type': 'video', 'id': '2046148161090068480'}]</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>{'name': 'عبدالصاحب السجواني', 'screenName': 'alsajwani1', 'followersCount': 622, 'favouritesCount': 55, 'friendsCount': 2015, 'description': '\u200fمدرب ومستشار ريادة الأعمال  trainer and adviser Entrepreneurs'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="K84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L84" t="n">
         <v>0</v>
@@ -6364,12 +6357,12 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>47</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>2046133214998114511</t>
+          <t>2046148156560121974</t>
         </is>
       </c>
     </row>
@@ -6379,49 +6372,52 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2046133214998114511</t>
+          <t>https://x.com/emiratesislamic/status/2046148156560121974</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2046133214998114511</t>
+          <t>2046148156560121974</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2046154630548402178</t>
+          <t>2046215312949879234</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>https://x.com/alsajwani1/status/2046154630548402178</t>
+          <t>https://x.com/emiratesislamic/status/2046215312949879234</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>@emiratesislamic أنا اريد إنهاء الإجراء ولا اريد رد كلمات</t>
+          <t>Exclusively for Emaratis. Apply for an Emarati Credit Card &amp;amp; get a welcome bonus of up to 150,000 EI SmartMiles worth AED 1,500
+✅ No annual membership fee
+📈 Earn up to 3.75 EI SmartMiles back per AED spend
+🍔 50% discount on talabat https://t.co/pIT39d8ym8</t>
         </is>
       </c>
       <c r="G85" t="n">
-        <v>1776676254000</v>
+        <v>1776690722000</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2044702429464441285</t>
+          <t>2046215312949879234</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGWd-66WYAAChSk.jpg', 'type': 'photo', 'id': '2046215310001201152'}]</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>{'name': 'عبدالصاحب السجواني', 'screenName': 'alsajwani1', 'followersCount': 622, 'favouritesCount': 55, 'friendsCount': 2015, 'description': '\u200fمدرب ومستشار ريادة الأعمال  trainer and adviser Entrepreneurs'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="K85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L85" t="n">
         <v>0</v>
@@ -6434,14 +6430,10 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="P85" t="inlineStr">
-        <is>
-          <t>2046133214998114511</t>
-        </is>
-      </c>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
@@ -6507,7 +6499,7 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>177</t>
+          <t>179</t>
         </is>
       </c>
       <c r="P86" t="inlineStr"/>
@@ -6716,7 +6708,7 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -6731,25 +6723,234 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
+          <t>https://x.com/emiratesislamic/status/2046125792552222931</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>2046125792552222931</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>2045083218303402442</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2045083218303402442</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Get a chance to win a total of AED 1,000,000 in cash prizes.
+55 businesses will be winners. Will you be one of them?
+⭐️Grand cash prize: AED 250,000 (1 winner)
+💸 Second cash prize: AED 100,000 each (2 winners) https://t.co/V52QeTxHT6</t>
+        </is>
+      </c>
+      <c r="G90" t="n">
+        <v>1776420809000</v>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>2045083218303402442</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGGYWVTWUAEdJxW.jpg', 'type': 'photo', 'id': '2045083215245758465'}]</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="K90" t="n">
+        <v>2</v>
+      </c>
+      <c r="L90" t="n">
+        <v>0</v>
+      </c>
+      <c r="M90" t="n">
+        <v>0</v>
+      </c>
+      <c r="N90" t="n">
+        <v>1</v>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="n">
+        <v>89</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046125792552222931</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>2046125792552222931</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>2045520833406464393</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>https://x.com/gassann20203/status/2045520833406464393</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>@emiratesislamic Before few days u stopped the otp which was protecting our account from any fake or steeling money then we star receiving  withdraw from our account without permission I think u stolen our money</t>
+        </is>
+      </c>
+      <c r="G91" t="n">
+        <v>1776525145000</v>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>2045083218303402442</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>{'name': 'gazan', 'screenName': 'gassann20203', 'followersCount': 36, 'favouritesCount': 17, 'friendsCount': 35, 'description': 'Bloch chain expert'}</t>
+        </is>
+      </c>
+      <c r="K91" t="n">
+        <v>1</v>
+      </c>
+      <c r="L91" t="n">
+        <v>0</v>
+      </c>
+      <c r="M91" t="n">
+        <v>0</v>
+      </c>
+      <c r="N91" t="n">
+        <v>0</v>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>2045083218303402442</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="n">
+        <v>90</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046125792552222931</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>2046125792552222931</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>2046125792552222931</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046125792552222931</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>@gassann20203 Dear customer, we will connect with you on private messaging to serve you better</t>
+        </is>
+      </c>
+      <c r="G92" t="n">
+        <v>1776669378000</v>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>2045083218303402442</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="K92" t="n">
+        <v>0</v>
+      </c>
+      <c r="L92" t="n">
+        <v>0</v>
+      </c>
+      <c r="M92" t="n">
+        <v>0</v>
+      </c>
+      <c r="N92" t="n">
+        <v>0</v>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>2045520833406464393</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="n">
+        <v>91</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
           <t>https://x.com/emiratesislamic/status/2046125857643606493</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
+      <c r="C93" t="inlineStr">
         <is>
           <t>2046125857643606493</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
+      <c r="D93" t="inlineStr">
         <is>
           <t>2044321422282240384</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
+      <c r="E93" t="inlineStr">
         <is>
           <t>https://x.com/ADIBTweets/status/2044321422282240384</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr">
+      <c r="F93" t="inlineStr">
         <is>
           <t>قد تكون رسالة من “قريب”... لكنها احتيال. 
 أجب واربح 
@@ -6767,462 +6968,253 @@
 مسابقة_مصرف_أبوظبي_الإسلامي</t>
         </is>
       </c>
-      <c r="G90" t="n">
+      <c r="G93" t="n">
         <v>1776239183000</v>
       </c>
-      <c r="H90" t="inlineStr">
+      <c r="H93" t="inlineStr">
         <is>
           <t>2044321422282240384</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr">
+      <c r="I93" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF7jf0ba0AAZFPu.jpg', 'type': 'photo', 'id': '2044321416661880832'}]</t>
         </is>
       </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>{'name': 'ADIB Tweets', 'screenName': 'ADIBTweets', 'followersCount': 137563, 'favouritesCount': 2888, 'friendsCount': 104, 'description': 'حياكم في الحساب الرسمي لمصرف أبوظبي الإسلامي، شركة مساهمة عامة. Welcome to Abu Dhabi Islamic Bank Public Joint Stock Company official account'}</t>
-        </is>
-      </c>
-      <c r="K90" t="n">
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>{'name': 'ADIB Tweets', 'screenName': 'ADIBTweets', 'followersCount': 137558, 'favouritesCount': 2888, 'friendsCount': 104, 'description': 'حياكم في الحساب الرسمي لمصرف أبوظبي الإسلامي، شركة مساهمة عامة. Welcome to Abu Dhabi Islamic Bank Public Joint Stock Company official account'}</t>
+        </is>
+      </c>
+      <c r="K93" t="n">
         <v>393</v>
       </c>
-      <c r="L90" t="n">
-        <v>0</v>
-      </c>
-      <c r="M90" t="n">
+      <c r="L93" t="n">
+        <v>0</v>
+      </c>
+      <c r="M93" t="n">
         <v>69</v>
       </c>
-      <c r="N90" t="n">
+      <c r="N93" t="n">
         <v>206</v>
       </c>
-      <c r="O90" t="inlineStr">
-        <is>
-          <t>1435558</t>
-        </is>
-      </c>
-      <c r="P90" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="1" t="n">
-        <v>89</v>
-      </c>
-      <c r="B91" t="inlineStr">
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>1440541</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="n">
+        <v>92</v>
+      </c>
+      <c r="B94" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2046125857643606493</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
+      <c r="C94" t="inlineStr">
         <is>
           <t>2046125857643606493</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr">
+      <c r="D94" t="inlineStr">
         <is>
           <t>2045175695169732901</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
+      <c r="E94" t="inlineStr">
         <is>
           <t>https://x.com/mohmd_moh/status/2045175695169732901</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr">
+      <c r="F94" t="inlineStr">
         <is>
           <t>لماذ البنك لايتحمل المسوؤلية إذا تم اختراق الحساب الشخصي وتم سحب مبلغ من المال بدون اي ادارة امن الحسابات او عن طريق ارسال OTP ويدعي انه تم التحويل بالفعل والبنك غير قادر علي فعل شيي و يجب ان يتحمل صاحب الحساب تكاليف اصدار بطاقة جديده و تحمل المبلغ المسحوب و كأن الحسابات الشخصية سبيل متاح لاي عملية إحتيال وعلي صاحب الحساب تحمل كامل المسؤلية والبنك الذي من المفترض هو المؤتمن علي هذا المال لايتحمل إي مسؤلية.. علي فكره انتم من البنوك التي لاتهتم بحمايه العميل لكن هناك بنوك مثل الامارات الإسلامي له كل الشكر والامتنان لانه حدث معي عمليه احتيال و خلال اسبوع تحمل البنك المبلغ وتم إيداعه في حسابي وتم اصدار بطاقة جديده بدون اي تكلفة.
 كل الشكر الي بنك الإمارات الإسلامي @emiratesislamic</t>
         </is>
       </c>
-      <c r="G91" t="n">
+      <c r="G94" t="n">
         <v>1776442857000</v>
       </c>
-      <c r="H91" t="inlineStr">
+      <c r="H94" t="inlineStr">
         <is>
           <t>2044321422282240384</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr">
+      <c r="I94" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="J91" t="inlineStr">
+      <c r="J94" t="inlineStr">
         <is>
           <t>{'name': 'Mohamed Mohamed', 'screenName': 'mohmd_moh', 'followersCount': 195, 'favouritesCount': 6659, 'friendsCount': 1287, 'description': ''}</t>
         </is>
       </c>
-      <c r="K91" t="n">
+      <c r="K94" t="n">
         <v>3</v>
       </c>
-      <c r="L91" t="n">
-        <v>0</v>
-      </c>
-      <c r="M91" t="n">
-        <v>0</v>
-      </c>
-      <c r="N91" t="n">
-        <v>0</v>
-      </c>
-      <c r="O91" t="inlineStr">
+      <c r="L94" t="n">
+        <v>0</v>
+      </c>
+      <c r="M94" t="n">
+        <v>0</v>
+      </c>
+      <c r="N94" t="n">
+        <v>0</v>
+      </c>
+      <c r="O94" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="P91" t="inlineStr">
+      <c r="P94" t="inlineStr">
         <is>
           <t>2044321422282240384</t>
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="1" t="n">
-        <v>90</v>
-      </c>
-      <c r="B92" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="1" t="n">
+        <v>93</v>
+      </c>
+      <c r="B95" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2046125857643606493</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
+      <c r="C95" t="inlineStr">
         <is>
           <t>2046125857643606493</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
+      <c r="D95" t="inlineStr">
         <is>
           <t>2046125857643606493</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
+      <c r="E95" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2046125857643606493</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr">
+      <c r="F95" t="inlineStr">
         <is>
           <t>@mohmd_moh مرحبا ، يأسفنا سماع تجربتك! فريقنا ملتزم بمعالجة هذا الأمر على الفور. لحماية خصوصيتك ، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل. رضاك أولويتنا.</t>
         </is>
       </c>
-      <c r="G92" t="n">
+      <c r="G95" t="n">
         <v>1776669394000</v>
       </c>
-      <c r="H92" t="inlineStr">
+      <c r="H95" t="inlineStr">
         <is>
           <t>2044321422282240384</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr">
+      <c r="I95" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="J92" t="inlineStr">
+      <c r="J95" t="inlineStr">
         <is>
           <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
-      <c r="K92" t="n">
+      <c r="K95" t="n">
         <v>1</v>
       </c>
-      <c r="L92" t="n">
-        <v>0</v>
-      </c>
-      <c r="M92" t="n">
-        <v>0</v>
-      </c>
-      <c r="N92" t="n">
-        <v>0</v>
-      </c>
-      <c r="O92" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="P92" t="inlineStr">
+      <c r="L95" t="n">
+        <v>0</v>
+      </c>
+      <c r="M95" t="n">
+        <v>0</v>
+      </c>
+      <c r="N95" t="n">
+        <v>0</v>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
         <is>
           <t>2045175695169732901</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="1" t="n">
-        <v>91</v>
-      </c>
-      <c r="B93" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="1" t="n">
+        <v>94</v>
+      </c>
+      <c r="B96" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2046125857643606493</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
+      <c r="C96" t="inlineStr">
         <is>
           <t>2046125857643606493</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr">
+      <c r="D96" t="inlineStr">
         <is>
           <t>2046224051438526663</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
+      <c r="E96" t="inlineStr">
         <is>
           <t>https://x.com/mohmd_moh/status/2046224051438526663</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr">
+      <c r="F96" t="inlineStr">
         <is>
           <t>الشكر الجزيل لكم .  ليس لدي اي مشكلة حاليا أنا فقط ذكرت ماحدث معي للإشادة بكم علي سرعة الحل المقدم من طرفكم وسرعة استجابتكم وتحملكم المسؤلية تجاه العملاء .
 تعامل راقي وليس هدفكم المكسب فقط ولكن هدفكم الاول هو ارضاء العميل وهذا ذكاء منكم لأنكم بهذا الأسلوب سوف تكسبوا ثقة العملاء وبالتالي زيادة العملاء ويأتي المكسب مضاعف لاحقا . 
 كلمة حق تقال ان نهج الإمارات الإسلامي يستحق ان يقتدي به جميع البنوك.</t>
         </is>
       </c>
-      <c r="G93" t="n">
+      <c r="G96" t="n">
         <v>1776692805000</v>
       </c>
-      <c r="H93" t="inlineStr">
+      <c r="H96" t="inlineStr">
         <is>
           <t>2044321422282240384</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr">
+      <c r="I96" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="J93" t="inlineStr">
+      <c r="J96" t="inlineStr">
         <is>
           <t>{'name': 'Mohamed Mohamed', 'screenName': 'mohmd_moh', 'followersCount': 195, 'favouritesCount': 6659, 'friendsCount': 1287, 'description': ''}</t>
         </is>
       </c>
-      <c r="K93" t="n">
-        <v>0</v>
-      </c>
-      <c r="L93" t="n">
-        <v>0</v>
-      </c>
-      <c r="M93" t="n">
-        <v>0</v>
-      </c>
-      <c r="N93" t="n">
-        <v>0</v>
-      </c>
-      <c r="O93" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="P93" t="inlineStr">
+      <c r="K96" t="n">
+        <v>0</v>
+      </c>
+      <c r="L96" t="n">
+        <v>0</v>
+      </c>
+      <c r="M96" t="n">
+        <v>0</v>
+      </c>
+      <c r="N96" t="n">
+        <v>0</v>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
         <is>
           <t>2046125857643606493</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="1" t="n">
-        <v>92</v>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2046125792552222931</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>2046125792552222931</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>2045083218303402442</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2045083218303402442</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>Get a chance to win a total of AED 1,000,000 in cash prizes.
-55 businesses will be winners. Will you be one of them?
-⭐️Grand cash prize: AED 250,000 (1 winner)
-💸 Second cash prize: AED 100,000 each (2 winners) https://t.co/V52QeTxHT6</t>
-        </is>
-      </c>
-      <c r="G94" t="n">
-        <v>1776420809000</v>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>2045083218303402442</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGGYWVTWUAEdJxW.jpg', 'type': 'photo', 'id': '2045083215245758465'}]</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="K94" t="n">
-        <v>2</v>
-      </c>
-      <c r="L94" t="n">
-        <v>0</v>
-      </c>
-      <c r="M94" t="n">
-        <v>0</v>
-      </c>
-      <c r="N94" t="n">
-        <v>1</v>
-      </c>
-      <c r="O94" t="inlineStr">
-        <is>
-          <t>177</t>
-        </is>
-      </c>
-      <c r="P94" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="1" t="n">
-        <v>93</v>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2046125792552222931</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>2046125792552222931</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>2045520833406464393</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>https://x.com/gassann20203/status/2045520833406464393</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>@emiratesislamic Before few days u stopped the otp which was protecting our account from any fake or steeling money then we star receiving  withdraw from our account without permission I think u stolen our money</t>
-        </is>
-      </c>
-      <c r="G95" t="n">
-        <v>1776525145000</v>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>2045083218303402442</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>{'name': 'gazan', 'screenName': 'gassann20203', 'followersCount': 36, 'favouritesCount': 17, 'friendsCount': 35, 'description': 'Bloch chain expert'}</t>
-        </is>
-      </c>
-      <c r="K95" t="n">
-        <v>1</v>
-      </c>
-      <c r="L95" t="n">
-        <v>0</v>
-      </c>
-      <c r="M95" t="n">
-        <v>0</v>
-      </c>
-      <c r="N95" t="n">
-        <v>0</v>
-      </c>
-      <c r="O95" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="P95" t="inlineStr">
-        <is>
-          <t>2045083218303402442</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="1" t="n">
-        <v>94</v>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2046125792552222931</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>2046125792552222931</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>2046125792552222931</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2046125792552222931</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>@gassann20203 Dear customer, we will connect with you on private messaging to serve you better</t>
-        </is>
-      </c>
-      <c r="G96" t="n">
-        <v>1776669378000</v>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>2045083218303402442</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="K96" t="n">
-        <v>0</v>
-      </c>
-      <c r="L96" t="n">
-        <v>0</v>
-      </c>
-      <c r="M96" t="n">
-        <v>0</v>
-      </c>
-      <c r="N96" t="n">
-        <v>0</v>
-      </c>
-      <c r="O96" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="P96" t="inlineStr">
-        <is>
-          <t>2045520833406464393</t>
         </is>
       </c>
     </row>
@@ -7289,7 +7281,7 @@
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>66</t>
         </is>
       </c>
       <c r="P97" t="inlineStr"/>
@@ -7360,7 +7352,7 @@
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>19</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
@@ -7431,7 +7423,7 @@
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>46</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
@@ -7503,7 +7495,7 @@
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>66</t>
         </is>
       </c>
       <c r="P100" t="inlineStr"/>
@@ -7574,7 +7566,7 @@
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>19</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
@@ -7645,7 +7637,7 @@
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>46</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
@@ -7720,7 +7712,7 @@
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>34</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
@@ -7862,222 +7854,10 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>68</t>
         </is>
       </c>
       <c r="P105" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="1" t="n">
-        <v>104</v>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2046106592114856006</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>2046106592114856006</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>2046106592114856006</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2046106592114856006</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>الاستثمار ليس معقداً، بل يحتاج إلى تخطيط ذكي.
-مع منصة الثروات الرقمية من الإمارات الإسلامي، يمكنك البدء بثقة عبر تجربة رقمية سلسة ومتوافقة مع الشريعة الإسلامية، صُممت لمساعدتك على:
-✔️ الوصول إلى مجموعة واسعة من خيارات الاستثمار المتوافقة مع الشريعة الإسلامية</t>
-        </is>
-      </c>
-      <c r="G106" t="n">
-        <v>1776664801000</v>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>2046106592114856006</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="K106" t="n">
-        <v>1</v>
-      </c>
-      <c r="L106" t="n">
-        <v>0</v>
-      </c>
-      <c r="M106" t="n">
-        <v>0</v>
-      </c>
-      <c r="N106" t="n">
-        <v>0</v>
-      </c>
-      <c r="O106" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="P106" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="1" t="n">
-        <v>105</v>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2046106592114856006</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>2046106592114856006</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>2046106595369615672</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2046106595369615672</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>✔️ متابعة استثماراتك لحظة بلحظة
-✔️ الحصول على إرشادات ذكية لدعم قراراتك المالية
-✔️ الاستمتاع بتجربة رقمية متكاملة وسهلة
-ابدأ بمبلغ صغير، ضع أهدافاً بعيدة المدى، والتزم بالانضباط لتحقيق نتائج ملموسة.
-للمزيد من المعلومات، تفضل بزيارة الرابط التالي:
-https://t.co/PgcKVmrsKA</t>
-        </is>
-      </c>
-      <c r="G107" t="n">
-        <v>1776664801000</v>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>2046106592114856006</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="K107" t="n">
-        <v>1</v>
-      </c>
-      <c r="L107" t="n">
-        <v>0</v>
-      </c>
-      <c r="M107" t="n">
-        <v>0</v>
-      </c>
-      <c r="N107" t="n">
-        <v>0</v>
-      </c>
-      <c r="O107" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="P107" t="inlineStr">
-        <is>
-          <t>2046106592114856006</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="1" t="n">
-        <v>106</v>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2046106592114856006</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>2046106592114856006</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>2046215312949879234</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2046215312949879234</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>Exclusively for Emaratis. Apply for an Emarati Credit Card &amp;amp; get a welcome bonus of up to 150,000 EI SmartMiles worth AED 1,500
-✅ No annual membership fee
-📈 Earn up to 3.75 EI SmartMiles back per AED spend
-🍔 50% discount on talabat https://t.co/pIT39d8ym8</t>
-        </is>
-      </c>
-      <c r="G108" t="n">
-        <v>1776690722000</v>
-      </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>2046215312949879234</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGWd-66WYAAChSk.jpg', 'type': 'photo', 'id': '2046215310001201152'}]</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="K108" t="n">
-        <v>2</v>
-      </c>
-      <c r="L108" t="n">
-        <v>0</v>
-      </c>
-      <c r="M108" t="n">
-        <v>0</v>
-      </c>
-      <c r="N108" t="n">
-        <v>0</v>
-      </c>
-      <c r="O108" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="P108" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Xpost_df_comments.xlsx
+++ b/Xpost_df_comments.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P121"/>
+  <dimension ref="A1:P107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,35 +511,38 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://x.com/abhiseksonusonu/status/2047512157030645934</t>
+          <t>https://x.com/karim_alharby/status/2047809819265110291</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2047512157030645934</t>
+          <t>2047809819265110291</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2047512157030645934</t>
+          <t>2047809819265110291</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://x.com/abhiseksonusonu/status/2047512157030645934</t>
+          <t>https://x.com/karim_alharby/status/2047809819265110291</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE @LivBank It’s been 4 days since I raised the complaint. My due date is this Monday this delay is unacceptable. Please treat this as urgent and resolve on priority.</t>
+          <t>حبيت أفتح حساب جولد في بنك المشرق لقيتهم عاوزني ابقى مليونير علشان يبدأو معايا الكلام بسم الله يا سيد الناس خد الشروط..
+راتبك 80 الف درهم فيما فوق 
+رصيدك مينزلش عن 500 الف درهم 
+كان في شرط تالت ورابع قومت فاتح المحفظة وبايس كروت ADCB و ENBD و البنك الأهلي المصري وصليت ركعتين شكر</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1776999913000</v>
+        <v>1777070882000</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2047512157030645934</t>
+          <t>2047809819265110291</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -549,7 +552,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>{'name': 'A R mishra', 'screenName': 'abhiseksonusonu', 'followersCount': 0, 'favouritesCount': 0, 'friendsCount': 37, 'description': ''}</t>
+          <t>{'name': 'KARIM 🎩', 'screenName': 'karim_alharby', 'followersCount': 8057, 'favouritesCount': 31929, 'friendsCount': 441, 'description': 'Perfumer &amp; owner @ https://t.co/k1MCEdWq9g'}</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -562,11 +565,11 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2083</t>
         </is>
       </c>
       <c r="P2" t="inlineStr"/>
@@ -577,46 +580,36 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://x.com/Sarah23386430/status/2047432576336351289</t>
+          <t>https://x.com/Barigiin7m/status/2047712208696614977</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2047432576336351289</t>
+          <t>2047712208696614977</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2047432576336351289</t>
+          <t>2042645533164999079</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://x.com/Sarah23386430/status/2047432576336351289</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2042645533164999079</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>⎐كُـود⎐كوبِون⎐خـِصم⎐
-e1HcWgcAZOk
-⎐نون⎐
-⊵CBB54⊴
-⎐باث▬اند▬بودي⎐
-Af8p⊴
-⎐مفارش▬الحبيب⎐
-⊵sm29⊴
-⎐نمشي⎐
-⊵BLK13⊴
-^^^^
-ENbd</t>
+          <t>سيارة حلمك تقدر تتملكها
+جديدة ولا مستعملة نمولها لك مع التمويل التأجيري للسيارات من بنك الإمارات دبي الوطني</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1776980940000</v>
+        <v>1775839620000</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2047432576336351289</t>
+          <t>2042645533164999079</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -626,11 +619,11 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>{'name': 'Sarah', 'screenName': 'Sarah23386430', 'followersCount': 0, 'favouritesCount': 0, 'friendsCount': 0, 'description': ''}</t>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17365, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -641,7 +634,11 @@
       <c r="N3" t="n">
         <v>0</v>
       </c>
-      <c r="O3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>1795</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr"/>
     </row>
     <row r="4">
@@ -650,46 +647,35 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://x.com/Sarah23386430/status/2047432576336351289</t>
+          <t>https://x.com/Barigiin7m/status/2047712208696614977</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2047432576336351289</t>
+          <t>2047712208696614977</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2047526492096049564</t>
+          <t>2047712208696614977</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://x.com/Sarah23386430/status/2047526492096049564</t>
+          <t>https://x.com/Barigiin7m/status/2047712208696614977</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>⎐كُـود⎐كوبِون⎐خـِصم⎐
-e1HfMeyBZvL
-⎐ممزورلد⎐
-⊵jor⊴
-⎐ايهرب⎐ايهيرب اهرب
-⊵KIH8768⊴
-⎐باث▬اند▬بودي⎐
-AF8p⊴
-⎐نمشي⎐
-⊵BLK13⊴
-^^^^
-QjdQ</t>
+          <t>@EmiratesNBD_KSA اود تقديم قرض كيف أتواصل معكم</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1777003331000</v>
+        <v>1777047609000</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2047526492096049564</t>
+          <t>2042645533164999079</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -699,11 +685,11 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>{'name': 'Sarah', 'screenName': 'Sarah23386430', 'followersCount': 0, 'favouritesCount': 0, 'friendsCount': 0, 'description': ''}</t>
+          <t>{'name': 'Barigi', 'screenName': 'Barigiin7m', 'followersCount': 0, 'favouritesCount': 0, 'friendsCount': 103, 'description': ''}</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -714,8 +700,16 @@
       <c r="N4" t="n">
         <v>0</v>
       </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2042645533164999079</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -723,46 +717,36 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://x.com/Sarah23386430/status/2047432576336351289</t>
+          <t>https://x.com/Barigiin7m/status/2047712208696614977</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2047432576336351289</t>
+          <t>2047712208696614977</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2047527689691566501</t>
+          <t>2047714668169339163</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://x.com/Sarah23386430/status/2047527689691566501</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2047714668169339163</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>⎐كُـود⎐كوبِون⎐خـِصم⎐
-jC7pOqCjxA2
-⎐ايهرب⎐ايهيرب اهرب
-⊵KIH8768⊴
-⎐نمشى⎐
-⊵BLK13⊴
-⎐تُيموُ⎐
-⊵tea37⊴
-⎐نون⎐
-⊵Cbb54⊴
-^^^^
-SVnK</t>
+          <t>@Barigiin7m يرجي مراجعه التفاصيل وكيفيه التقديم من خلال هذا الرابط
+https://t.co/QV8KdPce6H</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1777003617000</v>
+        <v>1777048196000</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2047527689691566501</t>
+          <t>2042645533164999079</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -772,7 +756,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>{'name': 'Sarah', 'screenName': 'Sarah23386430', 'followersCount': 0, 'favouritesCount': 0, 'friendsCount': 0, 'description': ''}</t>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17365, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -787,8 +771,16 @@
       <c r="N5" t="n">
         <v>0</v>
       </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2047712208696614977</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -796,52 +788,50 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>https://x.com/jazz29210933/status/2047406903240565091</t>
+          <t>https://x.com/ENBDdeals/status/2047692986402643994</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2047406903240565091</t>
+          <t>2047692986402643994</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2047364023784529957</t>
+          <t>2047692986402643994</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2047364023784529957</t>
+          <t>https://x.com/ENBDdeals/status/2047692986402643994</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>We've reported AED 8.2 billion in profit before tax for Q1, up 6% year on year, driven by solid growth, resilient margins and record non-funded income. 
-https://t.co/oVickxRJGZ
-حققنا 8.2 مليار درهم أرباحًا قبل الضريبة في الربع الأول، بزيادة 6% مقارنة بالفترة ذاتها من العام السابق، مدعومة بنمو قوي، وهوامش ربح مرنة، ونمو قياسي في الدخل غير الممول.
-https://t.co/q7H1c2ANA3</t>
+          <t>Get an AED 500 Pet Corner Gift Card when you apply for an Emirates NBD noon One Visa Credit Card.
+Apply Now: https://t.co/vPejTs11gM https://t.co/RjpetrwLd9</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1776964596000</v>
+        <v>1777043026000</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2047364023784529957</t>
+          <t>2047692986402643994</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGmyup-WMAA4jS3.png', 'type': 'video', 'id': '2047363884437094400'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGrd61bXUAAXvdG.jpg', 'type': 'photo', 'id': '2047692983437316096'}]</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174341, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Emirates NBD Deals', 'screenName': 'ENBDdeals', 'followersCount': 39175, 'favouritesCount': 61, 'friendsCount': 4, 'description': 'Welcome to the official account for Emirates NBD Deals. نرحب بكم في الحساب الرسمي لعروض بنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -850,11 +840,11 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>809</t>
+          <t>64</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
@@ -865,45 +855,48 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://x.com/jazz29210933/status/2047406903240565091</t>
+          <t>https://x.com/ENBDdeals/status/2047692986402643994</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2047406903240565091</t>
+          <t>2047692986402643994</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2047406903240565091</t>
+          <t>2046851288172810389</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://x.com/jazz29210933/status/2047406903240565091</t>
+          <t>https://x.com/ENBDdeals/status/2046851288172810389</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE https://t.co/HdUJGMSnZV</t>
+          <t>باقة ورد لكل لحظة مميزة مع فلاورد 💐
+احصل على خصم 20% على تنسيقات الورود الأنيقة، حصريًا عبر تطبيق تستاهل.
+لمعرفة المزيد:
+https://t.co/quzlzhDcXR https://t.co/Pj8RmtMYOK</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1776974819000</v>
+        <v>1776842350000</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2047364023784529957</t>
+          <t>2046851288172810389</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGnZuU4WUAEw5rB.jpg', 'type': 'photo', 'id': '2047406895518863361'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGfgZjWWYAARtsk.jpg', 'type': 'photo', 'id': '2046851285253513216'}]</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>{'name': 'Aslam Khan', 'screenName': 'jazz29210933', 'followersCount': 293, 'favouritesCount': 168, 'friendsCount': 320, 'description': 'Free Palestine, Free USA from \nIsraHell Mafia, Anti MAGA, Anti Fat Pedophile Felon Trump, Anti blood sucking billionaires.                    \n💚 Green Party 💚'}</t>
+          <t>{'name': 'Emirates NBD Deals', 'screenName': 'ENBDdeals', 'followersCount': 39175, 'favouritesCount': 61, 'friendsCount': 4, 'description': 'Welcome to the official account for Emirates NBD Deals. نرحب بكم في الحساب الرسمي لعروض بنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -916,18 +909,14 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2047364023784529957</t>
-        </is>
-      </c>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -935,39 +924,36 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>https://x.com/AndrisKaushelis/status/2047345158077702559</t>
+          <t>https://x.com/fortyxxl88/status/2047691273159528852</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2047345158077702559</t>
+          <t>2047691273159528852</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2047345158077702559</t>
+          <t>2046820251229159879</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://x.com/AndrisKaushelis/status/2047345158077702559</t>
+          <t>https://x.com/AbdulrhmanRF/status/2046820251229159879</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Банки ОАЭ в 2026: где реально открыть счёт 🏦
-RAKBANK и Mashreq — чаще открывают малому бизнесу; 
-Emirates NBD — при наличии офиса и оборотов; 
-Wio — быстро, но с лимитами.
-Частые причины отказа: крипто, нет сайта, размытый бизнес, рисковые юрисдикции.</t>
+          <t>متى بتفعلون خدمة SAMSUNG PAY ؟
+ @EmiratesNBD_KSA</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1776960098000</v>
+        <v>1776834950000</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2047345158077702559</t>
+          <t>2046820251229159879</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -977,24 +963,24 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>{'name': 'Andris Kaushelis', 'screenName': 'AndrisKaushelis', 'followersCount': 1, 'favouritesCount': 0, 'friendsCount': 2, 'description': '➡ Регистрация и сопровождение бизнеса в ОАЭ\n➡ Emirates ID\n➡ Индивидуальный подход\nРуководитель офиса @mirsatori в ОАЭ\nЗапись на консультацию ⬇'}</t>
+          <t>{'name': 'Abed', 'screenName': 'AbdulrhmanRF', 'followersCount': 2023, 'favouritesCount': 19524, 'friendsCount': 1152, 'description': 'A simple guy who likes محمد عبده /Tech/TV/Movies/روجر فيدرير Roger Federer // الهلال 💙 Al Hilal SFC'}</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>305</t>
         </is>
       </c>
       <c r="P8" t="inlineStr"/>
@@ -1005,36 +991,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>https://x.com/AndrisKaushelis/status/2047345158077702559</t>
+          <t>https://x.com/fortyxxl88/status/2047691273159528852</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2047345158077702559</t>
+          <t>2047691273159528852</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2047345180924137800</t>
+          <t>2046821489882624075</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://x.com/AndrisKaushelis/status/2047345180924137800</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2046821489882624075</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Банк оценивает риски, а не только компанию.
-Как вы оцениваете свои шансы на открытие счёта в ОАЭ сейчас?</t>
+          <t>@AbdulrhmanRF مرحبا, تم الرد على الخاص.</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1776960103000</v>
+        <v>1776835245000</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2047345158077702559</t>
+          <t>2046820251229159879</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1044,11 +1029,11 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>{'name': 'Andris Kaushelis', 'screenName': 'AndrisKaushelis', 'followersCount': 1, 'favouritesCount': 0, 'friendsCount': 2, 'description': '➡ Регистрация и сопровождение бизнеса в ОАЭ\n➡ Emirates ID\n➡ Индивидуальный подход\nРуководитель офиса @mirsatori в ОАЭ\nЗапись на консультацию ⬇'}</t>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17365, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -1061,12 +1046,12 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>175</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2047345158077702559</t>
+          <t>2046820251229159879</t>
         </is>
       </c>
     </row>
@@ -1076,36 +1061,36 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>https://x.com/AndrisKaushelis/status/2047345158077702559</t>
+          <t>https://x.com/fortyxxl88/status/2047691273159528852</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2047345158077702559</t>
+          <t>2047691273159528852</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2046982948507767088</t>
+          <t>2047663017521774593</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://x.com/AndrisKaushelis/status/2046982948507767088</t>
+          <t>https://x.com/buib102/status/2047663017521774593</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Travel ban в ОАЭ: долг может остановить вас в аэропорту ✈️
-Даже задолженность от 15 000 AED может привести к запрету на выезд: кредитор подаёт в суд, и данные попадают в систему без уведомлений.</t>
+          <t>@EmiratesNBD_KSA @AbdulrhmanRF حولت اليوم مبلغ مالي اكثر من 20 الف من حسابي لديكم لبنك @alinma
+متى توصل الحواله ؟</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1776873740000</v>
+        <v>1777035881000</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2046982948507767088</t>
+          <t>2046820251229159879</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1115,7 +1100,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>{'name': 'Andris Kaushelis', 'screenName': 'AndrisKaushelis', 'followersCount': 1, 'favouritesCount': 0, 'friendsCount': 2, 'description': '➡ Регистрация и сопровождение бизнеса в ОАЭ\n➡ Emirates ID\n➡ Индивидуальный подход\nРуководитель офиса @mirsatori в ОАЭ\nЗапись на консультацию ⬇'}</t>
+          <t>{'name': 'kal', 'screenName': 'buib102', 'followersCount': 3, 'favouritesCount': 131, 'friendsCount': 50, 'description': 'ا'}</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1132,10 +1117,14 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr"/>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2046821489882624075</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -1143,35 +1132,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>https://x.com/ARbinQA/status/2047337655638073470</t>
+          <t>https://x.com/fortyxxl88/status/2047691273159528852</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2047337655638073470</t>
+          <t>2047691273159528852</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2047270522849812926</t>
+          <t>2047665248799195623</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://x.com/business/status/2047270522849812926</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2047665248799195623</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Emirates President Tim Clark struck a defiant tone in his first media appearance since the war in Iran forced the world’s largest airline to curtain operations, saying demand is strong enough to rebound https://t.co/pDJ8RYrmJD</t>
+          <t>@buib102 مرحباً، شكرا لتواصلك معنا. يُرجى إرسال التفاصيل الخاصه بطلبك إلى رسائل الخاص حتي نتمكن من مساعدتك بشكل أفضل</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1776942303000</v>
+        <v>1777036413000</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2047270522849812926</t>
+          <t>2046820251229159879</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1181,27 +1170,31 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>{'name': 'Bloomberg', 'screenName': 'business', 'followersCount': 10010465, 'favouritesCount': 5518, 'friendsCount': 110, 'description': 'The first word in business news | Watch Live: https://t.co/nHEpHOAfg3 | Newsletters: https://t.co/nWaCxHTiks | Podcasts: https://t.co/096e9xMJF7'}</t>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17365, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>126</v>
+        <v>0</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>19767</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr"/>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2047663017521774593</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
@@ -1209,67 +1202,67 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>https://x.com/ARbinQA/status/2047337655638073470</t>
+          <t>https://x.com/fortyxxl88/status/2047691273159528852</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2047337655638073470</t>
+          <t>2047691273159528852</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2047337655638073470</t>
+          <t>2047671039249846621</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://x.com/ARbinQA/status/2047337655638073470</t>
+          <t>https://x.com/i_rh9590/status/2047671039249846621</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>@business #Redundancy #COVID @emirates @EmiratesSupport @EmiratesNBD_AE @DXB @DXBMediaOffice @HamdanMohammed @MohamedBinZayed @HHShkMohd @MOHRE_UAE @AbuDhabi_ADM @abudhabitv @abudhabitv @khaleejtimes @gulf_news @OPECSecretariat @OPECnews @OPECFundAr @GCC #GCC @mofauae Still awaitingsupport https://t.co/kYgfHEitVf</t>
+          <t>@EmiratesNBD_KSA عندي مشكلة في البطاقة و احاول اسحب منها يطلع ( خطأ في النظام ) مع العلم يوجد بها رصيد ، و خدمة العملاء عندكم للاسف مافي اي تعاون .</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1776958309000</v>
+        <v>1777037794000</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2047270522849812926</t>
+          <t>2046820251229159879</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGmavuWXsAAQepw.jpg', 'type': 'photo', 'id': '2047337650302988288'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGmavueWsAAzCO4.jpg', 'type': 'photo', 'id': '2047337650336477184'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>{'name': 'A R', 'screenName': 'ARbinQA', 'followersCount': 2, 'favouritesCount': 458, 'friendsCount': 0, 'description': ''}</t>
+          <t>{'name': 'رغد الحربي', 'screenName': 'i_rh9590', 'followersCount': 113, 'favouritesCount': 1989, 'friendsCount': 1338, 'description': '-'}</t>
         </is>
       </c>
       <c r="K12" t="n">
         <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2047270522849812926</t>
+          <t>2047665248799195623</t>
         </is>
       </c>
     </row>
@@ -1279,39 +1272,35 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>https://x.com/asu_dixit/status/2047342848086094191</t>
+          <t>https://x.com/fortyxxl88/status/2047691273159528852</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2047342848086094191</t>
+          <t>2047691273159528852</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2047342848086094191</t>
+          <t>2047673420695920899</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://x.com/asu_dixit/status/2047342848086094191</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2047673420695920899</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hooow long we r taking for an disinvestment ?4 years!!
-Even @115, Private bank PE ⬆️180/220. 
-Priceto converge 90-135 -&amp;gt;115/120
-Boost for the 35% remaining stake + 10lakh cr sentiment ⏫. 
-@PMOIndia @nsitharaman @SecyDIPAM @DasShaktikanta @EmiratesNBD_AE @nsitharamanoffc</t>
+          <t>@i_rh9590 مرحباً، نأسف لسماع أنك تواجه تجربة غير سارة. يسعدنا مساعدتك وحلها. يُرجى إرسال التفاصيل الخاصه بشكواك إلى رسائل الخاص حتي نتمكن من مساعدتك بشكل أفضل</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>1776959547000</v>
+        <v>1777038362000</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2047342848086094191</t>
+          <t>2046820251229159879</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1321,11 +1310,11 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>{'name': 'Asutosh Dixit', 'screenName': 'asu_dixit', 'followersCount': 378, 'favouritesCount': 6859, 'friendsCount': 1475, 'description': 'Software Engineer 💻 and interested in travel ✈️, people👨🏻\u200d🦰, books📚, food🍛, investment 📈 ,spirituality. ❤️ beats fr India 🇮🇳 and views🗣 r personal.'}</t>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17365, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1341,7 +1330,11 @@
           <t>19</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>2047671039249846621</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
@@ -1349,40 +1342,35 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>https://x.com/asu_dixit/status/2047342848086094191</t>
+          <t>https://x.com/fortyxxl88/status/2047691273159528852</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2047342848086094191</t>
+          <t>2047691273159528852</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2046795354205823361</t>
+          <t>2047691273159528852</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://x.com/asu_dixit/status/2046795354205823361</t>
+          <t>https://x.com/fortyxxl88/status/2047691273159528852</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dear @idco_odisha @MohanMOdisha @CMO_Odisha @SampadSwainBJP 
-Congratulations! 
-We must actively support AMNS new iron ore mines and make them production ready
-Help put slurry pipes. 
-Help taking ores - refine in other states.
-Acquire land @Kendrapada site. It can be useful.</t>
+          <t>@EmiratesNBD_KSA تشترون مديونية قطاع خاص غير معتمد ؟</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1776829014000</v>
+        <v>1777042618000</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2046795354205823361</t>
+          <t>2046820251229159879</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1392,7 +1380,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>{'name': 'Asutosh Dixit', 'screenName': 'asu_dixit', 'followersCount': 378, 'favouritesCount': 6859, 'friendsCount': 1475, 'description': 'Software Engineer 💻 and interested in travel ✈️, people👨🏻\u200d🦰, books📚, food🍛, investment 📈 ,spirituality. ❤️ beats fr India 🇮🇳 and views🗣 r personal.'}</t>
+          <t>{'name': 'forty', 'screenName': 'fortyxxl88', 'followersCount': 1, 'favouritesCount': 43, 'friendsCount': 50, 'description': ''}</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1409,10 +1397,14 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr"/>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>2047673420695920899</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
@@ -1420,62 +1412,63 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>https://x.com/EMD0958/status/2047327801745842508</t>
+          <t>https://x.com/i_rh9590/status/2047671039249846621</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2047327801745842508</t>
+          <t>2047671039249846621</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2047327620354994312</t>
+          <t>2046820251229159879</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://x.com/Forsan_UAE/status/2047327620354994312</t>
+          <t>https://x.com/AbdulrhmanRF/status/2046820251229159879</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>بدخل يصل لـ14.4 مليار درهم بنمو 13%، وودائع بلغت 44 مليار درهم بزيادة قدرها 6%.. #بنك_الإمارات_دبي_الوطني يواصل تألقه بنتائج قياسية خلال الربع الأول من 2026 https://t.co/RGczynJXtC</t>
+          <t>متى بتفعلون خدمة SAMSUNG PAY ؟
+ @EmiratesNBD_KSA</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1776955916000</v>
+        <v>1776834950000</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2047327620354994312</t>
+          <t>2046820251229159879</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGmRndRaYAARh_E.jpg', 'type': 'photo', 'id': '2047327612675186688'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>{'name': 'فرسان الإمارات', 'screenName': 'Forsan_UAE', 'followersCount': 625428, 'favouritesCount': 302, 'friendsCount': 80, 'description': 'الدفاع عن الوطن واجب مقدس، وشرف تعشقه قلوب أبناء زايد'}</t>
+          <t>{'name': 'Abed', 'screenName': 'AbdulrhmanRF', 'followersCount': 2023, 'favouritesCount': 19524, 'friendsCount': 1152, 'description': 'A simple guy who likes محمد عبده /Tech/TV/Movies/روجر فيدرير Roger Federer // الهلال 💙 Al Hilal SFC'}</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>770</t>
+          <t>305</t>
         </is>
       </c>
       <c r="P15" t="inlineStr"/>
@@ -1486,35 +1479,35 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>https://x.com/EMD0958/status/2047327801745842508</t>
+          <t>https://x.com/i_rh9590/status/2047671039249846621</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2047327801745842508</t>
+          <t>2047671039249846621</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2047327801745842508</t>
+          <t>2046821489882624075</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://x.com/EMD0958/status/2047327801745842508</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2046821489882624075</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>@Forsan_UAE @EmiratesNBD_AE https://t.co/4ASu117jo9</t>
+          <t>@AbdulrhmanRF مرحبا, تم الرد على الخاص.</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1776955960000</v>
+        <v>1776835245000</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2047327620354994312</t>
+          <t>2046820251229159879</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1524,11 +1517,11 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>{'name': 'EMDHoresman', 'screenName': 'EMD0958', 'followersCount': 183, 'favouritesCount': 188, 'friendsCount': 3185, 'description': ''}</t>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17365, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -1541,12 +1534,12 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>175</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2047327620354994312</t>
+          <t>2046820251229159879</t>
         </is>
       </c>
     </row>
@@ -1556,51 +1549,50 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>https://x.com/ABCinGCC/status/2047322098696163735</t>
+          <t>https://x.com/i_rh9590/status/2047671039249846621</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2047322098696163735</t>
+          <t>2047671039249846621</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2047322098696163735</t>
+          <t>2047663017521774593</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://x.com/ABCinGCC/status/2047322098696163735</t>
+          <t>https://x.com/buib102/status/2047663017521774593</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Emirates NBD, in line with the resilient operating environment in the UAE, reported a profit before tax of AED8.2 billion ($2.23 billion) for the first quarter of 2026.
-Read more on https://t.co/Nn6AqaDch6
-#ABCNews #Profit #Growth #StrategicInvestment #UAE https://t.co/Q0uOolHeF2</t>
+          <t>@EmiratesNBD_KSA @AbdulrhmanRF حولت اليوم مبلغ مالي اكثر من 20 الف من حسابي لديكم لبنك @alinma
+متى توصل الحواله ؟</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1776954600000</v>
+        <v>1777035881000</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2047322098696163735</t>
+          <t>2046820251229159879</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGlvjm4bcAAWkyh.jpg', 'type': 'photo', 'id': '2047290163139932160'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>{'name': 'Arabian Business Community (ABC GCC)', 'screenName': 'ABCinGCC', 'followersCount': 355, 'favouritesCount': 8, 'friendsCount': 180, 'description': 'Official Twitter of the Arabian Business Community (ABC). We’ll be tweeting about business news and popular business categories in the Gulf region.'}</t>
+          <t>{'name': 'kal', 'screenName': 'buib102', 'followersCount': 3, 'favouritesCount': 131, 'friendsCount': 50, 'description': 'ا'}</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -1613,10 +1605,14 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr"/>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>2046821489882624075</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
@@ -1624,51 +1620,49 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>https://x.com/ABCinGCC/status/2047322098696163735</t>
+          <t>https://x.com/i_rh9590/status/2047671039249846621</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2047322098696163735</t>
+          <t>2047671039249846621</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2047329655724581037</t>
+          <t>2047665248799195623</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://x.com/ABCinGCC/status/2047329655724581037</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2047665248799195623</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>DMCC has announced the launch of One Uptown Place and Two Uptown Place, two new premium commercial towers within its flagship Uptown Dubai district, representing the latest milestone in the district’s expansion.
-Read more on https://t.co/K2EMlFIFzy
-#ABCNews #CommercialTowers https://t.co/zPgztC8nQE</t>
+          <t>@buib102 مرحباً، شكرا لتواصلك معنا. يُرجى إرسال التفاصيل الخاصه بطلبك إلى رسائل الخاص حتي نتمكن من مساعدتك بشكل أفضل</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>1776956402000</v>
+        <v>1777036413000</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2047329655724581037</t>
+          <t>2046820251229159879</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGlx9DGacAA7ZCb.jpg', 'type': 'photo', 'id': '2047292799234764800'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>{'name': 'Arabian Business Community (ABC GCC)', 'screenName': 'ABCinGCC', 'followersCount': 355, 'favouritesCount': 8, 'friendsCount': 180, 'description': 'Official Twitter of the Arabian Business Community (ABC). We’ll be tweeting about business news and popular business categories in the Gulf region.'}</t>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17365, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -1681,10 +1675,14 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr"/>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>2047663017521774593</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
@@ -1692,54 +1690,49 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>https://x.com/CyberxGlobal/status/2047320011086389312</t>
+          <t>https://x.com/i_rh9590/status/2047671039249846621</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2047320011086389312</t>
+          <t>2047671039249846621</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2047320011086389312</t>
+          <t>2047671039249846621</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://x.com/CyberxGlobal/status/2047320011086389312</t>
+          <t>https://x.com/i_rh9590/status/2047671039249846621</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Speaker Announcement – CyberX Egypt 2026
-We’re excited to welcome Hisham Mohamed Aly, Chief Information Security Officer at Emirates NBD Egypt as a featured speaker at CyberX Egypt 2026.
-🗓 18 May 2026
-📍New Cairo, Egypt
- Apply now: https://t.co/bFrDYoxMSe
-#CyberXEgypt https://t.co/gIEqC0W76B</t>
+          <t>@EmiratesNBD_KSA عندي مشكلة في البطاقة و احاول اسحب منها يطلع ( خطأ في النظام ) مع العلم يوجد بها رصيد ، و خدمة العملاء عندكم للاسف مافي اي تعاون .</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>1776954102000</v>
+        <v>1777037794000</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2047320011086389312</t>
+          <t>2046820251229159879</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGmKL3naEAAKNd4.jpg', 'type': 'photo', 'id': '2047319442129031168'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>{'name': 'CyberxGlobal', 'screenName': 'CyberxGlobal', 'followersCount': 49, 'favouritesCount': 61, 'friendsCount': 15, 'description': 'CYBERX GLOBAL is a dedicated series for Cyber Security, OT &amp; ICS Conferences and Seminars in Middle East, Africa, India and South East Asia.'}</t>
+          <t>{'name': 'رغد الحربي', 'screenName': 'i_rh9590', 'followersCount': 113, 'favouritesCount': 1989, 'friendsCount': 1338, 'description': '-'}</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -1752,10 +1745,14 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>2047665248799195623</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
@@ -1763,54 +1760,49 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>https://x.com/CyberxGlobal/status/2047320011086389312</t>
+          <t>https://x.com/i_rh9590/status/2047671039249846621</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2047320011086389312</t>
+          <t>2047671039249846621</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2047318648508035212</t>
+          <t>2047673420695920899</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://x.com/CyberxGlobal/status/2047318648508035212</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2047673420695920899</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Media Partner Announcement - CyberX Indonesia 2026    
-We are proud to announce Gazet International Magazine as a media partner for CyberX Indonesia 2026
-🗓 28 April 2026 
-📍 Fairmont Hotel, Jakarta, Indonesia    
-Secure your spot now: https://t.co/veR16zImuE
-#CyberXIndonesia https://t.co/ghuwCuRQz7</t>
+          <t>@i_rh9590 مرحباً، نأسف لسماع أنك تواجه تجربة غير سارة. يسعدنا مساعدتك وحلها. يُرجى إرسال التفاصيل الخاصه بشكواك إلى رسائل الخاص حتي نتمكن من مساعدتك بشكل أفضل</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>1776953777000</v>
+        <v>1777038362000</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2047318648508035212</t>
+          <t>2046820251229159879</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGmIuXabIAA5OE6.jpg', 'type': 'photo', 'id': '2047317835756806144'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>{'name': 'CyberxGlobal', 'screenName': 'CyberxGlobal', 'followersCount': 49, 'favouritesCount': 61, 'friendsCount': 15, 'description': 'CYBERX GLOBAL is a dedicated series for Cyber Security, OT &amp; ICS Conferences and Seminars in Middle East, Africa, India and South East Asia.'}</t>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17365, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -1819,14 +1811,18 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr"/>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>2047671039249846621</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
@@ -1834,64 +1830,64 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>https://x.com/Forbes_MENA_/status/2047302322716340460</t>
+          <t>https://x.com/AmalaAyesha/status/2047666831612149831</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2047302322716340460</t>
+          <t>2047666831612149831</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2047302322716340460</t>
+          <t>2047620964712693908</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://x.com/Forbes_MENA_/status/2047302322716340460</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2047620964712693908</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>FAB, Emirates NBD, and ADCB have posted combined Q1 2026 net profits of $4 billion, reaffirming the UAE banking sector’s strength despite persistent regional headwinds. Here’s how the nation’s top 3 banks navigated a turbulent quarter.
-#Forbes 
-For More Details: https://t.co/6pj7bhaQHT</t>
+          <t>You get an unexpected payment request. What do you do?
+Stay Safe, Stay Vigilant. #UnitedAgainstFraud
+https://t.co/YpRWtBZrhq</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>1776949885000</v>
+        <v>1777025855000</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2047302322716340460</t>
+          <t>2047620964712693908</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGl6nC7WsAADnIL.jpg', 'type': 'photo', 'id': '2047302316835909632'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>{'name': 'Forbes Middle East', 'screenName': 'Forbes_MENA_', 'followersCount': 19664, 'favouritesCount': 182, 'friendsCount': 6, 'description': "The Homepage of The World's Business Leaders.\nFollow @ForbesME for breaking news and latest updates in Arabic."}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174349, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
         <v>1</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>316</t>
         </is>
       </c>
       <c r="P21" t="inlineStr"/>
@@ -1902,45 +1898,45 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>https://x.com/Forbes_MENA_/status/2047302322716340460</t>
+          <t>https://x.com/AmalaAyesha/status/2047666831612149831</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2047302322716340460</t>
+          <t>2047666831612149831</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2047331247572001247</t>
+          <t>2047666831612149831</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://x.com/Forbes_MENA_/status/2047331247572001247</t>
+          <t>https://x.com/AmalaAyesha/status/2047666831612149831</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>At the Abu Dhabi Global Entrepreneurship Festival, Nader Nassar, Founder and CEO of Hlthera and Board Member of the Forbes Middle East Youth Council, says the event is one of the most significant initiatives for entrepreneurs in the UAE, bringing together founders, accelerator programs, and knowledge-sharing opportunities in one place.</t>
+          <t>@EmiratesNBD_AE Is this biggest joke ?</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>1776956781000</v>
+        <v>1777036791000</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2047331247572001247</t>
+          <t>2047620964712693908</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGmTrsYXMAAJ5gB.jpg', 'type': 'video', 'id': '2047325722478256128'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>{'name': 'Forbes Middle East', 'screenName': 'Forbes_MENA_', 'followersCount': 19664, 'favouritesCount': 182, 'friendsCount': 6, 'description': "The Homepage of The World's Business Leaders.\nFollow @ForbesME for breaking news and latest updates in Arabic."}</t>
+          <t>{'name': 'Ayesha.amala', 'screenName': 'AmalaAyesha', 'followersCount': 39, 'favouritesCount': 20, 'friendsCount': 135, 'description': ''}</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -1950,17 +1946,21 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>197</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr"/>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>2047620964712693908</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
@@ -1968,35 +1968,36 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>https://x.com/deegrose/status/2047306816560705775</t>
+          <t>https://x.com/AmalaAyesha/status/2047666831612149831</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2047306816560705775</t>
+          <t>2047666831612149831</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2047306816560705775</t>
+          <t>2047668962998034824</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://x.com/deegrose/status/2047306816560705775</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2047668962998034824</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Emirates NBD Q1 profit rises 3%, beats estimates https://t.co/ZnaITHVNDR</t>
+          <t>@AmalaAyesha Hi Ayesha, Please find the below link for more details. Thanks- Zubair 
+https://t.co/YpRWtBZrhq</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>1776950956000</v>
+        <v>1777037299000</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2047306816560705775</t>
+          <t>2047620964712693908</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2006,7 +2007,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>{'name': 'DeeG (Maria)', 'screenName': 'deegrose', 'followersCount': 12442, 'favouritesCount': 443407, 'friendsCount': 8658, 'description': ''}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174349, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -2023,10 +2024,14 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr"/>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>2047666831612149831</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
@@ -2034,35 +2039,35 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>https://x.com/deegrose/status/2047306816560705775</t>
+          <t>https://x.com/abhiseksonusonu/status/2047678055070757117</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2047306816560705775</t>
+          <t>2047678055070757117</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2047469626863358363</t>
+          <t>2047678055070757117</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://x.com/deegrose/status/2047469626863358363</t>
+          <t>https://x.com/abhiseksonusonu/status/2047678055070757117</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Iraq’s “Man in the Shadows”: Intelligence Chief Emerges as Consensus PM Candidate | Search 4 Dinar https://t.co/qRHYc2we70</t>
+          <t>@LivBank @EmiratesNBD_AE  My issue regarding the credit card payment has now been successfully resolved.I would like to extend my sincere thanks to the bank’s support team for their prompt response and professional assistance throughout the process.Thank you once again.</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>1776989773000</v>
+        <v>1777039467000</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2047469626863358363</t>
+          <t>2047678055070757117</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2072,7 +2077,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>{'name': 'DeeG (Maria)', 'screenName': 'deegrose', 'followersCount': 12442, 'favouritesCount': 443407, 'friendsCount': 8658, 'description': ''}</t>
+          <t>{'name': 'A R mishra', 'screenName': 'abhiseksonusonu', 'followersCount': 0, 'favouritesCount': 0, 'friendsCount': 37, 'description': ''}</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -2085,11 +2090,11 @@
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>16</t>
         </is>
       </c>
       <c r="P24" t="inlineStr"/>
@@ -2100,65 +2105,63 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>https://x.com/hspropertydubai/status/2047296929651130678</t>
+          <t>https://x.com/buib102/status/2047663017521774593</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2047296929651130678</t>
+          <t>2047663017521774593</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2047296929651130678</t>
+          <t>2046820251229159879</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://x.com/hspropertydubai/status/2047296929651130678</t>
+          <t>https://x.com/AbdulrhmanRF/status/2046820251229159879</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Want to invest in Dubai off-plan projects with less cash? 🔑
-Thanks to Emirates NBD, Emaar, Nakheel, and Dubai Holding, you can now use a mortgage during construction.
-Plan your future more clearly and invest smartly.
-#InvestInDubai #Emaar #DubaiRealEstate #OffPlanInvesting https://t.co/jepcUuYehh</t>
+          <t>متى بتفعلون خدمة SAMSUNG PAY ؟
+ @EmiratesNBD_KSA</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>1776948599000</v>
+        <v>1776834950000</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2047296929651130678</t>
+          <t>2046820251229159879</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2047296827842813952/img/8FjyJ1uk5TJBoqYQ.jpg', 'type': 'video', 'id': '2047296827842813952'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>{'name': 'H&amp;S Real Estate', 'screenName': 'hspropertydubai', 'followersCount': 1093, 'favouritesCount': 3, 'friendsCount': 236, 'description': 'H&amp;S Real Estate is the No. 1 firm in Dubai for off-plan real estate investment.\n\n+971 526 902 884'}</t>
+          <t>{'name': 'Abed', 'screenName': 'AbdulrhmanRF', 'followersCount': 2023, 'favouritesCount': 19524, 'friendsCount': 1152, 'description': 'A simple guy who likes محمد عبده /Tech/TV/Movies/روجر فيدرير Roger Federer // الهلال 💙 Al Hilal SFC'}</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>305</t>
         </is>
       </c>
       <c r="P25" t="inlineStr"/>
@@ -2169,53 +2172,49 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>https://x.com/hspropertydubai/status/2047296929651130678</t>
+          <t>https://x.com/buib102/status/2047663017521774593</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2047296929651130678</t>
+          <t>2047663017521774593</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2046926039549702580</t>
+          <t>2046821489882624075</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://x.com/hspropertydubai/status/2046926039549702580</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2046821489882624075</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>⸻
-“If your money isn’t growing, you’re losing purchasing power.” 💡
-In Dubai, no income tax, no capital gains tax, and active capital. Yields 6%-12%, off-plan appreciation 15%-40%.
-Global capital asks, “Where does my money perform better?” The answer: Dubai.
-#InvestInDubai https://t.co/vgNlslTiHR</t>
+          <t>@AbdulrhmanRF مرحبا, تم الرد على الخاص.</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>1776860172000</v>
+        <v>1776835245000</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2046926039549702580</t>
+          <t>2046820251229159879</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2046925950642946048/img/x2C_wP0TfnP7gCF0.jpg', 'type': 'video', 'id': '2046925950642946048'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>{'name': 'H&amp;S Real Estate', 'screenName': 'hspropertydubai', 'followersCount': 1093, 'favouritesCount': 3, 'friendsCount': 236, 'description': 'H&amp;S Real Estate is the No. 1 firm in Dubai for off-plan real estate investment.\n\n+971 526 902 884'}</t>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17365, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -2224,14 +2223,18 @@
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr"/>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>2046820251229159879</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
@@ -2239,35 +2242,36 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>https://x.com/ArgaamPlus/status/2047291417643340140</t>
+          <t>https://x.com/buib102/status/2047663017521774593</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2047291417643340140</t>
+          <t>2047663017521774593</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2047291417643340140</t>
+          <t>2047663017521774593</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://x.com/ArgaamPlus/status/2047291417643340140</t>
+          <t>https://x.com/buib102/status/2047663017521774593</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Emirates NBD Q1 2026 up 3% YoY to AED 6.40 billion</t>
+          <t>@EmiratesNBD_KSA @AbdulrhmanRF حولت اليوم مبلغ مالي اكثر من 20 الف من حسابي لديكم لبنك @alinma
+متى توصل الحواله ؟</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>1776947285000</v>
+        <v>1777035881000</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2047291417643340140</t>
+          <t>2046820251229159879</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2277,11 +2281,11 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>{'name': 'Argaam Plus', 'screenName': 'ArgaamPlus', 'followersCount': 29012, 'favouritesCount': 19, 'friendsCount': 7, 'description': "Market data, analysis, and commentary from Saudi Arabia's leading business news provider. \n\nArabic Account: @Argaam"}</t>
+          <t>{'name': 'kal', 'screenName': 'buib102', 'followersCount': 3, 'favouritesCount': 131, 'friendsCount': 50, 'description': 'ا'}</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -2294,10 +2298,14 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr"/>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>2046821489882624075</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
@@ -2305,51 +2313,49 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>https://x.com/TradeArabia/status/2047275289659539631</t>
+          <t>https://x.com/buib102/status/2047663017521774593</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2047275289659539631</t>
+          <t>2047663017521774593</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2047275289659539631</t>
+          <t>2047665248799195623</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://x.com/TradeArabia/status/2047275289659539631</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2047665248799195623</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Emirates NBD reported a profit before tax of AED8.2 billion ($2.23 billion) for the first quarter of 2026, up 6% yoy, driven by strong balance sheet growth, resilient margins and record non-funded income growth.
-Read more on https://t.co/SIUcQ2s7tw
-#Tradearabia #emirates #finance https://t.co/48rJKsVpNb</t>
+          <t>@buib102 مرحباً، شكرا لتواصلك معنا. يُرجى إرسال التفاصيل الخاصه بطلبك إلى رسائل الخاص حتي نتمكن من مساعدتك بشكل أفضل</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>1776943440000</v>
+        <v>1777036413000</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2047275289659539631</t>
+          <t>2046820251229159879</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGlGt4Ra4AEuMpi.jpg', 'type': 'photo', 'id': '2047245259630108673'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>{'name': 'Trade Arabia', 'screenName': 'TradeArabia', 'followersCount': 16376, 'favouritesCount': 199, 'friendsCount': 48, 'description': "Trade Arabia is the leading portal for business information and trade news covering the Middle East. 'Like' us on \nhttps://t.co/PrFoU4Ciw4"}</t>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17365, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -2362,10 +2368,14 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr"/>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>2047663017521774593</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
@@ -2373,64 +2383,63 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>https://x.com/TradeArabia/status/2047275289659539631</t>
+          <t>https://x.com/ren_fernz/status/2047629578990936518</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2047275289659539631</t>
+          <t>2047629578990936518</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2047305740419826118</t>
+          <t>2047629578990936518</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://x.com/TradeArabia/status/2047305740419826118</t>
+          <t>https://x.com/ren_fernz/status/2047629578990936518</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gulf women continue to strengthen their presence in the development journey of GCC countries, supported by a young population base and growing participation in the labour market
-Read more on https://t.co/xjqrqS1PA5
-#Tradearabia #Gulf #womenempowerment https://t.co/BJl4kbM156</t>
+          <t>Very disappointed with @ENBDdeals 
+I moved from UAE since Sept 2025 and I’m paying my bills every month by 23rd. Since I’m out of country I won’t be having same time zone and I always see glitch in the ENBD app . I see the outstanding balance keep changing every time</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>1776950700000</v>
+        <v>1777027909000</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2047305740419826118</t>
+          <t>2047629578990936518</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGlHAAXbwAAlAZC.jpg', 'type': 'photo', 'id': '2047245571040460800'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>{'name': 'Trade Arabia', 'screenName': 'TradeArabia', 'followersCount': 16376, 'favouritesCount': 199, 'friendsCount': 48, 'description': "Trade Arabia is the leading portal for business information and trade news covering the Middle East. 'Like' us on \nhttps://t.co/PrFoU4Ciw4"}</t>
+          <t>{'name': 'Ren', 'screenName': 'ren_fernz', 'followersCount': 4059, 'favouritesCount': 6485, 'friendsCount': 862, 'description': ''}</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>32</t>
         </is>
       </c>
       <c r="P29" t="inlineStr"/>
@@ -2441,49 +2450,49 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>https://x.com/royamoney/status/2047271389288083759</t>
+          <t>https://x.com/ren_fernz/status/2047629578990936518</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2047271389288083759</t>
+          <t>2047629578990936518</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2047271389288083759</t>
+          <t>2047629581159477750</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://x.com/royamoney/status/2047271389288083759</t>
+          <t>https://x.com/ren_fernz/status/2047629581159477750</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>حقق Emirates NBD أرباحًا قبل الضريبة 8.2 مليار درهم (+6%) في الربع الأول 2026، مع إيرادات 14.4 مليار وأصول تتجاوز 1.2 تريليون. النمو مدعوم بالتوسع والرقمنة، مع أداء قوي أيضًا لـ Emirates Islamic. https://t.co/JrTGPuxva9</t>
+          <t>I tried to contact in Jan and Feb on WhatsApp but was unable to contact with customer service in Feb it was due to ramdan . Last I came back to pay the bills and I saw the outstanding balance is again more . I saw the transaction history there is nothing but when I contact CS</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>1776942510000</v>
+        <v>1777027909000</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2047271389288083759</t>
+          <t>2047629578990936518</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGled5zXoAEVx_z.jpg', 'type': 'photo', 'id': '2047271373442097153'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>{'name': 'رؤيا مال وأعمال', 'screenName': 'royamoney', 'followersCount': 1, 'favouritesCount': 0, 'friendsCount': 1, 'description': 'نرصد سوق المال والأعمال ببساطة.'}</t>
+          <t>{'name': 'Ren', 'screenName': 'ren_fernz', 'followersCount': 4059, 'favouritesCount': 6485, 'friendsCount': 862, 'description': ''}</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -2496,10 +2505,14 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>2047629578990936518</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
@@ -2507,46 +2520,45 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>https://x.com/royamoney/status/2047271389288083759</t>
+          <t>https://x.com/NovoCinemas/status/2047647028012876081</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2047271389288083759</t>
+          <t>2047647028012876081</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2047295679458906286</t>
+          <t>2047647028012876081</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://x.com/royamoney/status/2047295679458906286</t>
+          <t>https://x.com/NovoCinemas/status/2047647028012876081</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>أعلن نقيب أصحاب محلات الحلي والمجوهرات، ربحي علان، عن قرار النقابة بوقف نشر التسعيرة اليومية الموحدة لمصاغات الذهب من عيار 14 اعتبارا من يوم السبت، وذلك بعد مرور قرابة عام على طرحه في الأسواق الأردنية.
-تفاصيل: https://t.co/1sqjpxockw https://t.co/UM0sp4YPt0</t>
+          <t>Sometimes, all you need is a quiet escape into a great story. 🎞️🤍 Use your Emirates NBD card at Novo Cinemas to enjoy 15% off tickets any day of the week. A simple way to reward yourself with a moment of peace. Book your tickets now by visiting https://t.co/w2yAiSn6ht or the App https://t.co/ps8Dxgg3Bm</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>1776948301000</v>
+        <v>1777032069000</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2047295679458906286</t>
+          <t>2047647028012876081</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGl0hkfXsAA-dTZ.jpg', 'type': 'photo', 'id': '2047295625696358400'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGq0Hv-XgAII1HC.jpg', 'type': 'photo', 'id': '2047647025823449090'}]</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>{'name': 'رؤيا مال وأعمال', 'screenName': 'royamoney', 'followersCount': 1, 'favouritesCount': 0, 'friendsCount': 1, 'description': 'نرصد سوق المال والأعمال ببساطة.'}</t>
+          <t>{'name': 'Novo Cinemas', 'screenName': 'NovoCinemas', 'followersCount': 18752, 'favouritesCount': 2497, 'friendsCount': 1471, 'description': 'Offering you A Great Time Out with 2D, 3D &amp; luxury 7-Star VIP experiences. Contact customerservice@novocinemas.com for support.'}</t>
         </is>
       </c>
       <c r="K31" t="n">
@@ -2563,7 +2575,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>29</t>
         </is>
       </c>
       <c r="P31" t="inlineStr"/>
@@ -2574,62 +2586,62 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>https://x.com/alsawaeid_al/status/2047269288839426260</t>
+          <t>https://x.com/NovoCinemas/status/2047647028012876081</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2047269288839426260</t>
+          <t>2047647028012876081</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2047256583240073652</t>
+          <t>2047616654280953919</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://x.com/DXBMediaOffice/status/2047256583240073652</t>
+          <t>https://x.com/NovoCinemas/status/2047616654280953919</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>بنك الإمارات دبي الوطني يحقق نتائج قياسية خلال الربع الأول من عام 2026. https://t.co/pfSai48QFX</t>
+          <t>Bro life… but extra chaos 🍻🔥#VaazhaII continues to pull crowds with fun, madness and those “this is so real” moments. Watch it now at Novo Cinemas. Book on https://t.co/w2yAiSn6ht or the Novo App. https://t.co/ycxZoinbXq</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>1776938980000</v>
+        <v>1777024827000</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2047256583240073652</t>
+          <t>2047616654280953919</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGlQ8cZaQAAFjpn.jpg', 'type': 'photo', 'id': '2047256504961744896'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGqYfrJWAAAgCku.jpg', 'type': 'photo', 'id': '2047616650518593536'}]</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>{'name': 'Dubai Media Office', 'screenName': 'DXBMediaOffice', 'followersCount': 2331844, 'favouritesCount': 2, 'friendsCount': 161, 'description': 'الحساب الرسمي للمكتب الإعلامي لحكومة دبي\n\nThe official account of the Government of Dubai Media Office'}</t>
+          <t>{'name': 'Novo Cinemas', 'screenName': 'NovoCinemas', 'followersCount': 18752, 'favouritesCount': 2497, 'friendsCount': 1471, 'description': 'Offering you A Great Time Out with 2D, 3D &amp; luxury 7-Star VIP experiences. Contact customerservice@novocinemas.com for support.'}</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>4515</t>
+          <t>28</t>
         </is>
       </c>
       <c r="P32" t="inlineStr"/>
@@ -2640,35 +2652,36 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>https://x.com/alsawaeid_al/status/2047269288839426260</t>
+          <t>https://x.com/ren_fernz/status/2047629586435817682</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2047269288839426260</t>
+          <t>2047629586435817682</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2047269288839426260</t>
+          <t>2047629578990936518</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://x.com/alsawaeid_al/status/2047269288839426260</t>
+          <t>https://x.com/ren_fernz/status/2047629578990936518</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>@DXBMediaOffice @EmiratesNBD_AE https://t.co/S9u750ekZh</t>
+          <t>Very disappointed with @ENBDdeals 
+I moved from UAE since Sept 2025 and I’m paying my bills every month by 23rd. Since I’m out of country I won’t be having same time zone and I always see glitch in the ENBD app . I see the outstanding balance keep changing every time</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>1776942009000</v>
+        <v>1777027909000</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2047256583240073652</t>
+          <t>2047629578990936518</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2678,11 +2691,11 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>{'name': 'هكر اخلاقي _ مؤسسة الصقر الخفي', 'screenName': 'alsawaeid_al', 'followersCount': 97162, 'favouritesCount': 2126, 'friendsCount': 51, 'description': '#هكر_اخلاقي واستشاري مختص في مجال التقنيات الحديثة ، و حل قضايا #الابتزاز | معتمد وموثوق في وزارة التجارة .\nرقم : 7053508417'}</t>
+          <t>{'name': 'Ren', 'screenName': 'ren_fernz', 'followersCount': 4059, 'favouritesCount': 6485, 'friendsCount': 862, 'description': ''}</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -2695,14 +2708,10 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>2047256583240073652</t>
-        </is>
-      </c>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
@@ -2710,67 +2719,69 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>https://x.com/BinsalamahTariq/status/2047264777831862651</t>
+          <t>https://x.com/ren_fernz/status/2047629586435817682</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2047264777831862651</t>
+          <t>2047629586435817682</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2047264777831862651</t>
+          <t>2047629581159477750</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://x.com/BinsalamahTariq/status/2047264777831862651</t>
+          <t>https://x.com/ren_fernz/status/2047629581159477750</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Emirates NBD, the region’s 4th largest lender by market capitalization, posted a 3% year-on-year (YoY) rise in first quarter 2026 net profit to AED 6.4 billion ($1.74 billion)
-The result beat analysts’ mean estimate of AED 5.69 billion
-https://t.co/7Ieq9hEQ2y https://t.co/B8gBsDKXAX</t>
+          <t>I tried to contact in Jan and Feb on WhatsApp but was unable to contact with customer service in Feb it was due to ramdan . Last I came back to pay the bills and I saw the outstanding balance is again more . I saw the transaction history there is nothing but when I contact CS</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>1776940934000</v>
+        <v>1777027909000</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2047264777831862651</t>
+          <t>2047629578990936518</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGlYJ2sWkAAfYr8.jpg', 'type': 'photo', 'id': '2047264431940210688'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>{'name': 'Tariq BinSalamah', 'screenName': 'BinsalamahTariq', 'followersCount': 1166, 'favouritesCount': 890, 'friendsCount': 133, 'description': 'Authorized Capital Market Practitioner'}</t>
+          <t>{'name': 'Ren', 'screenName': 'ren_fernz', 'followersCount': 4059, 'favouritesCount': 6485, 'friendsCount': 862, 'description': ''}</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
         <v>0</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>2047629578990936518</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
@@ -2778,65 +2789,69 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>https://x.com/BinsalamahTariq/status/2047264777831862651</t>
+          <t>https://x.com/ren_fernz/status/2047629586435817682</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2047264777831862651</t>
+          <t>2047629586435817682</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2046984425078935918</t>
+          <t>2047629583571186141</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://x.com/BinsalamahTariq/status/2046984425078935918</t>
+          <t>https://x.com/ren_fernz/status/2047629583571186141</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>SAQL: Exchange Ticker has secured Public Investment Fund (PIF) seed funding of $100m listed on Deutsche Borse &amp;amp; London Stock Exchange.. https://t.co/3dUD3f2sht</t>
+          <t>They mentioned I got a penalty of late payment fees charges of 230AED +11AED vat. I asked them check if I got previously, so agent told me to check the application but on application there is nothing shown. So she told to check the Estatement.</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>1776874092000</v>
+        <v>1777027910000</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2046984425078935918</t>
+          <t>2047629578990936518</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGhYqBPXAAEbQop.jpg', 'type': 'photo', 'id': '2046983509550497793'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>{'name': 'Tariq BinSalamah', 'screenName': 'BinsalamahTariq', 'followersCount': 1166, 'favouritesCount': 890, 'friendsCount': 133, 'description': 'Authorized Capital Market Practitioner'}</t>
+          <t>{'name': 'Ren', 'screenName': 'ren_fernz', 'followersCount': 4059, 'favouritesCount': 6485, 'friendsCount': 862, 'description': ''}</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>219</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr"/>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>2047629581159477750</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
@@ -2844,47 +2859,45 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>https://x.com/AzzamAlAseel/status/2047263845274484876</t>
+          <t>https://x.com/ren_fernz/status/2047629586435817682</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2047263845274484876</t>
+          <t>2047629586435817682</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2046943784525599100</t>
+          <t>2047629586435817682</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2046943784525599100</t>
+          <t>https://x.com/ren_fernz/status/2047629586435817682</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>ليلة زواجك، مثل ما تتمنّى وأكثر 💍✨
-قدم على التمويل الشخصي وبهامش ربح تنافسي من #بنك_الامارات_دبي_الوطني 💙
-للتفاصيل:https://t.co/5oaojOqJ8v https://t.co/6LHBU3Yt0q</t>
+          <t>As I was late to university I thought just downloading and then going through so I just opened and saw that I have been charged on JAN and Feb and so I contacted ENBD CS again and asked them to revert the previous charges and they told me they can only remove for April which</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>1776864403000</v>
+        <v>1777027911000</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2046943784525599100</t>
+          <t>2047629578990936518</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/ext_tw_video_thumb/2046943757950480384/pu/img/mi4I-rg9GSJC7_ep.jpg', 'type': 'video', 'id': '2046943757950480384'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17361, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
+          <t>{'name': 'Ren', 'screenName': 'ren_fernz', 'followersCount': 4059, 'favouritesCount': 6485, 'friendsCount': 862, 'description': ''}</t>
         </is>
       </c>
       <c r="K36" t="n">
@@ -2894,17 +2907,21 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>937</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>2047629583571186141</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
@@ -2912,35 +2929,35 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>https://x.com/AzzamAlAseel/status/2047263845274484876</t>
+          <t>https://x.com/ren_fernz/status/2047629586435817682</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2047263845274484876</t>
+          <t>2047629586435817682</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2047263845274484876</t>
+          <t>2047629588675575900</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://x.com/AzzamAlAseel/status/2047263845274484876</t>
+          <t>https://x.com/ren_fernz/status/2047629588675575900</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA كيف التواصل معكم بخصوص شراء مديونية؟</t>
+          <t>Was yesterday and they won’t able to do for Jan and Feb. My question is why don’t the @ENBDdeals application show the late fees charges applied on my card?? If I knew I would have not made the repeated mistake. I wanted to close my ADCB Bank but as I wanted to pay the CC bills</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>1776940711000</v>
+        <v>1777027911000</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2046943784525599100</t>
+          <t>2047629578990936518</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2950,7 +2967,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>{'name': 'عزّام الأصيــل', 'screenName': 'AzzamAlAseel', 'followersCount': 0, 'favouritesCount': 15, 'friendsCount': 70, 'description': 'لا ديمومة لشيء ..'}</t>
+          <t>{'name': 'Ren', 'screenName': 'ren_fernz', 'followersCount': 4059, 'favouritesCount': 6485, 'friendsCount': 862, 'description': ''}</t>
         </is>
       </c>
       <c r="K37" t="n">
@@ -2963,16 +2980,16 @@
         <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2046943784525599100</t>
+          <t>2047629586435817682</t>
         </is>
       </c>
     </row>
@@ -2982,49 +2999,52 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>https://x.com/AzzamAlAseel/status/2047263845274484876</t>
+          <t>https://x.com/dandbdubai/status/2047628468545110433</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2047263845274484876</t>
+          <t>2047628468545110433</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2047267674904826221</t>
+          <t>2047628468545110433</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2047267674904826221</t>
+          <t>https://x.com/dandbdubai/status/2047628468545110433</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>@AzzamAlAseel مرحبا, يرجى إرسال رقم هاتفك و رقم الهوية عبر الخاص ليمكننا مساعدتك, شكرا</t>
+          <t>Breaking News 📢 Dubai Real Estate Just Entered a New Era 🌇
+▪️50/50 Strategy: Pay 50% and leverage ENBD financing for the rest.
+▪️Project Readiness: Available on premium projects at least 30% complete.
+▪️Maximum Liquidity: Grow your portfolio without tying up all your cash. https://t.co/e4xRBY8CCu</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>1776941624000</v>
+        <v>1777027644000</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2046943784525599100</t>
+          <t>2047628468545110433</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGqjLC9aIAAcfHM.jpg', 'type': 'photo', 'id': '2047628390761635840'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGqjLC8acAAmIIP.jpg', 'type': 'photo', 'id': '2047628390757462016'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGqjLDCaEAAgV9I.jpg', 'type': 'photo', 'id': '2047628390782603264'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGqjLC7awAA0pEW.jpg', 'type': 'photo', 'id': '2047628390753288192'}]</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17361, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
+          <t>{'name': 'D&amp;B Properties', 'screenName': 'dandbdubai', 'followersCount': 589, 'favouritesCount': 930, 'friendsCount': 828, 'description': 'Multi-Award Winning Real Estate Brokerage in Dubai\nSales | Leasing | Off-Plan | Commercial | Asset Management | Valuations &amp; Advisory | Holiday Homes'}</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
@@ -3037,14 +3057,10 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>2047263845274484876</t>
-        </is>
-      </c>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
@@ -3052,62 +3068,65 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>https://x.com/abd11ulla/status/2047265666320011311</t>
+          <t>https://x.com/dandbdubai/status/2047628468545110433</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2047265666320011311</t>
+          <t>2047628468545110433</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2047265666320011311</t>
+          <t>2046932416754012230</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://x.com/abd11ulla/status/2047265666320011311</t>
+          <t>https://x.com/dandbdubai/status/2046932416754012230</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE أفضل ويتفوق رغماً عن الأزمة 👏🏻</t>
+          <t>Proud to call the UAE home 🇦🇪
+The UAE continues to inspire, build, and lead and we’re proud to be part of that story.
+Here’s to growth, innovation, and everything ahead
+#UAE #ProudOfUAE #UAENationalPride #Dubai #DubaiLife https://t.co/bnUJHbF5lp</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>1776941145000</v>
+        <v>1776861692000</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2047265666320011311</t>
+          <t>2046932416754012230</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2046932359065591808/img/bJGTr1dd5W2_rytA.jpg', 'type': 'video', 'id': '2046932359065591808'}]</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>{'name': 'Abdulla', 'screenName': 'abd11ulla', 'followersCount': 2979, 'favouritesCount': 130246, 'friendsCount': 6667, 'description': 'The Emirates ( UAE ) = 🗺️'}</t>
+          <t>{'name': 'D&amp;B Properties', 'screenName': 'dandbdubai', 'followersCount': 589, 'favouritesCount': 930, 'friendsCount': 828, 'description': 'Multi-Award Winning Real Estate Brokerage in Dubai\nSales | Leasing | Off-Plan | Commercial | Asset Management | Valuations &amp; Advisory | Holiday Homes'}</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N39" t="n">
         <v>1</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>37</t>
         </is>
       </c>
       <c r="P39" t="inlineStr"/>
@@ -3118,35 +3137,35 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>https://x.com/abd11ulla/status/2047265666320011311</t>
+          <t>https://x.com/XSilverMermaidX/status/2047601280143724646</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2047265666320011311</t>
+          <t>2047601280143724646</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2047502441709797406</t>
+          <t>2047601280143724646</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://x.com/abd11ulla/status/2047502441709797406</t>
+          <t>https://x.com/XSilverMermaidX/status/2047601280143724646</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>زعيم الشرق الأوسط 🌍 ، محمد بن زايد ( بوخالد ) 🇦🇪 .</t>
+          <t>@EmiratesNBD_AE  hello, i want to check, is there an issue with the SMS server? I stopped receiving SMS after April 7th</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>1776997597000</v>
+        <v>1777021162000</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2047502441709797406</t>
+          <t>2047601280143724646</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -3156,24 +3175,24 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>{'name': 'Abdulla', 'screenName': 'abd11ulla', 'followersCount': 2979, 'favouritesCount': 130246, 'friendsCount': 6667, 'description': 'The Emirates ( UAE ) = 🗺️'}</t>
+          <t>{'name': 'Kang Hori', 'screenName': 'XSilverMermaidX', 'followersCount': 172, 'favouritesCount': 3163, 'friendsCount': 162, 'description': '🔬💼👩🏻\u200d💻🇦🇪'}</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P40" t="inlineStr"/>
@@ -3184,46 +3203,45 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>https://x.com/ForumRemittance/status/2047260484458467333</t>
+          <t>https://x.com/XSilverMermaidX/status/2047601280143724646</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2047260484458467333</t>
+          <t>2047601280143724646</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2047260484458467333</t>
+          <t>2047606015684718778</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://x.com/ForumRemittance/status/2047260484458467333</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2047606015684718778</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Emirates NBD, Dubai’s largest bank, reported a profit before tax of Dh8.2 billion for Q1 2026, up 6% year-on-year, supported by strong balance sheet growth, resilient margins, and record non-funded income.
-#EmiratesNBD #Dubai #Banking #Finance #UAE #Earnings #Q12026 https://t.co/3eCdGIZS7E</t>
+          <t>@XSilverMermaidX We have replied to your message in private</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>1776939910000</v>
+        <v>1777022291000</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2047260484458467333</t>
+          <t>2047601280143724646</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGlUfj8WAAAr12L.jpg', 'type': 'photo', 'id': '2047260406817619968'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>{'name': 'World Remittance Action Forum', 'screenName': 'ForumRemittance', 'followersCount': 15, 'favouritesCount': 0, 'friendsCount': 3, 'description': 'Empowering global money transfers | 💸 Fast, secure, and affordable remittance solutions | 🌐 Connecting families worldwide #Remittance #Fintech #GlobalPayments'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174349, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="K41" t="n">
@@ -3240,10 +3258,14 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="P41" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>2047601280143724646</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
@@ -3251,62 +3273,64 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>https://x.com/ForumRemittance/status/2047260484458467333</t>
+          <t>https://x.com/zachrose51/status/2047564934997762494</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2047260484458467333</t>
+          <t>2047564934997762494</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2046552367068258687</t>
+          <t>2047367142367191224</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://x.com/ForumRemittance/status/2046552367068258687</t>
+          <t>https://x.com/zachrose51/status/2047367142367191224</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Speedinvest launches its first flagship fund for early-growth startups across the Middle East and Africa, backed by Mubadala Investment Company, Qatar Investment Authority, and European Investment Bank, expanding its regional investment strategy.#Speedinvest #MiddleEast #Africa https://t.co/2PFCFcHWJE</t>
+          <t>We just killed cold email: Introducing Draftboard.
+The world’s first AI Sales Director that outperforms any human.
+Comment your website and we’ll find you intros to 10 dream prospects for free. https://t.co/DK7wDKVQl7</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>1776771082000</v>
+        <v>1776965339000</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2046552367068258687</t>
+          <t>2047367142367191224</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGbQfggXsAAQAwW.jpg', 'type': 'photo', 'id': '2046552320406695936'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2047366826984972288/img/qZKW_Emc0-7B9Jot.jpg', 'type': 'video', 'id': '2047366826984972288'}]</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>{'name': 'World Remittance Action Forum', 'screenName': 'ForumRemittance', 'followersCount': 15, 'favouritesCount': 0, 'friendsCount': 3, 'description': 'Empowering global money transfers | 💸 Fast, secure, and affordable remittance solutions | 🌐 Connecting families worldwide #Remittance #Fintech #GlobalPayments'}</t>
+          <t>{'name': 'Zach Roseman', 'screenName': 'zachrose51', 'followersCount': 692, 'favouritesCount': 10161, 'friendsCount': 485, 'description': 'Cold outbound is dead. Building the fix @Draftboard - map warm intro paths from your network to your prospects. Ex-CEO Mosaic Group (acq. by Bending Spoons)'}</t>
         </is>
       </c>
       <c r="K42" t="n">
-        <v>1</v>
+        <v>574</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>152</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="N42" t="n">
-        <v>1</v>
+        <v>1134</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>782043</t>
         </is>
       </c>
       <c r="P42" t="inlineStr"/>
@@ -3317,64 +3341,40 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>https://x.com/DXBMediaOffice/status/2047256960563810466</t>
+          <t>https://x.com/zachrose51/status/2047564934997762494</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2047256960563810466</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>2047256960563810466</t>
-        </is>
-      </c>
+          <t>2047564934997762494</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://x.com/DXBMediaOffice/status/2047256960563810466</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Emirates NBD reports strong results in Q1 2026. https://t.co/bdt7wIIuTc</t>
-        </is>
-      </c>
+          <t>https://x.com/undefined/status/undefined</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
       <c r="G43" t="n">
-        <v>1776939070000</v>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>2047256960563810466</t>
-        </is>
-      </c>
+        <v>1777086542741</v>
+      </c>
+      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGlRT18asAAIrl4.jpg', 'type': 'photo', 'id': '2047256906956451840'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>{'name': 'Dubai Media Office', 'screenName': 'DXBMediaOffice', 'followersCount': 2331844, 'favouritesCount': 2, 'friendsCount': 161, 'description': 'الحساب الرسمي للمكتب الإعلامي لحكومة دبي\n\nThe official account of the Government of Dubai Media Office'}</t>
-        </is>
-      </c>
-      <c r="K43" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" t="n">
-        <v>0</v>
-      </c>
-      <c r="M43" t="n">
-        <v>5</v>
-      </c>
-      <c r="N43" t="n">
-        <v>33</v>
-      </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>4150</t>
-        </is>
-      </c>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr"/>
     </row>
     <row r="44">
@@ -3383,70 +3383,69 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>https://x.com/DXBMediaOffice/status/2047256960563810466</t>
+          <t>https://x.com/zachrose51/status/2047564934997762494</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2047256960563810466</t>
+          <t>2047564934997762494</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2047277766769545352</t>
+          <t>2047564934997762494</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://x.com/HHShkMohd/status/2047277766769545352</t>
+          <t>https://x.com/zachrose51/status/2047564934997762494</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Under the directives of the President of the UAE, we launch a new government model. Within two years, 50% of government sectors, services, and operations will run on Agentic AI, making the UAE the first government globally to operate at this scale through autonomous systems.
-AI is no longer a tool. It analyses, decides, executes, and improves in real time. It will become our executive partner to enhance services, accelerate decisions, and raise efficiency.
-This transformation has a clear timeline. Two years. Performance across government will be measured by speed of adoption, quality of implementation, and mastery of AI in redesigning government work.
-We are investing in our people. Every federal employee will be trained to master AI, building one of the world’s strongest capabilities in AI-driven government.
-Implementation will be overseen by Sheikh Mansour bin Zayed, with a dedicated taskforce chaired by Mohammad Al Gergawi driving execution.
-The world is changing. Technology is accelerating. Our principle remains constant. People come first. Our goal is a government that is faster, more responsive, and more impactful.</t>
+          <t>@coiningmaxi Alright - found some of your customers: PayTabs, Telr, Network International, Magnati, Emirates NBD and Mashreq Bank. Sound right? Going to use these to track down real prospects at your dream customers and map intro paths to them</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>1776944030000</v>
+        <v>1777012497000</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2047277766769545352</t>
+          <t>2047367142367191224</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGlkRYOakAASWH_.jpg', 'type': 'photo', 'id': '2047277755340066816'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGlkRYCbIAInaJr.jpg', 'type': 'photo', 'id': '2047277755289772034'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGlkRYCaIAAG5YS.jpg', 'type': 'photo', 'id': '2047277755289706496'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGlkRYJb0AAbm_7.jpg', 'type': 'photo', 'id': '2047277755319177216'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>{'name': 'HH Sheikh Mohammed', 'screenName': 'HHShkMohd', 'followersCount': 10024602, 'favouritesCount': 1, 'friendsCount': 68, 'description': 'الحساب الرسمي لصاحب السمو الشيخ محمد بن راشد آل مكتوم  | Official account of His Highness Sheikh Mohammed bin Rashid Al Maktoum'}</t>
+          <t>{'name': 'Zach Roseman', 'screenName': 'zachrose51', 'followersCount': 692, 'favouritesCount': 10161, 'friendsCount': 485, 'description': 'Cold outbound is dead. Building the fix @Draftboard - map warm intro paths from your network to your prospects. Ex-CEO Mosaic Group (acq. by Bending Spoons)'}</t>
         </is>
       </c>
       <c r="K44" t="n">
-        <v>823</v>
+        <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>945</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>2040</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>10869</v>
+        <v>0</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>1733227</t>
-        </is>
-      </c>
-      <c r="P44" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>2047564727421964462</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
@@ -3454,65 +3453,64 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>https://x.com/Economy_ME/status/2047228305686876507</t>
+          <t>https://x.com/hkayyal/status/2047530498705195395</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2047228305686876507</t>
+          <t>2047530498705195395</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2047228305686876507</t>
+          <t>2047530181221613706</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://x.com/Economy_ME/status/2047228305686876507</t>
+          <t>https://x.com/hkayyal/status/2047530181221613706</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Emirates NBD reported record Q1 2026 results, with total income reaching AED14.4 billion ($3.92 billion), up 21% year-on-year and 13% quarter-on-quarter, driven by strong asset growth and record non-funded income.
-Profit before tax rose 6% year-on-year to AED8.2 billion, while net profit increased 3% annually and 27% quarterly to AED6.4 billion ($1.74 billion), reflecting resilient margins and solid balance sheet performance.
-@EmiratesNBD_AE 
-#EmiratesNBD #UAE #Banking #Finance #Earnings</t>
+          <t>🧵 Gulf Fintech Daily — April 24, 2026
+AI as infrastructure. Sovereign capital as catalyst. 5 stories 👇
+#GulfFintech #MENA #FinTech</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>1776932238000</v>
+        <v>1777004211000</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2047228305686876507</t>
+          <t>2047530181221613706</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGk3SqFWgAAGj6x.jpg', 'type': 'photo', 'id': '2047228299290509312'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>{'name': 'Economy Middle East', 'screenName': 'Economy_ME', 'followersCount': 4471, 'favouritesCount': 207, 'friendsCount': 12, 'description': '#EconomyMiddleEast Summit 2026\nThe Economy of Tomorrow: The UAE Emerges Stronger 🇦🇪\n📅 May 21, 2026\n📍 Rosewood, Abu Dhabi\nRegister now ⬇️'}</t>
+          <t>{'name': 'Houssam Kayyal حسام كيال', 'screenName': 'hkayyal', 'followersCount': 689, 'favouritesCount': 2385, 'friendsCount': 946, 'description': 'Managing Partner @ DefineX | Embedded Finance &amp; Digital-Payments Strategist | Ex-CRO @ FOO | Advisor to Banks &amp; Telcos'}</t>
         </is>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>26</t>
         </is>
       </c>
       <c r="P45" t="inlineStr"/>
@@ -3523,66 +3521,72 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>https://x.com/Economy_ME/status/2047228305686876507</t>
+          <t>https://x.com/hkayyal/status/2047530498705195395</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2047228305686876507</t>
+          <t>2047530498705195395</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2047281955725611430</t>
+          <t>2047530498705195395</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://x.com/Economy_ME/status/2047281955725611430</t>
+          <t>https://x.com/hkayyal/status/2047530498705195395</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Abu Dhabi Commercial Bank (ADCB) reported a record profit before tax of AED3.781 billion ($1.03 billion) in Q1 2026, up 30 percent year on year, extending its track record of profit growth to 19 consecutive quarters. The strong performance was driven by the effective implementation of strategy, a resilient business model and operational continuity throughout the period. Net profit after tax reached AED3.361 billion, translating into a return on average equity of 16.3 percent.
-#ADCB #UAEbanks #FinancialResults</t>
+          <t>3️⃣ Dubai South × Emirates NBD sign MoU for streamlined SME banking access.
+Corporate account opening + tailored banking within the free zone.
+94% of UAE businesses are SMEs. Financial onboarding friction is being systematically removed.
+#Dubai #SME #D33</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>1776945029000</v>
+        <v>1777004286000</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2047281955725611430</t>
+          <t>2047530181221613706</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGloDXAW4AAmXTI.jpg', 'type': 'photo', 'id': '2047281912541011968'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>{'name': 'Economy Middle East', 'screenName': 'Economy_ME', 'followersCount': 4471, 'favouritesCount': 207, 'friendsCount': 12, 'description': '#EconomyMiddleEast Summit 2026\nThe Economy of Tomorrow: The UAE Emerges Stronger 🇦🇪\n📅 May 21, 2026\n📍 Rosewood, Abu Dhabi\nRegister now ⬇️'}</t>
+          <t>{'name': 'Houssam Kayyal حسام كيال', 'screenName': 'hkayyal', 'followersCount': 689, 'favouritesCount': 2385, 'friendsCount': 946, 'description': 'Managing Partner @ DefineX | Embedded Finance &amp; Digital-Payments Strategist | Ex-CRO @ FOO | Advisor to Banks &amp; Telcos'}</t>
         </is>
       </c>
       <c r="K46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>162</t>
-        </is>
-      </c>
-      <c r="P46" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>2047530181221613706</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
@@ -3590,39 +3594,35 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>https://x.com/abd11ulla/status/2047246858716930242</t>
+          <t>https://x.com/abhiseksonusonu/status/2047512157030645934</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2047246858716930242</t>
+          <t>2047512157030645934</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2047246858716930242</t>
+          <t>2047512157030645934</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://x.com/abd11ulla/status/2047246858716930242</t>
+          <t>https://x.com/abhiseksonusonu/status/2047512157030645934</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>للأسف البنك من أسوء من تعامل مع الأزمة والظروف
-صافي الأرباح لم يسجل نمواً مقارنة بالفترة ذاتها من
-العام الماضي على الطرف الأخر سجل دبي الوطني نمواً
-في صافي الربح مقارنة بالفترة ذاتها من العام الماضي
-رغم الأزمة تفوق ENBD على FAB و سجل أرقاماً قياسية .</t>
+          <t>@EmiratesNBD_AE @LivBank It’s been 4 days since I raised the complaint. My due date is this Monday this delay is unacceptable. Please treat this as urgent and resolve on priority.</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>1776936661000</v>
+        <v>1776999913000</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2047246858716930242</t>
+          <t>2047512157030645934</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3632,24 +3632,24 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>{'name': 'Abdulla', 'screenName': 'abd11ulla', 'followersCount': 2979, 'favouritesCount': 130246, 'friendsCount': 6667, 'description': 'The Emirates ( UAE ) = 🗺️'}</t>
+          <t>{'name': 'A R mishra', 'screenName': 'abhiseksonusonu', 'followersCount': 0, 'favouritesCount': 0, 'friendsCount': 37, 'description': ''}</t>
         </is>
       </c>
       <c r="K47" t="n">
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>46</t>
         </is>
       </c>
       <c r="P47" t="inlineStr"/>
@@ -3660,62 +3660,62 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>https://x.com/abd11ulla/status/2047246858716930242</t>
+          <t>https://x.com/iDenville/status/2047835274818748466</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2047246858716930242</t>
+          <t>2047835274818748466</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2047502441709797406</t>
+          <t>2029505253947629989</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://x.com/abd11ulla/status/2047502441709797406</t>
+          <t>https://x.com/JDunlap1974/status/2029505253947629989</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>زعيم الشرق الأوسط 🌍 ، محمد بن زايد ( بوخالد ) 🇦🇪 .</t>
+          <t>Judge overturns election after Democrats caught ballot stuffing. https://t.co/sCEs1CS21j</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>1776997597000</v>
+        <v>1772706733000</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2047502441709797406</t>
+          <t>2029505253947629989</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/ext_tw_video_thumb/2029505138055139328/pu/img/WpN4JWq99VF-NMQD.jpg', 'type': 'video', 'id': '2029505138055139328'}]</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>{'name': 'Abdulla', 'screenName': 'abd11ulla', 'followersCount': 2979, 'favouritesCount': 130246, 'friendsCount': 6667, 'description': 'The Emirates ( UAE ) = 🗺️'}</t>
+          <t>{'name': 'JOSH DUNLAP', 'screenName': 'JDunlap1974', 'followersCount': 373880, 'favouritesCount': 120460, 'friendsCount': 44620, 'description': '🇺🇲 MAYOR OF MAGADONIA 🇺🇲 ✝️ CHRISTIAN ✝️ MAGA\n📣 📣BREAKING NEWS FIRST HERE 📣📣'}</t>
         </is>
       </c>
       <c r="K48" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="M48" t="n">
-        <v>1</v>
+        <v>279</v>
       </c>
       <c r="N48" t="n">
-        <v>4</v>
+        <v>1256</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>11948</t>
         </is>
       </c>
       <c r="P48" t="inlineStr"/>
@@ -3726,69 +3726,69 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>https://x.com/researchUSAI/status/2047227343916368335</t>
+          <t>https://x.com/iDenville/status/2047835274818748466</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2047227343916368335</t>
+          <t>2047835274818748466</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2047227343916368335</t>
+          <t>2029530832042393630</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://x.com/researchUSAI/status/2047227343916368335</t>
+          <t>https://x.com/iDenville/status/2029530832042393630</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>🇦🇪
-While Gulf economies reel from Hormuz woes..
-First Abu Dhabi Bank and Emirates NBD post strong Q1 earnings amid regional war uncertainty
-Iran's conflict closes Strait of Hormuz, slashes Gulf exports, spikes energy prices and hits jet fuel in China, India, South Korea; yet UAE lenders thrive
-Resilient banks signal UAE stability as 30-nation push led by UK, France aims to reopen strait, but IEA flags history's biggest energy threat if tensions drag</t>
+          <t>@JDunlap1974 Now audit North Carolina's primaries!!  This is Lakeshia Alston, the woman who ran for election as a REPUBLICAN and won!! https://t.co/vQrXOOfnIW</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>1776932009000</v>
+        <v>1772712831000</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2047227343916368335</t>
+          <t>2029505253947629989</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HCpXbMYbwAEvTXt.jpg', 'type': 'photo', 'id': '2029530706775621633'}]</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>{'name': 'U.S.A.I. 🇺🇸', 'screenName': 'researchUSAI', 'followersCount': 1419, 'favouritesCount': 7656, 'friendsCount': 1, 'description': "🚨 BREAKING: THE WORLD'S MOST GREATEST"}</t>
+          <t>{'name': 'DenvilleCommunity', 'screenName': 'iDenville', 'followersCount': 23512, 'favouritesCount': 181621, 'friendsCount': 23653, 'description': "Paralegal, Cert. in Veteran's Law. Content Provider for Small  \nBiz - Denville, downtowndenville, Morris County, ProudArmyMom.  \nSee my XArticles - https://t.co/jr1UygtUyx"}</t>
         </is>
       </c>
       <c r="K49" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="P49" t="inlineStr"/>
+          <t>5946</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>2029505253947629989</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
@@ -3796,39 +3796,35 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>https://x.com/researchUSAI/status/2047227343916368335</t>
+          <t>https://x.com/iDenville/status/2047835274818748466</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2047227343916368335</t>
+          <t>2047835274818748466</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2047529482358018270</t>
+          <t>2047834245423395027</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://x.com/researchUSAI/status/2047529482358018270</t>
+          <t>https://x.com/stelpetla/status/2047834245423395027</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>🇺🇸
-Remains unearthed in..
-A gruesome discovery in a Hollywood impound lot triggered a months-long investigation, culminating in murder and sex abuse charges against a 21-year-old singer
-The case originated from the shocking find in the impound lot, prompting authorities to pursue leads that exposed alleged crimes severe enough for dual felony charges against the young musician
-As the investigation wraps, the case now heads toward legal proceedings, with a detailed look revealing potential trials that could spotlight vulnerabilities in entertainment circles and impound security protocols</t>
+          <t>@iDenville @JDunlap1974 How are they allowed to enter a bank? I’m not allowed to go in my bank wearing sunglasses or a hat.</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>1777004044000</v>
+        <v>1777076705000</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2047529482358018270</t>
+          <t>2029505253947629989</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3838,11 +3834,11 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>{'name': 'U.S.A.I. 🇺🇸', 'screenName': 'researchUSAI', 'followersCount': 1419, 'favouritesCount': 7656, 'friendsCount': 1, 'description': "🚨 BREAKING: THE WORLD'S MOST GREATEST"}</t>
+          <t>{'name': 'Stella Pet 🇺🇸', 'screenName': 'stelpetla', 'followersCount': 685, 'favouritesCount': 27509, 'friendsCount': 1544, 'description': 'GenX/Jersey Girl. 🇺🇸 Mayflower Descendant, DAR. 12th generation American. Trump X 3'}</t>
         </is>
       </c>
       <c r="K50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
@@ -3851,10 +3847,18 @@
         <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
-      </c>
-      <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>2029530832042393630</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
@@ -3862,47 +3866,45 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>https://x.com/Fyan2016/status/2047245588618465658</t>
+          <t>https://x.com/iDenville/status/2047835274818748466</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2047245588618465658</t>
+          <t>2047835274818748466</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2047245588618465658</t>
+          <t>2047835274818748466</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://x.com/Fyan2016/status/2047245588618465658</t>
+          <t>https://x.com/iDenville/status/2047835274818748466</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>💰 سجل بنك بنود الإمارات (Emirates NBD)، أكبر البنوك أصولاً في دبي، ارتفاعاً في صافي أرباحه للربع الأول من عام 2026.
-قفز صافي الأرباح بنسبة 3% ليصل إلى 6.4 مليار درهم إماراتي (1.7 مليار دولار)، مدعوماً بنمو الإيداع والإقراض، بينما ارتفع إجمالي الدخل 21% مسجلاً 14.4 مليار درهم.
-#اقتصاد #الخليج #بنوك #الإمارات</t>
+          <t>@stelpetla @JDunlap1974 Most of the Islamic banking is done through a different system, Bai' al-Sarf.  They have their own banks: Emirates Islamic Bank, Al Rajhi Bank, Abu Dhabi Islamic Bank and more.  They come with apps.</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>1776936358000</v>
+        <v>1777076951000</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2047245588618465658</t>
+          <t>2029505253947629989</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGlHAhMXgAAU3WA.jpg', 'type': 'photo', 'id': '2047245579852414976'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>{'name': 'فايز المالكي', 'screenName': 'Fyan2016', 'followersCount': 262, 'favouritesCount': 10399, 'friendsCount': 1796, 'description': 'مهندس.. ماجستير ادارة اعمال تنفيذية.. مهتم بالعقار والديكور والتقنيات الزراعية الحديثة والطبيعة والفيزياء واشياء اخرى'}</t>
+          <t>{'name': 'DenvilleCommunity', 'screenName': 'iDenville', 'followersCount': 23512, 'favouritesCount': 181621, 'friendsCount': 23653, 'description': "Paralegal, Cert. in Veteran's Law. Content Provider for Small  \nBiz - Denville, downtowndenville, Morris County, ProudArmyMom.  \nSee my XArticles - https://t.co/jr1UygtUyx"}</t>
         </is>
       </c>
       <c r="K51" t="n">
@@ -3915,14 +3917,18 @@
         <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="P51" t="inlineStr"/>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>2047834245423395027</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
@@ -3930,55 +3936,52 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>https://x.com/Fyan2016/status/2047245588618465658</t>
+          <t>https://x.com/abhiseksonusonu/status/2047511223839908158</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2047245588618465658</t>
+          <t>2047511223839908158</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2047382489803461045</t>
+          <t>2047511223839908158</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>https://x.com/Fyan2016/status/2047382489803461045</t>
+          <t>https://x.com/abhiseksonusonu/status/2047511223839908158</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>🌍 مسؤول إيراني يزعم أن طهران بدأت بتلقي إيرادات رسوم العبور من مضيق هرمز
-نقلت وكالة "تسنيم" عن نائب رئيس البرلمان الإيراني، حميد رضا حاجي بابائي، أن أول إيرادات الرسوم المفروضة على المضيق قد أودعت في حساب البنك المركزي.
-في سياق متصل، كشفت بيانات ملاحية عن عبور 187 سفينة وناقلة نفط المضيق منذ إغلاقه في 4 مارس الماضي، بمتوسط 4 سفن يومياً، منها 23% مسجلة في الصين.
-#الخليج #الشرق_الأوسط #اقتصاد #جيوسياسة #طاقة</t>
+          <t>@LivBank @EmiratesNBD_AE I deposited cash via ENBD ATM toward my credit card on 21st April but amount got stuck. Complaint already raised, yet the amount is still not credited. My due date is this Monday. Request urgent resolution and credit of funds.</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>1776968998000</v>
+        <v>1776999691000</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2047382489803461045</t>
+          <t>2047511223839908158</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGnDhajWQAAyt9N.jpg', 'type': 'photo', 'id': '2047382484447281152'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>{'name': 'فايز المالكي', 'screenName': 'Fyan2016', 'followersCount': 262, 'favouritesCount': 10399, 'friendsCount': 1796, 'description': 'مهندس.. ماجستير ادارة اعمال تنفيذية.. مهتم بالعقار والديكور والتقنيات الزراعية الحديثة والطبيعة والفيزياء واشياء اخرى'}</t>
+          <t>{'name': 'A R mishra', 'screenName': 'abhiseksonusonu', 'followersCount': 0, 'favouritesCount': 0, 'friendsCount': 37, 'description': ''}</t>
         </is>
       </c>
       <c r="K52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M52" t="n">
         <v>0</v>
@@ -3988,7 +3991,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>67</t>
         </is>
       </c>
       <c r="P52" t="inlineStr"/>
@@ -3999,35 +4002,35 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>https://x.com/TheNationalNews/status/2047226752414421132</t>
+          <t>https://x.com/abhiseksonusonu/status/2047511223839908158</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2047226752414421132</t>
+          <t>2047511223839908158</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2047226752414421132</t>
+          <t>2047534633697308773</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://x.com/TheNationalNews/status/2047226752414421132</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2047534633697308773</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>First Abu Dhabi Bank and Emirates NBD report strong first-quarter earnings despite war uncertainty https://t.co/IoAlA6QA7W</t>
+          <t>@abhiseksonusonu We regret to hear you had an unpleasant experience, please share with us your concern from your registered email address for further communication to livsocialconnect@liv.me and tag the case reference number #1001503 in the subject line.</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>1776931868000</v>
+        <v>1777005272000</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2047226752414421132</t>
+          <t>2047511223839908158</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -4037,27 +4040,31 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>{'name': 'The National', 'screenName': 'TheNationalNews', 'followersCount': 1078350, 'favouritesCount': 3463, 'friendsCount': 206, 'description': "The world has borders. Our stories don't."}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174349, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="K53" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>1108</t>
-        </is>
-      </c>
-      <c r="P53" t="inlineStr"/>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>2047511223839908158</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
@@ -4065,45 +4072,48 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>https://x.com/ReutersWorld/status/2047218961809277291</t>
+          <t>https://x.com/emiratesislamic/status/2047717990762782723</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2047218961809277291</t>
+          <t>2047717990762782723</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2047218961809277291</t>
+          <t>2047717988195852322</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://x.com/ReutersWorld/status/2047218961809277291</t>
+          <t>https://x.com/emiratesislamic/status/2047717988195852322</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Emirates NBD posts quarterly profit rise in first results since Iran conflict https://t.co/v7FHKB736C https://t.co/v7FHKB736C</t>
+          <t>🇦🇪 We salute the nation’s heroes 
+We value your commitment and have designed exclusive banking benefits for your peace of mind.
+📈 Attractive finance profit rates
+🏦 Zero processing fees https://t.co/Q8zlLDLLW1</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>1776930010000</v>
+        <v>1777048987000</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2047218961809277291</t>
+          <t>2047717988195852322</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGr0p_HW8AA45jd.jpg', 'type': 'photo', 'id': '2047717982747422720'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGr0qJzWcAAnD8P.jpg', 'type': 'photo', 'id': '2047717985616293888'}]</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>{'name': 'Reuters World', 'screenName': 'ReutersWorld', 'followersCount': 1026793, 'favouritesCount': 10, 'friendsCount': 161, 'description': 'Your source for top international news and analysis.'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18451, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="K54" t="n">
@@ -4113,14 +4123,14 @@
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>2945</t>
+          <t>42</t>
         </is>
       </c>
       <c r="P54" t="inlineStr"/>
@@ -4131,35 +4141,40 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>https://x.com/ReutersWorld/status/2047218961809277291</t>
+          <t>https://x.com/emiratesislamic/status/2047717990762782723</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2047218961809277291</t>
+          <t>2047717990762782723</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2047227568915403232</t>
+          <t>2047717990762782723</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>https://x.com/doraxtalk/status/2047227568915403232</t>
+          <t>https://x.com/emiratesislamic/status/2047717990762782723</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>@ReutersWorld Ok</t>
+          <t>⏳Payment holidays
+🎁 Exclusive prizes with Kunooz Millionaire Account
+Terms and conditions apply.
+Know more
+https://t.co/OfDhWyedzP
+#EmiratesIslamic #FrontlineHeroes</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>1776932062000</v>
+        <v>1777048988000</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2047218961809277291</t>
+          <t>2047717988195852322</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -4169,7 +4184,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>{'name': 'Dora', 'screenName': 'doraxtalk', 'followersCount': 944, 'favouritesCount': 2651, 'friendsCount': 988, 'description': 'Comentando sobre tudo!'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18451, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="K55" t="n">
@@ -4186,12 +4201,12 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>26</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>2047218961809277291</t>
+          <t>2047717988195852322</t>
         </is>
       </c>
     </row>
@@ -4201,45 +4216,47 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>https://x.com/NikunjSOF/status/2047219745053917579</t>
+          <t>https://x.com/ABCinGCC/status/2047575014564921667</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2047219745053917579</t>
+          <t>2047575014564921667</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2047219745053917579</t>
+          <t>2047575014564921667</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://x.com/NikunjSOF/status/2047219745053917579</t>
+          <t>https://x.com/ABCinGCC/status/2047575014564921667</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>The paperwork is nearly finished. By the first week of June, Emirates NBD will officially become the majority owner, and RBL Bank will begin operating as a foreign-owned subsidiary. While it is difficult to predict exactly how aggressive the new management will be or what their specific plans are, having such a strong promoter will definitely help RBL Bank’s stability and growth.</t>
+          <t>Emirates Islamic has reported an operating profit of AED1.1 billion ($299.52 million) for the quarter ending March 31, 2026, 7% growth over the same period last year.
+Read more on https://t.co/I3d8g2xghd
+#ABCNews #Profit #Banking #FinancialInstitution https://t.co/jfJF6uK62j</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>1776930197000</v>
+        <v>1777014900000</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2047219745053917579</t>
+          <t>2047575014564921667</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGl1UAxasAAkYXs.jpg', 'type': 'photo', 'id': '2047296492281704448'}]</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>{'name': 'CA Nikunj', 'screenName': 'NikunjSOF', 'followersCount': 486, 'favouritesCount': 1776, 'friendsCount': 247, 'description': 'Equity &amp; Mutual Fund | Direct/ indirect Tax | Chartered Accountant\n\nhttps://t.co/13qe7OF4yb\n\nDM or email at nrchowdhary@gmail.com'}</t>
+          <t>{'name': 'Arabian Business Community (ABC GCC)', 'screenName': 'ABCinGCC', 'followersCount': 355, 'favouritesCount': 8, 'friendsCount': 180, 'description': 'Official Twitter of the Arabian Business Community (ABC). We’ll be tweeting about business news and popular business categories in the Gulf region.'}</t>
         </is>
       </c>
       <c r="K56" t="n">
@@ -4256,7 +4273,7 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P56" t="inlineStr"/>
@@ -4267,51 +4284,51 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>https://x.com/NikunjSOF/status/2047219745053917579</t>
+          <t>https://x.com/ABCinGCC/status/2047575014564921667</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2047219745053917579</t>
+          <t>2047575014564921667</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2047215759290769819</t>
+          <t>2047597663634457003</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://x.com/NikunjSOF/status/2047215759290769819</t>
+          <t>https://x.com/ABCinGCC/status/2047597663634457003</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>E2E Networks is a Service Provider (Cloud): They buy GPUs, host them in their own data centers, and "rent" the power to customers on a monthly/hourly basis.
-Netweb Technologies is a Manufacturer (OEM): They design and build the physical supercomputers and AI servers. They make money by "selling" the hardware and software directly to companies or the government to own.
-In simple terms: Netweb is the car manufacturer (selling the vehicle), while E2E is the taxi service (renting the ride).</t>
+          <t>UAE-based @AziziGroup  Developments has announced that construction at Beach Oasis II - its vibrant mixed-use community in the dynamic, rapidly growing Dubai Studio City - has reached 43% completion.
+Read more on https://t.co/Y5AVR722nO
+#ABCNews #Developments #BeachOasis #UAE https://t.co/eVcDwo33OV</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>1776929247000</v>
+        <v>1777020300000</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2047215759290769819</t>
+          <t>2047597663634457003</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGl180kaQAAsBhe.jpg', 'type': 'photo', 'id': '2047297193380560896'}]</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>{'name': 'CA Nikunj', 'screenName': 'NikunjSOF', 'followersCount': 486, 'favouritesCount': 1776, 'friendsCount': 247, 'description': 'Equity &amp; Mutual Fund | Direct/ indirect Tax | Chartered Accountant\n\nhttps://t.co/13qe7OF4yb\n\nDM or email at nrchowdhary@gmail.com'}</t>
+          <t>{'name': 'Arabian Business Community (ABC GCC)', 'screenName': 'ABCinGCC', 'followersCount': 355, 'favouritesCount': 8, 'friendsCount': 180, 'description': 'Official Twitter of the Arabian Business Community (ABC). We’ll be tweeting about business news and popular business categories in the Gulf region.'}</t>
         </is>
       </c>
       <c r="K57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
@@ -4320,11 +4337,11 @@
         <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>14</t>
         </is>
       </c>
       <c r="P57" t="inlineStr"/>
@@ -4335,46 +4352,49 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>https://x.com/timesofdubai_/status/2047222852135621054</t>
+          <t>https://x.com/emiratesislamic/status/2047556140431556611</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2047222852135621054</t>
+          <t>2047556140431556611</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2047222852135621054</t>
+          <t>2047556140431556611</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://x.com/timesofdubai_/status/2047222852135621054</t>
+          <t>https://x.com/emiratesislamic/status/2047556140431556611</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dubai South and Emirates NBD sign a strategic partnership to support businesses, enhance financial solutions, and drive economic growth across Dubai’s dynamic ecosystem.
-#DubaiSouth #EmiratesNBD #DubaiEconomy #BusinessGrowth #UAE #Innovation #SMEs #Entrepreneurs #FutureDubai https://t.co/PU7c1kWtMA</t>
+          <t>You have an unpaid fine – click here
+Do not fall for the traps. Stay alert to scams.
+#EIAgainstFraud with Emirates Islamic.
+#TogetherAgainstFraud
+https://t.co/y7eSpGNdfk</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>1776930938000</v>
+        <v>1777010400000</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2047222852135621054</t>
+          <t>2047556140431556611</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGkyVJiaIAEMiJn.jpg', 'type': 'photo', 'id': '2047222844535480321'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>{'name': 'Times of Dubai', 'screenName': 'timesofdubai_', 'followersCount': 65, 'favouritesCount': 250, 'friendsCount': 12, 'description': 'Latest Dubai &amp; Gulf news, breaking news, exclusive insights &amp; everything in between!  A part of GH Media Network LLC'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18451, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="K58" t="n">
@@ -4391,7 +4411,7 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>37</t>
         </is>
       </c>
       <c r="P58" t="inlineStr"/>
@@ -4402,65 +4422,65 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>https://x.com/SNABusiness/status/2047217611763834945</t>
+          <t>https://x.com/emiratesislamic/status/2047556140431556611</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2047217611763834945</t>
+          <t>2047556140431556611</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2047217611763834945</t>
+          <t>2047717988195852322</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://x.com/SNABusiness/status/2047217611763834945</t>
+          <t>https://x.com/emiratesislamic/status/2047717988195852322</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>إيرادات "الإمارات دبي الوطني" تهزم التوقعات وتصل إلى 14.4 مليار درهم خلال الربع الأول.. بنمو 21 بالمئة على أساس سنوي
-#اقتصاد_سكاي 
-#البنوك #الإمارات 
-#ENBD   https://t.co/EmGP9DqiNz</t>
+          <t>🇦🇪 We salute the nation’s heroes 
+We value your commitment and have designed exclusive banking benefits for your peace of mind.
+📈 Attractive finance profit rates
+🏦 Zero processing fees https://t.co/Q8zlLDLLW1</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>1776929688000</v>
+        <v>1777048987000</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2047217611763834945</t>
+          <t>2047717988195852322</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGr0p_HW8AA45jd.jpg', 'type': 'photo', 'id': '2047717982747422720'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGr0qJzWcAAnD8P.jpg', 'type': 'photo', 'id': '2047717985616293888'}]</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>{'name': 'اقتصاد سكاي نيوز عربية', 'screenName': 'SNABusiness', 'followersCount': 221871, 'favouritesCount': 32, 'friendsCount': 2, 'description': 'مصدرك الموثوق للمعلومة الاقتصادية'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18451, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="K59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>858</t>
+          <t>42</t>
         </is>
       </c>
       <c r="P59" t="inlineStr"/>
@@ -4471,66 +4491,65 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>https://x.com/SNABusiness/status/2047217611763834945</t>
+          <t>https://x.com/emiratesislamic/status/2047631640168374617</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2047217611763834945</t>
+          <t>2047631640168374617</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2047330009199817002</t>
+          <t>2047631640168374617</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://x.com/SNABusiness/status/2047330009199817002</t>
+          <t>https://x.com/emiratesislamic/status/2047631640168374617</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>دبي تعيد رسم خارطة المستقبل.. مشروع "الخط الذهبي" لمترو دبي ينطلق باستثمارات 34 مليار درهم، ليعزز ربط المدينة ويقود مرحلة جديدة من النمو.
-@KhaledKibbiSKY 
-#مترو_دبي #دبي #الإمارات 
-#اقتصاد_بلس 
-#اقتصاد_سكاي https://t.co/5bfv7kZBTw</t>
+          <t>Get a guaranteed iPhone 17 when you apply for an Emirates Islamic Personal Finance.
+Also, enjoy exclusive benefits:
+📊 Profit rates starting from 2.59% flat p.a.(approximately equivalent to 4.74% p.a. reducing profit rate)
+🏦 Finance amount of up to AED 4,000,000 https://t.co/QSbM2ZKbuH</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>1776956486000</v>
+        <v>1777028400000</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2047330009199817002</t>
+          <t>2047631640168374617</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2047329662007922688/img/2MYlnJ1RfGnjH8aB.jpg', 'type': 'video', 'id': '2047329662007922688'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGp7wFoXwAAtDsB.jpg', 'type': 'photo', 'id': '2047585046668754944'}]</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>{'name': 'اقتصاد سكاي نيوز عربية', 'screenName': 'SNABusiness', 'followersCount': 221871, 'favouritesCount': 32, 'friendsCount': 2, 'description': 'مصدرك الموثوق للمعلومة الاقتصادية'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18451, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="K60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>5077</t>
+          <t>27</t>
         </is>
       </c>
       <c r="P60" t="inlineStr"/>
@@ -4541,46 +4560,49 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>https://x.com/AlArabiya_Bn/status/2047215137723973688</t>
+          <t>https://x.com/emiratesislamic/status/2047631640168374617</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2047215137723973688</t>
+          <t>2047631640168374617</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2047215137723973688</t>
+          <t>2047631643901390924</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>https://x.com/AlArabiya_Bn/status/2047215137723973688</t>
+          <t>https://x.com/emiratesislamic/status/2047631643901390924</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>بنك ENBD: نقوم بدعم العملاء عبر إجراءات تشمل إعفاءات أو تأجيل الرسوم لمساعدة الشركات على التكيف مع الظروف الحالية
-#العربية_Business https://t.co/KdnwaQVmL6</t>
+          <t>✈️Payment holiday up to 6 months 
+🔒 Complimentary Takaful coverage
+Offer valid until 30 April 2026.
+T&amp;amp;Cs apply.
+https://t.co/ZafvBWp0Cl</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>1776929098000</v>
+        <v>1777028401000</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2047215137723973688</t>
+          <t>2047631640168374617</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGkrUNxXQAA-hXR.jpg', 'type': 'video', 'id': '2047214999056076800'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>{'name': 'العربية Business', 'screenName': 'AlArabiya_Bn', 'followersCount': 1995732, 'favouritesCount': 0, 'friendsCount': 53, 'description': 'المصدر الرئيسي لأخبار الاقتصاد والأعمال في الشرق الأوسط @AlArabiya'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18451, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="K61" t="n">
@@ -4590,17 +4612,21 @@
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
         <v>0</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>1348</t>
-        </is>
-      </c>
-      <c r="P61" t="inlineStr"/>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>2047631640168374617</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
@@ -4608,65 +4634,65 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>https://x.com/AlArabiya_Bn/status/2047215137723973688</t>
+          <t>https://x.com/emiratesislamic/status/2047631640168374617</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2047215137723973688</t>
+          <t>2047631640168374617</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2047420244361154671</t>
+          <t>2047717988195852322</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>https://x.com/AlArabiya_Bn/status/2047420244361154671</t>
+          <t>https://x.com/emiratesislamic/status/2047717988195852322</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>من #الرياض إلى #اسطنبول بتوقف واحد!
-سيارة كهربائية ثورية في #الصين، فيما المنافسة تشتعل بين BYD وCATL.. لكن أين #تسلا؟ وأين فخر الصناعة الألمانية؟
-@OAlladan 
-#العربية_Business https://t.co/hsUDzuQOdC</t>
+          <t>🇦🇪 We salute the nation’s heroes 
+We value your commitment and have designed exclusive banking benefits for your peace of mind.
+📈 Attractive finance profit rates
+🏦 Zero processing fees https://t.co/Q8zlLDLLW1</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>1776978000000</v>
+        <v>1777048987000</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2047420244361154671</t>
+          <t>2047717988195852322</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2047394401249353728/img/lhOeFsdI9JVbFJvz.jpg', 'type': 'video', 'id': '2047394401249353728'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGr0p_HW8AA45jd.jpg', 'type': 'photo', 'id': '2047717982747422720'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGr0qJzWcAAnD8P.jpg', 'type': 'photo', 'id': '2047717985616293888'}]</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>{'name': 'العربية Business', 'screenName': 'AlArabiya_Bn', 'followersCount': 1995732, 'favouritesCount': 0, 'friendsCount': 53, 'description': 'المصدر الرئيسي لأخبار الاقتصاد والأعمال في الشرق الأوسط @AlArabiya'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18451, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="K62" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>215</v>
+        <v>1</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>9318</t>
+          <t>44</t>
         </is>
       </c>
       <c r="P62" t="inlineStr"/>
@@ -4677,64 +4703,69 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>https://x.com/77dd14cbca18474/status/2047207203501973938</t>
+          <t>https://x.com/emiratesislamic/status/2047657988064727443</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2047207203501973938</t>
+          <t>2047657988064727443</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2047193752767193369</t>
+          <t>2047657988064727443</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2047193752767193369</t>
+          <t>https://x.com/emiratesislamic/status/2047657988064727443</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>This is the ‘snowball effect’ your savings love.
-Guess and drop your answer below.
-#ENBDRiddleOfTheWeek #GrowYourMoney #SmartSaving https://t.co/FZ9IMHLqZg</t>
+          <t>نقدم لك تجربة مصرفية مميزة مع حساب ALPHA للأبناء، الذي يوفر:
+📱تطبيق للخدمات المصرفية عبر الهاتف المتحرك مخصص لأبنائك
+💳 بطاقة خصم للأبناء
+⭐عروض وخصومات حصرية
+🎁مكافأة بقيمة 100 درهم بمناسبة يوم ميلاد الأبناء
+🏆جوائز نقدية يومية وشهرية
+علمهم صغار!
+تطبق الشروط والأحكام. https://t.co/j3JLeVQTou</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>1776924000000</v>
+        <v>1777034682000</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2047193752767193369</t>
+          <t>2047657988064727443</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGfmSCYWYAAeGEP.jpg', 'type': 'photo', 'id': '2046857753214214144'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGq-FHDWUAA0A9i.jpg', 'type': 'photo', 'id': '2047657975595028480'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGq-FZ7WkAAuMQK.jpg', 'type': 'photo', 'id': '2047657980661764096'}]</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174341, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18451, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="K63" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>61</t>
         </is>
       </c>
       <c r="P63" t="inlineStr"/>
@@ -4745,45 +4776,48 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>https://x.com/77dd14cbca18474/status/2047207203501973938</t>
+          <t>https://x.com/emiratesislamic/status/2047657988064727443</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2047207203501973938</t>
+          <t>2047657988064727443</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2047202084769206665</t>
+          <t>2047717988195852322</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>https://x.com/77dd14cbca18474/status/2047202084769206665</t>
+          <t>https://x.com/emiratesislamic/status/2047717988195852322</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Worst bank ever iam following up since 1 year for cancellation of wealth account still nothing</t>
+          <t>🇦🇪 We salute the nation’s heroes 
+We value your commitment and have designed exclusive banking benefits for your peace of mind.
+📈 Attractive finance profit rates
+🏦 Zero processing fees https://t.co/Q8zlLDLLW1</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>1776925986000</v>
+        <v>1777048987000</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2047193752767193369</t>
+          <t>2047717988195852322</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGr0p_HW8AA45jd.jpg', 'type': 'photo', 'id': '2047717982747422720'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGr0qJzWcAAnD8P.jpg', 'type': 'photo', 'id': '2047717985616293888'}]</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>{'name': 'Abid Khan', 'screenName': '77dd14cbca18474', 'followersCount': 0, 'favouritesCount': 9, 'friendsCount': 21, 'description': ''}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18451, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="K64" t="n">
@@ -4796,18 +4830,14 @@
         <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="P64" t="inlineStr">
-        <is>
-          <t>2047193752767193369</t>
-        </is>
-      </c>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
@@ -4815,45 +4845,47 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>https://x.com/77dd14cbca18474/status/2047207203501973938</t>
+          <t>https://x.com/emiratesislamic/status/2047717920193622257</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2047207203501973938</t>
+          <t>2047717920193622257</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2047206058129559636</t>
+          <t>2047717917324710124</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2047206058129559636</t>
+          <t>https://x.com/emiratesislamic/status/2047717917324710124</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Hi, thank you for sharing your feedback. We’re sorry that you had experienced this, it is not what we expect our customers to feel nor see. We kindly request you to send us more details and your registered mobile number via social@emiratesnbd.com and quote Case #1001012 for us to assist you better. Thanks.</t>
+          <t>🇦🇪 تحية تقدير وامتنان لأبطال الوطن
+تقديراً لإخلاصك وتفانيك في خدمة الوطن، قمنا بتصميم باقة حصرية من المزايا المصرفية لنمنحك راحة البال.
+📈 معدلات أرباح مميزة على التمويل https://t.co/DrYnMIk6Zd</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>1776926934000</v>
+        <v>1777048970000</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2047193752767193369</t>
+          <t>2047717917324710124</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGr0l1oXYAEHNu8.jpg', 'type': 'photo', 'id': '2047717911482032129'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGr0mAsWkAIOAAv.jpg', 'type': 'photo', 'id': '2047717914451546114'}]</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174341, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18451, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="K65" t="n">
@@ -4870,14 +4902,10 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="P65" t="inlineStr">
-        <is>
-          <t>2047202084769206665</t>
-        </is>
-      </c>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
@@ -4885,35 +4913,41 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>https://x.com/77dd14cbca18474/status/2047207203501973938</t>
+          <t>https://x.com/emiratesislamic/status/2047717920193622257</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2047207203501973938</t>
+          <t>2047717920193622257</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2047207203501973938</t>
+          <t>2047717920193622257</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>https://x.com/77dd14cbca18474/status/2047207203501973938</t>
+          <t>https://x.com/emiratesislamic/status/2047717920193622257</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE I did before also no results we will doing also now. Check your email</t>
+          <t>🏦 بدون رسوم إجراءات
+⏳ تأجيل الأقساط
+🎁 جوائز حصرية مع حساب كنوز المليونير
+تطبق الشروط والأحكام.
+لمعرفة المزيد، تفضل بزيارة
+https://t.co/N2GRIcHWnS
+#الإمارات_الإسلامي #أبطال_الوطن</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>1776927207000</v>
+        <v>1777048971000</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2047193752767193369</t>
+          <t>2047717917324710124</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4923,11 +4957,11 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>{'name': 'Abid Khan', 'screenName': '77dd14cbca18474', 'followersCount': 0, 'favouritesCount': 9, 'friendsCount': 21, 'description': ''}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18451, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="K66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
@@ -4940,12 +4974,12 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>217</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>2047206058129559636</t>
+          <t>2047717917324710124</t>
         </is>
       </c>
     </row>
@@ -4955,49 +4989,51 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>https://x.com/77dd14cbca18474/status/2047207203501973938</t>
+          <t>https://x.com/emiratesislamic/status/2047717917324710124</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2047207203501973938</t>
+          <t>2047717917324710124</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2047213444760273209</t>
+          <t>2047717917324710124</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2047213444760273209</t>
+          <t>https://x.com/emiratesislamic/status/2047717917324710124</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>@77dd14cbca18474 We sincerely apologize for the inconvenience caused to you. We will review your email and will take necessary action and update you via email as soon as possible. Thanks</t>
+          <t>🇦🇪 تحية تقدير وامتنان لأبطال الوطن
+تقديراً لإخلاصك وتفانيك في خدمة الوطن، قمنا بتصميم باقة حصرية من المزايا المصرفية لنمنحك راحة البال.
+📈 معدلات أرباح مميزة على التمويل https://t.co/DrYnMIk6Zd</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>1776928695000</v>
+        <v>1777048970000</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2047193752767193369</t>
+          <t>2047717917324710124</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGr0l1oXYAEHNu8.jpg', 'type': 'photo', 'id': '2047717911482032129'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGr0mAsWkAIOAAv.jpg', 'type': 'photo', 'id': '2047717914451546114'}]</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174341, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18451, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="K67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
@@ -5010,14 +5046,10 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="P67" t="inlineStr">
-        <is>
-          <t>2047207203501973938</t>
-        </is>
-      </c>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
@@ -5025,47 +5057,51 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>https://x.com/uaefintechvibes/status/2047212376362234309</t>
+          <t>https://x.com/emiratesislamic/status/2047717917324710124</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2047212376362234309</t>
+          <t>2047717917324710124</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2047212376362234309</t>
+          <t>2047717920193622257</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>https://x.com/uaefintechvibes/status/2047212376362234309</t>
+          <t>https://x.com/emiratesislamic/status/2047717920193622257</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dubai South and Emirates NBD have just signed an MoU to make SME banking in UAE faster, smoother, and more accessible! This is a massive step forward for the Ease of Doing Business in UAE.
-https://t.co/IBP0r0ZWHq
-#dubaisouth #smebanking https://t.co/aJmPeuMCjZ</t>
+          <t>🏦 بدون رسوم إجراءات
+⏳ تأجيل الأقساط
+🎁 جوائز حصرية مع حساب كنوز المليونير
+تطبق الشروط والأحكام.
+لمعرفة المزيد، تفضل بزيارة
+https://t.co/N2GRIcHWnS
+#الإمارات_الإسلامي #أبطال_الوطن</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>1776928440000</v>
+        <v>1777048971000</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2047212376362234309</t>
+          <t>2047717917324710124</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGkomqsagAAL8el.jpg', 'type': 'photo', 'id': '2047212150377316352'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>{'name': 'UAE Fintechvibes', 'screenName': 'uaefintechvibes', 'followersCount': 0, 'favouritesCount': 16, 'friendsCount': 29, 'description': 'Latest Fintech News in the UAE - We provide daily fintech news happening within the UAE. \nSend your news at info@uaefintechvibes.com'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18451, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="K68" t="n">
@@ -5078,14 +5114,18 @@
         <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="P68" t="inlineStr"/>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>2047717917324710124</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
@@ -5093,47 +5133,52 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>https://x.com/uaefintechvibes/status/2047212376362234309</t>
+          <t>https://x.com/emiratesislamic/status/2047717917324710124</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2047212376362234309</t>
+          <t>2047717917324710124</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2046938769685938442</t>
+          <t>2047657988064727443</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>https://x.com/uaefintechvibes/status/2046938769685938442</t>
+          <t>https://x.com/emiratesislamic/status/2047657988064727443</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>The @DIFC has officially announced a roadmap to become the world’s first AI-native financial center. 
-https://t.co/9ElZqfVH4o
-#FinancialNews #fintech https://t.co/Wuonrb13Ou</t>
+          <t>نقدم لك تجربة مصرفية مميزة مع حساب ALPHA للأبناء، الذي يوفر:
+📱تطبيق للخدمات المصرفية عبر الهاتف المتحرك مخصص لأبنائك
+💳 بطاقة خصم للأبناء
+⭐عروض وخصومات حصرية
+🎁مكافأة بقيمة 100 درهم بمناسبة يوم ميلاد الأبناء
+🏆جوائز نقدية يومية وشهرية
+علمهم صغار!
+تطبق الشروط والأحكام. https://t.co/j3JLeVQTou</t>
         </is>
       </c>
       <c r="G69" t="n">
-        <v>1776863207000</v>
+        <v>1777034682000</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2046938769685938442</t>
+          <t>2047657988064727443</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGgv7-QbYAASlaK.jpg', 'type': 'photo', 'id': '2046938738010578944'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGq-FHDWUAA0A9i.jpg', 'type': 'photo', 'id': '2047657975595028480'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGq-FZ7WkAAuMQK.jpg', 'type': 'photo', 'id': '2047657980661764096'}]</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>{'name': 'UAE Fintechvibes', 'screenName': 'uaefintechvibes', 'followersCount': 0, 'favouritesCount': 16, 'friendsCount': 29, 'description': 'Latest Fintech News in the UAE - We provide daily fintech news happening within the UAE. \nSend your news at info@uaefintechvibes.com'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18451, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="K69" t="n">
@@ -5146,11 +5191,11 @@
         <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>61</t>
         </is>
       </c>
       <c r="P69" t="inlineStr"/>
@@ -5161,64 +5206,69 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>https://x.com/77dd14cbca18474/status/2047202084769206665</t>
+          <t>https://x.com/emiratesislamic/status/2047657974936604881</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2047202084769206665</t>
+          <t>2047657974936604881</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2047193752767193369</t>
+          <t>2047657960227176876</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2047193752767193369</t>
+          <t>https://x.com/emiratesislamic/status/2047657960227176876</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>This is the ‘snowball effect’ your savings love.
-Guess and drop your answer below.
-#ENBDRiddleOfTheWeek #GrowYourMoney #SmartSaving https://t.co/FZ9IMHLqZg</t>
+          <t>نقدم لك تجربة مصرفية مميزة مع حساب ALPHA للأبناء، الذي يوفر:
+📱تطبيق للخدمات المصرفية عبر الهاتف المتحرك مخصص لأبنائك
+💳 بطاقة خصم للأبناء
+⭐عروض وخصومات حصرية
+🎁مكافأة بقيمة 100 درهم بمناسبة يوم ميلاد الأبناء
+🏆جوائز نقدية يومية وشهرية
+علمهم صغار!
+تطبق الشروط والأحكام. https://t.co/PUCOpaLwMF</t>
         </is>
       </c>
       <c r="G70" t="n">
-        <v>1776924000000</v>
+        <v>1777034676000</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2047193752767193369</t>
+          <t>2047657960227176876</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGfmSCYWYAAeGEP.jpg', 'type': 'photo', 'id': '2046857753214214144'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGq-Dy9W4AA2EvQ.jpg', 'type': 'photo', 'id': '2047657953021321216'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGq-ECIWoAAdlCp.jpg', 'type': 'photo', 'id': '2047657957093974016'}]</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174341, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18451, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="K70" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>49</t>
         </is>
       </c>
       <c r="P70" t="inlineStr"/>
@@ -5229,35 +5279,35 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>https://x.com/77dd14cbca18474/status/2047202084769206665</t>
+          <t>https://x.com/emiratesislamic/status/2047657974936604881</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2047202084769206665</t>
+          <t>2047657974936604881</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2047202084769206665</t>
+          <t>2047657962978558100</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>https://x.com/77dd14cbca18474/status/2047202084769206665</t>
+          <t>https://x.com/emiratesislamic/status/2047657962978558100</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Worst bank ever iam following up since 1 year for cancellation of wealth account still nothing</t>
+          <t>لمعرفة المزيد، يرجى زيارة https://t.co/Dacednep0G</t>
         </is>
       </c>
       <c r="G71" t="n">
-        <v>1776925986000</v>
+        <v>1777034676000</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2047193752767193369</t>
+          <t>2047657960227176876</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -5267,7 +5317,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>{'name': 'Abid Khan', 'screenName': '77dd14cbca18474', 'followersCount': 0, 'favouritesCount': 9, 'friendsCount': 21, 'description': ''}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18451, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="K71" t="n">
@@ -5284,12 +5334,12 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>2047193752767193369</t>
+          <t>2047657960227176876</t>
         </is>
       </c>
     </row>
@@ -5299,45 +5349,51 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>https://x.com/77dd14cbca18474/status/2047202084769206665</t>
+          <t>https://x.com/emiratesislamic/status/2047657974936604881</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2047202084769206665</t>
+          <t>2047657974936604881</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2047206058129559636</t>
+          <t>2047657972390560162</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2047206058129559636</t>
+          <t>https://x.com/emiratesislamic/status/2047657972390560162</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Hi, thank you for sharing your feedback. We’re sorry that you had experienced this, it is not what we expect our customers to feel nor see. We kindly request you to send us more details and your registered mobile number via social@emiratesnbd.com and quote Case #1001012 for us to assist you better. Thanks.</t>
+          <t>Introducing the ALPHA Youth Account, a banking experience that offers:
+📱 Access to a dedicated mobile app
+💳 Complimentary Debit Card for youth
+🏆 Daily &amp;amp; monthly cash prizes
+🎁 A birthday reward of AED 100 for your child
+⭐ Exclusive offers &amp;amp; discounts
+Start them young! https://t.co/cHbCHEecyD</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>1776926934000</v>
+        <v>1777034678000</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2047193752767193369</t>
+          <t>2047657960227176876</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGq-EiyXYAAScez.jpg', 'type': 'photo', 'id': '2047657965860118528'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGq-EwlWwAAzeCE.jpg', 'type': 'photo', 'id': '2047657969563648000'}]</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174341, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18451, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="K72" t="n">
@@ -5354,12 +5410,12 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>48</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>2047202084769206665</t>
+          <t>2047657962978558100</t>
         </is>
       </c>
     </row>
@@ -5369,35 +5425,36 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>https://x.com/77dd14cbca18474/status/2047201786570907985</t>
+          <t>https://x.com/emiratesislamic/status/2047657974936604881</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2047201786570907985</t>
+          <t>2047657974936604881</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2047201786570907985</t>
+          <t>2047657974936604881</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>https://x.com/77dd14cbca18474/status/2047201786570907985</t>
+          <t>https://x.com/emiratesislamic/status/2047657974936604881</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Hello its been 1 year iam following for account cancellation called many times to call center posted in X also still not cancelled?? Whats happening</t>
+          <t>Terms &amp;amp; condition apply.
+To know more, please visit https://t.co/Um2N1hjaxk</t>
         </is>
       </c>
       <c r="G73" t="n">
-        <v>1776925915000</v>
+        <v>1777034679000</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2047201786570907985</t>
+          <t>2047657960227176876</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -5407,7 +5464,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>{'name': 'Abid Khan', 'screenName': '77dd14cbca18474', 'followersCount': 0, 'favouritesCount': 9, 'friendsCount': 21, 'description': ''}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18451, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="K73" t="n">
@@ -5424,10 +5481,14 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="P73" t="inlineStr"/>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>2047657972390560162</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
@@ -5435,64 +5496,69 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>https://x.com/SelmaRomola/status/2047199400414650716</t>
+          <t>https://x.com/emiratesislamic/status/2047657972390560162</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2047199400414650716</t>
+          <t>2047657972390560162</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2047193752767172824</t>
+          <t>2047657960227176876</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2047193752767172824</t>
+          <t>https://x.com/emiratesislamic/status/2047657960227176876</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>هذا هو «تأثير كرة الثلج» الذي تحبه مدخراتك.
-خمن الإجابة واكتبها في التعليقات أدناه.
-#لغز_الأسبوع_ENBD #نمِّ_أموالك #ادخار_ذكي https://t.co/7DKysuXUir</t>
+          <t>نقدم لك تجربة مصرفية مميزة مع حساب ALPHA للأبناء، الذي يوفر:
+📱تطبيق للخدمات المصرفية عبر الهاتف المتحرك مخصص لأبنائك
+💳 بطاقة خصم للأبناء
+⭐عروض وخصومات حصرية
+🎁مكافأة بقيمة 100 درهم بمناسبة يوم ميلاد الأبناء
+🏆جوائز نقدية يومية وشهرية
+علمهم صغار!
+تطبق الشروط والأحكام. https://t.co/PUCOpaLwMF</t>
         </is>
       </c>
       <c r="G74" t="n">
-        <v>1776924000000</v>
+        <v>1777034676000</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2047193752767172824</t>
+          <t>2047657960227176876</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGhKElnXsAAucKZ.jpg', 'type': 'photo', 'id': '2046967473317064704'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGq-Dy9W4AA2EvQ.jpg', 'type': 'photo', 'id': '2047657953021321216'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGq-ECIWoAAdlCp.jpg', 'type': 'photo', 'id': '2047657957093974016'}]</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174341, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18451, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="K74" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L74" t="n">
         <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>317</t>
+          <t>49</t>
         </is>
       </c>
       <c r="P74" t="inlineStr"/>
@@ -5503,35 +5569,35 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>https://x.com/SelmaRomola/status/2047199400414650716</t>
+          <t>https://x.com/emiratesislamic/status/2047657972390560162</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2047199400414650716</t>
+          <t>2047657972390560162</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2047199400414650716</t>
+          <t>2047657962978558100</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>https://x.com/SelmaRomola/status/2047199400414650716</t>
+          <t>https://x.com/emiratesislamic/status/2047657962978558100</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Compound Interest</t>
+          <t>لمعرفة المزيد، يرجى زيارة https://t.co/Dacednep0G</t>
         </is>
       </c>
       <c r="G75" t="n">
-        <v>1776925346000</v>
+        <v>1777034676000</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2047193752767172824</t>
+          <t>2047657960227176876</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5541,11 +5607,11 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>{'name': 'Selma Romola', 'screenName': 'SelmaRomola', 'followersCount': 1149, 'favouritesCount': 19748, 'friendsCount': 1783, 'description': ''}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18451, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="K75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L75" t="n">
         <v>0</v>
@@ -5558,12 +5624,12 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>2047193752767172824</t>
+          <t>2047657960227176876</t>
         </is>
       </c>
     </row>
@@ -5573,53 +5639,55 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>https://x.com/AletihadEn/status/2047197832806072615</t>
+          <t>https://x.com/emiratesislamic/status/2047657972390560162</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2047197832806072615</t>
+          <t>2047657972390560162</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2047197832806072615</t>
+          <t>2047657972390560162</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>https://x.com/AletihadEn/status/2047197832806072615</t>
+          <t>https://x.com/emiratesislamic/status/2047657972390560162</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Emirates NBD reports Dh8.2 billion profit before tax in Q1 2026, up 6% YoY 
-Total income increased 21% year-on-year and 13% quarter-on-quarter to Dh14.4 billion, supported by strong asset growth and a sharp rise in non-funded income, which surged 42% year-on-year to Dh4.9 billion.
-Net profit stood at Dh6.4 billion, up 27% quarter-on-quarter but down 3% year-on-year, reflecting overall solid performance during the period.
-Read more: https://t.co/5WKoAM1fAJ 
-#AletihadNewsCenter #UAE #banking  @ENBDdeals</t>
+          <t>Introducing the ALPHA Youth Account, a banking experience that offers:
+📱 Access to a dedicated mobile app
+💳 Complimentary Debit Card for youth
+🏆 Daily &amp;amp; monthly cash prizes
+🎁 A birthday reward of AED 100 for your child
+⭐ Exclusive offers &amp;amp; discounts
+Start them young! https://t.co/cHbCHEecyD</t>
         </is>
       </c>
       <c r="G76" t="n">
-        <v>1776924973000</v>
+        <v>1777034678000</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2047197832806072615</t>
+          <t>2047657960227176876</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGq-EiyXYAAScez.jpg', 'type': 'photo', 'id': '2047657965860118528'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGq-EwlWwAAzeCE.jpg', 'type': 'photo', 'id': '2047657969563648000'}]</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>{'name': 'Aletihad English', 'screenName': 'AletihadEn', 'followersCount': 1100, 'favouritesCount': 9, 'friendsCount': 12, 'description': 'Aletihad English - Aletihad News Center'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18451, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="K76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L76" t="n">
         <v>0</v>
@@ -5632,10 +5700,14 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="P76" t="inlineStr"/>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>2047657962978558100</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
@@ -5643,37 +5715,36 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>https://x.com/AletihadEn/status/2047197832806072615</t>
+          <t>https://x.com/emiratesislamic/status/2047657972390560162</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2047197832806072615</t>
+          <t>2047657972390560162</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2047357381013897297</t>
+          <t>2047657974936604881</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>https://x.com/AletihadEn/status/2047357381013897297</t>
+          <t>https://x.com/emiratesislamic/status/2047657974936604881</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Abu Dhabi Civil Defence Authority reinforces readiness and integration of field operations 
-Read more: https://t.co/TlPHChPWwt 
-#AletihadNewsCenter #UAE #abudhabicivildefence</t>
+          <t>Terms &amp;amp; condition apply.
+To know more, please visit https://t.co/Um2N1hjaxk</t>
         </is>
       </c>
       <c r="G77" t="n">
-        <v>1776963012000</v>
+        <v>1777034679000</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2047357381013897297</t>
+          <t>2047657960227176876</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5683,7 +5754,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>{'name': 'Aletihad English', 'screenName': 'AletihadEn', 'followersCount': 1100, 'favouritesCount': 9, 'friendsCount': 12, 'description': 'Aletihad English - Aletihad News Center'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18451, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="K77" t="n">
@@ -5696,14 +5767,18 @@
         <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="P77" t="inlineStr"/>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>2047657972390560162</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
@@ -5711,64 +5786,64 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>https://x.com/SelmaRomola/status/2047199350926070265</t>
+          <t>https://x.com/emiratesislamic/status/2047632173461561410</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2047199350926070265</t>
+          <t>2047632173461561410</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2047193752767193369</t>
+          <t>2047632164863250935</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2047193752767193369</t>
+          <t>https://x.com/emiratesislamic/status/2047632164863250935</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>This is the ‘snowball effect’ your savings love.
-Guess and drop your answer below.
-#ENBDRiddleOfTheWeek #GrowYourMoney #SmartSaving https://t.co/FZ9IMHLqZg</t>
+          <t>Transfer your salary now &amp;amp; enjoy rewarding benefits and guaranteed cashback of up to AED 6,000!
+Enjoy more rewards:
+💳 Exclusive Credit Card benefits, airport lounge access, rewards &amp;amp; more https://t.co/w9nMkMnJJb</t>
         </is>
       </c>
       <c r="G78" t="n">
-        <v>1776924000000</v>
+        <v>1777028525000</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2047193752767193369</t>
+          <t>2047632164863250935</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGfmSCYWYAAeGEP.jpg', 'type': 'photo', 'id': '2046857753214214144'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGqmmaBXUAEX6Xi.jpg', 'type': 'photo', 'id': '2047632159343595521'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGqmmlvW4AErjsf.jpg', 'type': 'photo', 'id': '2047632162489294849'}]</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174341, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18451, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="K78" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L78" t="n">
         <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>389</t>
+          <t>37</t>
         </is>
       </c>
       <c r="P78" t="inlineStr"/>
@@ -5779,45 +5854,49 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>https://x.com/SelmaRomola/status/2047199350926070265</t>
+          <t>https://x.com/emiratesislamic/status/2047632173461561410</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2047199350926070265</t>
+          <t>2047632173461561410</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2047199350926070265</t>
+          <t>2047632173461561410</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>https://x.com/SelmaRomola/status/2047199350926070265</t>
+          <t>https://x.com/emiratesislamic/status/2047632173461561410</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Compound Interest</t>
+          <t>🎁 Reward of AED 100 with an ALPHA Youth Account
+And much more.
+Offer valid till 31 May 2026.
+Terms &amp;amp; conditions apply.
+https://t.co/Hgg0TFDsUE https://t.co/MBZ0YjVgiN</t>
         </is>
       </c>
       <c r="G79" t="n">
-        <v>1776925335000</v>
+        <v>1777028527000</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2047193752767193369</t>
+          <t>2047632164863250935</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGqmm5VWkAAB2mi.jpg', 'type': 'photo', 'id': '2047632167748931584'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGqmnGiWkAAtXIq.jpg', 'type': 'photo', 'id': '2047632171293118464'}]</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>{'name': 'Selma Romola', 'screenName': 'SelmaRomola', 'followersCount': 1149, 'favouritesCount': 19748, 'friendsCount': 1783, 'description': ''}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18451, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="K79" t="n">
@@ -5834,12 +5913,12 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>2047193752767193369</t>
+          <t>2047632164863250935</t>
         </is>
       </c>
     </row>
@@ -5849,67 +5928,69 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>https://x.com/AlArabiya_Bn/status/2047196564540502492</t>
+          <t>https://x.com/emiratesislamic/status/2047657962978558100</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2047196564540502492</t>
+          <t>2047657962978558100</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2047196564540502492</t>
+          <t>2047657960227176876</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>https://x.com/AlArabiya_Bn/status/2047196564540502492</t>
+          <t>https://x.com/emiratesislamic/status/2047657960227176876</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>افتتاحية خضراء لكافة المؤشرات الكويتية والإماراتية باستثناء مؤشر أبو ظبي..
-📌 ارتفاع أرباح دو الفصلية 15% إلى 834 مليون درهم
-📌 ارتفاع أرباح بنك ENBD الفصلية 3% إلى 6.4 مليار درهم
-@Noufhijazi_bn
-#افتتاح_الأسواق
-#العربية_Business https://t.co/dWhxxqe7Bt</t>
+          <t>نقدم لك تجربة مصرفية مميزة مع حساب ALPHA للأبناء، الذي يوفر:
+📱تطبيق للخدمات المصرفية عبر الهاتف المتحرك مخصص لأبنائك
+💳 بطاقة خصم للأبناء
+⭐عروض وخصومات حصرية
+🎁مكافأة بقيمة 100 درهم بمناسبة يوم ميلاد الأبناء
+🏆جوائز نقدية يومية وشهرية
+علمهم صغار!
+تطبق الشروط والأحكام. https://t.co/PUCOpaLwMF</t>
         </is>
       </c>
       <c r="G80" t="n">
-        <v>1776924670000</v>
+        <v>1777034676000</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2047196564540502492</t>
+          <t>2047657960227176876</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGkabKkXoAAyNBd.jpg', 'type': 'video', 'id': '2047196052474757120'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGq-Dy9W4AA2EvQ.jpg', 'type': 'photo', 'id': '2047657953021321216'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGq-ECIWoAAdlCp.jpg', 'type': 'photo', 'id': '2047657957093974016'}]</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>{'name': 'العربية Business', 'screenName': 'AlArabiya_Bn', 'followersCount': 1995732, 'favouritesCount': 0, 'friendsCount': 53, 'description': 'المصدر الرئيسي لأخبار الاقتصاد والأعمال في الشرق الأوسط @AlArabiya'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18451, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="K80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L80" t="n">
         <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>1747</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P80" t="inlineStr"/>
@@ -5920,68 +6001,69 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>https://x.com/AlArabiya_Bn/status/2047196564540502492</t>
+          <t>https://x.com/emiratesislamic/status/2047657962978558100</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2047196564540502492</t>
+          <t>2047657962978558100</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2047420244361154671</t>
+          <t>2047657962978558100</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>https://x.com/AlArabiya_Bn/status/2047420244361154671</t>
+          <t>https://x.com/emiratesislamic/status/2047657962978558100</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>من #الرياض إلى #اسطنبول بتوقف واحد!
-سيارة كهربائية ثورية في #الصين، فيما المنافسة تشتعل بين BYD وCATL.. لكن أين #تسلا؟ وأين فخر الصناعة الألمانية؟
-@OAlladan 
-#العربية_Business https://t.co/hsUDzuQOdC</t>
+          <t>لمعرفة المزيد، يرجى زيارة https://t.co/Dacednep0G</t>
         </is>
       </c>
       <c r="G81" t="n">
-        <v>1776978000000</v>
+        <v>1777034676000</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2047420244361154671</t>
+          <t>2047657960227176876</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2047394401249353728/img/lhOeFsdI9JVbFJvz.jpg', 'type': 'video', 'id': '2047394401249353728'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>{'name': 'العربية Business', 'screenName': 'AlArabiya_Bn', 'followersCount': 1995732, 'favouritesCount': 0, 'friendsCount': 53, 'description': 'المصدر الرئيسي لأخبار الاقتصاد والأعمال في الشرق الأوسط @AlArabiya'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18451, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="K81" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>9344</t>
-        </is>
-      </c>
-      <c r="P81" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>2047657960227176876</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
@@ -5989,50 +6071,55 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>https://x.com/gulfhindinews/status/2047193081275916312</t>
+          <t>https://x.com/emiratesislamic/status/2047657962978558100</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2047193081275916312</t>
+          <t>2047657962978558100</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2047193081275916312</t>
+          <t>2047657972390560162</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>https://x.com/gulfhindinews/status/2047193081275916312</t>
+          <t>https://x.com/emiratesislamic/status/2047657972390560162</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Emirates NBD ने कमाई में बनाया रिकॉर्ड, 2026 की पहली तिमाही में 14.4 अरब दिरहम की इनकम, मुनाफ़ा भी बढ़ा
-https://t.co/rdoDZ4ySML https://t.co/QqRyIX35EU https://t.co/pGXfJonLfe</t>
+          <t>Introducing the ALPHA Youth Account, a banking experience that offers:
+📱 Access to a dedicated mobile app
+💳 Complimentary Debit Card for youth
+🏆 Daily &amp;amp; monthly cash prizes
+🎁 A birthday reward of AED 100 for your child
+⭐ Exclusive offers &amp;amp; discounts
+Start them young! https://t.co/cHbCHEecyD</t>
         </is>
       </c>
       <c r="G82" t="n">
-        <v>1776923840000</v>
+        <v>1777034678000</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2047193081275916312</t>
+          <t>2047657960227176876</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGkXQkaW0AAm4zV.jpg', 'type': 'photo', 'id': '2047193079036170240'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGq-EiyXYAAScez.jpg', 'type': 'photo', 'id': '2047657965860118528'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGq-EwlWwAAzeCE.jpg', 'type': 'photo', 'id': '2047657969563648000'}]</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>{'name': 'GulfHindi.com', 'screenName': 'gulfhindinews', 'followersCount': 16612, 'favouritesCount': 110, 'friendsCount': 119, 'description': 'UAE, सउदी अरब, कुवैत, क़तर, बहरीन, ओमान और येमन की ख़बरें हिंदी में. Download APP: https://t.co/ilPRB3y2jq also join us on https://t.co/RwcIcNAEJY'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18451, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="K82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L82" t="n">
         <v>0</v>
@@ -6041,14 +6128,18 @@
         <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="P82" t="inlineStr"/>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>2047657962978558100</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
@@ -6056,50 +6147,51 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>https://x.com/gulfhindinews/status/2047193081275916312</t>
+          <t>https://x.com/emiratesislamic/status/2047632164863250935</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2047193081275916312</t>
+          <t>2047632164863250935</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2047524015179174079</t>
+          <t>2047632164863250935</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>https://x.com/gulfhindinews/status/2047524015179174079</t>
+          <t>https://x.com/emiratesislamic/status/2047632164863250935</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>UAE में पासपोर्ट और कांसुलर सेवाओं के नियम बदलेंगे, अब Alhind संभालेगा काम, शुल्क मात्र 19 दिरहम होगा
-https://t.co/0ShRzcscPQ https://t.co/dq1WqzOGmd https://t.co/71d9d3KoRm</t>
+          <t>Transfer your salary now &amp;amp; enjoy rewarding benefits and guaranteed cashback of up to AED 6,000!
+Enjoy more rewards:
+💳 Exclusive Credit Card benefits, airport lounge access, rewards &amp;amp; more https://t.co/w9nMkMnJJb</t>
         </is>
       </c>
       <c r="G83" t="n">
-        <v>1777002741000</v>
+        <v>1777028525000</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2047524015179174079</t>
+          <t>2047632164863250935</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGpEPciXwAA9n-p.jpg', 'type': 'photo', 'id': '2047524012742393856'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGqmmaBXUAEX6Xi.jpg', 'type': 'photo', 'id': '2047632159343595521'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGqmmlvW4AErjsf.jpg', 'type': 'photo', 'id': '2047632162489294849'}]</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>{'name': 'GulfHindi.com', 'screenName': 'gulfhindinews', 'followersCount': 16612, 'favouritesCount': 110, 'friendsCount': 119, 'description': 'UAE, सउदी अरब, कुवैत, क़तर, बहरीन, ओमान और येमन की ख़बरें हिंदी में. Download APP: https://t.co/ilPRB3y2jq also join us on https://t.co/RwcIcNAEJY'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18451, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="K83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L83" t="n">
         <v>0</v>
@@ -6112,7 +6204,7 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>38</t>
         </is>
       </c>
       <c r="P83" t="inlineStr"/>
@@ -6123,68 +6215,73 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>https://x.com/HarshGada76429/status/2047182474049106165</t>
+          <t>https://x.com/emiratesislamic/status/2047632164863250935</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2047182474049106165</t>
+          <t>2047632164863250935</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2038970719238045794</t>
+          <t>2047632173461561410</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>https://x.com/HarshGada76429/status/2038970719238045794</t>
+          <t>https://x.com/emiratesislamic/status/2047632173461561410</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>@RBLBankCares
-@rblbank
-I have been a loyal customer for last 3yrs using your world safari credit card I have achieved the milestone but missed the redemption date by 7 days 
-Request you to send me new redemption link for 10000rs voucher or I will have to end the relationship now</t>
+          <t>🎁 Reward of AED 100 with an ALPHA Youth Account
+And much more.
+Offer valid till 31 May 2026.
+Terms &amp;amp; conditions apply.
+https://t.co/Hgg0TFDsUE https://t.co/MBZ0YjVgiN</t>
         </is>
       </c>
       <c r="G84" t="n">
-        <v>1774963476000</v>
+        <v>1777028527000</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2038970719238045794</t>
+          <t>2047632164863250935</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGqmm5VWkAAB2mi.jpg', 'type': 'photo', 'id': '2047632167748931584'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGqmnGiWkAAtXIq.jpg', 'type': 'photo', 'id': '2047632171293118464'}]</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>{'name': 'Harsh Gada', 'screenName': 'HarshGada76429', 'followersCount': 0, 'favouritesCount': 1, 'friendsCount': 21, 'description': ''}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18451, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="K84" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L84" t="n">
         <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N84" t="n">
         <v>0</v>
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="P84" t="inlineStr"/>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>2047632164863250935</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
@@ -6192,47 +6289,48 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>https://x.com/HarshGada76429/status/2047182474049106165</t>
+          <t>https://x.com/emiratesislamic/status/2047632164863250935</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2047182474049106165</t>
+          <t>2047632164863250935</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2047182474049106165</t>
+          <t>2047717988195852322</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>https://x.com/HarshGada76429/status/2047182474049106165</t>
+          <t>https://x.com/emiratesislamic/status/2047717988195852322</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Pathetic services and poor client retention services by RBL Bank
-@RBLBankCares 
-@EmiratesNBD_AE</t>
+          <t>🇦🇪 We salute the nation’s heroes 
+We value your commitment and have designed exclusive banking benefits for your peace of mind.
+📈 Attractive finance profit rates
+🏦 Zero processing fees https://t.co/Q8zlLDLLW1</t>
         </is>
       </c>
       <c r="G85" t="n">
-        <v>1776921311000</v>
+        <v>1777048987000</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2038970719238045794</t>
+          <t>2047717988195852322</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGr0p_HW8AA45jd.jpg', 'type': 'photo', 'id': '2047717982747422720'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGr0qJzWcAAnD8P.jpg', 'type': 'photo', 'id': '2047717985616293888'}]</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>{'name': 'Harsh Gada', 'screenName': 'HarshGada76429', 'followersCount': 0, 'favouritesCount': 1, 'friendsCount': 21, 'description': ''}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18451, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="K85" t="n">
@@ -6245,18 +6343,14 @@
         <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="P85" t="inlineStr">
-        <is>
-          <t>2038970719238045794</t>
-        </is>
-      </c>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
@@ -6264,49 +6358,56 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>https://x.com/HarshGada76429/status/2047182474049106165</t>
+          <t>https://x.com/emiratesislamic/status/2047657960227176876</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2047182474049106165</t>
+          <t>2047657960227176876</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2047184999158599844</t>
+          <t>2047657960227176876</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>https://x.com/RBLBankCares/status/2047184999158599844</t>
+          <t>https://x.com/emiratesislamic/status/2047657960227176876</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>@HarshGada76429 Hello, our representative will get in touch with you at the earliest to address your query. Regards, RBL Bank.</t>
+          <t>نقدم لك تجربة مصرفية مميزة مع حساب ALPHA للأبناء، الذي يوفر:
+📱تطبيق للخدمات المصرفية عبر الهاتف المتحرك مخصص لأبنائك
+💳 بطاقة خصم للأبناء
+⭐عروض وخصومات حصرية
+🎁مكافأة بقيمة 100 درهم بمناسبة يوم ميلاد الأبناء
+🏆جوائز نقدية يومية وشهرية
+علمهم صغار!
+تطبق الشروط والأحكام. https://t.co/PUCOpaLwMF</t>
         </is>
       </c>
       <c r="G86" t="n">
-        <v>1776921913000</v>
+        <v>1777034676000</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2038970719238045794</t>
+          <t>2047657960227176876</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGq-Dy9W4AA2EvQ.jpg', 'type': 'photo', 'id': '2047657953021321216'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGq-ECIWoAAdlCp.jpg', 'type': 'photo', 'id': '2047657957093974016'}]</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>{'name': 'RBL Bank Cares', 'screenName': 'RBLBankCares', 'followersCount': 15184, 'favouritesCount': 107, 'friendsCount': 1, 'description': 'Welcome to the official service handle of RBL Bank for addressing your queries. The Bank’s social media guidelines are available on: https://t.co/4latICF1Kx'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18451, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="K86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L86" t="n">
         <v>0</v>
@@ -6319,14 +6420,10 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="P86" t="inlineStr">
-        <is>
-          <t>2047182474049106165</t>
-        </is>
-      </c>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
@@ -6334,36 +6431,35 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>https://x.com/abd11ulla/status/2047178753684762646</t>
+          <t>https://x.com/emiratesislamic/status/2047657960227176876</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2047178753684762646</t>
+          <t>2047657960227176876</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2047178753684762646</t>
+          <t>2047657962978558100</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>https://x.com/abd11ulla/status/2047178753684762646</t>
+          <t>https://x.com/emiratesislamic/status/2047657962978558100</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>لا مقارنة بين بنك أبوظبي الأول و الإمارات دبي الوطني
-ENBD أثبت تفوقه المصرفي في أخر 3 أعوام على FAB</t>
+          <t>لمعرفة المزيد، يرجى زيارة https://t.co/Dacednep0G</t>
         </is>
       </c>
       <c r="G87" t="n">
-        <v>1776920424000</v>
+        <v>1777034676000</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2047178753684762646</t>
+          <t>2047657960227176876</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -6373,7 +6469,7 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>{'name': 'Abdulla', 'screenName': 'abd11ulla', 'followersCount': 2979, 'favouritesCount': 130246, 'friendsCount': 6667, 'description': 'The Emirates ( UAE ) = 🗺️'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18451, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="K87" t="n">
@@ -6386,14 +6482,18 @@
         <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>405</t>
-        </is>
-      </c>
-      <c r="P87" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>2047657960227176876</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
@@ -6401,46 +6501,48 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>https://x.com/abd11ulla/status/2047178753684762646</t>
+          <t>https://x.com/emiratesislamic/status/2047657960227176876</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2047178753684762646</t>
+          <t>2047657960227176876</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2047199345783754795</t>
+          <t>2047717988195852322</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>https://x.com/ahmedalwahedi/status/2047199345783754795</t>
+          <t>https://x.com/emiratesislamic/status/2047717988195852322</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>@abd11ulla تداوم عندهم اظاهر
-مافي نفس اديب وابوظبي التجاري 😌</t>
+          <t>🇦🇪 We salute the nation’s heroes 
+We value your commitment and have designed exclusive banking benefits for your peace of mind.
+📈 Attractive finance profit rates
+🏦 Zero processing fees https://t.co/Q8zlLDLLW1</t>
         </is>
       </c>
       <c r="G88" t="n">
-        <v>1776925333000</v>
+        <v>1777048987000</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2047178753684762646</t>
+          <t>2047717988195852322</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGr0p_HW8AA45jd.jpg', 'type': 'photo', 'id': '2047717982747422720'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGr0qJzWcAAnD8P.jpg', 'type': 'photo', 'id': '2047717985616293888'}]</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>{'name': 'أحمد الواحدي', 'screenName': 'ahmedalwahedi', 'followersCount': 4658, 'favouritesCount': 580, 'friendsCount': 241, 'description': 'من سلالة بني أميه 🇦🇪🧑\u200d🧑\u200d🧒\u200d🧒'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18451, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="K88" t="n">
@@ -6457,14 +6559,10 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="P88" t="inlineStr">
-        <is>
-          <t>2047178753684762646</t>
-        </is>
-      </c>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
@@ -6472,49 +6570,51 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>https://x.com/abd11ulla/status/2047170067444760649</t>
+          <t>https://x.com/emiratesislamic/status/2047632125583605871</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2047170067444760649</t>
+          <t>2047632125583605871</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2047170067444760649</t>
+          <t>2047632116649689120</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>https://x.com/abd11ulla/status/2047170067444760649</t>
+          <t>https://x.com/emiratesislamic/status/2047632116649689120</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>ماشاءالله 👏🏻 أفضل بنك في الإمارات ENBD 🇦🇪</t>
+          <t>حوّل راتبك الآن و استمتع بمزايا خاصة واكسب استرداداً نقدياً مضموناً يصل إلى 6,000 درهم!
+استمتع بالمزيد من المكافآت:
+💳 مزايا حصرية على البطاقة الائتمانية والدخول إلى صالات المطارات والمكافآت والمزيد https://t.co/DfoSsbwLQd</t>
         </is>
       </c>
       <c r="G89" t="n">
-        <v>1776918353000</v>
+        <v>1777028514000</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2047170067444760649</t>
+          <t>2047632116649689120</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGqmjnLXwAAvwdB.jpg', 'type': 'photo', 'id': '2047632111335620608'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGqmjyyXAAAadnx.jpg', 'type': 'photo', 'id': '2047632114451939328'}]</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>{'name': 'Abdulla', 'screenName': 'abd11ulla', 'followersCount': 2979, 'favouritesCount': 130246, 'friendsCount': 6667, 'description': 'The Emirates ( UAE ) = 🗺️'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18451, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="K89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L89" t="n">
         <v>0</v>
@@ -6523,11 +6623,11 @@
         <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>37</t>
         </is>
       </c>
       <c r="P89" t="inlineStr"/>
@@ -6538,45 +6638,50 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>https://x.com/abd11ulla/status/2047170067444760649</t>
+          <t>https://x.com/emiratesislamic/status/2047632125583605871</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2047170067444760649</t>
+          <t>2047632125583605871</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2047502441709797406</t>
+          <t>2047632125583605871</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>https://x.com/abd11ulla/status/2047502441709797406</t>
+          <t>https://x.com/emiratesislamic/status/2047632125583605871</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>زعيم الشرق الأوسط 🌍 ، محمد بن زايد ( بوخالد ) 🇦🇪 .</t>
+          <t>💰 معدلات ربح تنافسية على تمويل السيارات والتمويل السكني
+🎁 مكافأة 100 درهم مع حساب ALPHA للأبناء
+وغير ذلك الكثير.
+يسري العرض لغاية 31 مايو 2026.
+تطبق الشروط والأحكام.
+https://t.co/909hzRsLZr https://t.co/Ff41FuCAen</t>
         </is>
       </c>
       <c r="G90" t="n">
-        <v>1776997597000</v>
+        <v>1777028516000</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2047502441709797406</t>
+          <t>2047632116649689120</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGqmkG7WcAEveRR.jpg', 'type': 'photo', 'id': '2047632119858360321'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGqmkUZWQAEKDDE.jpg', 'type': 'photo', 'id': '2047632123473838081'}]</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>{'name': 'Abdulla', 'screenName': 'abd11ulla', 'followersCount': 2979, 'favouritesCount': 130246, 'friendsCount': 6667, 'description': 'The Emirates ( UAE ) = 🗺️'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18451, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="K90" t="n">
@@ -6586,17 +6691,21 @@
         <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="P90" t="inlineStr"/>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>2047632116649689120</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
@@ -6604,49 +6713,52 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>https://x.com/diegobloomberg/status/2047162845263978833</t>
+          <t>https://x.com/emiratesislamic/status/2047631643926483032</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2047162845263978833</t>
+          <t>2047631643926483032</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2047162845263978833</t>
+          <t>2047631639946093018</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>https://x.com/diegobloomberg/status/2047162845263978833</t>
+          <t>https://x.com/emiratesislamic/status/2047631639946093018</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>*EMIRATES NBD 1Q OPER INCOME 14.4B DIRHAMS, EST. 13.16B DIRHAMS</t>
+          <t>احصل على iPhone 17 مضمون عند التقدم بطلب تمويل شخصي من الإمارات الإسلامي.
+استمتع أيضاً بالمزايا الحصرية:
+📊 معدلات ربح تبدأ من %2.59 ثابتة سنوياً (ما يعادل تقريباً %4.74 كمعدل متناقص سنوياً).
+🏦 مبلغ تمويلي يصل إلى 4,000,000 درهم https://t.co/eMEYGVmxwY</t>
         </is>
       </c>
       <c r="G91" t="n">
-        <v>1776916631000</v>
+        <v>1777028400000</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2047162845263978833</t>
+          <t>2047631639946093018</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGp1V6aW8AAL6dm.jpg', 'type': 'photo', 'id': '2047577999910825984'}]</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>{'name': 'diego bloomberg', 'screenName': 'diegobloomberg', 'followersCount': 1411, 'favouritesCount': 2, 'friendsCount': 6, 'description': 'Fastest news on X. Premium financial headlines at zero cost— Diego wants to keep finance free, fast, and friendly. Activate notifications to stay ahead.'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18451, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="K91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L91" t="n">
         <v>0</v>
@@ -6659,7 +6771,7 @@
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>43</t>
         </is>
       </c>
       <c r="P91" t="inlineStr"/>
@@ -6670,35 +6782,39 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>https://x.com/diegobloomberg/status/2047162845263978833</t>
+          <t>https://x.com/emiratesislamic/status/2047631643926483032</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2047162845263978833</t>
+          <t>2047631643926483032</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2047426055137333385</t>
+          <t>2047631643926483032</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>https://x.com/diegobloomberg/status/2047426055137333385</t>
+          <t>https://x.com/emiratesislamic/status/2047631643926483032</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>*ISRAEL-LEBANON CEASEFIRE EXTENDED BY THREE WEEKS, TRUMP SAYS</t>
+          <t>✈️ تأجيل القسط الأول لمدة تصل إلى 6 شهور
+🔒 تغطية تكافلية
+يسري العرض لغاية 30 أبريل 2026.
+تطبق الشروط والأحكام.
+https://t.co/WVHANHvCwT</t>
         </is>
       </c>
       <c r="G92" t="n">
-        <v>1776979385000</v>
+        <v>1777028401000</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2047426055137333385</t>
+          <t>2047631639946093018</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -6708,7 +6824,7 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>{'name': 'diego bloomberg', 'screenName': 'diegobloomberg', 'followersCount': 1411, 'favouritesCount': 2, 'friendsCount': 6, 'description': 'Fastest news on X. Premium financial headlines at zero cost— Diego wants to keep finance free, fast, and friendly. Activate notifications to stay ahead.'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18451, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="K92" t="n">
@@ -6721,14 +6837,18 @@
         <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>245</t>
-        </is>
-      </c>
-      <c r="P92" t="inlineStr"/>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>2047631639946093018</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
@@ -6736,49 +6856,51 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>https://x.com/MarketNews_Feed/status/2047162941082882185</t>
+          <t>https://x.com/emiratesislamic/status/2047632116649689120</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2047162941082882185</t>
+          <t>2047632116649689120</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2047162941082882185</t>
+          <t>2047632116649689120</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>https://x.com/MarketNews_Feed/status/2047162941082882185</t>
+          <t>https://x.com/emiratesislamic/status/2047632116649689120</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>*EMIRATES NBD 1Q OPER INCOME 14.4B DIRHAMS, EST. 13.16B DIRHAMS ...</t>
+          <t>حوّل راتبك الآن و استمتع بمزايا خاصة واكسب استرداداً نقدياً مضموناً يصل إلى 6,000 درهم!
+استمتع بالمزيد من المكافآت:
+💳 مزايا حصرية على البطاقة الائتمانية والدخول إلى صالات المطارات والمكافآت والمزيد https://t.co/DfoSsbwLQd</t>
         </is>
       </c>
       <c r="G93" t="n">
-        <v>1776916654000</v>
+        <v>1777028514000</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2047162941082882185</t>
+          <t>2047632116649689120</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGqmjnLXwAAvwdB.jpg', 'type': 'photo', 'id': '2047632111335620608'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGqmjyyXAAAadnx.jpg', 'type': 'photo', 'id': '2047632114451939328'}]</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>{'name': 'MarketNewsFeed', 'screenName': 'MarketNews_Feed', 'followersCount': 6505, 'favouritesCount': 691, 'friendsCount': 4, 'description': 'The number 1 ranked news aggregator voted unanimously  (by me). All financial and tech headlines in one place. Sources are cited in TG - @MarketFeed'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18451, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="K93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L93" t="n">
         <v>0</v>
@@ -6791,7 +6913,7 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>37</t>
         </is>
       </c>
       <c r="P93" t="inlineStr"/>
@@ -6802,45 +6924,50 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>https://x.com/MarketNews_Feed/status/2047162941082882185</t>
+          <t>https://x.com/emiratesislamic/status/2047632116649689120</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2047162941082882185</t>
+          <t>2047632116649689120</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2047530582981165068</t>
+          <t>2047632125583605871</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>https://x.com/MarketNews_Feed/status/2047530582981165068</t>
+          <t>https://x.com/emiratesislamic/status/2047632125583605871</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>RBC LIFTS PRICE TARGET ON UNION PACIFIC TO $289 VERSUS $273 EARLIER ...</t>
+          <t>💰 معدلات ربح تنافسية على تمويل السيارات والتمويل السكني
+🎁 مكافأة 100 درهم مع حساب ALPHA للأبناء
+وغير ذلك الكثير.
+يسري العرض لغاية 31 مايو 2026.
+تطبق الشروط والأحكام.
+https://t.co/909hzRsLZr https://t.co/Ff41FuCAen</t>
         </is>
       </c>
       <c r="G94" t="n">
-        <v>1777004306000</v>
+        <v>1777028516000</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2047530582981165068</t>
+          <t>2047632116649689120</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGqmkG7WcAEveRR.jpg', 'type': 'photo', 'id': '2047632119858360321'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGqmkUZWQAEKDDE.jpg', 'type': 'photo', 'id': '2047632123473838081'}]</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>{'name': 'MarketNewsFeed', 'screenName': 'MarketNews_Feed', 'followersCount': 6505, 'favouritesCount': 691, 'friendsCount': 4, 'description': 'The number 1 ranked news aggregator voted unanimously  (by me). All financial and tech headlines in one place. Sources are cited in TG - @MarketFeed'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18451, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="K94" t="n">
@@ -6857,10 +6984,14 @@
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="P94" t="inlineStr"/>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>2047632116649689120</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
@@ -6868,49 +6999,51 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047289060557824183</t>
+          <t>https://x.com/emiratesislamic/status/2047632116649689120</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2047289060557824183</t>
+          <t>2047632116649689120</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2047289060557824183</t>
+          <t>2047717917324710124</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047289060557824183</t>
+          <t>https://x.com/emiratesislamic/status/2047717917324710124</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>البدء مبكرًا والاستمرار بثبات يساعدان على نمو أموالك مع الوقت. خطوات بسيطة اليوم قد تساهم في بناء مستقبل مالي أكثر استقرارًا وثقة. https://t.co/aGfu3GLgq9</t>
+          <t>🇦🇪 تحية تقدير وامتنان لأبطال الوطن
+تقديراً لإخلاصك وتفانيك في خدمة الوطن، قمنا بتصميم باقة حصرية من المزايا المصرفية لنمنحك راحة البال.
+📈 معدلات أرباح مميزة على التمويل https://t.co/DrYnMIk6Zd</t>
         </is>
       </c>
       <c r="G95" t="n">
-        <v>1776946723000</v>
+        <v>1777048970000</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2047289060557824183</t>
+          <t>2047717917324710124</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/ext_tw_video_thumb/2047288959890284544/pu/img/4RhwHt3nX1yIPtrZ.jpg', 'type': 'video', 'id': '2047288959890284544'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGr0l1oXYAEHNu8.jpg', 'type': 'photo', 'id': '2047717911482032129'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGr0mAsWkAIOAAv.jpg', 'type': 'photo', 'id': '2047717914451546114'}]</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18449, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18451, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="K95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L95" t="n">
         <v>0</v>
@@ -6923,7 +7056,7 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>37</t>
         </is>
       </c>
       <c r="P95" t="inlineStr"/>
@@ -6934,50 +7067,52 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047289060557824183</t>
+          <t>https://x.com/emiratesislamic/status/2047631639946093018</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2047289060557824183</t>
+          <t>2047631639946093018</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2047287763796427063</t>
+          <t>2047631639946093018</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047287763796427063</t>
+          <t>https://x.com/emiratesislamic/status/2047631639946093018</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Starting early and staying consistent can help your money grow over time. Small steps today can support a more secure and confident financial future.
-#Finwell #FinancialWellbeing #EmiratesIslamic #Investing https://t.co/7rh6hiRrKq</t>
+          <t>احصل على iPhone 17 مضمون عند التقدم بطلب تمويل شخصي من الإمارات الإسلامي.
+استمتع أيضاً بالمزايا الحصرية:
+📊 معدلات ربح تبدأ من %2.59 ثابتة سنوياً (ما يعادل تقريباً %4.74 كمعدل متناقص سنوياً).
+🏦 مبلغ تمويلي يصل إلى 4,000,000 درهم https://t.co/eMEYGVmxwY</t>
         </is>
       </c>
       <c r="G96" t="n">
-        <v>1776946414000</v>
+        <v>1777028400000</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2047287763796427063</t>
+          <t>2047631639946093018</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/ext_tw_video_thumb/2047287721278783488/pu/img/1XDZTp3BhshZyriP.jpg', 'type': 'video', 'id': '2047287721278783488'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGp1V6aW8AAL6dm.jpg', 'type': 'photo', 'id': '2047577999910825984'}]</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18449, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18451, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="K96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L96" t="n">
         <v>0</v>
@@ -6990,7 +7125,7 @@
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>44</t>
         </is>
       </c>
       <c r="P96" t="inlineStr"/>
@@ -7001,69 +7136,73 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>https://x.com/IshwarT74378521/status/2047120928795247018</t>
+          <t>https://x.com/emiratesislamic/status/2047631639946093018</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2047120928795247018</t>
+          <t>2047631639946093018</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2023349339113107783</t>
+          <t>2047631643926483032</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>https://x.com/IdbiFor/status/2023349339113107783</t>
+          <t>https://x.com/emiratesislamic/status/2047631643926483032</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Representatives of All India IDBI Bank Officers met  Mr. @BaburaoGolla MP Rajya Sabha, @YSR Congress Party from #AndhraPradesh .
-Honouable MP informed that he will take up the issue of IDBI Privatisation immediately and raise this issue in parliament. 
-#SaveIDBI
-#StopPrivatisation
-@Oaktree @RBI @supriya_sule @RajeevRai</t>
+          <t>✈️ تأجيل القسط الأول لمدة تصل إلى 6 شهور
+🔒 تغطية تكافلية
+يسري العرض لغاية 30 أبريل 2026.
+تطبق الشروط والأحكام.
+https://t.co/WVHANHvCwT</t>
         </is>
       </c>
       <c r="G97" t="n">
-        <v>1771239049000</v>
+        <v>1777028401000</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2023349339113107783</t>
+          <t>2047631639946093018</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HBRhgDcacAATOmz.jpg', 'type': 'photo', 'id': '2023349335904382976'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>{'name': 'Together for IDBI', 'screenName': 'IdbiFor', 'followersCount': 2379, 'favouritesCount': 7619, 'friendsCount': 157, 'description': 'An awareness initiative run by United Forum of IDBI Officers and Employees.\n\nWe oppose privatization. \n\n#StopPrivatization'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18451, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="K97" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="L97" t="n">
         <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>1921</t>
-        </is>
-      </c>
-      <c r="P97" t="inlineStr"/>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>2047631639946093018</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
@@ -7071,45 +7210,47 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>https://x.com/IshwarT74378521/status/2047120928795247018</t>
+          <t>https://x.com/emiratesislamic/status/2047631639946093018</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2047120928795247018</t>
+          <t>2047631639946093018</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2023696356918149472</t>
+          <t>2047717917324710124</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>https://x.com/IshwarT74378521/status/2023696356918149472</t>
+          <t>https://x.com/emiratesislamic/status/2047717917324710124</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>@IdbiFor @BaburaoGolla @RahulGandhi @PawanKalyan @GauravGogoiAsm @FFH_TO @EmiratesNBD_AE @FinMinIndia @DFS_India @SecyDIPAM @bsindia @INCIndia Save IDBI</t>
+          <t>🇦🇪 تحية تقدير وامتنان لأبطال الوطن
+تقديراً لإخلاصك وتفانيك في خدمة الوطن، قمنا بتصميم باقة حصرية من المزايا المصرفية لنمنحك راحة البال.
+📈 معدلات أرباح مميزة على التمويل https://t.co/DrYnMIk6Zd</t>
         </is>
       </c>
       <c r="G98" t="n">
-        <v>1771321784000</v>
+        <v>1777048970000</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2023349339113107783</t>
+          <t>2047717917324710124</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGr0l1oXYAEHNu8.jpg', 'type': 'photo', 'id': '2047717911482032129'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGr0mAsWkAIOAAv.jpg', 'type': 'photo', 'id': '2047717914451546114'}]</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>{'name': 'IshwarTiwari', 'screenName': 'IshwarT74378521', 'followersCount': 1, 'favouritesCount': 110, 'friendsCount': 68, 'description': ''}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18451, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="K98" t="n">
@@ -7119,21 +7260,17 @@
         <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="P98" t="inlineStr">
-        <is>
-          <t>2023349339113107783</t>
-        </is>
-      </c>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
@@ -7141,35 +7278,38 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>https://x.com/IshwarT74378521/status/2047120928795247018</t>
+          <t>https://x.com/emiratesislamic/status/2047556140511162463</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2047120928795247018</t>
+          <t>2047556140511162463</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2047120928795247018</t>
+          <t>2047556140511162463</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>https://x.com/IshwarT74378521/status/2047120928795247018</t>
+          <t>https://x.com/emiratesislamic/status/2047556140511162463</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>@IdbiFor @BaburaoGolla @RahulGandhi @PawanKalyan @GauravGogoiAsm @FFH_TO @EmiratesNBD_AE @FinMinIndia @DFS_India @SecyDIPAM @bsindia @INCIndia Save IDBI</t>
+          <t>عليك غرامة لم تُسدّد بعد – اضغط هنا
+لا تقع في الفخ. احذر الاحتيال.
+#متحّدون_ضد_الاحتيال مع الإمارات الإسلامي.
+https://t.co/ltnxcRlBOA</t>
         </is>
       </c>
       <c r="G99" t="n">
-        <v>1776906637000</v>
+        <v>1777010400000</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2023349339113107783</t>
+          <t>2047556140511162463</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -7179,7 +7319,7 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>{'name': 'IshwarTiwari', 'screenName': 'IshwarT74378521', 'followersCount': 1, 'favouritesCount': 110, 'friendsCount': 68, 'description': ''}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18451, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="K99" t="n">
@@ -7196,14 +7336,10 @@
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="P99" t="inlineStr">
-        <is>
-          <t>2023696356918149472</t>
-        </is>
-      </c>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
@@ -7211,45 +7347,48 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047249946475160040</t>
+          <t>https://x.com/emiratesislamic/status/2047556140511162463</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2047249946475160040</t>
+          <t>2047556140511162463</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2047249881757085701</t>
+          <t>2047717988195852322</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047249881757085701</t>
+          <t>https://x.com/emiratesislamic/status/2047717988195852322</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>تعكس النتائج المالية للإمارات الإسلامي للربع الأول من عام 2026 مرونة القطاع المالي في الدولة وجاهزيته لمواكبة المتغيرات والتحديات الراهنة. https://t.co/0CC4kCWK5A</t>
+          <t>🇦🇪 We salute the nation’s heroes 
+We value your commitment and have designed exclusive banking benefits for your peace of mind.
+📈 Attractive finance profit rates
+🏦 Zero processing fees https://t.co/Q8zlLDLLW1</t>
         </is>
       </c>
       <c r="G100" t="n">
-        <v>1776937382000</v>
+        <v>1777048987000</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2047249881757085701</t>
+          <t>2047717988195852322</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/ext_tw_video_thumb/2047249829034606592/pu/img/L09wsSrWqyKvM73G.jpg', 'type': 'video', 'id': '2047249829034606592'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGr0p_HW8AA45jd.jpg', 'type': 'photo', 'id': '2047717982747422720'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGr0qJzWcAAnD8P.jpg', 'type': 'photo', 'id': '2047717985616293888'}]</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18449, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18451, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="K100" t="n">
@@ -7262,11 +7401,11 @@
         <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>44</t>
         </is>
       </c>
       <c r="P100" t="inlineStr"/>
@@ -7277,46 +7416,48 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047249946475160040</t>
+          <t>https://x.com/emiratesislamic/status/2047631643901390924</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2047249946475160040</t>
+          <t>2047631643901390924</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2047249884101673033</t>
+          <t>2047631640168374617</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047249884101673033</t>
+          <t>https://x.com/emiratesislamic/status/2047631640168374617</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>وقد ارتفع الربح التشغيلي بنسبة %7 على أساس سنوي ليصل إلى 1.1 مليار درهم إماراتي، كما نما إجمالي الدخل بنسبة %6 على أساس سنوي.
-https://t.co/gvo0477mob</t>
+          <t>Get a guaranteed iPhone 17 when you apply for an Emirates Islamic Personal Finance.
+Also, enjoy exclusive benefits:
+📊 Profit rates starting from 2.59% flat p.a.(approximately equivalent to 4.74% p.a. reducing profit rate)
+🏦 Finance amount of up to AED 4,000,000 https://t.co/QSbM2ZKbuH</t>
         </is>
       </c>
       <c r="G101" t="n">
-        <v>1776937383000</v>
+        <v>1777028400000</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2047249881757085701</t>
+          <t>2047631640168374617</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGp7wFoXwAAtDsB.jpg', 'type': 'photo', 'id': '2047585046668754944'}]</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18449, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18451, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="K101" t="n">
@@ -7333,14 +7474,10 @@
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="P101" t="inlineStr">
-        <is>
-          <t>2047249881757085701</t>
-        </is>
-      </c>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
@@ -7348,46 +7485,49 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047249946475160040</t>
+          <t>https://x.com/emiratesislamic/status/2047631643901390924</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2047249946475160040</t>
+          <t>2047631643901390924</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2047249946475160040</t>
+          <t>2047631643901390924</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047249946475160040</t>
+          <t>https://x.com/emiratesislamic/status/2047631643901390924</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Emirates Islamic’s financial results for the first quarter of 2026 reflect the nation’s financial resilience and preparedness through the current environment. Operating Profit was up by 7% y-o-y to AED 1.1 billion and total income grew 6% y-o-y.
-https://t.co/s9M3UfTGFW https://t.co/DymCZHgrV1</t>
+          <t>✈️Payment holiday up to 6 months 
+🔒 Complimentary Takaful coverage
+Offer valid until 30 April 2026.
+T&amp;amp;Cs apply.
+https://t.co/ZafvBWp0Cl</t>
         </is>
       </c>
       <c r="G102" t="n">
-        <v>1776937397000</v>
+        <v>1777028401000</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2047249881757085701</t>
+          <t>2047631640168374617</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/ext_tw_video_thumb/2047249892804857856/pu/img/DlhEWBM_8yLjhOal.jpg', 'type': 'video', 'id': '2047249892804857856'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18449, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18451, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="K102" t="n">
@@ -7404,12 +7544,12 @@
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>19</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>2047249884101673033</t>
+          <t>2047631640168374617</t>
         </is>
       </c>
     </row>
@@ -7419,50 +7559,51 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047287763796427063</t>
+          <t>https://x.com/emiratesislamic/status/2047541045768962304</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2047287763796427063</t>
+          <t>2047541045768962304</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2047287763796427063</t>
+          <t>2047541041612427486</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047287763796427063</t>
+          <t>https://x.com/emiratesislamic/status/2047541041612427486</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Starting early and staying consistent can help your money grow over time. Small steps today can support a more secure and confident financial future.
-#Finwell #FinancialWellbeing #EmiratesIslamic #Investing https://t.co/7rh6hiRrKq</t>
+          <t>معًا، نُعلي راية الفخر احتفاءً بالإمارات وقيمها الراسخة 🇦🇪
+من قلب فروعنا، اجتمع الموظفون والعملاء في أجواء وطنية جسّدت روح الانتماء والوحدة، وعكست مشاعر الفخر بالوطن.
+#فخورين_بالإمارات https://t.co/b3HOjAP5Rw</t>
         </is>
       </c>
       <c r="G103" t="n">
-        <v>1776946414000</v>
+        <v>1777006800000</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2047287763796427063</t>
+          <t>2047541041612427486</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/ext_tw_video_thumb/2047287721278783488/pu/img/1XDZTp3BhshZyriP.jpg', 'type': 'video', 'id': '2047287721278783488'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/ext_tw_video_thumb/2047358056963473408/pu/img/J1OcKdI5JfoHlVrB.jpg', 'type': 'video', 'id': '2047358056963473408'}]</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18449, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18451, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="K103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L103" t="n">
         <v>0</v>
@@ -7471,11 +7612,11 @@
         <v>0</v>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>209</t>
         </is>
       </c>
       <c r="P103" t="inlineStr"/>
@@ -7486,45 +7627,47 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047287763796427063</t>
+          <t>https://x.com/emiratesislamic/status/2047541045768962304</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2047287763796427063</t>
+          <t>2047541045768962304</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2047289060557824183</t>
+          <t>2047541045768962304</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047289060557824183</t>
+          <t>https://x.com/emiratesislamic/status/2047541045768962304</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>البدء مبكرًا والاستمرار بثبات يساعدان على نمو أموالك مع الوقت. خطوات بسيطة اليوم قد تساهم في بناء مستقبل مالي أكثر استقرارًا وثقة. https://t.co/aGfu3GLgq9</t>
+          <t>Together, we raise the flag with pride, celebrating the UAE and its enduring values 🇦🇪
+Across our branches, staff and customers came together in a patriotic atmosphere that embodied unity, belonging, and a deep sense of pride in the nation.
+#ProudOfUAE</t>
         </is>
       </c>
       <c r="G104" t="n">
-        <v>1776946723000</v>
+        <v>1777006801000</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2047289060557824183</t>
+          <t>2047541041612427486</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/ext_tw_video_thumb/2047288959890284544/pu/img/4RhwHt3nX1yIPtrZ.jpg', 'type': 'video', 'id': '2047288959890284544'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18449, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18451, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="K104" t="n">
@@ -7541,10 +7684,14 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="P104" t="inlineStr"/>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>2047541041612427486</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
@@ -7552,46 +7699,47 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047241499490807897</t>
+          <t>https://x.com/emiratesislamic/status/2047541041612427486</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2047241499490807897</t>
+          <t>2047541041612427486</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2046584718758707650</t>
+          <t>2047541041612427486</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>https://x.com/UpendraS83806/status/2046584718758707650</t>
+          <t>https://x.com/emiratesislamic/status/2047541041612427486</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>@emiratesislamic My client transferred payment from your bank but still not credited into my account.
-Please advise.</t>
+          <t>معًا، نُعلي راية الفخر احتفاءً بالإمارات وقيمها الراسخة 🇦🇪
+من قلب فروعنا، اجتمع الموظفون والعملاء في أجواء وطنية جسّدت روح الانتماء والوحدة، وعكست مشاعر الفخر بالوطن.
+#فخورين_بالإمارات https://t.co/b3HOjAP5Rw</t>
         </is>
       </c>
       <c r="G105" t="n">
-        <v>1776778795000</v>
+        <v>1777006800000</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2046584718758707650</t>
+          <t>2047541041612427486</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/ext_tw_video_thumb/2047358056963473408/pu/img/J1OcKdI5JfoHlVrB.jpg', 'type': 'video', 'id': '2047358056963473408'}]</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>{'name': 'Upendra Singh', 'screenName': 'UpendraS83806', 'followersCount': 1, 'favouritesCount': 0, 'friendsCount': 13, 'description': ''}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18451, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="K105" t="n">
@@ -7604,11 +7752,11 @@
         <v>0</v>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>209</t>
         </is>
       </c>
       <c r="P105" t="inlineStr"/>
@@ -7619,35 +7767,37 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047241499490807897</t>
+          <t>https://x.com/emiratesislamic/status/2047541041612427486</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2047241499490807897</t>
+          <t>2047541041612427486</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2046878598796112328</t>
+          <t>2047541045768962304</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2046878598796112328</t>
+          <t>https://x.com/emiratesislamic/status/2047541045768962304</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>@UpendraS83806 Dear Customer, Thanks for getting in touch. Your privacy is important to us, and to ensure your confidentiality, we've sent you a message requesting further details. Please check your direct messages at your earliest convenience.</t>
+          <t>Together, we raise the flag with pride, celebrating the UAE and its enduring values 🇦🇪
+Across our branches, staff and customers came together in a patriotic atmosphere that embodied unity, belonging, and a deep sense of pride in the nation.
+#ProudOfUAE</t>
         </is>
       </c>
       <c r="G106" t="n">
-        <v>1776848861000</v>
+        <v>1777006801000</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2046584718758707650</t>
+          <t>2047541041612427486</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -7657,11 +7807,11 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18449, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18451, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="K106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L106" t="n">
         <v>0</v>
@@ -7674,12 +7824,12 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>49</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>2046584718758707650</t>
+          <t>2047541041612427486</t>
         </is>
       </c>
     </row>
@@ -7689,45 +7839,48 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047241499490807897</t>
+          <t>https://x.com/emiratesislamic/status/2047541041612427486</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2047241499490807897</t>
+          <t>